--- a/latest.xlsx
+++ b/latest.xlsx
@@ -3489,24 +3489,20 @@
       <c r="H19" s="7" t="n">
         <v>11000</v>
       </c>
-      <c r="I19" s="119">
-        <f>IFERROR(VLOOKUP(B19,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I19" s="119" t="n">
+        <v>1482.8</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>16310800</v>
       </c>
-      <c r="K19" s="9">
-        <f>IFERROR(ROUND(H19*I19,0),0)</f>
-        <v/>
-      </c>
-      <c r="L19" s="9">
-        <f>IFERROR(VLOOKUP(B19,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="9">
-        <f>IFERROR(VLOOKUP(B19,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+      <c r="K19" s="9" t="n">
+        <v>16310800</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>462</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>296</v>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
@@ -3560,16 +3556,14 @@
         <f>S19+T19+W19</f>
         <v/>
       </c>
-      <c r="AA19" s="10">
-        <f>K19+L19+M19+IFERROR(VLOOKUP(B19,RemitTable2,9,FALSE()),0)+Y19+Z19</f>
-        <v/>
+      <c r="AA19" s="10" t="n">
+        <v>20915590</v>
       </c>
       <c r="AB19" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="AC19" s="10">
-        <f>ROUND(AA19/AB19,0)</f>
-        <v/>
+      <c r="AC19" s="10" t="n">
+        <v>10457795</v>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
@@ -3620,24 +3614,20 @@
       <c r="H20" s="7" t="n">
         <v>286580</v>
       </c>
-      <c r="I20" s="119">
-        <f>IFERROR(VLOOKUP(B20,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I20" s="119" t="n">
+        <v>1482.8</v>
       </c>
       <c r="J20" s="9" t="n">
         <v>424990980</v>
       </c>
-      <c r="K20" s="9">
-        <f>IFERROR(ROUND(H20*I20,0),0)</f>
-        <v/>
-      </c>
-      <c r="L20" s="9">
-        <f>IFERROR(VLOOKUP(B20,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="9">
-        <f>IFERROR(VLOOKUP(B20,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+      <c r="K20" s="9" t="n">
+        <v>424990980</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>12038</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>7704</v>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
@@ -3691,16 +3681,14 @@
         <f>S20+T20+W20</f>
         <v/>
       </c>
-      <c r="AA20" s="10">
-        <f>K20+L20+M20+IFERROR(VLOOKUP(B20,RemitTable2,9,FALSE()),0)+Y20+Z20</f>
-        <v/>
+      <c r="AA20" s="10" t="n">
+        <v>473718807</v>
       </c>
       <c r="AB20" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="AC20" s="10">
-        <f>ROUND(AA20/AB20,0)</f>
-        <v/>
+      <c r="AC20" s="10" t="n">
+        <v>16918529</v>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
@@ -5031,24 +5019,20 @@
       <c r="H31" s="125" t="n">
         <v>4388.4</v>
       </c>
-      <c r="I31" s="126">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I31" s="126" t="n">
+        <v>1741.08</v>
       </c>
       <c r="J31" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="127">
-        <f>IFERROR(ROUND(H31*I31,0),0)</f>
-        <v/>
-      </c>
-      <c r="L31" s="127">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M31" s="127">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>7702082</v>
+      </c>
+      <c r="K31" s="127" t="n">
+        <v>7702082</v>
+      </c>
+      <c r="L31" s="127" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M31" s="127" t="n">
+        <v>8000</v>
       </c>
       <c r="N31" s="123" t="inlineStr">
         <is>
@@ -5100,16 +5084,14 @@
         <f>S31+T31+W31</f>
         <v/>
       </c>
-      <c r="AA31" s="128">
-        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
-        <v/>
+      <c r="AA31" s="128" t="n">
+        <v>7763609</v>
       </c>
       <c r="AB31" s="129" t="n">
         <v>60</v>
       </c>
-      <c r="AC31" s="128">
-        <f>ROUND(AA31/AB31,0)</f>
-        <v/>
+      <c r="AC31" s="128" t="n">
+        <v>129393</v>
       </c>
       <c r="AD31" s="123" t="inlineStr">
         <is>
@@ -10535,7 +10517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="107" min="1" max="1"/>
@@ -13770,19 +13752,9 @@
         <v>7763609</v>
       </c>
     </row>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
     <row r="76">
       <c r="M76" s="56" t="n"/>
     </row>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A33:L33"/>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -32,6 +32,7 @@
     <numFmt numFmtId="168" formatCode="0&quot;일&quot;"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="170" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="171" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -406,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -927,6 +928,39 @@
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8435,7 +8469,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="21" t="n">
         <v>1</v>
       </c>
@@ -8462,25 +8496,17 @@
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
-        <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="I3" s="21" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
+      <c r="G3" s="190" t="n">
+        <v>45925</v>
+      </c>
+      <c r="H3" s="190" t="n">
+        <v>46080</v>
+      </c>
+      <c r="I3" s="190" t="n">
+        <v>45913</v>
+      </c>
+      <c r="J3" s="190" t="n">
+        <v>46262</v>
       </c>
       <c r="K3" s="21" t="inlineStr">
         <is>
@@ -8488,7 +8514,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="21" t="n">
         <v>2</v>
       </c>
@@ -8515,25 +8541,17 @@
           <t>HFR License</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="I4" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
+      <c r="G4" s="190" t="n">
+        <v>45982</v>
+      </c>
+      <c r="H4" s="190" t="n">
+        <v>46014</v>
+      </c>
+      <c r="I4" s="190" t="n">
+        <v>45992</v>
+      </c>
+      <c r="J4" s="190" t="n">
+        <v>46356</v>
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
@@ -8541,7 +8559,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" s="21" t="n">
         <v>3</v>
       </c>
@@ -8568,25 +8586,17 @@
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-21</t>
-        </is>
+      <c r="G5" s="190" t="n">
+        <v>45993</v>
+      </c>
+      <c r="H5" s="190" t="n">
+        <v>46064</v>
+      </c>
+      <c r="I5" s="190" t="n">
+        <v>46013</v>
+      </c>
+      <c r="J5" s="190" t="n">
+        <v>46377</v>
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
@@ -8594,7 +8604,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" s="21" t="n">
         <v>4</v>
       </c>
@@ -8621,25 +8631,17 @@
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G6" s="190" t="n">
+        <v>46007</v>
+      </c>
+      <c r="H6" s="190" t="n">
+        <v>46043</v>
+      </c>
+      <c r="I6" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J6" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K6" s="21" t="inlineStr">
         <is>
@@ -8647,7 +8649,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="21" t="n">
         <v>5</v>
       </c>
@@ -8674,25 +8676,17 @@
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
+      <c r="G7" s="190" t="n">
+        <v>46007</v>
+      </c>
+      <c r="H7" s="190" t="n">
+        <v>46043</v>
+      </c>
+      <c r="I7" s="190" t="n">
+        <v>45962</v>
+      </c>
+      <c r="J7" s="190" t="n">
+        <v>46325</v>
       </c>
       <c r="K7" s="21" t="inlineStr">
         <is>
@@ -8700,7 +8694,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" s="21" t="n">
         <v>6</v>
       </c>
@@ -8727,25 +8721,17 @@
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G8" s="190" t="n">
+        <v>46010</v>
+      </c>
+      <c r="H8" s="190" t="n">
+        <v>46080</v>
+      </c>
+      <c r="I8" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J8" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K8" s="21" t="inlineStr">
         <is>
@@ -8753,7 +8739,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" s="21" t="n">
         <v>7</v>
       </c>
@@ -8780,25 +8766,19 @@
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
+      <c r="G9" s="190" t="n">
+        <v>46015</v>
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="I9" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J9" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K9" s="21" t="inlineStr">
         <is>
@@ -8806,7 +8786,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" s="21" t="n">
         <v>8</v>
       </c>
@@ -8833,25 +8813,17 @@
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t>2027-01-29</t>
-        </is>
+      <c r="G10" s="190" t="n">
+        <v>46029</v>
+      </c>
+      <c r="H10" s="190" t="n">
+        <v>46072</v>
+      </c>
+      <c r="I10" s="190" t="n">
+        <v>46052</v>
+      </c>
+      <c r="J10" s="190" t="n">
+        <v>46416</v>
       </c>
       <c r="K10" s="21" t="inlineStr">
         <is>
@@ -8859,7 +8831,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" s="21" t="n">
         <v>9</v>
       </c>
@@ -8886,10 +8858,8 @@
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
+      <c r="G11" s="190" t="n">
+        <v>46029</v>
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
@@ -8912,7 +8882,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" s="21" t="n">
         <v>10</v>
       </c>
@@ -8939,25 +8909,17 @@
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G12" s="190" t="n">
+        <v>46042</v>
+      </c>
+      <c r="H12" s="190" t="n">
+        <v>46057</v>
+      </c>
+      <c r="I12" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J12" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K12" s="21" t="inlineStr">
         <is>
@@ -8965,7 +8927,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" s="21" t="n">
         <v>11</v>
       </c>
@@ -8992,25 +8954,17 @@
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G13" s="190" t="n">
+        <v>46042</v>
+      </c>
+      <c r="H13" s="190" t="n">
+        <v>46057</v>
+      </c>
+      <c r="I13" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J13" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K13" s="21" t="inlineStr">
         <is>
@@ -9018,7 +8972,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="21" t="n">
         <v>12</v>
       </c>
@@ -9045,25 +8999,17 @@
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="G14" s="190" t="n">
+        <v>46042</v>
+      </c>
+      <c r="H14" s="190" t="n">
+        <v>46057</v>
+      </c>
+      <c r="I14" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J14" s="190" t="n">
+        <v>46387</v>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>
@@ -9071,7 +9017,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="16" customHeight="1">
       <c r="A15" s="21" t="n">
         <v>13</v>
       </c>
@@ -9098,25 +9044,17 @@
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="J15" s="95" t="inlineStr">
-        <is>
-          <t>2027-02-28</t>
-        </is>
+      <c r="G15" s="190" t="n">
+        <v>46057</v>
+      </c>
+      <c r="H15" s="190" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I15" s="190" t="n">
+        <v>46082</v>
+      </c>
+      <c r="J15" s="191" t="n">
+        <v>46446</v>
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
@@ -9124,7 +9062,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="16" customHeight="1">
       <c r="A16" s="21" t="n">
         <v>14</v>
       </c>
@@ -9151,25 +9089,17 @@
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="J16" s="95" t="inlineStr">
-        <is>
-          <t>2027-02-22</t>
-        </is>
+      <c r="G16" s="190" t="n">
+        <v>46060</v>
+      </c>
+      <c r="H16" s="190" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I16" s="190" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J16" s="191" t="n">
+        <v>46440</v>
       </c>
       <c r="K16" s="21" t="inlineStr">
         <is>
@@ -9177,7 +9107,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="16" customHeight="1">
       <c r="A17" s="21" t="n">
         <v>15</v>
       </c>
@@ -9204,25 +9134,17 @@
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="J17" s="95" t="inlineStr">
-        <is>
-          <t>2027-02-28</t>
-        </is>
+      <c r="G17" s="190" t="n">
+        <v>46080</v>
+      </c>
+      <c r="H17" s="190" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I17" s="190" t="n">
+        <v>46082</v>
+      </c>
+      <c r="J17" s="191" t="n">
+        <v>46446</v>
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
@@ -9230,60 +9152,56 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="39" t="n">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="95" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="95" t="inlineStr">
         <is>
           <t>GPO471</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="C18" s="181" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D18" s="92" t="inlineStr">
+      <c r="D18" s="181" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="E18" s="94" t="n">
+      <c r="E18" s="182" t="n">
         <v>500</v>
       </c>
-      <c r="F18" s="39" t="inlineStr">
+      <c r="F18" s="95" t="inlineStr">
         <is>
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="G18" s="39" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="H18" s="39" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="I18" s="39" t="inlineStr">
+      <c r="G18" s="191" t="n">
+        <v>46088</v>
+      </c>
+      <c r="H18" s="191" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I18" s="95" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
       </c>
-      <c r="J18" s="96" t="inlineStr">
+      <c r="J18" s="95" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
       </c>
-      <c r="K18" s="21" t="inlineStr">
+      <c r="K18" s="95" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="16" customHeight="1">
       <c r="A19" s="21" t="n">
         <v>17</v>
       </c>
@@ -9310,25 +9228,19 @@
           <t>EW (CGV 동백 외 Warranty Extension)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
+      <c r="G19" s="190" t="n">
+        <v>46109</v>
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="J19" s="95" t="inlineStr">
-        <is>
-          <t>2027-03-31</t>
-        </is>
+      <c r="I19" s="190" t="n">
+        <v>46113</v>
+      </c>
+      <c r="J19" s="191" t="n">
+        <v>46477</v>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
@@ -9336,95 +9248,95 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="150" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="150" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="183" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="183" t="inlineStr">
         <is>
           <t>CPO697</t>
         </is>
       </c>
-      <c r="C20" s="151" t="inlineStr">
+      <c r="C20" s="184" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D20" s="151" t="inlineStr">
+      <c r="D20" s="184" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="E20" s="152" t="n">
+      <c r="E20" s="185" t="n">
         <v>15289</v>
       </c>
-      <c r="F20" s="150" t="inlineStr">
+      <c r="F20" s="183" t="inlineStr">
         <is>
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대</t>
         </is>
       </c>
-      <c r="G20" s="153" t="n">
+      <c r="G20" s="186" t="n">
         <v>46136</v>
       </c>
-      <c r="H20" s="150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="153" t="n">
+      <c r="H20" s="186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="186" t="n">
         <v>46168</v>
       </c>
-      <c r="J20" s="153" t="n">
+      <c r="J20" s="186" t="n">
         <v>46532</v>
       </c>
-      <c r="K20" s="150" t="inlineStr">
+      <c r="K20" s="183" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="150" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="150" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="183" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="183" t="inlineStr">
         <is>
           <t>CPO693-2</t>
         </is>
       </c>
-      <c r="C21" s="151" t="inlineStr">
+      <c r="C21" s="184" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D21" s="151" t="inlineStr">
+      <c r="D21" s="184" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="E21" s="152" t="n">
+      <c r="E21" s="185" t="n">
         <v>2550</v>
       </c>
-      <c r="F21" s="150" t="inlineStr">
+      <c r="F21" s="183" t="inlineStr">
         <is>
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="G21" s="153" t="n">
+      <c r="G21" s="186" t="n">
         <v>46133</v>
       </c>
-      <c r="H21" s="150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="153" t="n">
+      <c r="H21" s="186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="186" t="n">
         <v>46142</v>
       </c>
-      <c r="J21" s="153" t="n">
+      <c r="J21" s="186" t="n">
         <v>46872</v>
       </c>
-      <c r="K21" s="150" t="inlineStr">
+      <c r="K21" s="183" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
@@ -10614,185 +10526,185 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="39" t="n">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>2025.12.01</t>
         </is>
       </c>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D3" s="39" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>CPO668-3, CPO673</t>
         </is>
       </c>
-      <c r="E3" s="40" t="n">
+      <c r="E3" s="44" t="n">
         <v>35563</v>
       </c>
-      <c r="F3" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="39" t="n">
+      <c r="F3" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H3" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="42">
+      <c r="H3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9">
         <f>ROUND((E3+G3)*F3+H3+I3,0)</f>
         <v/>
       </c>
-      <c r="L3" s="43">
+      <c r="L3" s="46">
         <f>J3-K3</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="39" t="n">
+      <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>2025.12.02</t>
         </is>
       </c>
-      <c r="C4" s="92" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>GPO-445, 446-1, 447, 448</t>
         </is>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="44" t="n">
         <v>55830</v>
       </c>
-      <c r="F4" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="39" t="n">
+      <c r="F4" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H4" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="42">
+      <c r="H4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
         <f>ROUND((E4+G4)*F4+H4+I4,0)</f>
         <v/>
       </c>
-      <c r="L4" s="43">
+      <c r="L4" s="46">
         <f>J4-K4</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="39" t="n">
+      <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>2025.12.02</t>
         </is>
       </c>
-      <c r="C5" s="92" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Thali Consulting</t>
         </is>
       </c>
-      <c r="D5" s="39" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>(PO미기재)</t>
         </is>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="44" t="n">
         <v>9247.690000000001</v>
       </c>
-      <c r="F5" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="39" t="n">
+      <c r="F5" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H5" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="42">
+      <c r="H5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
         <f>ROUND((E5+G5)*F5+H5+I5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="46">
         <f>J5-K5</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="39" t="n">
+      <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>2025.12.02</t>
         </is>
       </c>
-      <c r="C6" s="92" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D6" s="39" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>CPO-669</t>
         </is>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="44" t="n">
         <v>7410</v>
       </c>
-      <c r="F6" s="161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="39" t="n">
+      <c r="F6" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="42">
+      <c r="H6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
         <f>ROUND((E6+G6)*F6+H6+I6,0)</f>
         <v/>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="46">
         <f>J6-K6</f>
         <v/>
       </c>
@@ -10982,47 +10894,47 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>2025.12.19</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>GDC(라이센스)</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>/ROC/라이센스</t>
         </is>
       </c>
-      <c r="E11" s="47" t="n">
+      <c r="E11" s="44" t="n">
         <v>1200</v>
       </c>
-      <c r="F11" s="163" t="n">
+      <c r="F11" s="162" t="n">
         <v>1464.9</v>
       </c>
-      <c r="G11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="19">
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
         <f>ROUND((E11+G11)*F11+H11+I11,0)</f>
         <v/>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="46">
         <f>J11-K11</f>
         <v/>
       </c>
@@ -11718,277 +11630,277 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="13" t="n">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>2026.04.14</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>GPO468-1, 472, 468-2</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="n">
+        <v>57650</v>
+      </c>
+      <c r="F27" s="162" t="n">
+        <v>1481.9</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>85481673</v>
+      </c>
+      <c r="K27" s="9">
+        <f>ROUND((E27+G27)*F27+H27+I27,0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="46">
+        <f>J27-K27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="171" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>2026.04.14</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>GPO468-1, 472, 468-2</t>
-        </is>
-      </c>
-      <c r="E27" s="47" t="n">
-        <v>57650</v>
-      </c>
-      <c r="F27" s="163" t="n">
-        <v>1481.9</v>
-      </c>
-      <c r="G27" s="13" t="n">
+      <c r="B28" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C28" s="172" t="inlineStr">
+        <is>
+          <t>Swank</t>
+        </is>
+      </c>
+      <c r="D28" s="171" t="inlineStr">
+        <is>
+          <t>(영화 라이센스)</t>
+        </is>
+      </c>
+      <c r="E28" s="173" t="n">
+        <v>814</v>
+      </c>
+      <c r="F28" s="187" t="n">
+        <v>1505</v>
+      </c>
+      <c r="G28" s="171" t="n">
         <v>20</v>
       </c>
-      <c r="H27" s="19" t="n">
+      <c r="H28" s="176" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I28" s="176" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J28" s="176" t="n">
+        <v>1268170</v>
+      </c>
+      <c r="K28" s="176">
+        <f>ROUND((E28+G28)*F28+H28+I28,0)</f>
+        <v/>
+      </c>
+      <c r="L28" s="177">
+        <f>J28-K28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="27.75" customHeight="1">
+      <c r="A29" s="171" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.02</t>
+        </is>
+      </c>
+      <c r="C29" s="172" t="inlineStr">
+        <is>
+          <t>Monoplex</t>
+        </is>
+      </c>
+      <c r="D29" s="171" t="inlineStr">
+        <is>
+          <t>(영업)</t>
+        </is>
+      </c>
+      <c r="E29" s="173" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F29" s="187" t="n">
+        <v>1520.1</v>
+      </c>
+      <c r="G29" s="171" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" s="176" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I29" s="176" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J29" s="176" t="n">
+        <v>45666402</v>
+      </c>
+      <c r="K29" s="176">
+        <f>ROUND((E29+G29)*F29+H29+I29,0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="177">
+        <f>J29-K29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="171" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.21</t>
+        </is>
+      </c>
+      <c r="C30" s="172" t="inlineStr">
+        <is>
+          <t>Ferco</t>
+        </is>
+      </c>
+      <c r="D30" s="171" t="inlineStr">
+        <is>
+          <t>MONOPLEX20260126-01</t>
+        </is>
+      </c>
+      <c r="E30" s="173" t="n">
+        <v>25976</v>
+      </c>
+      <c r="F30" s="187" t="n">
+        <v>1473.3</v>
+      </c>
+      <c r="G30" s="171" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" s="176" t="n">
         <v>12500</v>
       </c>
-      <c r="I27" s="19" t="n">
+      <c r="I30" s="176" t="n">
         <v>8000</v>
       </c>
-      <c r="J27" s="19" t="n">
-        <v>85481673</v>
-      </c>
-      <c r="K27" s="19">
-        <f>ROUND((E27+G27)*F27+H27+I27,0)</f>
-        <v/>
-      </c>
-      <c r="L27" s="49">
-        <f>J27-K27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="164" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C28" s="165" t="inlineStr">
-        <is>
-          <t>Swank</t>
-        </is>
-      </c>
-      <c r="D28" s="164" t="inlineStr">
-        <is>
-          <t>(영화 라이센스)</t>
-        </is>
-      </c>
-      <c r="E28" s="166" t="n">
-        <v>814</v>
-      </c>
-      <c r="F28" s="167" t="n">
-        <v>1505</v>
-      </c>
-      <c r="G28" s="164" t="n">
+      <c r="J30" s="176" t="n">
+        <v>38320406</v>
+      </c>
+      <c r="K30" s="176">
+        <f>ROUND((E30+G30)*F30+H30+I30,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="177">
+        <f>J30-K30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="171" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C31" s="172" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D31" s="171" t="inlineStr">
+        <is>
+          <t>CPO692(692-1, 692-2)</t>
+        </is>
+      </c>
+      <c r="E31" s="173" t="n">
+        <v>297580</v>
+      </c>
+      <c r="F31" s="187" t="n">
+        <v>1482.8</v>
+      </c>
+      <c r="G31" s="171" t="n">
         <v>20</v>
       </c>
-      <c r="H28" s="168" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I28" s="168" t="n">
+      <c r="H31" s="176" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I31" s="176" t="n">
         <v>8000</v>
       </c>
-      <c r="J28" s="168" t="n">
-        <v>1268170</v>
-      </c>
-      <c r="K28" s="168">
-        <f>ROUND((E28+G28)*F28+H28+I28,0)</f>
-        <v/>
-      </c>
-      <c r="L28" s="169">
-        <f>J28-K28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="27.75" customHeight="1">
-      <c r="A29" s="164" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.02</t>
-        </is>
-      </c>
-      <c r="C29" s="165" t="inlineStr">
-        <is>
-          <t>Monoplex</t>
-        </is>
-      </c>
-      <c r="D29" s="164" t="inlineStr">
-        <is>
-          <t>(영업)</t>
-        </is>
-      </c>
-      <c r="E29" s="166" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F29" s="167" t="n">
-        <v>1520.1</v>
-      </c>
-      <c r="G29" s="164" t="n">
-        <v>20</v>
-      </c>
-      <c r="H29" s="168" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I29" s="168" t="n">
+      <c r="J31" s="176" t="n">
+        <v>441301780</v>
+      </c>
+      <c r="K31" s="176">
+        <f>ROUND((E31+G31)*F31+H31+I31,0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="177">
+        <f>J31-K31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="171" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="171" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C32" s="172" t="inlineStr">
+        <is>
+          <t>Elicent (EUR)</t>
+        </is>
+      </c>
+      <c r="D32" s="171" t="inlineStr">
+        <is>
+          <t>EPO18</t>
+        </is>
+      </c>
+      <c r="E32" s="173" t="n">
+        <v>4388.4</v>
+      </c>
+      <c r="F32" s="187" t="n">
+        <v>1741.08</v>
+      </c>
+      <c r="G32" s="171" t="n">
+        <v>25</v>
+      </c>
+      <c r="H32" s="176" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I32" s="176" t="n">
         <v>8000</v>
       </c>
-      <c r="J29" s="168" t="n">
-        <v>45666402</v>
-      </c>
-      <c r="K29" s="168">
-        <f>ROUND((E29+G29)*F29+H29+I29,0)</f>
-        <v/>
-      </c>
-      <c r="L29" s="169">
-        <f>J29-K29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="164" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.21</t>
-        </is>
-      </c>
-      <c r="C30" s="165" t="inlineStr">
-        <is>
-          <t>Ferco</t>
-        </is>
-      </c>
-      <c r="D30" s="164" t="inlineStr">
-        <is>
-          <t>MONOPLEX20260126-01</t>
-        </is>
-      </c>
-      <c r="E30" s="166" t="n">
-        <v>25976</v>
-      </c>
-      <c r="F30" s="167" t="n">
-        <v>1473.3</v>
-      </c>
-      <c r="G30" s="164" t="n">
-        <v>20</v>
-      </c>
-      <c r="H30" s="168" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I30" s="168" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J30" s="168" t="n">
-        <v>38320406</v>
-      </c>
-      <c r="K30" s="168">
-        <f>ROUND((E30+G30)*F30+H30+I30,0)</f>
-        <v/>
-      </c>
-      <c r="L30" s="169">
-        <f>J30-K30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="164" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C31" s="165" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D31" s="164" t="inlineStr">
-        <is>
-          <t>CPO692(692-1, 692-2)</t>
-        </is>
-      </c>
-      <c r="E31" s="166" t="n">
-        <v>297580</v>
-      </c>
-      <c r="F31" s="167" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="G31" s="164" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" s="168" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I31" s="168" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J31" s="168" t="n">
-        <v>441301780</v>
-      </c>
-      <c r="K31" s="168">
-        <f>ROUND((E31+G31)*F31+H31+I31,0)</f>
-        <v/>
-      </c>
-      <c r="L31" s="169">
-        <f>J31-K31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="164" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="164" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C32" s="165" t="inlineStr">
-        <is>
-          <t>Elicent (EUR)</t>
-        </is>
-      </c>
-      <c r="D32" s="164" t="inlineStr">
-        <is>
-          <t>EPO18</t>
-        </is>
-      </c>
-      <c r="E32" s="166" t="n">
-        <v>4388.4</v>
-      </c>
-      <c r="F32" s="167" t="n">
-        <v>1741.08</v>
-      </c>
-      <c r="G32" s="164" t="n">
-        <v>25</v>
-      </c>
-      <c r="H32" s="168" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I32" s="168" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J32" s="168" t="n">
+      <c r="J32" s="176" t="n">
         <v>7702082</v>
       </c>
-      <c r="K32" s="168">
+      <c r="K32" s="176">
         <f>ROUND((E32+G32)*F32+H32+I32,0)</f>
         <v/>
       </c>
-      <c r="L32" s="169">
+      <c r="L32" s="177">
         <f>J32-K32</f>
         <v/>
       </c>
@@ -12095,31 +12007,32 @@
       <c r="E35" s="44" t="n">
         <v>143557</v>
       </c>
-      <c r="F35" s="170">
-        <f>D30/E30</f>
-        <v/>
-      </c>
-      <c r="G35" s="119" t="n">
-        <v>1479.7</v>
+      <c r="F35" s="188">
+        <f>D35/E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="44">
+        <f>F10</f>
+        <v/>
       </c>
       <c r="H35" s="9">
-        <f>ROUND(D30*G30,0)</f>
+        <f>ROUND(D35*G35,0)</f>
         <v/>
       </c>
       <c r="I35" s="9">
-        <f>ROUND(20*G30*F30,0)</f>
+        <f>ROUND(G10*F35*G35,0)</f>
         <v/>
       </c>
       <c r="J35" s="9">
-        <f>ROUND(H10*F30,0)</f>
+        <f>ROUND(H10*F35,0)</f>
         <v/>
       </c>
       <c r="K35" s="9">
-        <f>ROUND(I10*F30,0)</f>
+        <f>ROUND(I10*F35,0)</f>
         <v/>
       </c>
       <c r="L35" s="46">
-        <f>H30+I30+J30+K30</f>
+        <f>H35+I35+J35+K35</f>
         <v/>
       </c>
     </row>
@@ -12145,31 +12058,32 @@
       <c r="E36" s="44" t="n">
         <v>143557</v>
       </c>
-      <c r="F36" s="170">
-        <f>D31/E31</f>
-        <v/>
-      </c>
-      <c r="G36" s="119" t="n">
-        <v>1479.7</v>
+      <c r="F36" s="188">
+        <f>D36/E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="44">
+        <f>F10</f>
+        <v/>
       </c>
       <c r="H36" s="9">
-        <f>ROUND(D31*G31,0)</f>
+        <f>ROUND(D36*G36,0)</f>
         <v/>
       </c>
       <c r="I36" s="9">
-        <f>ROUND(20*G31*F31,0)</f>
+        <f>ROUND(G10*F36*G36,0)</f>
         <v/>
       </c>
       <c r="J36" s="9">
-        <f>ROUND(H10*F31,0)</f>
+        <f>ROUND(H10*F36,0)</f>
         <v/>
       </c>
       <c r="K36" s="9">
-        <f>ROUND(I10*F31,0)</f>
+        <f>ROUND(I10*F36,0)</f>
         <v/>
       </c>
       <c r="L36" s="46">
-        <f>H31+I31+J31+K31</f>
+        <f>H36+I36+J36+K36</f>
         <v/>
       </c>
     </row>
@@ -12195,31 +12109,32 @@
       <c r="E37" s="44" t="n">
         <v>15040</v>
       </c>
-      <c r="F37" s="170">
-        <f>D32/E32</f>
-        <v/>
-      </c>
-      <c r="G37" s="119" t="n">
-        <v>1480</v>
+      <c r="F37" s="188">
+        <f>D37/E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="44">
+        <f>F9</f>
+        <v/>
       </c>
       <c r="H37" s="9">
-        <f>ROUND(D32*G32,0)</f>
+        <f>ROUND(D37*G37,0)</f>
         <v/>
       </c>
       <c r="I37" s="9">
-        <f>ROUND(20*G32*F32,0)</f>
+        <f>ROUND(G9*F37*G37,0)</f>
         <v/>
       </c>
       <c r="J37" s="9">
-        <f>ROUND(H9*F32,0)</f>
+        <f>ROUND(H9*F37,0)</f>
         <v/>
       </c>
       <c r="K37" s="9">
-        <f>ROUND(I9*F32,0)</f>
+        <f>ROUND(I9*F37,0)</f>
         <v/>
       </c>
       <c r="L37" s="46">
-        <f>H32+I32+J32+K32</f>
+        <f>H37+I37+J37+K37</f>
         <v/>
       </c>
     </row>
@@ -12245,31 +12160,32 @@
       <c r="E38" s="44" t="n">
         <v>13860</v>
       </c>
-      <c r="F38" s="170">
-        <f>D33/E33</f>
-        <v/>
-      </c>
-      <c r="G38" s="119" t="n">
-        <v>1439.1</v>
+      <c r="F38" s="188">
+        <f>D38/E38</f>
+        <v/>
+      </c>
+      <c r="G38" s="44">
+        <f>F12</f>
+        <v/>
       </c>
       <c r="H38" s="9">
-        <f>ROUND(D33*G33,0)</f>
+        <f>ROUND(D38*G38,0)</f>
         <v/>
       </c>
       <c r="I38" s="9">
-        <f>ROUND(20*G33*F33,0)</f>
+        <f>ROUND(G12*F38*G38,0)</f>
         <v/>
       </c>
       <c r="J38" s="9">
-        <f>ROUND(H12*F33,0)</f>
+        <f>ROUND(H12*F38,0)</f>
         <v/>
       </c>
       <c r="K38" s="9">
-        <f>ROUND(I12*F33,0)</f>
+        <f>ROUND(I12*F38,0)</f>
         <v/>
       </c>
       <c r="L38" s="46">
-        <f>H33+I33+J33+K33</f>
+        <f>H38+I38+J38+K38</f>
         <v/>
       </c>
     </row>
@@ -12295,31 +12211,32 @@
       <c r="E39" s="44" t="n">
         <v>13860</v>
       </c>
-      <c r="F39" s="170">
-        <f>D34/E34</f>
-        <v/>
-      </c>
-      <c r="G39" s="119" t="n">
-        <v>1439.1</v>
+      <c r="F39" s="188">
+        <f>D39/E39</f>
+        <v/>
+      </c>
+      <c r="G39" s="44">
+        <f>F12</f>
+        <v/>
       </c>
       <c r="H39" s="9">
-        <f>ROUND(D34*G34,0)</f>
+        <f>ROUND(D39*G39,0)</f>
         <v/>
       </c>
       <c r="I39" s="9">
-        <f>ROUND(20*G34*F34,0)</f>
+        <f>ROUND(G12*F39*G39,0)</f>
         <v/>
       </c>
       <c r="J39" s="9">
-        <f>ROUND(H12*F34,0)</f>
+        <f>ROUND(H12*F39,0)</f>
         <v/>
       </c>
       <c r="K39" s="9">
-        <f>ROUND(I12*F34,0)</f>
+        <f>ROUND(I12*F39,0)</f>
         <v/>
       </c>
       <c r="L39" s="46">
-        <f>H34+I34+J34+K34</f>
+        <f>H39+I39+J39+K39</f>
         <v/>
       </c>
     </row>
@@ -12345,31 +12262,32 @@
       <c r="E40" s="44" t="n">
         <v>252</v>
       </c>
-      <c r="F40" s="170">
-        <f>D35/E35</f>
-        <v/>
-      </c>
-      <c r="G40" s="119" t="n">
-        <v>1479</v>
+      <c r="F40" s="188">
+        <f>D40/E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="44">
+        <f>F14</f>
+        <v/>
       </c>
       <c r="H40" s="9">
-        <f>ROUND(D35*G35,0)</f>
+        <f>ROUND(D40*G40,0)</f>
         <v/>
       </c>
       <c r="I40" s="9">
-        <f>ROUND(20*G35*F35,0)</f>
+        <f>ROUND(G14*F40*G40,0)</f>
         <v/>
       </c>
       <c r="J40" s="9">
-        <f>ROUND(H14*F35,0)</f>
+        <f>ROUND(H14*F40,0)</f>
         <v/>
       </c>
       <c r="K40" s="9">
-        <f>ROUND(I14*F35,0)</f>
+        <f>ROUND(I14*F40,0)</f>
         <v/>
       </c>
       <c r="L40" s="46">
-        <f>H35+I35+J35+K35</f>
+        <f>H40+I40+J40+K40</f>
         <v/>
       </c>
     </row>
@@ -12395,31 +12313,32 @@
       <c r="E41" s="44" t="n">
         <v>3700</v>
       </c>
-      <c r="F41" s="170">
-        <f>D36/E36</f>
-        <v/>
-      </c>
-      <c r="G41" s="119" t="n">
-        <v>1475.7</v>
+      <c r="F41" s="188">
+        <f>D41/E41</f>
+        <v/>
+      </c>
+      <c r="G41" s="44">
+        <f>F15</f>
+        <v/>
       </c>
       <c r="H41" s="9">
-        <f>ROUND(D36*G36,0)</f>
+        <f>ROUND(D41*G41,0)</f>
         <v/>
       </c>
       <c r="I41" s="9">
-        <f>ROUND(20*G36*F36,0)</f>
+        <f>ROUND(G15*F41*G41,0)</f>
         <v/>
       </c>
       <c r="J41" s="9">
-        <f>ROUND(H15*F36,0)</f>
+        <f>ROUND(H15*F41,0)</f>
         <v/>
       </c>
       <c r="K41" s="9">
-        <f>ROUND(I15*F36,0)</f>
+        <f>ROUND(I15*F41,0)</f>
         <v/>
       </c>
       <c r="L41" s="46">
-        <f>H36+I36+J36+K36</f>
+        <f>H41+I41+J41+K41</f>
         <v/>
       </c>
     </row>
@@ -12445,31 +12364,32 @@
       <c r="E42" s="44" t="n">
         <v>3700</v>
       </c>
-      <c r="F42" s="170">
-        <f>D37/E37</f>
-        <v/>
-      </c>
-      <c r="G42" s="119" t="n">
-        <v>1475.7</v>
+      <c r="F42" s="188">
+        <f>D42/E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="44">
+        <f>F15</f>
+        <v/>
       </c>
       <c r="H42" s="9">
-        <f>ROUND(D37*G37,0)</f>
+        <f>ROUND(D42*G42,0)</f>
         <v/>
       </c>
       <c r="I42" s="9">
-        <f>ROUND(20*G37*F37,0)</f>
+        <f>ROUND(G15*F42*G42,0)</f>
         <v/>
       </c>
       <c r="J42" s="9">
-        <f>ROUND(H15*F37,0)</f>
+        <f>ROUND(H15*F42,0)</f>
         <v/>
       </c>
       <c r="K42" s="9">
-        <f>ROUND(I15*F37,0)</f>
+        <f>ROUND(I15*F42,0)</f>
         <v/>
       </c>
       <c r="L42" s="46">
-        <f>H37+I37+J37+K37</f>
+        <f>H42+I42+J42+K42</f>
         <v/>
       </c>
     </row>
@@ -12495,31 +12415,32 @@
       <c r="E43" s="44" t="n">
         <v>3700</v>
       </c>
-      <c r="F43" s="170">
-        <f>D38/E38</f>
-        <v/>
-      </c>
-      <c r="G43" s="119" t="n">
-        <v>1475.7</v>
+      <c r="F43" s="188">
+        <f>D43/E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="44">
+        <f>F15</f>
+        <v/>
       </c>
       <c r="H43" s="9">
-        <f>ROUND(D38*G38,0)</f>
+        <f>ROUND(D43*G43,0)</f>
         <v/>
       </c>
       <c r="I43" s="9">
-        <f>ROUND(20*G38*F38,0)</f>
+        <f>ROUND(G15*F43*G43,0)</f>
         <v/>
       </c>
       <c r="J43" s="9">
-        <f>ROUND(H15*F38,0)</f>
+        <f>ROUND(H15*F43,0)</f>
         <v/>
       </c>
       <c r="K43" s="9">
-        <f>ROUND(I15*F38,0)</f>
+        <f>ROUND(I15*F43,0)</f>
         <v/>
       </c>
       <c r="L43" s="46">
-        <f>H38+I38+J38+K38</f>
+        <f>H43+I43+J43+K43</f>
         <v/>
       </c>
     </row>
@@ -12545,31 +12466,32 @@
       <c r="E44" s="44" t="n">
         <v>9626.35</v>
       </c>
-      <c r="F44" s="170">
-        <f>D39/E39</f>
-        <v/>
-      </c>
-      <c r="G44" s="119" t="n">
-        <v>1476</v>
+      <c r="F44" s="188">
+        <f>D44/E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="44">
+        <f>F16</f>
+        <v/>
       </c>
       <c r="H44" s="9">
-        <f>ROUND(D39*G39,0)</f>
+        <f>ROUND(D44*G44,0)</f>
         <v/>
       </c>
       <c r="I44" s="9">
-        <f>ROUND(20*G39*F39,0)</f>
+        <f>ROUND(G16*F44*G44,0)</f>
         <v/>
       </c>
       <c r="J44" s="9">
-        <f>ROUND(H16*F39,0)</f>
+        <f>ROUND(H16*F44,0)</f>
         <v/>
       </c>
       <c r="K44" s="9">
-        <f>ROUND(I16*F39,0)</f>
+        <f>ROUND(I16*F44,0)</f>
         <v/>
       </c>
       <c r="L44" s="46">
-        <f>H39+I39+J39+K39</f>
+        <f>H44+I44+J44+K44</f>
         <v/>
       </c>
     </row>
@@ -12595,31 +12517,32 @@
       <c r="E45" s="44" t="n">
         <v>5056.8</v>
       </c>
-      <c r="F45" s="170">
-        <f>D40/E40</f>
-        <v/>
-      </c>
-      <c r="G45" s="119" t="n">
-        <v>1445.5</v>
+      <c r="F45" s="188">
+        <f>D45/E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="44">
+        <f>F17</f>
+        <v/>
       </c>
       <c r="H45" s="9">
-        <f>ROUND(D40*G40,0)</f>
+        <f>ROUND(D45*G45,0)</f>
         <v/>
       </c>
       <c r="I45" s="9">
-        <f>ROUND(20*G40*F40,0)</f>
+        <f>ROUND(G17*F45*G45,0)</f>
         <v/>
       </c>
       <c r="J45" s="9">
-        <f>ROUND(H17*F40,0)</f>
+        <f>ROUND(H17*F45,0)</f>
         <v/>
       </c>
       <c r="K45" s="9">
-        <f>ROUND(I17*F40,0)</f>
+        <f>ROUND(I17*F45,0)</f>
         <v/>
       </c>
       <c r="L45" s="46">
-        <f>H40+I40+J40+K40</f>
+        <f>H45+I45+J45+K45</f>
         <v/>
       </c>
     </row>
@@ -12645,31 +12568,32 @@
       <c r="E46" s="44" t="n">
         <v>24794</v>
       </c>
-      <c r="F46" s="170">
-        <f>D41/E41</f>
-        <v/>
-      </c>
-      <c r="G46" s="119" t="n">
-        <v>1454.7</v>
+      <c r="F46" s="188">
+        <f>D46/E46</f>
+        <v/>
+      </c>
+      <c r="G46" s="44">
+        <f>F19</f>
+        <v/>
       </c>
       <c r="H46" s="9">
-        <f>ROUND(D41*G41,0)</f>
+        <f>ROUND(D46*G46,0)</f>
         <v/>
       </c>
       <c r="I46" s="9">
-        <f>ROUND(20*G41*F41,0)</f>
+        <f>ROUND(G19*F46*G46,0)</f>
         <v/>
       </c>
       <c r="J46" s="9">
-        <f>ROUND(H19*F41,0)</f>
+        <f>ROUND(H19*F46,0)</f>
         <v/>
       </c>
       <c r="K46" s="9">
-        <f>ROUND(I19*F41,0)</f>
+        <f>ROUND(I19*F46,0)</f>
         <v/>
       </c>
       <c r="L46" s="46">
-        <f>H41+I41+J41+K41</f>
+        <f>H46+I46+J46+K46</f>
         <v/>
       </c>
     </row>
@@ -12695,31 +12619,32 @@
       <c r="E47" s="44" t="n">
         <v>24794</v>
       </c>
-      <c r="F47" s="170">
-        <f>D42/E42</f>
-        <v/>
-      </c>
-      <c r="G47" s="119" t="n">
-        <v>1454.7</v>
+      <c r="F47" s="188">
+        <f>D47/E47</f>
+        <v/>
+      </c>
+      <c r="G47" s="44">
+        <f>F19</f>
+        <v/>
       </c>
       <c r="H47" s="9">
-        <f>ROUND(D42*G42,0)</f>
+        <f>ROUND(D47*G47,0)</f>
         <v/>
       </c>
       <c r="I47" s="9">
-        <f>ROUND(20*G42*F42,0)</f>
+        <f>ROUND(G19*F47*G47,0)</f>
         <v/>
       </c>
       <c r="J47" s="9">
-        <f>ROUND(H19*F42,0)</f>
+        <f>ROUND(H19*F47,0)</f>
         <v/>
       </c>
       <c r="K47" s="9">
-        <f>ROUND(I19*F42,0)</f>
+        <f>ROUND(I19*F47,0)</f>
         <v/>
       </c>
       <c r="L47" s="46">
-        <f>H42+I42+J42+K42</f>
+        <f>H47+I47+J47+K47</f>
         <v/>
       </c>
     </row>
@@ -12745,31 +12670,32 @@
       <c r="E48" s="44" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F48" s="170">
-        <f>D43/E43</f>
-        <v/>
-      </c>
-      <c r="G48" s="119" t="n">
-        <v>1453.6</v>
+      <c r="F48" s="188">
+        <f>D48/E48</f>
+        <v/>
+      </c>
+      <c r="G48" s="44">
+        <f>F20</f>
+        <v/>
       </c>
       <c r="H48" s="9">
-        <f>ROUND(D43*G43,0)</f>
+        <f>ROUND(D48*G48,0)</f>
         <v/>
       </c>
       <c r="I48" s="9">
-        <f>ROUND(20*G43*F43,0)</f>
+        <f>ROUND(G20*F48*G48,0)</f>
         <v/>
       </c>
       <c r="J48" s="9">
-        <f>ROUND(H20*F43,0)</f>
+        <f>ROUND(H20*F48,0)</f>
         <v/>
       </c>
       <c r="K48" s="9">
-        <f>ROUND(I20*F43,0)</f>
+        <f>ROUND(I20*F48,0)</f>
         <v/>
       </c>
       <c r="L48" s="46">
-        <f>H43+I43+J43+K43</f>
+        <f>H48+I48+J48+K48</f>
         <v/>
       </c>
     </row>
@@ -12795,31 +12721,32 @@
       <c r="E49" s="44" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F49" s="170">
-        <f>D44/E44</f>
-        <v/>
-      </c>
-      <c r="G49" s="119" t="n">
-        <v>1453.6</v>
+      <c r="F49" s="188">
+        <f>D49/E49</f>
+        <v/>
+      </c>
+      <c r="G49" s="44">
+        <f>F20</f>
+        <v/>
       </c>
       <c r="H49" s="9">
-        <f>ROUND(D44*G44,0)</f>
+        <f>ROUND(D49*G49,0)</f>
         <v/>
       </c>
       <c r="I49" s="9">
-        <f>ROUND(20*G44*F44,0)</f>
+        <f>ROUND(G20*F49*G49,0)</f>
         <v/>
       </c>
       <c r="J49" s="9">
-        <f>ROUND(H20*F44,0)</f>
+        <f>ROUND(H20*F49,0)</f>
         <v/>
       </c>
       <c r="K49" s="9">
-        <f>ROUND(I20*F44,0)</f>
+        <f>ROUND(I20*F49,0)</f>
         <v/>
       </c>
       <c r="L49" s="46">
-        <f>H44+I44+J44+K44</f>
+        <f>H49+I49+J49+K49</f>
         <v/>
       </c>
     </row>
@@ -12845,31 +12772,32 @@
       <c r="E50" s="44" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F50" s="170">
-        <f>D45/E45</f>
-        <v/>
-      </c>
-      <c r="G50" s="119" t="n">
-        <v>1453.6</v>
+      <c r="F50" s="188">
+        <f>D50/E50</f>
+        <v/>
+      </c>
+      <c r="G50" s="44">
+        <f>F20</f>
+        <v/>
       </c>
       <c r="H50" s="9">
-        <f>ROUND(D45*G45,0)</f>
+        <f>ROUND(D50*G50,0)</f>
         <v/>
       </c>
       <c r="I50" s="9">
-        <f>ROUND(20*G45*F45,0)</f>
+        <f>ROUND(G20*F50*G50,0)</f>
         <v/>
       </c>
       <c r="J50" s="9">
-        <f>ROUND(H20*F45,0)</f>
+        <f>ROUND(H20*F50,0)</f>
         <v/>
       </c>
       <c r="K50" s="9">
-        <f>ROUND(I20*F45,0)</f>
+        <f>ROUND(I20*F50,0)</f>
         <v/>
       </c>
       <c r="L50" s="46">
-        <f>H45+I45+J45+K45</f>
+        <f>H50+I50+J50+K50</f>
         <v/>
       </c>
     </row>
@@ -12895,31 +12823,32 @@
       <c r="E51" s="44" t="n">
         <v>26358</v>
       </c>
-      <c r="F51" s="170">
-        <f>D46/E46</f>
-        <v/>
-      </c>
-      <c r="G51" s="119" t="n">
-        <v>1460.7</v>
+      <c r="F51" s="188">
+        <f>D51/E51</f>
+        <v/>
+      </c>
+      <c r="G51" s="44">
+        <f>F21</f>
+        <v/>
       </c>
       <c r="H51" s="9">
-        <f>ROUND(D46*G46,0)</f>
+        <f>ROUND(D51*G51,0)</f>
         <v/>
       </c>
       <c r="I51" s="9">
-        <f>ROUND(20*G46*F46,0)</f>
+        <f>ROUND(G21*F51*G51,0)</f>
         <v/>
       </c>
       <c r="J51" s="9">
-        <f>ROUND(H21*F46,0)</f>
+        <f>ROUND(H21*F51,0)</f>
         <v/>
       </c>
       <c r="K51" s="9">
-        <f>ROUND(I21*F46,0)</f>
+        <f>ROUND(I21*F51,0)</f>
         <v/>
       </c>
       <c r="L51" s="46">
-        <f>H46+I46+J46+K46</f>
+        <f>H51+I51+J51+K51</f>
         <v/>
       </c>
     </row>
@@ -12945,31 +12874,32 @@
       <c r="E52" s="44" t="n">
         <v>17538</v>
       </c>
-      <c r="F52" s="170">
-        <f>D47/E47</f>
-        <v/>
-      </c>
-      <c r="G52" s="119" t="n">
-        <v>1451.7</v>
+      <c r="F52" s="188">
+        <f>D52/E52</f>
+        <v/>
+      </c>
+      <c r="G52" s="44">
+        <f>F22</f>
+        <v/>
       </c>
       <c r="H52" s="9">
-        <f>ROUND(D47*G47,0)</f>
+        <f>ROUND(D52*G52,0)</f>
         <v/>
       </c>
       <c r="I52" s="9">
-        <f>ROUND(20*G47*F47,0)</f>
+        <f>ROUND(G22*F52*G52,0)</f>
         <v/>
       </c>
       <c r="J52" s="9">
-        <f>ROUND(H22*F47,0)</f>
+        <f>ROUND(H22*F52,0)</f>
         <v/>
       </c>
       <c r="K52" s="9">
-        <f>ROUND(I22*F47,0)</f>
+        <f>ROUND(I22*F52,0)</f>
         <v/>
       </c>
       <c r="L52" s="46">
-        <f>H47+I47+J47+K47</f>
+        <f>H52+I52+J52+K52</f>
         <v/>
       </c>
     </row>
@@ -12995,30 +12925,34 @@
       <c r="E53" s="44" t="n">
         <v>17538</v>
       </c>
-      <c r="F53" s="170">
-        <f>D48/E48</f>
-        <v/>
-      </c>
-      <c r="G53" s="119" t="n">
-        <v>1451.7</v>
+      <c r="F53" s="188">
+        <f>D53/E53</f>
+        <v/>
+      </c>
+      <c r="G53" s="44">
+        <f>F22</f>
+        <v/>
       </c>
       <c r="H53" s="9">
-        <f>ROUND(D48*G48,0)</f>
+        <f>ROUND(D53*G53,0)</f>
         <v/>
       </c>
       <c r="I53" s="9">
-        <f>ROUND(20*G48*F48,0)</f>
+        <f>ROUND(G22*F53*G53,0)</f>
         <v/>
       </c>
       <c r="J53" s="9">
-        <f>ROUND(H22*F48,0)</f>
+        <f>ROUND(H22*F53,0)</f>
         <v/>
       </c>
       <c r="K53" s="9">
-        <f>ROUND(I22*F48,0)</f>
-        <v/>
-      </c>
-      <c r="L53" s="46" t="n"/>
+        <f>ROUND(I22*F53,0)</f>
+        <v/>
+      </c>
+      <c r="L53" s="46">
+        <f>H53+I53+J53+K53</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
@@ -13042,31 +12976,32 @@
       <c r="E54" s="44" t="n">
         <v>142189</v>
       </c>
-      <c r="F54" s="170">
-        <f>D49/E49</f>
-        <v/>
-      </c>
-      <c r="G54" s="119" t="n">
-        <v>1441.6</v>
+      <c r="F54" s="188">
+        <f>D54/E54</f>
+        <v/>
+      </c>
+      <c r="G54" s="44">
+        <f>F23</f>
+        <v/>
       </c>
       <c r="H54" s="9">
-        <f>ROUND(D49*G49,0)</f>
+        <f>ROUND(D54*G54,0)</f>
         <v/>
       </c>
       <c r="I54" s="9">
-        <f>ROUND(20*G49*F49,0)</f>
+        <f>ROUND(G23*F54*G54,0)</f>
         <v/>
       </c>
       <c r="J54" s="9">
-        <f>ROUND(H23*F49,0)</f>
+        <f>ROUND(H23*F54,0)</f>
         <v/>
       </c>
       <c r="K54" s="9">
-        <f>ROUND(I23*F49,0)</f>
+        <f>ROUND(I23*F54,0)</f>
         <v/>
       </c>
       <c r="L54" s="46">
-        <f>H49+I49+J49+K49</f>
+        <f>H54+I54+J54+K54</f>
         <v/>
       </c>
     </row>
@@ -13092,31 +13027,32 @@
       <c r="E55" s="44" t="n">
         <v>142189</v>
       </c>
-      <c r="F55" s="170">
-        <f>D50/E50</f>
-        <v/>
-      </c>
-      <c r="G55" s="119" t="n">
-        <v>1441.6</v>
+      <c r="F55" s="188">
+        <f>D55/E55</f>
+        <v/>
+      </c>
+      <c r="G55" s="44">
+        <f>F23</f>
+        <v/>
       </c>
       <c r="H55" s="9">
-        <f>ROUND(D50*G50,0)</f>
+        <f>ROUND(D55*G55,0)</f>
         <v/>
       </c>
       <c r="I55" s="9">
-        <f>ROUND(20*G50*F50,0)</f>
+        <f>ROUND(G23*F55*G55,0)</f>
         <v/>
       </c>
       <c r="J55" s="9">
-        <f>ROUND(H23*F50,0)</f>
+        <f>ROUND(H23*F55,0)</f>
         <v/>
       </c>
       <c r="K55" s="9">
-        <f>ROUND(I23*F50,0)</f>
+        <f>ROUND(I23*F55,0)</f>
         <v/>
       </c>
       <c r="L55" s="46">
-        <f>H50+I50+J50+K50</f>
+        <f>H55+I55+J55+K55</f>
         <v/>
       </c>
     </row>
@@ -13142,31 +13078,32 @@
       <c r="E56" s="44" t="n">
         <v>137850</v>
       </c>
-      <c r="F56" s="170">
-        <f>D51/E51</f>
-        <v/>
-      </c>
-      <c r="G56" s="119" t="n">
-        <v>1477.6</v>
+      <c r="F56" s="188">
+        <f>D56/E56</f>
+        <v/>
+      </c>
+      <c r="G56" s="44">
+        <f>F24</f>
+        <v/>
       </c>
       <c r="H56" s="9">
-        <f>ROUND(D51*G51,0)</f>
+        <f>ROUND(D56*G56,0)</f>
         <v/>
       </c>
       <c r="I56" s="9">
-        <f>ROUND(20*G51*F51,0)</f>
+        <f>ROUND(G24*F56*G56,0)</f>
         <v/>
       </c>
       <c r="J56" s="9">
-        <f>ROUND(H24*F51,0)</f>
+        <f>ROUND(H24*F56,0)</f>
         <v/>
       </c>
       <c r="K56" s="9">
-        <f>ROUND(I24*F51,0)</f>
+        <f>ROUND(I24*F56,0)</f>
         <v/>
       </c>
       <c r="L56" s="46">
-        <f>H51+I51+J51+K51</f>
+        <f>H56+I56+J56+K56</f>
         <v/>
       </c>
     </row>
@@ -13192,31 +13129,32 @@
       <c r="E57" s="44" t="n">
         <v>34354</v>
       </c>
-      <c r="F57" s="170">
-        <f>D52/E52</f>
-        <v/>
-      </c>
-      <c r="G57" s="119" t="n">
-        <v>1505.7</v>
+      <c r="F57" s="188">
+        <f>D57/E57</f>
+        <v/>
+      </c>
+      <c r="G57" s="44">
+        <f>F25</f>
+        <v/>
       </c>
       <c r="H57" s="9">
-        <f>ROUND(D52*G52,0)</f>
+        <f>ROUND(D57*G57,0)</f>
         <v/>
       </c>
       <c r="I57" s="9">
-        <f>ROUND(20*G52*F52,0)</f>
+        <f>ROUND(G25*F57*G57,0)</f>
         <v/>
       </c>
       <c r="J57" s="9">
-        <f>ROUND(H25*F52,0)</f>
+        <f>ROUND(H25*F57,0)</f>
         <v/>
       </c>
       <c r="K57" s="9">
-        <f>ROUND(I25*F52,0)</f>
+        <f>ROUND(I25*F57,0)</f>
         <v/>
       </c>
       <c r="L57" s="46">
-        <f>H52+I52+J52+K52</f>
+        <f>H57+I57+J57+K57</f>
         <v/>
       </c>
     </row>
@@ -13242,31 +13180,32 @@
       <c r="E58" s="44" t="n">
         <v>34354</v>
       </c>
-      <c r="F58" s="170">
-        <f>D53/E53</f>
-        <v/>
-      </c>
-      <c r="G58" s="119" t="n">
-        <v>1505.7</v>
+      <c r="F58" s="188">
+        <f>D58/E58</f>
+        <v/>
+      </c>
+      <c r="G58" s="44">
+        <f>F25</f>
+        <v/>
       </c>
       <c r="H58" s="9">
-        <f>ROUND(D53*G53,0)</f>
+        <f>ROUND(D58*G58,0)</f>
         <v/>
       </c>
       <c r="I58" s="9">
-        <f>ROUND(20*G53*F53,0)</f>
+        <f>ROUND(G25*F58*G58,0)</f>
         <v/>
       </c>
       <c r="J58" s="9">
-        <f>ROUND(H25*F53,0)</f>
+        <f>ROUND(H25*F58,0)</f>
         <v/>
       </c>
       <c r="K58" s="9">
-        <f>ROUND(I25*F53,0)</f>
+        <f>ROUND(I25*F58,0)</f>
         <v/>
       </c>
       <c r="L58" s="46">
-        <f>H53+I53+J53+K53</f>
+        <f>H58+I58+J58+K58</f>
         <v/>
       </c>
     </row>
@@ -13292,31 +13231,32 @@
       <c r="E59" s="44" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F59" s="170">
-        <f>D54/E54</f>
-        <v/>
-      </c>
-      <c r="G59" s="119" t="n">
-        <v>1506.4</v>
+      <c r="F59" s="188">
+        <f>D59/E59</f>
+        <v/>
+      </c>
+      <c r="G59" s="44">
+        <f>F26</f>
+        <v/>
       </c>
       <c r="H59" s="9">
-        <f>ROUND(D54*G54,0)</f>
+        <f>ROUND(D59*G59,0)</f>
         <v/>
       </c>
       <c r="I59" s="9">
-        <f>ROUND(20*G54*F54,0)</f>
+        <f>ROUND(G26*F59*G59,0)</f>
         <v/>
       </c>
       <c r="J59" s="9">
-        <f>ROUND(H26*F54,0)</f>
+        <f>ROUND(H26*F59,0)</f>
         <v/>
       </c>
       <c r="K59" s="9">
-        <f>ROUND(I26*F54,0)</f>
+        <f>ROUND(I26*F59,0)</f>
         <v/>
       </c>
       <c r="L59" s="46">
-        <f>H54+I54+J54+K54</f>
+        <f>H59+I59+J59+K59</f>
         <v/>
       </c>
     </row>
@@ -13342,31 +13282,32 @@
       <c r="E60" s="44" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F60" s="170">
-        <f>D55/E55</f>
-        <v/>
-      </c>
-      <c r="G60" s="119" t="n">
-        <v>1506.4</v>
+      <c r="F60" s="188">
+        <f>D60/E60</f>
+        <v/>
+      </c>
+      <c r="G60" s="44">
+        <f>F26</f>
+        <v/>
       </c>
       <c r="H60" s="9">
-        <f>ROUND(D55*G55,0)</f>
+        <f>ROUND(D60*G60,0)</f>
         <v/>
       </c>
       <c r="I60" s="9">
-        <f>ROUND(20*G55*F55,0)</f>
+        <f>ROUND(G26*F60*G60,0)</f>
         <v/>
       </c>
       <c r="J60" s="9">
-        <f>ROUND(H26*F55,0)</f>
+        <f>ROUND(H26*F60,0)</f>
         <v/>
       </c>
       <c r="K60" s="9">
-        <f>ROUND(I26*F55,0)</f>
+        <f>ROUND(I26*F60,0)</f>
         <v/>
       </c>
       <c r="L60" s="46">
-        <f>H55+I55+J55+K55</f>
+        <f>H60+I60+J60+K60</f>
         <v/>
       </c>
     </row>
@@ -13392,31 +13333,32 @@
       <c r="E61" s="44" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F61" s="170">
-        <f>D56/E56</f>
-        <v/>
-      </c>
-      <c r="G61" s="119" t="n">
-        <v>1506.4</v>
+      <c r="F61" s="188">
+        <f>D61/E61</f>
+        <v/>
+      </c>
+      <c r="G61" s="44">
+        <f>F26</f>
+        <v/>
       </c>
       <c r="H61" s="9">
-        <f>ROUND(D56*G56,0)</f>
+        <f>ROUND(D61*G61,0)</f>
         <v/>
       </c>
       <c r="I61" s="9">
-        <f>ROUND(20*G56*F56,0)</f>
+        <f>ROUND(G26*F61*G61,0)</f>
         <v/>
       </c>
       <c r="J61" s="9">
-        <f>ROUND(H26*F56,0)</f>
+        <f>ROUND(H26*F61,0)</f>
         <v/>
       </c>
       <c r="K61" s="9">
-        <f>ROUND(I26*F56,0)</f>
+        <f>ROUND(I26*F61,0)</f>
         <v/>
       </c>
       <c r="L61" s="46">
-        <f>H56+I56+J56+K56</f>
+        <f>H61+I61+J61+K61</f>
         <v/>
       </c>
     </row>
@@ -13442,31 +13384,32 @@
       <c r="E62" s="44" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F62" s="170">
-        <f>D57/E57</f>
-        <v/>
-      </c>
-      <c r="G62" s="119" t="n">
-        <v>1506.4</v>
+      <c r="F62" s="188">
+        <f>D62/E62</f>
+        <v/>
+      </c>
+      <c r="G62" s="44">
+        <f>F26</f>
+        <v/>
       </c>
       <c r="H62" s="9">
-        <f>ROUND(D57*G57,0)</f>
+        <f>ROUND(D62*G62,0)</f>
         <v/>
       </c>
       <c r="I62" s="9">
-        <f>ROUND(20*G57*F57,0)</f>
+        <f>ROUND(G26*F62*G62,0)</f>
         <v/>
       </c>
       <c r="J62" s="9">
-        <f>ROUND(H26*F57,0)</f>
+        <f>ROUND(H26*F62,0)</f>
         <v/>
       </c>
       <c r="K62" s="9">
-        <f>ROUND(I26*F57,0)</f>
+        <f>ROUND(I26*F62,0)</f>
         <v/>
       </c>
       <c r="L62" s="46">
-        <f>H57+I57+J57+K57</f>
+        <f>H62+I62+J62+K62</f>
         <v/>
       </c>
     </row>
@@ -13492,31 +13435,32 @@
       <c r="E63" s="44" t="n">
         <v>57650</v>
       </c>
-      <c r="F63" s="170">
-        <f>D58/E58</f>
-        <v/>
-      </c>
-      <c r="G63" s="119" t="n">
-        <v>1481.9</v>
+      <c r="F63" s="188">
+        <f>D63/E63</f>
+        <v/>
+      </c>
+      <c r="G63" s="44">
+        <f>F27</f>
+        <v/>
       </c>
       <c r="H63" s="9">
-        <f>ROUND(D58*G58,0)</f>
+        <f>ROUND(D63*G63,0)</f>
         <v/>
       </c>
       <c r="I63" s="9">
-        <f>ROUND(20*G58*F58,0)</f>
+        <f>ROUND(G27*F63*G63,0)</f>
         <v/>
       </c>
       <c r="J63" s="9">
-        <f>ROUND(H27*F58,0)</f>
+        <f>ROUND(H27*F63,0)</f>
         <v/>
       </c>
       <c r="K63" s="9">
-        <f>ROUND(I27*F58,0)</f>
+        <f>ROUND(I27*F63,0)</f>
         <v/>
       </c>
       <c r="L63" s="46">
-        <f>H58+I58+J58+K58</f>
+        <f>H63+I63+J63+K63</f>
         <v/>
       </c>
     </row>
@@ -13542,31 +13486,32 @@
       <c r="E64" s="44" t="n">
         <v>57650</v>
       </c>
-      <c r="F64" s="170">
-        <f>D59/E59</f>
-        <v/>
-      </c>
-      <c r="G64" s="119" t="n">
-        <v>1481.9</v>
+      <c r="F64" s="188">
+        <f>D64/E64</f>
+        <v/>
+      </c>
+      <c r="G64" s="44">
+        <f>F27</f>
+        <v/>
       </c>
       <c r="H64" s="9">
-        <f>ROUND(D59*G59,0)</f>
+        <f>ROUND(D64*G64,0)</f>
         <v/>
       </c>
       <c r="I64" s="9">
-        <f>ROUND(20*G59*F59,0)</f>
+        <f>ROUND(G27*F64*G64,0)</f>
         <v/>
       </c>
       <c r="J64" s="9">
-        <f>ROUND(H27*F59,0)</f>
+        <f>ROUND(H27*F64,0)</f>
         <v/>
       </c>
       <c r="K64" s="9">
-        <f>ROUND(I27*F59,0)</f>
+        <f>ROUND(I27*F64,0)</f>
         <v/>
       </c>
       <c r="L64" s="46">
-        <f>H59+I59+J59+K59</f>
+        <f>H64+I64+J64+K64</f>
         <v/>
       </c>
     </row>
@@ -13592,31 +13537,32 @@
       <c r="E65" s="44" t="n">
         <v>57650</v>
       </c>
-      <c r="F65" s="170">
-        <f>D60/E60</f>
-        <v/>
-      </c>
-      <c r="G65" s="119" t="n">
-        <v>1481.9</v>
+      <c r="F65" s="188">
+        <f>D65/E65</f>
+        <v/>
+      </c>
+      <c r="G65" s="44">
+        <f>F27</f>
+        <v/>
       </c>
       <c r="H65" s="9">
-        <f>ROUND(D60*G60,0)</f>
+        <f>ROUND(D65*G65,0)</f>
         <v/>
       </c>
       <c r="I65" s="9">
-        <f>ROUND(20*G60*F60,0)</f>
+        <f>ROUND(G27*F65*G65,0)</f>
         <v/>
       </c>
       <c r="J65" s="9">
-        <f>ROUND(H27*F60,0)</f>
+        <f>ROUND(H27*F65,0)</f>
         <v/>
       </c>
       <c r="K65" s="9">
-        <f>ROUND(I27*F60,0)</f>
+        <f>ROUND(I27*F65,0)</f>
         <v/>
       </c>
       <c r="L65" s="46">
-        <f>H60+I60+J60+K60</f>
+        <f>H65+I65+J65+K65</f>
         <v/>
       </c>
     </row>
@@ -13642,26 +13588,33 @@
       <c r="E66" s="173" t="n">
         <v>297580</v>
       </c>
-      <c r="F66" s="174" t="n">
-        <v>0.03696484978829222</v>
-      </c>
-      <c r="G66" s="175" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="H66" s="176" t="n">
-        <v>16310800</v>
-      </c>
-      <c r="I66" s="176" t="n">
-        <v>1096</v>
-      </c>
-      <c r="J66" s="176" t="n">
-        <v>462</v>
-      </c>
-      <c r="K66" s="176" t="n">
-        <v>296</v>
-      </c>
-      <c r="L66" s="177" t="n">
-        <v>16312654</v>
+      <c r="F66" s="189">
+        <f>D66/E66</f>
+        <v/>
+      </c>
+      <c r="G66" s="173">
+        <f>F31</f>
+        <v/>
+      </c>
+      <c r="H66" s="176">
+        <f>ROUND(D66*G66,0)</f>
+        <v/>
+      </c>
+      <c r="I66" s="176">
+        <f>ROUND(G31*F66*G66,0)</f>
+        <v/>
+      </c>
+      <c r="J66" s="176">
+        <f>ROUND(H31*F66,0)</f>
+        <v/>
+      </c>
+      <c r="K66" s="176">
+        <f>ROUND(I31*F66,0)</f>
+        <v/>
+      </c>
+      <c r="L66" s="177">
+        <f>H66+I66+J66+K66</f>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -13686,26 +13639,33 @@
       <c r="E67" s="173" t="n">
         <v>297580</v>
       </c>
-      <c r="F67" s="174" t="n">
-        <v>0.9630351502117078</v>
-      </c>
-      <c r="G67" s="175" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="H67" s="176" t="n">
-        <v>424990980</v>
-      </c>
-      <c r="I67" s="176" t="n">
-        <v>28560</v>
-      </c>
-      <c r="J67" s="176" t="n">
-        <v>12038</v>
-      </c>
-      <c r="K67" s="176" t="n">
-        <v>7704</v>
-      </c>
-      <c r="L67" s="177" t="n">
-        <v>425039282</v>
+      <c r="F67" s="189">
+        <f>D67/E67</f>
+        <v/>
+      </c>
+      <c r="G67" s="173">
+        <f>F31</f>
+        <v/>
+      </c>
+      <c r="H67" s="176">
+        <f>ROUND(D67*G67,0)</f>
+        <v/>
+      </c>
+      <c r="I67" s="176">
+        <f>ROUND(G31*F67*G67,0)</f>
+        <v/>
+      </c>
+      <c r="J67" s="176">
+        <f>ROUND(H31*F67,0)</f>
+        <v/>
+      </c>
+      <c r="K67" s="176">
+        <f>ROUND(I31*F67,0)</f>
+        <v/>
+      </c>
+      <c r="L67" s="177">
+        <f>H67+I67+J67+K67</f>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -13730,26 +13690,33 @@
       <c r="E68" s="173" t="n">
         <v>4388.4</v>
       </c>
-      <c r="F68" s="174" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="175" t="n">
-        <v>1741.08</v>
-      </c>
-      <c r="H68" s="176" t="n">
-        <v>7702082</v>
-      </c>
-      <c r="I68" s="176" t="n">
-        <v>43527</v>
-      </c>
-      <c r="J68" s="176" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K68" s="176" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L68" s="177" t="n">
-        <v>7763609</v>
+      <c r="F68" s="189">
+        <f>D68/E68</f>
+        <v/>
+      </c>
+      <c r="G68" s="173">
+        <f>F32</f>
+        <v/>
+      </c>
+      <c r="H68" s="176">
+        <f>ROUND(D68*G68,0)</f>
+        <v/>
+      </c>
+      <c r="I68" s="176">
+        <f>ROUND(G32*F68*G68,0)</f>
+        <v/>
+      </c>
+      <c r="J68" s="176">
+        <f>ROUND(H32*F68,0)</f>
+        <v/>
+      </c>
+      <c r="K68" s="176">
+        <f>ROUND(I32*F68,0)</f>
+        <v/>
+      </c>
+      <c r="L68" s="177">
+        <f>H68+I68+J68+K68</f>
+        <v/>
       </c>
     </row>
     <row r="76">

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -2058,16 +2058,8 @@
           <t>Parts (국내)</t>
         </is>
       </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O8" s="12" t="n"/>
+      <c r="P8" s="12" t="n"/>
       <c r="Q8" s="18" t="n"/>
       <c r="R8" s="18" t="n"/>
       <c r="S8" s="18" t="n">
@@ -2110,11 +2102,7 @@
         <f>ROUND(AA8/AB8,0)</f>
         <v/>
       </c>
-      <c r="AD8" s="12" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
+      <c r="AD8" s="12" t="n"/>
       <c r="AE8" s="12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3876,16 +3864,8 @@
           <t>Projector (한국)</t>
         </is>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O22" s="12" t="n"/>
+      <c r="P22" s="12" t="n"/>
       <c r="Q22" s="18" t="n"/>
       <c r="R22" s="18" t="n"/>
       <c r="S22" s="18" t="n">
@@ -3928,11 +3908,7 @@
         <f>ROUND(AA22/AB22,0)</f>
         <v/>
       </c>
-      <c r="AD22" s="12" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
+      <c r="AD22" s="12" t="n"/>
       <c r="AE22" s="12" t="inlineStr">
         <is>
           <t>-</t>
@@ -5015,16 +4991,8 @@
           <t>AXC 200 ELICENT 60ea (EUR / 재고)</t>
         </is>
       </c>
-      <c r="O31" s="149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P31" s="78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O31" s="149" t="n"/>
+      <c r="P31" s="78" t="n"/>
       <c r="Q31" s="151">
         <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5069,11 +5037,7 @@
       <c r="AC31" s="83" t="n">
         <v>129393</v>
       </c>
-      <c r="AD31" s="78" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
+      <c r="AD31" s="78" t="n"/>
       <c r="AE31" s="78" t="n"/>
       <c r="AF31" s="78" t="n"/>
     </row>
@@ -5134,16 +5098,8 @@
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="O32" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P32" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O32" s="20" t="n"/>
+      <c r="P32" s="20" t="n"/>
       <c r="Q32" s="26">
         <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5265,16 +5221,8 @@
           <t>HFR License</t>
         </is>
       </c>
-      <c r="O33" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P33" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O33" s="20" t="n"/>
+      <c r="P33" s="20" t="n"/>
       <c r="Q33" s="26">
         <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5396,16 +5344,8 @@
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="O34" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P34" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O34" s="20" t="n"/>
+      <c r="P34" s="20" t="n"/>
       <c r="Q34" s="26">
         <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5527,16 +5467,8 @@
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="O35" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P35" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O35" s="20" t="n"/>
+      <c r="P35" s="20" t="n"/>
       <c r="Q35" s="26">
         <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5658,16 +5590,8 @@
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="O36" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P36" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O36" s="20" t="n"/>
+      <c r="P36" s="20" t="n"/>
       <c r="Q36" s="26">
         <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5789,16 +5713,8 @@
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="O37" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P37" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O37" s="20" t="n"/>
+      <c r="P37" s="20" t="n"/>
       <c r="Q37" s="26">
         <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5922,16 +5838,8 @@
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="O38" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P38" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O38" s="20" t="n"/>
+      <c r="P38" s="20" t="n"/>
       <c r="Q38" s="26">
         <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6053,16 +5961,8 @@
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="O39" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P39" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O39" s="20" t="n"/>
+      <c r="P39" s="20" t="n"/>
       <c r="Q39" s="26">
         <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6186,16 +6086,8 @@
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="O40" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P40" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O40" s="20" t="n"/>
+      <c r="P40" s="20" t="n"/>
       <c r="Q40" s="26">
         <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6317,16 +6209,8 @@
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="O41" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P41" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O41" s="20" t="n"/>
+      <c r="P41" s="20" t="n"/>
       <c r="Q41" s="26">
         <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6448,16 +6332,8 @@
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="O42" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P42" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O42" s="20" t="n"/>
+      <c r="P42" s="20" t="n"/>
       <c r="Q42" s="26">
         <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6579,16 +6455,8 @@
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="O43" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P43" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O43" s="20" t="n"/>
+      <c r="P43" s="20" t="n"/>
       <c r="Q43" s="26">
         <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6710,16 +6578,8 @@
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="O44" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P44" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O44" s="20" t="n"/>
+      <c r="P44" s="20" t="n"/>
       <c r="Q44" s="26">
         <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6841,16 +6701,8 @@
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="O45" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P45" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O45" s="20" t="n"/>
+      <c r="P45" s="20" t="n"/>
       <c r="Q45" s="26">
         <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6972,16 +6824,8 @@
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="O46" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P46" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O46" s="20" t="n"/>
+      <c r="P46" s="20" t="n"/>
       <c r="Q46" s="26">
         <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7103,16 +6947,8 @@
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="O47" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P47" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O47" s="20" t="n"/>
+      <c r="P47" s="20" t="n"/>
       <c r="Q47" s="26">
         <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7234,16 +7070,8 @@
           <t>EW (CGV 동백 외)</t>
         </is>
       </c>
-      <c r="O48" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P48" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O48" s="20" t="n"/>
+      <c r="P48" s="20" t="n"/>
       <c r="Q48" s="26">
         <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7367,16 +7195,8 @@
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O49" s="155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O49" s="155" t="n"/>
+      <c r="P49" s="85" t="n"/>
       <c r="Q49" s="157">
         <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7490,16 +7310,8 @@
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O50" s="155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P50" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O50" s="155" t="n"/>
+      <c r="P50" s="85" t="n"/>
       <c r="Q50" s="157">
         <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7613,16 +7425,8 @@
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O51" s="12" t="n"/>
+      <c r="P51" s="12" t="n"/>
       <c r="Q51" s="18">
         <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE()),""))</f>
         <v/>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="FxRateTable">환율!$A$7:$D$34</definedName>
     <definedName name="RemitTable1">외화송금내역!$A$3:$L$34</definedName>
     <definedName name="RemitTable2">외화송금내역!$A$37:$L$74</definedName>
+    <definedName name="FxRateTable">환율!$A$7:$D$37</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16096,7 +16096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -16631,6 +16631,38 @@
       </c>
       <c r="D35" s="7" t="n">
         <v>1479.34</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="144" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B36" s="144" t="n">
+        <v>46144</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1476.92</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="144" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B37" s="144" t="n">
+        <v>46151</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1476.35</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -5098,8 +5098,16 @@
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="O32" s="20" t="n"/>
-      <c r="P32" s="20" t="n"/>
+      <c r="O32" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P32" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q32" s="26">
         <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5221,8 +5229,16 @@
           <t>HFR License</t>
         </is>
       </c>
-      <c r="O33" s="20" t="n"/>
-      <c r="P33" s="20" t="n"/>
+      <c r="O33" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P33" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q33" s="26">
         <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5344,8 +5360,16 @@
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="O34" s="20" t="n"/>
-      <c r="P34" s="20" t="n"/>
+      <c r="O34" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q34" s="26">
         <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5467,8 +5491,16 @@
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="O35" s="20" t="n"/>
-      <c r="P35" s="20" t="n"/>
+      <c r="O35" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P35" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q35" s="26">
         <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5590,8 +5622,16 @@
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="O36" s="20" t="n"/>
-      <c r="P36" s="20" t="n"/>
+      <c r="O36" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P36" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q36" s="26">
         <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5713,8 +5753,16 @@
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="O37" s="20" t="n"/>
-      <c r="P37" s="20" t="n"/>
+      <c r="O37" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P37" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q37" s="26">
         <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5838,8 +5886,16 @@
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="O38" s="20" t="n"/>
-      <c r="P38" s="20" t="n"/>
+      <c r="O38" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P38" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q38" s="26">
         <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5961,8 +6017,16 @@
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="O39" s="20" t="n"/>
-      <c r="P39" s="20" t="n"/>
+      <c r="O39" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P39" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q39" s="26">
         <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6086,8 +6150,16 @@
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="O40" s="20" t="n"/>
-      <c r="P40" s="20" t="n"/>
+      <c r="O40" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P40" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q40" s="26">
         <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6209,8 +6281,16 @@
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="O41" s="20" t="n"/>
-      <c r="P41" s="20" t="n"/>
+      <c r="O41" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P41" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q41" s="26">
         <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6332,8 +6412,16 @@
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="O42" s="20" t="n"/>
-      <c r="P42" s="20" t="n"/>
+      <c r="O42" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P42" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q42" s="26">
         <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6455,8 +6543,16 @@
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="O43" s="20" t="n"/>
-      <c r="P43" s="20" t="n"/>
+      <c r="O43" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q43" s="26">
         <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6578,8 +6674,16 @@
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="O44" s="20" t="n"/>
-      <c r="P44" s="20" t="n"/>
+      <c r="O44" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P44" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q44" s="26">
         <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6701,8 +6805,16 @@
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="O45" s="20" t="n"/>
-      <c r="P45" s="20" t="n"/>
+      <c r="O45" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P45" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q45" s="26">
         <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6824,8 +6936,16 @@
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="O46" s="20" t="n"/>
-      <c r="P46" s="20" t="n"/>
+      <c r="O46" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P46" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q46" s="26">
         <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6947,8 +7067,16 @@
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="O47" s="20" t="n"/>
-      <c r="P47" s="20" t="n"/>
+      <c r="O47" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P47" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q47" s="26">
         <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7070,8 +7198,16 @@
           <t>EW (CGV 동백 외)</t>
         </is>
       </c>
-      <c r="O48" s="20" t="n"/>
-      <c r="P48" s="20" t="n"/>
+      <c r="O48" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P48" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q48" s="26">
         <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7195,8 +7331,16 @@
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O49" s="155" t="n"/>
-      <c r="P49" s="85" t="n"/>
+      <c r="O49" s="155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q49" s="157">
         <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7310,8 +7454,16 @@
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O50" s="155" t="n"/>
-      <c r="P50" s="85" t="n"/>
+      <c r="O50" s="155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q50" s="157">
         <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7425,8 +7577,16 @@
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q51" s="18">
         <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE()),""))</f>
         <v/>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -4949,12 +4949,12 @@
       </c>
       <c r="C31" s="78" t="inlineStr">
         <is>
-          <t>Elicent</t>
+          <t>MAICO Italia</t>
         </is>
       </c>
       <c r="D31" s="78" t="inlineStr">
         <is>
-          <t>T/T (EUR)</t>
+          <t>100% TT in advance</t>
         </is>
       </c>
       <c r="E31" s="78" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="N31" s="78" t="inlineStr">
         <is>
-          <t>AXC 200 ELICENT 60ea (EUR / 재고)</t>
+          <t>AXC 200 ELICENT VENTILATORE/FAN (60EA, EUR)</t>
         </is>
       </c>
       <c r="O31" s="149" t="n"/>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="C32" s="103" t="inlineStr">
         <is>
-          <t>Elicent (EUR)</t>
+          <t>MAICO Italia (EUR)</t>
         </is>
       </c>
       <c r="D32" s="102" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="C70" s="103" t="inlineStr">
         <is>
-          <t>Elicent</t>
+          <t>MAICO Italia</t>
         </is>
       </c>
       <c r="D70" s="104" t="n">

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="Q5" s="7">
-        <f>IF(P5="","",IFERROR(VLOOKUP(O5,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P5="","",IFERROR(VLOOKUP(O5,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R5" s="7">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="Q6" s="7">
-        <f>IF(P6="","",IFERROR(VLOOKUP(O6,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P6="","",IFERROR(VLOOKUP(O6,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R6" s="7">
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="Q7" s="7">
-        <f>IF(P7="","",IFERROR(VLOOKUP(O7,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P7="","",IFERROR(VLOOKUP(O7,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R7" s="7">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="Q9" s="7">
-        <f>IF(P9="","",IFERROR(VLOOKUP(O9,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P9="","",IFERROR(VLOOKUP(O9,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R9" s="7">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="Q10" s="7">
-        <f>IF(P10="","",IFERROR(VLOOKUP(O10,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P10="","",IFERROR(VLOOKUP(O10,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R10" s="7">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="Q11" s="7">
-        <f>IF(P11="","",IFERROR(VLOOKUP(O11,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P11="","",IFERROR(VLOOKUP(O11,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R11" s="7">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="Q12" s="7">
-        <f>IF(P12="","",IFERROR(VLOOKUP(O12,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P12="","",IFERROR(VLOOKUP(O12,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R12" s="7">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="Q13" s="7">
-        <f>IF(P13="","",IFERROR(VLOOKUP(O13,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P13="","",IFERROR(VLOOKUP(O13,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R13" s="7">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="Q14" s="7">
-        <f>IF(P14="","",IFERROR(VLOOKUP(O14,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P14="","",IFERROR(VLOOKUP(O14,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R14" s="7">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="Q15" s="7">
-        <f>IF(P15="","",IFERROR(VLOOKUP(O15,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P15="","",IFERROR(VLOOKUP(O15,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R15" s="7">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="Q16" s="7">
-        <f>IF(P16="","",IFERROR(VLOOKUP(O16,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P16="","",IFERROR(VLOOKUP(O16,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R16" s="7">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="Q17" s="7">
-        <f>IF(P17="","",IFERROR(VLOOKUP(O17,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P17="","",IFERROR(VLOOKUP(O17,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R17" s="7">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="Q18" s="7">
-        <f>IF(P18="","",IFERROR(VLOOKUP(O18,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P18="","",IFERROR(VLOOKUP(O18,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R18" s="7">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="Q19" s="7">
-        <f>IF(P19="","",IFERROR(VLOOKUP(O19,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P19="","",IFERROR(VLOOKUP(O19,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R19" s="7">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="Q20" s="7">
-        <f>IF(P20="","",IFERROR(VLOOKUP(O20,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P20="","",IFERROR(VLOOKUP(O20,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R20" s="7">
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Q21" s="7">
-        <f>IF(P21="","",IFERROR(VLOOKUP(O21,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P21="","",IFERROR(VLOOKUP(O21,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R21" s="7">
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="Q23" s="7">
-        <f>IF(P23="","",IFERROR(VLOOKUP(O23,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P23="","",IFERROR(VLOOKUP(O23,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R23" s="7">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="Q24" s="7">
-        <f>IF(P24="","",IFERROR(VLOOKUP(O24,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P24="","",IFERROR(VLOOKUP(O24,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R24" s="7">
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="Q25" s="7">
-        <f>IF(P25="","",IFERROR(VLOOKUP(O25,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P25="","",IFERROR(VLOOKUP(O25,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R25" s="7">
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="Q26" s="7">
-        <f>IF(P26="","",IFERROR(VLOOKUP(O26,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P26="","",IFERROR(VLOOKUP(O26,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R26" s="7">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="Q27" s="7">
-        <f>IF(P27="","",IFERROR(VLOOKUP(O27,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P27="","",IFERROR(VLOOKUP(O27,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R27" s="7">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="Q28" s="7">
-        <f>IF(P28="","",IFERROR(VLOOKUP(O28,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P28="","",IFERROR(VLOOKUP(O28,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R28" s="7">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="Q29" s="151">
-        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R29" s="80">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="Q30" s="151">
-        <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R30" s="80">
@@ -4994,7 +4994,7 @@
       <c r="O31" s="149" t="n"/>
       <c r="P31" s="78" t="n"/>
       <c r="Q31" s="151">
-        <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R31" s="80">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="Q32" s="26">
-        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R32" s="26">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="Q33" s="26">
-        <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R33" s="26">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="Q34" s="26">
-        <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R34" s="26">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="Q35" s="26">
-        <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R35" s="26">
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="Q36" s="26">
-        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R36" s="26">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="Q37" s="26">
-        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R37" s="26">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="Q38" s="26">
-        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R38" s="26">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="Q39" s="26">
-        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R39" s="26">
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="Q40" s="26">
-        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R40" s="26">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="Q41" s="26">
-        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R41" s="26">
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="Q42" s="26">
-        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R42" s="26">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="Q43" s="26">
-        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R43" s="26">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="Q44" s="26">
-        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R44" s="26">
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="Q45" s="26">
-        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R45" s="26">
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Q46" s="26">
-        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R46" s="26">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="Q47" s="26">
-        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R47" s="26">
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="Q48" s="26">
-        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R48" s="26">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Q49" s="157">
-        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R49" s="87">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="Q50" s="157">
-        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R50" s="87">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Q51" s="18">
-        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R51" s="18">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="Q52" s="18">
-        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P52="","",IFERROR(VLOOKUP(O52,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R52" s="18">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="Q53" s="7">
-        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R53" s="7">

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -989,69 +989,62 @@
     <author>RNR 재무팀</author>
   </authors>
   <commentList>
-    <comment ref="S6" authorId="0" shapeId="0">
+    <comment ref="S7" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8543 — 디지털시네마 서버/IMB
 (정보기술협정 양허품목)</t>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S11" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8518/8543 디지털시네마장비</t>
       </text>
     </comment>
-    <comment ref="S12" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8543 — 디지털시네마 프로젝터
 (정보기술협정 양허품목)</t>
       </text>
     </comment>
-    <comment ref="S14" authorId="0" shapeId="0">
+    <comment ref="S15" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8414.59 — Projector cooling fan
 (WTO 협정세율 0%)</t>
       </text>
     </comment>
-    <comment ref="S15" authorId="0" shapeId="0">
+    <comment ref="S16" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8518/8543 디지털시네마장비</t>
       </text>
     </comment>
-    <comment ref="S16" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 Fedex 직통관 (관세사 미경유)</t>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8543 — 디지털시네마 서버/IMB
 (정보기술협정 양허품목)</t>
       </text>
     </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8518/8543 디지털시네마장비</t>
       </text>
     </comment>
-    <comment ref="S23" authorId="0" shapeId="0">
+    <comment ref="S24" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 Fedex 직통관 (관세사 미경유)</t>
-      </text>
-    </comment>
-    <comment ref="S24" authorId="0" shapeId="0">
-      <text>
-        <t>ITA(정보기술협정) 관세면제
-HS 8543 — 디지털시네마 서버/IMB
-(정보기술협정 양허품목)</t>
       </text>
     </comment>
     <comment ref="S25" authorId="0" shapeId="0">
@@ -1062,6 +1055,13 @@
       </text>
     </comment>
     <comment ref="S26" authorId="0" shapeId="0">
+      <text>
+        <t>ITA(정보기술협정) 관세면제
+HS 8543 — 디지털시네마 서버/IMB
+(정보기술협정 양허품목)</t>
+      </text>
+    </comment>
+    <comment ref="S27" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8518/8543 디지털시네마장비</t>
@@ -1612,63 +1612,63 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CPO678-1</t>
+          <t>IPO016</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>Integ Process Group</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>50% TT advance, 50% Net 30</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품</t>
         </is>
       </c>
       <c r="F5" s="143" t="n">
-        <v>45965</v>
+        <v>45881</v>
       </c>
       <c r="G5" s="144" t="n">
-        <v>46007</v>
+        <v>46146</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>139083</v>
+        <v>6800</v>
       </c>
       <c r="I5" s="145">
-        <f>IFERROR(VLOOKUP(B5,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B5,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J5" s="9" t="n">
-        <v>212471386</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9">
         <f>IFERROR(ROUND(H5*I5,0),0)</f>
         <v/>
       </c>
       <c r="L5" s="9">
-        <f>IFERROR(VLOOKUP(B5,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B5,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M5" s="9">
-        <f>IFERROR(VLOOKUP(B5,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B5,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Projector</t>
+          <t>JNIOR Model 410 (20EA)</t>
         </is>
       </c>
       <c r="O5" s="144" t="n">
-        <v>46002</v>
+        <v>45905</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>1219925801471M</t>
+          <t>883504210357</t>
         </is>
       </c>
       <c r="Q5" s="7">
@@ -1680,50 +1680,48 @@
         <v/>
       </c>
       <c r="S5" s="9" t="n">
-        <v>1682291</v>
+        <v>0</v>
       </c>
       <c r="T5" s="9" t="n">
-        <v>20784342</v>
-      </c>
-      <c r="U5" s="143" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
+        <v>954760</v>
+      </c>
+      <c r="U5" s="143" t="n">
+        <v>45905</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>다민관세사</t>
+          <t>인천세관</t>
         </is>
       </c>
       <c r="W5" s="9" t="n">
-        <v>149729</v>
+        <v>0</v>
       </c>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>진로직스</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>2470670</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="9">
         <f>S5+T5+W5</f>
         <v/>
       </c>
-      <c r="AA5" s="10">
-        <f>K5+L5+M5+IFERROR(VLOOKUP(B5,RemitTable2,9,FALSE()),0)+Y5+Z5</f>
+      <c r="AA5" s="175">
+        <f>K5+L5+M5+IFERROR(VLOOKUP(B5,RemitTable2,9,FALSE),0)+Y5+Z5</f>
         <v/>
       </c>
       <c r="AB5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="10">
+        <v>20</v>
+      </c>
+      <c r="AC5" s="175">
         <f>ROUND(AA5/AB5,0)</f>
         <v/>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr">
@@ -1743,17 +1741,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>GPO451</t>
+          <t>CPO678-1</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1762,20 +1760,20 @@
         </is>
       </c>
       <c r="F6" s="143" t="n">
-        <v>45982</v>
+        <v>45965</v>
       </c>
       <c r="G6" s="144" t="n">
-        <v>46020</v>
+        <v>46007</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>9060</v>
+        <v>139083</v>
       </c>
       <c r="I6" s="145">
         <f>IFERROR(VLOOKUP(B6,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J6" s="9" t="n">
-        <v>18264679</v>
+        <v>212471386</v>
       </c>
       <c r="K6" s="9">
         <f>IFERROR(ROUND(H6*I6,0),0)</f>
@@ -1791,15 +1789,15 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>IMB/Server</t>
+          <t>Projector</t>
         </is>
       </c>
       <c r="O6" s="144" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>2317625939353M</t>
+          <t>1219925801471M</t>
         </is>
       </c>
       <c r="Q6" s="7">
@@ -1811,31 +1809,31 @@
         <v/>
       </c>
       <c r="S6" s="9" t="n">
-        <v>0</v>
+        <v>1682291</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>1352610</v>
+        <v>20784342</v>
       </c>
       <c r="U6" s="143" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>다민관세사</t>
         </is>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0</v>
+        <v>149729</v>
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>Fedex</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>0</v>
+        <v>2470670</v>
       </c>
       <c r="Z6" s="9">
         <f>S6+T6+W6</f>
@@ -1874,39 +1872,39 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>CPO679</t>
+          <t>GPO451</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F7" s="143" t="n">
-        <v>45987</v>
+        <v>45982</v>
       </c>
       <c r="G7" s="144" t="n">
-        <v>46007</v>
+        <v>46020</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>4474</v>
+        <v>9060</v>
       </c>
       <c r="I7" s="145">
         <f>IFERROR(VLOOKUP(B7,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>212471386</v>
+        <v>18264679</v>
       </c>
       <c r="K7" s="9">
         <f>IFERROR(ROUND(H7*I7,0),0)</f>
@@ -1922,15 +1920,15 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>IMB/Server</t>
         </is>
       </c>
       <c r="O7" s="144" t="n">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>1421425100697M</t>
+          <t>2317625939353M</t>
         </is>
       </c>
       <c r="Q7" s="7">
@@ -1942,31 +1940,31 @@
         <v/>
       </c>
       <c r="S7" s="9" t="n">
-        <v>560630</v>
+        <v>0</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>756850</v>
+        <v>1352610</v>
       </c>
       <c r="U7" s="143" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>아인관세사</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W7" s="9" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>진로직스</t>
+          <t>Fedex</t>
         </is>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>590823</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="9">
         <f>S7+T7+W7</f>
@@ -1985,261 +1983,261 @@
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>CPO679</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="F8" s="143" t="n">
+        <v>45987</v>
+      </c>
+      <c r="G8" s="144" t="n">
+        <v>46007</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>4474</v>
+      </c>
+      <c r="I8" s="145">
+        <f>IFERROR(VLOOKUP(B8,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>212471386</v>
+      </c>
+      <c r="K8" s="9">
+        <f>IFERROR(ROUND(H8*I8,0),0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="9">
+        <f>IFERROR(VLOOKUP(B8,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="9">
+        <f>IFERROR(VLOOKUP(B8,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="O8" s="144" t="n">
+        <v>45989</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>1421425100697M</t>
+        </is>
+      </c>
+      <c r="Q8" s="7">
+        <f>IF(P8="","",IFERROR(VLOOKUP(O8,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R8" s="7">
+        <f>IF(P8="","",H8)</f>
+        <v/>
+      </c>
+      <c r="S8" s="9" t="n">
+        <v>560630</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>756850</v>
+      </c>
+      <c r="U8" s="143" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>아인관세사</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="n">
+        <v>36000</v>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>590823</v>
+      </c>
+      <c r="Z8" s="9">
+        <f>S8+T8+W8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="10">
+        <f>K8+L8+M8+IFERROR(VLOOKUP(B8,RemitTable2,9,FALSE()),0)+Y8+Z8</f>
+        <v/>
+      </c>
+      <c r="AB8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="10">
+        <f>ROUND(AA8/AB8,0)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr">
+      <c r="AE8" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>CPO684</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>부품</t>
         </is>
       </c>
-      <c r="F8" s="146" t="n">
+      <c r="F9" s="146" t="n">
         <v>45993</v>
       </c>
-      <c r="G8" s="147" t="inlineStr">
+      <c r="G9" s="147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H9" s="16" t="n">
         <v>362.25</v>
       </c>
-      <c r="I8" s="148">
-        <f>IFERROR(VLOOKUP(B8,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18">
-        <f>IFERROR(ROUND(H8*I8,0),0)</f>
-        <v/>
-      </c>
-      <c r="L8" s="18">
-        <f>IFERROR(VLOOKUP(B8,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="18">
-        <f>IFERROR(VLOOKUP(B8,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="I9" s="148">
+        <f>IFERROR(VLOOKUP(B9,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="18">
+        <f>IFERROR(ROUND(H9*I9,0),0)</f>
+        <v/>
+      </c>
+      <c r="L9" s="18">
+        <f>IFERROR(VLOOKUP(B9,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M9" s="18">
+        <f>IFERROR(VLOOKUP(B9,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t>Parts (국내)</t>
         </is>
       </c>
-      <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="18" t="n"/>
-      <c r="R8" s="18" t="n"/>
-      <c r="S8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="12" t="inlineStr">
+      <c r="O9" s="12" t="n"/>
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="18" t="n"/>
+      <c r="R9" s="18" t="n"/>
+      <c r="S9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="13" t="inlineStr">
+      <c r="W9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="18">
-        <f>S8+T8+W8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="18">
-        <f>K8+L8+M8+IFERROR(VLOOKUP(B8,RemitTable2,9,FALSE()),0)+Y8+Z8</f>
-        <v/>
-      </c>
-      <c r="AB8" s="19" t="n">
+      <c r="Y9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="18">
+        <f>S9+T9+W9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="18">
+        <f>K9+L9+M9+IFERROR(VLOOKUP(B9,RemitTable2,9,FALSE()),0)+Y9+Z9</f>
+        <v/>
+      </c>
+      <c r="AB9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="AC8" s="18">
-        <f>ROUND(AA8/AB8,0)</f>
-        <v/>
-      </c>
-      <c r="AD8" s="12" t="n"/>
-      <c r="AE8" s="12" t="inlineStr">
+      <c r="AC9" s="18">
+        <f>ROUND(AA9/AB9,0)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="12" t="n"/>
+      <c r="AE9" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>CPO680</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>부품</t>
-        </is>
-      </c>
-      <c r="F9" s="143" t="n">
-        <v>45995</v>
-      </c>
-      <c r="G9" s="144" t="n">
-        <v>46035</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>252</v>
-      </c>
-      <c r="I9" s="145">
-        <f>IFERROR(VLOOKUP(B9,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>412788</v>
-      </c>
-      <c r="K9" s="9">
-        <f>IFERROR(ROUND(H9*I9,0),0)</f>
-        <v/>
-      </c>
-      <c r="L9" s="9">
-        <f>IFERROR(VLOOKUP(B9,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="9">
-        <f>IFERROR(VLOOKUP(B9,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Parts</t>
-        </is>
-      </c>
-      <c r="O9" s="144" t="n">
-        <v>46002</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>1219925801471M</t>
-        </is>
-      </c>
-      <c r="Q9" s="7">
-        <f>IF(P9="","",IFERROR(VLOOKUP(O9,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R9" s="7">
-        <f>IF(P9="","",H9)</f>
-        <v/>
-      </c>
-      <c r="S9" s="9" t="n">
-        <v>29879</v>
-      </c>
-      <c r="T9" s="9" t="n">
-        <v>37658</v>
-      </c>
-      <c r="U9" s="143" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>다민관세사</t>
-        </is>
-      </c>
-      <c r="W9" s="9" t="n">
-        <v>271</v>
-      </c>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>진로직스</t>
-        </is>
-      </c>
-      <c r="Y9" s="9" t="n">
-        <v>4477</v>
-      </c>
-      <c r="Z9" s="9">
-        <f>S9+T9+W9</f>
-        <v/>
-      </c>
-      <c r="AA9" s="10">
-        <f>K9+L9+M9+IFERROR(VLOOKUP(B9,RemitTable2,9,FALSE()),0)+Y9+Z9</f>
-        <v/>
-      </c>
-      <c r="AB9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="10">
-        <f>ROUND(AA9/AB9,0)</f>
-        <v/>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AF9" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2251,39 +2249,39 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>GPO460</t>
+          <t>CPO680</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품</t>
         </is>
       </c>
       <c r="F10" s="143" t="n">
-        <v>46007</v>
+        <v>45995</v>
       </c>
       <c r="G10" s="144" t="n">
-        <v>46043</v>
+        <v>46035</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>2710</v>
+        <v>252</v>
       </c>
       <c r="I10" s="145">
         <f>IFERROR(VLOOKUP(B10,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>5505104</v>
+        <v>412788</v>
       </c>
       <c r="K10" s="9">
         <f>IFERROR(ROUND(H10*I10,0),0)</f>
@@ -2299,15 +2297,15 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>SR-1000</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="O10" s="144" t="n">
-        <v>46023</v>
+        <v>46002</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>2317626006259M</t>
+          <t>1219925801471M</t>
         </is>
       </c>
       <c r="Q10" s="7">
@@ -2319,31 +2317,31 @@
         <v/>
       </c>
       <c r="S10" s="9" t="n">
-        <v>0</v>
+        <v>29879</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>399770</v>
+        <v>37658</v>
       </c>
       <c r="U10" s="143" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>다민관세사</t>
         </is>
       </c>
       <c r="W10" s="9" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>Fedex</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>0</v>
+        <v>4477</v>
       </c>
       <c r="Z10" s="9">
         <f>S10+T10+W10</f>
@@ -2362,7 +2360,7 @@
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE10" s="3" t="inlineStr">
@@ -2382,17 +2380,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>LPO001</t>
+          <t>GPO460</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>TT Advance</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2404,17 +2402,17 @@
         <v>46007</v>
       </c>
       <c r="G11" s="144" t="n">
-        <v>46052</v>
+        <v>46043</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>5056.8</v>
+        <v>2710</v>
       </c>
       <c r="I11" s="145">
         <f>IFERROR(VLOOKUP(B11,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J11" s="9" t="n">
-        <v>7356514</v>
+        <v>5505104</v>
       </c>
       <c r="K11" s="9">
         <f>IFERROR(ROUND(H11*I11,0),0)</f>
@@ -2430,15 +2428,15 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>ICP+TPC (6EA)</t>
+          <t>SR-1000</t>
         </is>
       </c>
       <c r="O11" s="144" t="n">
-        <v>46090</v>
+        <v>46023</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>1421426100183M</t>
+          <t>2317626006259M</t>
         </is>
       </c>
       <c r="Q11" s="7">
@@ -2450,31 +2448,31 @@
         <v/>
       </c>
       <c r="S11" s="9" t="n">
-        <v>240450</v>
+        <v>0</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>831820</v>
+        <v>399770</v>
       </c>
       <c r="U11" s="143" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>아인관세사</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W11" s="9" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>진로직스</t>
+          <t>Fedex</t>
         </is>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>581438</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="9">
         <f>S11+T11+W11</f>
@@ -2485,7 +2483,7 @@
         <v/>
       </c>
       <c r="AB11" s="11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC11" s="10">
         <f>ROUND(AA11/AB11,0)</f>
@@ -2493,7 +2491,7 @@
       </c>
       <c r="AD11" s="3" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE11" s="3" t="inlineStr">
@@ -2513,17 +2511,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CPO678-2</t>
+          <t>LPO001</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>TT Advance</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -2532,20 +2530,20 @@
         </is>
       </c>
       <c r="F12" s="143" t="n">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="G12" s="144" t="n">
-        <v>46087</v>
+        <v>46052</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>137850</v>
+        <v>5056.8</v>
       </c>
       <c r="I12" s="145">
         <f>IFERROR(VLOOKUP(B12,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>203737212</v>
+        <v>7356514</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(ROUND(H12*I12,0),0)</f>
@@ -2561,15 +2559,15 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>CP4425-RGB Projector (3EA)</t>
+          <t>ICP+TPC (6EA)</t>
         </is>
       </c>
       <c r="O12" s="144" t="n">
-        <v>46030</v>
+        <v>46090</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>1400826101004M</t>
+          <t>1421426100183M</t>
         </is>
       </c>
       <c r="Q12" s="7">
@@ -2581,23 +2579,23 @@
         <v/>
       </c>
       <c r="S12" s="9" t="n">
-        <v>0</v>
+        <v>240450</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>19976300</v>
+        <v>831820</v>
       </c>
       <c r="U12" s="143" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>조운관세사</t>
+          <t>아인관세사</t>
         </is>
       </c>
       <c r="W12" s="9" t="n">
-        <v>263400</v>
+        <v>36000</v>
       </c>
       <c r="X12" s="4" t="inlineStr">
         <is>
@@ -2605,7 +2603,7 @@
         </is>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>2385057</v>
+        <v>581438</v>
       </c>
       <c r="Z12" s="9">
         <f>S12+T12+W12</f>
@@ -2616,7 +2614,7 @@
         <v/>
       </c>
       <c r="AB12" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC12" s="10">
         <f>ROUND(AA12/AB12,0)</f>
@@ -2624,7 +2622,7 @@
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="AE12" s="3" t="inlineStr">
@@ -2644,7 +2642,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>CPO682</t>
+          <t>CPO678-2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2663,20 +2661,20 @@
         </is>
       </c>
       <c r="F13" s="143" t="n">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="G13" s="144" t="n">
-        <v>46057</v>
+        <v>46087</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>20174</v>
+        <v>137850</v>
       </c>
       <c r="I13" s="145">
         <f>IFERROR(VLOOKUP(B13,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>36117425</v>
+        <v>203737212</v>
       </c>
       <c r="K13" s="9">
         <f>IFERROR(ROUND(H13*I13,0),0)</f>
@@ -2692,15 +2690,15 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Projector + Touch Screen (2EA)</t>
+          <t>CP4425-RGB Projector (3EA)</t>
         </is>
       </c>
       <c r="O13" s="144" t="n">
-        <v>46015</v>
+        <v>46030</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>1400825101450M</t>
+          <t>1400826101004M</t>
         </is>
       </c>
       <c r="Q13" s="7">
@@ -2712,23 +2710,23 @@
         <v/>
       </c>
       <c r="S13" s="9" t="n">
-        <v>84170</v>
+        <v>0</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>3156262</v>
+        <v>19976300</v>
       </c>
       <c r="U13" s="143" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>아인관세사</t>
+          <t>조운관세사</t>
         </is>
       </c>
       <c r="W13" s="9" t="n">
-        <v>92978</v>
+        <v>263400</v>
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
@@ -2736,7 +2734,7 @@
         </is>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>1864148</v>
+        <v>2385057</v>
       </c>
       <c r="Z13" s="9">
         <f>S13+T13+W13</f>
@@ -2747,7 +2745,7 @@
         <v/>
       </c>
       <c r="AB13" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC13" s="10">
         <f>ROUND(AA13/AB13,0)</f>
@@ -2755,7 +2753,7 @@
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE13" s="3" t="inlineStr">
@@ -2775,7 +2773,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>CPO683</t>
+          <t>CPO682</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2800,7 +2798,7 @@
         <v>46057</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4620</v>
+        <v>20174</v>
       </c>
       <c r="I14" s="145">
         <f>IFERROR(VLOOKUP(B14,RemitTable2,7,FALSE()),0)</f>
@@ -2823,7 +2821,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Fan (15EA)</t>
+          <t>Projector + Touch Screen (2EA)</t>
         </is>
       </c>
       <c r="O14" s="144" t="n">
@@ -2843,10 +2841,10 @@
         <v/>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0</v>
+        <v>84170</v>
       </c>
       <c r="T14" s="9" t="n">
-        <v>722808</v>
+        <v>3156262</v>
       </c>
       <c r="U14" s="143" t="inlineStr">
         <is>
@@ -2859,7 +2857,7 @@
         </is>
       </c>
       <c r="W14" s="9" t="n">
-        <v>14422</v>
+        <v>92978</v>
       </c>
       <c r="X14" s="4" t="inlineStr">
         <is>
@@ -2867,7 +2865,7 @@
         </is>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>426904</v>
+        <v>1864148</v>
       </c>
       <c r="Z14" s="9">
         <f>S14+T14+W14</f>
@@ -2906,17 +2904,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>MPO66</t>
+          <t>CPO683</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>T/T</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -2925,20 +2923,20 @@
         </is>
       </c>
       <c r="F15" s="143" t="n">
-        <v>46011</v>
+        <v>46010</v>
       </c>
       <c r="G15" s="144" t="n">
-        <v>46043</v>
+        <v>46057</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>9626.35</v>
+        <v>4620</v>
       </c>
       <c r="I15" s="145">
         <f>IFERROR(VLOOKUP(B15,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>14256012</v>
+        <v>36117425</v>
       </c>
       <c r="K15" s="9">
         <f>IFERROR(ROUND(H15*I15,0),0)</f>
@@ -2954,15 +2952,15 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>DCO-16000/L-SUB (13EA)</t>
+          <t>Fan (15EA)</t>
         </is>
       </c>
       <c r="O15" s="144" t="n">
-        <v>46072</v>
+        <v>46015</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>1421426100153M</t>
+          <t>1400825101450M</t>
         </is>
       </c>
       <c r="Q15" s="7">
@@ -2977,11 +2975,11 @@
         <v>0</v>
       </c>
       <c r="T15" s="9" t="n">
-        <v>1704871</v>
+        <v>722808</v>
       </c>
       <c r="U15" s="143" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
@@ -2990,7 +2988,7 @@
         </is>
       </c>
       <c r="W15" s="9" t="n">
-        <v>93591</v>
+        <v>14422</v>
       </c>
       <c r="X15" s="4" t="inlineStr">
         <is>
@@ -2998,7 +2996,7 @@
         </is>
       </c>
       <c r="Y15" s="9" t="n">
-        <v>2690702</v>
+        <v>426904</v>
       </c>
       <c r="Z15" s="9">
         <f>S15+T15+W15</f>
@@ -3009,7 +3007,7 @@
         <v/>
       </c>
       <c r="AB15" s="11" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AC15" s="10">
         <f>ROUND(AA15/AB15,0)</f>
@@ -3017,7 +3015,7 @@
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE15" s="3" t="inlineStr">
@@ -3037,7 +3035,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>MPO65</t>
+          <t>MPO66</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3059,17 +3057,17 @@
         <v>46011</v>
       </c>
       <c r="G16" s="144" t="n">
-        <v>46007</v>
+        <v>46043</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>4936</v>
+        <v>9626.35</v>
       </c>
       <c r="I16" s="145">
         <f>IFERROR(VLOOKUP(B16,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>22306800</v>
+        <v>14256012</v>
       </c>
       <c r="K16" s="9">
         <f>IFERROR(ROUND(H16*I16,0),0)</f>
@@ -3085,7 +3083,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Audio Amp</t>
+          <t>DCO-16000/L-SUB (13EA)</t>
         </is>
       </c>
       <c r="O16" s="144" t="n">
@@ -3108,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="9" t="n">
-        <v>874189</v>
+        <v>1704871</v>
       </c>
       <c r="U16" s="143" t="inlineStr">
         <is>
@@ -3121,7 +3119,7 @@
         </is>
       </c>
       <c r="W16" s="9" t="n">
-        <v>47990</v>
+        <v>93591</v>
       </c>
       <c r="X16" s="4" t="inlineStr">
         <is>
@@ -3129,7 +3127,7 @@
         </is>
       </c>
       <c r="Y16" s="9" t="n">
-        <v>1379682</v>
+        <v>2690702</v>
       </c>
       <c r="Z16" s="9">
         <f>S16+T16+W16</f>
@@ -3140,7 +3138,7 @@
         <v/>
       </c>
       <c r="AB16" s="11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AC16" s="10">
         <f>ROUND(AA16/AB16,0)</f>
@@ -3168,39 +3166,39 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CPO689</t>
+          <t>MPO65</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>T/T</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F17" s="143" t="n">
-        <v>46025</v>
+        <v>46011</v>
       </c>
       <c r="G17" s="144" t="n">
-        <v>46072</v>
+        <v>46007</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>2745</v>
+        <v>4936</v>
       </c>
       <c r="I17" s="145">
         <f>IFERROR(VLOOKUP(B17,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>25506948</v>
+        <v>22306800</v>
       </c>
       <c r="K17" s="9">
         <f>IFERROR(ROUND(H17*I17,0),0)</f>
@@ -3216,15 +3214,15 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Audio Amp</t>
         </is>
       </c>
       <c r="O17" s="144" t="n">
-        <v>46042</v>
+        <v>46072</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>2317626055855M</t>
+          <t>1421426100153M</t>
         </is>
       </c>
       <c r="Q17" s="7">
@@ -3236,31 +3234,31 @@
         <v/>
       </c>
       <c r="S17" s="9" t="n">
-        <v>20430</v>
+        <v>0</v>
       </c>
       <c r="T17" s="9" t="n">
-        <v>409790</v>
+        <v>874189</v>
       </c>
       <c r="U17" s="143" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아인관세사</t>
         </is>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0</v>
+        <v>47990</v>
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>Fedex</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>162080</v>
+        <v>1379682</v>
       </c>
       <c r="Z17" s="9">
         <f>S17+T17+W17</f>
@@ -3279,7 +3277,7 @@
       </c>
       <c r="AD17" s="3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="AE17" s="3" t="inlineStr">
@@ -3299,39 +3297,39 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>GPO467</t>
+          <t>CPO689</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품</t>
         </is>
       </c>
       <c r="F18" s="143" t="n">
-        <v>46029</v>
+        <v>46025</v>
       </c>
       <c r="G18" s="144" t="n">
-        <v>46113</v>
+        <v>46072</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1700</v>
+        <v>2745</v>
       </c>
       <c r="I18" s="145">
         <f>IFERROR(VLOOKUP(B18,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>9919642</v>
+        <v>25506948</v>
       </c>
       <c r="K18" s="9">
         <f>IFERROR(ROUND(H18*I18,0),0)</f>
@@ -3347,15 +3345,15 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>SR-1000 Face Plate(20)+Security Gate(10)</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="O18" s="144" t="n">
-        <v>46056</v>
+        <v>46042</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>2317626105219M</t>
+          <t>2317626055855M</t>
         </is>
       </c>
       <c r="Q18" s="7">
@@ -3367,14 +3365,14 @@
         <v/>
       </c>
       <c r="S18" s="9" t="n">
-        <v>0</v>
+        <v>20430</v>
       </c>
       <c r="T18" s="9" t="n">
-        <v>250080</v>
+        <v>409790</v>
       </c>
       <c r="U18" s="143" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -3391,7 +3389,7 @@
         </is>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>136050</v>
+        <v>162080</v>
       </c>
       <c r="Z18" s="9">
         <f>S18+T18+W18</f>
@@ -3402,7 +3400,7 @@
         <v/>
       </c>
       <c r="AB18" s="11" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="AC18" s="10">
         <f>ROUND(AA18/AB18,0)</f>
@@ -3410,7 +3408,7 @@
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE18" s="3" t="inlineStr">
@@ -3430,59 +3428,63 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>CPO692-1</t>
+          <t>GPO467</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>부품(렌즈)</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F19" s="143" t="n">
-        <v>46035</v>
+        <v>46029</v>
       </c>
       <c r="G19" s="144" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>11000</v>
-      </c>
-      <c r="I19" s="145" t="n">
-        <v>1482.8</v>
+        <v>1700</v>
+      </c>
+      <c r="I19" s="145">
+        <f>IFERROR(VLOOKUP(B19,RemitTable2,7,FALSE()),0)</f>
+        <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>16310800</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>16310800</v>
-      </c>
-      <c r="L19" s="9" t="n">
-        <v>462</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>296</v>
+        <v>9919642</v>
+      </c>
+      <c r="K19" s="9">
+        <f>IFERROR(ROUND(H19*I19,0),0)</f>
+        <v/>
+      </c>
+      <c r="L19" s="9">
+        <f>IFERROR(VLOOKUP(B19,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M19" s="9">
+        <f>IFERROR(VLOOKUP(B19,RemitTable2,11,FALSE()),0)</f>
+        <v/>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Lens (2EA)</t>
+          <t>SR-1000 Face Plate(20)+Security Gate(10)</t>
         </is>
       </c>
       <c r="O19" s="144" t="n">
-        <v>46064</v>
+        <v>46056</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>2235626138790M</t>
+          <t>2317626105219M</t>
         </is>
       </c>
       <c r="Q19" s="7">
@@ -3494,14 +3496,14 @@
         <v/>
       </c>
       <c r="S19" s="9" t="n">
-        <v>1297810</v>
+        <v>0</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>1752040</v>
+        <v>250080</v>
       </c>
       <c r="U19" s="143" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
@@ -3514,24 +3516,26 @@
       </c>
       <c r="X19" s="4" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Fedex</t>
         </is>
       </c>
       <c r="Y19" s="9" t="n">
-        <v>1553086</v>
+        <v>136050</v>
       </c>
       <c r="Z19" s="9">
         <f>S19+T19+W19</f>
         <v/>
       </c>
-      <c r="AA19" s="10" t="n">
-        <v>20915590</v>
+      <c r="AA19" s="10">
+        <f>K19+L19+M19+IFERROR(VLOOKUP(B19,RemitTable2,9,FALSE()),0)+Y19+Z19</f>
+        <v/>
       </c>
       <c r="AB19" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC19" s="10" t="n">
-        <v>10457795</v>
+        <v>30</v>
+      </c>
+      <c r="AC19" s="10">
+        <f>ROUND(AA19/AB19,0)</f>
+        <v/>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
@@ -3555,7 +3559,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>CPO692-2</t>
+          <t>CPO692-1</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3570,7 +3574,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품(렌즈)</t>
         </is>
       </c>
       <c r="F20" s="143" t="n">
@@ -3580,34 +3584,34 @@
         <v>46134</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>286580</v>
+        <v>11000</v>
       </c>
       <c r="I20" s="145" t="n">
         <v>1482.8</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>424990980</v>
+        <v>16310800</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>424990980</v>
+        <v>16310800</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>12038</v>
+        <v>462</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>7704</v>
+        <v>296</v>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Projector+Lens+ASSY (28EA)</t>
+          <t>Lens (2EA)</t>
         </is>
       </c>
       <c r="O20" s="144" t="n">
-        <v>46073</v>
+        <v>46064</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>1400826101051M</t>
+          <t>2235626138790M</t>
         </is>
       </c>
       <c r="Q20" s="7">
@@ -3619,44 +3623,44 @@
         <v/>
       </c>
       <c r="S20" s="9" t="n">
-        <v>3450410</v>
+        <v>1297810</v>
       </c>
       <c r="T20" s="9" t="n">
-        <v>42329590</v>
+        <v>1752040</v>
       </c>
       <c r="U20" s="143" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>조운관세사</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W20" s="9" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="X20" s="4" t="inlineStr">
         <is>
-          <t>진로직스</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="Y20" s="9" t="n">
-        <v>2649525</v>
+        <v>1553086</v>
       </c>
       <c r="Z20" s="9">
         <f>S20+T20+W20</f>
         <v/>
       </c>
       <c r="AA20" s="10" t="n">
-        <v>473718807</v>
+        <v>20915590</v>
       </c>
       <c r="AB20" s="11" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC20" s="10" t="n">
-        <v>16918529</v>
+        <v>10457795</v>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
@@ -3680,7 +3684,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CPO690</t>
+          <t>CPO692-2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3695,48 +3699,44 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F21" s="143" t="n">
-        <v>46050</v>
+        <v>46035</v>
       </c>
       <c r="G21" s="144" t="n">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>9740</v>
-      </c>
-      <c r="I21" s="145">
-        <f>IFERROR(VLOOKUP(B21,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+        <v>286580</v>
+      </c>
+      <c r="I21" s="145" t="n">
+        <v>1482.8</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>51777431</v>
-      </c>
-      <c r="K21" s="9">
-        <f>IFERROR(ROUND(H21*I21,0),0)</f>
-        <v/>
-      </c>
-      <c r="L21" s="9">
-        <f>IFERROR(VLOOKUP(B21,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="9">
-        <f>IFERROR(VLOOKUP(B21,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>424990980</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>424990980</v>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>12038</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>7704</v>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>ASSY Liquid Cooling (20EA)</t>
+          <t>Projector+Lens+ASSY (28EA)</t>
         </is>
       </c>
       <c r="O21" s="144" t="n">
-        <v>46053</v>
+        <v>46073</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>2235626096487M</t>
+          <t>1400826101051M</t>
         </is>
       </c>
       <c r="Q21" s="7">
@@ -3748,306 +3748,302 @@
         <v/>
       </c>
       <c r="S21" s="9" t="n">
-        <v>0</v>
+        <v>3450410</v>
       </c>
       <c r="T21" s="9" t="n">
-        <v>1493440</v>
+        <v>42329590</v>
       </c>
       <c r="U21" s="143" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>조운관세사</t>
         </is>
       </c>
       <c r="W21" s="9" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="X21" s="4" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y21" s="9" t="n">
-        <v>1561040</v>
+        <v>2649525</v>
       </c>
       <c r="Z21" s="9">
         <f>S21+T21+W21</f>
         <v/>
       </c>
-      <c r="AA21" s="10">
-        <f>K21+L21+M21+IFERROR(VLOOKUP(B21,RemitTable2,9,FALSE()),0)+Y21+Z21</f>
-        <v/>
+      <c r="AA21" s="10" t="n">
+        <v>473718807</v>
       </c>
       <c r="AB21" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC21" s="10" t="n">
+        <v>16918529</v>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>CPO690</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="F22" s="143" t="n">
+        <v>46050</v>
+      </c>
+      <c r="G22" s="144" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>9740</v>
+      </c>
+      <c r="I22" s="145">
+        <f>IFERROR(VLOOKUP(B22,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>51777431</v>
+      </c>
+      <c r="K22" s="9">
+        <f>IFERROR(ROUND(H22*I22,0),0)</f>
+        <v/>
+      </c>
+      <c r="L22" s="9">
+        <f>IFERROR(VLOOKUP(B22,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="9">
+        <f>IFERROR(VLOOKUP(B22,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>ASSY Liquid Cooling (20EA)</t>
+        </is>
+      </c>
+      <c r="O22" s="144" t="n">
+        <v>46053</v>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>2235626096487M</t>
+        </is>
+      </c>
+      <c r="Q22" s="7">
+        <f>IF(P22="","",IFERROR(VLOOKUP(O22,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R22" s="7">
+        <f>IF(P22="","",H22)</f>
+        <v/>
+      </c>
+      <c r="S22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>1493440</v>
+      </c>
+      <c r="U22" s="143" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="4" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="Y22" s="9" t="n">
+        <v>1561040</v>
+      </c>
+      <c r="Z22" s="9">
+        <f>S22+T22+W22</f>
+        <v/>
+      </c>
+      <c r="AA22" s="10">
+        <f>K22+L22+M22+IFERROR(VLOOKUP(B22,RemitTable2,9,FALSE()),0)+Y22+Z22</f>
+        <v/>
+      </c>
+      <c r="AB22" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="AC21" s="10">
-        <f>ROUND(AA21/AB21,0)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="3" t="inlineStr">
+      <c r="AC22" s="10">
+        <f>ROUND(AA22/AB22,0)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE21" s="3" t="inlineStr">
+      <c r="AE22" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>CPO693</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>장비</t>
         </is>
       </c>
-      <c r="F22" s="146" t="n">
+      <c r="F23" s="146" t="n">
         <v>46071</v>
       </c>
-      <c r="G22" s="147" t="inlineStr">
+      <c r="G23" s="147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="H23" s="16" t="n">
         <v>35674</v>
       </c>
-      <c r="I22" s="148">
-        <f>IFERROR(VLOOKUP(B22,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="18">
-        <f>IFERROR(ROUND(H22*I22,0),0)</f>
-        <v/>
-      </c>
-      <c r="L22" s="18">
-        <f>IFERROR(VLOOKUP(B22,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="18">
-        <f>IFERROR(VLOOKUP(B22,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N22" s="12" t="inlineStr">
+      <c r="I23" s="148">
+        <f>IFERROR(VLOOKUP(B23,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="18">
+        <f>IFERROR(ROUND(H23*I23,0),0)</f>
+        <v/>
+      </c>
+      <c r="L23" s="18">
+        <f>IFERROR(VLOOKUP(B23,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="18">
+        <f>IFERROR(VLOOKUP(B23,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
         <is>
           <t>Projector (한국)</t>
         </is>
       </c>
-      <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="18" t="n"/>
-      <c r="R22" s="18" t="n"/>
-      <c r="S22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="12" t="inlineStr">
+      <c r="O23" s="12" t="n"/>
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="18" t="n"/>
+      <c r="R23" s="18" t="n"/>
+      <c r="S23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="13" t="inlineStr">
+      <c r="W23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="18">
-        <f>S22+T22+W22</f>
-        <v/>
-      </c>
-      <c r="AA22" s="18">
-        <f>K22+L22+M22+IFERROR(VLOOKUP(B22,RemitTable2,9,FALSE()),0)+Y22+Z22</f>
-        <v/>
-      </c>
-      <c r="AB22" s="19" t="n">
+      <c r="Y23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="18">
+        <f>S23+T23+W23</f>
+        <v/>
+      </c>
+      <c r="AA23" s="18">
+        <f>K23+L23+M23+IFERROR(VLOOKUP(B23,RemitTable2,9,FALSE()),0)+Y23+Z23</f>
+        <v/>
+      </c>
+      <c r="AB23" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="AC22" s="18">
-        <f>ROUND(AA22/AB22,0)</f>
-        <v/>
-      </c>
-      <c r="AD22" s="12" t="n"/>
-      <c r="AE22" s="12" t="inlineStr">
+      <c r="AC23" s="18">
+        <f>ROUND(AA23/AB23,0)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="12" t="n"/>
+      <c r="AE23" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>GPO468-1</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>장비</t>
-        </is>
-      </c>
-      <c r="F23" s="143" t="n">
-        <v>46080</v>
-      </c>
-      <c r="G23" s="144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>36190</v>
-      </c>
-      <c r="I23" s="145">
-        <f>IFERROR(VLOOKUP(B23,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9">
-        <f>IFERROR(ROUND(H23*I23,0),0)</f>
-        <v/>
-      </c>
-      <c r="L23" s="9">
-        <f>IFERROR(VLOOKUP(B23,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M23" s="9">
-        <f>IFERROR(VLOOKUP(B23,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>SR-1000 IMB (10EA)</t>
-        </is>
-      </c>
-      <c r="O23" s="144" t="n">
-        <v>46095</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>1400826101085M</t>
-        </is>
-      </c>
-      <c r="Q23" s="7">
-        <f>IF(P23="","",IFERROR(VLOOKUP(O23,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R23" s="7">
-        <f>IF(P23="","",H23)</f>
-        <v/>
-      </c>
-      <c r="S23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="9" t="n">
-        <v>5395574</v>
-      </c>
-      <c r="U23" s="143" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>조운관세사</t>
-        </is>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>137864</v>
-      </c>
-      <c r="X23" s="4" t="inlineStr">
-        <is>
-          <t>진로직스</t>
-        </is>
-      </c>
-      <c r="Y23" s="9" t="n">
-        <v>1232133</v>
-      </c>
-      <c r="Z23" s="9">
-        <f>S23+T23+W23</f>
-        <v/>
-      </c>
-      <c r="AA23" s="10">
-        <f>K23+L23+M23+IFERROR(VLOOKUP(B23,RemitTable2,9,FALSE()),0)+Y23+Z23</f>
-        <v/>
-      </c>
-      <c r="AB23" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC23" s="10">
-        <f>ROUND(AA23/AB23,0)</f>
-        <v/>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="AE23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AF23" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4059,7 +4055,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>GPO472</t>
+          <t>GPO468-1</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -4074,11 +4070,11 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F24" s="143" t="n">
-        <v>46088</v>
+        <v>46080</v>
       </c>
       <c r="G24" s="144" t="inlineStr">
         <is>
@@ -4086,7 +4082,7 @@
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>180</v>
+        <v>36190</v>
       </c>
       <c r="I24" s="145">
         <f>IFERROR(VLOOKUP(B24,RemitTable2,7,FALSE()),0)</f>
@@ -4109,7 +4105,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>SR-1000 Coverplate (3EA)</t>
+          <t>SR-1000 IMB (10EA)</t>
         </is>
       </c>
       <c r="O24" s="144" t="n">
@@ -4132,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="9" t="n">
-        <v>26836</v>
+        <v>5395574</v>
       </c>
       <c r="U24" s="143" t="inlineStr">
         <is>
@@ -4145,7 +4141,7 @@
         </is>
       </c>
       <c r="W24" s="9" t="n">
-        <v>536</v>
+        <v>137864</v>
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
@@ -4153,7 +4149,7 @@
         </is>
       </c>
       <c r="Y24" s="9" t="n">
-        <v>6128</v>
+        <v>1232133</v>
       </c>
       <c r="Z24" s="9">
         <f>S24+T24+W24</f>
@@ -4164,7 +4160,7 @@
         <v/>
       </c>
       <c r="AB24" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AC24" s="10">
         <f>ROUND(AA24/AB24,0)</f>
@@ -4192,7 +4188,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GPO468-2</t>
+          <t>GPO472</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -4207,7 +4203,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품</t>
         </is>
       </c>
       <c r="F25" s="143" t="n">
@@ -4219,7 +4215,7 @@
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>21280</v>
+        <v>180</v>
       </c>
       <c r="I25" s="145">
         <f>IFERROR(VLOOKUP(B25,RemitTable2,7,FALSE()),0)</f>
@@ -4242,15 +4238,15 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>IMB</t>
+          <t>SR-1000 Coverplate (3EA)</t>
         </is>
       </c>
       <c r="O25" s="144" t="n">
-        <v>46104</v>
+        <v>46095</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>2317626258975M</t>
+          <t>1400826101085M</t>
         </is>
       </c>
       <c r="Q25" s="7">
@@ -4265,28 +4261,28 @@
         <v>0</v>
       </c>
       <c r="T25" s="9" t="n">
-        <v>4747530</v>
+        <v>26836</v>
       </c>
       <c r="U25" s="143" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>조운관세사</t>
         </is>
       </c>
       <c r="W25" s="9" t="n">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="X25" s="4" t="inlineStr">
         <is>
-          <t>Fedex</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y25" s="9" t="n">
-        <v>904960</v>
+        <v>6128</v>
       </c>
       <c r="Z25" s="9">
         <f>S25+T25+W25</f>
@@ -4297,7 +4293,7 @@
         <v/>
       </c>
       <c r="AB25" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC25" s="10">
         <f>ROUND(AA25/AB25,0)</f>
@@ -4325,32 +4321,34 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>CPO695-1</t>
+          <t>GPO468-2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>부품(Fan)</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F26" s="143" t="n">
-        <v>46098</v>
-      </c>
-      <c r="G26" s="144" t="n">
-        <v>46146</v>
+        <v>46088</v>
+      </c>
+      <c r="G26" s="144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>2058</v>
+        <v>21280</v>
       </c>
       <c r="I26" s="145">
         <f>IFERROR(VLOOKUP(B26,RemitTable2,7,FALSE()),0)</f>
@@ -4373,15 +4371,15 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Fan (7EA)</t>
+          <t>IMB</t>
         </is>
       </c>
       <c r="O26" s="144" t="n">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>2235626283517M</t>
+          <t>2317626258975M</t>
         </is>
       </c>
       <c r="Q26" s="7">
@@ -4396,16 +4394,16 @@
         <v>0</v>
       </c>
       <c r="T26" s="9" t="n">
-        <v>350480</v>
+        <v>4747530</v>
       </c>
       <c r="U26" s="143" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>운서합동</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W26" s="9" t="n">
@@ -4413,11 +4411,11 @@
       </c>
       <c r="X26" s="4" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Fedex</t>
         </is>
       </c>
       <c r="Y26" s="9" t="n">
-        <v>6264783</v>
+        <v>904960</v>
       </c>
       <c r="Z26" s="9">
         <f>S26+T26+W26</f>
@@ -4428,7 +4426,7 @@
         <v/>
       </c>
       <c r="AB26" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC26" s="10">
         <f>ROUND(AA26/AB26,0)</f>
@@ -4456,7 +4454,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CPO695-2</t>
+          <t>CPO695-1</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -4471,7 +4469,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>부품(Filter)</t>
+          <t>부품(Fan)</t>
         </is>
       </c>
       <c r="F27" s="143" t="n">
@@ -4481,7 +4479,7 @@
         <v>46146</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1977</v>
+        <v>2058</v>
       </c>
       <c r="I27" s="145">
         <f>IFERROR(VLOOKUP(B27,RemitTable2,7,FALSE()),0)</f>
@@ -4504,15 +4502,15 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Filter(11EA)+Fan(5EA)</t>
+          <t>Fan (7EA)</t>
         </is>
       </c>
       <c r="O27" s="144" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>2235626277307M</t>
+          <t>2235626283517M</t>
         </is>
       </c>
       <c r="Q27" s="7">
@@ -4524,14 +4522,14 @@
         <v/>
       </c>
       <c r="S27" s="9" t="n">
-        <v>50790</v>
+        <v>0</v>
       </c>
       <c r="T27" s="9" t="n">
-        <v>317310</v>
+        <v>350480</v>
       </c>
       <c r="U27" s="143" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
@@ -4548,7 +4546,7 @@
         </is>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>1454605</v>
+        <v>6264783</v>
       </c>
       <c r="Z27" s="9">
         <f>S27+T27+W27</f>
@@ -4559,7 +4557,7 @@
         <v/>
       </c>
       <c r="AB27" s="11" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC27" s="10">
         <f>ROUND(AA27/AB27,0)</f>
@@ -4587,7 +4585,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CPO698</t>
+          <t>CPO695-2</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -4602,21 +4600,25 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>부품(렌즈)</t>
+          <t>부품(Filter)</t>
         </is>
       </c>
       <c r="F28" s="143" t="n">
-        <v>46106</v>
-      </c>
-      <c r="G28" s="144" t="n"/>
+        <v>46098</v>
+      </c>
+      <c r="G28" s="144" t="n">
+        <v>46146</v>
+      </c>
       <c r="H28" s="7" t="n">
-        <v>4290</v>
+        <v>1977</v>
       </c>
       <c r="I28" s="145">
         <f>IFERROR(VLOOKUP(B28,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J28" s="9" t="n"/>
+      <c r="J28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="K28" s="9">
         <f>IFERROR(ROUND(H28*I28,0),0)</f>
         <v/>
@@ -4631,15 +4633,15 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Lens 1.62-2.7 (2EA)</t>
+          <t>Filter(11EA)+Fan(5EA)</t>
         </is>
       </c>
       <c r="O28" s="144" t="n">
-        <v>46122</v>
+        <v>46104</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>2235626346781M</t>
+          <t>2235626277307M</t>
         </is>
       </c>
       <c r="Q28" s="7">
@@ -4651,12 +4653,16 @@
         <v/>
       </c>
       <c r="S28" s="9" t="n">
-        <v>524320</v>
+        <v>50790</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>707830</v>
-      </c>
-      <c r="U28" s="143" t="n"/>
+        <v>317310</v>
+      </c>
+      <c r="U28" s="143" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
           <t>운서합동</t>
@@ -4671,7 +4677,7 @@
         </is>
       </c>
       <c r="Y28" s="9" t="n">
-        <v>0</v>
+        <v>1454605</v>
       </c>
       <c r="Z28" s="9">
         <f>S28+T28+W28</f>
@@ -4682,7 +4688,7 @@
         <v/>
       </c>
       <c r="AB28" s="11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AC28" s="10">
         <f>ROUND(AA28/AB28,0)</f>
@@ -4690,132 +4696,134 @@
       </c>
       <c r="AD28" s="3" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>CPO698</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>부품(렌즈)</t>
+        </is>
+      </c>
+      <c r="F29" s="143" t="n">
+        <v>46106</v>
+      </c>
+      <c r="G29" s="144" t="n"/>
+      <c r="H29" s="7" t="n">
+        <v>4290</v>
+      </c>
+      <c r="I29" s="145">
+        <f>IFERROR(VLOOKUP(B29,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9">
+        <f>IFERROR(ROUND(H29*I29,0),0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="9">
+        <f>IFERROR(VLOOKUP(B29,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="9">
+        <f>IFERROR(VLOOKUP(B29,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Lens 1.62-2.7 (2EA)</t>
+        </is>
+      </c>
+      <c r="O29" s="144" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>2235626346781M</t>
+        </is>
+      </c>
+      <c r="Q29" s="7">
+        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R29" s="7">
+        <f>IF(P29="","",H29)</f>
+        <v/>
+      </c>
+      <c r="S29" s="9" t="n">
+        <v>524320</v>
+      </c>
+      <c r="T29" s="9" t="n">
+        <v>707830</v>
+      </c>
+      <c r="U29" s="143" t="n"/>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>운서합동</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="Y29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="9">
+        <f>S29+T29+W29</f>
+        <v/>
+      </c>
+      <c r="AA29" s="10">
+        <f>K29+L29+M29+IFERROR(VLOOKUP(B29,RemitTable2,9,FALSE()),0)+Y29+Z29</f>
+        <v/>
+      </c>
+      <c r="AB29" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC29" s="10">
+        <f>ROUND(AA29/AB29,0)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE28" s="3" t="n"/>
-      <c r="AF28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="78" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="78" t="inlineStr">
-        <is>
-          <t>CPO696-1</t>
-        </is>
-      </c>
-      <c r="C29" s="78" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D29" s="78" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E29" s="78" t="inlineStr">
-        <is>
-          <t>장비</t>
-        </is>
-      </c>
-      <c r="F29" s="149" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G29" s="149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="80" t="n">
-        <v>78209</v>
-      </c>
-      <c r="I29" s="150">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="82">
-        <f>IFERROR(ROUND(H29*I29,0),0)</f>
-        <v/>
-      </c>
-      <c r="L29" s="82">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M29" s="82">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N29" s="78" t="inlineStr">
-        <is>
-          <t>CP4445-RGB Projector 외 (렌탈용)</t>
-        </is>
-      </c>
-      <c r="O29" s="149" t="n">
-        <v>46129</v>
-      </c>
-      <c r="P29" s="78" t="inlineStr">
-        <is>
-          <t>14008-26-101125M</t>
-        </is>
-      </c>
-      <c r="Q29" s="151">
-        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R29" s="80">
-        <f>IF(P29="","",H29)</f>
-        <v/>
-      </c>
-      <c r="S29" s="82" t="n">
-        <v>67570</v>
-      </c>
-      <c r="T29" s="82" t="n">
-        <v>12073120</v>
-      </c>
-      <c r="U29" s="149" t="n"/>
-      <c r="V29" s="78" t="inlineStr">
-        <is>
-          <t>조운관세사무소</t>
-        </is>
-      </c>
-      <c r="W29" s="82" t="n">
-        <v>286000</v>
-      </c>
-      <c r="X29" s="78" t="inlineStr">
-        <is>
-          <t>진로직스</t>
-        </is>
-      </c>
-      <c r="Y29" s="82" t="n">
-        <v>3909069</v>
-      </c>
-      <c r="Z29" s="82">
-        <f>S29+T29+W29</f>
-        <v/>
-      </c>
-      <c r="AA29" s="83">
-        <f>K29+L29+M29+IFERROR(VLOOKUP(B29,RemitTable2,9,FALSE()),0)+Y29+Z29</f>
-        <v/>
-      </c>
-      <c r="AB29" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="83">
-        <f>ROUND(AA29/AB29,0)</f>
-        <v/>
-      </c>
-      <c r="AD29" s="78" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="AE29" s="78" t="n"/>
-      <c r="AF29" s="78" t="n"/>
+      <c r="AE29" s="3" t="n"/>
+      <c r="AF29" s="4" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="78" t="n">
@@ -4823,7 +4831,7 @@
       </c>
       <c r="B30" s="78" t="inlineStr">
         <is>
-          <t>CPO696-2</t>
+          <t>CPO696-1</t>
         </is>
       </c>
       <c r="C30" s="78" t="inlineStr">
@@ -4850,7 +4858,7 @@
         </is>
       </c>
       <c r="H30" s="80" t="n">
-        <v>8140</v>
+        <v>78209</v>
       </c>
       <c r="I30" s="150">
         <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
@@ -4873,15 +4881,15 @@
       </c>
       <c r="N30" s="78" t="inlineStr">
         <is>
-          <t>SMC Chiller HRS-040 외</t>
+          <t>CP4445-RGB Projector 외 (렌탈용)</t>
         </is>
       </c>
       <c r="O30" s="149" t="n">
-        <v>46132</v>
+        <v>46129</v>
       </c>
       <c r="P30" s="78" t="inlineStr">
         <is>
-          <t>14008-26-101129M</t>
+          <t>14008-26-101125M</t>
         </is>
       </c>
       <c r="Q30" s="151">
@@ -4893,10 +4901,10 @@
         <v/>
       </c>
       <c r="S30" s="82" t="n">
-        <v>1019820</v>
+        <v>67570</v>
       </c>
       <c r="T30" s="82" t="n">
-        <v>1376760</v>
+        <v>12073120</v>
       </c>
       <c r="U30" s="149" t="n"/>
       <c r="V30" s="78" t="inlineStr">
@@ -4905,7 +4913,7 @@
         </is>
       </c>
       <c r="W30" s="82" t="n">
-        <v>33000</v>
+        <v>286000</v>
       </c>
       <c r="X30" s="78" t="inlineStr">
         <is>
@@ -4913,7 +4921,7 @@
         </is>
       </c>
       <c r="Y30" s="82" t="n">
-        <v>846621</v>
+        <v>3909069</v>
       </c>
       <c r="Z30" s="82">
         <f>S30+T30+W30</f>
@@ -4944,55 +4952,67 @@
       </c>
       <c r="B31" s="78" t="inlineStr">
         <is>
-          <t>EPO18</t>
+          <t>CPO696-2</t>
         </is>
       </c>
       <c r="C31" s="78" t="inlineStr">
         <is>
-          <t>MAICO Italia</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D31" s="78" t="inlineStr">
         <is>
-          <t>100% TT in advance</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E31" s="78" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F31" s="149" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G31" s="149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="80" t="n">
+        <v>8140</v>
+      </c>
+      <c r="I31" s="150">
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J31" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="82">
+        <f>IFERROR(ROUND(H31*I31,0),0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="82">
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M31" s="82">
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N31" s="78" t="inlineStr">
+        <is>
+          <t>SMC Chiller HRS-040 외</t>
+        </is>
+      </c>
+      <c r="O31" s="149" t="n">
         <v>46132</v>
       </c>
-      <c r="G31" s="149" t="n">
-        <v>46134</v>
-      </c>
-      <c r="H31" s="80" t="n">
-        <v>4388.4</v>
-      </c>
-      <c r="I31" s="150" t="n">
-        <v>1741.08</v>
-      </c>
-      <c r="J31" s="82" t="n">
-        <v>7702082</v>
-      </c>
-      <c r="K31" s="82" t="n">
-        <v>7702082</v>
-      </c>
-      <c r="L31" s="82" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M31" s="82" t="n">
-        <v>8000</v>
-      </c>
-      <c r="N31" s="78" t="inlineStr">
-        <is>
-          <t>AXC 200 ELICENT VENTILATORE/FAN (60EA, EUR)</t>
-        </is>
-      </c>
-      <c r="O31" s="149" t="n"/>
-      <c r="P31" s="78" t="n"/>
+      <c r="P31" s="78" t="inlineStr">
+        <is>
+          <t>14008-26-101129M</t>
+        </is>
+      </c>
       <c r="Q31" s="151">
         <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE),""))</f>
         <v/>
@@ -5002,175 +5022,153 @@
         <v/>
       </c>
       <c r="S31" s="82" t="n">
-        <v>0</v>
+        <v>1019820</v>
       </c>
       <c r="T31" s="82" t="n">
-        <v>0</v>
+        <v>1376760</v>
       </c>
       <c r="U31" s="149" t="n"/>
       <c r="V31" s="78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>조운관세사무소</t>
         </is>
       </c>
       <c r="W31" s="82" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="X31" s="78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y31" s="82" t="n">
-        <v>0</v>
+        <v>846621</v>
       </c>
       <c r="Z31" s="82">
         <f>S31+T31+W31</f>
         <v/>
       </c>
-      <c r="AA31" s="83" t="n">
-        <v>7763609</v>
+      <c r="AA31" s="83">
+        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
+        <v/>
       </c>
       <c r="AB31" s="84" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC31" s="83" t="n">
-        <v>129393</v>
-      </c>
-      <c r="AD31" s="78" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AC31" s="83">
+        <f>ROUND(AA31/AB31,0)</f>
+        <v/>
+      </c>
+      <c r="AD31" s="78" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
       <c r="AE31" s="78" t="n"/>
       <c r="AF31" s="78" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="20" t="n">
+      <c r="A32" s="78" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>CPO667</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F32" s="152" t="n">
-        <v>45925</v>
-      </c>
-      <c r="G32" s="153" t="n">
-        <v>46080</v>
-      </c>
-      <c r="H32" s="24" t="n">
-        <v>5673</v>
-      </c>
-      <c r="I32" s="154">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J32" s="26" t="n">
-        <v>205028994</v>
-      </c>
-      <c r="K32" s="26">
-        <f>IFERROR(ROUND(H29*I29,0),0)</f>
-        <v/>
-      </c>
-      <c r="L32" s="26">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M32" s="26">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
-        <is>
-          <t>EW CP2220</t>
-        </is>
-      </c>
-      <c r="O32" s="20" t="inlineStr">
+      <c r="B32" s="78" t="inlineStr">
+        <is>
+          <t>EPO18</t>
+        </is>
+      </c>
+      <c r="C32" s="78" t="inlineStr">
+        <is>
+          <t>MAICO Italia</t>
+        </is>
+      </c>
+      <c r="D32" s="78" t="inlineStr">
+        <is>
+          <t>100% TT in advance</t>
+        </is>
+      </c>
+      <c r="E32" s="78" t="inlineStr">
+        <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="F32" s="149" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G32" s="149" t="n">
+        <v>46134</v>
+      </c>
+      <c r="H32" s="80" t="n">
+        <v>4388.4</v>
+      </c>
+      <c r="I32" s="150" t="n">
+        <v>1741.08</v>
+      </c>
+      <c r="J32" s="82" t="n">
+        <v>7702082</v>
+      </c>
+      <c r="K32" s="82" t="n">
+        <v>7702082</v>
+      </c>
+      <c r="L32" s="82" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M32" s="82" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N32" s="78" t="inlineStr">
+        <is>
+          <t>AXC 200 ELICENT VENTILATORE/FAN (60EA, EUR)</t>
+        </is>
+      </c>
+      <c r="O32" s="149" t="n"/>
+      <c r="P32" s="78" t="n"/>
+      <c r="Q32" s="151">
+        <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R32" s="80">
+        <f>IF(P32="","",H32)</f>
+        <v/>
+      </c>
+      <c r="S32" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="149" t="n"/>
+      <c r="V32" s="78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P32" s="20" t="inlineStr">
+      <c r="W32" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q32" s="26">
-        <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R32" s="26">
-        <f>IF(P29="","",H29)</f>
-        <v/>
-      </c>
-      <c r="S32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="26">
-        <f>S29+T29+W29</f>
-        <v/>
-      </c>
-      <c r="AA32" s="26">
-        <f>K29+L29+M29+IFERROR(VLOOKUP(B29,RemitTable2,9,FALSE()),0)+Y29+Z29</f>
-        <v/>
-      </c>
-      <c r="AB32" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="26">
-        <f>ROUND(AA29/AB29,0)</f>
-        <v/>
-      </c>
-      <c r="AD32" s="20" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="AE32" s="153" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AF32" s="152" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="Y32" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="82">
+        <f>S32+T32+W32</f>
+        <v/>
+      </c>
+      <c r="AA32" s="83" t="n">
+        <v>7763609</v>
+      </c>
+      <c r="AB32" s="84" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC32" s="83" t="n">
+        <v>129393</v>
+      </c>
+      <c r="AD32" s="78" t="n"/>
+      <c r="AE32" s="78" t="n"/>
+      <c r="AF32" s="78" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="20" t="n">
@@ -5178,39 +5176,39 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>GPO458</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F33" s="152" t="n">
-        <v>45982</v>
+        <v>45925</v>
       </c>
       <c r="G33" s="153" t="n">
-        <v>46020</v>
+        <v>46080</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>350</v>
+        <v>5673</v>
       </c>
       <c r="I33" s="154">
         <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J33" s="26" t="n">
-        <v>18264679</v>
+        <v>205028994</v>
       </c>
       <c r="K33" s="26">
         <f>IFERROR(ROUND(H30*I30,0),0)</f>
@@ -5226,7 +5224,7 @@
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>HFR License</t>
+          <t>EW CP2220</t>
         </is>
       </c>
       <c r="O33" s="20" t="inlineStr">
@@ -5289,17 +5287,17 @@
       </c>
       <c r="AD33" s="20" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="AE33" s="153" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AF33" s="152" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -5309,39 +5307,39 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F34" s="152" t="n">
-        <v>45993</v>
+        <v>45982</v>
       </c>
       <c r="G34" s="153" t="n">
-        <v>46064</v>
+        <v>46020</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>26358</v>
+        <v>350</v>
       </c>
       <c r="I34" s="154">
         <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J34" s="26" t="n">
-        <v>38550844</v>
+        <v>18264679</v>
       </c>
       <c r="K34" s="26">
         <f>IFERROR(ROUND(H31*I31,0),0)</f>
@@ -5357,7 +5355,7 @@
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>EW CP2309/2315/2320-RGB</t>
+          <t>HFR License</t>
         </is>
       </c>
       <c r="O34" s="20" t="inlineStr">
@@ -5425,12 +5423,12 @@
       </c>
       <c r="AE34" s="153" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AF34" s="152" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-11-30</t>
         </is>
       </c>
     </row>
@@ -5440,17 +5438,17 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>GPO459</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -5459,20 +5457,20 @@
         </is>
       </c>
       <c r="F35" s="152" t="n">
-        <v>46007</v>
+        <v>45993</v>
       </c>
       <c r="G35" s="153" t="n">
-        <v>46043</v>
+        <v>46064</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>450</v>
+        <v>26358</v>
       </c>
       <c r="I35" s="154">
         <f>IFERROR(VLOOKUP(B32,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J35" s="26" t="n">
-        <v>5505104</v>
+        <v>38550844</v>
       </c>
       <c r="K35" s="26">
         <f>IFERROR(ROUND(H32*I32,0),0)</f>
@@ -5488,7 +5486,7 @@
       </c>
       <c r="N35" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 EW</t>
+          <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
       <c r="O35" s="20" t="inlineStr">
@@ -5551,17 +5549,17 @@
       </c>
       <c r="AD35" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE35" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AF35" s="152" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-21</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5569,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -5596,7 +5594,7 @@
         <v>46043</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="I36" s="154">
         <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE()),0)</f>
@@ -5619,7 +5617,7 @@
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 EW</t>
+          <t>TMS-2000 EW</t>
         </is>
       </c>
       <c r="O36" s="20" t="inlineStr">
@@ -5682,17 +5680,17 @@
       </c>
       <c r="AD36" s="20" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE36" s="153" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF36" s="152" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
@@ -5702,17 +5700,17 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -5721,20 +5719,20 @@
         </is>
       </c>
       <c r="F37" s="152" t="n">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="G37" s="153" t="n">
-        <v>46080</v>
+        <v>46043</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>136516</v>
+        <v>540</v>
       </c>
       <c r="I37" s="154">
         <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J37" s="26" t="n">
-        <v>205028994</v>
+        <v>5505104</v>
       </c>
       <c r="K37" s="26">
         <f>IFERROR(ROUND(H34*I34,0),0)</f>
@@ -5750,7 +5748,7 @@
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (CP2208~CP4450)</t>
+          <t>TMS-1000 EW</t>
         </is>
       </c>
       <c r="O37" s="20" t="inlineStr">
@@ -5813,17 +5811,17 @@
       </c>
       <c r="AD37" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="AE37" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AF37" s="152" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5833,17 +5831,17 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>GPO465</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -5852,22 +5850,20 @@
         </is>
       </c>
       <c r="F38" s="152" t="n">
-        <v>46015</v>
-      </c>
-      <c r="G38" s="153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46010</v>
+      </c>
+      <c r="G38" s="153" t="n">
+        <v>46080</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>76054</v>
+        <v>136516</v>
       </c>
       <c r="I38" s="154">
         <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J38" s="26" t="n">
-        <v>0</v>
+        <v>205028994</v>
       </c>
       <c r="K38" s="26">
         <f>IFERROR(ROUND(H35*I35,0),0)</f>
@@ -5883,7 +5879,7 @@
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (SR/SX/TMS)</t>
+          <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
       <c r="O38" s="20" t="inlineStr">
@@ -5966,17 +5962,17 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>GPO465</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -5985,20 +5981,22 @@
         </is>
       </c>
       <c r="F39" s="152" t="n">
-        <v>46029</v>
-      </c>
-      <c r="G39" s="153" t="n">
-        <v>46072</v>
+        <v>46015</v>
+      </c>
+      <c r="G39" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H39" s="24" t="n">
-        <v>14793</v>
+        <v>76054</v>
       </c>
       <c r="I39" s="154">
         <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J39" s="26" t="n">
-        <v>25506948</v>
+        <v>0</v>
       </c>
       <c r="K39" s="26">
         <f>IFERROR(ROUND(H36*I36,0),0)</f>
@@ -6014,7 +6012,7 @@
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>EW CP2315/CP4440-RGB</t>
+          <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
       <c r="O39" s="20" t="inlineStr">
@@ -6082,12 +6080,12 @@
       </c>
       <c r="AE39" s="153" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF39" s="152" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6095,7 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>CPO687</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
@@ -6118,20 +6116,18 @@
       <c r="F40" s="152" t="n">
         <v>46029</v>
       </c>
-      <c r="G40" s="153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G40" s="153" t="n">
+        <v>46072</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>26656</v>
+        <v>14793</v>
       </c>
       <c r="I40" s="154">
         <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J40" s="26" t="n">
-        <v>0</v>
+        <v>25506948</v>
       </c>
       <c r="K40" s="26">
         <f>IFERROR(ROUND(H37*I37,0),0)</f>
@@ -6147,7 +6143,7 @@
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>EW (홀딩)</t>
+          <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
       <c r="O40" s="20" t="inlineStr">
@@ -6215,12 +6211,12 @@
       </c>
       <c r="AE40" s="153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AF40" s="152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-01-29</t>
         </is>
       </c>
     </row>
@@ -6230,39 +6226,41 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>CPO687</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F41" s="152" t="n">
-        <v>46042</v>
-      </c>
-      <c r="G41" s="153" t="n">
-        <v>46057</v>
+        <v>46029</v>
+      </c>
+      <c r="G41" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H41" s="24" t="n">
-        <v>1440</v>
+        <v>26656</v>
       </c>
       <c r="I41" s="154">
         <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J41" s="26" t="n">
-        <v>16908206</v>
+        <v>0</v>
       </c>
       <c r="K41" s="26">
         <f>IFERROR(ROUND(H38*I38,0),0)</f>
@@ -6278,7 +6276,7 @@
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 License</t>
+          <t>EW (홀딩)</t>
         </is>
       </c>
       <c r="O41" s="20" t="inlineStr">
@@ -6346,12 +6344,12 @@
       </c>
       <c r="AE41" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AF41" s="152" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6359,7 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
@@ -6376,7 +6374,7 @@
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F42" s="152" t="n">
@@ -6386,7 +6384,7 @@
         <v>46057</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>4489</v>
+        <v>1440</v>
       </c>
       <c r="I42" s="154">
         <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE()),0)</f>
@@ -6409,7 +6407,7 @@
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>SX/SR EW (CGV/Lotte)</t>
+          <t>TMS-2000 License</t>
         </is>
       </c>
       <c r="O42" s="20" t="inlineStr">
@@ -6492,7 +6490,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
@@ -6517,7 +6515,7 @@
         <v>46057</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>5670.57</v>
+        <v>4489</v>
       </c>
       <c r="I43" s="154">
         <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE()),0)</f>
@@ -6540,7 +6538,7 @@
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
-          <t>SR-1000/SX-3000 EW</t>
+          <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
       <c r="O43" s="20" t="inlineStr">
@@ -6623,17 +6621,17 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E44" s="21" t="inlineStr">
@@ -6642,20 +6640,20 @@
         </is>
       </c>
       <c r="F44" s="152" t="n">
+        <v>46042</v>
+      </c>
+      <c r="G44" s="153" t="n">
         <v>46057</v>
       </c>
-      <c r="G44" s="153" t="n">
-        <v>46113</v>
-      </c>
       <c r="H44" s="24" t="n">
-        <v>24614</v>
+        <v>5670.57</v>
       </c>
       <c r="I44" s="154">
         <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J44" s="26" t="n">
-        <v>51777431</v>
+        <v>16908206</v>
       </c>
       <c r="K44" s="26">
         <f>IFERROR(ROUND(H41*I41,0),0)</f>
@@ -6671,7 +6669,7 @@
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t>EW (메가박스 외)</t>
+          <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
       <c r="O44" s="20" t="inlineStr">
@@ -6734,17 +6732,17 @@
       </c>
       <c r="AD44" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE44" s="153" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF44" s="152" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
@@ -6754,17 +6752,17 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E45" s="21" t="inlineStr">
@@ -6773,20 +6771,20 @@
         </is>
       </c>
       <c r="F45" s="152" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="G45" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>3993.05</v>
+        <v>24614</v>
       </c>
       <c r="I45" s="154">
         <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J45" s="26" t="n">
-        <v>9919642</v>
+        <v>51777431</v>
       </c>
       <c r="K45" s="26">
         <f>IFERROR(ROUND(H42*I42,0),0)</f>
@@ -6802,7 +6800,7 @@
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>SR/SX EW (하남미사 외)</t>
+          <t>EW (메가박스 외)</t>
         </is>
       </c>
       <c r="O45" s="20" t="inlineStr">
@@ -6865,17 +6863,17 @@
       </c>
       <c r="AD45" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="AE45" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AF45" s="152" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-28</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6883,7 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>GPO469</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
@@ -6900,17 +6898,17 @@
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F46" s="152" t="n">
-        <v>46080</v>
+        <v>46060</v>
       </c>
       <c r="G46" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>360</v>
+        <v>3993.05</v>
       </c>
       <c r="I46" s="154">
         <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE()),0)</f>
@@ -6933,7 +6931,7 @@
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 License</t>
+          <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
       <c r="O46" s="20" t="inlineStr">
@@ -6996,17 +6994,17 @@
       </c>
       <c r="AD46" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE46" s="153" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF46" s="152" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-02-22</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7014,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>GPO470</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
@@ -7035,13 +7033,13 @@
         </is>
       </c>
       <c r="F47" s="152" t="n">
-        <v>46088</v>
+        <v>46080</v>
       </c>
       <c r="G47" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="I47" s="154">
         <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE()),0)</f>
@@ -7064,7 +7062,7 @@
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
-          <t>Dolby Atmos License</t>
+          <t>TMS-1000 License</t>
         </is>
       </c>
       <c r="O47" s="20" t="inlineStr">
@@ -7132,12 +7130,12 @@
       </c>
       <c r="AE47" s="153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AF47" s="152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-02-28</t>
         </is>
       </c>
     </row>
@@ -7147,55 +7145,55 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>GPO471</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F48" s="152" t="n">
-        <v>46109</v>
+        <v>46088</v>
       </c>
       <c r="G48" s="153" t="n">
-        <v>46146</v>
+        <v>46113</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>17404</v>
+        <v>500</v>
       </c>
       <c r="I48" s="154">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J48" s="26" t="n">
-        <v>0</v>
+        <v>9919642</v>
       </c>
       <c r="K48" s="26">
-        <f>IFERROR(ROUND(H48*I48,0),0)</f>
+        <f>IFERROR(ROUND(H45*I45,0),0)</f>
         <v/>
       </c>
       <c r="L48" s="26">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M48" s="26">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>EW (CGV 동백 외)</t>
+          <t>Dolby Atmos License</t>
         </is>
       </c>
       <c r="O48" s="20" t="inlineStr">
@@ -7213,7 +7211,7 @@
         <v/>
       </c>
       <c r="R48" s="26">
-        <f>IF(P48="","",H48)</f>
+        <f>IF(P45="","",H45)</f>
         <v/>
       </c>
       <c r="S48" s="26" t="n">
@@ -7242,158 +7240,166 @@
         <v>0</v>
       </c>
       <c r="Z48" s="26">
-        <f>S48+T48+W48</f>
+        <f>S45+T45+W45</f>
         <v/>
       </c>
       <c r="AA48" s="26">
-        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE()),0)+Y48+Z48</f>
+        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE()),0)+Y45+Z45</f>
         <v/>
       </c>
       <c r="AB48" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC48" s="26">
-        <f>ROUND(AA48/AB48,0)</f>
+        <f>ROUND(AA45/AB45,0)</f>
         <v/>
       </c>
       <c r="AD48" s="20" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE48" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF48" s="152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>CPO694</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F49" s="152" t="n">
+        <v>46109</v>
+      </c>
+      <c r="G49" s="153" t="n">
+        <v>46146</v>
+      </c>
+      <c r="H49" s="24" t="n">
+        <v>17404</v>
+      </c>
+      <c r="I49" s="154">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="26">
+        <f>IFERROR(ROUND(H49*I49,0),0)</f>
+        <v/>
+      </c>
+      <c r="L49" s="26">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M49" s="26">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>EW (CGV 동백 외)</t>
+        </is>
+      </c>
+      <c r="O49" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q49" s="26">
+        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R49" s="26">
+        <f>IF(P49="","",H49)</f>
+        <v/>
+      </c>
+      <c r="S49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="26">
+        <f>S49+T49+W49</f>
+        <v/>
+      </c>
+      <c r="AA49" s="26">
+        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE()),0)+Y49+Z49</f>
+        <v/>
+      </c>
+      <c r="AB49" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="26">
+        <f>ROUND(AA49/AB49,0)</f>
+        <v/>
+      </c>
+      <c r="AD49" s="20" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE48" s="153" t="inlineStr">
+      <c r="AE49" s="153" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AF48" s="152" t="inlineStr">
+      <c r="AF49" s="152" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="85" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="85" t="inlineStr">
-        <is>
-          <t>CPO697</t>
-        </is>
-      </c>
-      <c r="C49" s="85" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D49" s="85" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E49" s="85" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F49" s="155" t="n">
-        <v>46136</v>
-      </c>
-      <c r="G49" s="155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="87" t="n">
-        <v>15289</v>
-      </c>
-      <c r="I49" s="156">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="89">
-        <f>IFERROR(ROUND(H49*I49,0),0)</f>
-        <v/>
-      </c>
-      <c r="L49" s="89">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M49" s="89">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N49" s="85" t="inlineStr">
-        <is>
-          <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
-        </is>
-      </c>
-      <c r="O49" s="155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q49" s="157">
-        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R49" s="87">
-        <f>IF(P49="","",H49)</f>
-        <v/>
-      </c>
-      <c r="S49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="155" t="n"/>
-      <c r="V49" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="89">
-        <f>S49+T49+W49</f>
-        <v/>
-      </c>
-      <c r="AA49" s="89">
-        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE()),0)+Y49+Z49</f>
-        <v/>
-      </c>
-      <c r="AB49" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC49" s="89">
-        <f>ROUND(AA49/AB49,0)</f>
-        <v/>
-      </c>
-      <c r="AD49" s="85" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="AE49" s="155" t="n"/>
-      <c r="AF49" s="155" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="85" t="n">
@@ -7401,7 +7407,7 @@
       </c>
       <c r="B50" s="85" t="inlineStr">
         <is>
-          <t>CPO693-2</t>
+          <t>CPO697</t>
         </is>
       </c>
       <c r="C50" s="85" t="inlineStr">
@@ -7420,7 +7426,7 @@
         </is>
       </c>
       <c r="F50" s="155" t="n">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="G50" s="155" t="inlineStr">
         <is>
@@ -7428,7 +7434,7 @@
         </is>
       </c>
       <c r="H50" s="87" t="n">
-        <v>2550</v>
+        <v>15289</v>
       </c>
       <c r="I50" s="156">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE()),0)</f>
@@ -7451,7 +7457,7 @@
       </c>
       <c r="N50" s="85" t="inlineStr">
         <is>
-          <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
+          <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
       <c r="O50" s="155" t="inlineStr">
@@ -7519,137 +7525,127 @@
       <c r="AF50" s="155" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="85" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>CPO688</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="B51" s="85" t="inlineStr">
+        <is>
+          <t>CPO693-2</t>
+        </is>
+      </c>
+      <c r="C51" s="85" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="85" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-      <c r="F51" s="146" t="n">
-        <v>46037</v>
-      </c>
-      <c r="G51" s="147" t="inlineStr">
+      <c r="E51" s="85" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F51" s="155" t="n">
+        <v>46133</v>
+      </c>
+      <c r="G51" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H51" s="16" t="n">
-        <v>4180</v>
-      </c>
-      <c r="I51" s="148">
-        <f>IFERROR(VLOOKUP(B46,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="18">
-        <f>IFERROR(ROUND(H46*I46,0),0)</f>
-        <v/>
-      </c>
-      <c r="L51" s="18">
-        <f>IFERROR(VLOOKUP(B46,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="18">
-        <f>IFERROR(VLOOKUP(B46,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>Inspection fee</t>
-        </is>
-      </c>
-      <c r="O51" s="12" t="inlineStr">
+      <c r="H51" s="87" t="n">
+        <v>2550</v>
+      </c>
+      <c r="I51" s="156">
+        <f>IFERROR(VLOOKUP(B51,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="89">
+        <f>IFERROR(ROUND(H51*I51,0),0)</f>
+        <v/>
+      </c>
+      <c r="L51" s="89">
+        <f>IFERROR(VLOOKUP(B51,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M51" s="89">
+        <f>IFERROR(VLOOKUP(B51,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N51" s="85" t="inlineStr">
+        <is>
+          <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
+        </is>
+      </c>
+      <c r="O51" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P51" s="12" t="inlineStr">
+      <c r="P51" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q51" s="18">
+      <c r="Q51" s="157">
         <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R51" s="18">
-        <f>IF(P46="","",H46)</f>
-        <v/>
-      </c>
-      <c r="S51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="12" t="inlineStr">
+      <c r="R51" s="87">
+        <f>IF(P51="","",H51)</f>
+        <v/>
+      </c>
+      <c r="S51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="155" t="n"/>
+      <c r="V51" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="13" t="inlineStr">
+      <c r="W51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="18">
-        <f>S46+T46+W46</f>
-        <v/>
-      </c>
-      <c r="AA51" s="18">
-        <f>K46+L46+M46+IFERROR(VLOOKUP(B46,RemitTable2,9,FALSE()),0)+Y46+Z46</f>
-        <v/>
-      </c>
-      <c r="AB51" s="19" t="n">
+      <c r="Y51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="89">
+        <f>S51+T51+W51</f>
+        <v/>
+      </c>
+      <c r="AA51" s="89">
+        <f>K51+L51+M51+IFERROR(VLOOKUP(B51,RemitTable2,9,FALSE()),0)+Y51+Z51</f>
+        <v/>
+      </c>
+      <c r="AB51" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="AC51" s="18">
-        <f>ROUND(AA46/AB46,0)</f>
-        <v/>
-      </c>
-      <c r="AD51" s="12" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="AE51" s="147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF51" s="146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AC51" s="89">
+        <f>ROUND(AA51/AB51,0)</f>
+        <v/>
+      </c>
+      <c r="AD51" s="85" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="AE51" s="155" t="n"/>
+      <c r="AF51" s="155" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -7657,28 +7653,34 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>SX3000수리</t>
+          <t>CPO688</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>Inspection</t>
+        </is>
+      </c>
+      <c r="F52" s="146" t="n">
+        <v>46037</v>
+      </c>
+      <c r="G52" s="147" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>수리반환</t>
-        </is>
-      </c>
-      <c r="F52" s="146" t="n"/>
-      <c r="G52" s="147" t="n"/>
       <c r="H52" s="16" t="n">
-        <v>400</v>
+        <v>4180</v>
       </c>
       <c r="I52" s="148">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE()),0)</f>
@@ -7701,15 +7703,17 @@
       </c>
       <c r="N52" s="12" t="inlineStr">
         <is>
-          <t>Display Card (수리반환 5PCS)</t>
-        </is>
-      </c>
-      <c r="O52" s="12" t="n">
-        <v>46125</v>
+          <t>Inspection fee</t>
+        </is>
+      </c>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>2235626351613M</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q52" s="18">
@@ -7724,12 +7728,14 @@
         <v>0</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>67750</v>
-      </c>
-      <c r="U52" s="13" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="V52" s="12" t="inlineStr">
         <is>
-          <t>운서합동</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W52" s="18" t="n">
@@ -7737,7 +7743,7 @@
       </c>
       <c r="X52" s="13" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y52" s="18" t="n">
@@ -7752,7 +7758,7 @@
         <v/>
       </c>
       <c r="AB52" s="19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC52" s="18">
         <f>ROUND(AA47/AB47,0)</f>
@@ -7760,140 +7766,134 @@
       </c>
       <c r="AD52" s="12" t="inlineStr">
         <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AE52" s="147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF52" s="146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>SX3000수리</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>수리반환</t>
+        </is>
+      </c>
+      <c r="F53" s="146" t="n"/>
+      <c r="G53" s="147" t="n"/>
+      <c r="H53" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="I53" s="148">
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="18">
+        <f>IFERROR(ROUND(H48*I48,0),0)</f>
+        <v/>
+      </c>
+      <c r="L53" s="18">
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M53" s="18">
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N53" s="12" t="inlineStr">
+        <is>
+          <t>Display Card (수리반환 5PCS)</t>
+        </is>
+      </c>
+      <c r="O53" s="12" t="n">
+        <v>46125</v>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>2235626351613M</t>
+        </is>
+      </c>
+      <c r="Q53" s="18">
+        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R53" s="18">
+        <f>IF(P48="","",H48)</f>
+        <v/>
+      </c>
+      <c r="S53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="18" t="n">
+        <v>67750</v>
+      </c>
+      <c r="U53" s="13" t="n"/>
+      <c r="V53" s="12" t="inlineStr">
+        <is>
+          <t>운서합동</t>
+        </is>
+      </c>
+      <c r="W53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="13" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="Y53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="18">
+        <f>S48+T48+W48</f>
+        <v/>
+      </c>
+      <c r="AA53" s="18">
+        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE()),0)+Y48+Z48</f>
+        <v/>
+      </c>
+      <c r="AB53" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC53" s="18">
+        <f>ROUND(AA48/AB48,0)</f>
+        <v/>
+      </c>
+      <c r="AD53" s="12" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE52" s="147" t="n"/>
-      <c r="AF52" s="146" t="n"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>IPO016</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Integ Process Group</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>50% TT advance, 50% Net 30</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>부품</t>
-        </is>
-      </c>
-      <c r="F53" s="143" t="n">
-        <v>45881</v>
-      </c>
-      <c r="G53" s="144" t="n">
-        <v>46146</v>
-      </c>
-      <c r="H53" s="7" t="n">
-        <v>6800</v>
-      </c>
-      <c r="I53" s="145">
-        <f>IFERROR(VLOOKUP(B53,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="9">
-        <f>IFERROR(ROUND(H53*I53,0),0)</f>
-        <v/>
-      </c>
-      <c r="L53" s="9">
-        <f>IFERROR(VLOOKUP(B53,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M53" s="9">
-        <f>IFERROR(VLOOKUP(B53,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N53" s="3" t="inlineStr">
-        <is>
-          <t>JNIOR Model 410 (20EA)</t>
-        </is>
-      </c>
-      <c r="O53" s="144" t="n">
-        <v>45905</v>
-      </c>
-      <c r="P53" s="3" t="inlineStr">
-        <is>
-          <t>883504210357</t>
-        </is>
-      </c>
-      <c r="Q53" s="7">
-        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R53" s="7">
-        <f>IF(P53="","",H53)</f>
-        <v/>
-      </c>
-      <c r="S53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="9" t="n">
-        <v>954760</v>
-      </c>
-      <c r="U53" s="143" t="n">
-        <v>45905</v>
-      </c>
-      <c r="V53" s="3" t="inlineStr">
-        <is>
-          <t>인천세관</t>
-        </is>
-      </c>
-      <c r="W53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="4" t="inlineStr">
-        <is>
-          <t>DHL</t>
-        </is>
-      </c>
-      <c r="Y53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="9">
-        <f>S53+T53+W53</f>
-        <v/>
-      </c>
-      <c r="AA53" s="175">
-        <f>K53+L53+M53+IFERROR(VLOOKUP(B53,RemitTable2,9,FALSE()),0)+Y53+Z53</f>
-        <v/>
-      </c>
-      <c r="AB53" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC53" s="175">
-        <f>ROUND(AA53/AB53,0)</f>
-        <v/>
-      </c>
-      <c r="AD53" s="3" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="AE53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF53" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AE53" s="147" t="n"/>
+      <c r="AF53" s="146" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="125" t="inlineStr">
@@ -7908,24 +7908,24 @@
       <c r="F54" s="126" t="n"/>
       <c r="G54" s="127" t="n"/>
       <c r="H54" s="91">
-        <f>SUBTOTAL(9,H5:H31,H53)</f>
+        <f>SUBTOTAL(9,H5:H32)</f>
         <v/>
       </c>
       <c r="I54" s="92" t="n"/>
       <c r="J54" s="93">
-        <f>SUBTOTAL(9,J5:J31,J53)</f>
+        <f>SUBTOTAL(9,J5:J32)</f>
         <v/>
       </c>
       <c r="K54" s="93">
-        <f>SUBTOTAL(9,K5:K31,K53)</f>
+        <f>SUBTOTAL(9,K5:K32)</f>
         <v/>
       </c>
       <c r="L54" s="93">
-        <f>SUBTOTAL(9,L5:L31,L53)</f>
+        <f>SUBTOTAL(9,L5:L32)</f>
         <v/>
       </c>
       <c r="M54" s="93">
-        <f>SUBTOTAL(9,M5:M28,M53)</f>
+        <f>SUBTOTAL(9,M5:M29)</f>
         <v/>
       </c>
       <c r="N54" s="92" t="n"/>
@@ -7934,30 +7934,30 @@
       <c r="Q54" s="93" t="n"/>
       <c r="R54" s="91" t="n"/>
       <c r="S54" s="93">
-        <f>SUBTOTAL(9,S5:S31,S53)</f>
+        <f>SUBTOTAL(9,S5:S32)</f>
         <v/>
       </c>
       <c r="T54" s="93">
-        <f>SUBTOTAL(9,T5:T31,T53)</f>
+        <f>SUBTOTAL(9,T5:T32)</f>
         <v/>
       </c>
       <c r="U54" s="92" t="n"/>
       <c r="V54" s="92" t="n"/>
       <c r="W54" s="93">
-        <f>SUBTOTAL(9,W5:W31,W53)</f>
+        <f>SUBTOTAL(9,W5:W32)</f>
         <v/>
       </c>
       <c r="X54" s="92" t="n"/>
       <c r="Y54" s="93">
-        <f>SUBTOTAL(9,Y5:Y31,Y53)</f>
+        <f>SUBTOTAL(9,Y5:Y32)</f>
         <v/>
       </c>
       <c r="Z54" s="93">
-        <f>SUBTOTAL(9,Z5:Z31,Z53)</f>
+        <f>SUBTOTAL(9,Z5:Z32)</f>
         <v/>
       </c>
       <c r="AA54" s="93">
-        <f>SUBTOTAL(9,AA5:AA31,AA53)</f>
+        <f>SUBTOTAL(9,AA5:AA32)</f>
         <v/>
       </c>
       <c r="AB54" s="92" t="n"/>
@@ -7979,24 +7979,24 @@
       <c r="F55" s="126" t="n"/>
       <c r="G55" s="127" t="n"/>
       <c r="H55" s="91">
-        <f>SUBTOTAL(9,H32:H50)</f>
+        <f>SUBTOTAL(9,H33:H51)</f>
         <v/>
       </c>
       <c r="I55" s="92" t="n"/>
       <c r="J55" s="93">
-        <f>SUBTOTAL(9,J32:J50)</f>
+        <f>SUBTOTAL(9,J33:J51)</f>
         <v/>
       </c>
       <c r="K55" s="93">
-        <f>SUBTOTAL(9,K32:K50)</f>
+        <f>SUBTOTAL(9,K33:K51)</f>
         <v/>
       </c>
       <c r="L55" s="93">
-        <f>SUBTOTAL(9,L32:L50)</f>
+        <f>SUBTOTAL(9,L33:L51)</f>
         <v/>
       </c>
       <c r="M55" s="93">
-        <f>SUBTOTAL(9,M29:M45)</f>
+        <f>SUBTOTAL(9,M30:M46)</f>
         <v/>
       </c>
       <c r="N55" s="92" t="n"/>
@@ -8005,30 +8005,30 @@
       <c r="Q55" s="93" t="n"/>
       <c r="R55" s="91" t="n"/>
       <c r="S55" s="93">
-        <f>SUBTOTAL(9,S32:S50)</f>
+        <f>SUBTOTAL(9,S33:S51)</f>
         <v/>
       </c>
       <c r="T55" s="93">
-        <f>SUBTOTAL(9,T32:T50)</f>
+        <f>SUBTOTAL(9,T33:T51)</f>
         <v/>
       </c>
       <c r="U55" s="92" t="n"/>
       <c r="V55" s="92" t="n"/>
       <c r="W55" s="93">
-        <f>SUBTOTAL(9,W32:W50)</f>
+        <f>SUBTOTAL(9,W33:W51)</f>
         <v/>
       </c>
       <c r="X55" s="92" t="n"/>
       <c r="Y55" s="93">
-        <f>SUBTOTAL(9,Y32:Y50)</f>
+        <f>SUBTOTAL(9,Y33:Y51)</f>
         <v/>
       </c>
       <c r="Z55" s="93">
-        <f>SUBTOTAL(9,Z32:Z50)</f>
+        <f>SUBTOTAL(9,Z33:Z51)</f>
         <v/>
       </c>
       <c r="AA55" s="93">
-        <f>SUBTOTAL(9,AA32:AA50)</f>
+        <f>SUBTOTAL(9,AA33:AA51)</f>
         <v/>
       </c>
       <c r="AB55" s="92" t="n"/>
@@ -8050,24 +8050,24 @@
       <c r="F56" s="126" t="n"/>
       <c r="G56" s="127" t="n"/>
       <c r="H56" s="91">
-        <f>H51+H52</f>
+        <f>H52+H53</f>
         <v/>
       </c>
       <c r="I56" s="92" t="n"/>
       <c r="J56" s="93">
-        <f>J51+J52</f>
+        <f>J52+J53</f>
         <v/>
       </c>
       <c r="K56" s="93">
-        <f>K51+K52</f>
+        <f>K52+K53</f>
         <v/>
       </c>
       <c r="L56" s="93">
-        <f>L51+L52</f>
+        <f>L52+L53</f>
         <v/>
       </c>
       <c r="M56" s="93">
-        <f>M46+M47</f>
+        <f>M47+M48</f>
         <v/>
       </c>
       <c r="N56" s="92" t="n"/>
@@ -8076,30 +8076,30 @@
       <c r="Q56" s="93" t="n"/>
       <c r="R56" s="91" t="n"/>
       <c r="S56" s="93">
-        <f>S51+S52</f>
+        <f>S52+S53</f>
         <v/>
       </c>
       <c r="T56" s="93">
-        <f>T51+T52</f>
+        <f>T52+T53</f>
         <v/>
       </c>
       <c r="U56" s="92" t="n"/>
       <c r="V56" s="92" t="n"/>
       <c r="W56" s="93">
-        <f>W51+W52</f>
+        <f>W52+W53</f>
         <v/>
       </c>
       <c r="X56" s="92" t="n"/>
       <c r="Y56" s="93">
-        <f>Y51+Y52</f>
+        <f>Y52+Y53</f>
         <v/>
       </c>
       <c r="Z56" s="93">
-        <f>Z51+Z52</f>
+        <f>Z52+Z53</f>
         <v/>
       </c>
       <c r="AA56" s="93">
-        <f>AA51+AA52</f>
+        <f>AA52+AA53</f>
         <v/>
       </c>
       <c r="AB56" s="92" t="n"/>
@@ -8138,7 +8138,7 @@
         <v/>
       </c>
       <c r="M57" s="96">
-        <f>SUBTOTAL(9,M5:M53)</f>
+        <f>SUBTOTAL(9,M5:M48)</f>
         <v/>
       </c>
       <c r="N57" s="95" t="n"/>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="RemitTable1">외화송금내역!$A$3:$L$34</definedName>
     <definedName name="RemitTable2">외화송금내역!$A$37:$L$74</definedName>
-    <definedName name="FxRateTable">환율!$A$7:$D$37</definedName>
+    <definedName name="FxRateTable">환율!$A$7:$D$39</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,13 +24,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0&quot;일&quot;"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -180,8 +181,23 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -260,8 +276,33 @@
         <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -402,11 +443,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -906,6 +981,98 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="15" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="23" fillId="17" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="17" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="24" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="14" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="16" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1285,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF76"/>
+  <dimension ref="A1:AF83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" style="135" min="1" max="1"/>
@@ -1351,7 +1518,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="131" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-05-06  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-05-19  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="123" t="n"/>
@@ -5171,546 +5338,464 @@
       <c r="AF32" s="78" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>CPO667</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="A33" s="176" t="n">
+        <v>50</v>
+      </c>
+      <c r="B33" s="176" t="inlineStr">
+        <is>
+          <t>CPO696-3</t>
+        </is>
+      </c>
+      <c r="C33" s="176" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="176" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F33" s="152" t="n">
-        <v>45925</v>
-      </c>
-      <c r="G33" s="153" t="n">
-        <v>46080</v>
-      </c>
-      <c r="H33" s="24" t="n">
-        <v>5673</v>
-      </c>
-      <c r="I33" s="154">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J33" s="26" t="n">
-        <v>205028994</v>
-      </c>
-      <c r="K33" s="26">
-        <f>IFERROR(ROUND(H30*I30,0),0)</f>
-        <v/>
-      </c>
-      <c r="L33" s="26">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M33" s="26">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N33" s="20" t="inlineStr">
-        <is>
-          <t>EW CP2220</t>
-        </is>
-      </c>
-      <c r="O33" s="20" t="inlineStr">
+      <c r="E33" s="176" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F33" s="202" t="n">
+        <v>46127</v>
+      </c>
+      <c r="G33" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P33" s="20" t="inlineStr">
+      <c r="H33" s="178" t="n">
+        <v>351274</v>
+      </c>
+      <c r="I33" s="179">
+        <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J33" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="180">
+        <f>IFERROR(ROUND(H33*I33,0),0)</f>
+        <v/>
+      </c>
+      <c r="L33" s="180">
+        <f>IFERROR(VLOOKUP(B33,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M33" s="180">
+        <f>IFERROR(VLOOKUP(B33,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N33" s="181" t="inlineStr"/>
+      <c r="O33" s="203" t="n">
+        <v>46141</v>
+      </c>
+      <c r="P33" s="181" t="inlineStr">
+        <is>
+          <t>14008-26-101140M</t>
+        </is>
+      </c>
+      <c r="Q33" s="179">
+        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R33" s="178">
+        <f>IF(P33="","",H33)</f>
+        <v/>
+      </c>
+      <c r="S33" s="180" t="n">
+        <v>522900</v>
+      </c>
+      <c r="T33" s="180" t="n">
+        <v>52140300</v>
+      </c>
+      <c r="U33" s="181" t="inlineStr"/>
+      <c r="V33" s="181" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W33" s="180" t="n">
+        <v>250000</v>
+      </c>
+      <c r="X33" s="181" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="Y33" s="180" t="n">
+        <v>3103207</v>
+      </c>
+      <c r="Z33" s="180">
+        <f>S33+T33+W33</f>
+        <v/>
+      </c>
+      <c r="AA33" s="183">
+        <f>K33+L33+M33+IFERROR(VLOOKUP(B33,RemitTable2,9,FALSE),0)+Y33+Z33</f>
+        <v/>
+      </c>
+      <c r="AB33" s="180" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC33" s="183">
+        <f>ROUND(AA33/AB33,0)</f>
+        <v/>
+      </c>
+      <c r="AD33" s="181" t="inlineStr"/>
+      <c r="AE33" s="181" t="inlineStr"/>
+      <c r="AF33" s="181" t="inlineStr"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="176" t="n">
+        <v>51</v>
+      </c>
+      <c r="B34" s="176" t="inlineStr">
+        <is>
+          <t>CPO696-4</t>
+        </is>
+      </c>
+      <c r="C34" s="176" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D34" s="176" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E34" s="176" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F34" s="202" t="n">
+        <v>46143</v>
+      </c>
+      <c r="G34" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q33" s="26">
-        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R33" s="26">
-        <f>IF(P30="","",H30)</f>
-        <v/>
-      </c>
-      <c r="S33" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="20" t="inlineStr">
+      <c r="H34" s="178" t="n">
+        <v>807233</v>
+      </c>
+      <c r="I34" s="179">
+        <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J34" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="180">
+        <f>IFERROR(ROUND(H34*I34,0),0)</f>
+        <v/>
+      </c>
+      <c r="L34" s="180">
+        <f>IFERROR(VLOOKUP(B34,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M34" s="180">
+        <f>IFERROR(VLOOKUP(B34,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N34" s="181" t="inlineStr"/>
+      <c r="O34" s="203" t="n">
+        <v>46157</v>
+      </c>
+      <c r="P34" s="181" t="inlineStr">
+        <is>
+          <t>14008-26-101168M</t>
+        </is>
+      </c>
+      <c r="Q34" s="179">
+        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R34" s="178">
+        <f>IF(P34="","",H34)</f>
+        <v/>
+      </c>
+      <c r="S34" s="180" t="n">
+        <v>1229900</v>
+      </c>
+      <c r="T34" s="180" t="n">
+        <v>118665800</v>
+      </c>
+      <c r="U34" s="181" t="inlineStr"/>
+      <c r="V34" s="181" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W34" s="180" t="n">
+        <v>250000</v>
+      </c>
+      <c r="X34" s="181" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="Y34" s="180" t="n">
+        <v>3270326</v>
+      </c>
+      <c r="Z34" s="180">
+        <f>S34+T34+W34</f>
+        <v/>
+      </c>
+      <c r="AA34" s="183">
+        <f>K34+L34+M34+IFERROR(VLOOKUP(B34,RemitTable2,9,FALSE),0)+Y34+Z34</f>
+        <v/>
+      </c>
+      <c r="AB34" s="180" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC34" s="183">
+        <f>ROUND(AA34/AB34,0)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="181" t="inlineStr"/>
+      <c r="AE34" s="181" t="inlineStr"/>
+      <c r="AF34" s="181" t="inlineStr"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="176" t="n">
+        <v>52</v>
+      </c>
+      <c r="B35" s="176" t="inlineStr">
+        <is>
+          <t>GPO473-1</t>
+        </is>
+      </c>
+      <c r="C35" s="176" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D35" s="176" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E35" s="176" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F35" s="202" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G35" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W33" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" s="21" t="inlineStr">
+      <c r="H35" s="178" t="n">
+        <v>98800</v>
+      </c>
+      <c r="I35" s="179">
+        <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J35" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="180">
+        <f>IFERROR(ROUND(H35*I35,0),0)</f>
+        <v/>
+      </c>
+      <c r="L35" s="180">
+        <f>IFERROR(VLOOKUP(B35,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M35" s="180">
+        <f>IFERROR(VLOOKUP(B35,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N35" s="181" t="inlineStr"/>
+      <c r="O35" s="203" t="n">
+        <v>46146</v>
+      </c>
+      <c r="P35" s="181" t="inlineStr">
+        <is>
+          <t>14008-26-101148M</t>
+        </is>
+      </c>
+      <c r="Q35" s="179">
+        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R35" s="178">
+        <f>IF(P35="","",H35)</f>
+        <v/>
+      </c>
+      <c r="S35" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="180" t="n">
+        <v>14902330</v>
+      </c>
+      <c r="U35" s="181" t="inlineStr"/>
+      <c r="V35" s="181" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W35" s="180" t="n">
+        <v>250000</v>
+      </c>
+      <c r="X35" s="181" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="Y35" s="180" t="n">
+        <v>3636072</v>
+      </c>
+      <c r="Z35" s="180">
+        <f>S35+T35+W35</f>
+        <v/>
+      </c>
+      <c r="AA35" s="183">
+        <f>K35+L35+M35+IFERROR(VLOOKUP(B35,RemitTable2,9,FALSE),0)+Y35+Z35</f>
+        <v/>
+      </c>
+      <c r="AB35" s="180" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC35" s="183">
+        <f>ROUND(AA35/AB35,0)</f>
+        <v/>
+      </c>
+      <c r="AD35" s="181" t="inlineStr"/>
+      <c r="AE35" s="181" t="inlineStr"/>
+      <c r="AF35" s="181" t="inlineStr"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="176" t="n">
+        <v>53</v>
+      </c>
+      <c r="B36" s="176" t="inlineStr">
+        <is>
+          <t>GPO479</t>
+        </is>
+      </c>
+      <c r="C36" s="176" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D36" s="176" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E36" s="176" t="inlineStr">
+        <is>
+          <t>부품(Fan)</t>
+        </is>
+      </c>
+      <c r="F36" s="202" t="n">
+        <v>46127</v>
+      </c>
+      <c r="G36" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y33" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="26">
-        <f>S30+T30+W30</f>
-        <v/>
-      </c>
-      <c r="AA33" s="26">
-        <f>K30+L30+M30+IFERROR(VLOOKUP(B30,RemitTable2,9,FALSE()),0)+Y30+Z30</f>
-        <v/>
-      </c>
-      <c r="AB33" s="27" t="n">
+      <c r="H36" s="178" t="n">
+        <v>90</v>
+      </c>
+      <c r="I36" s="179">
+        <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J36" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="180">
+        <f>IFERROR(ROUND(H36*I36,0),0)</f>
+        <v/>
+      </c>
+      <c r="L36" s="180">
+        <f>IFERROR(VLOOKUP(B36,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M36" s="180">
+        <f>IFERROR(VLOOKUP(B36,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N36" s="181" t="inlineStr"/>
+      <c r="O36" s="181" t="inlineStr"/>
+      <c r="P36" s="181" t="inlineStr"/>
+      <c r="Q36" s="179">
+        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R36" s="178">
+        <f>IF(P36="","",H36)</f>
+        <v/>
+      </c>
+      <c r="S36" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="181" t="inlineStr"/>
+      <c r="V36" s="181" t="inlineStr"/>
+      <c r="W36" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y36" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="180">
+        <f>S36+T36+W36</f>
+        <v/>
+      </c>
+      <c r="AA36" s="183">
+        <f>K36+L36+M36+IFERROR(VLOOKUP(B36,RemitTable2,9,FALSE),0)+Y36+Z36</f>
+        <v/>
+      </c>
+      <c r="AB36" s="180" t="n">
         <v>1</v>
       </c>
-      <c r="AC33" s="26">
-        <f>ROUND(AA30/AB30,0)</f>
-        <v/>
-      </c>
-      <c r="AD33" s="20" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="AE33" s="153" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AF33" s="152" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>GPO458</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F34" s="152" t="n">
-        <v>45982</v>
-      </c>
-      <c r="G34" s="153" t="n">
-        <v>46020</v>
-      </c>
-      <c r="H34" s="24" t="n">
-        <v>350</v>
-      </c>
-      <c r="I34" s="154">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J34" s="26" t="n">
-        <v>18264679</v>
-      </c>
-      <c r="K34" s="26">
-        <f>IFERROR(ROUND(H31*I31,0),0)</f>
-        <v/>
-      </c>
-      <c r="L34" s="26">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M34" s="26">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N34" s="20" t="inlineStr">
-        <is>
-          <t>HFR License</t>
-        </is>
-      </c>
-      <c r="O34" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P34" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q34" s="26">
-        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R34" s="26">
-        <f>IF(P31="","",H31)</f>
-        <v/>
-      </c>
-      <c r="S34" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W34" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y34" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="26">
-        <f>S31+T31+W31</f>
-        <v/>
-      </c>
-      <c r="AA34" s="26">
-        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
-        <v/>
-      </c>
-      <c r="AB34" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="26">
-        <f>ROUND(AA31/AB31,0)</f>
-        <v/>
-      </c>
-      <c r="AD34" s="20" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AE34" s="153" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AF34" s="152" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="20" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>CPO681</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F35" s="152" t="n">
-        <v>45993</v>
-      </c>
-      <c r="G35" s="153" t="n">
-        <v>46064</v>
-      </c>
-      <c r="H35" s="24" t="n">
-        <v>26358</v>
-      </c>
-      <c r="I35" s="154">
-        <f>IFERROR(VLOOKUP(B32,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J35" s="26" t="n">
-        <v>38550844</v>
-      </c>
-      <c r="K35" s="26">
-        <f>IFERROR(ROUND(H32*I32,0),0)</f>
-        <v/>
-      </c>
-      <c r="L35" s="26">
-        <f>IFERROR(VLOOKUP(B32,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M35" s="26">
-        <f>IFERROR(VLOOKUP(B32,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N35" s="20" t="inlineStr">
-        <is>
-          <t>EW CP2309/2315/2320-RGB</t>
-        </is>
-      </c>
-      <c r="O35" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P35" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q35" s="26">
-        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R35" s="26">
-        <f>IF(P32="","",H32)</f>
-        <v/>
-      </c>
-      <c r="S35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="26">
-        <f>S32+T32+W32</f>
-        <v/>
-      </c>
-      <c r="AA35" s="26">
-        <f>K32+L32+M32+IFERROR(VLOOKUP(B32,RemitTable2,9,FALSE()),0)+Y32+Z32</f>
-        <v/>
-      </c>
-      <c r="AB35" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC35" s="26">
-        <f>ROUND(AA32/AB32,0)</f>
-        <v/>
-      </c>
-      <c r="AD35" s="20" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AE35" s="153" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AF35" s="152" t="inlineStr">
-        <is>
-          <t>2026-12-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>GPO459</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F36" s="152" t="n">
-        <v>46007</v>
-      </c>
-      <c r="G36" s="153" t="n">
-        <v>46043</v>
-      </c>
-      <c r="H36" s="24" t="n">
-        <v>450</v>
-      </c>
-      <c r="I36" s="154">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J36" s="26" t="n">
-        <v>5505104</v>
-      </c>
-      <c r="K36" s="26">
-        <f>IFERROR(ROUND(H33*I33,0),0)</f>
-        <v/>
-      </c>
-      <c r="L36" s="26">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M36" s="26">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N36" s="20" t="inlineStr">
-        <is>
-          <t>TMS-2000 EW</t>
-        </is>
-      </c>
-      <c r="O36" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P36" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q36" s="26">
-        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R36" s="26">
-        <f>IF(P33="","",H33)</f>
-        <v/>
-      </c>
-      <c r="S36" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W36" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y36" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="26">
-        <f>S33+T33+W33</f>
-        <v/>
-      </c>
-      <c r="AA36" s="26">
-        <f>K33+L33+M33+IFERROR(VLOOKUP(B33,RemitTable2,9,FALSE()),0)+Y33+Z33</f>
-        <v/>
-      </c>
-      <c r="AB36" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC36" s="26">
-        <f>ROUND(AA33/AB33,0)</f>
-        <v/>
-      </c>
-      <c r="AD36" s="20" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="AE36" s="153" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF36" s="152" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
+      <c r="AC36" s="183">
+        <f>ROUND(AA36/AB36,0)</f>
+        <v/>
+      </c>
+      <c r="AD36" s="181" t="inlineStr"/>
+      <c r="AE36" s="181" t="inlineStr"/>
+      <c r="AF36" s="181" t="inlineStr"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="20" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -5719,36 +5804,36 @@
         </is>
       </c>
       <c r="F37" s="152" t="n">
-        <v>46007</v>
+        <v>45925</v>
       </c>
       <c r="G37" s="153" t="n">
-        <v>46043</v>
+        <v>46080</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>540</v>
+        <v>5673</v>
       </c>
       <c r="I37" s="154">
-        <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J37" s="26" t="n">
-        <v>5505104</v>
+        <v>205028994</v>
       </c>
       <c r="K37" s="26">
-        <f>IFERROR(ROUND(H34*I34,0),0)</f>
+        <f>IFERROR(ROUND(H30*I30,0),0)</f>
         <v/>
       </c>
       <c r="L37" s="26">
-        <f>IFERROR(VLOOKUP(B34,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B30,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M37" s="26">
-        <f>IFERROR(VLOOKUP(B34,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B30,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 EW</t>
+          <t>EW CP2220</t>
         </is>
       </c>
       <c r="O37" s="20" t="inlineStr">
@@ -5762,11 +5847,11 @@
         </is>
       </c>
       <c r="Q37" s="26">
-        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R37" s="26">
-        <f>IF(P34="","",H34)</f>
+        <f>IF(P30="","",H30)</f>
         <v/>
       </c>
       <c r="S37" s="26" t="n">
@@ -5795,91 +5880,91 @@
         <v>0</v>
       </c>
       <c r="Z37" s="26">
-        <f>S34+T34+W34</f>
+        <f>S30+T30+W30</f>
         <v/>
       </c>
       <c r="AA37" s="26">
-        <f>K34+L34+M34+IFERROR(VLOOKUP(B34,RemitTable2,9,FALSE()),0)+Y34+Z34</f>
+        <f>K30+L30+M30+IFERROR(VLOOKUP(B30,RemitTable2,9,FALSE()),0)+Y30+Z30</f>
         <v/>
       </c>
       <c r="AB37" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC37" s="26">
-        <f>ROUND(AA34/AB34,0)</f>
+        <f>ROUND(AA30/AB30,0)</f>
         <v/>
       </c>
       <c r="AD37" s="20" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="AE37" s="153" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AF37" s="152" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="20" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F38" s="152" t="n">
-        <v>46010</v>
+        <v>45982</v>
       </c>
       <c r="G38" s="153" t="n">
-        <v>46080</v>
+        <v>46020</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>136516</v>
+        <v>350</v>
       </c>
       <c r="I38" s="154">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J38" s="26" t="n">
-        <v>205028994</v>
+        <v>18264679</v>
       </c>
       <c r="K38" s="26">
-        <f>IFERROR(ROUND(H35*I35,0),0)</f>
+        <f>IFERROR(ROUND(H31*I31,0),0)</f>
         <v/>
       </c>
       <c r="L38" s="26">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M38" s="26">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (CP2208~CP4450)</t>
+          <t>HFR License</t>
         </is>
       </c>
       <c r="O38" s="20" t="inlineStr">
@@ -5893,11 +5978,11 @@
         </is>
       </c>
       <c r="Q38" s="26">
-        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R38" s="26">
-        <f>IF(P35="","",H35)</f>
+        <f>IF(P31="","",H31)</f>
         <v/>
       </c>
       <c r="S38" s="26" t="n">
@@ -5926,53 +6011,53 @@
         <v>0</v>
       </c>
       <c r="Z38" s="26">
-        <f>S35+T35+W35</f>
+        <f>S31+T31+W31</f>
         <v/>
       </c>
       <c r="AA38" s="26">
-        <f>K35+L35+M35+IFERROR(VLOOKUP(B35,RemitTable2,9,FALSE()),0)+Y35+Z35</f>
+        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
         <v/>
       </c>
       <c r="AB38" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC38" s="26">
-        <f>ROUND(AA35/AB35,0)</f>
+        <f>ROUND(AA31/AB31,0)</f>
         <v/>
       </c>
       <c r="AD38" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE38" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AF38" s="152" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="20" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>GPO465</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -5981,131 +6066,129 @@
         </is>
       </c>
       <c r="F39" s="152" t="n">
-        <v>46015</v>
-      </c>
-      <c r="G39" s="153" t="inlineStr">
+        <v>45993</v>
+      </c>
+      <c r="G39" s="153" t="n">
+        <v>46064</v>
+      </c>
+      <c r="H39" s="24" t="n">
+        <v>26358</v>
+      </c>
+      <c r="I39" s="154">
+        <f>IFERROR(VLOOKUP(B32,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J39" s="26" t="n">
+        <v>38550844</v>
+      </c>
+      <c r="K39" s="26">
+        <f>IFERROR(ROUND(H32*I32,0),0)</f>
+        <v/>
+      </c>
+      <c r="L39" s="26">
+        <f>IFERROR(VLOOKUP(B32,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M39" s="26">
+        <f>IFERROR(VLOOKUP(B32,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N39" s="20" t="inlineStr">
+        <is>
+          <t>EW CP2309/2315/2320-RGB</t>
+        </is>
+      </c>
+      <c r="O39" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H39" s="24" t="n">
-        <v>76054</v>
-      </c>
-      <c r="I39" s="154">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="26">
-        <f>IFERROR(ROUND(H36*I36,0),0)</f>
-        <v/>
-      </c>
-      <c r="L39" s="26">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M39" s="26">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N39" s="20" t="inlineStr">
-        <is>
-          <t>EW 대량 (SR/SX/TMS)</t>
-        </is>
-      </c>
-      <c r="O39" s="20" t="inlineStr">
+      <c r="P39" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P39" s="20" t="inlineStr">
+      <c r="Q39" s="26">
+        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R39" s="26">
+        <f>IF(P32="","",H32)</f>
+        <v/>
+      </c>
+      <c r="S39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q39" s="26">
-        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R39" s="26">
-        <f>IF(P36="","",H36)</f>
-        <v/>
-      </c>
-      <c r="S39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="20" t="inlineStr">
+      <c r="W39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="Y39" s="26" t="n">
         <v>0</v>
       </c>
       <c r="Z39" s="26">
-        <f>S36+T36+W36</f>
+        <f>S32+T32+W32</f>
         <v/>
       </c>
       <c r="AA39" s="26">
-        <f>K36+L36+M36+IFERROR(VLOOKUP(B36,RemitTable2,9,FALSE()),0)+Y36+Z36</f>
+        <f>K32+L32+M32+IFERROR(VLOOKUP(B32,RemitTable2,9,FALSE()),0)+Y32+Z32</f>
         <v/>
       </c>
       <c r="AB39" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC39" s="26">
-        <f>ROUND(AA36/AB36,0)</f>
+        <f>ROUND(AA32/AB32,0)</f>
         <v/>
       </c>
       <c r="AD39" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE39" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AF39" s="152" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-21</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -6114,36 +6197,36 @@
         </is>
       </c>
       <c r="F40" s="152" t="n">
-        <v>46029</v>
+        <v>46007</v>
       </c>
       <c r="G40" s="153" t="n">
-        <v>46072</v>
+        <v>46043</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>14793</v>
+        <v>450</v>
       </c>
       <c r="I40" s="154">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J40" s="26" t="n">
-        <v>25506948</v>
+        <v>5505104</v>
       </c>
       <c r="K40" s="26">
-        <f>IFERROR(ROUND(H37*I37,0),0)</f>
+        <f>IFERROR(ROUND(H33*I33,0),0)</f>
         <v/>
       </c>
       <c r="L40" s="26">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B33,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M40" s="26">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B33,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>EW CP2315/CP4440-RGB</t>
+          <t>TMS-2000 EW</t>
         </is>
       </c>
       <c r="O40" s="20" t="inlineStr">
@@ -6157,11 +6240,11 @@
         </is>
       </c>
       <c r="Q40" s="26">
-        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R40" s="26">
-        <f>IF(P37="","",H37)</f>
+        <f>IF(P33="","",H33)</f>
         <v/>
       </c>
       <c r="S40" s="26" t="n">
@@ -6190,18 +6273,18 @@
         <v>0</v>
       </c>
       <c r="Z40" s="26">
-        <f>S37+T37+W37</f>
+        <f>S33+T33+W33</f>
         <v/>
       </c>
       <c r="AA40" s="26">
-        <f>K37+L37+M37+IFERROR(VLOOKUP(B37,RemitTable2,9,FALSE()),0)+Y37+Z37</f>
+        <f>K33+L33+M33+IFERROR(VLOOKUP(B33,RemitTable2,9,FALSE()),0)+Y33+Z33</f>
         <v/>
       </c>
       <c r="AB40" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC40" s="26">
-        <f>ROUND(AA37/AB37,0)</f>
+        <f>ROUND(AA33/AB33,0)</f>
         <v/>
       </c>
       <c r="AD40" s="20" t="inlineStr">
@@ -6211,32 +6294,32 @@
       </c>
       <c r="AE40" s="153" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF40" s="152" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="20" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>CPO687</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
@@ -6245,169 +6328,167 @@
         </is>
       </c>
       <c r="F41" s="152" t="n">
-        <v>46029</v>
-      </c>
-      <c r="G41" s="153" t="inlineStr">
+        <v>46007</v>
+      </c>
+      <c r="G41" s="153" t="n">
+        <v>46043</v>
+      </c>
+      <c r="H41" s="24" t="n">
+        <v>540</v>
+      </c>
+      <c r="I41" s="154">
+        <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J41" s="26" t="n">
+        <v>5505104</v>
+      </c>
+      <c r="K41" s="26">
+        <f>IFERROR(ROUND(H34*I34,0),0)</f>
+        <v/>
+      </c>
+      <c r="L41" s="26">
+        <f>IFERROR(VLOOKUP(B34,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M41" s="26">
+        <f>IFERROR(VLOOKUP(B34,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
+        <is>
+          <t>TMS-1000 EW</t>
+        </is>
+      </c>
+      <c r="O41" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H41" s="24" t="n">
-        <v>26656</v>
-      </c>
-      <c r="I41" s="154">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="26">
-        <f>IFERROR(ROUND(H38*I38,0),0)</f>
-        <v/>
-      </c>
-      <c r="L41" s="26">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M41" s="26">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N41" s="20" t="inlineStr">
-        <is>
-          <t>EW (홀딩)</t>
-        </is>
-      </c>
-      <c r="O41" s="20" t="inlineStr">
+      <c r="P41" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P41" s="20" t="inlineStr">
+      <c r="Q41" s="26">
+        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R41" s="26">
+        <f>IF(P34="","",H34)</f>
+        <v/>
+      </c>
+      <c r="S41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q41" s="26">
-        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R41" s="26">
-        <f>IF(P38="","",H38)</f>
-        <v/>
-      </c>
-      <c r="S41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="20" t="inlineStr">
+      <c r="W41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="Y41" s="26" t="n">
         <v>0</v>
       </c>
       <c r="Z41" s="26">
-        <f>S38+T38+W38</f>
+        <f>S34+T34+W34</f>
         <v/>
       </c>
       <c r="AA41" s="26">
-        <f>K38+L38+M38+IFERROR(VLOOKUP(B38,RemitTable2,9,FALSE()),0)+Y38+Z38</f>
+        <f>K34+L34+M34+IFERROR(VLOOKUP(B34,RemitTable2,9,FALSE()),0)+Y34+Z34</f>
         <v/>
       </c>
       <c r="AB41" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC41" s="26">
-        <f>ROUND(AA38/AB38,0)</f>
+        <f>ROUND(AA34/AB34,0)</f>
         <v/>
       </c>
       <c r="AD41" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="AE41" s="153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AF41" s="152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F42" s="152" t="n">
-        <v>46042</v>
+        <v>46010</v>
       </c>
       <c r="G42" s="153" t="n">
-        <v>46057</v>
+        <v>46080</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>1440</v>
+        <v>136516</v>
       </c>
       <c r="I42" s="154">
-        <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J42" s="26" t="n">
-        <v>16908206</v>
+        <v>205028994</v>
       </c>
       <c r="K42" s="26">
-        <f>IFERROR(ROUND(H39*I39,0),0)</f>
+        <f>IFERROR(ROUND(H35*I35,0),0)</f>
         <v/>
       </c>
       <c r="L42" s="26">
-        <f>IFERROR(VLOOKUP(B39,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B35,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M42" s="26">
-        <f>IFERROR(VLOOKUP(B39,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B35,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 License</t>
+          <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
       <c r="O42" s="20" t="inlineStr">
@@ -6421,11 +6502,11 @@
         </is>
       </c>
       <c r="Q42" s="26">
-        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R42" s="26">
-        <f>IF(P39="","",H39)</f>
+        <f>IF(P35="","",H35)</f>
         <v/>
       </c>
       <c r="S42" s="26" t="n">
@@ -6454,18 +6535,18 @@
         <v>0</v>
       </c>
       <c r="Z42" s="26">
-        <f>S39+T39+W39</f>
+        <f>S35+T35+W35</f>
         <v/>
       </c>
       <c r="AA42" s="26">
-        <f>K39+L39+M39+IFERROR(VLOOKUP(B39,RemitTable2,9,FALSE()),0)+Y39+Z39</f>
+        <f>K35+L35+M35+IFERROR(VLOOKUP(B35,RemitTable2,9,FALSE()),0)+Y35+Z35</f>
         <v/>
       </c>
       <c r="AB42" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC42" s="26">
-        <f>ROUND(AA39/AB39,0)</f>
+        <f>ROUND(AA35/AB35,0)</f>
         <v/>
       </c>
       <c r="AD42" s="20" t="inlineStr">
@@ -6486,11 +6567,11 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="20" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>GPO465</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
@@ -6509,36 +6590,38 @@
         </is>
       </c>
       <c r="F43" s="152" t="n">
-        <v>46042</v>
-      </c>
-      <c r="G43" s="153" t="n">
-        <v>46057</v>
+        <v>46015</v>
+      </c>
+      <c r="G43" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H43" s="24" t="n">
-        <v>4489</v>
+        <v>76054</v>
       </c>
       <c r="I43" s="154">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J43" s="26" t="n">
-        <v>16908206</v>
+        <v>0</v>
       </c>
       <c r="K43" s="26">
-        <f>IFERROR(ROUND(H40*I40,0),0)</f>
+        <f>IFERROR(ROUND(H36*I36,0),0)</f>
         <v/>
       </c>
       <c r="L43" s="26">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B36,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M43" s="26">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B36,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
-          <t>SX/SR EW (CGV/Lotte)</t>
+          <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
       <c r="O43" s="20" t="inlineStr">
@@ -6552,11 +6635,11 @@
         </is>
       </c>
       <c r="Q43" s="26">
-        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R43" s="26">
-        <f>IF(P40="","",H40)</f>
+        <f>IF(P36="","",H36)</f>
         <v/>
       </c>
       <c r="S43" s="26" t="n">
@@ -6585,18 +6668,18 @@
         <v>0</v>
       </c>
       <c r="Z43" s="26">
-        <f>S40+T40+W40</f>
+        <f>S36+T36+W36</f>
         <v/>
       </c>
       <c r="AA43" s="26">
-        <f>K40+L40+M40+IFERROR(VLOOKUP(B40,RemitTable2,9,FALSE()),0)+Y40+Z40</f>
+        <f>K36+L36+M36+IFERROR(VLOOKUP(B36,RemitTable2,9,FALSE()),0)+Y36+Z36</f>
         <v/>
       </c>
       <c r="AB43" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC43" s="26">
-        <f>ROUND(AA40/AB40,0)</f>
+        <f>ROUND(AA36/AB36,0)</f>
         <v/>
       </c>
       <c r="AD43" s="20" t="inlineStr">
@@ -6617,21 +6700,21 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="20" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E44" s="21" t="inlineStr">
@@ -6640,36 +6723,36 @@
         </is>
       </c>
       <c r="F44" s="152" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="G44" s="153" t="n">
-        <v>46057</v>
+        <v>46072</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>5670.57</v>
+        <v>14793</v>
       </c>
       <c r="I44" s="154">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J44" s="26" t="n">
-        <v>16908206</v>
+        <v>25506948</v>
       </c>
       <c r="K44" s="26">
-        <f>IFERROR(ROUND(H41*I41,0),0)</f>
+        <f>IFERROR(ROUND(H37*I37,0),0)</f>
         <v/>
       </c>
       <c r="L44" s="26">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B37,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M44" s="26">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B37,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t>SR-1000/SX-3000 EW</t>
+          <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
       <c r="O44" s="20" t="inlineStr">
@@ -6683,11 +6766,11 @@
         </is>
       </c>
       <c r="Q44" s="26">
-        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R44" s="26">
-        <f>IF(P41="","",H41)</f>
+        <f>IF(P37="","",H37)</f>
         <v/>
       </c>
       <c r="S44" s="26" t="n">
@@ -6716,18 +6799,18 @@
         <v>0</v>
       </c>
       <c r="Z44" s="26">
-        <f>S41+T41+W41</f>
+        <f>S37+T37+W37</f>
         <v/>
       </c>
       <c r="AA44" s="26">
-        <f>K41+L41+M41+IFERROR(VLOOKUP(B41,RemitTable2,9,FALSE()),0)+Y41+Z41</f>
+        <f>K37+L37+M37+IFERROR(VLOOKUP(B37,RemitTable2,9,FALSE()),0)+Y37+Z37</f>
         <v/>
       </c>
       <c r="AB44" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC44" s="26">
-        <f>ROUND(AA41/AB41,0)</f>
+        <f>ROUND(AA37/AB37,0)</f>
         <v/>
       </c>
       <c r="AD44" s="20" t="inlineStr">
@@ -6737,22 +6820,22 @@
       </c>
       <c r="AE44" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AF44" s="152" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-29</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="20" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>CPO687</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
@@ -6771,36 +6854,38 @@
         </is>
       </c>
       <c r="F45" s="152" t="n">
-        <v>46057</v>
-      </c>
-      <c r="G45" s="153" t="n">
-        <v>46113</v>
+        <v>46029</v>
+      </c>
+      <c r="G45" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H45" s="24" t="n">
-        <v>24614</v>
+        <v>26656</v>
       </c>
       <c r="I45" s="154">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J45" s="26" t="n">
-        <v>51777431</v>
+        <v>0</v>
       </c>
       <c r="K45" s="26">
-        <f>IFERROR(ROUND(H42*I42,0),0)</f>
+        <f>IFERROR(ROUND(H38*I38,0),0)</f>
         <v/>
       </c>
       <c r="L45" s="26">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B38,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M45" s="26">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B38,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>EW (메가박스 외)</t>
+          <t>EW (홀딩)</t>
         </is>
       </c>
       <c r="O45" s="20" t="inlineStr">
@@ -6814,11 +6899,11 @@
         </is>
       </c>
       <c r="Q45" s="26">
-        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R45" s="26">
-        <f>IF(P42="","",H42)</f>
+        <f>IF(P38="","",H38)</f>
         <v/>
       </c>
       <c r="S45" s="26" t="n">
@@ -6847,43 +6932,43 @@
         <v>0</v>
       </c>
       <c r="Z45" s="26">
-        <f>S42+T42+W42</f>
+        <f>S38+T38+W38</f>
         <v/>
       </c>
       <c r="AA45" s="26">
-        <f>K42+L42+M42+IFERROR(VLOOKUP(B42,RemitTable2,9,FALSE()),0)+Y42+Z42</f>
+        <f>K38+L38+M38+IFERROR(VLOOKUP(B38,RemitTable2,9,FALSE()),0)+Y38+Z38</f>
         <v/>
       </c>
       <c r="AB45" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC45" s="26">
-        <f>ROUND(AA42/AB42,0)</f>
+        <f>ROUND(AA38/AB38,0)</f>
         <v/>
       </c>
       <c r="AD45" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE45" s="153" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AF45" s="152" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="20" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
@@ -6898,40 +6983,40 @@
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F46" s="152" t="n">
-        <v>46060</v>
+        <v>46042</v>
       </c>
       <c r="G46" s="153" t="n">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>3993.05</v>
+        <v>1440</v>
       </c>
       <c r="I46" s="154">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J46" s="26" t="n">
-        <v>9919642</v>
+        <v>16908206</v>
       </c>
       <c r="K46" s="26">
-        <f>IFERROR(ROUND(H43*I43,0),0)</f>
+        <f>IFERROR(ROUND(H39*I39,0),0)</f>
         <v/>
       </c>
       <c r="L46" s="26">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B39,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M46" s="26">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B39,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>SR/SX EW (하남미사 외)</t>
+          <t>TMS-2000 License</t>
         </is>
       </c>
       <c r="O46" s="20" t="inlineStr">
@@ -6945,11 +7030,11 @@
         </is>
       </c>
       <c r="Q46" s="26">
-        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R46" s="26">
-        <f>IF(P43="","",H43)</f>
+        <f>IF(P39="","",H39)</f>
         <v/>
       </c>
       <c r="S46" s="26" t="n">
@@ -6978,18 +7063,18 @@
         <v>0</v>
       </c>
       <c r="Z46" s="26">
-        <f>S43+T43+W43</f>
+        <f>S39+T39+W39</f>
         <v/>
       </c>
       <c r="AA46" s="26">
-        <f>K43+L43+M43+IFERROR(VLOOKUP(B43,RemitTable2,9,FALSE()),0)+Y43+Z43</f>
+        <f>K39+L39+M39+IFERROR(VLOOKUP(B39,RemitTable2,9,FALSE()),0)+Y39+Z39</f>
         <v/>
       </c>
       <c r="AB46" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC46" s="26">
-        <f>ROUND(AA43/AB43,0)</f>
+        <f>ROUND(AA39/AB39,0)</f>
         <v/>
       </c>
       <c r="AD46" s="20" t="inlineStr">
@@ -7004,17 +7089,17 @@
       </c>
       <c r="AF46" s="152" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="20" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
@@ -7029,40 +7114,40 @@
       </c>
       <c r="E47" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F47" s="152" t="n">
-        <v>46080</v>
+        <v>46042</v>
       </c>
       <c r="G47" s="153" t="n">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>360</v>
+        <v>4489</v>
       </c>
       <c r="I47" s="154">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J47" s="26" t="n">
-        <v>9919642</v>
+        <v>16908206</v>
       </c>
       <c r="K47" s="26">
-        <f>IFERROR(ROUND(H44*I44,0),0)</f>
+        <f>IFERROR(ROUND(H40*I40,0),0)</f>
         <v/>
       </c>
       <c r="L47" s="26">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M47" s="26">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 License</t>
+          <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
       <c r="O47" s="20" t="inlineStr">
@@ -7076,11 +7161,11 @@
         </is>
       </c>
       <c r="Q47" s="26">
-        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R47" s="26">
-        <f>IF(P44="","",H44)</f>
+        <f>IF(P40="","",H40)</f>
         <v/>
       </c>
       <c r="S47" s="26" t="n">
@@ -7109,43 +7194,43 @@
         <v>0</v>
       </c>
       <c r="Z47" s="26">
-        <f>S44+T44+W44</f>
+        <f>S40+T40+W40</f>
         <v/>
       </c>
       <c r="AA47" s="26">
-        <f>K44+L44+M44+IFERROR(VLOOKUP(B44,RemitTable2,9,FALSE()),0)+Y44+Z44</f>
+        <f>K40+L40+M40+IFERROR(VLOOKUP(B40,RemitTable2,9,FALSE()),0)+Y40+Z40</f>
         <v/>
       </c>
       <c r="AB47" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC47" s="26">
-        <f>ROUND(AA44/AB44,0)</f>
+        <f>ROUND(AA40/AB40,0)</f>
         <v/>
       </c>
       <c r="AD47" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE47" s="153" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF47" s="152" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
@@ -7160,40 +7245,40 @@
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F48" s="152" t="n">
-        <v>46088</v>
+        <v>46042</v>
       </c>
       <c r="G48" s="153" t="n">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>500</v>
+        <v>5670.57</v>
       </c>
       <c r="I48" s="154">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J48" s="26" t="n">
-        <v>9919642</v>
+        <v>16908206</v>
       </c>
       <c r="K48" s="26">
-        <f>IFERROR(ROUND(H45*I45,0),0)</f>
+        <f>IFERROR(ROUND(H41*I41,0),0)</f>
         <v/>
       </c>
       <c r="L48" s="26">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B41,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M48" s="26">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B41,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>Dolby Atmos License</t>
+          <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
       <c r="O48" s="20" t="inlineStr">
@@ -7207,11 +7292,11 @@
         </is>
       </c>
       <c r="Q48" s="26">
-        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R48" s="26">
-        <f>IF(P45="","",H45)</f>
+        <f>IF(P41="","",H41)</f>
         <v/>
       </c>
       <c r="S48" s="26" t="n">
@@ -7240,43 +7325,43 @@
         <v>0</v>
       </c>
       <c r="Z48" s="26">
-        <f>S45+T45+W45</f>
+        <f>S41+T41+W41</f>
         <v/>
       </c>
       <c r="AA48" s="26">
-        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE()),0)+Y45+Z45</f>
+        <f>K41+L41+M41+IFERROR(VLOOKUP(B41,RemitTable2,9,FALSE()),0)+Y41+Z41</f>
         <v/>
       </c>
       <c r="AB48" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC48" s="26">
-        <f>ROUND(AA45/AB45,0)</f>
+        <f>ROUND(AA41/AB41,0)</f>
         <v/>
       </c>
       <c r="AD48" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE48" s="153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF48" s="152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="20" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
@@ -7295,36 +7380,36 @@
         </is>
       </c>
       <c r="F49" s="152" t="n">
-        <v>46109</v>
+        <v>46057</v>
       </c>
       <c r="G49" s="153" t="n">
-        <v>46146</v>
+        <v>46113</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>17404</v>
+        <v>24614</v>
       </c>
       <c r="I49" s="154">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J49" s="26" t="n">
-        <v>0</v>
+        <v>51777431</v>
       </c>
       <c r="K49" s="26">
-        <f>IFERROR(ROUND(H49*I49,0),0)</f>
+        <f>IFERROR(ROUND(H42*I42,0),0)</f>
         <v/>
       </c>
       <c r="L49" s="26">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B42,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M49" s="26">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B42,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
-          <t>EW (CGV 동백 외)</t>
+          <t>EW (메가박스 외)</t>
         </is>
       </c>
       <c r="O49" s="20" t="inlineStr">
@@ -7338,11 +7423,11 @@
         </is>
       </c>
       <c r="Q49" s="26">
-        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R49" s="26">
-        <f>IF(P49="","",H49)</f>
+        <f>IF(P42="","",H42)</f>
         <v/>
       </c>
       <c r="S49" s="26" t="n">
@@ -7371,997 +7456,1834 @@
         <v>0</v>
       </c>
       <c r="Z49" s="26">
-        <f>S49+T49+W49</f>
+        <f>S42+T42+W42</f>
         <v/>
       </c>
       <c r="AA49" s="26">
-        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE()),0)+Y49+Z49</f>
+        <f>K42+L42+M42+IFERROR(VLOOKUP(B42,RemitTable2,9,FALSE()),0)+Y42+Z42</f>
         <v/>
       </c>
       <c r="AB49" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC49" s="26">
+        <f>ROUND(AA42/AB42,0)</f>
+        <v/>
+      </c>
+      <c r="AD49" s="20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE49" s="153" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AF49" s="152" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>GPO469</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F50" s="152" t="n">
+        <v>46060</v>
+      </c>
+      <c r="G50" s="153" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H50" s="24" t="n">
+        <v>3993.05</v>
+      </c>
+      <c r="I50" s="154">
+        <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J50" s="26" t="n">
+        <v>9919642</v>
+      </c>
+      <c r="K50" s="26">
+        <f>IFERROR(ROUND(H43*I43,0),0)</f>
+        <v/>
+      </c>
+      <c r="L50" s="26">
+        <f>IFERROR(VLOOKUP(B43,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M50" s="26">
+        <f>IFERROR(VLOOKUP(B43,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N50" s="20" t="inlineStr">
+        <is>
+          <t>SR/SX EW (하남미사 외)</t>
+        </is>
+      </c>
+      <c r="O50" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q50" s="26">
+        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R50" s="26">
+        <f>IF(P43="","",H43)</f>
+        <v/>
+      </c>
+      <c r="S50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="26">
+        <f>S43+T43+W43</f>
+        <v/>
+      </c>
+      <c r="AA50" s="26">
+        <f>K43+L43+M43+IFERROR(VLOOKUP(B43,RemitTable2,9,FALSE()),0)+Y43+Z43</f>
+        <v/>
+      </c>
+      <c r="AB50" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC50" s="26">
+        <f>ROUND(AA43/AB43,0)</f>
+        <v/>
+      </c>
+      <c r="AD50" s="20" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AE50" s="153" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AF50" s="152" t="inlineStr">
+        <is>
+          <t>2027-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>GPO470</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F51" s="152" t="n">
+        <v>46080</v>
+      </c>
+      <c r="G51" s="153" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H51" s="24" t="n">
+        <v>360</v>
+      </c>
+      <c r="I51" s="154">
+        <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J51" s="26" t="n">
+        <v>9919642</v>
+      </c>
+      <c r="K51" s="26">
+        <f>IFERROR(ROUND(H44*I44,0),0)</f>
+        <v/>
+      </c>
+      <c r="L51" s="26">
+        <f>IFERROR(VLOOKUP(B44,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M51" s="26">
+        <f>IFERROR(VLOOKUP(B44,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N51" s="20" t="inlineStr">
+        <is>
+          <t>TMS-1000 License</t>
+        </is>
+      </c>
+      <c r="O51" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q51" s="26">
+        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R51" s="26">
+        <f>IF(P44="","",H44)</f>
+        <v/>
+      </c>
+      <c r="S51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="26">
+        <f>S44+T44+W44</f>
+        <v/>
+      </c>
+      <c r="AA51" s="26">
+        <f>K44+L44+M44+IFERROR(VLOOKUP(B44,RemitTable2,9,FALSE()),0)+Y44+Z44</f>
+        <v/>
+      </c>
+      <c r="AB51" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" s="26">
+        <f>ROUND(AA44/AB44,0)</f>
+        <v/>
+      </c>
+      <c r="AD51" s="20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE51" s="153" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AF51" s="152" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>GPO471</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F52" s="152" t="n">
+        <v>46088</v>
+      </c>
+      <c r="G52" s="153" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H52" s="24" t="n">
+        <v>500</v>
+      </c>
+      <c r="I52" s="154">
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J52" s="26" t="n">
+        <v>9919642</v>
+      </c>
+      <c r="K52" s="26">
+        <f>IFERROR(ROUND(H45*I45,0),0)</f>
+        <v/>
+      </c>
+      <c r="L52" s="26">
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M52" s="26">
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N52" s="20" t="inlineStr">
+        <is>
+          <t>Dolby Atmos License</t>
+        </is>
+      </c>
+      <c r="O52" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P52" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q52" s="26">
+        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R52" s="26">
+        <f>IF(P45="","",H45)</f>
+        <v/>
+      </c>
+      <c r="S52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="26">
+        <f>S45+T45+W45</f>
+        <v/>
+      </c>
+      <c r="AA52" s="26">
+        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE()),0)+Y45+Z45</f>
+        <v/>
+      </c>
+      <c r="AB52" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC52" s="26">
+        <f>ROUND(AA45/AB45,0)</f>
+        <v/>
+      </c>
+      <c r="AD52" s="20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE52" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF52" s="152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>CPO694</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F53" s="152" t="n">
+        <v>46109</v>
+      </c>
+      <c r="G53" s="153" t="n">
+        <v>46146</v>
+      </c>
+      <c r="H53" s="24" t="n">
+        <v>17404</v>
+      </c>
+      <c r="I53" s="154">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="26">
+        <f>IFERROR(ROUND(H49*I49,0),0)</f>
+        <v/>
+      </c>
+      <c r="L53" s="26">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M53" s="26">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N53" s="20" t="inlineStr">
+        <is>
+          <t>EW (CGV 동백 외)</t>
+        </is>
+      </c>
+      <c r="O53" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P53" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q53" s="26">
+        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R53" s="26">
+        <f>IF(P49="","",H49)</f>
+        <v/>
+      </c>
+      <c r="S53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="26">
+        <f>S49+T49+W49</f>
+        <v/>
+      </c>
+      <c r="AA53" s="26">
+        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE()),0)+Y49+Z49</f>
+        <v/>
+      </c>
+      <c r="AB53" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC53" s="26">
         <f>ROUND(AA49/AB49,0)</f>
         <v/>
       </c>
-      <c r="AD49" s="20" t="inlineStr">
+      <c r="AD53" s="20" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE49" s="153" t="inlineStr">
+      <c r="AE53" s="153" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AF49" s="152" t="inlineStr">
+      <c r="AF53" s="152" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="85" t="n">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="85" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="85" t="inlineStr">
+      <c r="B54" s="85" t="inlineStr">
         <is>
           <t>CPO697</t>
         </is>
       </c>
-      <c r="C50" s="85" t="inlineStr">
+      <c r="C54" s="85" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D50" s="85" t="inlineStr">
+      <c r="D54" s="85" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E50" s="85" t="inlineStr">
+      <c r="E54" s="85" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F50" s="155" t="n">
+      <c r="F54" s="155" t="n">
         <v>46136</v>
       </c>
-      <c r="G50" s="155" t="inlineStr">
+      <c r="G54" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H50" s="87" t="n">
+      <c r="H54" s="87" t="n">
         <v>15289</v>
       </c>
-      <c r="I50" s="156">
+      <c r="I54" s="156">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J50" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="89">
+      <c r="J54" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="89">
         <f>IFERROR(ROUND(H50*I50,0),0)</f>
         <v/>
       </c>
-      <c r="L50" s="89">
+      <c r="L54" s="89">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="M50" s="89">
+      <c r="M54" s="89">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="N50" s="85" t="inlineStr">
+      <c r="N54" s="85" t="inlineStr">
         <is>
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O50" s="155" t="inlineStr">
+      <c r="O54" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P50" s="85" t="inlineStr">
+      <c r="P54" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q50" s="157">
+      <c r="Q54" s="157">
         <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R50" s="87">
+      <c r="R54" s="87">
         <f>IF(P50="","",H50)</f>
         <v/>
       </c>
-      <c r="S50" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="155" t="n"/>
-      <c r="V50" s="85" t="inlineStr">
+      <c r="S54" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="155" t="n"/>
+      <c r="V54" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W50" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="85" t="inlineStr">
+      <c r="W54" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y50" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="89">
+      <c r="Y54" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="89">
         <f>S50+T50+W50</f>
         <v/>
       </c>
-      <c r="AA50" s="89">
+      <c r="AA54" s="89">
         <f>K50+L50+M50+IFERROR(VLOOKUP(B50,RemitTable2,9,FALSE()),0)+Y50+Z50</f>
         <v/>
       </c>
-      <c r="AB50" s="90" t="n">
+      <c r="AB54" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="AC50" s="89">
+      <c r="AC54" s="89">
         <f>ROUND(AA50/AB50,0)</f>
         <v/>
       </c>
-      <c r="AD50" s="85" t="inlineStr">
+      <c r="AD54" s="85" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE50" s="155" t="n"/>
-      <c r="AF50" s="155" t="n"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="85" t="n">
+      <c r="AE54" s="155" t="n"/>
+      <c r="AF54" s="155" t="n"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="85" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="85" t="inlineStr">
+      <c r="B55" s="85" t="inlineStr">
         <is>
           <t>CPO693-2</t>
         </is>
       </c>
-      <c r="C51" s="85" t="inlineStr">
+      <c r="C55" s="85" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D51" s="85" t="inlineStr">
+      <c r="D55" s="85" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E51" s="85" t="inlineStr">
+      <c r="E55" s="85" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F51" s="155" t="n">
+      <c r="F55" s="155" t="n">
         <v>46133</v>
       </c>
-      <c r="G51" s="155" t="inlineStr">
+      <c r="G55" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H51" s="87" t="n">
+      <c r="H55" s="87" t="n">
         <v>2550</v>
       </c>
-      <c r="I51" s="156">
+      <c r="I55" s="156">
         <f>IFERROR(VLOOKUP(B51,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J51" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="89">
+      <c r="J55" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="89">
         <f>IFERROR(ROUND(H51*I51,0),0)</f>
         <v/>
       </c>
-      <c r="L51" s="89">
+      <c r="L55" s="89">
         <f>IFERROR(VLOOKUP(B51,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="M51" s="89">
+      <c r="M55" s="89">
         <f>IFERROR(VLOOKUP(B51,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="N51" s="85" t="inlineStr">
+      <c r="N55" s="85" t="inlineStr">
         <is>
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O51" s="155" t="inlineStr">
+      <c r="O55" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P51" s="85" t="inlineStr">
+      <c r="P55" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q51" s="157">
+      <c r="Q55" s="157">
         <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R51" s="87">
+      <c r="R55" s="87">
         <f>IF(P51="","",H51)</f>
         <v/>
       </c>
-      <c r="S51" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="155" t="n"/>
-      <c r="V51" s="85" t="inlineStr">
+      <c r="S55" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="155" t="n"/>
+      <c r="V55" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W51" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="85" t="inlineStr">
+      <c r="W55" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y51" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="89">
+      <c r="Y55" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="89">
         <f>S51+T51+W51</f>
         <v/>
       </c>
-      <c r="AA51" s="89">
+      <c r="AA55" s="89">
         <f>K51+L51+M51+IFERROR(VLOOKUP(B51,RemitTable2,9,FALSE()),0)+Y51+Z51</f>
         <v/>
       </c>
-      <c r="AB51" s="90" t="n">
+      <c r="AB55" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="AC51" s="89">
+      <c r="AC55" s="89">
         <f>ROUND(AA51/AB51,0)</f>
         <v/>
       </c>
-      <c r="AD51" s="85" t="inlineStr">
+      <c r="AD55" s="85" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE51" s="155" t="n"/>
-      <c r="AF51" s="155" t="n"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="12" t="n">
+      <c r="AE55" s="155" t="n"/>
+      <c r="AF55" s="155" t="n"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="184" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="184" t="inlineStr">
+        <is>
+          <t>GPO478</t>
+        </is>
+      </c>
+      <c r="C56" s="184" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D56" s="184" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E56" s="184" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F56" s="204" t="n">
+        <v>46127</v>
+      </c>
+      <c r="G56" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="186" t="n">
+        <v>180</v>
+      </c>
+      <c r="I56" s="187">
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J56" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="188">
+        <f>IFERROR(ROUND(H56*I56,0),0)</f>
+        <v/>
+      </c>
+      <c r="L56" s="188">
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M56" s="188">
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N56" s="189" t="inlineStr"/>
+      <c r="O56" s="189" t="inlineStr"/>
+      <c r="P56" s="189" t="inlineStr"/>
+      <c r="Q56" s="187">
+        <f>IF(P56="","",IFERROR(VLOOKUP(O56,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R56" s="186">
+        <f>IF(P56="","",H56)</f>
+        <v/>
+      </c>
+      <c r="S56" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="189" t="inlineStr"/>
+      <c r="V56" s="189" t="inlineStr"/>
+      <c r="W56" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y56" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="188">
+        <f>S56+T56+W56</f>
+        <v/>
+      </c>
+      <c r="AA56" s="188">
+        <f>K56+L56+M56+IFERROR(VLOOKUP(B56,RemitTable2,9,FALSE),0)+Y56+Z56</f>
+        <v/>
+      </c>
+      <c r="AB56" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC56" s="188">
+        <f>ROUND(AA56/AB56,0)</f>
+        <v/>
+      </c>
+      <c r="AD56" s="189" t="inlineStr"/>
+      <c r="AE56" s="205" t="n">
+        <v>46143</v>
+      </c>
+      <c r="AF56" s="205" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="184" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="184" t="inlineStr">
+        <is>
+          <t>GPO480</t>
+        </is>
+      </c>
+      <c r="C57" s="184" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D57" s="184" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E57" s="184" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F57" s="204" t="n">
+        <v>46137</v>
+      </c>
+      <c r="G57" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="186" t="n">
+        <v>250</v>
+      </c>
+      <c r="I57" s="187">
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J57" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="188">
+        <f>IFERROR(ROUND(H57*I57,0),0)</f>
+        <v/>
+      </c>
+      <c r="L57" s="188">
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M57" s="188">
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N57" s="189" t="inlineStr"/>
+      <c r="O57" s="189" t="inlineStr"/>
+      <c r="P57" s="189" t="inlineStr"/>
+      <c r="Q57" s="187">
+        <f>IF(P57="","",IFERROR(VLOOKUP(O57,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R57" s="186">
+        <f>IF(P57="","",H57)</f>
+        <v/>
+      </c>
+      <c r="S57" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="189" t="inlineStr"/>
+      <c r="V57" s="189" t="inlineStr"/>
+      <c r="W57" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y57" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="188">
+        <f>S57+T57+W57</f>
+        <v/>
+      </c>
+      <c r="AA57" s="188">
+        <f>K57+L57+M57+IFERROR(VLOOKUP(B57,RemitTable2,9,FALSE),0)+Y57+Z57</f>
+        <v/>
+      </c>
+      <c r="AB57" s="188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="188">
+        <f>ROUND(AA57/AB57,0)</f>
+        <v/>
+      </c>
+      <c r="AD57" s="189" t="inlineStr"/>
+      <c r="AE57" s="189" t="inlineStr"/>
+      <c r="AF57" s="189" t="inlineStr"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="184" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="184" t="inlineStr">
+        <is>
+          <t>GPO481</t>
+        </is>
+      </c>
+      <c r="C58" s="184" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D58" s="184" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E58" s="184" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F58" s="204" t="n">
+        <v>46152</v>
+      </c>
+      <c r="G58" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="186" t="n">
+        <v>500</v>
+      </c>
+      <c r="I58" s="187">
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J58" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="188">
+        <f>IFERROR(ROUND(H58*I58,0),0)</f>
+        <v/>
+      </c>
+      <c r="L58" s="188">
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M58" s="188">
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N58" s="189" t="inlineStr"/>
+      <c r="O58" s="189" t="inlineStr"/>
+      <c r="P58" s="189" t="inlineStr"/>
+      <c r="Q58" s="187">
+        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R58" s="186">
+        <f>IF(P58="","",H58)</f>
+        <v/>
+      </c>
+      <c r="S58" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="189" t="inlineStr"/>
+      <c r="V58" s="189" t="inlineStr"/>
+      <c r="W58" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y58" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="188">
+        <f>S58+T58+W58</f>
+        <v/>
+      </c>
+      <c r="AA58" s="188">
+        <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
+        <v/>
+      </c>
+      <c r="AB58" s="188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="188">
+        <f>ROUND(AA58/AB58,0)</f>
+        <v/>
+      </c>
+      <c r="AD58" s="189" t="inlineStr"/>
+      <c r="AE58" s="189" t="inlineStr"/>
+      <c r="AF58" s="189" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>CPO688</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="F52" s="146" t="n">
+      <c r="F59" s="146" t="n">
         <v>46037</v>
       </c>
-      <c r="G52" s="147" t="inlineStr">
+      <c r="G59" s="147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="16" t="n">
+      <c r="H59" s="16" t="n">
         <v>4180</v>
       </c>
-      <c r="I52" s="148">
+      <c r="I59" s="148">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J52" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="18">
+      <c r="J59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="18">
         <f>IFERROR(ROUND(H47*I47,0),0)</f>
         <v/>
       </c>
-      <c r="L52" s="18">
+      <c r="L59" s="18">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="M52" s="18">
+      <c r="M59" s="18">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="N52" s="12" t="inlineStr">
+      <c r="N59" s="12" t="inlineStr">
         <is>
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O52" s="12" t="inlineStr">
+      <c r="O59" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P52" s="12" t="inlineStr">
+      <c r="P59" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q52" s="18">
+      <c r="Q59" s="18">
         <f>IF(P52="","",IFERROR(VLOOKUP(O52,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R52" s="18">
+      <c r="R59" s="18">
         <f>IF(P47="","",H47)</f>
         <v/>
       </c>
-      <c r="S52" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="12" t="inlineStr">
+      <c r="S59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W52" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" s="13" t="inlineStr">
+      <c r="W59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y52" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="18">
+      <c r="Y59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="18">
         <f>S47+T47+W47</f>
         <v/>
       </c>
-      <c r="AA52" s="18">
+      <c r="AA59" s="18">
         <f>K47+L47+M47+IFERROR(VLOOKUP(B47,RemitTable2,9,FALSE()),0)+Y47+Z47</f>
         <v/>
       </c>
-      <c r="AB52" s="19" t="n">
+      <c r="AB59" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="AC52" s="18">
+      <c r="AC59" s="18">
         <f>ROUND(AA47/AB47,0)</f>
         <v/>
       </c>
-      <c r="AD52" s="12" t="inlineStr">
+      <c r="AD59" s="12" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE52" s="147" t="inlineStr">
+      <c r="AE59" s="147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF52" s="146" t="inlineStr">
+      <c r="AF59" s="146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="12" t="n">
+    <row r="60">
+      <c r="A60" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>SX3000수리</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>수리반환</t>
         </is>
       </c>
-      <c r="F53" s="146" t="n"/>
-      <c r="G53" s="147" t="n"/>
-      <c r="H53" s="16" t="n">
+      <c r="F60" s="146" t="n"/>
+      <c r="G60" s="147" t="n"/>
+      <c r="H60" s="16" t="n">
         <v>400</v>
       </c>
-      <c r="I53" s="148">
+      <c r="I60" s="148">
         <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J53" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="18">
+      <c r="J60" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="18">
         <f>IFERROR(ROUND(H48*I48,0),0)</f>
         <v/>
       </c>
-      <c r="L53" s="18">
+      <c r="L60" s="18">
         <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="M53" s="18">
+      <c r="M60" s="18">
         <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="N53" s="12" t="inlineStr">
+      <c r="N60" s="12" t="inlineStr">
         <is>
           <t>Display Card (수리반환 5PCS)</t>
         </is>
       </c>
-      <c r="O53" s="12" t="n">
+      <c r="O60" s="206" t="n">
         <v>46125</v>
       </c>
-      <c r="P53" s="12" t="inlineStr">
-        <is>
-          <t>2235626351613M</t>
-        </is>
-      </c>
-      <c r="Q53" s="18">
+      <c r="P60" s="12" t="inlineStr">
+        <is>
+          <t>22356-26-351613M</t>
+        </is>
+      </c>
+      <c r="Q60" s="18">
         <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R53" s="18">
+      <c r="R60" s="18">
         <f>IF(P48="","",H48)</f>
         <v/>
       </c>
-      <c r="S53" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="18" t="n">
+      <c r="S60" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="18" t="n">
         <v>67750</v>
       </c>
-      <c r="U53" s="13" t="n"/>
-      <c r="V53" s="12" t="inlineStr">
+      <c r="U60" s="13" t="n"/>
+      <c r="V60" s="12" t="inlineStr">
         <is>
           <t>운서합동</t>
         </is>
       </c>
-      <c r="W53" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="13" t="inlineStr">
+      <c r="W60" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="13" t="inlineStr">
         <is>
           <t>DHL</t>
         </is>
       </c>
-      <c r="Y53" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="18">
+      <c r="Y60" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="18">
         <f>S48+T48+W48</f>
         <v/>
       </c>
-      <c r="AA53" s="18">
+      <c r="AA60" s="18">
         <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE()),0)+Y48+Z48</f>
         <v/>
       </c>
-      <c r="AB53" s="19" t="n">
+      <c r="AB60" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="AC53" s="18">
+      <c r="AC60" s="18">
         <f>ROUND(AA48/AB48,0)</f>
         <v/>
       </c>
-      <c r="AD53" s="12" t="inlineStr">
+      <c r="AD60" s="12" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE53" s="147" t="n"/>
-      <c r="AF53" s="146" t="n"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="125" t="inlineStr">
+      <c r="AE60" s="147" t="n"/>
+      <c r="AF60" s="146" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="192" t="inlineStr">
         <is>
           <t>장비/부품 합계</t>
         </is>
       </c>
-      <c r="B54" s="126" t="n"/>
-      <c r="C54" s="126" t="n"/>
-      <c r="D54" s="126" t="n"/>
-      <c r="E54" s="126" t="n"/>
-      <c r="F54" s="126" t="n"/>
-      <c r="G54" s="127" t="n"/>
-      <c r="H54" s="91">
-        <f>SUBTOTAL(9,H5:H32)</f>
-        <v/>
-      </c>
-      <c r="I54" s="92" t="n"/>
-      <c r="J54" s="93">
-        <f>SUBTOTAL(9,J5:J32)</f>
-        <v/>
-      </c>
-      <c r="K54" s="93">
-        <f>SUBTOTAL(9,K5:K32)</f>
-        <v/>
-      </c>
-      <c r="L54" s="93">
-        <f>SUBTOTAL(9,L5:L32)</f>
-        <v/>
-      </c>
-      <c r="M54" s="93">
-        <f>SUBTOTAL(9,M5:M29)</f>
-        <v/>
-      </c>
-      <c r="N54" s="92" t="n"/>
-      <c r="O54" s="92" t="n"/>
-      <c r="P54" s="92" t="n"/>
-      <c r="Q54" s="93" t="n"/>
-      <c r="R54" s="91" t="n"/>
-      <c r="S54" s="93">
-        <f>SUBTOTAL(9,S5:S32)</f>
-        <v/>
-      </c>
-      <c r="T54" s="93">
-        <f>SUBTOTAL(9,T5:T32)</f>
-        <v/>
-      </c>
-      <c r="U54" s="92" t="n"/>
-      <c r="V54" s="92" t="n"/>
-      <c r="W54" s="93">
-        <f>SUBTOTAL(9,W5:W32)</f>
-        <v/>
-      </c>
-      <c r="X54" s="92" t="n"/>
-      <c r="Y54" s="93">
-        <f>SUBTOTAL(9,Y5:Y32)</f>
-        <v/>
-      </c>
-      <c r="Z54" s="93">
-        <f>SUBTOTAL(9,Z5:Z32)</f>
-        <v/>
-      </c>
-      <c r="AA54" s="93">
-        <f>SUBTOTAL(9,AA5:AA32)</f>
-        <v/>
-      </c>
-      <c r="AB54" s="92" t="n"/>
-      <c r="AC54" s="92" t="n"/>
-      <c r="AD54" s="92" t="n"/>
-      <c r="AE54" s="92" t="n"/>
-      <c r="AF54" s="92" t="n"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="125" t="inlineStr">
+      <c r="B61" s="193" t="n"/>
+      <c r="C61" s="193" t="n"/>
+      <c r="D61" s="193" t="n"/>
+      <c r="E61" s="193" t="n"/>
+      <c r="F61" s="193" t="n"/>
+      <c r="G61" s="194" t="n"/>
+      <c r="H61" s="197">
+        <f>SUBTOTAL(9,H5:H36)</f>
+        <v/>
+      </c>
+      <c r="I61" s="196" t="n"/>
+      <c r="J61" s="197">
+        <f>SUBTOTAL(9,J5:J36)</f>
+        <v/>
+      </c>
+      <c r="K61" s="197">
+        <f>SUBTOTAL(9,K5:K36)</f>
+        <v/>
+      </c>
+      <c r="L61" s="197">
+        <f>SUBTOTAL(9,L5:L36)</f>
+        <v/>
+      </c>
+      <c r="M61" s="197">
+        <f>SUBTOTAL(9,M5:M36)</f>
+        <v/>
+      </c>
+      <c r="N61" s="196" t="n"/>
+      <c r="O61" s="196" t="n"/>
+      <c r="P61" s="196" t="n"/>
+      <c r="Q61" s="197" t="n"/>
+      <c r="R61" s="195" t="n"/>
+      <c r="S61" s="197">
+        <f>SUBTOTAL(9,S5:S36)</f>
+        <v/>
+      </c>
+      <c r="T61" s="197">
+        <f>SUBTOTAL(9,T5:T36)</f>
+        <v/>
+      </c>
+      <c r="U61" s="196" t="n"/>
+      <c r="V61" s="196" t="n"/>
+      <c r="W61" s="197">
+        <f>SUBTOTAL(9,W5:W36)</f>
+        <v/>
+      </c>
+      <c r="X61" s="196" t="n"/>
+      <c r="Y61" s="197">
+        <f>SUBTOTAL(9,Y5:Y36)</f>
+        <v/>
+      </c>
+      <c r="Z61" s="197">
+        <f>SUBTOTAL(9,Z5:Z36)</f>
+        <v/>
+      </c>
+      <c r="AA61" s="197">
+        <f>SUBTOTAL(9,AA5:AA36)</f>
+        <v/>
+      </c>
+      <c r="AB61" s="196" t="n"/>
+      <c r="AC61" s="196" t="n"/>
+      <c r="AD61" s="196" t="n"/>
+      <c r="AE61" s="196" t="n"/>
+      <c r="AF61" s="196" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="192" t="inlineStr">
         <is>
           <t>라이센스/워런티 합계</t>
         </is>
       </c>
-      <c r="B55" s="126" t="n"/>
-      <c r="C55" s="126" t="n"/>
-      <c r="D55" s="126" t="n"/>
-      <c r="E55" s="126" t="n"/>
-      <c r="F55" s="126" t="n"/>
-      <c r="G55" s="127" t="n"/>
-      <c r="H55" s="91">
-        <f>SUBTOTAL(9,H33:H51)</f>
-        <v/>
-      </c>
-      <c r="I55" s="92" t="n"/>
-      <c r="J55" s="93">
-        <f>SUBTOTAL(9,J33:J51)</f>
-        <v/>
-      </c>
-      <c r="K55" s="93">
-        <f>SUBTOTAL(9,K33:K51)</f>
-        <v/>
-      </c>
-      <c r="L55" s="93">
-        <f>SUBTOTAL(9,L33:L51)</f>
-        <v/>
-      </c>
-      <c r="M55" s="93">
-        <f>SUBTOTAL(9,M30:M46)</f>
-        <v/>
-      </c>
-      <c r="N55" s="92" t="n"/>
-      <c r="O55" s="92" t="n"/>
-      <c r="P55" s="92" t="n"/>
-      <c r="Q55" s="93" t="n"/>
-      <c r="R55" s="91" t="n"/>
-      <c r="S55" s="93">
-        <f>SUBTOTAL(9,S33:S51)</f>
-        <v/>
-      </c>
-      <c r="T55" s="93">
-        <f>SUBTOTAL(9,T33:T51)</f>
-        <v/>
-      </c>
-      <c r="U55" s="92" t="n"/>
-      <c r="V55" s="92" t="n"/>
-      <c r="W55" s="93">
-        <f>SUBTOTAL(9,W33:W51)</f>
-        <v/>
-      </c>
-      <c r="X55" s="92" t="n"/>
-      <c r="Y55" s="93">
-        <f>SUBTOTAL(9,Y33:Y51)</f>
-        <v/>
-      </c>
-      <c r="Z55" s="93">
-        <f>SUBTOTAL(9,Z33:Z51)</f>
-        <v/>
-      </c>
-      <c r="AA55" s="93">
-        <f>SUBTOTAL(9,AA33:AA51)</f>
-        <v/>
-      </c>
-      <c r="AB55" s="92" t="n"/>
-      <c r="AC55" s="92" t="n"/>
-      <c r="AD55" s="92" t="n"/>
-      <c r="AE55" s="92" t="n"/>
-      <c r="AF55" s="92" t="n"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="125" t="inlineStr">
+      <c r="B62" s="193" t="n"/>
+      <c r="C62" s="193" t="n"/>
+      <c r="D62" s="193" t="n"/>
+      <c r="E62" s="193" t="n"/>
+      <c r="F62" s="193" t="n"/>
+      <c r="G62" s="194" t="n"/>
+      <c r="H62" s="197">
+        <f>SUBTOTAL(9,H37:H58)</f>
+        <v/>
+      </c>
+      <c r="I62" s="196" t="n"/>
+      <c r="J62" s="197">
+        <f>SUBTOTAL(9,J37:J58)</f>
+        <v/>
+      </c>
+      <c r="K62" s="197">
+        <f>SUBTOTAL(9,K37:K58)</f>
+        <v/>
+      </c>
+      <c r="L62" s="197">
+        <f>SUBTOTAL(9,L37:L58)</f>
+        <v/>
+      </c>
+      <c r="M62" s="197">
+        <f>SUBTOTAL(9,M37:M58)</f>
+        <v/>
+      </c>
+      <c r="N62" s="196" t="n"/>
+      <c r="O62" s="196" t="n"/>
+      <c r="P62" s="196" t="n"/>
+      <c r="Q62" s="197" t="n"/>
+      <c r="R62" s="195" t="n"/>
+      <c r="S62" s="197">
+        <f>SUBTOTAL(9,S37:S58)</f>
+        <v/>
+      </c>
+      <c r="T62" s="197">
+        <f>SUBTOTAL(9,T37:T58)</f>
+        <v/>
+      </c>
+      <c r="U62" s="196" t="n"/>
+      <c r="V62" s="196" t="n"/>
+      <c r="W62" s="197">
+        <f>SUBTOTAL(9,W37:W58)</f>
+        <v/>
+      </c>
+      <c r="X62" s="196" t="n"/>
+      <c r="Y62" s="197">
+        <f>SUBTOTAL(9,Y37:Y58)</f>
+        <v/>
+      </c>
+      <c r="Z62" s="197">
+        <f>SUBTOTAL(9,Z37:Z58)</f>
+        <v/>
+      </c>
+      <c r="AA62" s="197">
+        <f>SUBTOTAL(9,AA37:AA58)</f>
+        <v/>
+      </c>
+      <c r="AB62" s="196" t="n"/>
+      <c r="AC62" s="196" t="n"/>
+      <c r="AD62" s="196" t="n"/>
+      <c r="AE62" s="196" t="n"/>
+      <c r="AF62" s="196" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="192" t="inlineStr">
         <is>
           <t>기타 합계</t>
         </is>
       </c>
-      <c r="B56" s="126" t="n"/>
-      <c r="C56" s="126" t="n"/>
-      <c r="D56" s="126" t="n"/>
-      <c r="E56" s="126" t="n"/>
-      <c r="F56" s="126" t="n"/>
-      <c r="G56" s="127" t="n"/>
-      <c r="H56" s="91">
-        <f>H52+H53</f>
-        <v/>
-      </c>
-      <c r="I56" s="92" t="n"/>
-      <c r="J56" s="93">
-        <f>J52+J53</f>
-        <v/>
-      </c>
-      <c r="K56" s="93">
-        <f>K52+K53</f>
-        <v/>
-      </c>
-      <c r="L56" s="93">
-        <f>L52+L53</f>
-        <v/>
-      </c>
-      <c r="M56" s="93">
-        <f>M47+M48</f>
-        <v/>
-      </c>
-      <c r="N56" s="92" t="n"/>
-      <c r="O56" s="92" t="n"/>
-      <c r="P56" s="92" t="n"/>
-      <c r="Q56" s="93" t="n"/>
-      <c r="R56" s="91" t="n"/>
-      <c r="S56" s="93">
-        <f>S52+S53</f>
-        <v/>
-      </c>
-      <c r="T56" s="93">
-        <f>T52+T53</f>
-        <v/>
-      </c>
-      <c r="U56" s="92" t="n"/>
-      <c r="V56" s="92" t="n"/>
-      <c r="W56" s="93">
-        <f>W52+W53</f>
-        <v/>
-      </c>
-      <c r="X56" s="92" t="n"/>
-      <c r="Y56" s="93">
-        <f>Y52+Y53</f>
-        <v/>
-      </c>
-      <c r="Z56" s="93">
-        <f>Z52+Z53</f>
-        <v/>
-      </c>
-      <c r="AA56" s="93">
-        <f>AA52+AA53</f>
-        <v/>
-      </c>
-      <c r="AB56" s="92" t="n"/>
-      <c r="AC56" s="92" t="n"/>
-      <c r="AD56" s="92" t="n"/>
-      <c r="AE56" s="92" t="n"/>
-      <c r="AF56" s="92" t="n"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="129" t="inlineStr">
+      <c r="B63" s="193" t="n"/>
+      <c r="C63" s="193" t="n"/>
+      <c r="D63" s="193" t="n"/>
+      <c r="E63" s="193" t="n"/>
+      <c r="F63" s="193" t="n"/>
+      <c r="G63" s="194" t="n"/>
+      <c r="H63" s="197">
+        <f>H59+H60</f>
+        <v/>
+      </c>
+      <c r="I63" s="196" t="n"/>
+      <c r="J63" s="197">
+        <f>J59+J60</f>
+        <v/>
+      </c>
+      <c r="K63" s="197">
+        <f>K59+K60</f>
+        <v/>
+      </c>
+      <c r="L63" s="197">
+        <f>L59+L60</f>
+        <v/>
+      </c>
+      <c r="M63" s="197">
+        <f>M59+M60</f>
+        <v/>
+      </c>
+      <c r="N63" s="196" t="n"/>
+      <c r="O63" s="196" t="n"/>
+      <c r="P63" s="196" t="n"/>
+      <c r="Q63" s="197" t="n"/>
+      <c r="R63" s="195" t="n"/>
+      <c r="S63" s="197">
+        <f>S59+S60</f>
+        <v/>
+      </c>
+      <c r="T63" s="197">
+        <f>T59+T60</f>
+        <v/>
+      </c>
+      <c r="U63" s="196" t="n"/>
+      <c r="V63" s="196" t="n"/>
+      <c r="W63" s="197">
+        <f>W59+W60</f>
+        <v/>
+      </c>
+      <c r="X63" s="196" t="n"/>
+      <c r="Y63" s="197">
+        <f>Y59+Y60</f>
+        <v/>
+      </c>
+      <c r="Z63" s="197">
+        <f>Z59+Z60</f>
+        <v/>
+      </c>
+      <c r="AA63" s="197">
+        <f>AA59+AA60</f>
+        <v/>
+      </c>
+      <c r="AB63" s="196" t="n"/>
+      <c r="AC63" s="196" t="n"/>
+      <c r="AD63" s="196" t="n"/>
+      <c r="AE63" s="196" t="n"/>
+      <c r="AF63" s="196" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="198" t="inlineStr">
         <is>
           <t>총 합계</t>
         </is>
       </c>
-      <c r="B57" s="126" t="n"/>
-      <c r="C57" s="126" t="n"/>
-      <c r="D57" s="126" t="n"/>
-      <c r="E57" s="126" t="n"/>
-      <c r="F57" s="126" t="n"/>
-      <c r="G57" s="127" t="n"/>
-      <c r="H57" s="94">
-        <f>SUBTOTAL(9,H5:H53)</f>
-        <v/>
-      </c>
-      <c r="I57" s="95" t="n"/>
-      <c r="J57" s="96">
-        <f>SUBTOTAL(9,J5:J53)</f>
-        <v/>
-      </c>
-      <c r="K57" s="96">
-        <f>SUBTOTAL(9,K5:K53)</f>
-        <v/>
-      </c>
-      <c r="L57" s="96">
-        <f>SUBTOTAL(9,L5:L53)</f>
-        <v/>
-      </c>
-      <c r="M57" s="96">
-        <f>SUBTOTAL(9,M5:M48)</f>
-        <v/>
-      </c>
-      <c r="N57" s="95" t="n"/>
-      <c r="O57" s="95" t="n"/>
-      <c r="P57" s="95" t="n"/>
-      <c r="Q57" s="96" t="n"/>
-      <c r="R57" s="94" t="n"/>
-      <c r="S57" s="96">
-        <f>SUBTOTAL(9,S5:S53)</f>
-        <v/>
-      </c>
-      <c r="T57" s="96">
-        <f>SUBTOTAL(9,T5:T53)</f>
-        <v/>
-      </c>
-      <c r="U57" s="95" t="n"/>
-      <c r="V57" s="95" t="n"/>
-      <c r="W57" s="96">
-        <f>SUBTOTAL(9,W5:W53)</f>
-        <v/>
-      </c>
-      <c r="X57" s="95" t="n"/>
-      <c r="Y57" s="96">
-        <f>SUBTOTAL(9,Y5:Y53)</f>
-        <v/>
-      </c>
-      <c r="Z57" s="96">
-        <f>SUBTOTAL(9,Z5:Z53)</f>
-        <v/>
-      </c>
-      <c r="AA57" s="96">
-        <f>SUBTOTAL(9,AA5:AA53)</f>
-        <v/>
-      </c>
-      <c r="AB57" s="95" t="n"/>
-      <c r="AC57" s="95" t="n"/>
-      <c r="AD57" s="95" t="n"/>
-      <c r="AE57" s="95" t="n"/>
-      <c r="AF57" s="95" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="39" t="n"/>
-      <c r="B58" s="39" t="n"/>
-      <c r="C58" s="39" t="n"/>
-      <c r="D58" s="39" t="n"/>
-      <c r="E58" s="39" t="n"/>
-      <c r="F58" s="39" t="n"/>
-      <c r="G58" s="39" t="n"/>
-      <c r="H58" s="39" t="n"/>
-      <c r="I58" s="39" t="n"/>
-      <c r="J58" s="39" t="n"/>
-      <c r="K58" s="39" t="n"/>
-      <c r="L58" s="39" t="n"/>
-      <c r="M58" s="39" t="n"/>
-      <c r="N58" s="39" t="n"/>
-      <c r="O58" s="39" t="n"/>
-      <c r="P58" s="39" t="n"/>
-      <c r="Q58" s="39" t="n"/>
-      <c r="R58" s="39" t="n"/>
-      <c r="S58" s="39" t="n"/>
-      <c r="T58" s="39" t="n"/>
-      <c r="U58" s="39" t="n"/>
-      <c r="V58" s="39" t="n"/>
-      <c r="W58" s="39" t="n"/>
-      <c r="X58" s="75" t="n"/>
-      <c r="Y58" s="39" t="n"/>
-      <c r="Z58" s="39" t="n"/>
-      <c r="AA58" s="39" t="n"/>
-      <c r="AB58" s="39" t="n"/>
-      <c r="AC58" s="39" t="n"/>
-      <c r="AD58" s="39" t="n"/>
-      <c r="AE58" s="39" t="n"/>
-      <c r="AF58" s="39" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="39" t="n"/>
-      <c r="B59" s="39" t="n"/>
-      <c r="C59" s="39" t="n"/>
-      <c r="D59" s="39" t="n"/>
-      <c r="E59" s="39" t="n"/>
-      <c r="F59" s="39" t="n"/>
-      <c r="G59" s="39" t="n"/>
-      <c r="H59" s="39" t="n"/>
-      <c r="I59" s="39" t="n"/>
-      <c r="J59" s="39" t="n"/>
-      <c r="K59" s="39" t="n"/>
-      <c r="L59" s="39" t="n"/>
-      <c r="M59" s="39" t="n"/>
-      <c r="N59" s="39" t="n"/>
-      <c r="O59" s="39" t="n"/>
-      <c r="P59" s="39" t="n"/>
-      <c r="Q59" s="39" t="n"/>
-      <c r="R59" s="39" t="n"/>
-      <c r="S59" s="39" t="n"/>
-      <c r="T59" s="39" t="n"/>
-      <c r="U59" s="39" t="n"/>
-      <c r="V59" s="39" t="n"/>
-      <c r="W59" s="39" t="n"/>
-      <c r="X59" s="75" t="n"/>
-      <c r="Y59" s="39" t="n"/>
-      <c r="Z59" s="39" t="n"/>
-      <c r="AA59" s="39" t="n"/>
-      <c r="AB59" s="39" t="n"/>
-      <c r="AC59" s="39" t="n"/>
-      <c r="AD59" s="39" t="n"/>
-      <c r="AE59" s="39" t="n"/>
-      <c r="AF59" s="39" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="39" t="n"/>
-      <c r="B60" s="39" t="n"/>
-      <c r="C60" s="39" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="39" t="n"/>
-      <c r="F60" s="39" t="n"/>
-      <c r="G60" s="39" t="n"/>
-      <c r="H60" s="39" t="n"/>
-      <c r="I60" s="39" t="n"/>
-      <c r="J60" s="39" t="n"/>
-      <c r="K60" s="39" t="n"/>
-      <c r="L60" s="39" t="n"/>
-      <c r="M60" s="39" t="n"/>
-      <c r="N60" s="39" t="n"/>
-      <c r="O60" s="39" t="n"/>
-      <c r="P60" s="39" t="n"/>
-      <c r="Q60" s="39" t="n"/>
-      <c r="R60" s="39" t="n"/>
-      <c r="S60" s="39" t="n"/>
-      <c r="T60" s="39" t="n"/>
-      <c r="U60" s="39" t="n"/>
-      <c r="V60" s="39" t="n"/>
-      <c r="W60" s="39" t="n"/>
-      <c r="X60" s="75" t="n"/>
-      <c r="Y60" s="39" t="n"/>
-      <c r="Z60" s="39" t="n"/>
-      <c r="AA60" s="39" t="n"/>
-      <c r="AB60" s="39" t="n"/>
-      <c r="AC60" s="39" t="n"/>
-      <c r="AD60" s="39" t="n"/>
-      <c r="AE60" s="39" t="n"/>
-      <c r="AF60" s="39" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="39" t="n"/>
-      <c r="B61" s="39" t="n"/>
-      <c r="C61" s="39" t="n"/>
-      <c r="D61" s="39" t="n"/>
-      <c r="E61" s="39" t="n"/>
-      <c r="F61" s="39" t="n"/>
-      <c r="G61" s="39" t="n"/>
-      <c r="H61" s="39" t="n"/>
-      <c r="I61" s="39" t="n"/>
-      <c r="J61" s="39" t="n"/>
-      <c r="K61" s="39" t="n"/>
-      <c r="L61" s="39" t="n"/>
-      <c r="M61" s="39" t="n"/>
-      <c r="N61" s="39" t="n"/>
-      <c r="O61" s="39" t="n"/>
-      <c r="P61" s="39" t="n"/>
-      <c r="Q61" s="39" t="n"/>
-      <c r="R61" s="39" t="n"/>
-      <c r="S61" s="39" t="n"/>
-      <c r="T61" s="39" t="n"/>
-      <c r="U61" s="39" t="n"/>
-      <c r="V61" s="39" t="n"/>
-      <c r="W61" s="39" t="n"/>
-      <c r="X61" s="75" t="n"/>
-      <c r="Y61" s="39" t="n"/>
-      <c r="Z61" s="39" t="n"/>
-      <c r="AA61" s="39" t="n"/>
-      <c r="AB61" s="39" t="n"/>
-      <c r="AC61" s="39" t="n"/>
-      <c r="AD61" s="39" t="n"/>
-      <c r="AE61" s="39" t="n"/>
-      <c r="AF61" s="39" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="39" t="n"/>
-      <c r="B62" s="39" t="n"/>
-      <c r="C62" s="39" t="n"/>
-      <c r="D62" s="39" t="n"/>
-      <c r="E62" s="39" t="n"/>
-      <c r="F62" s="39" t="n"/>
-      <c r="G62" s="39" t="n"/>
-      <c r="H62" s="39" t="n"/>
-      <c r="I62" s="39" t="n"/>
-      <c r="J62" s="39" t="n"/>
-      <c r="K62" s="39" t="n"/>
-      <c r="L62" s="39" t="n"/>
-      <c r="M62" s="39" t="n"/>
-      <c r="N62" s="39" t="n"/>
-      <c r="O62" s="39" t="n"/>
-      <c r="P62" s="39" t="n"/>
-      <c r="Q62" s="39" t="n"/>
-      <c r="R62" s="39" t="n"/>
-      <c r="S62" s="39" t="n"/>
-      <c r="T62" s="39" t="n"/>
-      <c r="U62" s="39" t="n"/>
-      <c r="V62" s="39" t="n"/>
-      <c r="W62" s="39" t="n"/>
-      <c r="X62" s="75" t="n"/>
-      <c r="Y62" s="39" t="n"/>
-      <c r="Z62" s="39" t="n"/>
-      <c r="AA62" s="39" t="n"/>
-      <c r="AB62" s="39" t="n"/>
-      <c r="AC62" s="39" t="n"/>
-      <c r="AD62" s="39" t="n"/>
-      <c r="AE62" s="39" t="n"/>
-      <c r="AF62" s="39" t="n"/>
-    </row>
-    <row r="76">
-      <c r="M76" s="40" t="n"/>
+      <c r="B64" s="193" t="n"/>
+      <c r="C64" s="193" t="n"/>
+      <c r="D64" s="193" t="n"/>
+      <c r="E64" s="193" t="n"/>
+      <c r="F64" s="193" t="n"/>
+      <c r="G64" s="194" t="n"/>
+      <c r="H64" s="201">
+        <f>SUBTOTAL(9,H5:H60)</f>
+        <v/>
+      </c>
+      <c r="I64" s="200" t="n"/>
+      <c r="J64" s="201">
+        <f>SUBTOTAL(9,J5:J60)</f>
+        <v/>
+      </c>
+      <c r="K64" s="201">
+        <f>SUBTOTAL(9,K5:K60)</f>
+        <v/>
+      </c>
+      <c r="L64" s="201">
+        <f>SUBTOTAL(9,L5:L60)</f>
+        <v/>
+      </c>
+      <c r="M64" s="201">
+        <f>SUBTOTAL(9,M5:M60)</f>
+        <v/>
+      </c>
+      <c r="N64" s="200" t="n"/>
+      <c r="O64" s="200" t="n"/>
+      <c r="P64" s="200" t="n"/>
+      <c r="Q64" s="201" t="n"/>
+      <c r="R64" s="199" t="n"/>
+      <c r="S64" s="201">
+        <f>SUBTOTAL(9,S5:S60)</f>
+        <v/>
+      </c>
+      <c r="T64" s="201">
+        <f>SUBTOTAL(9,T5:T60)</f>
+        <v/>
+      </c>
+      <c r="U64" s="200" t="n"/>
+      <c r="V64" s="200" t="n"/>
+      <c r="W64" s="201">
+        <f>SUBTOTAL(9,W5:W60)</f>
+        <v/>
+      </c>
+      <c r="X64" s="200" t="n"/>
+      <c r="Y64" s="201">
+        <f>SUBTOTAL(9,Y5:Y60)</f>
+        <v/>
+      </c>
+      <c r="Z64" s="201">
+        <f>SUBTOTAL(9,Z5:Z60)</f>
+        <v/>
+      </c>
+      <c r="AA64" s="201">
+        <f>SUBTOTAL(9,AA5:AA60)</f>
+        <v/>
+      </c>
+      <c r="AB64" s="200" t="n"/>
+      <c r="AC64" s="200" t="n"/>
+      <c r="AD64" s="200" t="n"/>
+      <c r="AE64" s="200" t="n"/>
+      <c r="AF64" s="200" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="39" t="n"/>
+      <c r="B65" s="39" t="n"/>
+      <c r="C65" s="39" t="n"/>
+      <c r="D65" s="39" t="n"/>
+      <c r="E65" s="39" t="n"/>
+      <c r="F65" s="39" t="n"/>
+      <c r="G65" s="39" t="n"/>
+      <c r="H65" s="39" t="n"/>
+      <c r="I65" s="39" t="n"/>
+      <c r="J65" s="39" t="n"/>
+      <c r="K65" s="39" t="n"/>
+      <c r="L65" s="39" t="n"/>
+      <c r="M65" s="39" t="n"/>
+      <c r="N65" s="39" t="n"/>
+      <c r="O65" s="39" t="n"/>
+      <c r="P65" s="39" t="n"/>
+      <c r="Q65" s="39" t="n"/>
+      <c r="R65" s="39" t="n"/>
+      <c r="S65" s="39" t="n"/>
+      <c r="T65" s="39" t="n"/>
+      <c r="U65" s="39" t="n"/>
+      <c r="V65" s="39" t="n"/>
+      <c r="W65" s="39" t="n"/>
+      <c r="X65" s="75" t="n"/>
+      <c r="Y65" s="39" t="n"/>
+      <c r="Z65" s="39" t="n"/>
+      <c r="AA65" s="39" t="n"/>
+      <c r="AB65" s="39" t="n"/>
+      <c r="AC65" s="39" t="n"/>
+      <c r="AD65" s="39" t="n"/>
+      <c r="AE65" s="39" t="n"/>
+      <c r="AF65" s="39" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="39" t="n"/>
+      <c r="B66" s="39" t="n"/>
+      <c r="C66" s="39" t="n"/>
+      <c r="D66" s="39" t="n"/>
+      <c r="E66" s="39" t="n"/>
+      <c r="F66" s="39" t="n"/>
+      <c r="G66" s="39" t="n"/>
+      <c r="H66" s="39" t="n"/>
+      <c r="I66" s="39" t="n"/>
+      <c r="J66" s="39" t="n"/>
+      <c r="K66" s="39" t="n"/>
+      <c r="L66" s="39" t="n"/>
+      <c r="M66" s="39" t="n"/>
+      <c r="N66" s="39" t="n"/>
+      <c r="O66" s="39" t="n"/>
+      <c r="P66" s="39" t="n"/>
+      <c r="Q66" s="39" t="n"/>
+      <c r="R66" s="39" t="n"/>
+      <c r="S66" s="39" t="n"/>
+      <c r="T66" s="39" t="n"/>
+      <c r="U66" s="39" t="n"/>
+      <c r="V66" s="39" t="n"/>
+      <c r="W66" s="39" t="n"/>
+      <c r="X66" s="75" t="n"/>
+      <c r="Y66" s="39" t="n"/>
+      <c r="Z66" s="39" t="n"/>
+      <c r="AA66" s="39" t="n"/>
+      <c r="AB66" s="39" t="n"/>
+      <c r="AC66" s="39" t="n"/>
+      <c r="AD66" s="39" t="n"/>
+      <c r="AE66" s="39" t="n"/>
+      <c r="AF66" s="39" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="39" t="n"/>
+      <c r="B67" s="39" t="n"/>
+      <c r="C67" s="39" t="n"/>
+      <c r="D67" s="39" t="n"/>
+      <c r="E67" s="39" t="n"/>
+      <c r="F67" s="39" t="n"/>
+      <c r="G67" s="39" t="n"/>
+      <c r="H67" s="39" t="n"/>
+      <c r="I67" s="39" t="n"/>
+      <c r="J67" s="39" t="n"/>
+      <c r="K67" s="39" t="n"/>
+      <c r="L67" s="39" t="n"/>
+      <c r="M67" s="39" t="n"/>
+      <c r="N67" s="39" t="n"/>
+      <c r="O67" s="39" t="n"/>
+      <c r="P67" s="39" t="n"/>
+      <c r="Q67" s="39" t="n"/>
+      <c r="R67" s="39" t="n"/>
+      <c r="S67" s="39" t="n"/>
+      <c r="T67" s="39" t="n"/>
+      <c r="U67" s="39" t="n"/>
+      <c r="V67" s="39" t="n"/>
+      <c r="W67" s="39" t="n"/>
+      <c r="X67" s="75" t="n"/>
+      <c r="Y67" s="39" t="n"/>
+      <c r="Z67" s="39" t="n"/>
+      <c r="AA67" s="39" t="n"/>
+      <c r="AB67" s="39" t="n"/>
+      <c r="AC67" s="39" t="n"/>
+      <c r="AD67" s="39" t="n"/>
+      <c r="AE67" s="39" t="n"/>
+      <c r="AF67" s="39" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="39" t="n"/>
+      <c r="B68" s="39" t="n"/>
+      <c r="C68" s="39" t="n"/>
+      <c r="D68" s="39" t="n"/>
+      <c r="E68" s="39" t="n"/>
+      <c r="F68" s="39" t="n"/>
+      <c r="G68" s="39" t="n"/>
+      <c r="H68" s="39" t="n"/>
+      <c r="I68" s="39" t="n"/>
+      <c r="J68" s="39" t="n"/>
+      <c r="K68" s="39" t="n"/>
+      <c r="L68" s="39" t="n"/>
+      <c r="M68" s="39" t="n"/>
+      <c r="N68" s="39" t="n"/>
+      <c r="O68" s="39" t="n"/>
+      <c r="P68" s="39" t="n"/>
+      <c r="Q68" s="39" t="n"/>
+      <c r="R68" s="39" t="n"/>
+      <c r="S68" s="39" t="n"/>
+      <c r="T68" s="39" t="n"/>
+      <c r="U68" s="39" t="n"/>
+      <c r="V68" s="39" t="n"/>
+      <c r="W68" s="39" t="n"/>
+      <c r="X68" s="75" t="n"/>
+      <c r="Y68" s="39" t="n"/>
+      <c r="Z68" s="39" t="n"/>
+      <c r="AA68" s="39" t="n"/>
+      <c r="AB68" s="39" t="n"/>
+      <c r="AC68" s="39" t="n"/>
+      <c r="AD68" s="39" t="n"/>
+      <c r="AE68" s="39" t="n"/>
+      <c r="AF68" s="39" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="39" t="n"/>
+      <c r="B69" s="39" t="n"/>
+      <c r="C69" s="39" t="n"/>
+      <c r="D69" s="39" t="n"/>
+      <c r="E69" s="39" t="n"/>
+      <c r="F69" s="39" t="n"/>
+      <c r="G69" s="39" t="n"/>
+      <c r="H69" s="39" t="n"/>
+      <c r="I69" s="39" t="n"/>
+      <c r="J69" s="39" t="n"/>
+      <c r="K69" s="39" t="n"/>
+      <c r="L69" s="39" t="n"/>
+      <c r="M69" s="39" t="n"/>
+      <c r="N69" s="39" t="n"/>
+      <c r="O69" s="39" t="n"/>
+      <c r="P69" s="39" t="n"/>
+      <c r="Q69" s="39" t="n"/>
+      <c r="R69" s="39" t="n"/>
+      <c r="S69" s="39" t="n"/>
+      <c r="T69" s="39" t="n"/>
+      <c r="U69" s="39" t="n"/>
+      <c r="V69" s="39" t="n"/>
+      <c r="W69" s="39" t="n"/>
+      <c r="X69" s="75" t="n"/>
+      <c r="Y69" s="39" t="n"/>
+      <c r="Z69" s="39" t="n"/>
+      <c r="AA69" s="39" t="n"/>
+      <c r="AB69" s="39" t="n"/>
+      <c r="AC69" s="39" t="n"/>
+      <c r="AD69" s="39" t="n"/>
+      <c r="AE69" s="39" t="n"/>
+      <c r="AF69" s="39" t="n"/>
+    </row>
+    <row r="83">
+      <c r="M83" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A61:G61"/>
     <mergeCell ref="G3:N3"/>
-    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A62:G62"/>
     <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="A54:G54"/>
     <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="A64:G64"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="O3:W3"/>
@@ -16256,7 +17178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -16299,7 +17221,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="140" t="inlineStr">
         <is>
-          <t>업데이트: 2026-05-06 (관세청 고시환율)</t>
+          <t>업데이트: 2026-05-19 (관세청 고시환율)</t>
         </is>
       </c>
       <c r="B4" s="123" t="n"/>
@@ -16823,6 +17745,38 @@
       </c>
       <c r="D37" s="7" t="n">
         <v>1476.35</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="207" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B38" s="207" t="n">
+        <v>46158</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D38" s="163" t="n">
+        <v>1465.73</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="207" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B39" s="207" t="n">
+        <v>46165</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D39" s="163" t="n">
+        <v>1482.04</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0&quot;일&quot;"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -184,6 +184,13 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="17">
@@ -419,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1009,6 +1016,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1414,9 +1424,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="169" t="inlineStr">
-        <is>
-          <t>RNR 2026년 PO별 수입원가 산출표 (Master)</t>
+      <c r="A1" s="206" t="inlineStr">
+        <is>
+          <t>RNR 2026년 PO별 수입원가 산출표 (Master)  📊 https://rnrfin.github.io/rnr-importcost/</t>
         </is>
       </c>
       <c r="B1" s="148" t="n"/>
@@ -9225,6 +9235,9 @@
     <mergeCell ref="O3:W3"/>
     <mergeCell ref="A2:AF2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -15102,7 +15115,6 @@
         <v/>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="M76" s="40" t="n"/>
     </row>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="FxRateTable">환율!$A$7:$D$39</definedName>
     <definedName name="RemitTable1">외화송금내역!$A$3:$L$34</definedName>
     <definedName name="RemitTable2">외화송금내역!$A$37:$L$74</definedName>
+    <definedName name="FxRateTable">환율!$A$7:$D$40</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -193,7 +193,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -283,6 +283,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -426,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1019,6 +1025,82 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1398,7 +1480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF83"/>
+  <dimension ref="A1:AF86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" style="160" min="1" max="1"/>
@@ -1464,7 +1546,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-05-19  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-05-28  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="148" t="n"/>
@@ -5726,274 +5808,254 @@
       <c r="AF36" s="129" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>CPO667</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F37" s="183" t="n">
-        <v>45925</v>
-      </c>
-      <c r="G37" s="184" t="n">
-        <v>46080</v>
-      </c>
-      <c r="H37" s="24" t="n">
-        <v>5673</v>
-      </c>
-      <c r="I37" s="185">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J37" s="26" t="n">
-        <v>205028994</v>
-      </c>
-      <c r="K37" s="26">
-        <f>IFERROR(ROUND(H30*I30,0),0)</f>
-        <v/>
-      </c>
-      <c r="L37" s="26">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M37" s="26">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N37" s="20" t="inlineStr">
-        <is>
-          <t>EW CP2220</t>
-        </is>
-      </c>
-      <c r="O37" s="20" t="inlineStr">
+      <c r="A37" s="207" t="n">
+        <v>57</v>
+      </c>
+      <c r="B37" s="207" t="inlineStr">
+        <is>
+          <t>GPO473-2</t>
+        </is>
+      </c>
+      <c r="C37" s="208" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D37" s="207" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E37" s="208" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F37" s="209" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G37" s="210" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P37" s="20" t="inlineStr">
+      <c r="H37" s="211" t="n">
+        <v>69160</v>
+      </c>
+      <c r="I37" s="212">
+        <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J37" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="213">
+        <f>IFERROR(ROUND(H37*I37,0),0)</f>
+        <v/>
+      </c>
+      <c r="L37" s="213">
+        <f>IFERROR(VLOOKUP(B37,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M37" s="213">
+        <f>IFERROR(VLOOKUP(B37,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N37" s="207" t="inlineStr">
+        <is>
+          <t>SR-1000 (4K) Standalone IMB / 14 SET</t>
+        </is>
+      </c>
+      <c r="O37" s="210" t="n">
+        <v>46155</v>
+      </c>
+      <c r="P37" s="207" t="inlineStr">
+        <is>
+          <t>14008-26-101170M</t>
+        </is>
+      </c>
+      <c r="Q37" s="211">
+        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R37" s="211">
+        <f>IF(P37="","",H37)</f>
+        <v/>
+      </c>
+      <c r="S37" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="213" t="n">
+        <v>14809460</v>
+      </c>
+      <c r="U37" s="209" t="n"/>
+      <c r="V37" s="207" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W37" s="213" t="n">
+        <v>250000</v>
+      </c>
+      <c r="X37" s="208" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="Y37" s="213" t="n">
+        <v>3759954</v>
+      </c>
+      <c r="Z37" s="213">
+        <f>S37+T37+W37</f>
+        <v/>
+      </c>
+      <c r="AA37" s="214">
+        <f>K37+L37+M37+IFERROR(VLOOKUP(B37,RemitTable2,9,FALSE),0)+Y37+Z37</f>
+        <v/>
+      </c>
+      <c r="AB37" s="215" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC37" s="214">
+        <f>ROUND(AA37/AB37,0)</f>
+        <v/>
+      </c>
+      <c r="AD37" s="207" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE37" s="207" t="n"/>
+      <c r="AF37" s="208" t="n"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="207" t="n">
+        <v>58</v>
+      </c>
+      <c r="B38" s="207" t="inlineStr">
+        <is>
+          <t>GPO473-3</t>
+        </is>
+      </c>
+      <c r="C38" s="208" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D38" s="207" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E38" s="208" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F38" s="209" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G38" s="210" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q37" s="24">
-        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R37" s="26">
-        <f>IF(P30="","",H30)</f>
-        <v/>
-      </c>
-      <c r="S37" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W37" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y37" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="26">
-        <f>S30+T30+W30</f>
-        <v/>
-      </c>
-      <c r="AA37" s="26">
-        <f>K30+L30+M30+IFERROR(VLOOKUP(B30,RemitTable2,9,FALSE()),0)+Y30+Z30</f>
-        <v/>
-      </c>
-      <c r="AB37" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="26">
-        <f>ROUND(AA30/AB30,0)</f>
-        <v/>
-      </c>
-      <c r="AD37" s="20" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="AE37" s="184" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AF37" s="183" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>GPO458</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F38" s="183" t="n">
-        <v>45982</v>
-      </c>
-      <c r="G38" s="184" t="n">
-        <v>46020</v>
-      </c>
-      <c r="H38" s="24" t="n">
-        <v>350</v>
-      </c>
-      <c r="I38" s="185">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J38" s="26" t="n">
-        <v>18264679</v>
-      </c>
-      <c r="K38" s="26">
-        <f>IFERROR(ROUND(H31*I31,0),0)</f>
-        <v/>
-      </c>
-      <c r="L38" s="26">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M38" s="26">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N38" s="20" t="inlineStr">
-        <is>
-          <t>HFR License</t>
-        </is>
-      </c>
-      <c r="O38" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P38" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q38" s="24">
-        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R38" s="26">
-        <f>IF(P31="","",H31)</f>
-        <v/>
-      </c>
-      <c r="S38" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W38" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y38" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="26">
-        <f>S31+T31+W31</f>
-        <v/>
-      </c>
-      <c r="AA38" s="26">
-        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
-        <v/>
-      </c>
-      <c r="AB38" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="26">
-        <f>ROUND(AA31/AB31,0)</f>
-        <v/>
-      </c>
-      <c r="AD38" s="20" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AE38" s="184" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AF38" s="183" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
+      <c r="H38" s="211" t="n">
+        <v>49400</v>
+      </c>
+      <c r="I38" s="212">
+        <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J38" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="213">
+        <f>IFERROR(ROUND(H38*I38,0),0)</f>
+        <v/>
+      </c>
+      <c r="L38" s="213">
+        <f>IFERROR(VLOOKUP(B38,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M38" s="213">
+        <f>IFERROR(VLOOKUP(B38,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N38" s="207" t="inlineStr">
+        <is>
+          <t>SR-1000 (4K) Standalone IMB / 10 SET</t>
+        </is>
+      </c>
+      <c r="O38" s="210" t="n">
+        <v>46162</v>
+      </c>
+      <c r="P38" s="207" t="inlineStr">
+        <is>
+          <t>14008-26-101191M</t>
+        </is>
+      </c>
+      <c r="Q38" s="211">
+        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R38" s="211">
+        <f>IF(P38="","",H38)</f>
+        <v/>
+      </c>
+      <c r="S38" s="213" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="213" t="n">
+        <v>7510210</v>
+      </c>
+      <c r="U38" s="209" t="n"/>
+      <c r="V38" s="207" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W38" s="213" t="n">
+        <v>250000</v>
+      </c>
+      <c r="X38" s="208" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="Y38" s="213" t="n">
+        <v>2259958</v>
+      </c>
+      <c r="Z38" s="213">
+        <f>S38+T38+W38</f>
+        <v/>
+      </c>
+      <c r="AA38" s="214">
+        <f>K38+L38+M38+IFERROR(VLOOKUP(B38,RemitTable2,9,FALSE),0)+Y38+Z38</f>
+        <v/>
+      </c>
+      <c r="AB38" s="215" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC38" s="214">
+        <f>ROUND(AA38/AB38,0)</f>
+        <v/>
+      </c>
+      <c r="AD38" s="207" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE38" s="207" t="n"/>
+      <c r="AF38" s="208" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="20" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
@@ -6012,36 +6074,36 @@
         </is>
       </c>
       <c r="F39" s="183" t="n">
-        <v>45993</v>
+        <v>45925</v>
       </c>
       <c r="G39" s="184" t="n">
-        <v>46064</v>
+        <v>46080</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>26358</v>
+        <v>5673</v>
       </c>
       <c r="I39" s="185">
-        <f>IFERROR(VLOOKUP(B32,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J39" s="26" t="n">
-        <v>38550844</v>
+        <v>205028994</v>
       </c>
       <c r="K39" s="26">
-        <f>IFERROR(ROUND(H32*I32,0),0)</f>
+        <f>IFERROR(ROUND(H30*I30,0),0)</f>
         <v/>
       </c>
       <c r="L39" s="26">
-        <f>IFERROR(VLOOKUP(B32,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B30,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M39" s="26">
-        <f>IFERROR(VLOOKUP(B32,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B30,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>EW CP2309/2315/2320-RGB</t>
+          <t>EW CP2220</t>
         </is>
       </c>
       <c r="O39" s="20" t="inlineStr">
@@ -6055,11 +6117,11 @@
         </is>
       </c>
       <c r="Q39" s="24">
-        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R39" s="26">
-        <f>IF(P32="","",H32)</f>
+        <f>IF(P30="","",H30)</f>
         <v/>
       </c>
       <c r="S39" s="26" t="n">
@@ -6088,43 +6150,43 @@
         <v>0</v>
       </c>
       <c r="Z39" s="26">
-        <f>S32+T32+W32</f>
+        <f>S30+T30+W30</f>
         <v/>
       </c>
       <c r="AA39" s="26">
-        <f>K32+L32+M32+IFERROR(VLOOKUP(B32,RemitTable2,9,FALSE()),0)+Y32+Z32</f>
+        <f>K30+L30+M30+IFERROR(VLOOKUP(B30,RemitTable2,9,FALSE()),0)+Y30+Z30</f>
         <v/>
       </c>
       <c r="AB39" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC39" s="26">
-        <f>ROUND(AA32/AB32,0)</f>
+        <f>ROUND(AA30/AB30,0)</f>
         <v/>
       </c>
       <c r="AD39" s="20" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="AE39" s="184" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AF39" s="183" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>GPO459</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
@@ -6139,40 +6201,40 @@
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F40" s="183" t="n">
-        <v>46007</v>
+        <v>45982</v>
       </c>
       <c r="G40" s="184" t="n">
-        <v>46043</v>
+        <v>46020</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="I40" s="185">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J40" s="26" t="n">
-        <v>5505104</v>
+        <v>18264679</v>
       </c>
       <c r="K40" s="26">
-        <f>IFERROR(ROUND(H33*I33,0),0)</f>
+        <f>IFERROR(ROUND(H31*I31,0),0)</f>
         <v/>
       </c>
       <c r="L40" s="26">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M40" s="26">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 EW</t>
+          <t>HFR License</t>
         </is>
       </c>
       <c r="O40" s="20" t="inlineStr">
@@ -6186,11 +6248,11 @@
         </is>
       </c>
       <c r="Q40" s="24">
-        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R40" s="26">
-        <f>IF(P33="","",H33)</f>
+        <f>IF(P31="","",H31)</f>
         <v/>
       </c>
       <c r="S40" s="26" t="n">
@@ -6219,53 +6281,53 @@
         <v>0</v>
       </c>
       <c r="Z40" s="26">
-        <f>S33+T33+W33</f>
+        <f>S31+T31+W31</f>
         <v/>
       </c>
       <c r="AA40" s="26">
-        <f>K33+L33+M33+IFERROR(VLOOKUP(B33,RemitTable2,9,FALSE()),0)+Y33+Z33</f>
+        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
         <v/>
       </c>
       <c r="AB40" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC40" s="26">
-        <f>ROUND(AA33/AB33,0)</f>
+        <f>ROUND(AA31/AB31,0)</f>
         <v/>
       </c>
       <c r="AD40" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE40" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AF40" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="20" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
@@ -6274,36 +6336,36 @@
         </is>
       </c>
       <c r="F41" s="183" t="n">
-        <v>46007</v>
+        <v>45993</v>
       </c>
       <c r="G41" s="184" t="n">
-        <v>46043</v>
+        <v>46064</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>540</v>
+        <v>26358</v>
       </c>
       <c r="I41" s="185">
-        <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B32,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J41" s="26" t="n">
-        <v>5505104</v>
+        <v>38550844</v>
       </c>
       <c r="K41" s="26">
-        <f>IFERROR(ROUND(H34*I34,0),0)</f>
+        <f>IFERROR(ROUND(H32*I32,0),0)</f>
         <v/>
       </c>
       <c r="L41" s="26">
-        <f>IFERROR(VLOOKUP(B34,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B32,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M41" s="26">
-        <f>IFERROR(VLOOKUP(B34,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B32,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 EW</t>
+          <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
       <c r="O41" s="20" t="inlineStr">
@@ -6317,11 +6379,11 @@
         </is>
       </c>
       <c r="Q41" s="24">
-        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R41" s="26">
-        <f>IF(P34="","",H34)</f>
+        <f>IF(P32="","",H32)</f>
         <v/>
       </c>
       <c r="S41" s="26" t="n">
@@ -6350,53 +6412,53 @@
         <v>0</v>
       </c>
       <c r="Z41" s="26">
-        <f>S34+T34+W34</f>
+        <f>S32+T32+W32</f>
         <v/>
       </c>
       <c r="AA41" s="26">
-        <f>K34+L34+M34+IFERROR(VLOOKUP(B34,RemitTable2,9,FALSE()),0)+Y34+Z34</f>
+        <f>K32+L32+M32+IFERROR(VLOOKUP(B32,RemitTable2,9,FALSE()),0)+Y32+Z32</f>
         <v/>
       </c>
       <c r="AB41" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC41" s="26">
-        <f>ROUND(AA34/AB34,0)</f>
+        <f>ROUND(AA32/AB32,0)</f>
         <v/>
       </c>
       <c r="AD41" s="20" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE41" s="184" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AF41" s="183" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-21</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
@@ -6405,36 +6467,36 @@
         </is>
       </c>
       <c r="F42" s="183" t="n">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="G42" s="184" t="n">
-        <v>46080</v>
+        <v>46043</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>136516</v>
+        <v>450</v>
       </c>
       <c r="I42" s="185">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J42" s="26" t="n">
-        <v>205028994</v>
+        <v>5505104</v>
       </c>
       <c r="K42" s="26">
-        <f>IFERROR(ROUND(H35*I35,0),0)</f>
+        <f>IFERROR(ROUND(H33*I33,0),0)</f>
         <v/>
       </c>
       <c r="L42" s="26">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B33,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M42" s="26">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B33,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (CP2208~CP4450)</t>
+          <t>TMS-2000 EW</t>
         </is>
       </c>
       <c r="O42" s="20" t="inlineStr">
@@ -6448,11 +6510,11 @@
         </is>
       </c>
       <c r="Q42" s="24">
-        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R42" s="26">
-        <f>IF(P35="","",H35)</f>
+        <f>IF(P33="","",H33)</f>
         <v/>
       </c>
       <c r="S42" s="26" t="n">
@@ -6481,18 +6543,18 @@
         <v>0</v>
       </c>
       <c r="Z42" s="26">
-        <f>S35+T35+W35</f>
+        <f>S33+T33+W33</f>
         <v/>
       </c>
       <c r="AA42" s="26">
-        <f>K35+L35+M35+IFERROR(VLOOKUP(B35,RemitTable2,9,FALSE()),0)+Y35+Z35</f>
+        <f>K33+L33+M33+IFERROR(VLOOKUP(B33,RemitTable2,9,FALSE()),0)+Y33+Z33</f>
         <v/>
       </c>
       <c r="AB42" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC42" s="26">
-        <f>ROUND(AA35/AB35,0)</f>
+        <f>ROUND(AA33/AB33,0)</f>
         <v/>
       </c>
       <c r="AD42" s="20" t="inlineStr">
@@ -6513,11 +6575,11 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>GPO465</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
@@ -6536,121 +6598,119 @@
         </is>
       </c>
       <c r="F43" s="183" t="n">
-        <v>46015</v>
-      </c>
-      <c r="G43" s="184" t="inlineStr">
+        <v>46007</v>
+      </c>
+      <c r="G43" s="184" t="n">
+        <v>46043</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>540</v>
+      </c>
+      <c r="I43" s="185">
+        <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J43" s="26" t="n">
+        <v>5505104</v>
+      </c>
+      <c r="K43" s="26">
+        <f>IFERROR(ROUND(H34*I34,0),0)</f>
+        <v/>
+      </c>
+      <c r="L43" s="26">
+        <f>IFERROR(VLOOKUP(B34,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M43" s="26">
+        <f>IFERROR(VLOOKUP(B34,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N43" s="20" t="inlineStr">
+        <is>
+          <t>TMS-1000 EW</t>
+        </is>
+      </c>
+      <c r="O43" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H43" s="24" t="n">
-        <v>76054</v>
-      </c>
-      <c r="I43" s="185">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="26">
-        <f>IFERROR(ROUND(H36*I36,0),0)</f>
-        <v/>
-      </c>
-      <c r="L43" s="26">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M43" s="26">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N43" s="20" t="inlineStr">
-        <is>
-          <t>EW 대량 (SR/SX/TMS)</t>
-        </is>
-      </c>
-      <c r="O43" s="20" t="inlineStr">
+      <c r="P43" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P43" s="20" t="inlineStr">
+      <c r="Q43" s="24">
+        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R43" s="26">
+        <f>IF(P34="","",H34)</f>
+        <v/>
+      </c>
+      <c r="S43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q43" s="24">
-        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R43" s="26">
-        <f>IF(P36="","",H36)</f>
-        <v/>
-      </c>
-      <c r="S43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="20" t="inlineStr">
+      <c r="W43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="Y43" s="26" t="n">
         <v>0</v>
       </c>
       <c r="Z43" s="26">
-        <f>S36+T36+W36</f>
+        <f>S34+T34+W34</f>
         <v/>
       </c>
       <c r="AA43" s="26">
-        <f>K36+L36+M36+IFERROR(VLOOKUP(B36,RemitTable2,9,FALSE()),0)+Y36+Z36</f>
+        <f>K34+L34+M34+IFERROR(VLOOKUP(B34,RemitTable2,9,FALSE()),0)+Y34+Z34</f>
         <v/>
       </c>
       <c r="AB43" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC43" s="26">
-        <f>ROUND(AA36/AB36,0)</f>
+        <f>ROUND(AA34/AB34,0)</f>
         <v/>
       </c>
       <c r="AD43" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="AE43" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AF43" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
@@ -6669,36 +6729,36 @@
         </is>
       </c>
       <c r="F44" s="183" t="n">
-        <v>46029</v>
+        <v>46010</v>
       </c>
       <c r="G44" s="184" t="n">
-        <v>46072</v>
+        <v>46080</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>14793</v>
+        <v>136516</v>
       </c>
       <c r="I44" s="185">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J44" s="26" t="n">
-        <v>25506948</v>
+        <v>205028994</v>
       </c>
       <c r="K44" s="26">
-        <f>IFERROR(ROUND(H37*I37,0),0)</f>
+        <f>IFERROR(ROUND(H35*I35,0),0)</f>
         <v/>
       </c>
       <c r="L44" s="26">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B35,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M44" s="26">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B35,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t>EW CP2315/CP4440-RGB</t>
+          <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
       <c r="O44" s="20" t="inlineStr">
@@ -6712,11 +6772,11 @@
         </is>
       </c>
       <c r="Q44" s="24">
-        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R44" s="26">
-        <f>IF(P37="","",H37)</f>
+        <f>IF(P35="","",H35)</f>
         <v/>
       </c>
       <c r="S44" s="26" t="n">
@@ -6745,18 +6805,18 @@
         <v>0</v>
       </c>
       <c r="Z44" s="26">
-        <f>S37+T37+W37</f>
+        <f>S35+T35+W35</f>
         <v/>
       </c>
       <c r="AA44" s="26">
-        <f>K37+L37+M37+IFERROR(VLOOKUP(B37,RemitTable2,9,FALSE()),0)+Y37+Z37</f>
+        <f>K35+L35+M35+IFERROR(VLOOKUP(B35,RemitTable2,9,FALSE()),0)+Y35+Z35</f>
         <v/>
       </c>
       <c r="AB44" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC44" s="26">
-        <f>ROUND(AA37/AB37,0)</f>
+        <f>ROUND(AA35/AB35,0)</f>
         <v/>
       </c>
       <c r="AD44" s="20" t="inlineStr">
@@ -6766,32 +6826,32 @@
       </c>
       <c r="AE44" s="184" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF44" s="183" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="20" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>CPO687</t>
+          <t>GPO465</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E45" s="21" t="inlineStr">
@@ -6800,7 +6860,7 @@
         </is>
       </c>
       <c r="F45" s="183" t="n">
-        <v>46029</v>
+        <v>46015</v>
       </c>
       <c r="G45" s="184" t="inlineStr">
         <is>
@@ -6808,30 +6868,30 @@
         </is>
       </c>
       <c r="H45" s="24" t="n">
-        <v>26656</v>
+        <v>76054</v>
       </c>
       <c r="I45" s="185">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J45" s="26" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="26">
-        <f>IFERROR(ROUND(H38*I38,0),0)</f>
+        <f>IFERROR(ROUND(H36*I36,0),0)</f>
         <v/>
       </c>
       <c r="L45" s="26">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B36,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M45" s="26">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B36,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>EW (홀딩)</t>
+          <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
       <c r="O45" s="20" t="inlineStr">
@@ -6845,11 +6905,11 @@
         </is>
       </c>
       <c r="Q45" s="24">
-        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R45" s="26">
-        <f>IF(P38="","",H38)</f>
+        <f>IF(P36="","",H36)</f>
         <v/>
       </c>
       <c r="S45" s="26" t="n">
@@ -6878,18 +6938,18 @@
         <v>0</v>
       </c>
       <c r="Z45" s="26">
-        <f>S38+T38+W38</f>
+        <f>S36+T36+W36</f>
         <v/>
       </c>
       <c r="AA45" s="26">
-        <f>K38+L38+M38+IFERROR(VLOOKUP(B38,RemitTable2,9,FALSE()),0)+Y38+Z38</f>
+        <f>K36+L36+M36+IFERROR(VLOOKUP(B36,RemitTable2,9,FALSE()),0)+Y36+Z36</f>
         <v/>
       </c>
       <c r="AB45" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC45" s="26">
-        <f>ROUND(AA38/AB38,0)</f>
+        <f>ROUND(AA36/AB36,0)</f>
         <v/>
       </c>
       <c r="AD45" s="20" t="inlineStr">
@@ -6899,70 +6959,70 @@
       </c>
       <c r="AE45" s="184" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF45" s="183" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F46" s="183" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="G46" s="184" t="n">
-        <v>46057</v>
+        <v>46072</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>1440</v>
+        <v>14793</v>
       </c>
       <c r="I46" s="185">
-        <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J46" s="26" t="n">
-        <v>16908206</v>
+        <v>25506948</v>
       </c>
       <c r="K46" s="26">
-        <f>IFERROR(ROUND(H39*I39,0),0)</f>
+        <f>IFERROR(ROUND(H37*I37,0),0)</f>
         <v/>
       </c>
       <c r="L46" s="26">
-        <f>IFERROR(VLOOKUP(B39,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B37,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M46" s="26">
-        <f>IFERROR(VLOOKUP(B39,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B37,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 License</t>
+          <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
       <c r="O46" s="20" t="inlineStr">
@@ -6976,11 +7036,11 @@
         </is>
       </c>
       <c r="Q46" s="24">
-        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R46" s="26">
-        <f>IF(P39="","",H39)</f>
+        <f>IF(P37="","",H37)</f>
         <v/>
       </c>
       <c r="S46" s="26" t="n">
@@ -7009,18 +7069,18 @@
         <v>0</v>
       </c>
       <c r="Z46" s="26">
-        <f>S39+T39+W39</f>
+        <f>S37+T37+W37</f>
         <v/>
       </c>
       <c r="AA46" s="26">
-        <f>K39+L39+M39+IFERROR(VLOOKUP(B39,RemitTable2,9,FALSE()),0)+Y39+Z39</f>
+        <f>K37+L37+M37+IFERROR(VLOOKUP(B37,RemitTable2,9,FALSE()),0)+Y37+Z37</f>
         <v/>
       </c>
       <c r="AB46" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC46" s="26">
-        <f>ROUND(AA39/AB39,0)</f>
+        <f>ROUND(AA37/AB37,0)</f>
         <v/>
       </c>
       <c r="AD46" s="20" t="inlineStr">
@@ -7030,32 +7090,32 @@
       </c>
       <c r="AE46" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AF46" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-29</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="20" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>CPO687</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E47" s="21" t="inlineStr">
@@ -7064,36 +7124,38 @@
         </is>
       </c>
       <c r="F47" s="183" t="n">
-        <v>46042</v>
-      </c>
-      <c r="G47" s="184" t="n">
-        <v>46057</v>
+        <v>46029</v>
+      </c>
+      <c r="G47" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H47" s="24" t="n">
-        <v>4489</v>
+        <v>26656</v>
       </c>
       <c r="I47" s="185">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J47" s="26" t="n">
-        <v>16908206</v>
+        <v>0</v>
       </c>
       <c r="K47" s="26">
-        <f>IFERROR(ROUND(H40*I40,0),0)</f>
+        <f>IFERROR(ROUND(H38*I38,0),0)</f>
         <v/>
       </c>
       <c r="L47" s="26">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B38,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M47" s="26">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B38,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
-          <t>SX/SR EW (CGV/Lotte)</t>
+          <t>EW (홀딩)</t>
         </is>
       </c>
       <c r="O47" s="20" t="inlineStr">
@@ -7107,11 +7169,11 @@
         </is>
       </c>
       <c r="Q47" s="24">
-        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R47" s="26">
-        <f>IF(P40="","",H40)</f>
+        <f>IF(P38="","",H38)</f>
         <v/>
       </c>
       <c r="S47" s="26" t="n">
@@ -7140,18 +7202,18 @@
         <v>0</v>
       </c>
       <c r="Z47" s="26">
-        <f>S40+T40+W40</f>
+        <f>S38+T38+W38</f>
         <v/>
       </c>
       <c r="AA47" s="26">
-        <f>K40+L40+M40+IFERROR(VLOOKUP(B40,RemitTable2,9,FALSE()),0)+Y40+Z40</f>
+        <f>K38+L38+M38+IFERROR(VLOOKUP(B38,RemitTable2,9,FALSE()),0)+Y38+Z38</f>
         <v/>
       </c>
       <c r="AB47" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC47" s="26">
-        <f>ROUND(AA40/AB40,0)</f>
+        <f>ROUND(AA38/AB38,0)</f>
         <v/>
       </c>
       <c r="AD47" s="20" t="inlineStr">
@@ -7161,22 +7223,22 @@
       </c>
       <c r="AE47" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AF47" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
@@ -7191,7 +7253,7 @@
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F48" s="183" t="n">
@@ -7201,30 +7263,30 @@
         <v>46057</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>5670.57</v>
+        <v>1440</v>
       </c>
       <c r="I48" s="185">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J48" s="26" t="n">
         <v>16908206</v>
       </c>
       <c r="K48" s="26">
-        <f>IFERROR(ROUND(H41*I41,0),0)</f>
+        <f>IFERROR(ROUND(H39*I39,0),0)</f>
         <v/>
       </c>
       <c r="L48" s="26">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B39,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M48" s="26">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B39,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>SR-1000/SX-3000 EW</t>
+          <t>TMS-2000 License</t>
         </is>
       </c>
       <c r="O48" s="20" t="inlineStr">
@@ -7238,11 +7300,11 @@
         </is>
       </c>
       <c r="Q48" s="24">
-        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R48" s="26">
-        <f>IF(P41="","",H41)</f>
+        <f>IF(P39="","",H39)</f>
         <v/>
       </c>
       <c r="S48" s="26" t="n">
@@ -7271,18 +7333,18 @@
         <v>0</v>
       </c>
       <c r="Z48" s="26">
-        <f>S41+T41+W41</f>
+        <f>S39+T39+W39</f>
         <v/>
       </c>
       <c r="AA48" s="26">
-        <f>K41+L41+M41+IFERROR(VLOOKUP(B41,RemitTable2,9,FALSE()),0)+Y41+Z41</f>
+        <f>K39+L39+M39+IFERROR(VLOOKUP(B39,RemitTable2,9,FALSE()),0)+Y39+Z39</f>
         <v/>
       </c>
       <c r="AB48" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC48" s="26">
-        <f>ROUND(AA41/AB41,0)</f>
+        <f>ROUND(AA39/AB39,0)</f>
         <v/>
       </c>
       <c r="AD48" s="20" t="inlineStr">
@@ -7303,21 +7365,21 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="20" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E49" s="21" t="inlineStr">
@@ -7326,36 +7388,36 @@
         </is>
       </c>
       <c r="F49" s="183" t="n">
+        <v>46042</v>
+      </c>
+      <c r="G49" s="184" t="n">
         <v>46057</v>
       </c>
-      <c r="G49" s="184" t="n">
-        <v>46113</v>
-      </c>
       <c r="H49" s="24" t="n">
-        <v>24614</v>
+        <v>4489</v>
       </c>
       <c r="I49" s="185">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J49" s="26" t="n">
-        <v>51777431</v>
+        <v>16908206</v>
       </c>
       <c r="K49" s="26">
-        <f>IFERROR(ROUND(H42*I42,0),0)</f>
+        <f>IFERROR(ROUND(H40*I40,0),0)</f>
         <v/>
       </c>
       <c r="L49" s="26">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M49" s="26">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
-          <t>EW (메가박스 외)</t>
+          <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
       <c r="O49" s="20" t="inlineStr">
@@ -7369,11 +7431,11 @@
         </is>
       </c>
       <c r="Q49" s="24">
-        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R49" s="26">
-        <f>IF(P42="","",H42)</f>
+        <f>IF(P40="","",H40)</f>
         <v/>
       </c>
       <c r="S49" s="26" t="n">
@@ -7402,43 +7464,43 @@
         <v>0</v>
       </c>
       <c r="Z49" s="26">
-        <f>S42+T42+W42</f>
+        <f>S40+T40+W40</f>
         <v/>
       </c>
       <c r="AA49" s="26">
-        <f>K42+L42+M42+IFERROR(VLOOKUP(B42,RemitTable2,9,FALSE()),0)+Y42+Z42</f>
+        <f>K40+L40+M40+IFERROR(VLOOKUP(B40,RemitTable2,9,FALSE()),0)+Y40+Z40</f>
         <v/>
       </c>
       <c r="AB49" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC49" s="26">
-        <f>ROUND(AA42/AB42,0)</f>
+        <f>ROUND(AA40/AB40,0)</f>
         <v/>
       </c>
       <c r="AD49" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE49" s="184" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF49" s="183" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
@@ -7457,36 +7519,36 @@
         </is>
       </c>
       <c r="F50" s="183" t="n">
-        <v>46060</v>
+        <v>46042</v>
       </c>
       <c r="G50" s="184" t="n">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>3993.05</v>
+        <v>5670.57</v>
       </c>
       <c r="I50" s="185">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J50" s="26" t="n">
-        <v>9919642</v>
+        <v>16908206</v>
       </c>
       <c r="K50" s="26">
-        <f>IFERROR(ROUND(H43*I43,0),0)</f>
+        <f>IFERROR(ROUND(H41*I41,0),0)</f>
         <v/>
       </c>
       <c r="L50" s="26">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B41,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M50" s="26">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B41,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
-          <t>SR/SX EW (하남미사 외)</t>
+          <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
       <c r="O50" s="20" t="inlineStr">
@@ -7500,11 +7562,11 @@
         </is>
       </c>
       <c r="Q50" s="24">
-        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R50" s="26">
-        <f>IF(P43="","",H43)</f>
+        <f>IF(P41="","",H41)</f>
         <v/>
       </c>
       <c r="S50" s="26" t="n">
@@ -7533,18 +7595,18 @@
         <v>0</v>
       </c>
       <c r="Z50" s="26">
-        <f>S43+T43+W43</f>
+        <f>S41+T41+W41</f>
         <v/>
       </c>
       <c r="AA50" s="26">
-        <f>K43+L43+M43+IFERROR(VLOOKUP(B43,RemitTable2,9,FALSE()),0)+Y43+Z43</f>
+        <f>K41+L41+M41+IFERROR(VLOOKUP(B41,RemitTable2,9,FALSE()),0)+Y41+Z41</f>
         <v/>
       </c>
       <c r="AB50" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC50" s="26">
-        <f>ROUND(AA43/AB43,0)</f>
+        <f>ROUND(AA41/AB41,0)</f>
         <v/>
       </c>
       <c r="AD50" s="20" t="inlineStr">
@@ -7559,65 +7621,65 @@
       </c>
       <c r="AF50" s="183" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="20" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E51" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F51" s="183" t="n">
-        <v>46080</v>
+        <v>46057</v>
       </c>
       <c r="G51" s="184" t="n">
         <v>46113</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>360</v>
+        <v>24614</v>
       </c>
       <c r="I51" s="185">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J51" s="26" t="n">
-        <v>9919642</v>
+        <v>51777431</v>
       </c>
       <c r="K51" s="26">
-        <f>IFERROR(ROUND(H44*I44,0),0)</f>
+        <f>IFERROR(ROUND(H42*I42,0),0)</f>
         <v/>
       </c>
       <c r="L51" s="26">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B42,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M51" s="26">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B42,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 License</t>
+          <t>EW (메가박스 외)</t>
         </is>
       </c>
       <c r="O51" s="20" t="inlineStr">
@@ -7631,11 +7693,11 @@
         </is>
       </c>
       <c r="Q51" s="24">
-        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R51" s="26">
-        <f>IF(P44="","",H44)</f>
+        <f>IF(P42="","",H42)</f>
         <v/>
       </c>
       <c r="S51" s="26" t="n">
@@ -7664,18 +7726,18 @@
         <v>0</v>
       </c>
       <c r="Z51" s="26">
-        <f>S44+T44+W44</f>
+        <f>S42+T42+W42</f>
         <v/>
       </c>
       <c r="AA51" s="26">
-        <f>K44+L44+M44+IFERROR(VLOOKUP(B44,RemitTable2,9,FALSE()),0)+Y44+Z44</f>
+        <f>K42+L42+M42+IFERROR(VLOOKUP(B42,RemitTable2,9,FALSE()),0)+Y42+Z42</f>
         <v/>
       </c>
       <c r="AB51" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC51" s="26">
-        <f>ROUND(AA44/AB44,0)</f>
+        <f>ROUND(AA42/AB42,0)</f>
         <v/>
       </c>
       <c r="AD51" s="20" t="inlineStr">
@@ -7696,11 +7758,11 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>GPO469</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
@@ -7715,40 +7777,40 @@
       </c>
       <c r="E52" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F52" s="183" t="n">
-        <v>46088</v>
+        <v>46060</v>
       </c>
       <c r="G52" s="184" t="n">
         <v>46113</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>500</v>
+        <v>3993.05</v>
       </c>
       <c r="I52" s="185">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J52" s="26" t="n">
         <v>9919642</v>
       </c>
       <c r="K52" s="26">
-        <f>IFERROR(ROUND(H45*I45,0),0)</f>
+        <f>IFERROR(ROUND(H43*I43,0),0)</f>
         <v/>
       </c>
       <c r="L52" s="26">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B43,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M52" s="26">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B43,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
-          <t>Dolby Atmos License</t>
+          <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
       <c r="O52" s="20" t="inlineStr">
@@ -7762,11 +7824,11 @@
         </is>
       </c>
       <c r="Q52" s="24">
-        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R52" s="26">
-        <f>IF(P45="","",H45)</f>
+        <f>IF(P43="","",H43)</f>
         <v/>
       </c>
       <c r="S52" s="26" t="n">
@@ -7795,91 +7857,91 @@
         <v>0</v>
       </c>
       <c r="Z52" s="26">
-        <f>S45+T45+W45</f>
+        <f>S43+T43+W43</f>
         <v/>
       </c>
       <c r="AA52" s="26">
-        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE()),0)+Y45+Z45</f>
+        <f>K43+L43+M43+IFERROR(VLOOKUP(B43,RemitTable2,9,FALSE()),0)+Y43+Z43</f>
         <v/>
       </c>
       <c r="AB52" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC52" s="26">
-        <f>ROUND(AA45/AB45,0)</f>
+        <f>ROUND(AA43/AB43,0)</f>
         <v/>
       </c>
       <c r="AD52" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE52" s="184" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF52" s="183" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-02-22</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="20" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>GPO470</t>
         </is>
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F53" s="183" t="n">
-        <v>46109</v>
+        <v>46080</v>
       </c>
       <c r="G53" s="184" t="n">
-        <v>46146</v>
+        <v>46113</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>17404</v>
+        <v>360</v>
       </c>
       <c r="I53" s="185">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J53" s="26" t="n">
-        <v>0</v>
+        <v>9919642</v>
       </c>
       <c r="K53" s="26">
-        <f>IFERROR(ROUND(H49*I49,0),0)</f>
+        <f>IFERROR(ROUND(H44*I44,0),0)</f>
         <v/>
       </c>
       <c r="L53" s="26">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B44,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M53" s="26">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B44,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
-          <t>EW (CGV 동백 외)</t>
+          <t>TMS-1000 License</t>
         </is>
       </c>
       <c r="O53" s="20" t="inlineStr">
@@ -7893,11 +7955,11 @@
         </is>
       </c>
       <c r="Q53" s="24">
-        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R53" s="26">
-        <f>IF(P49="","",H49)</f>
+        <f>IF(P44="","",H44)</f>
         <v/>
       </c>
       <c r="S53" s="26" t="n">
@@ -7926,499 +7988,551 @@
         <v>0</v>
       </c>
       <c r="Z53" s="26">
-        <f>S49+T49+W49</f>
+        <f>S44+T44+W44</f>
         <v/>
       </c>
       <c r="AA53" s="26">
-        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE()),0)+Y49+Z49</f>
+        <f>K44+L44+M44+IFERROR(VLOOKUP(B44,RemitTable2,9,FALSE()),0)+Y44+Z44</f>
         <v/>
       </c>
       <c r="AB53" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC53" s="26">
+        <f>ROUND(AA44/AB44,0)</f>
+        <v/>
+      </c>
+      <c r="AD53" s="20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE53" s="184" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AF53" s="183" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>GPO471</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F54" s="183" t="n">
+        <v>46088</v>
+      </c>
+      <c r="G54" s="184" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H54" s="24" t="n">
+        <v>500</v>
+      </c>
+      <c r="I54" s="185">
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J54" s="26" t="n">
+        <v>9919642</v>
+      </c>
+      <c r="K54" s="26">
+        <f>IFERROR(ROUND(H45*I45,0),0)</f>
+        <v/>
+      </c>
+      <c r="L54" s="26">
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M54" s="26">
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N54" s="20" t="inlineStr">
+        <is>
+          <t>Dolby Atmos License</t>
+        </is>
+      </c>
+      <c r="O54" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P54" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q54" s="24">
+        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R54" s="26">
+        <f>IF(P45="","",H45)</f>
+        <v/>
+      </c>
+      <c r="S54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="26">
+        <f>S45+T45+W45</f>
+        <v/>
+      </c>
+      <c r="AA54" s="26">
+        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE()),0)+Y45+Z45</f>
+        <v/>
+      </c>
+      <c r="AB54" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" s="26">
+        <f>ROUND(AA45/AB45,0)</f>
+        <v/>
+      </c>
+      <c r="AD54" s="20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE54" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF54" s="183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>CPO694</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F55" s="183" t="n">
+        <v>46109</v>
+      </c>
+      <c r="G55" s="184" t="n">
+        <v>46146</v>
+      </c>
+      <c r="H55" s="24" t="n">
+        <v>17404</v>
+      </c>
+      <c r="I55" s="185">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="26">
+        <f>IFERROR(ROUND(H49*I49,0),0)</f>
+        <v/>
+      </c>
+      <c r="L55" s="26">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M55" s="26">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N55" s="20" t="inlineStr">
+        <is>
+          <t>EW (CGV 동백 외)</t>
+        </is>
+      </c>
+      <c r="O55" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P55" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q55" s="24">
+        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R55" s="26">
+        <f>IF(P49="","",H49)</f>
+        <v/>
+      </c>
+      <c r="S55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="26">
+        <f>S49+T49+W49</f>
+        <v/>
+      </c>
+      <c r="AA55" s="26">
+        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE()),0)+Y49+Z49</f>
+        <v/>
+      </c>
+      <c r="AB55" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC55" s="26">
         <f>ROUND(AA49/AB49,0)</f>
         <v/>
       </c>
-      <c r="AD53" s="20" t="inlineStr">
+      <c r="AD55" s="20" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE53" s="184" t="inlineStr">
+      <c r="AE55" s="184" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AF53" s="183" t="inlineStr">
+      <c r="AF55" s="183" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="85" t="n">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="85" t="n">
         <v>46</v>
       </c>
-      <c r="B54" s="85" t="inlineStr">
+      <c r="B56" s="85" t="inlineStr">
         <is>
           <t>CPO697</t>
         </is>
       </c>
-      <c r="C54" s="85" t="inlineStr">
+      <c r="C56" s="85" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D54" s="85" t="inlineStr">
+      <c r="D56" s="85" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E54" s="85" t="inlineStr">
+      <c r="E56" s="85" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F54" s="186" t="n">
+      <c r="F56" s="186" t="n">
         <v>46136</v>
       </c>
-      <c r="G54" s="186" t="inlineStr">
+      <c r="G56" s="186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H54" s="87" t="n">
+      <c r="H56" s="87" t="n">
         <v>15289</v>
       </c>
-      <c r="I54" s="187">
+      <c r="I56" s="187">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J54" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="89">
+      <c r="J56" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="89">
         <f>IFERROR(ROUND(H50*I50,0),0)</f>
         <v/>
       </c>
-      <c r="L54" s="89">
+      <c r="L56" s="89">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="M54" s="89">
+      <c r="M56" s="89">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="N54" s="85" t="inlineStr">
+      <c r="N56" s="85" t="inlineStr">
         <is>
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O54" s="186" t="inlineStr">
+      <c r="O56" s="186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P54" s="85" t="inlineStr">
+      <c r="P56" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q54" s="87">
+      <c r="Q56" s="87">
         <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R54" s="87">
+      <c r="R56" s="87">
         <f>IF(P50="","",H50)</f>
         <v/>
       </c>
-      <c r="S54" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="186" t="n"/>
-      <c r="V54" s="85" t="inlineStr">
+      <c r="S56" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="186" t="n"/>
+      <c r="V56" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W54" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" s="85" t="inlineStr">
+      <c r="W56" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y54" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="89">
+      <c r="Y56" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="89">
         <f>S50+T50+W50</f>
         <v/>
       </c>
-      <c r="AA54" s="89">
+      <c r="AA56" s="89">
         <f>K50+L50+M50+IFERROR(VLOOKUP(B50,RemitTable2,9,FALSE()),0)+Y50+Z50</f>
         <v/>
       </c>
-      <c r="AB54" s="90" t="n">
+      <c r="AB56" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="AC54" s="89">
+      <c r="AC56" s="89">
         <f>ROUND(AA50/AB50,0)</f>
         <v/>
       </c>
-      <c r="AD54" s="85" t="inlineStr">
+      <c r="AD56" s="85" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE54" s="186" t="n"/>
-      <c r="AF54" s="186" t="n"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="85" t="n">
+      <c r="AE56" s="186" t="n"/>
+      <c r="AF56" s="186" t="n"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="85" t="n">
         <v>47</v>
       </c>
-      <c r="B55" s="85" t="inlineStr">
+      <c r="B57" s="85" t="inlineStr">
         <is>
           <t>CPO693-2</t>
         </is>
       </c>
-      <c r="C55" s="85" t="inlineStr">
+      <c r="C57" s="85" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D55" s="85" t="inlineStr">
+      <c r="D57" s="85" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E55" s="85" t="inlineStr">
+      <c r="E57" s="85" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F55" s="186" t="n">
+      <c r="F57" s="186" t="n">
         <v>46133</v>
       </c>
-      <c r="G55" s="186" t="inlineStr">
+      <c r="G57" s="186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H55" s="87" t="n">
+      <c r="H57" s="87" t="n">
         <v>2550</v>
       </c>
-      <c r="I55" s="187">
+      <c r="I57" s="187">
         <f>IFERROR(VLOOKUP(B51,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J55" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="89">
+      <c r="J57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="89">
         <f>IFERROR(ROUND(H51*I51,0),0)</f>
         <v/>
       </c>
-      <c r="L55" s="89">
+      <c r="L57" s="89">
         <f>IFERROR(VLOOKUP(B51,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="M55" s="89">
+      <c r="M57" s="89">
         <f>IFERROR(VLOOKUP(B51,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="N55" s="85" t="inlineStr">
+      <c r="N57" s="85" t="inlineStr">
         <is>
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O55" s="186" t="inlineStr">
+      <c r="O57" s="186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P55" s="85" t="inlineStr">
+      <c r="P57" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q55" s="87">
+      <c r="Q57" s="87">
         <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R55" s="87">
+      <c r="R57" s="87">
         <f>IF(P51="","",H51)</f>
         <v/>
       </c>
-      <c r="S55" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="186" t="n"/>
-      <c r="V55" s="85" t="inlineStr">
+      <c r="S57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="186" t="n"/>
+      <c r="V57" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W55" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" s="85" t="inlineStr">
+      <c r="W57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y55" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="89">
+      <c r="Y57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="89">
         <f>S51+T51+W51</f>
         <v/>
       </c>
-      <c r="AA55" s="89">
+      <c r="AA57" s="89">
         <f>K51+L51+M51+IFERROR(VLOOKUP(B51,RemitTable2,9,FALSE()),0)+Y51+Z51</f>
         <v/>
       </c>
-      <c r="AB55" s="90" t="n">
+      <c r="AB57" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="AC55" s="89">
+      <c r="AC57" s="89">
         <f>ROUND(AA51/AB51,0)</f>
         <v/>
       </c>
-      <c r="AD55" s="85" t="inlineStr">
+      <c r="AD57" s="85" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE55" s="186" t="n"/>
-      <c r="AF55" s="186" t="n"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="132" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="132" t="inlineStr">
-        <is>
-          <t>GPO478</t>
-        </is>
-      </c>
-      <c r="C56" s="132" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D56" s="132" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E56" s="132" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F56" s="188" t="n">
-        <v>46127</v>
-      </c>
-      <c r="G56" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="134" t="n">
-        <v>180</v>
-      </c>
-      <c r="I56" s="134">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J56" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="136">
-        <f>IFERROR(ROUND(H56*I56,0),0)</f>
-        <v/>
-      </c>
-      <c r="L56" s="136">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M56" s="136">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N56" s="137" t="n"/>
-      <c r="O56" s="137" t="n"/>
-      <c r="P56" s="137" t="n"/>
-      <c r="Q56" s="134">
-        <f>IF(P56="","",IFERROR(VLOOKUP(O56,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R56" s="134">
-        <f>IF(P56="","",H56)</f>
-        <v/>
-      </c>
-      <c r="S56" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="137" t="n"/>
-      <c r="V56" s="137" t="n"/>
-      <c r="W56" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y56" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="136">
-        <f>S56+T56+W56</f>
-        <v/>
-      </c>
-      <c r="AA56" s="136">
-        <f>K56+L56+M56+IFERROR(VLOOKUP(B56,RemitTable2,9,FALSE),0)+Y56+Z56</f>
-        <v/>
-      </c>
-      <c r="AB56" s="168" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC56" s="136">
-        <f>ROUND(AA56/AB56,0)</f>
-        <v/>
-      </c>
-      <c r="AD56" s="137" t="n"/>
-      <c r="AE56" s="189" t="n">
-        <v>46143</v>
-      </c>
-      <c r="AF56" s="189" t="n">
-        <v>46507</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="132" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="132" t="inlineStr">
-        <is>
-          <t>GPO480</t>
-        </is>
-      </c>
-      <c r="C57" s="132" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D57" s="132" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E57" s="132" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F57" s="188" t="n">
-        <v>46137</v>
-      </c>
-      <c r="G57" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="134" t="n">
-        <v>250</v>
-      </c>
-      <c r="I57" s="134">
-        <f>IFERROR(VLOOKUP(B57,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J57" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="136">
-        <f>IFERROR(ROUND(H57*I57,0),0)</f>
-        <v/>
-      </c>
-      <c r="L57" s="136">
-        <f>IFERROR(VLOOKUP(B57,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M57" s="136">
-        <f>IFERROR(VLOOKUP(B57,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N57" s="137" t="n"/>
-      <c r="O57" s="137" t="n"/>
-      <c r="P57" s="137" t="n"/>
-      <c r="Q57" s="134">
-        <f>IF(P57="","",IFERROR(VLOOKUP(O57,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R57" s="134">
-        <f>IF(P57="","",H57)</f>
-        <v/>
-      </c>
-      <c r="S57" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="137" t="n"/>
-      <c r="V57" s="137" t="n"/>
-      <c r="W57" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y57" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="136">
-        <f>S57+T57+W57</f>
-        <v/>
-      </c>
-      <c r="AA57" s="136">
-        <f>K57+L57+M57+IFERROR(VLOOKUP(B57,RemitTable2,9,FALSE),0)+Y57+Z57</f>
-        <v/>
-      </c>
-      <c r="AB57" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC57" s="136">
-        <f>ROUND(AA57/AB57,0)</f>
-        <v/>
-      </c>
-      <c r="AD57" s="137" t="n"/>
-      <c r="AE57" s="137" t="n"/>
-      <c r="AF57" s="137" t="n"/>
+      <c r="AE57" s="186" t="n"/>
+      <c r="AF57" s="186" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="132" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B58" s="132" t="inlineStr">
         <is>
-          <t>GPO481</t>
+          <t>GPO478</t>
         </is>
       </c>
       <c r="C58" s="132" t="inlineStr">
@@ -8437,7 +8551,7 @@
         </is>
       </c>
       <c r="F58" s="188" t="n">
-        <v>46152</v>
+        <v>46127</v>
       </c>
       <c r="G58" s="132" t="inlineStr">
         <is>
@@ -8445,36 +8559,36 @@
         </is>
       </c>
       <c r="H58" s="134" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="I58" s="134">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,7,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J58" s="136" t="n">
         <v>0</v>
       </c>
       <c r="K58" s="136">
-        <f>IFERROR(ROUND(H58*I58,0),0)</f>
+        <f>IFERROR(ROUND(H56*I56,0),0)</f>
         <v/>
       </c>
       <c r="L58" s="136">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,10,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M58" s="136">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,11,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N58" s="137" t="n"/>
       <c r="O58" s="137" t="n"/>
       <c r="P58" s="137" t="n"/>
       <c r="Q58" s="134">
-        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P56="","",IFERROR(VLOOKUP(O56,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R58" s="134">
-        <f>IF(P58="","",H58)</f>
+        <f>IF(P56="","",H56)</f>
         <v/>
       </c>
       <c r="S58" s="136" t="n">
@@ -8497,489 +8611,605 @@
         <v>0</v>
       </c>
       <c r="Z58" s="136">
+        <f>S56+T56+W56</f>
+        <v/>
+      </c>
+      <c r="AA58" s="136">
+        <f>K56+L56+M56+IFERROR(VLOOKUP(B56,RemitTable2,9,FALSE),0)+Y56+Z56</f>
+        <v/>
+      </c>
+      <c r="AB58" s="168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC58" s="136">
+        <f>ROUND(AA56/AB56,0)</f>
+        <v/>
+      </c>
+      <c r="AD58" s="137" t="n"/>
+      <c r="AE58" s="189" t="n">
+        <v>46143</v>
+      </c>
+      <c r="AF58" s="189" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="132" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="132" t="inlineStr">
+        <is>
+          <t>GPO480</t>
+        </is>
+      </c>
+      <c r="C59" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D59" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E59" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F59" s="188" t="n">
+        <v>46137</v>
+      </c>
+      <c r="G59" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="134" t="n">
+        <v>250</v>
+      </c>
+      <c r="I59" s="134">
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J59" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="136">
+        <f>IFERROR(ROUND(H57*I57,0),0)</f>
+        <v/>
+      </c>
+      <c r="L59" s="136">
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M59" s="136">
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N59" s="137" t="n"/>
+      <c r="O59" s="137" t="n"/>
+      <c r="P59" s="137" t="n"/>
+      <c r="Q59" s="134">
+        <f>IF(P57="","",IFERROR(VLOOKUP(O57,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R59" s="134">
+        <f>IF(P57="","",H57)</f>
+        <v/>
+      </c>
+      <c r="S59" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="137" t="n"/>
+      <c r="V59" s="137" t="n"/>
+      <c r="W59" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y59" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="136">
+        <f>S57+T57+W57</f>
+        <v/>
+      </c>
+      <c r="AA59" s="136">
+        <f>K57+L57+M57+IFERROR(VLOOKUP(B57,RemitTable2,9,FALSE),0)+Y57+Z57</f>
+        <v/>
+      </c>
+      <c r="AB59" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="136">
+        <f>ROUND(AA57/AB57,0)</f>
+        <v/>
+      </c>
+      <c r="AD59" s="137" t="n"/>
+      <c r="AE59" s="137" t="n"/>
+      <c r="AF59" s="137" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="132" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="132" t="inlineStr">
+        <is>
+          <t>GPO481</t>
+        </is>
+      </c>
+      <c r="C60" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D60" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E60" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F60" s="188" t="n">
+        <v>46152</v>
+      </c>
+      <c r="G60" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="134" t="n">
+        <v>500</v>
+      </c>
+      <c r="I60" s="134">
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J60" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="136">
+        <f>IFERROR(ROUND(H58*I58,0),0)</f>
+        <v/>
+      </c>
+      <c r="L60" s="136">
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M60" s="136">
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N60" s="137" t="n"/>
+      <c r="O60" s="137" t="n"/>
+      <c r="P60" s="137" t="n"/>
+      <c r="Q60" s="134">
+        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R60" s="134">
+        <f>IF(P58="","",H58)</f>
+        <v/>
+      </c>
+      <c r="S60" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="137" t="n"/>
+      <c r="V60" s="137" t="n"/>
+      <c r="W60" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y60" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="136">
         <f>S58+T58+W58</f>
         <v/>
       </c>
-      <c r="AA58" s="136">
+      <c r="AA60" s="136">
         <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
         <v/>
       </c>
-      <c r="AB58" s="168" t="n">
+      <c r="AB60" s="168" t="n">
         <v>1</v>
       </c>
-      <c r="AC58" s="136">
+      <c r="AC60" s="136">
         <f>ROUND(AA58/AB58,0)</f>
         <v/>
       </c>
-      <c r="AD58" s="137" t="n"/>
-      <c r="AE58" s="137" t="n"/>
-      <c r="AF58" s="137" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="n">
+      <c r="AD60" s="137" t="n"/>
+      <c r="AE60" s="137" t="n"/>
+      <c r="AF60" s="137" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>CPO688</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="F59" s="176" t="n">
+      <c r="F61" s="176" t="n">
         <v>46037</v>
       </c>
-      <c r="G59" s="177" t="inlineStr">
+      <c r="G61" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H59" s="16" t="n">
+      <c r="H61" s="16" t="n">
         <v>4180</v>
       </c>
-      <c r="I59" s="178">
+      <c r="I61" s="178">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J59" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="18">
+      <c r="J61" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="18">
         <f>IFERROR(ROUND(H47*I47,0),0)</f>
         <v/>
       </c>
-      <c r="L59" s="18">
+      <c r="L61" s="18">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="M59" s="18">
+      <c r="M61" s="18">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="N59" s="12" t="inlineStr">
+      <c r="N61" s="12" t="inlineStr">
         <is>
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O59" s="12" t="inlineStr">
+      <c r="O61" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P59" s="12" t="inlineStr">
+      <c r="P61" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q59" s="16">
+      <c r="Q61" s="16">
         <f>IF(P52="","",IFERROR(VLOOKUP(O52,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R59" s="18">
+      <c r="R61" s="18">
         <f>IF(P47="","",H47)</f>
         <v/>
       </c>
-      <c r="S59" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="12" t="inlineStr">
+      <c r="S61" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W59" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" s="13" t="inlineStr">
+      <c r="W61" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y59" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="18">
+      <c r="Y61" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="18">
         <f>S47+T47+W47</f>
         <v/>
       </c>
-      <c r="AA59" s="18">
+      <c r="AA61" s="18">
         <f>K47+L47+M47+IFERROR(VLOOKUP(B47,RemitTable2,9,FALSE()),0)+Y47+Z47</f>
         <v/>
       </c>
-      <c r="AB59" s="19" t="n">
+      <c r="AB61" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="AC59" s="18">
+      <c r="AC61" s="18">
         <f>ROUND(AA47/AB47,0)</f>
         <v/>
       </c>
-      <c r="AD59" s="12" t="inlineStr">
+      <c r="AD61" s="12" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE59" s="177" t="inlineStr">
+      <c r="AE61" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF59" s="176" t="inlineStr">
+      <c r="AF61" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="12" t="n">
+    <row r="62">
+      <c r="A62" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>SX3000수리</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>수리반환</t>
         </is>
       </c>
-      <c r="F60" s="176" t="n"/>
-      <c r="G60" s="177" t="n"/>
-      <c r="H60" s="16" t="n">
+      <c r="F62" s="176" t="n"/>
+      <c r="G62" s="177" t="n"/>
+      <c r="H62" s="16" t="n">
         <v>400</v>
       </c>
-      <c r="I60" s="178">
+      <c r="I62" s="178">
         <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J60" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="18">
+      <c r="J62" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="18">
         <f>IFERROR(ROUND(H48*I48,0),0)</f>
         <v/>
       </c>
-      <c r="L60" s="18">
+      <c r="L62" s="18">
         <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="M60" s="18">
+      <c r="M62" s="18">
         <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="N60" s="12" t="inlineStr">
+      <c r="N62" s="12" t="inlineStr">
         <is>
           <t>Display Card (수리반환 5PCS)</t>
         </is>
       </c>
-      <c r="O60" s="177" t="n">
+      <c r="O62" s="177" t="n">
         <v>46125</v>
       </c>
-      <c r="P60" s="12" t="inlineStr">
+      <c r="P62" s="12" t="inlineStr">
         <is>
           <t>22356-26-351613M</t>
         </is>
       </c>
-      <c r="Q60" s="16">
+      <c r="Q62" s="16">
         <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R60" s="18">
+      <c r="R62" s="18">
         <f>IF(P48="","",H48)</f>
         <v/>
       </c>
-      <c r="S60" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="18" t="n">
+      <c r="S62" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="18" t="n">
         <v>67750</v>
       </c>
-      <c r="U60" s="13" t="n"/>
-      <c r="V60" s="12" t="inlineStr">
+      <c r="U62" s="13" t="n"/>
+      <c r="V62" s="12" t="inlineStr">
         <is>
           <t>운서합동</t>
         </is>
       </c>
-      <c r="W60" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="13" t="inlineStr">
+      <c r="W62" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="13" t="inlineStr">
         <is>
           <t>DHL</t>
         </is>
       </c>
-      <c r="Y60" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="18">
+      <c r="Y62" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="18">
         <f>S48+T48+W48</f>
         <v/>
       </c>
-      <c r="AA60" s="18">
+      <c r="AA62" s="18">
         <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE()),0)+Y48+Z48</f>
         <v/>
       </c>
-      <c r="AB60" s="19" t="n">
+      <c r="AB62" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="AC60" s="18">
+      <c r="AC62" s="18">
         <f>ROUND(AA48/AB48,0)</f>
         <v/>
       </c>
-      <c r="AD60" s="12" t="inlineStr">
+      <c r="AD62" s="12" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE60" s="177" t="n"/>
-      <c r="AF60" s="176" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="147" t="inlineStr">
+      <c r="AE62" s="177" t="n"/>
+      <c r="AF62" s="176" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="216" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="216" t="inlineStr">
+        <is>
+          <t>FRC-MONOPLEX26</t>
+        </is>
+      </c>
+      <c r="C63" s="217" t="inlineStr">
+        <is>
+          <t>Ferco</t>
+        </is>
+      </c>
+      <c r="D63" s="216" t="inlineStr">
+        <is>
+          <t>50% TT advance + 50% balance</t>
+        </is>
+      </c>
+      <c r="E63" s="217" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F63" s="218" t="n">
+        <v>46048</v>
+      </c>
+      <c r="G63" s="219" t="n">
+        <v>46133</v>
+      </c>
+      <c r="H63" s="220" t="n">
+        <v>51952</v>
+      </c>
+      <c r="I63" s="221">
+        <f>IFERROR(VLOOKUP(B63,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J63" s="222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="222">
+        <f>IFERROR(ROUND(H63*I63,0),0)</f>
+        <v/>
+      </c>
+      <c r="L63" s="222">
+        <f>IFERROR(VLOOKUP(B63,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M63" s="222">
+        <f>IFERROR(VLOOKUP(B63,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N63" s="216" t="inlineStr">
+        <is>
+          <t>Cinema Seat (Recliner) / 44 EA / Monoplex DH Bangbae</t>
+        </is>
+      </c>
+      <c r="O63" s="219" t="n">
+        <v>46153</v>
+      </c>
+      <c r="P63" s="216" t="inlineStr">
+        <is>
+          <t>14008-26-101147M</t>
+        </is>
+      </c>
+      <c r="Q63" s="220">
+        <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R63" s="220">
+        <f>IF(P63="","",H63)</f>
+        <v/>
+      </c>
+      <c r="S63" s="222" t="n">
+        <v>31050</v>
+      </c>
+      <c r="T63" s="222" t="n">
+        <v>7959560</v>
+      </c>
+      <c r="U63" s="218" t="n"/>
+      <c r="V63" s="216" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W63" s="222" t="n">
+        <v>250000</v>
+      </c>
+      <c r="X63" s="217" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="Y63" s="222" t="n">
+        <v>5002612</v>
+      </c>
+      <c r="Z63" s="222">
+        <f>S63+T63+W63</f>
+        <v/>
+      </c>
+      <c r="AA63" s="222">
+        <f>K63+L63+M63+IFERROR(VLOOKUP(B63,RemitTable2,9,FALSE),0)+Y63+Z63</f>
+        <v/>
+      </c>
+      <c r="AB63" s="223" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC63" s="222">
+        <f>ROUND(AA63/AB63,0)</f>
+        <v/>
+      </c>
+      <c r="AD63" s="216" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE63" s="216" t="n"/>
+      <c r="AF63" s="217" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="147" t="inlineStr">
         <is>
           <t>장비/부품 합계</t>
-        </is>
-      </c>
-      <c r="B61" s="148" t="n"/>
-      <c r="C61" s="148" t="n"/>
-      <c r="D61" s="148" t="n"/>
-      <c r="E61" s="148" t="n"/>
-      <c r="F61" s="148" t="n"/>
-      <c r="G61" s="149" t="n"/>
-      <c r="H61" s="142">
-        <f>SUBTOTAL(9,H5:H36)</f>
-        <v/>
-      </c>
-      <c r="I61" s="141" t="n"/>
-      <c r="J61" s="142">
-        <f>SUBTOTAL(9,J5:J36)</f>
-        <v/>
-      </c>
-      <c r="K61" s="142">
-        <f>SUBTOTAL(9,K5:K36)</f>
-        <v/>
-      </c>
-      <c r="L61" s="142">
-        <f>SUBTOTAL(9,L5:L36)</f>
-        <v/>
-      </c>
-      <c r="M61" s="142">
-        <f>SUBTOTAL(9,M5:M36)</f>
-        <v/>
-      </c>
-      <c r="N61" s="141" t="n"/>
-      <c r="O61" s="141" t="n"/>
-      <c r="P61" s="141" t="n"/>
-      <c r="Q61" s="142" t="n"/>
-      <c r="R61" s="140" t="n"/>
-      <c r="S61" s="142">
-        <f>SUBTOTAL(9,S5:S36)</f>
-        <v/>
-      </c>
-      <c r="T61" s="142">
-        <f>SUBTOTAL(9,T5:T36)</f>
-        <v/>
-      </c>
-      <c r="U61" s="141" t="n"/>
-      <c r="V61" s="141" t="n"/>
-      <c r="W61" s="142">
-        <f>SUBTOTAL(9,W5:W36)</f>
-        <v/>
-      </c>
-      <c r="X61" s="147" t="n"/>
-      <c r="Y61" s="142">
-        <f>SUBTOTAL(9,Y5:Y36)</f>
-        <v/>
-      </c>
-      <c r="Z61" s="142">
-        <f>SUBTOTAL(9,Z5:Z36)</f>
-        <v/>
-      </c>
-      <c r="AA61" s="142">
-        <f>SUBTOTAL(9,AA5:AA36)</f>
-        <v/>
-      </c>
-      <c r="AB61" s="147" t="n"/>
-      <c r="AC61" s="141" t="n"/>
-      <c r="AD61" s="141" t="n"/>
-      <c r="AE61" s="141" t="n"/>
-      <c r="AF61" s="141" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="147" t="inlineStr">
-        <is>
-          <t>라이센스/워런티 합계</t>
-        </is>
-      </c>
-      <c r="B62" s="148" t="n"/>
-      <c r="C62" s="148" t="n"/>
-      <c r="D62" s="148" t="n"/>
-      <c r="E62" s="148" t="n"/>
-      <c r="F62" s="148" t="n"/>
-      <c r="G62" s="149" t="n"/>
-      <c r="H62" s="142">
-        <f>SUBTOTAL(9,H37:H58)</f>
-        <v/>
-      </c>
-      <c r="I62" s="141" t="n"/>
-      <c r="J62" s="142">
-        <f>SUBTOTAL(9,J37:J58)</f>
-        <v/>
-      </c>
-      <c r="K62" s="142">
-        <f>SUBTOTAL(9,K37:K58)</f>
-        <v/>
-      </c>
-      <c r="L62" s="142">
-        <f>SUBTOTAL(9,L37:L58)</f>
-        <v/>
-      </c>
-      <c r="M62" s="142">
-        <f>SUBTOTAL(9,M37:M58)</f>
-        <v/>
-      </c>
-      <c r="N62" s="141" t="n"/>
-      <c r="O62" s="141" t="n"/>
-      <c r="P62" s="141" t="n"/>
-      <c r="Q62" s="142" t="n"/>
-      <c r="R62" s="140" t="n"/>
-      <c r="S62" s="142">
-        <f>SUBTOTAL(9,S37:S58)</f>
-        <v/>
-      </c>
-      <c r="T62" s="142">
-        <f>SUBTOTAL(9,T37:T58)</f>
-        <v/>
-      </c>
-      <c r="U62" s="141" t="n"/>
-      <c r="V62" s="141" t="n"/>
-      <c r="W62" s="142">
-        <f>SUBTOTAL(9,W37:W58)</f>
-        <v/>
-      </c>
-      <c r="X62" s="147" t="n"/>
-      <c r="Y62" s="142">
-        <f>SUBTOTAL(9,Y37:Y58)</f>
-        <v/>
-      </c>
-      <c r="Z62" s="142">
-        <f>SUBTOTAL(9,Z37:Z58)</f>
-        <v/>
-      </c>
-      <c r="AA62" s="142">
-        <f>SUBTOTAL(9,AA37:AA58)</f>
-        <v/>
-      </c>
-      <c r="AB62" s="147" t="n"/>
-      <c r="AC62" s="141" t="n"/>
-      <c r="AD62" s="141" t="n"/>
-      <c r="AE62" s="141" t="n"/>
-      <c r="AF62" s="141" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="147" t="inlineStr">
-        <is>
-          <t>기타 합계</t>
-        </is>
-      </c>
-      <c r="B63" s="148" t="n"/>
-      <c r="C63" s="148" t="n"/>
-      <c r="D63" s="148" t="n"/>
-      <c r="E63" s="148" t="n"/>
-      <c r="F63" s="148" t="n"/>
-      <c r="G63" s="149" t="n"/>
-      <c r="H63" s="142">
-        <f>H59+H60</f>
-        <v/>
-      </c>
-      <c r="I63" s="141" t="n"/>
-      <c r="J63" s="142">
-        <f>J59+J60</f>
-        <v/>
-      </c>
-      <c r="K63" s="142">
-        <f>K59+K60</f>
-        <v/>
-      </c>
-      <c r="L63" s="142">
-        <f>L59+L60</f>
-        <v/>
-      </c>
-      <c r="M63" s="142">
-        <f>M59+M60</f>
-        <v/>
-      </c>
-      <c r="N63" s="141" t="n"/>
-      <c r="O63" s="141" t="n"/>
-      <c r="P63" s="141" t="n"/>
-      <c r="Q63" s="142" t="n"/>
-      <c r="R63" s="140" t="n"/>
-      <c r="S63" s="142">
-        <f>S59+S60</f>
-        <v/>
-      </c>
-      <c r="T63" s="142">
-        <f>T59+T60</f>
-        <v/>
-      </c>
-      <c r="U63" s="141" t="n"/>
-      <c r="V63" s="141" t="n"/>
-      <c r="W63" s="142">
-        <f>W59+W60</f>
-        <v/>
-      </c>
-      <c r="X63" s="147" t="n"/>
-      <c r="Y63" s="142">
-        <f>Y59+Y60</f>
-        <v/>
-      </c>
-      <c r="Z63" s="142">
-        <f>Z59+Z60</f>
-        <v/>
-      </c>
-      <c r="AA63" s="142">
-        <f>AA59+AA60</f>
-        <v/>
-      </c>
-      <c r="AB63" s="147" t="n"/>
-      <c r="AC63" s="141" t="n"/>
-      <c r="AD63" s="141" t="n"/>
-      <c r="AE63" s="141" t="n"/>
-      <c r="AF63" s="141" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="154" t="inlineStr">
-        <is>
-          <t>총 합계</t>
         </is>
       </c>
       <c r="B64" s="148" t="n"/>
@@ -8988,166 +9218,277 @@
       <c r="E64" s="148" t="n"/>
       <c r="F64" s="148" t="n"/>
       <c r="G64" s="149" t="n"/>
-      <c r="H64" s="146">
-        <f>SUBTOTAL(9,H5:H60)</f>
-        <v/>
-      </c>
-      <c r="I64" s="145" t="n"/>
-      <c r="J64" s="146">
-        <f>SUBTOTAL(9,J5:J60)</f>
-        <v/>
-      </c>
-      <c r="K64" s="146">
-        <f>SUBTOTAL(9,K5:K60)</f>
-        <v/>
-      </c>
-      <c r="L64" s="146">
-        <f>SUBTOTAL(9,L5:L60)</f>
-        <v/>
-      </c>
-      <c r="M64" s="146">
-        <f>SUBTOTAL(9,M5:M60)</f>
-        <v/>
-      </c>
-      <c r="N64" s="145" t="n"/>
-      <c r="O64" s="145" t="n"/>
-      <c r="P64" s="145" t="n"/>
-      <c r="Q64" s="146" t="n"/>
-      <c r="R64" s="144" t="n"/>
-      <c r="S64" s="146">
-        <f>SUBTOTAL(9,S5:S60)</f>
-        <v/>
-      </c>
-      <c r="T64" s="146">
-        <f>SUBTOTAL(9,T5:T60)</f>
-        <v/>
-      </c>
-      <c r="U64" s="145" t="n"/>
-      <c r="V64" s="145" t="n"/>
-      <c r="W64" s="146">
-        <f>SUBTOTAL(9,W5:W60)</f>
-        <v/>
-      </c>
-      <c r="X64" s="154" t="n"/>
-      <c r="Y64" s="146">
-        <f>SUBTOTAL(9,Y5:Y60)</f>
-        <v/>
-      </c>
-      <c r="Z64" s="146">
-        <f>SUBTOTAL(9,Z5:Z60)</f>
-        <v/>
-      </c>
-      <c r="AA64" s="146">
-        <f>SUBTOTAL(9,AA5:AA60)</f>
-        <v/>
-      </c>
-      <c r="AB64" s="154" t="n"/>
-      <c r="AC64" s="145" t="n"/>
-      <c r="AD64" s="145" t="n"/>
-      <c r="AE64" s="145" t="n"/>
-      <c r="AF64" s="145" t="n"/>
+      <c r="H64" s="142">
+        <f>SUBTOTAL(9,H5:H38)</f>
+        <v/>
+      </c>
+      <c r="I64" s="141" t="n"/>
+      <c r="J64" s="142">
+        <f>SUBTOTAL(9,J5:J38)</f>
+        <v/>
+      </c>
+      <c r="K64" s="142">
+        <f>SUBTOTAL(9,K5:K38)</f>
+        <v/>
+      </c>
+      <c r="L64" s="142">
+        <f>SUBTOTAL(9,L5:L38)</f>
+        <v/>
+      </c>
+      <c r="M64" s="142">
+        <f>SUBTOTAL(9,M5:M38)</f>
+        <v/>
+      </c>
+      <c r="N64" s="141" t="n"/>
+      <c r="O64" s="141" t="n"/>
+      <c r="P64" s="141" t="n"/>
+      <c r="Q64" s="142" t="n"/>
+      <c r="R64" s="140" t="n"/>
+      <c r="S64" s="142">
+        <f>SUBTOTAL(9,S5:S38)</f>
+        <v/>
+      </c>
+      <c r="T64" s="142">
+        <f>SUBTOTAL(9,T5:T38)</f>
+        <v/>
+      </c>
+      <c r="U64" s="141" t="n"/>
+      <c r="V64" s="141" t="n"/>
+      <c r="W64" s="142">
+        <f>SUBTOTAL(9,W5:W38)</f>
+        <v/>
+      </c>
+      <c r="X64" s="147" t="n"/>
+      <c r="Y64" s="142">
+        <f>SUBTOTAL(9,Y5:Y38)</f>
+        <v/>
+      </c>
+      <c r="Z64" s="142">
+        <f>SUBTOTAL(9,Z5:Z38)</f>
+        <v/>
+      </c>
+      <c r="AA64" s="142">
+        <f>SUBTOTAL(9,AA5:AA38)</f>
+        <v/>
+      </c>
+      <c r="AB64" s="147" t="n"/>
+      <c r="AC64" s="141" t="n"/>
+      <c r="AD64" s="141" t="n"/>
+      <c r="AE64" s="141" t="n"/>
+      <c r="AF64" s="141" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="39" t="n"/>
-      <c r="B65" s="39" t="n"/>
-      <c r="C65" s="39" t="n"/>
-      <c r="D65" s="39" t="n"/>
-      <c r="E65" s="39" t="n"/>
-      <c r="F65" s="39" t="n"/>
-      <c r="G65" s="39" t="n"/>
-      <c r="H65" s="39" t="n"/>
-      <c r="I65" s="39" t="n"/>
-      <c r="J65" s="39" t="n"/>
-      <c r="K65" s="39" t="n"/>
-      <c r="L65" s="39" t="n"/>
-      <c r="M65" s="39" t="n"/>
-      <c r="N65" s="39" t="n"/>
-      <c r="O65" s="39" t="n"/>
-      <c r="P65" s="39" t="n"/>
-      <c r="Q65" s="39" t="n"/>
-      <c r="R65" s="39" t="n"/>
-      <c r="S65" s="39" t="n"/>
-      <c r="T65" s="39" t="n"/>
-      <c r="U65" s="39" t="n"/>
-      <c r="V65" s="39" t="n"/>
-      <c r="W65" s="39" t="n"/>
-      <c r="X65" s="75" t="n"/>
-      <c r="Y65" s="39" t="n"/>
-      <c r="Z65" s="39" t="n"/>
-      <c r="AA65" s="39" t="n"/>
-      <c r="AB65" s="75" t="n"/>
-      <c r="AC65" s="39" t="n"/>
-      <c r="AD65" s="39" t="n"/>
-      <c r="AE65" s="39" t="n"/>
-      <c r="AF65" s="39" t="n"/>
+      <c r="A65" s="147" t="inlineStr">
+        <is>
+          <t>라이센스/워런티 합계</t>
+        </is>
+      </c>
+      <c r="B65" s="148" t="n"/>
+      <c r="C65" s="148" t="n"/>
+      <c r="D65" s="148" t="n"/>
+      <c r="E65" s="148" t="n"/>
+      <c r="F65" s="148" t="n"/>
+      <c r="G65" s="149" t="n"/>
+      <c r="H65" s="142">
+        <f>SUBTOTAL(9,H39:H60)</f>
+        <v/>
+      </c>
+      <c r="I65" s="141" t="n"/>
+      <c r="J65" s="142">
+        <f>SUBTOTAL(9,J39:J60)</f>
+        <v/>
+      </c>
+      <c r="K65" s="142">
+        <f>SUBTOTAL(9,K39:K60)</f>
+        <v/>
+      </c>
+      <c r="L65" s="142">
+        <f>SUBTOTAL(9,L39:L60)</f>
+        <v/>
+      </c>
+      <c r="M65" s="142">
+        <f>SUBTOTAL(9,M39:M60)</f>
+        <v/>
+      </c>
+      <c r="N65" s="141" t="n"/>
+      <c r="O65" s="141" t="n"/>
+      <c r="P65" s="141" t="n"/>
+      <c r="Q65" s="142" t="n"/>
+      <c r="R65" s="140" t="n"/>
+      <c r="S65" s="142">
+        <f>SUBTOTAL(9,S39:S60)</f>
+        <v/>
+      </c>
+      <c r="T65" s="142">
+        <f>SUBTOTAL(9,T39:T60)</f>
+        <v/>
+      </c>
+      <c r="U65" s="141" t="n"/>
+      <c r="V65" s="141" t="n"/>
+      <c r="W65" s="142">
+        <f>SUBTOTAL(9,W39:W60)</f>
+        <v/>
+      </c>
+      <c r="X65" s="147" t="n"/>
+      <c r="Y65" s="142">
+        <f>SUBTOTAL(9,Y39:Y60)</f>
+        <v/>
+      </c>
+      <c r="Z65" s="142">
+        <f>SUBTOTAL(9,Z39:Z60)</f>
+        <v/>
+      </c>
+      <c r="AA65" s="142">
+        <f>SUBTOTAL(9,AA39:AA60)</f>
+        <v/>
+      </c>
+      <c r="AB65" s="147" t="n"/>
+      <c r="AC65" s="141" t="n"/>
+      <c r="AD65" s="141" t="n"/>
+      <c r="AE65" s="141" t="n"/>
+      <c r="AF65" s="141" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="39" t="n"/>
-      <c r="B66" s="39" t="n"/>
-      <c r="C66" s="39" t="n"/>
-      <c r="D66" s="39" t="n"/>
-      <c r="E66" s="39" t="n"/>
-      <c r="F66" s="39" t="n"/>
-      <c r="G66" s="39" t="n"/>
-      <c r="H66" s="39" t="n"/>
-      <c r="I66" s="39" t="n"/>
-      <c r="J66" s="39" t="n"/>
-      <c r="K66" s="39" t="n"/>
-      <c r="L66" s="39" t="n"/>
-      <c r="M66" s="39" t="n"/>
-      <c r="N66" s="39" t="n"/>
-      <c r="O66" s="39" t="n"/>
-      <c r="P66" s="39" t="n"/>
-      <c r="Q66" s="39" t="n"/>
-      <c r="R66" s="39" t="n"/>
-      <c r="S66" s="39" t="n"/>
-      <c r="T66" s="39" t="n"/>
-      <c r="U66" s="39" t="n"/>
-      <c r="V66" s="39" t="n"/>
-      <c r="W66" s="39" t="n"/>
-      <c r="X66" s="75" t="n"/>
-      <c r="Y66" s="39" t="n"/>
-      <c r="Z66" s="39" t="n"/>
-      <c r="AA66" s="39" t="n"/>
-      <c r="AB66" s="75" t="n"/>
-      <c r="AC66" s="39" t="n"/>
-      <c r="AD66" s="39" t="n"/>
-      <c r="AE66" s="39" t="n"/>
-      <c r="AF66" s="39" t="n"/>
+      <c r="A66" s="147" t="inlineStr">
+        <is>
+          <t>기타 합계</t>
+        </is>
+      </c>
+      <c r="B66" s="148" t="n"/>
+      <c r="C66" s="148" t="n"/>
+      <c r="D66" s="148" t="n"/>
+      <c r="E66" s="148" t="n"/>
+      <c r="F66" s="148" t="n"/>
+      <c r="G66" s="149" t="n"/>
+      <c r="H66" s="142">
+        <f>SUBTOTAL(9,H61:H63)</f>
+        <v/>
+      </c>
+      <c r="I66" s="141" t="n"/>
+      <c r="J66" s="142">
+        <f>SUBTOTAL(9,J61:J63)</f>
+        <v/>
+      </c>
+      <c r="K66" s="142">
+        <f>SUBTOTAL(9,K61:K63)</f>
+        <v/>
+      </c>
+      <c r="L66" s="142">
+        <f>SUBTOTAL(9,L61:L63)</f>
+        <v/>
+      </c>
+      <c r="M66" s="142">
+        <f>SUBTOTAL(9,M61:M63)</f>
+        <v/>
+      </c>
+      <c r="N66" s="141" t="n"/>
+      <c r="O66" s="141" t="n"/>
+      <c r="P66" s="141" t="n"/>
+      <c r="Q66" s="142" t="n"/>
+      <c r="R66" s="140" t="n"/>
+      <c r="S66" s="142">
+        <f>SUBTOTAL(9,S61:S63)</f>
+        <v/>
+      </c>
+      <c r="T66" s="142">
+        <f>SUBTOTAL(9,T61:T63)</f>
+        <v/>
+      </c>
+      <c r="U66" s="141" t="n"/>
+      <c r="V66" s="141" t="n"/>
+      <c r="W66" s="142">
+        <f>SUBTOTAL(9,W61:W63)</f>
+        <v/>
+      </c>
+      <c r="X66" s="147" t="n"/>
+      <c r="Y66" s="142">
+        <f>SUBTOTAL(9,Y61:Y63)</f>
+        <v/>
+      </c>
+      <c r="Z66" s="142">
+        <f>SUBTOTAL(9,Z61:Z63)</f>
+        <v/>
+      </c>
+      <c r="AA66" s="142">
+        <f>SUBTOTAL(9,AA61:AA63)</f>
+        <v/>
+      </c>
+      <c r="AB66" s="147" t="n"/>
+      <c r="AC66" s="141" t="n"/>
+      <c r="AD66" s="141" t="n"/>
+      <c r="AE66" s="141" t="n"/>
+      <c r="AF66" s="141" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="39" t="n"/>
-      <c r="B67" s="39" t="n"/>
-      <c r="C67" s="39" t="n"/>
-      <c r="D67" s="39" t="n"/>
-      <c r="E67" s="39" t="n"/>
-      <c r="F67" s="39" t="n"/>
-      <c r="G67" s="39" t="n"/>
-      <c r="H67" s="39" t="n"/>
-      <c r="I67" s="39" t="n"/>
-      <c r="J67" s="39" t="n"/>
-      <c r="K67" s="39" t="n"/>
-      <c r="L67" s="39" t="n"/>
-      <c r="M67" s="39" t="n"/>
-      <c r="N67" s="39" t="n"/>
-      <c r="O67" s="39" t="n"/>
-      <c r="P67" s="39" t="n"/>
-      <c r="Q67" s="39" t="n"/>
-      <c r="R67" s="39" t="n"/>
-      <c r="S67" s="39" t="n"/>
-      <c r="T67" s="39" t="n"/>
-      <c r="U67" s="39" t="n"/>
-      <c r="V67" s="39" t="n"/>
-      <c r="W67" s="39" t="n"/>
-      <c r="X67" s="75" t="n"/>
-      <c r="Y67" s="39" t="n"/>
-      <c r="Z67" s="39" t="n"/>
-      <c r="AA67" s="39" t="n"/>
-      <c r="AB67" s="75" t="n"/>
-      <c r="AC67" s="39" t="n"/>
-      <c r="AD67" s="39" t="n"/>
-      <c r="AE67" s="39" t="n"/>
-      <c r="AF67" s="39" t="n"/>
+      <c r="A67" s="154" t="inlineStr">
+        <is>
+          <t>총 합계</t>
+        </is>
+      </c>
+      <c r="B67" s="148" t="n"/>
+      <c r="C67" s="148" t="n"/>
+      <c r="D67" s="148" t="n"/>
+      <c r="E67" s="148" t="n"/>
+      <c r="F67" s="148" t="n"/>
+      <c r="G67" s="149" t="n"/>
+      <c r="H67" s="146">
+        <f>SUBTOTAL(9,H5:H63)</f>
+        <v/>
+      </c>
+      <c r="I67" s="145" t="n"/>
+      <c r="J67" s="146">
+        <f>SUBTOTAL(9,J5:J63)</f>
+        <v/>
+      </c>
+      <c r="K67" s="146">
+        <f>SUBTOTAL(9,K5:K63)</f>
+        <v/>
+      </c>
+      <c r="L67" s="146">
+        <f>SUBTOTAL(9,L5:L63)</f>
+        <v/>
+      </c>
+      <c r="M67" s="146">
+        <f>SUBTOTAL(9,M5:M63)</f>
+        <v/>
+      </c>
+      <c r="N67" s="145" t="n"/>
+      <c r="O67" s="145" t="n"/>
+      <c r="P67" s="145" t="n"/>
+      <c r="Q67" s="146" t="n"/>
+      <c r="R67" s="144" t="n"/>
+      <c r="S67" s="146">
+        <f>SUBTOTAL(9,S5:S63)</f>
+        <v/>
+      </c>
+      <c r="T67" s="146">
+        <f>SUBTOTAL(9,T5:T63)</f>
+        <v/>
+      </c>
+      <c r="U67" s="145" t="n"/>
+      <c r="V67" s="145" t="n"/>
+      <c r="W67" s="146">
+        <f>SUBTOTAL(9,W5:W63)</f>
+        <v/>
+      </c>
+      <c r="X67" s="154" t="n"/>
+      <c r="Y67" s="146">
+        <f>SUBTOTAL(9,Y5:Y63)</f>
+        <v/>
+      </c>
+      <c r="Z67" s="146">
+        <f>SUBTOTAL(9,Z5:Z63)</f>
+        <v/>
+      </c>
+      <c r="AA67" s="146">
+        <f>SUBTOTAL(9,AA5:AA63)</f>
+        <v/>
+      </c>
+      <c r="AB67" s="154" t="n"/>
+      <c r="AC67" s="145" t="n"/>
+      <c r="AD67" s="145" t="n"/>
+      <c r="AE67" s="145" t="n"/>
+      <c r="AF67" s="145" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="39" t="n"/>
@@ -9217,21 +9558,136 @@
       <c r="AE69" s="39" t="n"/>
       <c r="AF69" s="39" t="n"/>
     </row>
-    <row r="83">
-      <c r="M83" s="40" t="n"/>
+    <row r="70">
+      <c r="A70" s="39" t="n"/>
+      <c r="B70" s="39" t="n"/>
+      <c r="C70" s="39" t="n"/>
+      <c r="D70" s="39" t="n"/>
+      <c r="E70" s="39" t="n"/>
+      <c r="F70" s="39" t="n"/>
+      <c r="G70" s="39" t="n"/>
+      <c r="H70" s="39" t="n"/>
+      <c r="I70" s="39" t="n"/>
+      <c r="J70" s="39" t="n"/>
+      <c r="K70" s="39" t="n"/>
+      <c r="L70" s="39" t="n"/>
+      <c r="M70" s="39" t="n"/>
+      <c r="N70" s="39" t="n"/>
+      <c r="O70" s="39" t="n"/>
+      <c r="P70" s="39" t="n"/>
+      <c r="Q70" s="39" t="n"/>
+      <c r="R70" s="39" t="n"/>
+      <c r="S70" s="39" t="n"/>
+      <c r="T70" s="39" t="n"/>
+      <c r="U70" s="39" t="n"/>
+      <c r="V70" s="39" t="n"/>
+      <c r="W70" s="39" t="n"/>
+      <c r="X70" s="75" t="n"/>
+      <c r="Y70" s="39" t="n"/>
+      <c r="Z70" s="39" t="n"/>
+      <c r="AA70" s="39" t="n"/>
+      <c r="AB70" s="75" t="n"/>
+      <c r="AC70" s="39" t="n"/>
+      <c r="AD70" s="39" t="n"/>
+      <c r="AE70" s="39" t="n"/>
+      <c r="AF70" s="39" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="39" t="n"/>
+      <c r="B71" s="39" t="n"/>
+      <c r="C71" s="39" t="n"/>
+      <c r="D71" s="39" t="n"/>
+      <c r="E71" s="39" t="n"/>
+      <c r="F71" s="39" t="n"/>
+      <c r="G71" s="39" t="n"/>
+      <c r="H71" s="39" t="n"/>
+      <c r="I71" s="39" t="n"/>
+      <c r="J71" s="39" t="n"/>
+      <c r="K71" s="39" t="n"/>
+      <c r="L71" s="39" t="n"/>
+      <c r="M71" s="39" t="n"/>
+      <c r="N71" s="39" t="n"/>
+      <c r="O71" s="39" t="n"/>
+      <c r="P71" s="39" t="n"/>
+      <c r="Q71" s="39" t="n"/>
+      <c r="R71" s="39" t="n"/>
+      <c r="S71" s="39" t="n"/>
+      <c r="T71" s="39" t="n"/>
+      <c r="U71" s="39" t="n"/>
+      <c r="V71" s="39" t="n"/>
+      <c r="W71" s="39" t="n"/>
+      <c r="X71" s="75" t="n"/>
+      <c r="Y71" s="39" t="n"/>
+      <c r="Z71" s="39" t="n"/>
+      <c r="AA71" s="39" t="n"/>
+      <c r="AB71" s="75" t="n"/>
+      <c r="AC71" s="39" t="n"/>
+      <c r="AD71" s="39" t="n"/>
+      <c r="AE71" s="39" t="n"/>
+      <c r="AF71" s="39" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="39" t="n"/>
+      <c r="B72" s="39" t="n"/>
+      <c r="C72" s="39" t="n"/>
+      <c r="D72" s="39" t="n"/>
+      <c r="E72" s="39" t="n"/>
+      <c r="F72" s="39" t="n"/>
+      <c r="G72" s="39" t="n"/>
+      <c r="H72" s="39" t="n"/>
+      <c r="I72" s="39" t="n"/>
+      <c r="J72" s="39" t="n"/>
+      <c r="K72" s="39" t="n"/>
+      <c r="L72" s="39" t="n"/>
+      <c r="M72" s="39" t="n"/>
+      <c r="N72" s="39" t="n"/>
+      <c r="O72" s="39" t="n"/>
+      <c r="P72" s="39" t="n"/>
+      <c r="Q72" s="39" t="n"/>
+      <c r="R72" s="39" t="n"/>
+      <c r="S72" s="39" t="n"/>
+      <c r="T72" s="39" t="n"/>
+      <c r="U72" s="39" t="n"/>
+      <c r="V72" s="39" t="n"/>
+      <c r="W72" s="39" t="n"/>
+      <c r="X72" s="75" t="n"/>
+      <c r="Y72" s="39" t="n"/>
+      <c r="Z72" s="39" t="n"/>
+      <c r="AA72" s="39" t="n"/>
+      <c r="AB72" s="75" t="n"/>
+      <c r="AC72" s="39" t="n"/>
+      <c r="AD72" s="39" t="n"/>
+      <c r="AE72" s="39" t="n"/>
+      <c r="AF72" s="39" t="n"/>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86">
+      <c r="M86" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A66:G66"/>
     <mergeCell ref="G3:N3"/>
+    <mergeCell ref="A67:G67"/>
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A62:G62"/>
     <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="X3:Z3"/>
     <mergeCell ref="A64:G64"/>
-    <mergeCell ref="X3:Z3"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A65:G65"/>
     <mergeCell ref="O3:W3"/>
     <mergeCell ref="A2:AF2"/>
   </mergeCells>
@@ -10254,6 +10710,157 @@
       <c r="L21" s="115" t="n"/>
       <c r="M21" s="115" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" s="224" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="224" t="inlineStr">
+        <is>
+          <t>GPO478</t>
+        </is>
+      </c>
+      <c r="C22" s="225" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D22" s="225" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="E22" s="226" t="n">
+        <v>180</v>
+      </c>
+      <c r="F22" s="224" t="inlineStr">
+        <is>
+          <t>TMS-1000 License (NOWON THE FOREST 2 screens)</t>
+        </is>
+      </c>
+      <c r="G22" s="227" t="n">
+        <v>46127</v>
+      </c>
+      <c r="H22" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="227" t="n">
+        <v>46143</v>
+      </c>
+      <c r="J22" s="227" t="n">
+        <v>46507</v>
+      </c>
+      <c r="K22" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="L22" s="228" t="n"/>
+      <c r="M22" s="228" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="224" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="224" t="inlineStr">
+        <is>
+          <t>GPO480</t>
+        </is>
+      </c>
+      <c r="C23" s="225" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D23" s="225" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="E23" s="226" t="n">
+        <v>250</v>
+      </c>
+      <c r="F23" s="224" t="inlineStr">
+        <is>
+          <t>GDC SX-3000 PEM Cert Extension (Megabox Hwamyeong, 10y)</t>
+        </is>
+      </c>
+      <c r="G23" s="227" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H23" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="227" t="n">
+        <v>46143</v>
+      </c>
+      <c r="J23" s="227" t="n">
+        <v>49795</v>
+      </c>
+      <c r="K23" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="L23" s="228" t="n"/>
+      <c r="M23" s="228" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="224" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="224" t="inlineStr">
+        <is>
+          <t>GPO481</t>
+        </is>
+      </c>
+      <c r="C24" s="225" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D24" s="225" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="E24" s="226" t="n">
+        <v>500</v>
+      </c>
+      <c r="F24" s="224" t="inlineStr">
+        <is>
+          <t>Dolby Atmos Playback License (Megabox Mangyeong)</t>
+        </is>
+      </c>
+      <c r="G24" s="227" t="n">
+        <v>46152</v>
+      </c>
+      <c r="H24" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="227" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="J24" s="227" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="K24" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="L24" s="228" t="n"/>
+      <c r="M24" s="228" t="n"/>
+    </row>
     <row r="70">
       <c r="M70" s="40" t="n"/>
     </row>
@@ -11397,46 +12004,134 @@
       <c r="M26" s="115" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="115" t="n"/>
-      <c r="B27" s="115" t="n"/>
-      <c r="C27" s="115" t="n"/>
-      <c r="D27" s="115" t="n"/>
-      <c r="E27" s="115" t="n"/>
-      <c r="F27" s="115" t="n"/>
-      <c r="G27" s="115" t="n"/>
-      <c r="H27" s="115" t="n"/>
-      <c r="I27" s="115" t="n"/>
-      <c r="J27" s="115" t="n"/>
+      <c r="A27" s="229" t="inlineStr">
+        <is>
+          <t>14008-26-101147M</t>
+        </is>
+      </c>
+      <c r="B27" s="229" t="inlineStr">
+        <is>
+          <t>FRC-MONOPLEX26</t>
+        </is>
+      </c>
+      <c r="C27" s="230" t="n">
+        <v>51952</v>
+      </c>
+      <c r="D27" s="231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="229" t="inlineStr">
+        <is>
+          <t>조운관세사</t>
+        </is>
+      </c>
+      <c r="F27" s="232" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G27" s="229" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="H27" s="232" t="n">
+        <v>5002612</v>
+      </c>
+      <c r="I27" s="229" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J27" s="229" t="n"/>
       <c r="K27" s="115" t="n"/>
       <c r="L27" s="115" t="n"/>
       <c r="M27" s="115" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="115" t="n"/>
-      <c r="B28" s="115" t="n"/>
-      <c r="C28" s="115" t="n"/>
-      <c r="D28" s="115" t="n"/>
-      <c r="E28" s="115" t="n"/>
-      <c r="F28" s="115" t="n"/>
-      <c r="G28" s="115" t="n"/>
-      <c r="H28" s="115" t="n"/>
-      <c r="I28" s="115" t="n"/>
-      <c r="J28" s="115" t="n"/>
+      <c r="A28" s="229" t="inlineStr">
+        <is>
+          <t>14008-26-101170M</t>
+        </is>
+      </c>
+      <c r="B28" s="229" t="inlineStr">
+        <is>
+          <t>GPO473-2</t>
+        </is>
+      </c>
+      <c r="C28" s="230" t="n">
+        <v>69160</v>
+      </c>
+      <c r="D28" s="231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="229" t="inlineStr">
+        <is>
+          <t>조운관세사</t>
+        </is>
+      </c>
+      <c r="F28" s="232" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G28" s="229" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="H28" s="232" t="n">
+        <v>3759954</v>
+      </c>
+      <c r="I28" s="229" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J28" s="229" t="inlineStr">
+        <is>
+          <t>통관 USD 98,800 (FOC loan 6 SET 포함)</t>
+        </is>
+      </c>
       <c r="K28" s="115" t="n"/>
       <c r="L28" s="115" t="n"/>
       <c r="M28" s="115" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="115" t="n"/>
-      <c r="B29" s="115" t="n"/>
-      <c r="C29" s="115" t="n"/>
-      <c r="D29" s="115" t="n"/>
-      <c r="E29" s="115" t="n"/>
-      <c r="F29" s="115" t="n"/>
-      <c r="G29" s="115" t="n"/>
-      <c r="H29" s="115" t="n"/>
-      <c r="I29" s="115" t="n"/>
-      <c r="J29" s="115" t="n"/>
+      <c r="A29" s="229" t="inlineStr">
+        <is>
+          <t>14008-26-101191M</t>
+        </is>
+      </c>
+      <c r="B29" s="229" t="inlineStr">
+        <is>
+          <t>GPO473-3</t>
+        </is>
+      </c>
+      <c r="C29" s="230" t="n">
+        <v>49400</v>
+      </c>
+      <c r="D29" s="231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="229" t="inlineStr">
+        <is>
+          <t>조운관세사</t>
+        </is>
+      </c>
+      <c r="F29" s="232" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G29" s="229" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="H29" s="232" t="n">
+        <v>2259958</v>
+      </c>
+      <c r="I29" s="229" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J29" s="229" t="n"/>
       <c r="K29" s="115" t="n"/>
       <c r="L29" s="115" t="n"/>
       <c r="M29" s="115" t="n"/>
@@ -17127,7 +17822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -17170,7 +17865,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="205" t="inlineStr">
         <is>
-          <t>업데이트: 2026-05-19 (관세청 고시환율)</t>
+          <t>업데이트: 2026-05-28 (관세청 고시환율)</t>
         </is>
       </c>
       <c r="B4" s="148" t="n"/>
@@ -17726,6 +18421,22 @@
       </c>
       <c r="D39" s="7" t="n">
         <v>1482.04</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="210" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B40" s="210" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C40" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D40" s="211" t="n">
+        <v>1504.04</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="RemitTable1">외화송금내역!$A$3:$L$34</definedName>
-    <definedName name="RemitTable2">외화송금내역!$A$37:$L$74</definedName>
-    <definedName name="FxRateTable">환율!$A$7:$D$40</definedName>
+    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$39</definedName>
+    <definedName name="RemitTable2">'외화송금내역'!$A$42:$L$87</definedName>
+    <definedName name="FxRateTable">'환율'!$A$7:$D$41</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1546,7 +1546,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-05-28  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-06-02  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="148" t="n"/>
@@ -6083,22 +6083,22 @@
         <v>5673</v>
       </c>
       <c r="I39" s="185">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J39" s="26" t="n">
         <v>205028994</v>
       </c>
       <c r="K39" s="26">
-        <f>IFERROR(ROUND(H30*I30,0),0)</f>
+        <f>IFERROR(ROUND(H39*I39,0),0)</f>
         <v/>
       </c>
       <c r="L39" s="26">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B39,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M39" s="26">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B39,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N39" s="20" t="inlineStr">
@@ -6117,11 +6117,11 @@
         </is>
       </c>
       <c r="Q39" s="24">
-        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R39" s="26">
-        <f>IF(P30="","",H30)</f>
+        <f>IF(P39="","",H39)</f>
         <v/>
       </c>
       <c r="S39" s="26" t="n">
@@ -6150,18 +6150,18 @@
         <v>0</v>
       </c>
       <c r="Z39" s="26">
-        <f>S30+T30+W30</f>
+        <f>S39+T39+W39</f>
         <v/>
       </c>
       <c r="AA39" s="26">
-        <f>K30+L30+M30+IFERROR(VLOOKUP(B30,RemitTable2,9,FALSE()),0)+Y30+Z30</f>
+        <f>K39+L39+M39+IFERROR(VLOOKUP(B39,RemitTable2,9,FALSE),0)+Y39+Z39</f>
         <v/>
       </c>
       <c r="AB39" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC39" s="26">
-        <f>ROUND(AA30/AB30,0)</f>
+        <f>ROUND(AA39/AB39,0)</f>
         <v/>
       </c>
       <c r="AD39" s="20" t="inlineStr">
@@ -6214,22 +6214,22 @@
         <v>350</v>
       </c>
       <c r="I40" s="185">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J40" s="26" t="n">
         <v>18264679</v>
       </c>
       <c r="K40" s="26">
-        <f>IFERROR(ROUND(H31*I31,0),0)</f>
+        <f>IFERROR(ROUND(H40*I40,0),0)</f>
         <v/>
       </c>
       <c r="L40" s="26">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M40" s="26">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N40" s="20" t="inlineStr">
@@ -6248,11 +6248,11 @@
         </is>
       </c>
       <c r="Q40" s="24">
-        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R40" s="26">
-        <f>IF(P31="","",H31)</f>
+        <f>IF(P40="","",H40)</f>
         <v/>
       </c>
       <c r="S40" s="26" t="n">
@@ -6281,18 +6281,18 @@
         <v>0</v>
       </c>
       <c r="Z40" s="26">
-        <f>S31+T31+W31</f>
+        <f>S40+T40+W40</f>
         <v/>
       </c>
       <c r="AA40" s="26">
-        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
+        <f>K40+L40+M40+IFERROR(VLOOKUP(B40,RemitTable2,9,FALSE),0)+Y40+Z40</f>
         <v/>
       </c>
       <c r="AB40" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC40" s="26">
-        <f>ROUND(AA31/AB31,0)</f>
+        <f>ROUND(AA40/AB40,0)</f>
         <v/>
       </c>
       <c r="AD40" s="20" t="inlineStr">
@@ -6345,22 +6345,22 @@
         <v>26358</v>
       </c>
       <c r="I41" s="185">
-        <f>IFERROR(VLOOKUP(B32,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J41" s="26" t="n">
         <v>38550844</v>
       </c>
       <c r="K41" s="26">
-        <f>IFERROR(ROUND(H32*I32,0),0)</f>
+        <f>IFERROR(ROUND(H41*I41,0),0)</f>
         <v/>
       </c>
       <c r="L41" s="26">
-        <f>IFERROR(VLOOKUP(B32,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B41,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M41" s="26">
-        <f>IFERROR(VLOOKUP(B32,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B41,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N41" s="20" t="inlineStr">
@@ -6379,11 +6379,11 @@
         </is>
       </c>
       <c r="Q41" s="24">
-        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R41" s="26">
-        <f>IF(P32="","",H32)</f>
+        <f>IF(P41="","",H41)</f>
         <v/>
       </c>
       <c r="S41" s="26" t="n">
@@ -6412,18 +6412,18 @@
         <v>0</v>
       </c>
       <c r="Z41" s="26">
-        <f>S32+T32+W32</f>
+        <f>S41+T41+W41</f>
         <v/>
       </c>
       <c r="AA41" s="26">
-        <f>K32+L32+M32+IFERROR(VLOOKUP(B32,RemitTable2,9,FALSE()),0)+Y32+Z32</f>
+        <f>K41+L41+M41+IFERROR(VLOOKUP(B41,RemitTable2,9,FALSE),0)+Y41+Z41</f>
         <v/>
       </c>
       <c r="AB41" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC41" s="26">
-        <f>ROUND(AA32/AB32,0)</f>
+        <f>ROUND(AA41/AB41,0)</f>
         <v/>
       </c>
       <c r="AD41" s="20" t="inlineStr">
@@ -6476,22 +6476,22 @@
         <v>450</v>
       </c>
       <c r="I42" s="185">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J42" s="26" t="n">
         <v>5505104</v>
       </c>
       <c r="K42" s="26">
-        <f>IFERROR(ROUND(H33*I33,0),0)</f>
+        <f>IFERROR(ROUND(H42*I42,0),0)</f>
         <v/>
       </c>
       <c r="L42" s="26">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B42,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M42" s="26">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B42,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N42" s="20" t="inlineStr">
@@ -6510,11 +6510,11 @@
         </is>
       </c>
       <c r="Q42" s="24">
-        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R42" s="26">
-        <f>IF(P33="","",H33)</f>
+        <f>IF(P42="","",H42)</f>
         <v/>
       </c>
       <c r="S42" s="26" t="n">
@@ -6543,18 +6543,18 @@
         <v>0</v>
       </c>
       <c r="Z42" s="26">
-        <f>S33+T33+W33</f>
+        <f>S42+T42+W42</f>
         <v/>
       </c>
       <c r="AA42" s="26">
-        <f>K33+L33+M33+IFERROR(VLOOKUP(B33,RemitTable2,9,FALSE()),0)+Y33+Z33</f>
+        <f>K42+L42+M42+IFERROR(VLOOKUP(B42,RemitTable2,9,FALSE),0)+Y42+Z42</f>
         <v/>
       </c>
       <c r="AB42" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC42" s="26">
-        <f>ROUND(AA33/AB33,0)</f>
+        <f>ROUND(AA42/AB42,0)</f>
         <v/>
       </c>
       <c r="AD42" s="20" t="inlineStr">
@@ -6607,22 +6607,22 @@
         <v>540</v>
       </c>
       <c r="I43" s="185">
-        <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J43" s="26" t="n">
         <v>5505104</v>
       </c>
       <c r="K43" s="26">
-        <f>IFERROR(ROUND(H34*I34,0),0)</f>
+        <f>IFERROR(ROUND(H43*I43,0),0)</f>
         <v/>
       </c>
       <c r="L43" s="26">
-        <f>IFERROR(VLOOKUP(B34,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B43,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M43" s="26">
-        <f>IFERROR(VLOOKUP(B34,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B43,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N43" s="20" t="inlineStr">
@@ -6641,11 +6641,11 @@
         </is>
       </c>
       <c r="Q43" s="24">
-        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R43" s="26">
-        <f>IF(P34="","",H34)</f>
+        <f>IF(P43="","",H43)</f>
         <v/>
       </c>
       <c r="S43" s="26" t="n">
@@ -6674,18 +6674,18 @@
         <v>0</v>
       </c>
       <c r="Z43" s="26">
-        <f>S34+T34+W34</f>
+        <f>S43+T43+W43</f>
         <v/>
       </c>
       <c r="AA43" s="26">
-        <f>K34+L34+M34+IFERROR(VLOOKUP(B34,RemitTable2,9,FALSE()),0)+Y34+Z34</f>
+        <f>K43+L43+M43+IFERROR(VLOOKUP(B43,RemitTable2,9,FALSE),0)+Y43+Z43</f>
         <v/>
       </c>
       <c r="AB43" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC43" s="26">
-        <f>ROUND(AA34/AB34,0)</f>
+        <f>ROUND(AA43/AB43,0)</f>
         <v/>
       </c>
       <c r="AD43" s="20" t="inlineStr">
@@ -6738,22 +6738,22 @@
         <v>136516</v>
       </c>
       <c r="I44" s="185">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J44" s="26" t="n">
         <v>205028994</v>
       </c>
       <c r="K44" s="26">
-        <f>IFERROR(ROUND(H35*I35,0),0)</f>
+        <f>IFERROR(ROUND(H44*I44,0),0)</f>
         <v/>
       </c>
       <c r="L44" s="26">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B44,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M44" s="26">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B44,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N44" s="20" t="inlineStr">
@@ -6772,11 +6772,11 @@
         </is>
       </c>
       <c r="Q44" s="24">
-        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R44" s="26">
-        <f>IF(P35="","",H35)</f>
+        <f>IF(P44="","",H44)</f>
         <v/>
       </c>
       <c r="S44" s="26" t="n">
@@ -6805,18 +6805,18 @@
         <v>0</v>
       </c>
       <c r="Z44" s="26">
-        <f>S35+T35+W35</f>
+        <f>S44+T44+W44</f>
         <v/>
       </c>
       <c r="AA44" s="26">
-        <f>K35+L35+M35+IFERROR(VLOOKUP(B35,RemitTable2,9,FALSE()),0)+Y35+Z35</f>
+        <f>K44+L44+M44+IFERROR(VLOOKUP(B44,RemitTable2,9,FALSE),0)+Y44+Z44</f>
         <v/>
       </c>
       <c r="AB44" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC44" s="26">
-        <f>ROUND(AA35/AB35,0)</f>
+        <f>ROUND(AA44/AB44,0)</f>
         <v/>
       </c>
       <c r="AD44" s="20" t="inlineStr">
@@ -6871,22 +6871,22 @@
         <v>76054</v>
       </c>
       <c r="I45" s="185">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J45" s="26" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="26">
-        <f>IFERROR(ROUND(H36*I36,0),0)</f>
+        <f>IFERROR(ROUND(H45*I45,0),0)</f>
         <v/>
       </c>
       <c r="L45" s="26">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M45" s="26">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N45" s="20" t="inlineStr">
@@ -6905,11 +6905,11 @@
         </is>
       </c>
       <c r="Q45" s="24">
-        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R45" s="26">
-        <f>IF(P36="","",H36)</f>
+        <f>IF(P45="","",H45)</f>
         <v/>
       </c>
       <c r="S45" s="26" t="n">
@@ -6938,18 +6938,18 @@
         <v>0</v>
       </c>
       <c r="Z45" s="26">
-        <f>S36+T36+W36</f>
+        <f>S45+T45+W45</f>
         <v/>
       </c>
       <c r="AA45" s="26">
-        <f>K36+L36+M36+IFERROR(VLOOKUP(B36,RemitTable2,9,FALSE()),0)+Y36+Z36</f>
+        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE),0)+Y45+Z45</f>
         <v/>
       </c>
       <c r="AB45" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC45" s="26">
-        <f>ROUND(AA36/AB36,0)</f>
+        <f>ROUND(AA45/AB45,0)</f>
         <v/>
       </c>
       <c r="AD45" s="20" t="inlineStr">
@@ -7002,22 +7002,22 @@
         <v>14793</v>
       </c>
       <c r="I46" s="185">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B46,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J46" s="26" t="n">
         <v>25506948</v>
       </c>
       <c r="K46" s="26">
-        <f>IFERROR(ROUND(H37*I37,0),0)</f>
+        <f>IFERROR(ROUND(H46*I46,0),0)</f>
         <v/>
       </c>
       <c r="L46" s="26">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B46,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M46" s="26">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B46,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N46" s="20" t="inlineStr">
@@ -7036,11 +7036,11 @@
         </is>
       </c>
       <c r="Q46" s="24">
-        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R46" s="26">
-        <f>IF(P37="","",H37)</f>
+        <f>IF(P46="","",H46)</f>
         <v/>
       </c>
       <c r="S46" s="26" t="n">
@@ -7069,18 +7069,18 @@
         <v>0</v>
       </c>
       <c r="Z46" s="26">
-        <f>S37+T37+W37</f>
+        <f>S46+T46+W46</f>
         <v/>
       </c>
       <c r="AA46" s="26">
-        <f>K37+L37+M37+IFERROR(VLOOKUP(B37,RemitTable2,9,FALSE()),0)+Y37+Z37</f>
+        <f>K46+L46+M46+IFERROR(VLOOKUP(B46,RemitTable2,9,FALSE),0)+Y46+Z46</f>
         <v/>
       </c>
       <c r="AB46" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC46" s="26">
-        <f>ROUND(AA37/AB37,0)</f>
+        <f>ROUND(AA46/AB46,0)</f>
         <v/>
       </c>
       <c r="AD46" s="20" t="inlineStr">
@@ -7135,22 +7135,22 @@
         <v>26656</v>
       </c>
       <c r="I47" s="185">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J47" s="26" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="26">
-        <f>IFERROR(ROUND(H38*I38,0),0)</f>
+        <f>IFERROR(ROUND(H47*I47,0),0)</f>
         <v/>
       </c>
       <c r="L47" s="26">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B47,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M47" s="26">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B47,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N47" s="20" t="inlineStr">
@@ -7169,11 +7169,11 @@
         </is>
       </c>
       <c r="Q47" s="24">
-        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R47" s="26">
-        <f>IF(P38="","",H38)</f>
+        <f>IF(P47="","",H47)</f>
         <v/>
       </c>
       <c r="S47" s="26" t="n">
@@ -7202,18 +7202,18 @@
         <v>0</v>
       </c>
       <c r="Z47" s="26">
-        <f>S38+T38+W38</f>
+        <f>S47+T47+W47</f>
         <v/>
       </c>
       <c r="AA47" s="26">
-        <f>K38+L38+M38+IFERROR(VLOOKUP(B38,RemitTable2,9,FALSE()),0)+Y38+Z38</f>
+        <f>K47+L47+M47+IFERROR(VLOOKUP(B47,RemitTable2,9,FALSE),0)+Y47+Z47</f>
         <v/>
       </c>
       <c r="AB47" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC47" s="26">
-        <f>ROUND(AA38/AB38,0)</f>
+        <f>ROUND(AA47/AB47,0)</f>
         <v/>
       </c>
       <c r="AD47" s="20" t="inlineStr">
@@ -7266,22 +7266,22 @@
         <v>1440</v>
       </c>
       <c r="I48" s="185">
-        <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J48" s="26" t="n">
         <v>16908206</v>
       </c>
       <c r="K48" s="26">
-        <f>IFERROR(ROUND(H39*I39,0),0)</f>
+        <f>IFERROR(ROUND(H48*I48,0),0)</f>
         <v/>
       </c>
       <c r="L48" s="26">
-        <f>IFERROR(VLOOKUP(B39,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M48" s="26">
-        <f>IFERROR(VLOOKUP(B39,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N48" s="20" t="inlineStr">
@@ -7300,11 +7300,11 @@
         </is>
       </c>
       <c r="Q48" s="24">
-        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R48" s="26">
-        <f>IF(P39="","",H39)</f>
+        <f>IF(P48="","",H48)</f>
         <v/>
       </c>
       <c r="S48" s="26" t="n">
@@ -7333,18 +7333,18 @@
         <v>0</v>
       </c>
       <c r="Z48" s="26">
-        <f>S39+T39+W39</f>
+        <f>S48+T48+W48</f>
         <v/>
       </c>
       <c r="AA48" s="26">
-        <f>K39+L39+M39+IFERROR(VLOOKUP(B39,RemitTable2,9,FALSE()),0)+Y39+Z39</f>
+        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE),0)+Y48+Z48</f>
         <v/>
       </c>
       <c r="AB48" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC48" s="26">
-        <f>ROUND(AA39/AB39,0)</f>
+        <f>ROUND(AA48/AB48,0)</f>
         <v/>
       </c>
       <c r="AD48" s="20" t="inlineStr">
@@ -7397,22 +7397,22 @@
         <v>4489</v>
       </c>
       <c r="I49" s="185">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J49" s="26" t="n">
         <v>16908206</v>
       </c>
       <c r="K49" s="26">
-        <f>IFERROR(ROUND(H40*I40,0),0)</f>
+        <f>IFERROR(ROUND(H49*I49,0),0)</f>
         <v/>
       </c>
       <c r="L49" s="26">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M49" s="26">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N49" s="20" t="inlineStr">
@@ -7431,11 +7431,11 @@
         </is>
       </c>
       <c r="Q49" s="24">
-        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R49" s="26">
-        <f>IF(P40="","",H40)</f>
+        <f>IF(P49="","",H49)</f>
         <v/>
       </c>
       <c r="S49" s="26" t="n">
@@ -7464,18 +7464,18 @@
         <v>0</v>
       </c>
       <c r="Z49" s="26">
-        <f>S40+T40+W40</f>
+        <f>S49+T49+W49</f>
         <v/>
       </c>
       <c r="AA49" s="26">
-        <f>K40+L40+M40+IFERROR(VLOOKUP(B40,RemitTable2,9,FALSE()),0)+Y40+Z40</f>
+        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE),0)+Y49+Z49</f>
         <v/>
       </c>
       <c r="AB49" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC49" s="26">
-        <f>ROUND(AA40/AB40,0)</f>
+        <f>ROUND(AA49/AB49,0)</f>
         <v/>
       </c>
       <c r="AD49" s="20" t="inlineStr">
@@ -7528,22 +7528,22 @@
         <v>5670.57</v>
       </c>
       <c r="I50" s="185">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J50" s="26" t="n">
         <v>16908206</v>
       </c>
       <c r="K50" s="26">
-        <f>IFERROR(ROUND(H41*I41,0),0)</f>
+        <f>IFERROR(ROUND(H50*I50,0),0)</f>
         <v/>
       </c>
       <c r="L50" s="26">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B50,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M50" s="26">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B50,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N50" s="20" t="inlineStr">
@@ -7562,11 +7562,11 @@
         </is>
       </c>
       <c r="Q50" s="24">
-        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R50" s="26">
-        <f>IF(P41="","",H41)</f>
+        <f>IF(P50="","",H50)</f>
         <v/>
       </c>
       <c r="S50" s="26" t="n">
@@ -7595,18 +7595,18 @@
         <v>0</v>
       </c>
       <c r="Z50" s="26">
-        <f>S41+T41+W41</f>
+        <f>S50+T50+W50</f>
         <v/>
       </c>
       <c r="AA50" s="26">
-        <f>K41+L41+M41+IFERROR(VLOOKUP(B41,RemitTable2,9,FALSE()),0)+Y41+Z41</f>
+        <f>K50+L50+M50+IFERROR(VLOOKUP(B50,RemitTable2,9,FALSE),0)+Y50+Z50</f>
         <v/>
       </c>
       <c r="AB50" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC50" s="26">
-        <f>ROUND(AA41/AB41,0)</f>
+        <f>ROUND(AA50/AB50,0)</f>
         <v/>
       </c>
       <c r="AD50" s="20" t="inlineStr">
@@ -7659,22 +7659,22 @@
         <v>24614</v>
       </c>
       <c r="I51" s="185">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B51,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J51" s="26" t="n">
         <v>51777431</v>
       </c>
       <c r="K51" s="26">
-        <f>IFERROR(ROUND(H42*I42,0),0)</f>
+        <f>IFERROR(ROUND(H51*I51,0),0)</f>
         <v/>
       </c>
       <c r="L51" s="26">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B51,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M51" s="26">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B51,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N51" s="20" t="inlineStr">
@@ -7693,11 +7693,11 @@
         </is>
       </c>
       <c r="Q51" s="24">
-        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R51" s="26">
-        <f>IF(P42="","",H42)</f>
+        <f>IF(P51="","",H51)</f>
         <v/>
       </c>
       <c r="S51" s="26" t="n">
@@ -7726,18 +7726,18 @@
         <v>0</v>
       </c>
       <c r="Z51" s="26">
-        <f>S42+T42+W42</f>
+        <f>S51+T51+W51</f>
         <v/>
       </c>
       <c r="AA51" s="26">
-        <f>K42+L42+M42+IFERROR(VLOOKUP(B42,RemitTable2,9,FALSE()),0)+Y42+Z42</f>
+        <f>K51+L51+M51+IFERROR(VLOOKUP(B51,RemitTable2,9,FALSE),0)+Y51+Z51</f>
         <v/>
       </c>
       <c r="AB51" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC51" s="26">
-        <f>ROUND(AA42/AB42,0)</f>
+        <f>ROUND(AA51/AB51,0)</f>
         <v/>
       </c>
       <c r="AD51" s="20" t="inlineStr">
@@ -7790,22 +7790,22 @@
         <v>3993.05</v>
       </c>
       <c r="I52" s="185">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B52,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J52" s="26" t="n">
         <v>9919642</v>
       </c>
       <c r="K52" s="26">
-        <f>IFERROR(ROUND(H43*I43,0),0)</f>
+        <f>IFERROR(ROUND(H52*I52,0),0)</f>
         <v/>
       </c>
       <c r="L52" s="26">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B52,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M52" s="26">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B52,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N52" s="20" t="inlineStr">
@@ -7824,11 +7824,11 @@
         </is>
       </c>
       <c r="Q52" s="24">
-        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P52="","",IFERROR(VLOOKUP(O52,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R52" s="26">
-        <f>IF(P43="","",H43)</f>
+        <f>IF(P52="","",H52)</f>
         <v/>
       </c>
       <c r="S52" s="26" t="n">
@@ -7857,18 +7857,18 @@
         <v>0</v>
       </c>
       <c r="Z52" s="26">
-        <f>S43+T43+W43</f>
+        <f>S52+T52+W52</f>
         <v/>
       </c>
       <c r="AA52" s="26">
-        <f>K43+L43+M43+IFERROR(VLOOKUP(B43,RemitTable2,9,FALSE()),0)+Y43+Z43</f>
+        <f>K52+L52+M52+IFERROR(VLOOKUP(B52,RemitTable2,9,FALSE),0)+Y52+Z52</f>
         <v/>
       </c>
       <c r="AB52" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC52" s="26">
-        <f>ROUND(AA43/AB43,0)</f>
+        <f>ROUND(AA52/AB52,0)</f>
         <v/>
       </c>
       <c r="AD52" s="20" t="inlineStr">
@@ -7921,22 +7921,22 @@
         <v>360</v>
       </c>
       <c r="I53" s="185">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B53,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J53" s="26" t="n">
         <v>9919642</v>
       </c>
       <c r="K53" s="26">
-        <f>IFERROR(ROUND(H44*I44,0),0)</f>
+        <f>IFERROR(ROUND(H53*I53,0),0)</f>
         <v/>
       </c>
       <c r="L53" s="26">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B53,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M53" s="26">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B53,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N53" s="20" t="inlineStr">
@@ -7955,11 +7955,11 @@
         </is>
       </c>
       <c r="Q53" s="24">
-        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R53" s="26">
-        <f>IF(P44="","",H44)</f>
+        <f>IF(P53="","",H53)</f>
         <v/>
       </c>
       <c r="S53" s="26" t="n">
@@ -7988,18 +7988,18 @@
         <v>0</v>
       </c>
       <c r="Z53" s="26">
-        <f>S44+T44+W44</f>
+        <f>S53+T53+W53</f>
         <v/>
       </c>
       <c r="AA53" s="26">
-        <f>K44+L44+M44+IFERROR(VLOOKUP(B44,RemitTable2,9,FALSE()),0)+Y44+Z44</f>
+        <f>K53+L53+M53+IFERROR(VLOOKUP(B53,RemitTable2,9,FALSE),0)+Y53+Z53</f>
         <v/>
       </c>
       <c r="AB53" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC53" s="26">
-        <f>ROUND(AA44/AB44,0)</f>
+        <f>ROUND(AA53/AB53,0)</f>
         <v/>
       </c>
       <c r="AD53" s="20" t="inlineStr">
@@ -8052,22 +8052,22 @@
         <v>500</v>
       </c>
       <c r="I54" s="185">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B54,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J54" s="26" t="n">
         <v>9919642</v>
       </c>
       <c r="K54" s="26">
-        <f>IFERROR(ROUND(H45*I45,0),0)</f>
+        <f>IFERROR(ROUND(H54*I54,0),0)</f>
         <v/>
       </c>
       <c r="L54" s="26">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B54,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M54" s="26">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B54,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N54" s="20" t="inlineStr">
@@ -8086,11 +8086,11 @@
         </is>
       </c>
       <c r="Q54" s="24">
-        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P54="","",IFERROR(VLOOKUP(O54,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R54" s="26">
-        <f>IF(P45="","",H45)</f>
+        <f>IF(P54="","",H54)</f>
         <v/>
       </c>
       <c r="S54" s="26" t="n">
@@ -8119,18 +8119,18 @@
         <v>0</v>
       </c>
       <c r="Z54" s="26">
-        <f>S45+T45+W45</f>
+        <f>S54+T54+W54</f>
         <v/>
       </c>
       <c r="AA54" s="26">
-        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE()),0)+Y45+Z45</f>
+        <f>K54+L54+M54+IFERROR(VLOOKUP(B54,RemitTable2,9,FALSE),0)+Y54+Z54</f>
         <v/>
       </c>
       <c r="AB54" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC54" s="26">
-        <f>ROUND(AA45/AB45,0)</f>
+        <f>ROUND(AA54/AB54,0)</f>
         <v/>
       </c>
       <c r="AD54" s="20" t="inlineStr">
@@ -8183,22 +8183,22 @@
         <v>17404</v>
       </c>
       <c r="I55" s="185">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B55,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J55" s="26" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="26">
-        <f>IFERROR(ROUND(H49*I49,0),0)</f>
+        <f>IFERROR(ROUND(H55*I55,0),0)</f>
         <v/>
       </c>
       <c r="L55" s="26">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B55,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M55" s="26">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B55,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N55" s="20" t="inlineStr">
@@ -8217,11 +8217,11 @@
         </is>
       </c>
       <c r="Q55" s="24">
-        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P55="","",IFERROR(VLOOKUP(O55,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R55" s="26">
-        <f>IF(P49="","",H49)</f>
+        <f>IF(P55="","",H55)</f>
         <v/>
       </c>
       <c r="S55" s="26" t="n">
@@ -8250,18 +8250,18 @@
         <v>0</v>
       </c>
       <c r="Z55" s="26">
-        <f>S49+T49+W49</f>
+        <f>S55+T55+W55</f>
         <v/>
       </c>
       <c r="AA55" s="26">
-        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE()),0)+Y49+Z49</f>
+        <f>K55+L55+M55+IFERROR(VLOOKUP(B55,RemitTable2,9,FALSE),0)+Y55+Z55</f>
         <v/>
       </c>
       <c r="AB55" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC55" s="26">
-        <f>ROUND(AA49/AB49,0)</f>
+        <f>ROUND(AA55/AB55,0)</f>
         <v/>
       </c>
       <c r="AD55" s="20" t="inlineStr">
@@ -8316,22 +8316,22 @@
         <v>15289</v>
       </c>
       <c r="I56" s="187">
-        <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J56" s="89" t="n">
         <v>0</v>
       </c>
       <c r="K56" s="89">
-        <f>IFERROR(ROUND(H50*I50,0),0)</f>
+        <f>IFERROR(ROUND(H56*I56,0),0)</f>
         <v/>
       </c>
       <c r="L56" s="89">
-        <f>IFERROR(VLOOKUP(B50,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M56" s="89">
-        <f>IFERROR(VLOOKUP(B50,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N56" s="85" t="inlineStr">
@@ -8350,11 +8350,11 @@
         </is>
       </c>
       <c r="Q56" s="87">
-        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P56="","",IFERROR(VLOOKUP(O56,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R56" s="87">
-        <f>IF(P50="","",H50)</f>
+        <f>IF(P56="","",H56)</f>
         <v/>
       </c>
       <c r="S56" s="89" t="n">
@@ -8381,18 +8381,18 @@
         <v>0</v>
       </c>
       <c r="Z56" s="89">
-        <f>S50+T50+W50</f>
+        <f>S56+T56+W56</f>
         <v/>
       </c>
       <c r="AA56" s="89">
-        <f>K50+L50+M50+IFERROR(VLOOKUP(B50,RemitTable2,9,FALSE()),0)+Y50+Z50</f>
+        <f>K56+L56+M56+IFERROR(VLOOKUP(B56,RemitTable2,9,FALSE),0)+Y56+Z56</f>
         <v/>
       </c>
       <c r="AB56" s="90" t="n">
         <v>1</v>
       </c>
       <c r="AC56" s="89">
-        <f>ROUND(AA50/AB50,0)</f>
+        <f>ROUND(AA56/AB56,0)</f>
         <v/>
       </c>
       <c r="AD56" s="85" t="inlineStr">
@@ -8439,22 +8439,22 @@
         <v>2550</v>
       </c>
       <c r="I57" s="187">
-        <f>IFERROR(VLOOKUP(B51,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J57" s="89" t="n">
         <v>0</v>
       </c>
       <c r="K57" s="89">
-        <f>IFERROR(ROUND(H51*I51,0),0)</f>
+        <f>IFERROR(ROUND(H57*I57,0),0)</f>
         <v/>
       </c>
       <c r="L57" s="89">
-        <f>IFERROR(VLOOKUP(B51,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M57" s="89">
-        <f>IFERROR(VLOOKUP(B51,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N57" s="85" t="inlineStr">
@@ -8473,11 +8473,11 @@
         </is>
       </c>
       <c r="Q57" s="87">
-        <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P57="","",IFERROR(VLOOKUP(O57,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R57" s="87">
-        <f>IF(P51="","",H51)</f>
+        <f>IF(P57="","",H57)</f>
         <v/>
       </c>
       <c r="S57" s="89" t="n">
@@ -8504,18 +8504,18 @@
         <v>0</v>
       </c>
       <c r="Z57" s="89">
-        <f>S51+T51+W51</f>
+        <f>S57+T57+W57</f>
         <v/>
       </c>
       <c r="AA57" s="89">
-        <f>K51+L51+M51+IFERROR(VLOOKUP(B51,RemitTable2,9,FALSE()),0)+Y51+Z51</f>
+        <f>K57+L57+M57+IFERROR(VLOOKUP(B57,RemitTable2,9,FALSE),0)+Y57+Z57</f>
         <v/>
       </c>
       <c r="AB57" s="90" t="n">
         <v>1</v>
       </c>
       <c r="AC57" s="89">
-        <f>ROUND(AA51/AB51,0)</f>
+        <f>ROUND(AA57/AB57,0)</f>
         <v/>
       </c>
       <c r="AD57" s="85" t="inlineStr">
@@ -8562,33 +8562,33 @@
         <v>180</v>
       </c>
       <c r="I58" s="134">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,7,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J58" s="136" t="n">
         <v>0</v>
       </c>
       <c r="K58" s="136">
-        <f>IFERROR(ROUND(H56*I56,0),0)</f>
+        <f>IFERROR(ROUND(H58*I58,0),0)</f>
         <v/>
       </c>
       <c r="L58" s="136">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,10,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M58" s="136">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,11,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N58" s="137" t="n"/>
       <c r="O58" s="137" t="n"/>
       <c r="P58" s="137" t="n"/>
       <c r="Q58" s="134">
-        <f>IF(P56="","",IFERROR(VLOOKUP(O56,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R58" s="134">
-        <f>IF(P56="","",H56)</f>
+        <f>IF(P58="","",H58)</f>
         <v/>
       </c>
       <c r="S58" s="136" t="n">
@@ -8611,18 +8611,18 @@
         <v>0</v>
       </c>
       <c r="Z58" s="136">
-        <f>S56+T56+W56</f>
+        <f>S58+T58+W58</f>
         <v/>
       </c>
       <c r="AA58" s="136">
-        <f>K56+L56+M56+IFERROR(VLOOKUP(B56,RemitTable2,9,FALSE),0)+Y56+Z56</f>
+        <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
         <v/>
       </c>
       <c r="AB58" s="168" t="n">
         <v>2</v>
       </c>
       <c r="AC58" s="136">
-        <f>ROUND(AA56/AB56,0)</f>
+        <f>ROUND(AA58/AB58,0)</f>
         <v/>
       </c>
       <c r="AD58" s="137" t="n"/>
@@ -8669,33 +8669,33 @@
         <v>250</v>
       </c>
       <c r="I59" s="134">
-        <f>IFERROR(VLOOKUP(B57,RemitTable2,7,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B59,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J59" s="136" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="136">
-        <f>IFERROR(ROUND(H57*I57,0),0)</f>
+        <f>IFERROR(ROUND(H59*I59,0),0)</f>
         <v/>
       </c>
       <c r="L59" s="136">
-        <f>IFERROR(VLOOKUP(B57,RemitTable2,10,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B59,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M59" s="136">
-        <f>IFERROR(VLOOKUP(B57,RemitTable2,11,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B59,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N59" s="137" t="n"/>
       <c r="O59" s="137" t="n"/>
       <c r="P59" s="137" t="n"/>
       <c r="Q59" s="134">
-        <f>IF(P57="","",IFERROR(VLOOKUP(O57,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P59="","",IFERROR(VLOOKUP(O59,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R59" s="134">
-        <f>IF(P57="","",H57)</f>
+        <f>IF(P59="","",H59)</f>
         <v/>
       </c>
       <c r="S59" s="136" t="n">
@@ -8718,18 +8718,18 @@
         <v>0</v>
       </c>
       <c r="Z59" s="136">
-        <f>S57+T57+W57</f>
+        <f>S59+T59+W59</f>
         <v/>
       </c>
       <c r="AA59" s="136">
-        <f>K57+L57+M57+IFERROR(VLOOKUP(B57,RemitTable2,9,FALSE),0)+Y57+Z57</f>
+        <f>K59+L59+M59+IFERROR(VLOOKUP(B59,RemitTable2,9,FALSE),0)+Y59+Z59</f>
         <v/>
       </c>
       <c r="AB59" s="168" t="n">
         <v>1</v>
       </c>
       <c r="AC59" s="136">
-        <f>ROUND(AA57/AB57,0)</f>
+        <f>ROUND(AA59/AB59,0)</f>
         <v/>
       </c>
       <c r="AD59" s="137" t="n"/>
@@ -8772,33 +8772,33 @@
         <v>500</v>
       </c>
       <c r="I60" s="134">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,7,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B60,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J60" s="136" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="136">
-        <f>IFERROR(ROUND(H58*I58,0),0)</f>
+        <f>IFERROR(ROUND(H60*I60,0),0)</f>
         <v/>
       </c>
       <c r="L60" s="136">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,10,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B60,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M60" s="136">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,11,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(B60,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N60" s="137" t="n"/>
       <c r="O60" s="137" t="n"/>
       <c r="P60" s="137" t="n"/>
       <c r="Q60" s="134">
-        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P60="","",IFERROR(VLOOKUP(O60,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R60" s="134">
-        <f>IF(P58="","",H58)</f>
+        <f>IF(P60="","",H60)</f>
         <v/>
       </c>
       <c r="S60" s="136" t="n">
@@ -8821,18 +8821,18 @@
         <v>0</v>
       </c>
       <c r="Z60" s="136">
-        <f>S58+T58+W58</f>
+        <f>S60+T60+W60</f>
         <v/>
       </c>
       <c r="AA60" s="136">
-        <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
+        <f>K60+L60+M60+IFERROR(VLOOKUP(B60,RemitTable2,9,FALSE),0)+Y60+Z60</f>
         <v/>
       </c>
       <c r="AB60" s="168" t="n">
         <v>1</v>
       </c>
       <c r="AC60" s="136">
-        <f>ROUND(AA58/AB58,0)</f>
+        <f>ROUND(AA60/AB60,0)</f>
         <v/>
       </c>
       <c r="AD60" s="137" t="n"/>
@@ -8875,22 +8875,22 @@
         <v>4180</v>
       </c>
       <c r="I61" s="178">
-        <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B61,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J61" s="18" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="18">
-        <f>IFERROR(ROUND(H47*I47,0),0)</f>
+        <f>IFERROR(ROUND(H61*I61,0),0)</f>
         <v/>
       </c>
       <c r="L61" s="18">
-        <f>IFERROR(VLOOKUP(B47,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B61,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M61" s="18">
-        <f>IFERROR(VLOOKUP(B47,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B61,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N61" s="12" t="inlineStr">
@@ -8909,11 +8909,11 @@
         </is>
       </c>
       <c r="Q61" s="16">
-        <f>IF(P52="","",IFERROR(VLOOKUP(O52,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P61="","",IFERROR(VLOOKUP(O61,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R61" s="18">
-        <f>IF(P47="","",H47)</f>
+        <f>IF(P61="","",H61)</f>
         <v/>
       </c>
       <c r="S61" s="18" t="n">
@@ -8942,18 +8942,18 @@
         <v>0</v>
       </c>
       <c r="Z61" s="18">
-        <f>S47+T47+W47</f>
+        <f>S61+T61+W61</f>
         <v/>
       </c>
       <c r="AA61" s="18">
-        <f>K47+L47+M47+IFERROR(VLOOKUP(B47,RemitTable2,9,FALSE()),0)+Y47+Z47</f>
+        <f>K61+L61+M61+IFERROR(VLOOKUP(B61,RemitTable2,9,FALSE),0)+Y61+Z61</f>
         <v/>
       </c>
       <c r="AB61" s="19" t="n">
         <v>1</v>
       </c>
       <c r="AC61" s="18">
-        <f>ROUND(AA47/AB47,0)</f>
+        <f>ROUND(AA61/AB61,0)</f>
         <v/>
       </c>
       <c r="AD61" s="12" t="inlineStr">
@@ -9002,22 +9002,22 @@
         <v>400</v>
       </c>
       <c r="I62" s="178">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B62,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J62" s="18" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="18">
-        <f>IFERROR(ROUND(H48*I48,0),0)</f>
+        <f>IFERROR(ROUND(H62*I62,0),0)</f>
         <v/>
       </c>
       <c r="L62" s="18">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B62,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M62" s="18">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B62,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N62" s="12" t="inlineStr">
@@ -9034,11 +9034,11 @@
         </is>
       </c>
       <c r="Q62" s="16">
-        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
+        <f>IF(P62="","",IFERROR(VLOOKUP(O62,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R62" s="18">
-        <f>IF(P48="","",H48)</f>
+        <f>IF(P62="","",H62)</f>
         <v/>
       </c>
       <c r="S62" s="18" t="n">
@@ -9065,18 +9065,18 @@
         <v>0</v>
       </c>
       <c r="Z62" s="18">
-        <f>S48+T48+W48</f>
+        <f>S62+T62+W62</f>
         <v/>
       </c>
       <c r="AA62" s="18">
-        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE()),0)+Y48+Z48</f>
+        <f>K62+L62+M62+IFERROR(VLOOKUP(B62,RemitTable2,9,FALSE),0)+Y62+Z62</f>
         <v/>
       </c>
       <c r="AB62" s="19" t="n">
         <v>5</v>
       </c>
       <c r="AC62" s="18">
-        <f>ROUND(AA48/AB48,0)</f>
+        <f>ROUND(AA62/AB62,0)</f>
         <v/>
       </c>
       <c r="AD62" s="12" t="inlineStr">
@@ -9660,25 +9660,11 @@
       <c r="AE72" s="39" t="n"/>
       <c r="AF72" s="39" t="n"/>
     </row>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
     <row r="86">
       <c r="M86" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="A66:G66"/>
     <mergeCell ref="G3:N3"/>
     <mergeCell ref="A67:G67"/>
@@ -9686,8 +9672,9 @@
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A65:G65"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="O3:W3"/>
     <mergeCell ref="A2:AF2"/>
   </mergeCells>
@@ -12155,7 +12142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="160" min="1" max="1"/>
@@ -13758,1882 +13745,1853 @@
       <c r="M34" s="114" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="169" t="inlineStr">
+      <c r="A35" s="116" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.12</t>
+        </is>
+      </c>
+      <c r="C35" s="117" t="inlineStr">
+        <is>
+          <t>Ferco</t>
+        </is>
+      </c>
+      <c r="D35" s="116" t="inlineStr">
+        <is>
+          <t>PI44133-1</t>
+        </is>
+      </c>
+      <c r="E35" s="118" t="n">
+        <v>4416</v>
+      </c>
+      <c r="F35" s="197" t="n">
+        <v>1755.24</v>
+      </c>
+      <c r="G35" s="118" t="n">
+        <v>25</v>
+      </c>
+      <c r="H35" s="120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I35" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J35" s="120" t="n">
+        <v>7813020</v>
+      </c>
+      <c r="K35" s="120">
+        <f>ROUND((E35+G35)*F35+H35+I35,0)</f>
+        <v/>
+      </c>
+      <c r="L35" s="121">
+        <f>J35-K35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="116" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.19</t>
+        </is>
+      </c>
+      <c r="C36" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D36" s="116" t="inlineStr">
+        <is>
+          <t>GPO478</t>
+        </is>
+      </c>
+      <c r="E36" s="118" t="n">
+        <v>180</v>
+      </c>
+      <c r="F36" s="197" t="n">
+        <v>1518.9</v>
+      </c>
+      <c r="G36" s="118" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" s="120" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I36" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J36" s="120" t="n">
+        <v>314280</v>
+      </c>
+      <c r="K36" s="120">
+        <f>ROUND((E36+G36)*F36+H36+I36,0)</f>
+        <v/>
+      </c>
+      <c r="L36" s="121">
+        <f>J36-K36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="116" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.20</t>
+        </is>
+      </c>
+      <c r="C37" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D37" s="116" t="inlineStr">
+        <is>
+          <t>CPO698</t>
+        </is>
+      </c>
+      <c r="E37" s="118" t="n">
+        <v>4290</v>
+      </c>
+      <c r="F37" s="197" t="n">
+        <v>1510.6</v>
+      </c>
+      <c r="G37" s="118" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" s="120" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I37" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J37" s="120" t="n">
+        <v>6526186</v>
+      </c>
+      <c r="K37" s="120">
+        <f>ROUND((E37+G37)*F37+H37+I37,0)</f>
+        <v/>
+      </c>
+      <c r="L37" s="121">
+        <f>J37-K37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="116" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C38" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D38" s="116" t="inlineStr">
+        <is>
+          <t>GPO480, GPO479, GPO473-1</t>
+        </is>
+      </c>
+      <c r="E38" s="118" t="n">
+        <v>99140</v>
+      </c>
+      <c r="F38" s="197" t="n">
+        <v>1502.8</v>
+      </c>
+      <c r="G38" s="118" t="n">
+        <v>20</v>
+      </c>
+      <c r="H38" s="120" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I38" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J38" s="120" t="n">
+        <v>149038148</v>
+      </c>
+      <c r="K38" s="120">
+        <f>ROUND((E38+G38)*F38+H38+I38,0)</f>
+        <v/>
+      </c>
+      <c r="L38" s="121">
+        <f>J38-K38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="116" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C39" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D39" s="116" t="inlineStr">
+        <is>
+          <t>CPO697, CPO696-1, CPO696-2</t>
+        </is>
+      </c>
+      <c r="E39" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F39" s="197" t="n">
+        <v>1502.7</v>
+      </c>
+      <c r="G39" s="118" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" s="120" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I39" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J39" s="120" t="n">
+        <v>152781976</v>
+      </c>
+      <c r="K39" s="120">
+        <f>ROUND((E39+G39)*F39+H39+I39,0)</f>
+        <v/>
+      </c>
+      <c r="L39" s="121">
+        <f>J39-K39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="169" t="inlineStr">
         <is>
           <t>② PO별 비용 안분 내역</t>
         </is>
       </c>
-      <c r="B35" s="148" t="n"/>
-      <c r="C35" s="148" t="n"/>
-      <c r="D35" s="148" t="n"/>
-      <c r="E35" s="148" t="n"/>
-      <c r="F35" s="148" t="n"/>
-      <c r="G35" s="148" t="n"/>
-      <c r="H35" s="148" t="n"/>
-      <c r="I35" s="148" t="n"/>
-      <c r="J35" s="148" t="n"/>
-      <c r="K35" s="148" t="n"/>
-      <c r="L35" s="149" t="n"/>
-      <c r="M35" s="115" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="150" t="inlineStr">
+      <c r="B40" s="148" t="n"/>
+      <c r="C40" s="148" t="n"/>
+      <c r="D40" s="148" t="n"/>
+      <c r="E40" s="148" t="n"/>
+      <c r="F40" s="148" t="n"/>
+      <c r="G40" s="148" t="n"/>
+      <c r="H40" s="148" t="n"/>
+      <c r="I40" s="148" t="n"/>
+      <c r="J40" s="148" t="n"/>
+      <c r="K40" s="148" t="n"/>
+      <c r="L40" s="149" t="n"/>
+      <c r="M40" s="115" t="n"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="150" t="inlineStr">
         <is>
           <t>PO No.</t>
         </is>
       </c>
-      <c r="B36" s="150" t="inlineStr">
+      <c r="B41" s="150" t="inlineStr">
         <is>
           <t>송금일</t>
         </is>
       </c>
-      <c r="C36" s="150" t="inlineStr">
+      <c r="C41" s="150" t="inlineStr">
         <is>
           <t>업체</t>
         </is>
       </c>
-      <c r="D36" s="150" t="inlineStr">
+      <c r="D41" s="150" t="inlineStr">
         <is>
           <t>PO USD</t>
         </is>
       </c>
-      <c r="E36" s="150" t="inlineStr">
+      <c r="E41" s="150" t="inlineStr">
         <is>
           <t>그룹총USD</t>
         </is>
       </c>
-      <c r="F36" s="150" t="inlineStr">
+      <c r="F41" s="150" t="inlineStr">
         <is>
           <t>배부비율</t>
         </is>
       </c>
-      <c r="G36" s="150" t="inlineStr">
+      <c r="G41" s="150" t="inlineStr">
         <is>
           <t>적용환율</t>
         </is>
       </c>
-      <c r="H36" s="150" t="inlineStr">
+      <c r="H41" s="150" t="inlineStr">
         <is>
           <t>원화환산액</t>
         </is>
       </c>
-      <c r="I36" s="150" t="inlineStr">
+      <c r="I41" s="150" t="inlineStr">
         <is>
           <t>중개수수료안분</t>
         </is>
       </c>
-      <c r="J36" s="150" t="inlineStr">
+      <c r="J41" s="150" t="inlineStr">
         <is>
           <t>수수료안분</t>
         </is>
       </c>
-      <c r="K36" s="150" t="inlineStr">
+      <c r="K41" s="150" t="inlineStr">
         <is>
           <t>전신료안분</t>
         </is>
       </c>
-      <c r="L36" s="150" t="inlineStr">
+      <c r="L41" s="150" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="M36" s="115" t="n"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="M41" s="115" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="116" t="inlineStr">
         <is>
           <t>CPO678-1</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B42" s="116" t="inlineStr">
         <is>
           <t>2025.12.16</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C42" s="117" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D37" s="33" t="n">
+      <c r="D42" s="118" t="n">
         <v>139083</v>
       </c>
-      <c r="E37" s="33" t="n">
+      <c r="E42" s="118" t="n">
         <v>143557</v>
       </c>
-      <c r="F37" s="108">
-        <f>D37/E37</f>
-        <v/>
-      </c>
-      <c r="G37" s="33">
+      <c r="F42" s="122">
+        <f>D42/E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="118">
+        <f>F10</f>
+        <v/>
+      </c>
+      <c r="H42" s="120">
+        <f>ROUND(D42*G42,0)</f>
+        <v/>
+      </c>
+      <c r="I42" s="120">
+        <f>ROUND(G10*F42*G42,0)</f>
+        <v/>
+      </c>
+      <c r="J42" s="120">
+        <f>ROUND(H10*F42,0)</f>
+        <v/>
+      </c>
+      <c r="K42" s="120">
+        <f>ROUND(I10*F42,0)</f>
+        <v/>
+      </c>
+      <c r="L42" s="121">
+        <f>H42+I42+J42+K42</f>
+        <v/>
+      </c>
+      <c r="M42" s="115" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="116" t="inlineStr">
+        <is>
+          <t>CPO679</t>
+        </is>
+      </c>
+      <c r="B43" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.16</t>
+        </is>
+      </c>
+      <c r="C43" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D43" s="118" t="n">
+        <v>4474</v>
+      </c>
+      <c r="E43" s="118" t="n">
+        <v>143557</v>
+      </c>
+      <c r="F43" s="122">
+        <f>D43/E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="118">
+        <f>F10</f>
+        <v/>
+      </c>
+      <c r="H43" s="120">
+        <f>ROUND(D43*G43,0)</f>
+        <v/>
+      </c>
+      <c r="I43" s="120">
+        <f>ROUND(G10*F43*G43,0)</f>
+        <v/>
+      </c>
+      <c r="J43" s="120">
+        <f>ROUND(H10*F43,0)</f>
+        <v/>
+      </c>
+      <c r="K43" s="120">
+        <f>ROUND(I10*F43,0)</f>
+        <v/>
+      </c>
+      <c r="L43" s="121">
+        <f>H43+I43+J43+K43</f>
+        <v/>
+      </c>
+      <c r="M43" s="115" t="n"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="116" t="inlineStr">
+        <is>
+          <t>MPO65</t>
+        </is>
+      </c>
+      <c r="B44" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.16</t>
+        </is>
+      </c>
+      <c r="C44" s="117" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D44" s="118" t="n">
+        <v>4936</v>
+      </c>
+      <c r="E44" s="118" t="n">
+        <v>15040</v>
+      </c>
+      <c r="F44" s="122">
+        <f>D44/E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="118">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="H44" s="120">
+        <f>ROUND(D44*G44,0)</f>
+        <v/>
+      </c>
+      <c r="I44" s="120">
+        <f>ROUND(G9*F44*G44,0)</f>
+        <v/>
+      </c>
+      <c r="J44" s="120">
+        <f>ROUND(H9*F44,0)</f>
+        <v/>
+      </c>
+      <c r="K44" s="120">
+        <f>ROUND(I9*F44,0)</f>
+        <v/>
+      </c>
+      <c r="L44" s="121">
+        <f>H44+I44+J44+K44</f>
+        <v/>
+      </c>
+      <c r="M44" s="115" t="n"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="116" t="inlineStr">
+        <is>
+          <t>GPO451</t>
+        </is>
+      </c>
+      <c r="B45" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.29</t>
+        </is>
+      </c>
+      <c r="C45" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D45" s="118" t="n">
+        <v>9060</v>
+      </c>
+      <c r="E45" s="118" t="n">
+        <v>13860</v>
+      </c>
+      <c r="F45" s="122">
+        <f>D45/E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="118">
         <f>F12</f>
         <v/>
       </c>
-      <c r="H37" s="9">
-        <f>ROUND(D37*G37,0)</f>
-        <v/>
-      </c>
-      <c r="I37" s="9">
-        <f>ROUND(G12*F37*G37,0)</f>
-        <v/>
-      </c>
-      <c r="J37" s="9">
-        <f>ROUND(H12*F37,0)</f>
-        <v/>
-      </c>
-      <c r="K37" s="9">
-        <f>ROUND(I12*F37,0)</f>
-        <v/>
-      </c>
-      <c r="L37" s="35">
-        <f>H37+I37+J37+K37</f>
-        <v/>
-      </c>
-      <c r="M37" s="115" t="n"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>CPO679</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>2025.12.16</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="H45" s="120">
+        <f>ROUND(D45*G45,0)</f>
+        <v/>
+      </c>
+      <c r="I45" s="120">
+        <f>ROUND(G12*F45*G45,0)</f>
+        <v/>
+      </c>
+      <c r="J45" s="120">
+        <f>ROUND(H12*F45,0)</f>
+        <v/>
+      </c>
+      <c r="K45" s="120">
+        <f>ROUND(I12*F45,0)</f>
+        <v/>
+      </c>
+      <c r="L45" s="121">
+        <f>H45+I45+J45+K45</f>
+        <v/>
+      </c>
+      <c r="M45" s="115" t="n"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="116" t="inlineStr">
+        <is>
+          <t>GPO458</t>
+        </is>
+      </c>
+      <c r="B46" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.29</t>
+        </is>
+      </c>
+      <c r="C46" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D46" s="118" t="n">
+        <v>350</v>
+      </c>
+      <c r="E46" s="118" t="n">
+        <v>13860</v>
+      </c>
+      <c r="F46" s="122">
+        <f>D46/E46</f>
+        <v/>
+      </c>
+      <c r="G46" s="118">
+        <f>F12</f>
+        <v/>
+      </c>
+      <c r="H46" s="120">
+        <f>ROUND(D46*G46,0)</f>
+        <v/>
+      </c>
+      <c r="I46" s="120">
+        <f>ROUND(G12*F46*G46,0)</f>
+        <v/>
+      </c>
+      <c r="J46" s="120">
+        <f>ROUND(H12*F46,0)</f>
+        <v/>
+      </c>
+      <c r="K46" s="120">
+        <f>ROUND(I12*F46,0)</f>
+        <v/>
+      </c>
+      <c r="L46" s="121">
+        <f>H46+I46+J46+K46</f>
+        <v/>
+      </c>
+      <c r="M46" s="115" t="n"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="116" t="inlineStr">
+        <is>
+          <t>CPO680</t>
+        </is>
+      </c>
+      <c r="B47" s="116" t="inlineStr">
+        <is>
+          <t>2026.01.13</t>
+        </is>
+      </c>
+      <c r="C47" s="117" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D38" s="33" t="n">
-        <v>4474</v>
-      </c>
-      <c r="E38" s="33" t="n">
-        <v>143557</v>
-      </c>
-      <c r="F38" s="108">
-        <f>D38/E38</f>
-        <v/>
-      </c>
-      <c r="G38" s="33">
-        <f>F12</f>
-        <v/>
-      </c>
-      <c r="H38" s="9">
-        <f>ROUND(D38*G38,0)</f>
-        <v/>
-      </c>
-      <c r="I38" s="9">
-        <f>ROUND(G12*F38*G38,0)</f>
-        <v/>
-      </c>
-      <c r="J38" s="9">
-        <f>ROUND(H12*F38,0)</f>
-        <v/>
-      </c>
-      <c r="K38" s="9">
-        <f>ROUND(I12*F38,0)</f>
-        <v/>
-      </c>
-      <c r="L38" s="35">
-        <f>H38+I38+J38+K38</f>
-        <v/>
-      </c>
-      <c r="M38" s="115" t="n"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>MPO65</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>2025.12.16</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="D47" s="118" t="n">
+        <v>252</v>
+      </c>
+      <c r="E47" s="118" t="n">
+        <v>252</v>
+      </c>
+      <c r="F47" s="122">
+        <f>D47/E47</f>
+        <v/>
+      </c>
+      <c r="G47" s="118">
+        <f>F14</f>
+        <v/>
+      </c>
+      <c r="H47" s="120">
+        <f>ROUND(D47*G47,0)</f>
+        <v/>
+      </c>
+      <c r="I47" s="120">
+        <f>ROUND(G14*F47*G47,0)</f>
+        <v/>
+      </c>
+      <c r="J47" s="120">
+        <f>ROUND(H14*F47,0)</f>
+        <v/>
+      </c>
+      <c r="K47" s="120">
+        <f>ROUND(I14*F47,0)</f>
+        <v/>
+      </c>
+      <c r="L47" s="121">
+        <f>H47+I47+J47+K47</f>
+        <v/>
+      </c>
+      <c r="M47" s="115" t="n"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="116" t="inlineStr">
+        <is>
+          <t>GPO459</t>
+        </is>
+      </c>
+      <c r="B48" s="116" t="inlineStr">
+        <is>
+          <t>2026.01.21</t>
+        </is>
+      </c>
+      <c r="C48" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D48" s="118" t="n">
+        <v>450</v>
+      </c>
+      <c r="E48" s="118" t="n">
+        <v>3700</v>
+      </c>
+      <c r="F48" s="122">
+        <f>D48/E48</f>
+        <v/>
+      </c>
+      <c r="G48" s="118">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="H48" s="120">
+        <f>ROUND(D48*G48,0)</f>
+        <v/>
+      </c>
+      <c r="I48" s="120">
+        <f>ROUND(G15*F48*G48,0)</f>
+        <v/>
+      </c>
+      <c r="J48" s="120">
+        <f>ROUND(H15*F48,0)</f>
+        <v/>
+      </c>
+      <c r="K48" s="120">
+        <f>ROUND(I15*F48,0)</f>
+        <v/>
+      </c>
+      <c r="L48" s="121">
+        <f>H48+I48+J48+K48</f>
+        <v/>
+      </c>
+      <c r="M48" s="115" t="n"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="116" t="inlineStr">
+        <is>
+          <t>GPO460</t>
+        </is>
+      </c>
+      <c r="B49" s="116" t="inlineStr">
+        <is>
+          <t>2026.01.21</t>
+        </is>
+      </c>
+      <c r="C49" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D49" s="118" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E49" s="118" t="n">
+        <v>3700</v>
+      </c>
+      <c r="F49" s="122">
+        <f>D49/E49</f>
+        <v/>
+      </c>
+      <c r="G49" s="118">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="H49" s="120">
+        <f>ROUND(D49*G49,0)</f>
+        <v/>
+      </c>
+      <c r="I49" s="120">
+        <f>ROUND(G15*F49*G49,0)</f>
+        <v/>
+      </c>
+      <c r="J49" s="120">
+        <f>ROUND(H15*F49,0)</f>
+        <v/>
+      </c>
+      <c r="K49" s="120">
+        <f>ROUND(I15*F49,0)</f>
+        <v/>
+      </c>
+      <c r="L49" s="121">
+        <f>H49+I49+J49+K49</f>
+        <v/>
+      </c>
+      <c r="M49" s="115" t="n"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="116" t="inlineStr">
+        <is>
+          <t>GPO461</t>
+        </is>
+      </c>
+      <c r="B50" s="116" t="inlineStr">
+        <is>
+          <t>2026.01.21</t>
+        </is>
+      </c>
+      <c r="C50" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D50" s="118" t="n">
+        <v>540</v>
+      </c>
+      <c r="E50" s="118" t="n">
+        <v>3700</v>
+      </c>
+      <c r="F50" s="122">
+        <f>D50/E50</f>
+        <v/>
+      </c>
+      <c r="G50" s="118">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="H50" s="120">
+        <f>ROUND(D50*G50,0)</f>
+        <v/>
+      </c>
+      <c r="I50" s="120">
+        <f>ROUND(G15*F50*G50,0)</f>
+        <v/>
+      </c>
+      <c r="J50" s="120">
+        <f>ROUND(H15*F50,0)</f>
+        <v/>
+      </c>
+      <c r="K50" s="120">
+        <f>ROUND(I15*F50,0)</f>
+        <v/>
+      </c>
+      <c r="L50" s="121">
+        <f>H50+I50+J50+K50</f>
+        <v/>
+      </c>
+      <c r="M50" s="115" t="n"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="116" t="inlineStr">
+        <is>
+          <t>MPO66</t>
+        </is>
+      </c>
+      <c r="B51" s="116" t="inlineStr">
+        <is>
+          <t>2026.01.21</t>
+        </is>
+      </c>
+      <c r="C51" s="117" t="inlineStr">
         <is>
           <t>MAG</t>
         </is>
       </c>
-      <c r="D39" s="33" t="n">
-        <v>4936</v>
-      </c>
-      <c r="E39" s="33" t="n">
-        <v>15040</v>
-      </c>
-      <c r="F39" s="108">
-        <f>D39/E39</f>
-        <v/>
-      </c>
-      <c r="G39" s="33">
-        <f>F11</f>
-        <v/>
-      </c>
-      <c r="H39" s="9">
-        <f>ROUND(D39*G39,0)</f>
-        <v/>
-      </c>
-      <c r="I39" s="9">
-        <f>ROUND(G11*F39*G39,0)</f>
-        <v/>
-      </c>
-      <c r="J39" s="9">
-        <f>ROUND(H11*F39,0)</f>
-        <v/>
-      </c>
-      <c r="K39" s="9">
-        <f>ROUND(I11*F39,0)</f>
-        <v/>
-      </c>
-      <c r="L39" s="35">
-        <f>H39+I39+J39+K39</f>
-        <v/>
-      </c>
-      <c r="M39" s="115" t="n"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>GPO451</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>2025.12.29</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="D51" s="118" t="n">
+        <v>9626.35</v>
+      </c>
+      <c r="E51" s="118" t="n">
+        <v>9626.35</v>
+      </c>
+      <c r="F51" s="122">
+        <f>D51/E51</f>
+        <v/>
+      </c>
+      <c r="G51" s="118">
+        <f>F16</f>
+        <v/>
+      </c>
+      <c r="H51" s="120">
+        <f>ROUND(D51*G51,0)</f>
+        <v/>
+      </c>
+      <c r="I51" s="120">
+        <f>ROUND(G16*F51*G51,0)</f>
+        <v/>
+      </c>
+      <c r="J51" s="120">
+        <f>ROUND(H16*F51,0)</f>
+        <v/>
+      </c>
+      <c r="K51" s="120">
+        <f>ROUND(I16*F51,0)</f>
+        <v/>
+      </c>
+      <c r="L51" s="121">
+        <f>H51+I51+J51+K51</f>
+        <v/>
+      </c>
+      <c r="M51" s="115" t="n"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="116" t="inlineStr">
+        <is>
+          <t>LPO001</t>
+        </is>
+      </c>
+      <c r="B52" s="116" t="inlineStr">
+        <is>
+          <t>2026.01.30</t>
+        </is>
+      </c>
+      <c r="C52" s="117" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="D52" s="118" t="n">
+        <v>5056.8</v>
+      </c>
+      <c r="E52" s="118" t="n">
+        <v>5056.8</v>
+      </c>
+      <c r="F52" s="122">
+        <f>D52/E52</f>
+        <v/>
+      </c>
+      <c r="G52" s="118">
+        <f>F17</f>
+        <v/>
+      </c>
+      <c r="H52" s="120">
+        <f>ROUND(D52*G52,0)</f>
+        <v/>
+      </c>
+      <c r="I52" s="120">
+        <f>ROUND(G17*F52*G52,0)</f>
+        <v/>
+      </c>
+      <c r="J52" s="120">
+        <f>ROUND(H17*F52,0)</f>
+        <v/>
+      </c>
+      <c r="K52" s="120">
+        <f>ROUND(I17*F52,0)</f>
+        <v/>
+      </c>
+      <c r="L52" s="121">
+        <f>H52+I52+J52+K52</f>
+        <v/>
+      </c>
+      <c r="M52" s="115" t="n"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="116" t="inlineStr">
+        <is>
+          <t>CPO682</t>
+        </is>
+      </c>
+      <c r="B53" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.04</t>
+        </is>
+      </c>
+      <c r="C53" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D53" s="118" t="n">
+        <v>20174</v>
+      </c>
+      <c r="E53" s="118" t="n">
+        <v>24794</v>
+      </c>
+      <c r="F53" s="122">
+        <f>D53/E53</f>
+        <v/>
+      </c>
+      <c r="G53" s="118">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="H53" s="120">
+        <f>ROUND(D53*G53,0)</f>
+        <v/>
+      </c>
+      <c r="I53" s="120">
+        <f>ROUND(G19*F53*G53,0)</f>
+        <v/>
+      </c>
+      <c r="J53" s="120">
+        <f>ROUND(H19*F53,0)</f>
+        <v/>
+      </c>
+      <c r="K53" s="120">
+        <f>ROUND(I19*F53,0)</f>
+        <v/>
+      </c>
+      <c r="L53" s="121">
+        <f>H53+I53+J53+K53</f>
+        <v/>
+      </c>
+      <c r="M53" s="115" t="n"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="116" t="inlineStr">
+        <is>
+          <t>CPO683</t>
+        </is>
+      </c>
+      <c r="B54" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.04</t>
+        </is>
+      </c>
+      <c r="C54" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D54" s="118" t="n">
+        <v>4620</v>
+      </c>
+      <c r="E54" s="118" t="n">
+        <v>24794</v>
+      </c>
+      <c r="F54" s="122">
+        <f>D54/E54</f>
+        <v/>
+      </c>
+      <c r="G54" s="118">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="H54" s="120">
+        <f>ROUND(D54*G54,0)</f>
+        <v/>
+      </c>
+      <c r="I54" s="120">
+        <f>ROUND(G19*F54*G54,0)</f>
+        <v/>
+      </c>
+      <c r="J54" s="120">
+        <f>ROUND(H19*F54,0)</f>
+        <v/>
+      </c>
+      <c r="K54" s="120">
+        <f>ROUND(I19*F54,0)</f>
+        <v/>
+      </c>
+      <c r="L54" s="121">
+        <f>H54+I54+J54+K54</f>
+        <v/>
+      </c>
+      <c r="M54" s="115" t="n"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="116" t="inlineStr">
+        <is>
+          <t>GPO462</t>
+        </is>
+      </c>
+      <c r="B55" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.04</t>
+        </is>
+      </c>
+      <c r="C55" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D40" s="33" t="n">
-        <v>9060</v>
-      </c>
-      <c r="E40" s="33" t="n">
-        <v>13860</v>
-      </c>
-      <c r="F40" s="108">
-        <f>D40/E40</f>
-        <v/>
-      </c>
-      <c r="G40" s="33">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="H40" s="9">
-        <f>ROUND(D40*G40,0)</f>
-        <v/>
-      </c>
-      <c r="I40" s="9">
-        <f>ROUND(G14*F40*G40,0)</f>
-        <v/>
-      </c>
-      <c r="J40" s="9">
-        <f>ROUND(H14*F40,0)</f>
-        <v/>
-      </c>
-      <c r="K40" s="9">
-        <f>ROUND(I14*F40,0)</f>
-        <v/>
-      </c>
-      <c r="L40" s="35">
-        <f>H40+I40+J40+K40</f>
-        <v/>
-      </c>
-      <c r="M40" s="115" t="n"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>GPO458</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>2025.12.29</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="D55" s="118" t="n">
+        <v>1440</v>
+      </c>
+      <c r="E55" s="118" t="n">
+        <v>11599.57</v>
+      </c>
+      <c r="F55" s="122">
+        <f>D55/E55</f>
+        <v/>
+      </c>
+      <c r="G55" s="118">
+        <f>F20</f>
+        <v/>
+      </c>
+      <c r="H55" s="120">
+        <f>ROUND(D55*G55,0)</f>
+        <v/>
+      </c>
+      <c r="I55" s="120">
+        <f>ROUND(G20*F55*G55,0)</f>
+        <v/>
+      </c>
+      <c r="J55" s="120">
+        <f>ROUND(H20*F55,0)</f>
+        <v/>
+      </c>
+      <c r="K55" s="120">
+        <f>ROUND(I20*F55,0)</f>
+        <v/>
+      </c>
+      <c r="L55" s="121">
+        <f>H55+I55+J55+K55</f>
+        <v/>
+      </c>
+      <c r="M55" s="115" t="n"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="116" t="inlineStr">
+        <is>
+          <t>GPO463</t>
+        </is>
+      </c>
+      <c r="B56" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.04</t>
+        </is>
+      </c>
+      <c r="C56" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D41" s="33" t="n">
-        <v>350</v>
-      </c>
-      <c r="E41" s="33" t="n">
-        <v>13860</v>
-      </c>
-      <c r="F41" s="108">
-        <f>D41/E41</f>
-        <v/>
-      </c>
-      <c r="G41" s="33">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="H41" s="9">
-        <f>ROUND(D41*G41,0)</f>
-        <v/>
-      </c>
-      <c r="I41" s="9">
-        <f>ROUND(G14*F41*G41,0)</f>
-        <v/>
-      </c>
-      <c r="J41" s="9">
-        <f>ROUND(H14*F41,0)</f>
-        <v/>
-      </c>
-      <c r="K41" s="9">
-        <f>ROUND(I14*F41,0)</f>
-        <v/>
-      </c>
-      <c r="L41" s="35">
-        <f>H41+I41+J41+K41</f>
-        <v/>
-      </c>
-      <c r="M41" s="115" t="n"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>CPO680</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>2026.01.13</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="D56" s="118" t="n">
+        <v>4489</v>
+      </c>
+      <c r="E56" s="118" t="n">
+        <v>11599.57</v>
+      </c>
+      <c r="F56" s="122">
+        <f>D56/E56</f>
+        <v/>
+      </c>
+      <c r="G56" s="118">
+        <f>F20</f>
+        <v/>
+      </c>
+      <c r="H56" s="120">
+        <f>ROUND(D56*G56,0)</f>
+        <v/>
+      </c>
+      <c r="I56" s="120">
+        <f>ROUND(G20*F56*G56,0)</f>
+        <v/>
+      </c>
+      <c r="J56" s="120">
+        <f>ROUND(H20*F56,0)</f>
+        <v/>
+      </c>
+      <c r="K56" s="120">
+        <f>ROUND(I20*F56,0)</f>
+        <v/>
+      </c>
+      <c r="L56" s="121">
+        <f>H56+I56+J56+K56</f>
+        <v/>
+      </c>
+      <c r="M56" s="115" t="n"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="116" t="inlineStr">
+        <is>
+          <t>GPO464</t>
+        </is>
+      </c>
+      <c r="B57" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.04</t>
+        </is>
+      </c>
+      <c r="C57" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D57" s="118" t="n">
+        <v>5670.57</v>
+      </c>
+      <c r="E57" s="118" t="n">
+        <v>11599.57</v>
+      </c>
+      <c r="F57" s="122">
+        <f>D57/E57</f>
+        <v/>
+      </c>
+      <c r="G57" s="118">
+        <f>F20</f>
+        <v/>
+      </c>
+      <c r="H57" s="120">
+        <f>ROUND(D57*G57,0)</f>
+        <v/>
+      </c>
+      <c r="I57" s="120">
+        <f>ROUND(G20*F57*G57,0)</f>
+        <v/>
+      </c>
+      <c r="J57" s="120">
+        <f>ROUND(H20*F57,0)</f>
+        <v/>
+      </c>
+      <c r="K57" s="120">
+        <f>ROUND(I20*F57,0)</f>
+        <v/>
+      </c>
+      <c r="L57" s="121">
+        <f>H57+I57+J57+K57</f>
+        <v/>
+      </c>
+      <c r="M57" s="115" t="n"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="116" t="inlineStr">
+        <is>
+          <t>CPO681</t>
+        </is>
+      </c>
+      <c r="B58" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.11</t>
+        </is>
+      </c>
+      <c r="C58" s="117" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D42" s="33" t="n">
-        <v>252</v>
-      </c>
-      <c r="E42" s="33" t="n">
-        <v>252</v>
-      </c>
-      <c r="F42" s="108">
-        <f>D42/E42</f>
-        <v/>
-      </c>
-      <c r="G42" s="33">
-        <f>F16</f>
-        <v/>
-      </c>
-      <c r="H42" s="9">
-        <f>ROUND(D42*G42,0)</f>
-        <v/>
-      </c>
-      <c r="I42" s="9">
-        <f>ROUND(G16*F42*G42,0)</f>
-        <v/>
-      </c>
-      <c r="J42" s="9">
-        <f>ROUND(H16*F42,0)</f>
-        <v/>
-      </c>
-      <c r="K42" s="9">
-        <f>ROUND(I16*F42,0)</f>
-        <v/>
-      </c>
-      <c r="L42" s="35">
-        <f>H42+I42+J42+K42</f>
-        <v/>
-      </c>
-      <c r="M42" s="115" t="n"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>GPO459</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>2026.01.21</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="D58" s="118" t="n">
+        <v>26358</v>
+      </c>
+      <c r="E58" s="118" t="n">
+        <v>26358</v>
+      </c>
+      <c r="F58" s="122">
+        <f>D58/E58</f>
+        <v/>
+      </c>
+      <c r="G58" s="118">
+        <f>F21</f>
+        <v/>
+      </c>
+      <c r="H58" s="120">
+        <f>ROUND(D58*G58,0)</f>
+        <v/>
+      </c>
+      <c r="I58" s="120">
+        <f>ROUND(G21*F58*G58,0)</f>
+        <v/>
+      </c>
+      <c r="J58" s="120">
+        <f>ROUND(H21*F58,0)</f>
+        <v/>
+      </c>
+      <c r="K58" s="120">
+        <f>ROUND(I21*F58,0)</f>
+        <v/>
+      </c>
+      <c r="L58" s="121">
+        <f>H58+I58+J58+K58</f>
+        <v/>
+      </c>
+      <c r="M58" s="115" t="n"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="116" t="inlineStr">
+        <is>
+          <t>CPO686</t>
+        </is>
+      </c>
+      <c r="B59" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.19</t>
+        </is>
+      </c>
+      <c r="C59" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D59" s="118" t="n">
+        <v>14793</v>
+      </c>
+      <c r="E59" s="118" t="n">
+        <v>17538</v>
+      </c>
+      <c r="F59" s="122">
+        <f>D59/E59</f>
+        <v/>
+      </c>
+      <c r="G59" s="118">
+        <f>F22</f>
+        <v/>
+      </c>
+      <c r="H59" s="120">
+        <f>ROUND(D59*G59,0)</f>
+        <v/>
+      </c>
+      <c r="I59" s="120">
+        <f>ROUND(G22*F59*G59,0)</f>
+        <v/>
+      </c>
+      <c r="J59" s="120">
+        <f>ROUND(H22*F59,0)</f>
+        <v/>
+      </c>
+      <c r="K59" s="120">
+        <f>ROUND(I22*F59,0)</f>
+        <v/>
+      </c>
+      <c r="L59" s="121">
+        <f>H59+I59+J59+K59</f>
+        <v/>
+      </c>
+      <c r="M59" s="115" t="n"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="116" t="inlineStr">
+        <is>
+          <t>CPO689</t>
+        </is>
+      </c>
+      <c r="B60" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.19</t>
+        </is>
+      </c>
+      <c r="C60" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D60" s="118" t="n">
+        <v>2745</v>
+      </c>
+      <c r="E60" s="118" t="n">
+        <v>17538</v>
+      </c>
+      <c r="F60" s="122">
+        <f>D60/E60</f>
+        <v/>
+      </c>
+      <c r="G60" s="118">
+        <f>F22</f>
+        <v/>
+      </c>
+      <c r="H60" s="120">
+        <f>ROUND(D60*G60,0)</f>
+        <v/>
+      </c>
+      <c r="I60" s="120">
+        <f>ROUND(G22*F60*G60,0)</f>
+        <v/>
+      </c>
+      <c r="J60" s="120">
+        <f>ROUND(H22*F60,0)</f>
+        <v/>
+      </c>
+      <c r="K60" s="120">
+        <f>ROUND(I22*F60,0)</f>
+        <v/>
+      </c>
+      <c r="L60" s="121">
+        <f>H60+I60+J60+K60</f>
+        <v/>
+      </c>
+      <c r="M60" s="115" t="n"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="116" t="inlineStr">
+        <is>
+          <t>CPO667</t>
+        </is>
+      </c>
+      <c r="B61" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.27</t>
+        </is>
+      </c>
+      <c r="C61" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D61" s="118" t="n">
+        <v>5673</v>
+      </c>
+      <c r="E61" s="118" t="n">
+        <v>142189</v>
+      </c>
+      <c r="F61" s="122">
+        <f>D61/E61</f>
+        <v/>
+      </c>
+      <c r="G61" s="118">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="H61" s="120">
+        <f>ROUND(D61*G61,0)</f>
+        <v/>
+      </c>
+      <c r="I61" s="120">
+        <f>ROUND(G23*F61*G61,0)</f>
+        <v/>
+      </c>
+      <c r="J61" s="120">
+        <f>ROUND(H23*F61,0)</f>
+        <v/>
+      </c>
+      <c r="K61" s="120">
+        <f>ROUND(I23*F61,0)</f>
+        <v/>
+      </c>
+      <c r="L61" s="121">
+        <f>H61+I61+J61+K61</f>
+        <v/>
+      </c>
+      <c r="M61" s="115" t="n"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="116" t="inlineStr">
+        <is>
+          <t>CPO685</t>
+        </is>
+      </c>
+      <c r="B62" s="116" t="inlineStr">
+        <is>
+          <t>2026.02.27</t>
+        </is>
+      </c>
+      <c r="C62" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D62" s="118" t="n">
+        <v>136516</v>
+      </c>
+      <c r="E62" s="118" t="n">
+        <v>142189</v>
+      </c>
+      <c r="F62" s="122">
+        <f>D62/E62</f>
+        <v/>
+      </c>
+      <c r="G62" s="118">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="H62" s="120">
+        <f>ROUND(D62*G62,0)</f>
+        <v/>
+      </c>
+      <c r="I62" s="120">
+        <f>ROUND(G23*F62*G62,0)</f>
+        <v/>
+      </c>
+      <c r="J62" s="120">
+        <f>ROUND(H23*F62,0)</f>
+        <v/>
+      </c>
+      <c r="K62" s="120">
+        <f>ROUND(I23*F62,0)</f>
+        <v/>
+      </c>
+      <c r="L62" s="121">
+        <f>H62+I62+J62+K62</f>
+        <v/>
+      </c>
+      <c r="M62" s="115" t="n"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="116" t="inlineStr">
+        <is>
+          <t>CPO678-2</t>
+        </is>
+      </c>
+      <c r="B63" s="116" t="inlineStr">
+        <is>
+          <t>2026.03.06</t>
+        </is>
+      </c>
+      <c r="C63" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D63" s="118" t="n">
+        <v>137850</v>
+      </c>
+      <c r="E63" s="118" t="n">
+        <v>137850</v>
+      </c>
+      <c r="F63" s="122">
+        <f>D63/E63</f>
+        <v/>
+      </c>
+      <c r="G63" s="118">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="H63" s="120">
+        <f>ROUND(D63*G63,0)</f>
+        <v/>
+      </c>
+      <c r="I63" s="120">
+        <f>ROUND(G24*F63*G63,0)</f>
+        <v/>
+      </c>
+      <c r="J63" s="120">
+        <f>ROUND(H24*F63,0)</f>
+        <v/>
+      </c>
+      <c r="K63" s="120">
+        <f>ROUND(I24*F63,0)</f>
+        <v/>
+      </c>
+      <c r="L63" s="121">
+        <f>H63+I63+J63+K63</f>
+        <v/>
+      </c>
+      <c r="M63" s="115" t="n"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="116" t="inlineStr">
+        <is>
+          <t>CPO690</t>
+        </is>
+      </c>
+      <c r="B64" s="116" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C64" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D64" s="118" t="n">
+        <v>9740</v>
+      </c>
+      <c r="E64" s="118" t="n">
+        <v>34354</v>
+      </c>
+      <c r="F64" s="122">
+        <f>D64/E64</f>
+        <v/>
+      </c>
+      <c r="G64" s="118">
+        <f>F25</f>
+        <v/>
+      </c>
+      <c r="H64" s="120">
+        <f>ROUND(D64*G64,0)</f>
+        <v/>
+      </c>
+      <c r="I64" s="120">
+        <f>ROUND(G25*F64*G64,0)</f>
+        <v/>
+      </c>
+      <c r="J64" s="120">
+        <f>ROUND(H25*F64,0)</f>
+        <v/>
+      </c>
+      <c r="K64" s="120">
+        <f>ROUND(I25*F64,0)</f>
+        <v/>
+      </c>
+      <c r="L64" s="121">
+        <f>H64+I64+J64+K64</f>
+        <v/>
+      </c>
+      <c r="M64" s="115" t="n"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="116" t="inlineStr">
+        <is>
+          <t>CPO691</t>
+        </is>
+      </c>
+      <c r="B65" s="116" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C65" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D65" s="118" t="n">
+        <v>24614</v>
+      </c>
+      <c r="E65" s="118" t="n">
+        <v>34354</v>
+      </c>
+      <c r="F65" s="122">
+        <f>D65/E65</f>
+        <v/>
+      </c>
+      <c r="G65" s="118">
+        <f>F25</f>
+        <v/>
+      </c>
+      <c r="H65" s="120">
+        <f>ROUND(D65*G65,0)</f>
+        <v/>
+      </c>
+      <c r="I65" s="120">
+        <f>ROUND(G25*F65*G65,0)</f>
+        <v/>
+      </c>
+      <c r="J65" s="120">
+        <f>ROUND(H25*F65,0)</f>
+        <v/>
+      </c>
+      <c r="K65" s="120">
+        <f>ROUND(I25*F65,0)</f>
+        <v/>
+      </c>
+      <c r="L65" s="121">
+        <f>H65+I65+J65+K65</f>
+        <v/>
+      </c>
+      <c r="M65" s="115" t="n"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="116" t="inlineStr">
+        <is>
+          <t>GPO467</t>
+        </is>
+      </c>
+      <c r="B66" s="116" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C66" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D43" s="33" t="n">
-        <v>450</v>
-      </c>
-      <c r="E43" s="33" t="n">
-        <v>3700</v>
-      </c>
-      <c r="F43" s="108">
-        <f>D43/E43</f>
-        <v/>
-      </c>
-      <c r="G43" s="33">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="H43" s="9">
-        <f>ROUND(D43*G43,0)</f>
-        <v/>
-      </c>
-      <c r="I43" s="9">
-        <f>ROUND(G17*F43*G43,0)</f>
-        <v/>
-      </c>
-      <c r="J43" s="9">
-        <f>ROUND(H17*F43,0)</f>
-        <v/>
-      </c>
-      <c r="K43" s="9">
-        <f>ROUND(I17*F43,0)</f>
-        <v/>
-      </c>
-      <c r="L43" s="35">
-        <f>H43+I43+J43+K43</f>
-        <v/>
-      </c>
-      <c r="M43" s="115" t="n"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>GPO460</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>2026.01.21</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="D66" s="118" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E66" s="118" t="n">
+        <v>6553.05</v>
+      </c>
+      <c r="F66" s="122">
+        <f>D66/E66</f>
+        <v/>
+      </c>
+      <c r="G66" s="118">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="H66" s="120">
+        <f>ROUND(D66*G66,0)</f>
+        <v/>
+      </c>
+      <c r="I66" s="120">
+        <f>ROUND(G26*F66*G66,0)</f>
+        <v/>
+      </c>
+      <c r="J66" s="120">
+        <f>ROUND(H26*F66,0)</f>
+        <v/>
+      </c>
+      <c r="K66" s="120">
+        <f>ROUND(I26*F66,0)</f>
+        <v/>
+      </c>
+      <c r="L66" s="121">
+        <f>H66+I66+J66+K66</f>
+        <v/>
+      </c>
+      <c r="M66" s="115" t="n"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="116" t="inlineStr">
+        <is>
+          <t>GPO469</t>
+        </is>
+      </c>
+      <c r="B67" s="116" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C67" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D44" s="33" t="n">
-        <v>2710</v>
-      </c>
-      <c r="E44" s="33" t="n">
-        <v>3700</v>
-      </c>
-      <c r="F44" s="108">
-        <f>D44/E44</f>
-        <v/>
-      </c>
-      <c r="G44" s="33">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="H44" s="9">
-        <f>ROUND(D44*G44,0)</f>
-        <v/>
-      </c>
-      <c r="I44" s="9">
-        <f>ROUND(G17*F44*G44,0)</f>
-        <v/>
-      </c>
-      <c r="J44" s="9">
-        <f>ROUND(H17*F44,0)</f>
-        <v/>
-      </c>
-      <c r="K44" s="9">
-        <f>ROUND(I17*F44,0)</f>
-        <v/>
-      </c>
-      <c r="L44" s="35">
-        <f>H44+I44+J44+K44</f>
-        <v/>
-      </c>
-      <c r="M44" s="115" t="n"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>GPO461</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>2026.01.21</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="D67" s="118" t="n">
+        <v>3993.05</v>
+      </c>
+      <c r="E67" s="118" t="n">
+        <v>6553.05</v>
+      </c>
+      <c r="F67" s="122">
+        <f>D67/E67</f>
+        <v/>
+      </c>
+      <c r="G67" s="118">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="H67" s="120">
+        <f>ROUND(D67*G67,0)</f>
+        <v/>
+      </c>
+      <c r="I67" s="120">
+        <f>ROUND(G26*F67*G67,0)</f>
+        <v/>
+      </c>
+      <c r="J67" s="120">
+        <f>ROUND(H26*F67,0)</f>
+        <v/>
+      </c>
+      <c r="K67" s="120">
+        <f>ROUND(I26*F67,0)</f>
+        <v/>
+      </c>
+      <c r="L67" s="121">
+        <f>H67+I67+J67+K67</f>
+        <v/>
+      </c>
+      <c r="M67" s="115" t="n"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="116" t="inlineStr">
+        <is>
+          <t>GPO470</t>
+        </is>
+      </c>
+      <c r="B68" s="116" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C68" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D45" s="33" t="n">
-        <v>540</v>
-      </c>
-      <c r="E45" s="33" t="n">
-        <v>3700</v>
-      </c>
-      <c r="F45" s="108">
-        <f>D45/E45</f>
-        <v/>
-      </c>
-      <c r="G45" s="33">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="H45" s="9">
-        <f>ROUND(D45*G45,0)</f>
-        <v/>
-      </c>
-      <c r="I45" s="9">
-        <f>ROUND(G17*F45*G45,0)</f>
-        <v/>
-      </c>
-      <c r="J45" s="9">
-        <f>ROUND(H17*F45,0)</f>
-        <v/>
-      </c>
-      <c r="K45" s="9">
-        <f>ROUND(I17*F45,0)</f>
-        <v/>
-      </c>
-      <c r="L45" s="35">
-        <f>H45+I45+J45+K45</f>
-        <v/>
-      </c>
-      <c r="M45" s="115" t="n"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>MPO66</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>2026.01.21</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>MAG</t>
-        </is>
-      </c>
-      <c r="D46" s="33" t="n">
-        <v>9626.35</v>
-      </c>
-      <c r="E46" s="33" t="n">
-        <v>9626.35</v>
-      </c>
-      <c r="F46" s="108">
-        <f>D46/E46</f>
-        <v/>
-      </c>
-      <c r="G46" s="33">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="H46" s="9">
-        <f>ROUND(D46*G46,0)</f>
-        <v/>
-      </c>
-      <c r="I46" s="9">
-        <f>ROUND(G18*F46*G46,0)</f>
-        <v/>
-      </c>
-      <c r="J46" s="9">
-        <f>ROUND(H18*F46,0)</f>
-        <v/>
-      </c>
-      <c r="K46" s="9">
-        <f>ROUND(I18*F46,0)</f>
-        <v/>
-      </c>
-      <c r="L46" s="35">
-        <f>H46+I46+J46+K46</f>
-        <v/>
-      </c>
-      <c r="M46" s="115" t="n"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>LPO001</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>2026.01.30</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Lemon</t>
-        </is>
-      </c>
-      <c r="D47" s="33" t="n">
-        <v>5056.8</v>
-      </c>
-      <c r="E47" s="33" t="n">
-        <v>5056.8</v>
-      </c>
-      <c r="F47" s="108">
-        <f>D47/E47</f>
-        <v/>
-      </c>
-      <c r="G47" s="33">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="H47" s="9">
-        <f>ROUND(D47*G47,0)</f>
-        <v/>
-      </c>
-      <c r="I47" s="9">
-        <f>ROUND(G19*F47*G47,0)</f>
-        <v/>
-      </c>
-      <c r="J47" s="9">
-        <f>ROUND(H19*F47,0)</f>
-        <v/>
-      </c>
-      <c r="K47" s="9">
-        <f>ROUND(I19*F47,0)</f>
-        <v/>
-      </c>
-      <c r="L47" s="35">
-        <f>H47+I47+J47+K47</f>
-        <v/>
-      </c>
-      <c r="M47" s="115" t="n"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>CPO682</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.04</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D48" s="33" t="n">
-        <v>20174</v>
-      </c>
-      <c r="E48" s="33" t="n">
-        <v>24794</v>
-      </c>
-      <c r="F48" s="108">
-        <f>D48/E48</f>
-        <v/>
-      </c>
-      <c r="G48" s="33">
-        <f>F21</f>
-        <v/>
-      </c>
-      <c r="H48" s="9">
-        <f>ROUND(D48*G48,0)</f>
-        <v/>
-      </c>
-      <c r="I48" s="9">
-        <f>ROUND(G21*F48*G48,0)</f>
-        <v/>
-      </c>
-      <c r="J48" s="9">
-        <f>ROUND(H21*F48,0)</f>
-        <v/>
-      </c>
-      <c r="K48" s="9">
-        <f>ROUND(I21*F48,0)</f>
-        <v/>
-      </c>
-      <c r="L48" s="35">
-        <f>H48+I48+J48+K48</f>
-        <v/>
-      </c>
-      <c r="M48" s="115" t="n"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>CPO683</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.04</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D49" s="33" t="n">
-        <v>4620</v>
-      </c>
-      <c r="E49" s="33" t="n">
-        <v>24794</v>
-      </c>
-      <c r="F49" s="108">
-        <f>D49/E49</f>
-        <v/>
-      </c>
-      <c r="G49" s="33">
-        <f>F21</f>
-        <v/>
-      </c>
-      <c r="H49" s="9">
-        <f>ROUND(D49*G49,0)</f>
-        <v/>
-      </c>
-      <c r="I49" s="9">
-        <f>ROUND(G21*F49*G49,0)</f>
-        <v/>
-      </c>
-      <c r="J49" s="9">
-        <f>ROUND(H21*F49,0)</f>
-        <v/>
-      </c>
-      <c r="K49" s="9">
-        <f>ROUND(I21*F49,0)</f>
-        <v/>
-      </c>
-      <c r="L49" s="35">
-        <f>H49+I49+J49+K49</f>
-        <v/>
-      </c>
-      <c r="M49" s="115" t="n"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>GPO462</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.04</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="D68" s="118" t="n">
+        <v>360</v>
+      </c>
+      <c r="E68" s="118" t="n">
+        <v>6553.05</v>
+      </c>
+      <c r="F68" s="122">
+        <f>D68/E68</f>
+        <v/>
+      </c>
+      <c r="G68" s="118">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="H68" s="120">
+        <f>ROUND(D68*G68,0)</f>
+        <v/>
+      </c>
+      <c r="I68" s="120">
+        <f>ROUND(G26*F68*G68,0)</f>
+        <v/>
+      </c>
+      <c r="J68" s="120">
+        <f>ROUND(H26*F68,0)</f>
+        <v/>
+      </c>
+      <c r="K68" s="120">
+        <f>ROUND(I26*F68,0)</f>
+        <v/>
+      </c>
+      <c r="L68" s="121">
+        <f>H68+I68+J68+K68</f>
+        <v/>
+      </c>
+      <c r="M68" s="115" t="n"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="116" t="inlineStr">
+        <is>
+          <t>GPO471</t>
+        </is>
+      </c>
+      <c r="B69" s="116" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="C69" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D50" s="33" t="n">
-        <v>1440</v>
-      </c>
-      <c r="E50" s="33" t="n">
-        <v>11599.57</v>
-      </c>
-      <c r="F50" s="108">
-        <f>D50/E50</f>
-        <v/>
-      </c>
-      <c r="G50" s="33">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H50" s="9">
-        <f>ROUND(D50*G50,0)</f>
-        <v/>
-      </c>
-      <c r="I50" s="9">
-        <f>ROUND(G22*F50*G50,0)</f>
-        <v/>
-      </c>
-      <c r="J50" s="9">
-        <f>ROUND(H22*F50,0)</f>
-        <v/>
-      </c>
-      <c r="K50" s="9">
-        <f>ROUND(I22*F50,0)</f>
-        <v/>
-      </c>
-      <c r="L50" s="35">
-        <f>H50+I50+J50+K50</f>
-        <v/>
-      </c>
-      <c r="M50" s="115" t="n"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>GPO463</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.04</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="D69" s="118" t="n">
+        <v>500</v>
+      </c>
+      <c r="E69" s="118" t="n">
+        <v>6553.05</v>
+      </c>
+      <c r="F69" s="122">
+        <f>D69/E69</f>
+        <v/>
+      </c>
+      <c r="G69" s="118">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="H69" s="120">
+        <f>ROUND(D69*G69,0)</f>
+        <v/>
+      </c>
+      <c r="I69" s="120">
+        <f>ROUND(G26*F69*G69,0)</f>
+        <v/>
+      </c>
+      <c r="J69" s="120">
+        <f>ROUND(H26*F69,0)</f>
+        <v/>
+      </c>
+      <c r="K69" s="120">
+        <f>ROUND(I26*F69,0)</f>
+        <v/>
+      </c>
+      <c r="L69" s="121">
+        <f>H69+I69+J69+K69</f>
+        <v/>
+      </c>
+      <c r="M69" s="115" t="n"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="116" t="inlineStr">
+        <is>
+          <t>GPO468-1</t>
+        </is>
+      </c>
+      <c r="B70" s="116" t="inlineStr">
+        <is>
+          <t>2026.04.14</t>
+        </is>
+      </c>
+      <c r="C70" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D51" s="33" t="n">
-        <v>4489</v>
-      </c>
-      <c r="E51" s="33" t="n">
-        <v>11599.57</v>
-      </c>
-      <c r="F51" s="108">
-        <f>D51/E51</f>
-        <v/>
-      </c>
-      <c r="G51" s="33">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H51" s="9">
-        <f>ROUND(D51*G51,0)</f>
-        <v/>
-      </c>
-      <c r="I51" s="9">
-        <f>ROUND(G22*F51*G51,0)</f>
-        <v/>
-      </c>
-      <c r="J51" s="9">
-        <f>ROUND(H22*F51,0)</f>
-        <v/>
-      </c>
-      <c r="K51" s="9">
-        <f>ROUND(I22*F51,0)</f>
-        <v/>
-      </c>
-      <c r="L51" s="35">
-        <f>H51+I51+J51+K51</f>
-        <v/>
-      </c>
-      <c r="M51" s="115" t="n"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>GPO464</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.04</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="D70" s="118" t="n">
+        <v>36190</v>
+      </c>
+      <c r="E70" s="118" t="n">
+        <v>57650</v>
+      </c>
+      <c r="F70" s="122">
+        <f>D70/E70</f>
+        <v/>
+      </c>
+      <c r="G70" s="118">
+        <f>F27</f>
+        <v/>
+      </c>
+      <c r="H70" s="120">
+        <f>ROUND(D70*G70,0)</f>
+        <v/>
+      </c>
+      <c r="I70" s="120">
+        <f>ROUND(G27*F70*G70,0)</f>
+        <v/>
+      </c>
+      <c r="J70" s="120">
+        <f>ROUND(H27*F70,0)</f>
+        <v/>
+      </c>
+      <c r="K70" s="120">
+        <f>ROUND(I27*F70,0)</f>
+        <v/>
+      </c>
+      <c r="L70" s="121">
+        <f>H70+I70+J70+K70</f>
+        <v/>
+      </c>
+      <c r="M70" s="115" t="n"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="116" t="inlineStr">
+        <is>
+          <t>GPO472</t>
+        </is>
+      </c>
+      <c r="B71" s="116" t="inlineStr">
+        <is>
+          <t>2026.04.14</t>
+        </is>
+      </c>
+      <c r="C71" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D52" s="33" t="n">
-        <v>5670.57</v>
-      </c>
-      <c r="E52" s="33" t="n">
-        <v>11599.57</v>
-      </c>
-      <c r="F52" s="108">
-        <f>D52/E52</f>
-        <v/>
-      </c>
-      <c r="G52" s="33">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H52" s="9">
-        <f>ROUND(D52*G52,0)</f>
-        <v/>
-      </c>
-      <c r="I52" s="9">
-        <f>ROUND(G22*F52*G52,0)</f>
-        <v/>
-      </c>
-      <c r="J52" s="9">
-        <f>ROUND(H22*F52,0)</f>
-        <v/>
-      </c>
-      <c r="K52" s="9">
-        <f>ROUND(I22*F52,0)</f>
-        <v/>
-      </c>
-      <c r="L52" s="35">
-        <f>H52+I52+J52+K52</f>
-        <v/>
-      </c>
-      <c r="M52" s="115" t="n"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>CPO681</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.11</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D53" s="33" t="n">
-        <v>26358</v>
-      </c>
-      <c r="E53" s="33" t="n">
-        <v>26358</v>
-      </c>
-      <c r="F53" s="108">
-        <f>D53/E53</f>
-        <v/>
-      </c>
-      <c r="G53" s="33">
-        <f>F23</f>
-        <v/>
-      </c>
-      <c r="H53" s="9">
-        <f>ROUND(D53*G53,0)</f>
-        <v/>
-      </c>
-      <c r="I53" s="9">
-        <f>ROUND(G23*F53*G53,0)</f>
-        <v/>
-      </c>
-      <c r="J53" s="9">
-        <f>ROUND(H23*F53,0)</f>
-        <v/>
-      </c>
-      <c r="K53" s="9">
-        <f>ROUND(I23*F53,0)</f>
-        <v/>
-      </c>
-      <c r="L53" s="35">
-        <f>H53+I53+J53+K53</f>
-        <v/>
-      </c>
-      <c r="M53" s="115" t="n"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>CPO686</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.19</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D54" s="33" t="n">
-        <v>14793</v>
-      </c>
-      <c r="E54" s="33" t="n">
-        <v>17538</v>
-      </c>
-      <c r="F54" s="108">
-        <f>D54/E54</f>
-        <v/>
-      </c>
-      <c r="G54" s="33">
-        <f>F24</f>
-        <v/>
-      </c>
-      <c r="H54" s="9">
-        <f>ROUND(D54*G54,0)</f>
-        <v/>
-      </c>
-      <c r="I54" s="9">
-        <f>ROUND(G24*F54*G54,0)</f>
-        <v/>
-      </c>
-      <c r="J54" s="9">
-        <f>ROUND(H24*F54,0)</f>
-        <v/>
-      </c>
-      <c r="K54" s="9">
-        <f>ROUND(I24*F54,0)</f>
-        <v/>
-      </c>
-      <c r="L54" s="35">
-        <f>H54+I54+J54+K54</f>
-        <v/>
-      </c>
-      <c r="M54" s="115" t="n"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>CPO689</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.19</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D55" s="33" t="n">
-        <v>2745</v>
-      </c>
-      <c r="E55" s="33" t="n">
-        <v>17538</v>
-      </c>
-      <c r="F55" s="108">
-        <f>D55/E55</f>
-        <v/>
-      </c>
-      <c r="G55" s="33">
-        <f>F24</f>
-        <v/>
-      </c>
-      <c r="H55" s="9">
-        <f>ROUND(D55*G55,0)</f>
-        <v/>
-      </c>
-      <c r="I55" s="9">
-        <f>ROUND(G24*F55*G55,0)</f>
-        <v/>
-      </c>
-      <c r="J55" s="9">
-        <f>ROUND(H24*F55,0)</f>
-        <v/>
-      </c>
-      <c r="K55" s="9">
-        <f>ROUND(I24*F55,0)</f>
-        <v/>
-      </c>
-      <c r="L55" s="35">
-        <f>H55+I55+J55+K55</f>
-        <v/>
-      </c>
-      <c r="M55" s="115" t="n"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>CPO667</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.27</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D56" s="33" t="n">
-        <v>5673</v>
-      </c>
-      <c r="E56" s="33" t="n">
-        <v>142189</v>
-      </c>
-      <c r="F56" s="108">
-        <f>D56/E56</f>
-        <v/>
-      </c>
-      <c r="G56" s="33">
-        <f>F25</f>
-        <v/>
-      </c>
-      <c r="H56" s="9">
-        <f>ROUND(D56*G56,0)</f>
-        <v/>
-      </c>
-      <c r="I56" s="9">
-        <f>ROUND(G25*F56*G56,0)</f>
-        <v/>
-      </c>
-      <c r="J56" s="9">
-        <f>ROUND(H25*F56,0)</f>
-        <v/>
-      </c>
-      <c r="K56" s="9">
-        <f>ROUND(I25*F56,0)</f>
-        <v/>
-      </c>
-      <c r="L56" s="35">
-        <f>H56+I56+J56+K56</f>
-        <v/>
-      </c>
-      <c r="M56" s="115" t="n"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>CPO685</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>2026.02.27</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D57" s="33" t="n">
-        <v>136516</v>
-      </c>
-      <c r="E57" s="33" t="n">
-        <v>142189</v>
-      </c>
-      <c r="F57" s="108">
-        <f>D57/E57</f>
-        <v/>
-      </c>
-      <c r="G57" s="33">
-        <f>F25</f>
-        <v/>
-      </c>
-      <c r="H57" s="9">
-        <f>ROUND(D57*G57,0)</f>
-        <v/>
-      </c>
-      <c r="I57" s="9">
-        <f>ROUND(G25*F57*G57,0)</f>
-        <v/>
-      </c>
-      <c r="J57" s="9">
-        <f>ROUND(H25*F57,0)</f>
-        <v/>
-      </c>
-      <c r="K57" s="9">
-        <f>ROUND(I25*F57,0)</f>
-        <v/>
-      </c>
-      <c r="L57" s="35">
-        <f>H57+I57+J57+K57</f>
-        <v/>
-      </c>
-      <c r="M57" s="115" t="n"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>CPO678-2</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>2026.03.06</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D58" s="33" t="n">
-        <v>137850</v>
-      </c>
-      <c r="E58" s="33" t="n">
-        <v>137850</v>
-      </c>
-      <c r="F58" s="108">
-        <f>D58/E58</f>
-        <v/>
-      </c>
-      <c r="G58" s="33">
-        <f>F26</f>
-        <v/>
-      </c>
-      <c r="H58" s="9">
-        <f>ROUND(D58*G58,0)</f>
-        <v/>
-      </c>
-      <c r="I58" s="9">
-        <f>ROUND(G26*F58*G58,0)</f>
-        <v/>
-      </c>
-      <c r="J58" s="9">
-        <f>ROUND(H26*F58,0)</f>
-        <v/>
-      </c>
-      <c r="K58" s="9">
-        <f>ROUND(I26*F58,0)</f>
-        <v/>
-      </c>
-      <c r="L58" s="35">
-        <f>H58+I58+J58+K58</f>
-        <v/>
-      </c>
-      <c r="M58" s="115" t="n"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>CPO690</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D59" s="33" t="n">
-        <v>9740</v>
-      </c>
-      <c r="E59" s="33" t="n">
-        <v>34354</v>
-      </c>
-      <c r="F59" s="108">
-        <f>D59/E59</f>
-        <v/>
-      </c>
-      <c r="G59" s="33">
-        <f>F27</f>
-        <v/>
-      </c>
-      <c r="H59" s="9">
-        <f>ROUND(D59*G59,0)</f>
-        <v/>
-      </c>
-      <c r="I59" s="9">
-        <f>ROUND(G27*F59*G59,0)</f>
-        <v/>
-      </c>
-      <c r="J59" s="9">
-        <f>ROUND(H27*F59,0)</f>
-        <v/>
-      </c>
-      <c r="K59" s="9">
-        <f>ROUND(I27*F59,0)</f>
-        <v/>
-      </c>
-      <c r="L59" s="35">
-        <f>H59+I59+J59+K59</f>
-        <v/>
-      </c>
-      <c r="M59" s="115" t="n"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>CPO691</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D60" s="33" t="n">
-        <v>24614</v>
-      </c>
-      <c r="E60" s="33" t="n">
-        <v>34354</v>
-      </c>
-      <c r="F60" s="108">
-        <f>D60/E60</f>
-        <v/>
-      </c>
-      <c r="G60" s="33">
-        <f>F27</f>
-        <v/>
-      </c>
-      <c r="H60" s="9">
-        <f>ROUND(D60*G60,0)</f>
-        <v/>
-      </c>
-      <c r="I60" s="9">
-        <f>ROUND(G27*F60*G60,0)</f>
-        <v/>
-      </c>
-      <c r="J60" s="9">
-        <f>ROUND(H27*F60,0)</f>
-        <v/>
-      </c>
-      <c r="K60" s="9">
-        <f>ROUND(I27*F60,0)</f>
-        <v/>
-      </c>
-      <c r="L60" s="35">
-        <f>H60+I60+J60+K60</f>
-        <v/>
-      </c>
-      <c r="M60" s="115" t="n"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>GPO467</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D61" s="33" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E61" s="33" t="n">
-        <v>6553.05</v>
-      </c>
-      <c r="F61" s="108">
-        <f>D61/E61</f>
-        <v/>
-      </c>
-      <c r="G61" s="33">
-        <f>F28</f>
-        <v/>
-      </c>
-      <c r="H61" s="9">
-        <f>ROUND(D61*G61,0)</f>
-        <v/>
-      </c>
-      <c r="I61" s="9">
-        <f>ROUND(G28*F61*G61,0)</f>
-        <v/>
-      </c>
-      <c r="J61" s="9">
-        <f>ROUND(H28*F61,0)</f>
-        <v/>
-      </c>
-      <c r="K61" s="9">
-        <f>ROUND(I28*F61,0)</f>
-        <v/>
-      </c>
-      <c r="L61" s="35">
-        <f>H61+I61+J61+K61</f>
-        <v/>
-      </c>
-      <c r="M61" s="115" t="n"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>GPO469</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D62" s="33" t="n">
-        <v>3993.05</v>
-      </c>
-      <c r="E62" s="33" t="n">
-        <v>6553.05</v>
-      </c>
-      <c r="F62" s="108">
-        <f>D62/E62</f>
-        <v/>
-      </c>
-      <c r="G62" s="33">
-        <f>F28</f>
-        <v/>
-      </c>
-      <c r="H62" s="9">
-        <f>ROUND(D62*G62,0)</f>
-        <v/>
-      </c>
-      <c r="I62" s="9">
-        <f>ROUND(G28*F62*G62,0)</f>
-        <v/>
-      </c>
-      <c r="J62" s="9">
-        <f>ROUND(H28*F62,0)</f>
-        <v/>
-      </c>
-      <c r="K62" s="9">
-        <f>ROUND(I28*F62,0)</f>
-        <v/>
-      </c>
-      <c r="L62" s="35">
-        <f>H62+I62+J62+K62</f>
-        <v/>
-      </c>
-      <c r="M62" s="115" t="n"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>GPO470</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D63" s="33" t="n">
-        <v>360</v>
-      </c>
-      <c r="E63" s="33" t="n">
-        <v>6553.05</v>
-      </c>
-      <c r="F63" s="108">
-        <f>D63/E63</f>
-        <v/>
-      </c>
-      <c r="G63" s="33">
-        <f>F28</f>
-        <v/>
-      </c>
-      <c r="H63" s="9">
-        <f>ROUND(D63*G63,0)</f>
-        <v/>
-      </c>
-      <c r="I63" s="9">
-        <f>ROUND(G28*F63*G63,0)</f>
-        <v/>
-      </c>
-      <c r="J63" s="9">
-        <f>ROUND(H28*F63,0)</f>
-        <v/>
-      </c>
-      <c r="K63" s="9">
-        <f>ROUND(I28*F63,0)</f>
-        <v/>
-      </c>
-      <c r="L63" s="35">
-        <f>H63+I63+J63+K63</f>
-        <v/>
-      </c>
-      <c r="M63" s="115" t="n"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>GPO471</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D64" s="33" t="n">
-        <v>500</v>
-      </c>
-      <c r="E64" s="33" t="n">
-        <v>6553.05</v>
-      </c>
-      <c r="F64" s="108">
-        <f>D64/E64</f>
-        <v/>
-      </c>
-      <c r="G64" s="33">
-        <f>F28</f>
-        <v/>
-      </c>
-      <c r="H64" s="9">
-        <f>ROUND(D64*G64,0)</f>
-        <v/>
-      </c>
-      <c r="I64" s="9">
-        <f>ROUND(G28*F64*G64,0)</f>
-        <v/>
-      </c>
-      <c r="J64" s="9">
-        <f>ROUND(H28*F64,0)</f>
-        <v/>
-      </c>
-      <c r="K64" s="9">
-        <f>ROUND(I28*F64,0)</f>
-        <v/>
-      </c>
-      <c r="L64" s="35">
-        <f>H64+I64+J64+K64</f>
-        <v/>
-      </c>
-      <c r="M64" s="115" t="n"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>GPO468-1</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.14</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D65" s="33" t="n">
-        <v>36190</v>
-      </c>
-      <c r="E65" s="33" t="n">
+      <c r="D71" s="118" t="n">
+        <v>180</v>
+      </c>
+      <c r="E71" s="118" t="n">
         <v>57650</v>
-      </c>
-      <c r="F65" s="108">
-        <f>D65/E65</f>
-        <v/>
-      </c>
-      <c r="G65" s="33">
-        <f>F29</f>
-        <v/>
-      </c>
-      <c r="H65" s="9">
-        <f>ROUND(D65*G65,0)</f>
-        <v/>
-      </c>
-      <c r="I65" s="9">
-        <f>ROUND(G29*F65*G65,0)</f>
-        <v/>
-      </c>
-      <c r="J65" s="9">
-        <f>ROUND(H29*F65,0)</f>
-        <v/>
-      </c>
-      <c r="K65" s="9">
-        <f>ROUND(I29*F65,0)</f>
-        <v/>
-      </c>
-      <c r="L65" s="35">
-        <f>H65+I65+J65+K65</f>
-        <v/>
-      </c>
-      <c r="M65" s="115" t="n"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>GPO472</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.14</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D66" s="33" t="n">
-        <v>180</v>
-      </c>
-      <c r="E66" s="33" t="n">
-        <v>57650</v>
-      </c>
-      <c r="F66" s="108">
-        <f>D66/E66</f>
-        <v/>
-      </c>
-      <c r="G66" s="33">
-        <f>F29</f>
-        <v/>
-      </c>
-      <c r="H66" s="9">
-        <f>ROUND(D66*G66,0)</f>
-        <v/>
-      </c>
-      <c r="I66" s="9">
-        <f>ROUND(G29*F66*G66,0)</f>
-        <v/>
-      </c>
-      <c r="J66" s="9">
-        <f>ROUND(H29*F66,0)</f>
-        <v/>
-      </c>
-      <c r="K66" s="9">
-        <f>ROUND(I29*F66,0)</f>
-        <v/>
-      </c>
-      <c r="L66" s="35">
-        <f>H66+I66+J66+K66</f>
-        <v/>
-      </c>
-      <c r="M66" s="115" t="n"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>GPO468-2</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.14</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D67" s="33" t="n">
-        <v>21280</v>
-      </c>
-      <c r="E67" s="33" t="n">
-        <v>57650</v>
-      </c>
-      <c r="F67" s="108">
-        <f>D67/E67</f>
-        <v/>
-      </c>
-      <c r="G67" s="33">
-        <f>F29</f>
-        <v/>
-      </c>
-      <c r="H67" s="9">
-        <f>ROUND(D67*G67,0)</f>
-        <v/>
-      </c>
-      <c r="I67" s="9">
-        <f>ROUND(G29*F67*G67,0)</f>
-        <v/>
-      </c>
-      <c r="J67" s="9">
-        <f>ROUND(H29*F67,0)</f>
-        <v/>
-      </c>
-      <c r="K67" s="9">
-        <f>ROUND(I29*F67,0)</f>
-        <v/>
-      </c>
-      <c r="L67" s="35">
-        <f>H67+I67+J67+K67</f>
-        <v/>
-      </c>
-      <c r="M67" s="115" t="n"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="96" t="inlineStr">
-        <is>
-          <t>CPO692-1</t>
-        </is>
-      </c>
-      <c r="B68" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C68" s="97" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D68" s="98" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E68" s="98" t="n">
-        <v>297580</v>
-      </c>
-      <c r="F68" s="109">
-        <f>D68/E68</f>
-        <v/>
-      </c>
-      <c r="G68" s="98">
-        <f>F33</f>
-        <v/>
-      </c>
-      <c r="H68" s="99">
-        <f>ROUND(D68*G68,0)</f>
-        <v/>
-      </c>
-      <c r="I68" s="99">
-        <f>ROUND(G33*F68*G68,0)</f>
-        <v/>
-      </c>
-      <c r="J68" s="99">
-        <f>ROUND(H33*F68,0)</f>
-        <v/>
-      </c>
-      <c r="K68" s="99">
-        <f>ROUND(I33*F68,0)</f>
-        <v/>
-      </c>
-      <c r="L68" s="100">
-        <f>H68+I68+J68+K68</f>
-        <v/>
-      </c>
-      <c r="M68" s="115" t="n"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="96" t="inlineStr">
-        <is>
-          <t>CPO692-2</t>
-        </is>
-      </c>
-      <c r="B69" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C69" s="97" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D69" s="98" t="n">
-        <v>286580</v>
-      </c>
-      <c r="E69" s="98" t="n">
-        <v>297580</v>
-      </c>
-      <c r="F69" s="109">
-        <f>D69/E69</f>
-        <v/>
-      </c>
-      <c r="G69" s="98">
-        <f>F33</f>
-        <v/>
-      </c>
-      <c r="H69" s="99">
-        <f>ROUND(D69*G69,0)</f>
-        <v/>
-      </c>
-      <c r="I69" s="99">
-        <f>ROUND(G33*F69*G69,0)</f>
-        <v/>
-      </c>
-      <c r="J69" s="99">
-        <f>ROUND(H33*F69,0)</f>
-        <v/>
-      </c>
-      <c r="K69" s="99">
-        <f>ROUND(I33*F69,0)</f>
-        <v/>
-      </c>
-      <c r="L69" s="100">
-        <f>H69+I69+J69+K69</f>
-        <v/>
-      </c>
-      <c r="M69" s="115" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="96" t="inlineStr">
-        <is>
-          <t>EPO18</t>
-        </is>
-      </c>
-      <c r="B70" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C70" s="97" t="inlineStr">
-        <is>
-          <t>MAICO Italia</t>
-        </is>
-      </c>
-      <c r="D70" s="98" t="n">
-        <v>4388.4</v>
-      </c>
-      <c r="E70" s="98" t="n">
-        <v>4388.4</v>
-      </c>
-      <c r="F70" s="109">
-        <f>D70/E70</f>
-        <v/>
-      </c>
-      <c r="G70" s="98">
-        <f>F34</f>
-        <v/>
-      </c>
-      <c r="H70" s="99">
-        <f>ROUND(D70*G70,0)</f>
-        <v/>
-      </c>
-      <c r="I70" s="99">
-        <f>ROUND(G34*F70*G70,0)</f>
-        <v/>
-      </c>
-      <c r="J70" s="99">
-        <f>ROUND(H34*F70,0)</f>
-        <v/>
-      </c>
-      <c r="K70" s="99">
-        <f>ROUND(I34*F70,0)</f>
-        <v/>
-      </c>
-      <c r="L70" s="100">
-        <f>H70+I70+J70+K70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="116" t="inlineStr">
-        <is>
-          <t>CPO694</t>
-        </is>
-      </c>
-      <c r="B71" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.04</t>
-        </is>
-      </c>
-      <c r="C71" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D71" s="118" t="n">
-        <v>17404</v>
-      </c>
-      <c r="E71" s="118" t="n">
-        <v>21439</v>
       </c>
       <c r="F71" s="122">
         <f>D71/E71</f>
         <v/>
       </c>
       <c r="G71" s="118">
-        <f>F33</f>
+        <f>F27</f>
         <v/>
       </c>
       <c r="H71" s="120">
@@ -15641,50 +15599,51 @@
         <v/>
       </c>
       <c r="I71" s="120">
-        <f>ROUND(G33*F71*G71,0)</f>
+        <f>ROUND(G27*F71*G71,0)</f>
         <v/>
       </c>
       <c r="J71" s="120">
-        <f>ROUND(H33*F71,0)</f>
+        <f>ROUND(H27*F71,0)</f>
         <v/>
       </c>
       <c r="K71" s="120">
-        <f>ROUND(I33*F71,0)</f>
+        <f>ROUND(I27*F71,0)</f>
         <v/>
       </c>
       <c r="L71" s="121">
         <f>H71+I71+J71+K71</f>
         <v/>
       </c>
-    </row>
-    <row r="72">
+      <c r="M71" s="115" t="n"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="116" t="inlineStr">
         <is>
-          <t>CPO695-1</t>
+          <t>GPO468-2</t>
         </is>
       </c>
       <c r="B72" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C72" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D72" s="118" t="n">
-        <v>2058</v>
+        <v>21280</v>
       </c>
       <c r="E72" s="118" t="n">
-        <v>21439</v>
+        <v>57650</v>
       </c>
       <c r="F72" s="122">
         <f>D72/E72</f>
         <v/>
       </c>
       <c r="G72" s="118">
-        <f>F33</f>
+        <f>F27</f>
         <v/>
       </c>
       <c r="H72" s="120">
@@ -15692,31 +15651,32 @@
         <v/>
       </c>
       <c r="I72" s="120">
-        <f>ROUND(G33*F72*G72,0)</f>
+        <f>ROUND(G27*F72*G72,0)</f>
         <v/>
       </c>
       <c r="J72" s="120">
-        <f>ROUND(H33*F72,0)</f>
+        <f>ROUND(H27*F72,0)</f>
         <v/>
       </c>
       <c r="K72" s="120">
-        <f>ROUND(I33*F72,0)</f>
+        <f>ROUND(I27*F72,0)</f>
         <v/>
       </c>
       <c r="L72" s="121">
         <f>H72+I72+J72+K72</f>
         <v/>
       </c>
-    </row>
-    <row r="73">
+      <c r="M72" s="115" t="n"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="116" t="inlineStr">
         <is>
-          <t>CPO695-2</t>
+          <t>CPO692-1</t>
         </is>
       </c>
       <c r="B73" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C73" s="117" t="inlineStr">
@@ -15725,17 +15685,17 @@
         </is>
       </c>
       <c r="D73" s="118" t="n">
-        <v>1977</v>
+        <v>11000</v>
       </c>
       <c r="E73" s="118" t="n">
-        <v>21439</v>
+        <v>297580</v>
       </c>
       <c r="F73" s="122">
         <f>D73/E73</f>
         <v/>
       </c>
       <c r="G73" s="118">
-        <f>F33</f>
+        <f>F31</f>
         <v/>
       </c>
       <c r="H73" s="120">
@@ -15743,50 +15703,51 @@
         <v/>
       </c>
       <c r="I73" s="120">
-        <f>ROUND(G33*F73*G73,0)</f>
+        <f>ROUND(G31*F73*G73,0)</f>
         <v/>
       </c>
       <c r="J73" s="120">
-        <f>ROUND(H33*F73,0)</f>
+        <f>ROUND(H31*F73,0)</f>
         <v/>
       </c>
       <c r="K73" s="120">
-        <f>ROUND(I33*F73,0)</f>
+        <f>ROUND(I31*F73,0)</f>
         <v/>
       </c>
       <c r="L73" s="121">
         <f>H73+I73+J73+K73</f>
         <v/>
       </c>
-    </row>
-    <row r="74">
+      <c r="M73" s="115" t="n"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="116" t="inlineStr">
         <is>
-          <t>IPO016</t>
+          <t>CPO692-2</t>
         </is>
       </c>
       <c r="B74" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C74" s="117" t="inlineStr">
         <is>
-          <t>Integ</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D74" s="118" t="n">
-        <v>6800</v>
+        <v>286580</v>
       </c>
       <c r="E74" s="118" t="n">
-        <v>6800</v>
+        <v>297580</v>
       </c>
       <c r="F74" s="122">
         <f>D74/E74</f>
         <v/>
       </c>
       <c r="G74" s="118">
-        <f>F34</f>
+        <f>F31</f>
         <v/>
       </c>
       <c r="H74" s="120">
@@ -15794,29 +15755,691 @@
         <v/>
       </c>
       <c r="I74" s="120">
-        <f>ROUND(G34*F74*G74,0)</f>
+        <f>ROUND(G31*F74*G74,0)</f>
         <v/>
       </c>
       <c r="J74" s="120">
-        <f>ROUND(H34*F74,0)</f>
+        <f>ROUND(H31*F74,0)</f>
         <v/>
       </c>
       <c r="K74" s="120">
-        <f>ROUND(I34*F74,0)</f>
+        <f>ROUND(I31*F74,0)</f>
         <v/>
       </c>
       <c r="L74" s="121">
         <f>H74+I74+J74+K74</f>
         <v/>
       </c>
-    </row>
-    <row r="76">
-      <c r="M76" s="40" t="n"/>
+      <c r="M74" s="115" t="n"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="116" t="inlineStr">
+        <is>
+          <t>EPO18</t>
+        </is>
+      </c>
+      <c r="B75" s="116" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C75" s="117" t="inlineStr">
+        <is>
+          <t>MAICO Italia</t>
+        </is>
+      </c>
+      <c r="D75" s="118" t="n">
+        <v>4388.4</v>
+      </c>
+      <c r="E75" s="118" t="n">
+        <v>4388.4</v>
+      </c>
+      <c r="F75" s="122">
+        <f>D75/E75</f>
+        <v/>
+      </c>
+      <c r="G75" s="118">
+        <f>F32</f>
+        <v/>
+      </c>
+      <c r="H75" s="120">
+        <f>ROUND(D75*G75,0)</f>
+        <v/>
+      </c>
+      <c r="I75" s="120">
+        <f>ROUND(G32*F75*G75,0)</f>
+        <v/>
+      </c>
+      <c r="J75" s="120">
+        <f>ROUND(H32*F75,0)</f>
+        <v/>
+      </c>
+      <c r="K75" s="120">
+        <f>ROUND(I32*F75,0)</f>
+        <v/>
+      </c>
+      <c r="L75" s="121">
+        <f>H75+I75+J75+K75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="116" t="inlineStr">
+        <is>
+          <t>CPO694</t>
+        </is>
+      </c>
+      <c r="B76" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.04</t>
+        </is>
+      </c>
+      <c r="C76" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D76" s="118" t="n">
+        <v>17404</v>
+      </c>
+      <c r="E76" s="118" t="n">
+        <v>21439</v>
+      </c>
+      <c r="F76" s="122">
+        <f>D76/E76</f>
+        <v/>
+      </c>
+      <c r="G76" s="118">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="H76" s="120">
+        <f>ROUND(D76*G76,0)</f>
+        <v/>
+      </c>
+      <c r="I76" s="120">
+        <f>ROUND(G33*F76*G76,0)</f>
+        <v/>
+      </c>
+      <c r="J76" s="120">
+        <f>ROUND(H33*F76,0)</f>
+        <v/>
+      </c>
+      <c r="K76" s="120">
+        <f>ROUND(I33*F76,0)</f>
+        <v/>
+      </c>
+      <c r="L76" s="121">
+        <f>H76+I76+J76+K76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="116" t="inlineStr">
+        <is>
+          <t>CPO695-1</t>
+        </is>
+      </c>
+      <c r="B77" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.04</t>
+        </is>
+      </c>
+      <c r="C77" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D77" s="118" t="n">
+        <v>2058</v>
+      </c>
+      <c r="E77" s="118" t="n">
+        <v>21439</v>
+      </c>
+      <c r="F77" s="122">
+        <f>D77/E77</f>
+        <v/>
+      </c>
+      <c r="G77" s="118">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="H77" s="120">
+        <f>ROUND(D77*G77,0)</f>
+        <v/>
+      </c>
+      <c r="I77" s="120">
+        <f>ROUND(G33*F77*G77,0)</f>
+        <v/>
+      </c>
+      <c r="J77" s="120">
+        <f>ROUND(H33*F77,0)</f>
+        <v/>
+      </c>
+      <c r="K77" s="120">
+        <f>ROUND(I33*F77,0)</f>
+        <v/>
+      </c>
+      <c r="L77" s="121">
+        <f>H77+I77+J77+K77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="116" t="inlineStr">
+        <is>
+          <t>CPO695-2</t>
+        </is>
+      </c>
+      <c r="B78" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.04</t>
+        </is>
+      </c>
+      <c r="C78" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D78" s="118" t="n">
+        <v>1977</v>
+      </c>
+      <c r="E78" s="118" t="n">
+        <v>21439</v>
+      </c>
+      <c r="F78" s="122">
+        <f>D78/E78</f>
+        <v/>
+      </c>
+      <c r="G78" s="118">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="H78" s="120">
+        <f>ROUND(D78*G78,0)</f>
+        <v/>
+      </c>
+      <c r="I78" s="120">
+        <f>ROUND(G33*F78*G78,0)</f>
+        <v/>
+      </c>
+      <c r="J78" s="120">
+        <f>ROUND(H33*F78,0)</f>
+        <v/>
+      </c>
+      <c r="K78" s="120">
+        <f>ROUND(I33*F78,0)</f>
+        <v/>
+      </c>
+      <c r="L78" s="121">
+        <f>H78+I78+J78+K78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="116" t="inlineStr">
+        <is>
+          <t>IPO016</t>
+        </is>
+      </c>
+      <c r="B79" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.04</t>
+        </is>
+      </c>
+      <c r="C79" s="117" t="inlineStr">
+        <is>
+          <t>Integ</t>
+        </is>
+      </c>
+      <c r="D79" s="118" t="n">
+        <v>6800</v>
+      </c>
+      <c r="E79" s="118" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F79" s="122">
+        <f>D79/E79</f>
+        <v/>
+      </c>
+      <c r="G79" s="118">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="H79" s="120">
+        <f>ROUND(D79*G79,0)</f>
+        <v/>
+      </c>
+      <c r="I79" s="120">
+        <f>ROUND(G34*F79*G79,0)</f>
+        <v/>
+      </c>
+      <c r="J79" s="120">
+        <f>ROUND(H34*F79,0)</f>
+        <v/>
+      </c>
+      <c r="K79" s="120">
+        <f>ROUND(I34*F79,0)</f>
+        <v/>
+      </c>
+      <c r="L79" s="121">
+        <f>H79+I79+J79+K79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="116" t="inlineStr">
+        <is>
+          <t>GPO478</t>
+        </is>
+      </c>
+      <c r="B80" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.19</t>
+        </is>
+      </c>
+      <c r="C80" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D80" s="118" t="n">
+        <v>180</v>
+      </c>
+      <c r="E80" s="118" t="n">
+        <v>180</v>
+      </c>
+      <c r="F80" s="122">
+        <f>D80/E80</f>
+        <v/>
+      </c>
+      <c r="G80" s="118">
+        <f>F36</f>
+        <v/>
+      </c>
+      <c r="H80" s="120">
+        <f>ROUND(D80*G80,0)</f>
+        <v/>
+      </c>
+      <c r="I80" s="120">
+        <f>ROUND(G36*F80*G80,0)</f>
+        <v/>
+      </c>
+      <c r="J80" s="120">
+        <f>ROUND(H36*F80,0)</f>
+        <v/>
+      </c>
+      <c r="K80" s="120">
+        <f>ROUND(I36*F80,0)</f>
+        <v/>
+      </c>
+      <c r="L80" s="121">
+        <f>H80+I80+J80+K80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="116" t="inlineStr">
+        <is>
+          <t>CPO698</t>
+        </is>
+      </c>
+      <c r="B81" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.20</t>
+        </is>
+      </c>
+      <c r="C81" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D81" s="118" t="n">
+        <v>4290</v>
+      </c>
+      <c r="E81" s="118" t="n">
+        <v>4290</v>
+      </c>
+      <c r="F81" s="122">
+        <f>D81/E81</f>
+        <v/>
+      </c>
+      <c r="G81" s="118">
+        <f>F37</f>
+        <v/>
+      </c>
+      <c r="H81" s="120">
+        <f>ROUND(D81*G81,0)</f>
+        <v/>
+      </c>
+      <c r="I81" s="120">
+        <f>ROUND(G37*F81*G81,0)</f>
+        <v/>
+      </c>
+      <c r="J81" s="120">
+        <f>ROUND(H37*F81,0)</f>
+        <v/>
+      </c>
+      <c r="K81" s="120">
+        <f>ROUND(I37*F81,0)</f>
+        <v/>
+      </c>
+      <c r="L81" s="121">
+        <f>H81+I81+J81+K81</f>
+        <v/>
+      </c>
+      <c r="M81" s="40" t="n"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="116" t="inlineStr">
+        <is>
+          <t>GPO473-1</t>
+        </is>
+      </c>
+      <c r="B82" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C82" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D82" s="118" t="n">
+        <v>98800</v>
+      </c>
+      <c r="E82" s="118" t="n">
+        <v>99140</v>
+      </c>
+      <c r="F82" s="122">
+        <f>D82/E82</f>
+        <v/>
+      </c>
+      <c r="G82" s="118">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="H82" s="120">
+        <f>ROUND(D82*G82,0)</f>
+        <v/>
+      </c>
+      <c r="I82" s="120">
+        <f>ROUND(G38*F82*G82,0)</f>
+        <v/>
+      </c>
+      <c r="J82" s="120">
+        <f>ROUND(H38*F82,0)</f>
+        <v/>
+      </c>
+      <c r="K82" s="120">
+        <f>ROUND(I38*F82,0)</f>
+        <v/>
+      </c>
+      <c r="L82" s="121">
+        <f>H82+I82+J82+K82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="116" t="inlineStr">
+        <is>
+          <t>GPO480</t>
+        </is>
+      </c>
+      <c r="B83" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C83" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D83" s="118" t="n">
+        <v>250</v>
+      </c>
+      <c r="E83" s="118" t="n">
+        <v>99140</v>
+      </c>
+      <c r="F83" s="122">
+        <f>D83/E83</f>
+        <v/>
+      </c>
+      <c r="G83" s="118">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="H83" s="120">
+        <f>ROUND(D83*G83,0)</f>
+        <v/>
+      </c>
+      <c r="I83" s="120">
+        <f>ROUND(G38*F83*G83,0)</f>
+        <v/>
+      </c>
+      <c r="J83" s="120">
+        <f>ROUND(H38*F83,0)</f>
+        <v/>
+      </c>
+      <c r="K83" s="120">
+        <f>ROUND(I38*F83,0)</f>
+        <v/>
+      </c>
+      <c r="L83" s="121">
+        <f>H83+I83+J83+K83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="116" t="inlineStr">
+        <is>
+          <t>GPO479</t>
+        </is>
+      </c>
+      <c r="B84" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C84" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D84" s="118" t="n">
+        <v>90</v>
+      </c>
+      <c r="E84" s="118" t="n">
+        <v>99140</v>
+      </c>
+      <c r="F84" s="122">
+        <f>D84/E84</f>
+        <v/>
+      </c>
+      <c r="G84" s="118">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="H84" s="120">
+        <f>ROUND(D84*G84,0)</f>
+        <v/>
+      </c>
+      <c r="I84" s="120">
+        <f>ROUND(G38*F84*G84,0)</f>
+        <v/>
+      </c>
+      <c r="J84" s="120">
+        <f>ROUND(H38*F84,0)</f>
+        <v/>
+      </c>
+      <c r="K84" s="120">
+        <f>ROUND(I38*F84,0)</f>
+        <v/>
+      </c>
+      <c r="L84" s="121">
+        <f>H84+I84+J84+K84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="116" t="inlineStr">
+        <is>
+          <t>CPO697</t>
+        </is>
+      </c>
+      <c r="B85" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C85" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D85" s="118" t="n">
+        <v>15289</v>
+      </c>
+      <c r="E85" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F85" s="122">
+        <f>D85/E85</f>
+        <v/>
+      </c>
+      <c r="G85" s="118">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="H85" s="120">
+        <f>ROUND(D85*G85,0)</f>
+        <v/>
+      </c>
+      <c r="I85" s="120">
+        <f>ROUND(G39*F85*G85,0)</f>
+        <v/>
+      </c>
+      <c r="J85" s="120">
+        <f>ROUND(H39*F85,0)</f>
+        <v/>
+      </c>
+      <c r="K85" s="120">
+        <f>ROUND(I39*F85,0)</f>
+        <v/>
+      </c>
+      <c r="L85" s="121">
+        <f>H85+I85+J85+K85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="116" t="inlineStr">
+        <is>
+          <t>CPO696-1</t>
+        </is>
+      </c>
+      <c r="B86" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C86" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D86" s="118" t="n">
+        <v>78209</v>
+      </c>
+      <c r="E86" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F86" s="122">
+        <f>D86/E86</f>
+        <v/>
+      </c>
+      <c r="G86" s="118">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="H86" s="120">
+        <f>ROUND(D86*G86,0)</f>
+        <v/>
+      </c>
+      <c r="I86" s="120">
+        <f>ROUND(G39*F86*G86,0)</f>
+        <v/>
+      </c>
+      <c r="J86" s="120">
+        <f>ROUND(H39*F86,0)</f>
+        <v/>
+      </c>
+      <c r="K86" s="120">
+        <f>ROUND(I39*F86,0)</f>
+        <v/>
+      </c>
+      <c r="L86" s="121">
+        <f>H86+I86+J86+K86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="116" t="inlineStr">
+        <is>
+          <t>CPO696-2</t>
+        </is>
+      </c>
+      <c r="B87" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C87" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D87" s="118" t="n">
+        <v>8140</v>
+      </c>
+      <c r="E87" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F87" s="122">
+        <f>D87/E87</f>
+        <v/>
+      </c>
+      <c r="G87" s="118">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="H87" s="120">
+        <f>ROUND(D87*G87,0)</f>
+        <v/>
+      </c>
+      <c r="I87" s="120">
+        <f>ROUND(G39*F87*G87,0)</f>
+        <v/>
+      </c>
+      <c r="J87" s="120">
+        <f>ROUND(H39*F87,0)</f>
+        <v/>
+      </c>
+      <c r="K87" s="120">
+        <f>ROUND(I39*F87,0)</f>
+        <v/>
+      </c>
+      <c r="L87" s="121">
+        <f>H87+I87+J87+K87</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A40:L40"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A35:L35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -15875,7 +16498,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="163" t="inlineStr">
         <is>
-          <t>기준일: 2026-04-20  |  미상환 건만 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
+          <t>기준일: 2026-06-02  |  미상환 건만 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
         </is>
       </c>
     </row>
@@ -17822,7 +18445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -17865,7 +18488,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="205" t="inlineStr">
         <is>
-          <t>업데이트: 2026-05-28 (관세청 고시환율)</t>
+          <t>업데이트: 2026-06-02 (관세청 고시환율)</t>
         </is>
       </c>
       <c r="B4" s="148" t="n"/>
@@ -18437,6 +19060,22 @@
       </c>
       <c r="D40" s="211" t="n">
         <v>1504.04</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="210" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B41" s="210" t="n">
+        <v>46179</v>
+      </c>
+      <c r="C41" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D41" s="211" t="n">
+        <v>1507.15</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" tabRatio="500" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PO별 개당 수입원가" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라이센스_워런티" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="합배송_비용안분" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화송금내역" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usance_LC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PO별 개당 수입원가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="라이센스_워런티" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="합배송_비용안분" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="외화송금내역" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Usance_LC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$39</definedName>
-    <definedName name="RemitTable2">'외화송금내역'!$A$42:$L$87</definedName>
-    <definedName name="FxRateTable">'환율'!$A$7:$D$41</definedName>
+    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$40</definedName>
+    <definedName name="RemitTable2">'외화송금내역'!$A$43:$L$91</definedName>
+    <definedName name="FxRateTable">'환율'!$A$7:$D$42</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,11 +24,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0&quot;일&quot;"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -432,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1100,6 +1101,30 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="20" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1546,7 +1571,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-06-02  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-06-10  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="148" t="n"/>
@@ -5834,10 +5859,8 @@
       <c r="F37" s="209" t="n">
         <v>46113</v>
       </c>
-      <c r="G37" s="210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G37" s="210" t="n">
+        <v>46183</v>
       </c>
       <c r="H37" s="211" t="n">
         <v>69160</v>
@@ -5955,10 +5978,8 @@
       <c r="F38" s="209" t="n">
         <v>46113</v>
       </c>
-      <c r="G38" s="210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G38" s="210" t="n">
+        <v>46183</v>
       </c>
       <c r="H38" s="211" t="n">
         <v>49400</v>
@@ -8763,10 +8784,8 @@
       <c r="F60" s="188" t="n">
         <v>46152</v>
       </c>
-      <c r="G60" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G60" s="233" t="n">
+        <v>46183</v>
       </c>
       <c r="H60" s="134" t="n">
         <v>500</v>
@@ -8835,7 +8854,11 @@
         <f>ROUND(AA60/AB60,0)</f>
         <v/>
       </c>
-      <c r="AD60" s="137" t="n"/>
+      <c r="AD60" s="137" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
       <c r="AE60" s="137" t="n"/>
       <c r="AF60" s="137" t="n"/>
     </row>
@@ -10825,10 +10848,8 @@
       <c r="G24" s="227" t="n">
         <v>46152</v>
       </c>
-      <c r="H24" s="227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H24" s="227" t="n">
+        <v>46183</v>
       </c>
       <c r="I24" s="227" t="inlineStr">
         <is>
@@ -12142,7 +12163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="160" min="1" max="1"/>
@@ -13975,143 +13996,137 @@
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="169" t="inlineStr">
+      <c r="A40" s="234" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C40" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D40" s="234" t="inlineStr">
+        <is>
+          <t>GPO481, GPO473-2, GPO473-3</t>
+        </is>
+      </c>
+      <c r="E40" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F40" s="237" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="G40" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H40" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I40" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J40" s="238" t="n">
+        <v>181653224</v>
+      </c>
+      <c r="K40" s="238">
+        <f>ROUND((E40+G40)*F40+H40+I40,0)</f>
+        <v/>
+      </c>
+      <c r="L40" s="239">
+        <f>J40-K40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="169" t="inlineStr">
         <is>
           <t>② PO별 비용 안분 내역</t>
         </is>
       </c>
-      <c r="B40" s="148" t="n"/>
-      <c r="C40" s="148" t="n"/>
-      <c r="D40" s="148" t="n"/>
-      <c r="E40" s="148" t="n"/>
-      <c r="F40" s="148" t="n"/>
-      <c r="G40" s="148" t="n"/>
-      <c r="H40" s="148" t="n"/>
-      <c r="I40" s="148" t="n"/>
-      <c r="J40" s="148" t="n"/>
-      <c r="K40" s="148" t="n"/>
-      <c r="L40" s="149" t="n"/>
-      <c r="M40" s="115" t="n"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="150" t="inlineStr">
+      <c r="B41" s="148" t="n"/>
+      <c r="C41" s="148" t="n"/>
+      <c r="D41" s="148" t="n"/>
+      <c r="E41" s="148" t="n"/>
+      <c r="F41" s="148" t="n"/>
+      <c r="G41" s="148" t="n"/>
+      <c r="H41" s="148" t="n"/>
+      <c r="I41" s="148" t="n"/>
+      <c r="J41" s="148" t="n"/>
+      <c r="K41" s="148" t="n"/>
+      <c r="L41" s="149" t="n"/>
+      <c r="M41" s="115" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="150" t="inlineStr">
         <is>
           <t>PO No.</t>
         </is>
       </c>
-      <c r="B41" s="150" t="inlineStr">
+      <c r="B42" s="150" t="inlineStr">
         <is>
           <t>송금일</t>
         </is>
       </c>
-      <c r="C41" s="150" t="inlineStr">
+      <c r="C42" s="150" t="inlineStr">
         <is>
           <t>업체</t>
         </is>
       </c>
-      <c r="D41" s="150" t="inlineStr">
+      <c r="D42" s="150" t="inlineStr">
         <is>
           <t>PO USD</t>
         </is>
       </c>
-      <c r="E41" s="150" t="inlineStr">
+      <c r="E42" s="150" t="inlineStr">
         <is>
           <t>그룹총USD</t>
         </is>
       </c>
-      <c r="F41" s="150" t="inlineStr">
+      <c r="F42" s="150" t="inlineStr">
         <is>
           <t>배부비율</t>
         </is>
       </c>
-      <c r="G41" s="150" t="inlineStr">
+      <c r="G42" s="150" t="inlineStr">
         <is>
           <t>적용환율</t>
         </is>
       </c>
-      <c r="H41" s="150" t="inlineStr">
+      <c r="H42" s="150" t="inlineStr">
         <is>
           <t>원화환산액</t>
         </is>
       </c>
-      <c r="I41" s="150" t="inlineStr">
+      <c r="I42" s="150" t="inlineStr">
         <is>
           <t>중개수수료안분</t>
         </is>
       </c>
-      <c r="J41" s="150" t="inlineStr">
+      <c r="J42" s="150" t="inlineStr">
         <is>
           <t>수수료안분</t>
         </is>
       </c>
-      <c r="K41" s="150" t="inlineStr">
+      <c r="K42" s="150" t="inlineStr">
         <is>
           <t>전신료안분</t>
         </is>
       </c>
-      <c r="L41" s="150" t="inlineStr">
+      <c r="L42" s="150" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
-      </c>
-      <c r="M41" s="115" t="n"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="116" t="inlineStr">
-        <is>
-          <t>CPO678-1</t>
-        </is>
-      </c>
-      <c r="B42" s="116" t="inlineStr">
-        <is>
-          <t>2025.12.16</t>
-        </is>
-      </c>
-      <c r="C42" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D42" s="118" t="n">
-        <v>139083</v>
-      </c>
-      <c r="E42" s="118" t="n">
-        <v>143557</v>
-      </c>
-      <c r="F42" s="122">
-        <f>D42/E42</f>
-        <v/>
-      </c>
-      <c r="G42" s="118">
-        <f>F10</f>
-        <v/>
-      </c>
-      <c r="H42" s="120">
-        <f>ROUND(D42*G42,0)</f>
-        <v/>
-      </c>
-      <c r="I42" s="120">
-        <f>ROUND(G10*F42*G42,0)</f>
-        <v/>
-      </c>
-      <c r="J42" s="120">
-        <f>ROUND(H10*F42,0)</f>
-        <v/>
-      </c>
-      <c r="K42" s="120">
-        <f>ROUND(I10*F42,0)</f>
-        <v/>
-      </c>
-      <c r="L42" s="121">
-        <f>H42+I42+J42+K42</f>
-        <v/>
       </c>
       <c r="M42" s="115" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="116" t="inlineStr">
         <is>
-          <t>CPO679</t>
+          <t>CPO678-1</t>
         </is>
       </c>
       <c r="B43" s="116" t="inlineStr">
@@ -14125,7 +14140,7 @@
         </is>
       </c>
       <c r="D43" s="118" t="n">
-        <v>4474</v>
+        <v>139083</v>
       </c>
       <c r="E43" s="118" t="n">
         <v>143557</v>
@@ -14163,7 +14178,7 @@
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="116" t="inlineStr">
         <is>
-          <t>MPO65</t>
+          <t>CPO679</t>
         </is>
       </c>
       <c r="B44" s="116" t="inlineStr">
@@ -14173,21 +14188,21 @@
       </c>
       <c r="C44" s="117" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D44" s="118" t="n">
-        <v>4936</v>
+        <v>4474</v>
       </c>
       <c r="E44" s="118" t="n">
-        <v>15040</v>
+        <v>143557</v>
       </c>
       <c r="F44" s="122">
         <f>D44/E44</f>
         <v/>
       </c>
       <c r="G44" s="118">
-        <f>F9</f>
+        <f>F10</f>
         <v/>
       </c>
       <c r="H44" s="120">
@@ -14195,15 +14210,15 @@
         <v/>
       </c>
       <c r="I44" s="120">
-        <f>ROUND(G9*F44*G44,0)</f>
+        <f>ROUND(G10*F44*G44,0)</f>
         <v/>
       </c>
       <c r="J44" s="120">
-        <f>ROUND(H9*F44,0)</f>
+        <f>ROUND(H10*F44,0)</f>
         <v/>
       </c>
       <c r="K44" s="120">
-        <f>ROUND(I9*F44,0)</f>
+        <f>ROUND(I10*F44,0)</f>
         <v/>
       </c>
       <c r="L44" s="121">
@@ -14215,31 +14230,31 @@
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="116" t="inlineStr">
         <is>
-          <t>GPO451</t>
+          <t>MPO65</t>
         </is>
       </c>
       <c r="B45" s="116" t="inlineStr">
         <is>
-          <t>2025.12.29</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="C45" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D45" s="118" t="n">
-        <v>9060</v>
+        <v>4936</v>
       </c>
       <c r="E45" s="118" t="n">
-        <v>13860</v>
+        <v>15040</v>
       </c>
       <c r="F45" s="122">
         <f>D45/E45</f>
         <v/>
       </c>
       <c r="G45" s="118">
-        <f>F12</f>
+        <f>F9</f>
         <v/>
       </c>
       <c r="H45" s="120">
@@ -14247,15 +14262,15 @@
         <v/>
       </c>
       <c r="I45" s="120">
-        <f>ROUND(G12*F45*G45,0)</f>
+        <f>ROUND(G9*F45*G45,0)</f>
         <v/>
       </c>
       <c r="J45" s="120">
-        <f>ROUND(H12*F45,0)</f>
+        <f>ROUND(H9*F45,0)</f>
         <v/>
       </c>
       <c r="K45" s="120">
-        <f>ROUND(I12*F45,0)</f>
+        <f>ROUND(I9*F45,0)</f>
         <v/>
       </c>
       <c r="L45" s="121">
@@ -14267,7 +14282,7 @@
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="116" t="inlineStr">
         <is>
-          <t>GPO458</t>
+          <t>GPO451</t>
         </is>
       </c>
       <c r="B46" s="116" t="inlineStr">
@@ -14281,7 +14296,7 @@
         </is>
       </c>
       <c r="D46" s="118" t="n">
-        <v>350</v>
+        <v>9060</v>
       </c>
       <c r="E46" s="118" t="n">
         <v>13860</v>
@@ -14319,31 +14334,31 @@
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="116" t="inlineStr">
         <is>
-          <t>CPO680</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="B47" s="116" t="inlineStr">
         <is>
-          <t>2026.01.13</t>
+          <t>2025.12.29</t>
         </is>
       </c>
       <c r="C47" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D47" s="118" t="n">
-        <v>252</v>
+        <v>350</v>
       </c>
       <c r="E47" s="118" t="n">
-        <v>252</v>
+        <v>13860</v>
       </c>
       <c r="F47" s="122">
         <f>D47/E47</f>
         <v/>
       </c>
       <c r="G47" s="118">
-        <f>F14</f>
+        <f>F12</f>
         <v/>
       </c>
       <c r="H47" s="120">
@@ -14351,15 +14366,15 @@
         <v/>
       </c>
       <c r="I47" s="120">
-        <f>ROUND(G14*F47*G47,0)</f>
+        <f>ROUND(G12*F47*G47,0)</f>
         <v/>
       </c>
       <c r="J47" s="120">
-        <f>ROUND(H14*F47,0)</f>
+        <f>ROUND(H12*F47,0)</f>
         <v/>
       </c>
       <c r="K47" s="120">
-        <f>ROUND(I14*F47,0)</f>
+        <f>ROUND(I12*F47,0)</f>
         <v/>
       </c>
       <c r="L47" s="121">
@@ -14371,31 +14386,31 @@
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="116" t="inlineStr">
         <is>
-          <t>GPO459</t>
+          <t>CPO680</t>
         </is>
       </c>
       <c r="B48" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.01.13</t>
         </is>
       </c>
       <c r="C48" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D48" s="118" t="n">
-        <v>450</v>
+        <v>252</v>
       </c>
       <c r="E48" s="118" t="n">
-        <v>3700</v>
+        <v>252</v>
       </c>
       <c r="F48" s="122">
         <f>D48/E48</f>
         <v/>
       </c>
       <c r="G48" s="118">
-        <f>F15</f>
+        <f>F14</f>
         <v/>
       </c>
       <c r="H48" s="120">
@@ -14403,15 +14418,15 @@
         <v/>
       </c>
       <c r="I48" s="120">
-        <f>ROUND(G15*F48*G48,0)</f>
+        <f>ROUND(G14*F48*G48,0)</f>
         <v/>
       </c>
       <c r="J48" s="120">
-        <f>ROUND(H15*F48,0)</f>
+        <f>ROUND(H14*F48,0)</f>
         <v/>
       </c>
       <c r="K48" s="120">
-        <f>ROUND(I15*F48,0)</f>
+        <f>ROUND(I14*F48,0)</f>
         <v/>
       </c>
       <c r="L48" s="121">
@@ -14423,7 +14438,7 @@
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="116" t="inlineStr">
         <is>
-          <t>GPO460</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="B49" s="116" t="inlineStr">
@@ -14437,7 +14452,7 @@
         </is>
       </c>
       <c r="D49" s="118" t="n">
-        <v>2710</v>
+        <v>450</v>
       </c>
       <c r="E49" s="118" t="n">
         <v>3700</v>
@@ -14475,7 +14490,7 @@
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="116" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>GPO460</t>
         </is>
       </c>
       <c r="B50" s="116" t="inlineStr">
@@ -14489,7 +14504,7 @@
         </is>
       </c>
       <c r="D50" s="118" t="n">
-        <v>540</v>
+        <v>2710</v>
       </c>
       <c r="E50" s="118" t="n">
         <v>3700</v>
@@ -14527,7 +14542,7 @@
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="116" t="inlineStr">
         <is>
-          <t>MPO66</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="B51" s="116" t="inlineStr">
@@ -14537,21 +14552,21 @@
       </c>
       <c r="C51" s="117" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D51" s="118" t="n">
-        <v>9626.35</v>
+        <v>540</v>
       </c>
       <c r="E51" s="118" t="n">
-        <v>9626.35</v>
+        <v>3700</v>
       </c>
       <c r="F51" s="122">
         <f>D51/E51</f>
         <v/>
       </c>
       <c r="G51" s="118">
-        <f>F16</f>
+        <f>F15</f>
         <v/>
       </c>
       <c r="H51" s="120">
@@ -14559,15 +14574,15 @@
         <v/>
       </c>
       <c r="I51" s="120">
-        <f>ROUND(G16*F51*G51,0)</f>
+        <f>ROUND(G15*F51*G51,0)</f>
         <v/>
       </c>
       <c r="J51" s="120">
-        <f>ROUND(H16*F51,0)</f>
+        <f>ROUND(H15*F51,0)</f>
         <v/>
       </c>
       <c r="K51" s="120">
-        <f>ROUND(I16*F51,0)</f>
+        <f>ROUND(I15*F51,0)</f>
         <v/>
       </c>
       <c r="L51" s="121">
@@ -14579,31 +14594,31 @@
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="116" t="inlineStr">
         <is>
-          <t>LPO001</t>
+          <t>MPO66</t>
         </is>
       </c>
       <c r="B52" s="116" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C52" s="117" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D52" s="118" t="n">
-        <v>5056.8</v>
+        <v>9626.35</v>
       </c>
       <c r="E52" s="118" t="n">
-        <v>5056.8</v>
+        <v>9626.35</v>
       </c>
       <c r="F52" s="122">
         <f>D52/E52</f>
         <v/>
       </c>
       <c r="G52" s="118">
-        <f>F17</f>
+        <f>F16</f>
         <v/>
       </c>
       <c r="H52" s="120">
@@ -14611,15 +14626,15 @@
         <v/>
       </c>
       <c r="I52" s="120">
-        <f>ROUND(G17*F52*G52,0)</f>
+        <f>ROUND(G16*F52*G52,0)</f>
         <v/>
       </c>
       <c r="J52" s="120">
-        <f>ROUND(H17*F52,0)</f>
+        <f>ROUND(H16*F52,0)</f>
         <v/>
       </c>
       <c r="K52" s="120">
-        <f>ROUND(I17*F52,0)</f>
+        <f>ROUND(I16*F52,0)</f>
         <v/>
       </c>
       <c r="L52" s="121">
@@ -14631,31 +14646,31 @@
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="116" t="inlineStr">
         <is>
-          <t>CPO682</t>
+          <t>LPO001</t>
         </is>
       </c>
       <c r="B53" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="C53" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D53" s="118" t="n">
-        <v>20174</v>
+        <v>5056.8</v>
       </c>
       <c r="E53" s="118" t="n">
-        <v>24794</v>
+        <v>5056.8</v>
       </c>
       <c r="F53" s="122">
         <f>D53/E53</f>
         <v/>
       </c>
       <c r="G53" s="118">
-        <f>F19</f>
+        <f>F17</f>
         <v/>
       </c>
       <c r="H53" s="120">
@@ -14663,15 +14678,15 @@
         <v/>
       </c>
       <c r="I53" s="120">
-        <f>ROUND(G19*F53*G53,0)</f>
+        <f>ROUND(G17*F53*G53,0)</f>
         <v/>
       </c>
       <c r="J53" s="120">
-        <f>ROUND(H19*F53,0)</f>
+        <f>ROUND(H17*F53,0)</f>
         <v/>
       </c>
       <c r="K53" s="120">
-        <f>ROUND(I19*F53,0)</f>
+        <f>ROUND(I17*F53,0)</f>
         <v/>
       </c>
       <c r="L53" s="121">
@@ -14683,7 +14698,7 @@
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="116" t="inlineStr">
         <is>
-          <t>CPO683</t>
+          <t>CPO682</t>
         </is>
       </c>
       <c r="B54" s="116" t="inlineStr">
@@ -14697,7 +14712,7 @@
         </is>
       </c>
       <c r="D54" s="118" t="n">
-        <v>4620</v>
+        <v>20174</v>
       </c>
       <c r="E54" s="118" t="n">
         <v>24794</v>
@@ -14735,7 +14750,7 @@
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="116" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>CPO683</t>
         </is>
       </c>
       <c r="B55" s="116" t="inlineStr">
@@ -14745,21 +14760,21 @@
       </c>
       <c r="C55" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D55" s="118" t="n">
-        <v>1440</v>
+        <v>4620</v>
       </c>
       <c r="E55" s="118" t="n">
-        <v>11599.57</v>
+        <v>24794</v>
       </c>
       <c r="F55" s="122">
         <f>D55/E55</f>
         <v/>
       </c>
       <c r="G55" s="118">
-        <f>F20</f>
+        <f>F19</f>
         <v/>
       </c>
       <c r="H55" s="120">
@@ -14767,15 +14782,15 @@
         <v/>
       </c>
       <c r="I55" s="120">
-        <f>ROUND(G20*F55*G55,0)</f>
+        <f>ROUND(G19*F55*G55,0)</f>
         <v/>
       </c>
       <c r="J55" s="120">
-        <f>ROUND(H20*F55,0)</f>
+        <f>ROUND(H19*F55,0)</f>
         <v/>
       </c>
       <c r="K55" s="120">
-        <f>ROUND(I20*F55,0)</f>
+        <f>ROUND(I19*F55,0)</f>
         <v/>
       </c>
       <c r="L55" s="121">
@@ -14787,7 +14802,7 @@
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="116" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="B56" s="116" t="inlineStr">
@@ -14801,7 +14816,7 @@
         </is>
       </c>
       <c r="D56" s="118" t="n">
-        <v>4489</v>
+        <v>1440</v>
       </c>
       <c r="E56" s="118" t="n">
         <v>11599.57</v>
@@ -14839,7 +14854,7 @@
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="116" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="B57" s="116" t="inlineStr">
@@ -14853,7 +14868,7 @@
         </is>
       </c>
       <c r="D57" s="118" t="n">
-        <v>5670.57</v>
+        <v>4489</v>
       </c>
       <c r="E57" s="118" t="n">
         <v>11599.57</v>
@@ -14891,31 +14906,31 @@
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="116" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="B58" s="116" t="inlineStr">
         <is>
-          <t>2026.02.11</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C58" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D58" s="118" t="n">
-        <v>26358</v>
+        <v>5670.57</v>
       </c>
       <c r="E58" s="118" t="n">
-        <v>26358</v>
+        <v>11599.57</v>
       </c>
       <c r="F58" s="122">
         <f>D58/E58</f>
         <v/>
       </c>
       <c r="G58" s="118">
-        <f>F21</f>
+        <f>F20</f>
         <v/>
       </c>
       <c r="H58" s="120">
@@ -14923,15 +14938,15 @@
         <v/>
       </c>
       <c r="I58" s="120">
-        <f>ROUND(G21*F58*G58,0)</f>
+        <f>ROUND(G20*F58*G58,0)</f>
         <v/>
       </c>
       <c r="J58" s="120">
-        <f>ROUND(H21*F58,0)</f>
+        <f>ROUND(H20*F58,0)</f>
         <v/>
       </c>
       <c r="K58" s="120">
-        <f>ROUND(I21*F58,0)</f>
+        <f>ROUND(I20*F58,0)</f>
         <v/>
       </c>
       <c r="L58" s="121">
@@ -14943,12 +14958,12 @@
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="116" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="B59" s="116" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.02.11</t>
         </is>
       </c>
       <c r="C59" s="117" t="inlineStr">
@@ -14957,17 +14972,17 @@
         </is>
       </c>
       <c r="D59" s="118" t="n">
-        <v>14793</v>
+        <v>26358</v>
       </c>
       <c r="E59" s="118" t="n">
-        <v>17538</v>
+        <v>26358</v>
       </c>
       <c r="F59" s="122">
         <f>D59/E59</f>
         <v/>
       </c>
       <c r="G59" s="118">
-        <f>F22</f>
+        <f>F21</f>
         <v/>
       </c>
       <c r="H59" s="120">
@@ -14975,15 +14990,15 @@
         <v/>
       </c>
       <c r="I59" s="120">
-        <f>ROUND(G22*F59*G59,0)</f>
+        <f>ROUND(G21*F59*G59,0)</f>
         <v/>
       </c>
       <c r="J59" s="120">
-        <f>ROUND(H22*F59,0)</f>
+        <f>ROUND(H21*F59,0)</f>
         <v/>
       </c>
       <c r="K59" s="120">
-        <f>ROUND(I22*F59,0)</f>
+        <f>ROUND(I21*F59,0)</f>
         <v/>
       </c>
       <c r="L59" s="121">
@@ -14995,7 +15010,7 @@
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="116" t="inlineStr">
         <is>
-          <t>CPO689</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="B60" s="116" t="inlineStr">
@@ -15009,7 +15024,7 @@
         </is>
       </c>
       <c r="D60" s="118" t="n">
-        <v>2745</v>
+        <v>14793</v>
       </c>
       <c r="E60" s="118" t="n">
         <v>17538</v>
@@ -15047,12 +15062,12 @@
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="116" t="inlineStr">
         <is>
-          <t>CPO667</t>
+          <t>CPO689</t>
         </is>
       </c>
       <c r="B61" s="116" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C61" s="117" t="inlineStr">
@@ -15061,17 +15076,17 @@
         </is>
       </c>
       <c r="D61" s="118" t="n">
-        <v>5673</v>
+        <v>2745</v>
       </c>
       <c r="E61" s="118" t="n">
-        <v>142189</v>
+        <v>17538</v>
       </c>
       <c r="F61" s="122">
         <f>D61/E61</f>
         <v/>
       </c>
       <c r="G61" s="118">
-        <f>F23</f>
+        <f>F22</f>
         <v/>
       </c>
       <c r="H61" s="120">
@@ -15079,15 +15094,15 @@
         <v/>
       </c>
       <c r="I61" s="120">
-        <f>ROUND(G23*F61*G61,0)</f>
+        <f>ROUND(G22*F61*G61,0)</f>
         <v/>
       </c>
       <c r="J61" s="120">
-        <f>ROUND(H23*F61,0)</f>
+        <f>ROUND(H22*F61,0)</f>
         <v/>
       </c>
       <c r="K61" s="120">
-        <f>ROUND(I23*F61,0)</f>
+        <f>ROUND(I22*F61,0)</f>
         <v/>
       </c>
       <c r="L61" s="121">
@@ -15099,7 +15114,7 @@
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="116" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="B62" s="116" t="inlineStr">
@@ -15113,7 +15128,7 @@
         </is>
       </c>
       <c r="D62" s="118" t="n">
-        <v>136516</v>
+        <v>5673</v>
       </c>
       <c r="E62" s="118" t="n">
         <v>142189</v>
@@ -15151,12 +15166,12 @@
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="116" t="inlineStr">
         <is>
-          <t>CPO678-2</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="B63" s="116" t="inlineStr">
         <is>
-          <t>2026.03.06</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C63" s="117" t="inlineStr">
@@ -15165,17 +15180,17 @@
         </is>
       </c>
       <c r="D63" s="118" t="n">
-        <v>137850</v>
+        <v>136516</v>
       </c>
       <c r="E63" s="118" t="n">
-        <v>137850</v>
+        <v>142189</v>
       </c>
       <c r="F63" s="122">
         <f>D63/E63</f>
         <v/>
       </c>
       <c r="G63" s="118">
-        <f>F24</f>
+        <f>F23</f>
         <v/>
       </c>
       <c r="H63" s="120">
@@ -15183,15 +15198,15 @@
         <v/>
       </c>
       <c r="I63" s="120">
-        <f>ROUND(G24*F63*G63,0)</f>
+        <f>ROUND(G23*F63*G63,0)</f>
         <v/>
       </c>
       <c r="J63" s="120">
-        <f>ROUND(H24*F63,0)</f>
+        <f>ROUND(H23*F63,0)</f>
         <v/>
       </c>
       <c r="K63" s="120">
-        <f>ROUND(I24*F63,0)</f>
+        <f>ROUND(I23*F63,0)</f>
         <v/>
       </c>
       <c r="L63" s="121">
@@ -15203,12 +15218,12 @@
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="116" t="inlineStr">
         <is>
-          <t>CPO690</t>
+          <t>CPO678-2</t>
         </is>
       </c>
       <c r="B64" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.03.06</t>
         </is>
       </c>
       <c r="C64" s="117" t="inlineStr">
@@ -15217,17 +15232,17 @@
         </is>
       </c>
       <c r="D64" s="118" t="n">
-        <v>9740</v>
+        <v>137850</v>
       </c>
       <c r="E64" s="118" t="n">
-        <v>34354</v>
+        <v>137850</v>
       </c>
       <c r="F64" s="122">
         <f>D64/E64</f>
         <v/>
       </c>
       <c r="G64" s="118">
-        <f>F25</f>
+        <f>F24</f>
         <v/>
       </c>
       <c r="H64" s="120">
@@ -15235,15 +15250,15 @@
         <v/>
       </c>
       <c r="I64" s="120">
-        <f>ROUND(G25*F64*G64,0)</f>
+        <f>ROUND(G24*F64*G64,0)</f>
         <v/>
       </c>
       <c r="J64" s="120">
-        <f>ROUND(H25*F64,0)</f>
+        <f>ROUND(H24*F64,0)</f>
         <v/>
       </c>
       <c r="K64" s="120">
-        <f>ROUND(I25*F64,0)</f>
+        <f>ROUND(I24*F64,0)</f>
         <v/>
       </c>
       <c r="L64" s="121">
@@ -15255,7 +15270,7 @@
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="116" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>CPO690</t>
         </is>
       </c>
       <c r="B65" s="116" t="inlineStr">
@@ -15269,7 +15284,7 @@
         </is>
       </c>
       <c r="D65" s="118" t="n">
-        <v>24614</v>
+        <v>9740</v>
       </c>
       <c r="E65" s="118" t="n">
         <v>34354</v>
@@ -15307,7 +15322,7 @@
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="116" t="inlineStr">
         <is>
-          <t>GPO467</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="B66" s="116" t="inlineStr">
@@ -15317,21 +15332,21 @@
       </c>
       <c r="C66" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D66" s="118" t="n">
-        <v>1700</v>
+        <v>24614</v>
       </c>
       <c r="E66" s="118" t="n">
-        <v>6553.05</v>
+        <v>34354</v>
       </c>
       <c r="F66" s="122">
         <f>D66/E66</f>
         <v/>
       </c>
       <c r="G66" s="118">
-        <f>F26</f>
+        <f>F25</f>
         <v/>
       </c>
       <c r="H66" s="120">
@@ -15339,15 +15354,15 @@
         <v/>
       </c>
       <c r="I66" s="120">
-        <f>ROUND(G26*F66*G66,0)</f>
+        <f>ROUND(G25*F66*G66,0)</f>
         <v/>
       </c>
       <c r="J66" s="120">
-        <f>ROUND(H26*F66,0)</f>
+        <f>ROUND(H25*F66,0)</f>
         <v/>
       </c>
       <c r="K66" s="120">
-        <f>ROUND(I26*F66,0)</f>
+        <f>ROUND(I25*F66,0)</f>
         <v/>
       </c>
       <c r="L66" s="121">
@@ -15359,7 +15374,7 @@
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="116" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>GPO467</t>
         </is>
       </c>
       <c r="B67" s="116" t="inlineStr">
@@ -15373,7 +15388,7 @@
         </is>
       </c>
       <c r="D67" s="118" t="n">
-        <v>3993.05</v>
+        <v>1700</v>
       </c>
       <c r="E67" s="118" t="n">
         <v>6553.05</v>
@@ -15411,7 +15426,7 @@
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="116" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>GPO469</t>
         </is>
       </c>
       <c r="B68" s="116" t="inlineStr">
@@ -15425,7 +15440,7 @@
         </is>
       </c>
       <c r="D68" s="118" t="n">
-        <v>360</v>
+        <v>3993.05</v>
       </c>
       <c r="E68" s="118" t="n">
         <v>6553.05</v>
@@ -15463,7 +15478,7 @@
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="116" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>GPO470</t>
         </is>
       </c>
       <c r="B69" s="116" t="inlineStr">
@@ -15477,7 +15492,7 @@
         </is>
       </c>
       <c r="D69" s="118" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="E69" s="118" t="n">
         <v>6553.05</v>
@@ -15515,12 +15530,12 @@
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="116" t="inlineStr">
         <is>
-          <t>GPO468-1</t>
+          <t>GPO471</t>
         </is>
       </c>
       <c r="B70" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C70" s="117" t="inlineStr">
@@ -15529,17 +15544,17 @@
         </is>
       </c>
       <c r="D70" s="118" t="n">
-        <v>36190</v>
+        <v>500</v>
       </c>
       <c r="E70" s="118" t="n">
-        <v>57650</v>
+        <v>6553.05</v>
       </c>
       <c r="F70" s="122">
         <f>D70/E70</f>
         <v/>
       </c>
       <c r="G70" s="118">
-        <f>F27</f>
+        <f>F26</f>
         <v/>
       </c>
       <c r="H70" s="120">
@@ -15547,15 +15562,15 @@
         <v/>
       </c>
       <c r="I70" s="120">
-        <f>ROUND(G27*F70*G70,0)</f>
+        <f>ROUND(G26*F70*G70,0)</f>
         <v/>
       </c>
       <c r="J70" s="120">
-        <f>ROUND(H27*F70,0)</f>
+        <f>ROUND(H26*F70,0)</f>
         <v/>
       </c>
       <c r="K70" s="120">
-        <f>ROUND(I27*F70,0)</f>
+        <f>ROUND(I26*F70,0)</f>
         <v/>
       </c>
       <c r="L70" s="121">
@@ -15567,7 +15582,7 @@
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="116" t="inlineStr">
         <is>
-          <t>GPO472</t>
+          <t>GPO468-1</t>
         </is>
       </c>
       <c r="B71" s="116" t="inlineStr">
@@ -15581,7 +15596,7 @@
         </is>
       </c>
       <c r="D71" s="118" t="n">
-        <v>180</v>
+        <v>36190</v>
       </c>
       <c r="E71" s="118" t="n">
         <v>57650</v>
@@ -15619,7 +15634,7 @@
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="116" t="inlineStr">
         <is>
-          <t>GPO468-2</t>
+          <t>GPO472</t>
         </is>
       </c>
       <c r="B72" s="116" t="inlineStr">
@@ -15633,7 +15648,7 @@
         </is>
       </c>
       <c r="D72" s="118" t="n">
-        <v>21280</v>
+        <v>180</v>
       </c>
       <c r="E72" s="118" t="n">
         <v>57650</v>
@@ -15671,31 +15686,31 @@
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="116" t="inlineStr">
         <is>
-          <t>CPO692-1</t>
+          <t>GPO468-2</t>
         </is>
       </c>
       <c r="B73" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C73" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D73" s="118" t="n">
-        <v>11000</v>
+        <v>21280</v>
       </c>
       <c r="E73" s="118" t="n">
-        <v>297580</v>
+        <v>57650</v>
       </c>
       <c r="F73" s="122">
         <f>D73/E73</f>
         <v/>
       </c>
       <c r="G73" s="118">
-        <f>F31</f>
+        <f>F27</f>
         <v/>
       </c>
       <c r="H73" s="120">
@@ -15703,15 +15718,15 @@
         <v/>
       </c>
       <c r="I73" s="120">
-        <f>ROUND(G31*F73*G73,0)</f>
+        <f>ROUND(G27*F73*G73,0)</f>
         <v/>
       </c>
       <c r="J73" s="120">
-        <f>ROUND(H31*F73,0)</f>
+        <f>ROUND(H27*F73,0)</f>
         <v/>
       </c>
       <c r="K73" s="120">
-        <f>ROUND(I31*F73,0)</f>
+        <f>ROUND(I27*F73,0)</f>
         <v/>
       </c>
       <c r="L73" s="121">
@@ -15723,7 +15738,7 @@
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="116" t="inlineStr">
         <is>
-          <t>CPO692-2</t>
+          <t>CPO692-1</t>
         </is>
       </c>
       <c r="B74" s="116" t="inlineStr">
@@ -15737,7 +15752,7 @@
         </is>
       </c>
       <c r="D74" s="118" t="n">
-        <v>286580</v>
+        <v>11000</v>
       </c>
       <c r="E74" s="118" t="n">
         <v>297580</v>
@@ -15775,7 +15790,7 @@
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="116" t="inlineStr">
         <is>
-          <t>EPO18</t>
+          <t>CPO692-2</t>
         </is>
       </c>
       <c r="B75" s="116" t="inlineStr">
@@ -15785,21 +15800,21 @@
       </c>
       <c r="C75" s="117" t="inlineStr">
         <is>
-          <t>MAICO Italia</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D75" s="118" t="n">
-        <v>4388.4</v>
+        <v>286580</v>
       </c>
       <c r="E75" s="118" t="n">
-        <v>4388.4</v>
+        <v>297580</v>
       </c>
       <c r="F75" s="122">
         <f>D75/E75</f>
         <v/>
       </c>
       <c r="G75" s="118">
-        <f>F32</f>
+        <f>F31</f>
         <v/>
       </c>
       <c r="H75" s="120">
@@ -15807,50 +15822,51 @@
         <v/>
       </c>
       <c r="I75" s="120">
-        <f>ROUND(G32*F75*G75,0)</f>
+        <f>ROUND(G31*F75*G75,0)</f>
         <v/>
       </c>
       <c r="J75" s="120">
-        <f>ROUND(H32*F75,0)</f>
+        <f>ROUND(H31*F75,0)</f>
         <v/>
       </c>
       <c r="K75" s="120">
-        <f>ROUND(I32*F75,0)</f>
+        <f>ROUND(I31*F75,0)</f>
         <v/>
       </c>
       <c r="L75" s="121">
         <f>H75+I75+J75+K75</f>
         <v/>
       </c>
+      <c r="M75" s="115" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="116" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>EPO18</t>
         </is>
       </c>
       <c r="B76" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C76" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>MAICO Italia</t>
         </is>
       </c>
       <c r="D76" s="118" t="n">
-        <v>17404</v>
+        <v>4388.4</v>
       </c>
       <c r="E76" s="118" t="n">
-        <v>21439</v>
+        <v>4388.4</v>
       </c>
       <c r="F76" s="122">
         <f>D76/E76</f>
         <v/>
       </c>
       <c r="G76" s="118">
-        <f>F33</f>
+        <f>F32</f>
         <v/>
       </c>
       <c r="H76" s="120">
@@ -15858,15 +15874,15 @@
         <v/>
       </c>
       <c r="I76" s="120">
-        <f>ROUND(G33*F76*G76,0)</f>
+        <f>ROUND(G32*F76*G76,0)</f>
         <v/>
       </c>
       <c r="J76" s="120">
-        <f>ROUND(H33*F76,0)</f>
+        <f>ROUND(H32*F76,0)</f>
         <v/>
       </c>
       <c r="K76" s="120">
-        <f>ROUND(I33*F76,0)</f>
+        <f>ROUND(I32*F76,0)</f>
         <v/>
       </c>
       <c r="L76" s="121">
@@ -15877,7 +15893,7 @@
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="116" t="inlineStr">
         <is>
-          <t>CPO695-1</t>
+          <t>CPO694</t>
         </is>
       </c>
       <c r="B77" s="116" t="inlineStr">
@@ -15891,7 +15907,7 @@
         </is>
       </c>
       <c r="D77" s="118" t="n">
-        <v>2058</v>
+        <v>17404</v>
       </c>
       <c r="E77" s="118" t="n">
         <v>21439</v>
@@ -15928,7 +15944,7 @@
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="116" t="inlineStr">
         <is>
-          <t>CPO695-2</t>
+          <t>CPO695-1</t>
         </is>
       </c>
       <c r="B78" s="116" t="inlineStr">
@@ -15942,7 +15958,7 @@
         </is>
       </c>
       <c r="D78" s="118" t="n">
-        <v>1977</v>
+        <v>2058</v>
       </c>
       <c r="E78" s="118" t="n">
         <v>21439</v>
@@ -15979,7 +15995,7 @@
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="116" t="inlineStr">
         <is>
-          <t>IPO016</t>
+          <t>CPO695-2</t>
         </is>
       </c>
       <c r="B79" s="116" t="inlineStr">
@@ -15989,21 +16005,21 @@
       </c>
       <c r="C79" s="117" t="inlineStr">
         <is>
-          <t>Integ</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D79" s="118" t="n">
-        <v>6800</v>
+        <v>1977</v>
       </c>
       <c r="E79" s="118" t="n">
-        <v>6800</v>
+        <v>21439</v>
       </c>
       <c r="F79" s="122">
         <f>D79/E79</f>
         <v/>
       </c>
       <c r="G79" s="118">
-        <f>F34</f>
+        <f>F33</f>
         <v/>
       </c>
       <c r="H79" s="120">
@@ -16011,15 +16027,15 @@
         <v/>
       </c>
       <c r="I79" s="120">
-        <f>ROUND(G34*F79*G79,0)</f>
+        <f>ROUND(G33*F79*G79,0)</f>
         <v/>
       </c>
       <c r="J79" s="120">
-        <f>ROUND(H34*F79,0)</f>
+        <f>ROUND(H33*F79,0)</f>
         <v/>
       </c>
       <c r="K79" s="120">
-        <f>ROUND(I34*F79,0)</f>
+        <f>ROUND(I33*F79,0)</f>
         <v/>
       </c>
       <c r="L79" s="121">
@@ -16030,31 +16046,31 @@
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="116" t="inlineStr">
         <is>
-          <t>GPO478</t>
+          <t>IPO016</t>
         </is>
       </c>
       <c r="B80" s="116" t="inlineStr">
         <is>
-          <t>2026.05.19</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C80" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Integ</t>
         </is>
       </c>
       <c r="D80" s="118" t="n">
-        <v>180</v>
+        <v>6800</v>
       </c>
       <c r="E80" s="118" t="n">
-        <v>180</v>
+        <v>6800</v>
       </c>
       <c r="F80" s="122">
         <f>D80/E80</f>
         <v/>
       </c>
       <c r="G80" s="118">
-        <f>F36</f>
+        <f>F34</f>
         <v/>
       </c>
       <c r="H80" s="120">
@@ -16062,15 +16078,15 @@
         <v/>
       </c>
       <c r="I80" s="120">
-        <f>ROUND(G36*F80*G80,0)</f>
+        <f>ROUND(G34*F80*G80,0)</f>
         <v/>
       </c>
       <c r="J80" s="120">
-        <f>ROUND(H36*F80,0)</f>
+        <f>ROUND(H34*F80,0)</f>
         <v/>
       </c>
       <c r="K80" s="120">
-        <f>ROUND(I36*F80,0)</f>
+        <f>ROUND(I34*F80,0)</f>
         <v/>
       </c>
       <c r="L80" s="121">
@@ -16081,31 +16097,31 @@
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="116" t="inlineStr">
         <is>
-          <t>CPO698</t>
+          <t>GPO478</t>
         </is>
       </c>
       <c r="B81" s="116" t="inlineStr">
         <is>
-          <t>2026.05.20</t>
+          <t>2026.05.19</t>
         </is>
       </c>
       <c r="C81" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D81" s="118" t="n">
-        <v>4290</v>
+        <v>180</v>
       </c>
       <c r="E81" s="118" t="n">
-        <v>4290</v>
+        <v>180</v>
       </c>
       <c r="F81" s="122">
         <f>D81/E81</f>
         <v/>
       </c>
       <c r="G81" s="118">
-        <f>F37</f>
+        <f>F36</f>
         <v/>
       </c>
       <c r="H81" s="120">
@@ -16113,51 +16129,50 @@
         <v/>
       </c>
       <c r="I81" s="120">
-        <f>ROUND(G37*F81*G81,0)</f>
+        <f>ROUND(G36*F81*G81,0)</f>
         <v/>
       </c>
       <c r="J81" s="120">
-        <f>ROUND(H37*F81,0)</f>
+        <f>ROUND(H36*F81,0)</f>
         <v/>
       </c>
       <c r="K81" s="120">
-        <f>ROUND(I37*F81,0)</f>
+        <f>ROUND(I36*F81,0)</f>
         <v/>
       </c>
       <c r="L81" s="121">
         <f>H81+I81+J81+K81</f>
         <v/>
       </c>
-      <c r="M81" s="40" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="116" t="inlineStr">
         <is>
-          <t>GPO473-1</t>
+          <t>CPO698</t>
         </is>
       </c>
       <c r="B82" s="116" t="inlineStr">
         <is>
-          <t>2026.05.29</t>
+          <t>2026.05.20</t>
         </is>
       </c>
       <c r="C82" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D82" s="118" t="n">
-        <v>98800</v>
+        <v>4290</v>
       </c>
       <c r="E82" s="118" t="n">
-        <v>99140</v>
+        <v>4290</v>
       </c>
       <c r="F82" s="122">
         <f>D82/E82</f>
         <v/>
       </c>
       <c r="G82" s="118">
-        <f>F38</f>
+        <f>F37</f>
         <v/>
       </c>
       <c r="H82" s="120">
@@ -16165,26 +16180,27 @@
         <v/>
       </c>
       <c r="I82" s="120">
-        <f>ROUND(G38*F82*G82,0)</f>
+        <f>ROUND(G37*F82*G82,0)</f>
         <v/>
       </c>
       <c r="J82" s="120">
-        <f>ROUND(H38*F82,0)</f>
+        <f>ROUND(H37*F82,0)</f>
         <v/>
       </c>
       <c r="K82" s="120">
-        <f>ROUND(I38*F82,0)</f>
+        <f>ROUND(I37*F82,0)</f>
         <v/>
       </c>
       <c r="L82" s="121">
         <f>H82+I82+J82+K82</f>
         <v/>
       </c>
+      <c r="M82" s="40" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="116" t="inlineStr">
         <is>
-          <t>GPO480</t>
+          <t>GPO473-1</t>
         </is>
       </c>
       <c r="B83" s="116" t="inlineStr">
@@ -16198,7 +16214,7 @@
         </is>
       </c>
       <c r="D83" s="118" t="n">
-        <v>250</v>
+        <v>98800</v>
       </c>
       <c r="E83" s="118" t="n">
         <v>99140</v>
@@ -16235,7 +16251,7 @@
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="116" t="inlineStr">
         <is>
-          <t>GPO479</t>
+          <t>GPO480</t>
         </is>
       </c>
       <c r="B84" s="116" t="inlineStr">
@@ -16249,7 +16265,7 @@
         </is>
       </c>
       <c r="D84" s="118" t="n">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="E84" s="118" t="n">
         <v>99140</v>
@@ -16286,7 +16302,7 @@
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="116" t="inlineStr">
         <is>
-          <t>CPO697</t>
+          <t>GPO479</t>
         </is>
       </c>
       <c r="B85" s="116" t="inlineStr">
@@ -16296,21 +16312,21 @@
       </c>
       <c r="C85" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D85" s="118" t="n">
-        <v>15289</v>
+        <v>90</v>
       </c>
       <c r="E85" s="118" t="n">
-        <v>101638</v>
+        <v>99140</v>
       </c>
       <c r="F85" s="122">
         <f>D85/E85</f>
         <v/>
       </c>
       <c r="G85" s="118">
-        <f>F39</f>
+        <f>F38</f>
         <v/>
       </c>
       <c r="H85" s="120">
@@ -16318,15 +16334,15 @@
         <v/>
       </c>
       <c r="I85" s="120">
-        <f>ROUND(G39*F85*G85,0)</f>
+        <f>ROUND(G38*F85*G85,0)</f>
         <v/>
       </c>
       <c r="J85" s="120">
-        <f>ROUND(H39*F85,0)</f>
+        <f>ROUND(H38*F85,0)</f>
         <v/>
       </c>
       <c r="K85" s="120">
-        <f>ROUND(I39*F85,0)</f>
+        <f>ROUND(I38*F85,0)</f>
         <v/>
       </c>
       <c r="L85" s="121">
@@ -16337,7 +16353,7 @@
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="116" t="inlineStr">
         <is>
-          <t>CPO696-1</t>
+          <t>CPO697</t>
         </is>
       </c>
       <c r="B86" s="116" t="inlineStr">
@@ -16351,7 +16367,7 @@
         </is>
       </c>
       <c r="D86" s="118" t="n">
-        <v>78209</v>
+        <v>15289</v>
       </c>
       <c r="E86" s="118" t="n">
         <v>101638</v>
@@ -16388,7 +16404,7 @@
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="116" t="inlineStr">
         <is>
-          <t>CPO696-2</t>
+          <t>CPO696-1</t>
         </is>
       </c>
       <c r="B87" s="116" t="inlineStr">
@@ -16402,7 +16418,7 @@
         </is>
       </c>
       <c r="D87" s="118" t="n">
-        <v>8140</v>
+        <v>78209</v>
       </c>
       <c r="E87" s="118" t="n">
         <v>101638</v>
@@ -16436,9 +16452,213 @@
         <v/>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="116" t="inlineStr">
+        <is>
+          <t>CPO696-2</t>
+        </is>
+      </c>
+      <c r="B88" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C88" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D88" s="118" t="n">
+        <v>8140</v>
+      </c>
+      <c r="E88" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F88" s="122">
+        <f>D88/E88</f>
+        <v/>
+      </c>
+      <c r="G88" s="118">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="H88" s="120">
+        <f>ROUND(D88*G88,0)</f>
+        <v/>
+      </c>
+      <c r="I88" s="120">
+        <f>ROUND(G39*F88*G88,0)</f>
+        <v/>
+      </c>
+      <c r="J88" s="120">
+        <f>ROUND(H39*F88,0)</f>
+        <v/>
+      </c>
+      <c r="K88" s="120">
+        <f>ROUND(I39*F88,0)</f>
+        <v/>
+      </c>
+      <c r="L88" s="121">
+        <f>H88+I88+J88+K88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="234" t="inlineStr">
+        <is>
+          <t>GPO481</t>
+        </is>
+      </c>
+      <c r="B89" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C89" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D89" s="236" t="n">
+        <v>500</v>
+      </c>
+      <c r="E89" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F89" s="240">
+        <f>D89/E89</f>
+        <v/>
+      </c>
+      <c r="G89" s="236">
+        <f>F40</f>
+        <v/>
+      </c>
+      <c r="H89" s="238">
+        <f>ROUND(D89*G89,0)</f>
+        <v/>
+      </c>
+      <c r="I89" s="238">
+        <f>ROUND(G40*F89*G89,0)</f>
+        <v/>
+      </c>
+      <c r="J89" s="238">
+        <f>ROUND(H40*F89,0)</f>
+        <v/>
+      </c>
+      <c r="K89" s="238">
+        <f>ROUND(I40*F89,0)</f>
+        <v/>
+      </c>
+      <c r="L89" s="239">
+        <f>H89+I89+J89+K89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="234" t="inlineStr">
+        <is>
+          <t>GPO473-2</t>
+        </is>
+      </c>
+      <c r="B90" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C90" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D90" s="236" t="n">
+        <v>69160</v>
+      </c>
+      <c r="E90" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F90" s="240">
+        <f>D90/E90</f>
+        <v/>
+      </c>
+      <c r="G90" s="236">
+        <f>F40</f>
+        <v/>
+      </c>
+      <c r="H90" s="238">
+        <f>ROUND(D90*G90,0)</f>
+        <v/>
+      </c>
+      <c r="I90" s="238">
+        <f>ROUND(G40*F90*G90,0)</f>
+        <v/>
+      </c>
+      <c r="J90" s="238">
+        <f>ROUND(H40*F90,0)</f>
+        <v/>
+      </c>
+      <c r="K90" s="238">
+        <f>ROUND(I40*F90,0)</f>
+        <v/>
+      </c>
+      <c r="L90" s="239">
+        <f>H90+I90+J90+K90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="234" t="inlineStr">
+        <is>
+          <t>GPO473-3</t>
+        </is>
+      </c>
+      <c r="B91" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C91" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D91" s="236" t="n">
+        <v>49400</v>
+      </c>
+      <c r="E91" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F91" s="240">
+        <f>D91/E91</f>
+        <v/>
+      </c>
+      <c r="G91" s="236">
+        <f>F40</f>
+        <v/>
+      </c>
+      <c r="H91" s="238">
+        <f>ROUND(D91*G91,0)</f>
+        <v/>
+      </c>
+      <c r="I91" s="238">
+        <f>ROUND(G40*F91*G91,0)</f>
+        <v/>
+      </c>
+      <c r="J91" s="238">
+        <f>ROUND(H40*F91,0)</f>
+        <v/>
+      </c>
+      <c r="K91" s="238">
+        <f>ROUND(I40*F91,0)</f>
+        <v/>
+      </c>
+      <c r="L91" s="239">
+        <f>H91+I91+J91+K91</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A41:L41"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -16498,7 +16718,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="163" t="inlineStr">
         <is>
-          <t>기준일: 2026-06-02  |  미상환 건만 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
+          <t>기준일: 2026-06-10  |  미상환 건만 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
         </is>
       </c>
     </row>
@@ -16899,10 +17119,18 @@
       <c r="L17" s="200" t="n">
         <v>60</v>
       </c>
-      <c r="M17" s="59" t="n"/>
+      <c r="M17" s="59" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="N17" s="201" t="n"/>
       <c r="O17" s="63" t="n"/>
-      <c r="P17" s="59" t="n"/>
+      <c r="P17" s="59" t="inlineStr">
+        <is>
+          <t>6/9 만기 상환 완료 (USD 190,470)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="56" t="inlineStr">
@@ -18445,7 +18673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -19076,6 +19304,22 @@
       </c>
       <c r="D41" s="211" t="n">
         <v>1507.15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="210" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B42" s="210" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C42" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D42" s="211" t="n">
+        <v>1514.68</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -433,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1125,6 +1125,18 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1209,6 +1221,13 @@
     <author>RNR 재무팀</author>
   </authors>
   <commentList>
+    <comment ref="S5" authorId="0" shapeId="0">
+      <text>
+        <t>관세율 0% 적용 (DHL 특송/인천세관 직통관)
+신고필증 미확보 - 면세 사유 확인 필요
+(신고번호 883504210357, 수리일 2025-09-05)</t>
+      </text>
+    </comment>
     <comment ref="S7" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
@@ -1285,6 +1304,34 @@
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8518/8543 디지털시네마장비</t>
+      </text>
+    </comment>
+    <comment ref="S35" authorId="0" shapeId="0">
+      <text>
+        <t>ITA(정보기술협정) 관세면제
+HS 8543 — 디지털시네마 서버/IMB
+(정보기술협정 양허품목)</t>
+      </text>
+    </comment>
+    <comment ref="S37" authorId="0" shapeId="0">
+      <text>
+        <t>ITA(정보기술협정) 관세면제
+HS 8543 — 디지털시네마 서버/IMB
+(정보기술협정 양허품목)</t>
+      </text>
+    </comment>
+    <comment ref="S38" authorId="0" shapeId="0">
+      <text>
+        <t>ITA(정보기술협정) 관세면제
+HS 8543 — 디지털시네마 서버/IMB
+(정보기술협정 양허품목)</t>
+      </text>
+    </comment>
+    <comment ref="S62" authorId="0" shapeId="0">
+      <text>
+        <t>관세율 0.00% - 세율구분 C(가가, WTO/ITA 양허)
+수리반환 재수입 건, 부가세만 과세
+(신고필증 2235626351613M)</t>
       </text>
     </comment>
   </commentList>
@@ -4296,10 +4343,8 @@
       <c r="F24" s="174" t="n">
         <v>46080</v>
       </c>
-      <c r="G24" s="175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G24" s="175" t="n">
+        <v>46126</v>
       </c>
       <c r="H24" s="7" t="n">
         <v>36190</v>
@@ -4429,10 +4474,8 @@
       <c r="F25" s="174" t="n">
         <v>46088</v>
       </c>
-      <c r="G25" s="175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G25" s="175" t="n">
+        <v>46126</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>180</v>
@@ -4562,10 +4605,8 @@
       <c r="F26" s="174" t="n">
         <v>46088</v>
       </c>
-      <c r="G26" s="175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" s="175" t="n">
+        <v>46126</v>
       </c>
       <c r="H26" s="7" t="n">
         <v>21280</v>
@@ -4957,7 +4998,9 @@
       <c r="F29" s="174" t="n">
         <v>46106</v>
       </c>
-      <c r="G29" s="175" t="n"/>
+      <c r="G29" s="175" t="n">
+        <v>46162</v>
+      </c>
       <c r="H29" s="7" t="n">
         <v>4290</v>
       </c>
@@ -5072,10 +5115,8 @@
       <c r="F30" s="179" t="n">
         <v>46113</v>
       </c>
-      <c r="G30" s="179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G30" s="179" t="n">
+        <v>46171</v>
       </c>
       <c r="H30" s="80" t="n">
         <v>78209</v>
@@ -5193,10 +5234,8 @@
       <c r="F31" s="179" t="n">
         <v>46113</v>
       </c>
-      <c r="G31" s="179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G31" s="179" t="n">
+        <v>46171</v>
       </c>
       <c r="H31" s="80" t="n">
         <v>8140</v>
@@ -5499,7 +5538,11 @@
         <f>ROUND(AA33/AB33,0)</f>
         <v/>
       </c>
-      <c r="AD33" s="129" t="n"/>
+      <c r="AD33" s="129" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
       <c r="AE33" s="129" t="n"/>
       <c r="AF33" s="129" t="n"/>
     </row>
@@ -5612,7 +5655,11 @@
         <f>ROUND(AA34/AB34,0)</f>
         <v/>
       </c>
-      <c r="AD34" s="129" t="n"/>
+      <c r="AD34" s="129" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
       <c r="AE34" s="129" t="n"/>
       <c r="AF34" s="129" t="n"/>
     </row>
@@ -5643,10 +5690,8 @@
       <c r="F35" s="181" t="n">
         <v>46113</v>
       </c>
-      <c r="G35" s="124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G35" s="181" t="n">
+        <v>46171</v>
       </c>
       <c r="H35" s="126" t="n">
         <v>98800</v>
@@ -5725,7 +5770,11 @@
         <f>ROUND(AA35/AB35,0)</f>
         <v/>
       </c>
-      <c r="AD35" s="129" t="n"/>
+      <c r="AD35" s="129" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
       <c r="AE35" s="129" t="n"/>
       <c r="AF35" s="129" t="n"/>
     </row>
@@ -5756,10 +5805,8 @@
       <c r="F36" s="181" t="n">
         <v>46127</v>
       </c>
-      <c r="G36" s="124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G36" s="181" t="n">
+        <v>46171</v>
       </c>
       <c r="H36" s="126" t="n">
         <v>90</v>
@@ -8328,10 +8375,8 @@
       <c r="F56" s="186" t="n">
         <v>46136</v>
       </c>
-      <c r="G56" s="186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G56" s="186" t="n">
+        <v>46171</v>
       </c>
       <c r="H56" s="87" t="n">
         <v>15289</v>
@@ -8421,8 +8466,12 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE56" s="186" t="n"/>
-      <c r="AF56" s="186" t="n"/>
+      <c r="AE56" s="186" t="n">
+        <v>46168</v>
+      </c>
+      <c r="AF56" s="186" t="n">
+        <v>46532</v>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="85" t="n">
@@ -8544,8 +8593,12 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE57" s="186" t="n"/>
-      <c r="AF57" s="186" t="n"/>
+      <c r="AE57" s="186" t="n">
+        <v>46142</v>
+      </c>
+      <c r="AF57" s="186" t="n">
+        <v>46872</v>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="132" t="n">
@@ -8574,10 +8627,8 @@
       <c r="F58" s="188" t="n">
         <v>46127</v>
       </c>
-      <c r="G58" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G58" s="188" t="n">
+        <v>46161</v>
       </c>
       <c r="H58" s="134" t="n">
         <v>180</v>
@@ -8646,7 +8697,11 @@
         <f>ROUND(AA58/AB58,0)</f>
         <v/>
       </c>
-      <c r="AD58" s="137" t="n"/>
+      <c r="AD58" s="137" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
       <c r="AE58" s="189" t="n">
         <v>46143</v>
       </c>
@@ -8681,10 +8736,8 @@
       <c r="F59" s="188" t="n">
         <v>46137</v>
       </c>
-      <c r="G59" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G59" s="188" t="n">
+        <v>46171</v>
       </c>
       <c r="H59" s="134" t="n">
         <v>250</v>
@@ -8753,9 +8806,17 @@
         <f>ROUND(AA59/AB59,0)</f>
         <v/>
       </c>
-      <c r="AD59" s="137" t="n"/>
-      <c r="AE59" s="137" t="n"/>
-      <c r="AF59" s="137" t="n"/>
+      <c r="AD59" s="137" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE59" s="189" t="n">
+        <v>46143</v>
+      </c>
+      <c r="AF59" s="189" t="n">
+        <v>49795</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="132" t="n">
@@ -8859,8 +8920,16 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE60" s="137" t="n"/>
-      <c r="AF60" s="137" t="n"/>
+      <c r="AE60" s="137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF60" s="137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="n">
@@ -9020,7 +9089,11 @@
         </is>
       </c>
       <c r="F62" s="176" t="n"/>
-      <c r="G62" s="177" t="n"/>
+      <c r="G62" s="177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H62" s="16" t="n">
         <v>400</v>
       </c>
@@ -10422,7 +10495,7 @@
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
-          <t>홀딩</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="L15" s="115" t="n"/>
@@ -10603,10 +10676,8 @@
       <c r="G19" s="184" t="n">
         <v>46109</v>
       </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H19" s="184" t="n">
+        <v>46146</v>
       </c>
       <c r="I19" s="184" t="n">
         <v>46113</v>
@@ -10652,10 +10723,8 @@
       <c r="G20" s="191" t="n">
         <v>46136</v>
       </c>
-      <c r="H20" s="191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H20" s="191" t="n">
+        <v>46171</v>
       </c>
       <c r="I20" s="191" t="n">
         <v>46168</v>
@@ -10750,10 +10819,8 @@
       <c r="G22" s="227" t="n">
         <v>46127</v>
       </c>
-      <c r="H22" s="227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H22" s="227" t="n">
+        <v>46161</v>
       </c>
       <c r="I22" s="227" t="n">
         <v>46143</v>
@@ -10799,10 +10866,8 @@
       <c r="G23" s="227" t="n">
         <v>46137</v>
       </c>
-      <c r="H23" s="227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H23" s="227" t="n">
+        <v>46171</v>
       </c>
       <c r="I23" s="227" t="n">
         <v>46143</v>
@@ -12143,6 +12208,270 @@
       <c r="K29" s="115" t="n"/>
       <c r="L29" s="115" t="n"/>
       <c r="M29" s="115" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="241" t="inlineStr">
+        <is>
+          <t>14008-26-101140M</t>
+        </is>
+      </c>
+      <c r="B30" s="241" t="inlineStr">
+        <is>
+          <t>CPO696-3</t>
+        </is>
+      </c>
+      <c r="C30" s="242" t="n">
+        <v>351274</v>
+      </c>
+      <c r="D30" s="243">
+        <f>C30/C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F30" s="244" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G30" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="H30" s="244" t="n">
+        <v>3103207</v>
+      </c>
+      <c r="I30" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J30" s="241" t="n"/>
+      <c r="K30" s="228" t="n"/>
+      <c r="L30" s="228" t="n"/>
+      <c r="M30" s="228" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="241" t="inlineStr">
+        <is>
+          <t>14008-26-101148M</t>
+        </is>
+      </c>
+      <c r="B31" s="241" t="inlineStr">
+        <is>
+          <t>GPO473-1</t>
+        </is>
+      </c>
+      <c r="C31" s="242" t="n">
+        <v>98800</v>
+      </c>
+      <c r="D31" s="243">
+        <f>C31/C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F31" s="244" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G31" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="H31" s="244" t="n">
+        <v>3636072</v>
+      </c>
+      <c r="I31" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J31" s="241" t="n"/>
+      <c r="K31" s="228" t="n"/>
+      <c r="L31" s="228" t="n"/>
+      <c r="M31" s="228" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="241" t="inlineStr">
+        <is>
+          <t>14008-26-101168M</t>
+        </is>
+      </c>
+      <c r="B32" s="241" t="inlineStr">
+        <is>
+          <t>CPO696-4</t>
+        </is>
+      </c>
+      <c r="C32" s="242" t="n">
+        <v>807233</v>
+      </c>
+      <c r="D32" s="243">
+        <f>C32/C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F32" s="244" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G32" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="H32" s="244" t="n">
+        <v>3270326</v>
+      </c>
+      <c r="I32" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J32" s="241" t="n"/>
+      <c r="K32" s="228" t="n"/>
+      <c r="L32" s="228" t="n"/>
+      <c r="M32" s="228" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="241" t="inlineStr">
+        <is>
+          <t>883504210357</t>
+        </is>
+      </c>
+      <c r="B33" s="241" t="inlineStr">
+        <is>
+          <t>IPO016</t>
+        </is>
+      </c>
+      <c r="C33" s="242" t="n">
+        <v>6800</v>
+      </c>
+      <c r="D33" s="243">
+        <f>C33/C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="241" t="inlineStr">
+        <is>
+          <t>인천세관(특송)</t>
+        </is>
+      </c>
+      <c r="F33" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="241" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="H33" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J33" s="241" t="n"/>
+      <c r="K33" s="228" t="n"/>
+      <c r="L33" s="228" t="n"/>
+      <c r="M33" s="228" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="241" t="inlineStr">
+        <is>
+          <t>22356-26-351613M</t>
+        </is>
+      </c>
+      <c r="B34" s="241" t="inlineStr">
+        <is>
+          <t>SX3000수리</t>
+        </is>
+      </c>
+      <c r="C34" s="242" t="n">
+        <v>400</v>
+      </c>
+      <c r="D34" s="243">
+        <f>C34/C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="241" t="inlineStr">
+        <is>
+          <t>운서합동관세사무소</t>
+        </is>
+      </c>
+      <c r="F34" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J34" s="241" t="n"/>
+      <c r="K34" s="228" t="n"/>
+      <c r="L34" s="228" t="n"/>
+      <c r="M34" s="228" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="241" t="inlineStr">
+        <is>
+          <t>2235626346781M</t>
+        </is>
+      </c>
+      <c r="B35" s="241" t="inlineStr">
+        <is>
+          <t>CPO698</t>
+        </is>
+      </c>
+      <c r="C35" s="242" t="n">
+        <v>4290</v>
+      </c>
+      <c r="D35" s="243">
+        <f>C35/C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="241" t="inlineStr">
+        <is>
+          <t>운서합동관세사무소</t>
+        </is>
+      </c>
+      <c r="F35" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="241" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="H35" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J35" s="241" t="n"/>
+      <c r="K35" s="228" t="n"/>
+      <c r="L35" s="228" t="n"/>
+      <c r="M35" s="228" t="n"/>
     </row>
     <row r="71">
       <c r="M71" s="40" t="n"/>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1306,6 +1306,12 @@
 HS 8518/8543 디지털시네마장비</t>
       </text>
     </comment>
+    <comment ref="Y29" authorId="0" shapeId="0">
+      <text>
+        <t>DHL 2026-05월 인보이스 (AWB 2538226250, 4/8 Christie HK 발송)
+지출결의 2026-1344, 6/9 집행</t>
+      </text>
+    </comment>
     <comment ref="S35" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
@@ -1327,11 +1333,24 @@
 (정보기술협정 양허품목)</t>
       </text>
     </comment>
-    <comment ref="S62" authorId="0" shapeId="0">
+    <comment ref="Y39" authorId="0" shapeId="0">
+      <text>
+        <t>FedEx 2026-05월 인보이스 159,250원 선반영
+(AWB 870900398456, 4/21 INTEG 발송, 4/27 배달)
+인보이스/송금/수입신고 미도래 - 미확정 건</t>
+      </text>
+    </comment>
+    <comment ref="S63" authorId="0" shapeId="0">
       <text>
         <t>관세율 0.00% - 세율구분 C(가가, WTO/ITA 양허)
 수리반환 재수입 건, 부가세만 과세
 (신고필증 2235626351613M)</t>
+      </text>
+    </comment>
+    <comment ref="Y63" authorId="0" shapeId="0">
+      <text>
+        <t>DHL 2026-05월 인보이스 (AWB 5094871784 = 수입신고필증 B/L 일치)
+GDC RMA 수리반환 건, 지출결의 2026-1344, 6/9 집행</t>
       </text>
     </comment>
   </commentList>
@@ -1552,7 +1571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF86"/>
+  <dimension ref="A1:AF87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" style="160" min="1" max="1"/>
@@ -5063,7 +5082,7 @@
         </is>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>0</v>
+        <v>174806</v>
       </c>
       <c r="Z29" s="9">
         <f>S29+T29+W29</f>
@@ -6118,175 +6137,165 @@
       <c r="AF38" s="208" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>CPO667</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F39" s="183" t="n">
-        <v>45925</v>
-      </c>
-      <c r="G39" s="184" t="n">
-        <v>46080</v>
-      </c>
-      <c r="H39" s="24" t="n">
-        <v>5673</v>
-      </c>
-      <c r="I39" s="185">
+      <c r="A39" s="124" t="n">
+        <v>60</v>
+      </c>
+      <c r="B39" s="124" t="inlineStr">
+        <is>
+          <t>IPO017</t>
+        </is>
+      </c>
+      <c r="C39" s="124" t="inlineStr">
+        <is>
+          <t>Integ Process Group</t>
+        </is>
+      </c>
+      <c r="D39" s="124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="124" t="inlineStr">
+        <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="F39" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="126">
         <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
-      <c r="J39" s="26" t="n">
-        <v>205028994</v>
-      </c>
-      <c r="K39" s="26">
+      <c r="J39" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="128">
         <f>IFERROR(ROUND(H39*I39,0),0)</f>
         <v/>
       </c>
-      <c r="L39" s="26">
+      <c r="L39" s="128">
         <f>IFERROR(VLOOKUP(B39,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
-      <c r="M39" s="26">
+      <c r="M39" s="128">
         <f>IFERROR(VLOOKUP(B39,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N39" s="20" t="inlineStr">
-        <is>
-          <t>EW CP2220</t>
-        </is>
-      </c>
-      <c r="O39" s="20" t="inlineStr">
+      <c r="N39" s="129" t="inlineStr">
+        <is>
+          <t>JNIOR Model 410 (IPO017, FedEx 4/21 발송분)</t>
+        </is>
+      </c>
+      <c r="O39" s="129" t="n"/>
+      <c r="P39" s="129" t="n"/>
+      <c r="Q39" s="126">
+        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R39" s="126">
+        <f>IF(P39="","",H39)</f>
+        <v/>
+      </c>
+      <c r="S39" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="129" t="n"/>
+      <c r="V39" s="129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P39" s="20" t="inlineStr">
+      <c r="W39" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="124" t="inlineStr">
+        <is>
+          <t>FedEx</t>
+        </is>
+      </c>
+      <c r="Y39" s="128" t="n">
+        <v>159250</v>
+      </c>
+      <c r="Z39" s="128">
+        <f>S39+T39+W39</f>
+        <v/>
+      </c>
+      <c r="AA39" s="131">
+        <f>K39+L39+M39+IFERROR(VLOOKUP(B39,RemitTable2,9,FALSE),0)+Y39+Z39</f>
+        <v/>
+      </c>
+      <c r="AB39" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="131">
+        <f>ROUND(AA39/AB39,0)</f>
+        <v/>
+      </c>
+      <c r="AD39" s="129" t="n"/>
+      <c r="AE39" s="129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q39" s="24">
-        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R39" s="26">
-        <f>IF(P39="","",H39)</f>
-        <v/>
-      </c>
-      <c r="S39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="20" t="inlineStr">
+      <c r="AF39" s="129" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="W39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y39" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="26">
-        <f>S39+T39+W39</f>
-        <v/>
-      </c>
-      <c r="AA39" s="26">
-        <f>K39+L39+M39+IFERROR(VLOOKUP(B39,RemitTable2,9,FALSE),0)+Y39+Z39</f>
-        <v/>
-      </c>
-      <c r="AB39" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="26">
-        <f>ROUND(AA39/AB39,0)</f>
-        <v/>
-      </c>
-      <c r="AD39" s="20" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="AE39" s="184" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AF39" s="183" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>GPO458</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F40" s="183" t="n">
-        <v>45982</v>
+        <v>45925</v>
       </c>
       <c r="G40" s="184" t="n">
-        <v>46020</v>
+        <v>46080</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>350</v>
+        <v>5673</v>
       </c>
       <c r="I40" s="185">
         <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J40" s="26" t="n">
-        <v>18264679</v>
+        <v>205028994</v>
       </c>
       <c r="K40" s="26">
         <f>IFERROR(ROUND(H40*I40,0),0)</f>
@@ -6302,7 +6311,7 @@
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>HFR License</t>
+          <t>EW CP2220</t>
         </is>
       </c>
       <c r="O40" s="20" t="inlineStr">
@@ -6365,59 +6374,59 @@
       </c>
       <c r="AD40" s="20" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="AE40" s="184" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AF40" s="183" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F41" s="183" t="n">
-        <v>45993</v>
+        <v>45982</v>
       </c>
       <c r="G41" s="184" t="n">
-        <v>46064</v>
+        <v>46020</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>26358</v>
+        <v>350</v>
       </c>
       <c r="I41" s="185">
         <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J41" s="26" t="n">
-        <v>38550844</v>
+        <v>18264679</v>
       </c>
       <c r="K41" s="26">
         <f>IFERROR(ROUND(H41*I41,0),0)</f>
@@ -6433,7 +6442,7 @@
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>EW CP2309/2315/2320-RGB</t>
+          <t>HFR License</t>
         </is>
       </c>
       <c r="O41" s="20" t="inlineStr">
@@ -6501,32 +6510,32 @@
       </c>
       <c r="AE41" s="184" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AF41" s="183" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-11-30</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>GPO459</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
@@ -6535,20 +6544,20 @@
         </is>
       </c>
       <c r="F42" s="183" t="n">
-        <v>46007</v>
+        <v>45993</v>
       </c>
       <c r="G42" s="184" t="n">
-        <v>46043</v>
+        <v>46064</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>450</v>
+        <v>26358</v>
       </c>
       <c r="I42" s="185">
         <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J42" s="26" t="n">
-        <v>5505104</v>
+        <v>38550844</v>
       </c>
       <c r="K42" s="26">
         <f>IFERROR(ROUND(H42*I42,0),0)</f>
@@ -6564,7 +6573,7 @@
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 EW</t>
+          <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
       <c r="O42" s="20" t="inlineStr">
@@ -6627,27 +6636,27 @@
       </c>
       <c r="AD42" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE42" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AF42" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-21</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
@@ -6672,7 +6681,7 @@
         <v>46043</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="I43" s="185">
         <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE),0)</f>
@@ -6695,7 +6704,7 @@
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 EW</t>
+          <t>TMS-2000 EW</t>
         </is>
       </c>
       <c r="O43" s="20" t="inlineStr">
@@ -6758,37 +6767,37 @@
       </c>
       <c r="AD43" s="20" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE43" s="184" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF43" s="183" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E44" s="21" t="inlineStr">
@@ -6797,20 +6806,20 @@
         </is>
       </c>
       <c r="F44" s="183" t="n">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="G44" s="184" t="n">
-        <v>46080</v>
+        <v>46043</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>136516</v>
+        <v>540</v>
       </c>
       <c r="I44" s="185">
         <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J44" s="26" t="n">
-        <v>205028994</v>
+        <v>5505104</v>
       </c>
       <c r="K44" s="26">
         <f>IFERROR(ROUND(H44*I44,0),0)</f>
@@ -6826,7 +6835,7 @@
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (CP2208~CP4450)</t>
+          <t>TMS-1000 EW</t>
         </is>
       </c>
       <c r="O44" s="20" t="inlineStr">
@@ -6889,37 +6898,37 @@
       </c>
       <c r="AD44" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="AE44" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AF44" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>GPO465</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E45" s="21" t="inlineStr">
@@ -6928,22 +6937,20 @@
         </is>
       </c>
       <c r="F45" s="183" t="n">
-        <v>46015</v>
-      </c>
-      <c r="G45" s="184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46010</v>
+      </c>
+      <c r="G45" s="184" t="n">
+        <v>46080</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>76054</v>
+        <v>136516</v>
       </c>
       <c r="I45" s="185">
         <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J45" s="26" t="n">
-        <v>0</v>
+        <v>205028994</v>
       </c>
       <c r="K45" s="26">
         <f>IFERROR(ROUND(H45*I45,0),0)</f>
@@ -6959,7 +6966,7 @@
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (SR/SX/TMS)</t>
+          <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
       <c r="O45" s="20" t="inlineStr">
@@ -7038,21 +7045,21 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>GPO465</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E46" s="21" t="inlineStr">
@@ -7061,20 +7068,22 @@
         </is>
       </c>
       <c r="F46" s="183" t="n">
-        <v>46029</v>
-      </c>
-      <c r="G46" s="184" t="n">
-        <v>46072</v>
+        <v>46015</v>
+      </c>
+      <c r="G46" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H46" s="24" t="n">
-        <v>14793</v>
+        <v>76054</v>
       </c>
       <c r="I46" s="185">
         <f>IFERROR(VLOOKUP(B46,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J46" s="26" t="n">
-        <v>25506948</v>
+        <v>0</v>
       </c>
       <c r="K46" s="26">
         <f>IFERROR(ROUND(H46*I46,0),0)</f>
@@ -7090,7 +7099,7 @@
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>EW CP2315/CP4440-RGB</t>
+          <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
       <c r="O46" s="20" t="inlineStr">
@@ -7158,22 +7167,22 @@
       </c>
       <c r="AE46" s="184" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF46" s="183" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>CPO687</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
@@ -7194,20 +7203,18 @@
       <c r="F47" s="183" t="n">
         <v>46029</v>
       </c>
-      <c r="G47" s="184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" s="184" t="n">
+        <v>46072</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>26656</v>
+        <v>14793</v>
       </c>
       <c r="I47" s="185">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J47" s="26" t="n">
-        <v>0</v>
+        <v>25506948</v>
       </c>
       <c r="K47" s="26">
         <f>IFERROR(ROUND(H47*I47,0),0)</f>
@@ -7223,7 +7230,7 @@
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
-          <t>EW (홀딩)</t>
+          <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
       <c r="O47" s="20" t="inlineStr">
@@ -7291,54 +7298,56 @@
       </c>
       <c r="AE47" s="184" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AF47" s="183" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-01-29</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="20" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>CPO687</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F48" s="183" t="n">
-        <v>46042</v>
-      </c>
-      <c r="G48" s="184" t="n">
-        <v>46057</v>
+        <v>46029</v>
+      </c>
+      <c r="G48" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H48" s="24" t="n">
-        <v>1440</v>
+        <v>26656</v>
       </c>
       <c r="I48" s="185">
         <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J48" s="26" t="n">
-        <v>16908206</v>
+        <v>0</v>
       </c>
       <c r="K48" s="26">
         <f>IFERROR(ROUND(H48*I48,0),0)</f>
@@ -7354,7 +7363,7 @@
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 License</t>
+          <t>EW (홀딩)</t>
         </is>
       </c>
       <c r="O48" s="20" t="inlineStr">
@@ -7422,22 +7431,22 @@
       </c>
       <c r="AE48" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AF48" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="20" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
@@ -7452,7 +7461,7 @@
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F49" s="183" t="n">
@@ -7462,7 +7471,7 @@
         <v>46057</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>4489</v>
+        <v>1440</v>
       </c>
       <c r="I49" s="185">
         <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE),0)</f>
@@ -7485,7 +7494,7 @@
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
-          <t>SX/SR EW (CGV/Lotte)</t>
+          <t>TMS-2000 License</t>
         </is>
       </c>
       <c r="O49" s="20" t="inlineStr">
@@ -7564,11 +7573,11 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
@@ -7593,7 +7602,7 @@
         <v>46057</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>5670.57</v>
+        <v>4489</v>
       </c>
       <c r="I50" s="185">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE),0)</f>
@@ -7616,7 +7625,7 @@
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
-          <t>SR-1000/SX-3000 EW</t>
+          <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
       <c r="O50" s="20" t="inlineStr">
@@ -7695,21 +7704,21 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="20" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E51" s="21" t="inlineStr">
@@ -7718,20 +7727,20 @@
         </is>
       </c>
       <c r="F51" s="183" t="n">
+        <v>46042</v>
+      </c>
+      <c r="G51" s="184" t="n">
         <v>46057</v>
       </c>
-      <c r="G51" s="184" t="n">
-        <v>46113</v>
-      </c>
       <c r="H51" s="24" t="n">
-        <v>24614</v>
+        <v>5670.57</v>
       </c>
       <c r="I51" s="185">
         <f>IFERROR(VLOOKUP(B51,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J51" s="26" t="n">
-        <v>51777431</v>
+        <v>16908206</v>
       </c>
       <c r="K51" s="26">
         <f>IFERROR(ROUND(H51*I51,0),0)</f>
@@ -7747,7 +7756,7 @@
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>EW (메가박스 외)</t>
+          <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
       <c r="O51" s="20" t="inlineStr">
@@ -7810,37 +7819,37 @@
       </c>
       <c r="AD51" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE51" s="184" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF51" s="183" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E52" s="21" t="inlineStr">
@@ -7849,20 +7858,20 @@
         </is>
       </c>
       <c r="F52" s="183" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="G52" s="184" t="n">
         <v>46113</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>3993.05</v>
+        <v>24614</v>
       </c>
       <c r="I52" s="185">
         <f>IFERROR(VLOOKUP(B52,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J52" s="26" t="n">
-        <v>9919642</v>
+        <v>51777431</v>
       </c>
       <c r="K52" s="26">
         <f>IFERROR(ROUND(H52*I52,0),0)</f>
@@ -7878,7 +7887,7 @@
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
-          <t>SR/SX EW (하남미사 외)</t>
+          <t>EW (메가박스 외)</t>
         </is>
       </c>
       <c r="O52" s="20" t="inlineStr">
@@ -7941,27 +7950,27 @@
       </c>
       <c r="AD52" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="AE52" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AF52" s="183" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-28</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>GPO469</t>
         </is>
       </c>
       <c r="C53" s="21" t="inlineStr">
@@ -7976,17 +7985,17 @@
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F53" s="183" t="n">
-        <v>46080</v>
+        <v>46060</v>
       </c>
       <c r="G53" s="184" t="n">
         <v>46113</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>360</v>
+        <v>3993.05</v>
       </c>
       <c r="I53" s="185">
         <f>IFERROR(VLOOKUP(B53,RemitTable2,7,FALSE),0)</f>
@@ -8009,7 +8018,7 @@
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 License</t>
+          <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
       <c r="O53" s="20" t="inlineStr">
@@ -8072,27 +8081,27 @@
       </c>
       <c r="AD53" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE53" s="184" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF53" s="183" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-02-22</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>GPO470</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
@@ -8111,13 +8120,13 @@
         </is>
       </c>
       <c r="F54" s="183" t="n">
-        <v>46088</v>
+        <v>46080</v>
       </c>
       <c r="G54" s="184" t="n">
         <v>46113</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="I54" s="185">
         <f>IFERROR(VLOOKUP(B54,RemitTable2,7,FALSE),0)</f>
@@ -8140,7 +8149,7 @@
       </c>
       <c r="N54" s="20" t="inlineStr">
         <is>
-          <t>Dolby Atmos License</t>
+          <t>TMS-1000 License</t>
         </is>
       </c>
       <c r="O54" s="20" t="inlineStr">
@@ -8208,54 +8217,54 @@
       </c>
       <c r="AE54" s="184" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AF54" s="183" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-02-28</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>GPO471</t>
         </is>
       </c>
       <c r="C55" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E55" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F55" s="183" t="n">
-        <v>46109</v>
+        <v>46088</v>
       </c>
       <c r="G55" s="184" t="n">
-        <v>46146</v>
+        <v>46113</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>17404</v>
+        <v>500</v>
       </c>
       <c r="I55" s="185">
         <f>IFERROR(VLOOKUP(B55,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J55" s="26" t="n">
-        <v>0</v>
+        <v>9919642</v>
       </c>
       <c r="K55" s="26">
         <f>IFERROR(ROUND(H55*I55,0),0)</f>
@@ -8271,7 +8280,7 @@
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
-          <t>EW (CGV 동백 외)</t>
+          <t>Dolby Atmos License</t>
         </is>
       </c>
       <c r="O55" s="20" t="inlineStr">
@@ -8334,152 +8343,158 @@
       </c>
       <c r="AD55" s="20" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE55" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF55" s="183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>CPO694</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E56" s="21" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F56" s="183" t="n">
+        <v>46109</v>
+      </c>
+      <c r="G56" s="184" t="n">
+        <v>46146</v>
+      </c>
+      <c r="H56" s="24" t="n">
+        <v>17404</v>
+      </c>
+      <c r="I56" s="185">
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="26">
+        <f>IFERROR(ROUND(H56*I56,0),0)</f>
+        <v/>
+      </c>
+      <c r="L56" s="26">
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M56" s="26">
+        <f>IFERROR(VLOOKUP(B56,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>EW (CGV 동백 외)</t>
+        </is>
+      </c>
+      <c r="O56" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P56" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q56" s="24">
+        <f>IF(P56="","",IFERROR(VLOOKUP(O56,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R56" s="26">
+        <f>IF(P56="","",H56)</f>
+        <v/>
+      </c>
+      <c r="S56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="26">
+        <f>S56+T56+W56</f>
+        <v/>
+      </c>
+      <c r="AA56" s="26">
+        <f>K56+L56+M56+IFERROR(VLOOKUP(B56,RemitTable2,9,FALSE),0)+Y56+Z56</f>
+        <v/>
+      </c>
+      <c r="AB56" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="26">
+        <f>ROUND(AA56/AB56,0)</f>
+        <v/>
+      </c>
+      <c r="AD56" s="20" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE55" s="184" t="inlineStr">
+      <c r="AE56" s="184" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AF55" s="183" t="inlineStr">
+      <c r="AF56" s="183" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="85" t="n">
-        <v>46</v>
-      </c>
-      <c r="B56" s="85" t="inlineStr">
-        <is>
-          <t>CPO697</t>
-        </is>
-      </c>
-      <c r="C56" s="85" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D56" s="85" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E56" s="85" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F56" s="186" t="n">
-        <v>46136</v>
-      </c>
-      <c r="G56" s="186" t="n">
-        <v>46171</v>
-      </c>
-      <c r="H56" s="87" t="n">
-        <v>15289</v>
-      </c>
-      <c r="I56" s="187">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J56" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="89">
-        <f>IFERROR(ROUND(H56*I56,0),0)</f>
-        <v/>
-      </c>
-      <c r="L56" s="89">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M56" s="89">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N56" s="85" t="inlineStr">
-        <is>
-          <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
-        </is>
-      </c>
-      <c r="O56" s="186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P56" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q56" s="87">
-        <f>IF(P56="","",IFERROR(VLOOKUP(O56,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R56" s="87">
-        <f>IF(P56="","",H56)</f>
-        <v/>
-      </c>
-      <c r="S56" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="186" t="n"/>
-      <c r="V56" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W56" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y56" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="89">
-        <f>S56+T56+W56</f>
-        <v/>
-      </c>
-      <c r="AA56" s="89">
-        <f>K56+L56+M56+IFERROR(VLOOKUP(B56,RemitTable2,9,FALSE),0)+Y56+Z56</f>
-        <v/>
-      </c>
-      <c r="AB56" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC56" s="89">
-        <f>ROUND(AA56/AB56,0)</f>
-        <v/>
-      </c>
-      <c r="AD56" s="85" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="AE56" s="186" t="n">
-        <v>46168</v>
-      </c>
-      <c r="AF56" s="186" t="n">
-        <v>46532</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="85" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="85" t="inlineStr">
         <is>
-          <t>CPO693-2</t>
+          <t>CPO697</t>
         </is>
       </c>
       <c r="C57" s="85" t="inlineStr">
@@ -8498,15 +8513,13 @@
         </is>
       </c>
       <c r="F57" s="186" t="n">
-        <v>46133</v>
-      </c>
-      <c r="G57" s="186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46136</v>
+      </c>
+      <c r="G57" s="186" t="n">
+        <v>46171</v>
       </c>
       <c r="H57" s="87" t="n">
-        <v>2550</v>
+        <v>15289</v>
       </c>
       <c r="I57" s="187">
         <f>IFERROR(VLOOKUP(B57,RemitTable2,7,FALSE),0)</f>
@@ -8529,7 +8542,7 @@
       </c>
       <c r="N57" s="85" t="inlineStr">
         <is>
-          <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
+          <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
       <c r="O57" s="186" t="inlineStr">
@@ -8594,128 +8607,146 @@
         </is>
       </c>
       <c r="AE57" s="186" t="n">
+        <v>46168</v>
+      </c>
+      <c r="AF57" s="186" t="n">
+        <v>46532</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="85" t="n">
+        <v>47</v>
+      </c>
+      <c r="B58" s="85" t="inlineStr">
+        <is>
+          <t>CPO693-2</t>
+        </is>
+      </c>
+      <c r="C58" s="85" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D58" s="85" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E58" s="85" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F58" s="186" t="n">
+        <v>46133</v>
+      </c>
+      <c r="G58" s="186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="87" t="n">
+        <v>2550</v>
+      </c>
+      <c r="I58" s="187">
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J58" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="89">
+        <f>IFERROR(ROUND(H58*I58,0),0)</f>
+        <v/>
+      </c>
+      <c r="L58" s="89">
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M58" s="89">
+        <f>IFERROR(VLOOKUP(B58,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N58" s="85" t="inlineStr">
+        <is>
+          <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
+        </is>
+      </c>
+      <c r="O58" s="186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P58" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q58" s="87">
+        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R58" s="87">
+        <f>IF(P58="","",H58)</f>
+        <v/>
+      </c>
+      <c r="S58" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="186" t="n"/>
+      <c r="V58" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W58" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y58" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="89">
+        <f>S58+T58+W58</f>
+        <v/>
+      </c>
+      <c r="AA58" s="89">
+        <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
+        <v/>
+      </c>
+      <c r="AB58" s="90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="89">
+        <f>ROUND(AA58/AB58,0)</f>
+        <v/>
+      </c>
+      <c r="AD58" s="85" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="AE58" s="186" t="n">
         <v>46142</v>
       </c>
-      <c r="AF57" s="186" t="n">
+      <c r="AF58" s="186" t="n">
         <v>46872</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="132" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="132" t="inlineStr">
-        <is>
-          <t>GPO478</t>
-        </is>
-      </c>
-      <c r="C58" s="132" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D58" s="132" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E58" s="132" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F58" s="188" t="n">
-        <v>46127</v>
-      </c>
-      <c r="G58" s="188" t="n">
-        <v>46161</v>
-      </c>
-      <c r="H58" s="134" t="n">
-        <v>180</v>
-      </c>
-      <c r="I58" s="134">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J58" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="136">
-        <f>IFERROR(ROUND(H58*I58,0),0)</f>
-        <v/>
-      </c>
-      <c r="L58" s="136">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M58" s="136">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N58" s="137" t="n"/>
-      <c r="O58" s="137" t="n"/>
-      <c r="P58" s="137" t="n"/>
-      <c r="Q58" s="134">
-        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R58" s="134">
-        <f>IF(P58="","",H58)</f>
-        <v/>
-      </c>
-      <c r="S58" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="137" t="n"/>
-      <c r="V58" s="137" t="n"/>
-      <c r="W58" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y58" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="136">
-        <f>S58+T58+W58</f>
-        <v/>
-      </c>
-      <c r="AA58" s="136">
-        <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
-        <v/>
-      </c>
-      <c r="AB58" s="168" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC58" s="136">
-        <f>ROUND(AA58/AB58,0)</f>
-        <v/>
-      </c>
-      <c r="AD58" s="137" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="AE58" s="189" t="n">
-        <v>46143</v>
-      </c>
-      <c r="AF58" s="189" t="n">
-        <v>46507</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="132" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B59" s="132" t="inlineStr">
         <is>
-          <t>GPO480</t>
+          <t>GPO478</t>
         </is>
       </c>
       <c r="C59" s="132" t="inlineStr">
@@ -8734,13 +8765,13 @@
         </is>
       </c>
       <c r="F59" s="188" t="n">
-        <v>46137</v>
+        <v>46127</v>
       </c>
       <c r="G59" s="188" t="n">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="H59" s="134" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="I59" s="134">
         <f>IFERROR(VLOOKUP(B59,RemitTable2,7,FALSE),0)</f>
@@ -8800,7 +8831,7 @@
         <v/>
       </c>
       <c r="AB59" s="168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC59" s="136">
         <f>ROUND(AA59/AB59,0)</f>
@@ -8815,16 +8846,16 @@
         <v>46143</v>
       </c>
       <c r="AF59" s="189" t="n">
-        <v>49795</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="132" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B60" s="132" t="inlineStr">
         <is>
-          <t>GPO481</t>
+          <t>GPO480</t>
         </is>
       </c>
       <c r="C60" s="132" t="inlineStr">
@@ -8843,13 +8874,13 @@
         </is>
       </c>
       <c r="F60" s="188" t="n">
-        <v>46152</v>
-      </c>
-      <c r="G60" s="233" t="n">
-        <v>46183</v>
+        <v>46137</v>
+      </c>
+      <c r="G60" s="188" t="n">
+        <v>46171</v>
       </c>
       <c r="H60" s="134" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I60" s="134">
         <f>IFERROR(VLOOKUP(B60,RemitTable2,7,FALSE),0)</f>
@@ -8917,148 +8948,124 @@
       </c>
       <c r="AD60" s="137" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE60" s="189" t="n">
+        <v>46143</v>
+      </c>
+      <c r="AF60" s="189" t="n">
+        <v>49795</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="132" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" s="132" t="inlineStr">
+        <is>
+          <t>GPO481</t>
+        </is>
+      </c>
+      <c r="C61" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D61" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E61" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F61" s="188" t="n">
+        <v>46152</v>
+      </c>
+      <c r="G61" s="233" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H61" s="134" t="n">
+        <v>500</v>
+      </c>
+      <c r="I61" s="134">
+        <f>IFERROR(VLOOKUP(B61,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J61" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="136">
+        <f>IFERROR(ROUND(H61*I61,0),0)</f>
+        <v/>
+      </c>
+      <c r="L61" s="136">
+        <f>IFERROR(VLOOKUP(B61,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M61" s="136">
+        <f>IFERROR(VLOOKUP(B61,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N61" s="137" t="n"/>
+      <c r="O61" s="137" t="n"/>
+      <c r="P61" s="137" t="n"/>
+      <c r="Q61" s="134">
+        <f>IF(P61="","",IFERROR(VLOOKUP(O61,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R61" s="134">
+        <f>IF(P61="","",H61)</f>
+        <v/>
+      </c>
+      <c r="S61" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="137" t="n"/>
+      <c r="V61" s="137" t="n"/>
+      <c r="W61" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y61" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="136">
+        <f>S61+T61+W61</f>
+        <v/>
+      </c>
+      <c r="AA61" s="136">
+        <f>K61+L61+M61+IFERROR(VLOOKUP(B61,RemitTable2,9,FALSE),0)+Y61+Z61</f>
+        <v/>
+      </c>
+      <c r="AB61" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC61" s="136">
+        <f>ROUND(AA61/AB61,0)</f>
+        <v/>
+      </c>
+      <c r="AD61" s="137" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE60" s="137" t="inlineStr">
+      <c r="AE61" s="137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF60" s="137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>CPO688</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-      <c r="F61" s="176" t="n">
-        <v>46037</v>
-      </c>
-      <c r="G61" s="177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="16" t="n">
-        <v>4180</v>
-      </c>
-      <c r="I61" s="178">
-        <f>IFERROR(VLOOKUP(B61,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J61" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="18">
-        <f>IFERROR(ROUND(H61*I61,0),0)</f>
-        <v/>
-      </c>
-      <c r="L61" s="18">
-        <f>IFERROR(VLOOKUP(B61,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M61" s="18">
-        <f>IFERROR(VLOOKUP(B61,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N61" s="12" t="inlineStr">
-        <is>
-          <t>Inspection fee</t>
-        </is>
-      </c>
-      <c r="O61" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P61" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q61" s="16">
-        <f>IF(P61="","",IFERROR(VLOOKUP(O61,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R61" s="18">
-        <f>IF(P61="","",H61)</f>
-        <v/>
-      </c>
-      <c r="S61" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W61" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y61" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="18">
-        <f>S61+T61+W61</f>
-        <v/>
-      </c>
-      <c r="AA61" s="18">
-        <f>K61+L61+M61+IFERROR(VLOOKUP(B61,RemitTable2,9,FALSE),0)+Y61+Z61</f>
-        <v/>
-      </c>
-      <c r="AB61" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC61" s="18">
-        <f>ROUND(AA61/AB61,0)</f>
-        <v/>
-      </c>
-      <c r="AD61" s="12" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="AE61" s="177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF61" s="176" t="inlineStr">
+      <c r="AF61" s="137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9066,36 +9073,38 @@
     </row>
     <row r="62">
       <c r="A62" s="12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>SX3000수리</t>
+          <t>CPO688</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>Inspection</t>
+        </is>
+      </c>
+      <c r="F62" s="176" t="n">
+        <v>46037</v>
+      </c>
+      <c r="G62" s="177" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
-        <is>
-          <t>수리반환</t>
-        </is>
-      </c>
-      <c r="F62" s="176" t="n"/>
-      <c r="G62" s="177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H62" s="16" t="n">
-        <v>400</v>
+        <v>4180</v>
       </c>
       <c r="I62" s="178">
         <f>IFERROR(VLOOKUP(B62,RemitTable2,7,FALSE),0)</f>
@@ -9118,15 +9127,17 @@
       </c>
       <c r="N62" s="12" t="inlineStr">
         <is>
-          <t>Display Card (수리반환 5PCS)</t>
-        </is>
-      </c>
-      <c r="O62" s="177" t="n">
-        <v>46125</v>
+          <t>Inspection fee</t>
+        </is>
+      </c>
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P62" s="12" t="inlineStr">
         <is>
-          <t>22356-26-351613M</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q62" s="16">
@@ -9141,12 +9152,14 @@
         <v>0</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>67750</v>
-      </c>
-      <c r="U62" s="13" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="U62" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="V62" s="12" t="inlineStr">
         <is>
-          <t>운서합동</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W62" s="18" t="n">
@@ -9154,7 +9167,7 @@
       </c>
       <c r="X62" s="13" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y62" s="18" t="n">
@@ -9169,7 +9182,7 @@
         <v/>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC62" s="18">
         <f>ROUND(AA62/AB62,0)</f>
@@ -9177,206 +9190,262 @@
       </c>
       <c r="AD62" s="12" t="inlineStr">
         <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AE62" s="177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF62" s="176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>SX3000수리</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>수리반환</t>
+        </is>
+      </c>
+      <c r="F63" s="176" t="n"/>
+      <c r="G63" s="177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="I63" s="178">
+        <f>IFERROR(VLOOKUP(B63,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J63" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="18">
+        <f>IFERROR(ROUND(H63*I63,0),0)</f>
+        <v/>
+      </c>
+      <c r="L63" s="18">
+        <f>IFERROR(VLOOKUP(B63,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M63" s="18">
+        <f>IFERROR(VLOOKUP(B63,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N63" s="12" t="inlineStr">
+        <is>
+          <t>Display Card (수리반환 5PCS)</t>
+        </is>
+      </c>
+      <c r="O63" s="177" t="n">
+        <v>46125</v>
+      </c>
+      <c r="P63" s="12" t="inlineStr">
+        <is>
+          <t>22356-26-351613M</t>
+        </is>
+      </c>
+      <c r="Q63" s="16">
+        <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R63" s="18">
+        <f>IF(P63="","",H63)</f>
+        <v/>
+      </c>
+      <c r="S63" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="18" t="n">
+        <v>67750</v>
+      </c>
+      <c r="U63" s="13" t="n"/>
+      <c r="V63" s="12" t="inlineStr">
+        <is>
+          <t>운서합동</t>
+        </is>
+      </c>
+      <c r="W63" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="13" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="Y63" s="18" t="n">
+        <v>216006</v>
+      </c>
+      <c r="Z63" s="18">
+        <f>S63+T63+W63</f>
+        <v/>
+      </c>
+      <c r="AA63" s="18">
+        <f>K63+L63+M63+IFERROR(VLOOKUP(B63,RemitTable2,9,FALSE),0)+Y63+Z63</f>
+        <v/>
+      </c>
+      <c r="AB63" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC63" s="18">
+        <f>ROUND(AA63/AB63,0)</f>
+        <v/>
+      </c>
+      <c r="AD63" s="12" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE62" s="177" t="n"/>
-      <c r="AF62" s="176" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="216" t="n">
+      <c r="AE63" s="177" t="n"/>
+      <c r="AF63" s="176" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="216" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="216" t="inlineStr">
+      <c r="B64" s="216" t="inlineStr">
         <is>
           <t>FRC-MONOPLEX26</t>
         </is>
       </c>
-      <c r="C63" s="217" t="inlineStr">
+      <c r="C64" s="217" t="inlineStr">
         <is>
           <t>Ferco</t>
         </is>
       </c>
-      <c r="D63" s="216" t="inlineStr">
+      <c r="D64" s="216" t="inlineStr">
         <is>
           <t>50% TT advance + 50% balance</t>
         </is>
       </c>
-      <c r="E63" s="217" t="inlineStr">
+      <c r="E64" s="217" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="F63" s="218" t="n">
+      <c r="F64" s="218" t="n">
         <v>46048</v>
       </c>
-      <c r="G63" s="219" t="n">
+      <c r="G64" s="219" t="n">
         <v>46133</v>
       </c>
-      <c r="H63" s="220" t="n">
+      <c r="H64" s="220" t="n">
         <v>51952</v>
       </c>
-      <c r="I63" s="221">
-        <f>IFERROR(VLOOKUP(B63,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J63" s="222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="222">
-        <f>IFERROR(ROUND(H63*I63,0),0)</f>
-        <v/>
-      </c>
-      <c r="L63" s="222">
-        <f>IFERROR(VLOOKUP(B63,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M63" s="222">
-        <f>IFERROR(VLOOKUP(B63,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N63" s="216" t="inlineStr">
+      <c r="I64" s="221">
+        <f>IFERROR(VLOOKUP(B64,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J64" s="222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="222">
+        <f>IFERROR(ROUND(H64*I64,0),0)</f>
+        <v/>
+      </c>
+      <c r="L64" s="222">
+        <f>IFERROR(VLOOKUP(B64,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M64" s="222">
+        <f>IFERROR(VLOOKUP(B64,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N64" s="216" t="inlineStr">
         <is>
           <t>Cinema Seat (Recliner) / 44 EA / Monoplex DH Bangbae</t>
         </is>
       </c>
-      <c r="O63" s="219" t="n">
+      <c r="O64" s="219" t="n">
         <v>46153</v>
       </c>
-      <c r="P63" s="216" t="inlineStr">
+      <c r="P64" s="216" t="inlineStr">
         <is>
           <t>14008-26-101147M</t>
         </is>
       </c>
-      <c r="Q63" s="220">
-        <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R63" s="220">
-        <f>IF(P63="","",H63)</f>
-        <v/>
-      </c>
-      <c r="S63" s="222" t="n">
+      <c r="Q64" s="220">
+        <f>IF(P64="","",IFERROR(VLOOKUP(O64,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R64" s="220">
+        <f>IF(P64="","",H64)</f>
+        <v/>
+      </c>
+      <c r="S64" s="222" t="n">
         <v>31050</v>
       </c>
-      <c r="T63" s="222" t="n">
+      <c r="T64" s="222" t="n">
         <v>7959560</v>
       </c>
-      <c r="U63" s="218" t="n"/>
-      <c r="V63" s="216" t="inlineStr">
+      <c r="U64" s="218" t="n"/>
+      <c r="V64" s="216" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
       </c>
-      <c r="W63" s="222" t="n">
+      <c r="W64" s="222" t="n">
         <v>250000</v>
       </c>
-      <c r="X63" s="217" t="inlineStr">
+      <c r="X64" s="217" t="inlineStr">
         <is>
           <t>진로직스</t>
         </is>
       </c>
-      <c r="Y63" s="222" t="n">
+      <c r="Y64" s="222" t="n">
         <v>5002612</v>
       </c>
-      <c r="Z63" s="222">
-        <f>S63+T63+W63</f>
-        <v/>
-      </c>
-      <c r="AA63" s="222">
-        <f>K63+L63+M63+IFERROR(VLOOKUP(B63,RemitTable2,9,FALSE),0)+Y63+Z63</f>
-        <v/>
-      </c>
-      <c r="AB63" s="223" t="n">
+      <c r="Z64" s="222">
+        <f>S64+T64+W64</f>
+        <v/>
+      </c>
+      <c r="AA64" s="222">
+        <f>K64+L64+M64+IFERROR(VLOOKUP(B64,RemitTable2,9,FALSE),0)+Y64+Z64</f>
+        <v/>
+      </c>
+      <c r="AB64" s="223" t="n">
         <v>44</v>
       </c>
-      <c r="AC63" s="222">
-        <f>ROUND(AA63/AB63,0)</f>
-        <v/>
-      </c>
-      <c r="AD63" s="216" t="inlineStr">
+      <c r="AC64" s="222">
+        <f>ROUND(AA64/AB64,0)</f>
+        <v/>
+      </c>
+      <c r="AD64" s="216" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE63" s="216" t="n"/>
-      <c r="AF63" s="217" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="147" t="inlineStr">
-        <is>
-          <t>장비/부품 합계</t>
-        </is>
-      </c>
-      <c r="B64" s="148" t="n"/>
-      <c r="C64" s="148" t="n"/>
-      <c r="D64" s="148" t="n"/>
-      <c r="E64" s="148" t="n"/>
-      <c r="F64" s="148" t="n"/>
-      <c r="G64" s="149" t="n"/>
-      <c r="H64" s="142">
-        <f>SUBTOTAL(9,H5:H38)</f>
-        <v/>
-      </c>
-      <c r="I64" s="141" t="n"/>
-      <c r="J64" s="142">
-        <f>SUBTOTAL(9,J5:J38)</f>
-        <v/>
-      </c>
-      <c r="K64" s="142">
-        <f>SUBTOTAL(9,K5:K38)</f>
-        <v/>
-      </c>
-      <c r="L64" s="142">
-        <f>SUBTOTAL(9,L5:L38)</f>
-        <v/>
-      </c>
-      <c r="M64" s="142">
-        <f>SUBTOTAL(9,M5:M38)</f>
-        <v/>
-      </c>
-      <c r="N64" s="141" t="n"/>
-      <c r="O64" s="141" t="n"/>
-      <c r="P64" s="141" t="n"/>
-      <c r="Q64" s="142" t="n"/>
-      <c r="R64" s="140" t="n"/>
-      <c r="S64" s="142">
-        <f>SUBTOTAL(9,S5:S38)</f>
-        <v/>
-      </c>
-      <c r="T64" s="142">
-        <f>SUBTOTAL(9,T5:T38)</f>
-        <v/>
-      </c>
-      <c r="U64" s="141" t="n"/>
-      <c r="V64" s="141" t="n"/>
-      <c r="W64" s="142">
-        <f>SUBTOTAL(9,W5:W38)</f>
-        <v/>
-      </c>
-      <c r="X64" s="147" t="n"/>
-      <c r="Y64" s="142">
-        <f>SUBTOTAL(9,Y5:Y38)</f>
-        <v/>
-      </c>
-      <c r="Z64" s="142">
-        <f>SUBTOTAL(9,Z5:Z38)</f>
-        <v/>
-      </c>
-      <c r="AA64" s="142">
-        <f>SUBTOTAL(9,AA5:AA38)</f>
-        <v/>
-      </c>
-      <c r="AB64" s="147" t="n"/>
-      <c r="AC64" s="141" t="n"/>
-      <c r="AD64" s="141" t="n"/>
-      <c r="AE64" s="141" t="n"/>
-      <c r="AF64" s="141" t="n"/>
+      <c r="AE64" s="216" t="n"/>
+      <c r="AF64" s="217" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="147" t="inlineStr">
         <is>
-          <t>라이센스/워런티 합계</t>
+          <t>장비/부품 합계</t>
         </is>
       </c>
       <c r="B65" s="148" t="n"/>
@@ -9386,24 +9455,24 @@
       <c r="F65" s="148" t="n"/>
       <c r="G65" s="149" t="n"/>
       <c r="H65" s="142">
-        <f>SUBTOTAL(9,H39:H60)</f>
+        <f>SUBTOTAL(9,H5:H39)</f>
         <v/>
       </c>
       <c r="I65" s="141" t="n"/>
       <c r="J65" s="142">
-        <f>SUBTOTAL(9,J39:J60)</f>
+        <f>SUBTOTAL(9,J5:J39)</f>
         <v/>
       </c>
       <c r="K65" s="142">
-        <f>SUBTOTAL(9,K39:K60)</f>
+        <f>SUBTOTAL(9,K5:K39)</f>
         <v/>
       </c>
       <c r="L65" s="142">
-        <f>SUBTOTAL(9,L39:L60)</f>
+        <f>SUBTOTAL(9,L5:L39)</f>
         <v/>
       </c>
       <c r="M65" s="142">
-        <f>SUBTOTAL(9,M39:M60)</f>
+        <f>SUBTOTAL(9,M5:M39)</f>
         <v/>
       </c>
       <c r="N65" s="141" t="n"/>
@@ -9412,30 +9481,30 @@
       <c r="Q65" s="142" t="n"/>
       <c r="R65" s="140" t="n"/>
       <c r="S65" s="142">
-        <f>SUBTOTAL(9,S39:S60)</f>
+        <f>SUBTOTAL(9,S5:S39)</f>
         <v/>
       </c>
       <c r="T65" s="142">
-        <f>SUBTOTAL(9,T39:T60)</f>
+        <f>SUBTOTAL(9,T5:T39)</f>
         <v/>
       </c>
       <c r="U65" s="141" t="n"/>
       <c r="V65" s="141" t="n"/>
       <c r="W65" s="142">
-        <f>SUBTOTAL(9,W39:W60)</f>
+        <f>SUBTOTAL(9,W5:W39)</f>
         <v/>
       </c>
       <c r="X65" s="147" t="n"/>
       <c r="Y65" s="142">
-        <f>SUBTOTAL(9,Y39:Y60)</f>
+        <f>SUBTOTAL(9,Y5:Y39)</f>
         <v/>
       </c>
       <c r="Z65" s="142">
-        <f>SUBTOTAL(9,Z39:Z60)</f>
+        <f>SUBTOTAL(9,Z5:Z39)</f>
         <v/>
       </c>
       <c r="AA65" s="142">
-        <f>SUBTOTAL(9,AA39:AA60)</f>
+        <f>SUBTOTAL(9,AA5:AA39)</f>
         <v/>
       </c>
       <c r="AB65" s="147" t="n"/>
@@ -9447,7 +9516,7 @@
     <row r="66">
       <c r="A66" s="147" t="inlineStr">
         <is>
-          <t>기타 합계</t>
+          <t>라이센스/워런티 합계</t>
         </is>
       </c>
       <c r="B66" s="148" t="n"/>
@@ -9457,24 +9526,24 @@
       <c r="F66" s="148" t="n"/>
       <c r="G66" s="149" t="n"/>
       <c r="H66" s="142">
-        <f>SUBTOTAL(9,H61:H63)</f>
+        <f>SUBTOTAL(9,H40:H61)</f>
         <v/>
       </c>
       <c r="I66" s="141" t="n"/>
       <c r="J66" s="142">
-        <f>SUBTOTAL(9,J61:J63)</f>
+        <f>SUBTOTAL(9,J40:J61)</f>
         <v/>
       </c>
       <c r="K66" s="142">
-        <f>SUBTOTAL(9,K61:K63)</f>
+        <f>SUBTOTAL(9,K40:K61)</f>
         <v/>
       </c>
       <c r="L66" s="142">
-        <f>SUBTOTAL(9,L61:L63)</f>
+        <f>SUBTOTAL(9,L40:L61)</f>
         <v/>
       </c>
       <c r="M66" s="142">
-        <f>SUBTOTAL(9,M61:M63)</f>
+        <f>SUBTOTAL(9,M40:M61)</f>
         <v/>
       </c>
       <c r="N66" s="141" t="n"/>
@@ -9483,30 +9552,30 @@
       <c r="Q66" s="142" t="n"/>
       <c r="R66" s="140" t="n"/>
       <c r="S66" s="142">
-        <f>SUBTOTAL(9,S61:S63)</f>
+        <f>SUBTOTAL(9,S40:S61)</f>
         <v/>
       </c>
       <c r="T66" s="142">
-        <f>SUBTOTAL(9,T61:T63)</f>
+        <f>SUBTOTAL(9,T40:T61)</f>
         <v/>
       </c>
       <c r="U66" s="141" t="n"/>
       <c r="V66" s="141" t="n"/>
       <c r="W66" s="142">
-        <f>SUBTOTAL(9,W61:W63)</f>
+        <f>SUBTOTAL(9,W40:W61)</f>
         <v/>
       </c>
       <c r="X66" s="147" t="n"/>
       <c r="Y66" s="142">
-        <f>SUBTOTAL(9,Y61:Y63)</f>
+        <f>SUBTOTAL(9,Y40:Y61)</f>
         <v/>
       </c>
       <c r="Z66" s="142">
-        <f>SUBTOTAL(9,Z61:Z63)</f>
+        <f>SUBTOTAL(9,Z40:Z61)</f>
         <v/>
       </c>
       <c r="AA66" s="142">
-        <f>SUBTOTAL(9,AA61:AA63)</f>
+        <f>SUBTOTAL(9,AA40:AA61)</f>
         <v/>
       </c>
       <c r="AB66" s="147" t="n"/>
@@ -9516,9 +9585,9 @@
       <c r="AF66" s="141" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="154" t="inlineStr">
-        <is>
-          <t>총 합계</t>
+      <c r="A67" s="147" t="inlineStr">
+        <is>
+          <t>기타 합계</t>
         </is>
       </c>
       <c r="B67" s="148" t="n"/>
@@ -9527,98 +9596,135 @@
       <c r="E67" s="148" t="n"/>
       <c r="F67" s="148" t="n"/>
       <c r="G67" s="149" t="n"/>
-      <c r="H67" s="146">
-        <f>SUBTOTAL(9,H5:H63)</f>
-        <v/>
-      </c>
-      <c r="I67" s="145" t="n"/>
-      <c r="J67" s="146">
-        <f>SUBTOTAL(9,J5:J63)</f>
-        <v/>
-      </c>
-      <c r="K67" s="146">
-        <f>SUBTOTAL(9,K5:K63)</f>
-        <v/>
-      </c>
-      <c r="L67" s="146">
-        <f>SUBTOTAL(9,L5:L63)</f>
-        <v/>
-      </c>
-      <c r="M67" s="146">
-        <f>SUBTOTAL(9,M5:M63)</f>
-        <v/>
-      </c>
-      <c r="N67" s="145" t="n"/>
-      <c r="O67" s="145" t="n"/>
-      <c r="P67" s="145" t="n"/>
-      <c r="Q67" s="146" t="n"/>
-      <c r="R67" s="144" t="n"/>
-      <c r="S67" s="146">
-        <f>SUBTOTAL(9,S5:S63)</f>
-        <v/>
-      </c>
-      <c r="T67" s="146">
-        <f>SUBTOTAL(9,T5:T63)</f>
-        <v/>
-      </c>
-      <c r="U67" s="145" t="n"/>
-      <c r="V67" s="145" t="n"/>
-      <c r="W67" s="146">
-        <f>SUBTOTAL(9,W5:W63)</f>
-        <v/>
-      </c>
-      <c r="X67" s="154" t="n"/>
-      <c r="Y67" s="146">
-        <f>SUBTOTAL(9,Y5:Y63)</f>
-        <v/>
-      </c>
-      <c r="Z67" s="146">
-        <f>SUBTOTAL(9,Z5:Z63)</f>
-        <v/>
-      </c>
-      <c r="AA67" s="146">
-        <f>SUBTOTAL(9,AA5:AA63)</f>
-        <v/>
-      </c>
-      <c r="AB67" s="154" t="n"/>
-      <c r="AC67" s="145" t="n"/>
-      <c r="AD67" s="145" t="n"/>
-      <c r="AE67" s="145" t="n"/>
-      <c r="AF67" s="145" t="n"/>
+      <c r="H67" s="142">
+        <f>SUBTOTAL(9,H62:H64)</f>
+        <v/>
+      </c>
+      <c r="I67" s="141" t="n"/>
+      <c r="J67" s="142">
+        <f>SUBTOTAL(9,J62:J64)</f>
+        <v/>
+      </c>
+      <c r="K67" s="142">
+        <f>SUBTOTAL(9,K62:K64)</f>
+        <v/>
+      </c>
+      <c r="L67" s="142">
+        <f>SUBTOTAL(9,L62:L64)</f>
+        <v/>
+      </c>
+      <c r="M67" s="142">
+        <f>SUBTOTAL(9,M62:M64)</f>
+        <v/>
+      </c>
+      <c r="N67" s="141" t="n"/>
+      <c r="O67" s="141" t="n"/>
+      <c r="P67" s="141" t="n"/>
+      <c r="Q67" s="142" t="n"/>
+      <c r="R67" s="140" t="n"/>
+      <c r="S67" s="142">
+        <f>SUBTOTAL(9,S62:S64)</f>
+        <v/>
+      </c>
+      <c r="T67" s="142">
+        <f>SUBTOTAL(9,T62:T64)</f>
+        <v/>
+      </c>
+      <c r="U67" s="141" t="n"/>
+      <c r="V67" s="141" t="n"/>
+      <c r="W67" s="142">
+        <f>SUBTOTAL(9,W62:W64)</f>
+        <v/>
+      </c>
+      <c r="X67" s="147" t="n"/>
+      <c r="Y67" s="142">
+        <f>SUBTOTAL(9,Y62:Y64)</f>
+        <v/>
+      </c>
+      <c r="Z67" s="142">
+        <f>SUBTOTAL(9,Z62:Z64)</f>
+        <v/>
+      </c>
+      <c r="AA67" s="142">
+        <f>SUBTOTAL(9,AA62:AA64)</f>
+        <v/>
+      </c>
+      <c r="AB67" s="147" t="n"/>
+      <c r="AC67" s="141" t="n"/>
+      <c r="AD67" s="141" t="n"/>
+      <c r="AE67" s="141" t="n"/>
+      <c r="AF67" s="141" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="39" t="n"/>
-      <c r="B68" s="39" t="n"/>
-      <c r="C68" s="39" t="n"/>
-      <c r="D68" s="39" t="n"/>
-      <c r="E68" s="39" t="n"/>
-      <c r="F68" s="39" t="n"/>
-      <c r="G68" s="39" t="n"/>
-      <c r="H68" s="39" t="n"/>
-      <c r="I68" s="39" t="n"/>
-      <c r="J68" s="39" t="n"/>
-      <c r="K68" s="39" t="n"/>
-      <c r="L68" s="39" t="n"/>
-      <c r="M68" s="39" t="n"/>
-      <c r="N68" s="39" t="n"/>
-      <c r="O68" s="39" t="n"/>
-      <c r="P68" s="39" t="n"/>
-      <c r="Q68" s="39" t="n"/>
-      <c r="R68" s="39" t="n"/>
-      <c r="S68" s="39" t="n"/>
-      <c r="T68" s="39" t="n"/>
-      <c r="U68" s="39" t="n"/>
-      <c r="V68" s="39" t="n"/>
-      <c r="W68" s="39" t="n"/>
-      <c r="X68" s="75" t="n"/>
-      <c r="Y68" s="39" t="n"/>
-      <c r="Z68" s="39" t="n"/>
-      <c r="AA68" s="39" t="n"/>
-      <c r="AB68" s="75" t="n"/>
-      <c r="AC68" s="39" t="n"/>
-      <c r="AD68" s="39" t="n"/>
-      <c r="AE68" s="39" t="n"/>
-      <c r="AF68" s="39" t="n"/>
+      <c r="A68" s="154" t="inlineStr">
+        <is>
+          <t>총 합계</t>
+        </is>
+      </c>
+      <c r="B68" s="148" t="n"/>
+      <c r="C68" s="148" t="n"/>
+      <c r="D68" s="148" t="n"/>
+      <c r="E68" s="148" t="n"/>
+      <c r="F68" s="148" t="n"/>
+      <c r="G68" s="149" t="n"/>
+      <c r="H68" s="146">
+        <f>SUBTOTAL(9,H5:H64)</f>
+        <v/>
+      </c>
+      <c r="I68" s="145" t="n"/>
+      <c r="J68" s="146">
+        <f>SUBTOTAL(9,J5:J64)</f>
+        <v/>
+      </c>
+      <c r="K68" s="146">
+        <f>SUBTOTAL(9,K5:K64)</f>
+        <v/>
+      </c>
+      <c r="L68" s="146">
+        <f>SUBTOTAL(9,L5:L64)</f>
+        <v/>
+      </c>
+      <c r="M68" s="146">
+        <f>SUBTOTAL(9,M5:M64)</f>
+        <v/>
+      </c>
+      <c r="N68" s="145" t="n"/>
+      <c r="O68" s="145" t="n"/>
+      <c r="P68" s="145" t="n"/>
+      <c r="Q68" s="146" t="n"/>
+      <c r="R68" s="144" t="n"/>
+      <c r="S68" s="146">
+        <f>SUBTOTAL(9,S5:S64)</f>
+        <v/>
+      </c>
+      <c r="T68" s="146">
+        <f>SUBTOTAL(9,T5:T64)</f>
+        <v/>
+      </c>
+      <c r="U68" s="145" t="n"/>
+      <c r="V68" s="145" t="n"/>
+      <c r="W68" s="146">
+        <f>SUBTOTAL(9,W5:W64)</f>
+        <v/>
+      </c>
+      <c r="X68" s="154" t="n"/>
+      <c r="Y68" s="146">
+        <f>SUBTOTAL(9,Y5:Y64)</f>
+        <v/>
+      </c>
+      <c r="Z68" s="146">
+        <f>SUBTOTAL(9,Z5:Z64)</f>
+        <v/>
+      </c>
+      <c r="AA68" s="146">
+        <f>SUBTOTAL(9,AA5:AA64)</f>
+        <v/>
+      </c>
+      <c r="AB68" s="154" t="n"/>
+      <c r="AC68" s="145" t="n"/>
+      <c r="AD68" s="145" t="n"/>
+      <c r="AE68" s="145" t="n"/>
+      <c r="AF68" s="145" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="39" t="n"/>
@@ -9756,8 +9862,42 @@
       <c r="AE72" s="39" t="n"/>
       <c r="AF72" s="39" t="n"/>
     </row>
-    <row r="86">
-      <c r="M86" s="40" t="n"/>
+    <row r="73">
+      <c r="A73" s="39" t="n"/>
+      <c r="B73" s="39" t="n"/>
+      <c r="C73" s="39" t="n"/>
+      <c r="D73" s="39" t="n"/>
+      <c r="E73" s="39" t="n"/>
+      <c r="F73" s="39" t="n"/>
+      <c r="G73" s="39" t="n"/>
+      <c r="H73" s="39" t="n"/>
+      <c r="I73" s="39" t="n"/>
+      <c r="J73" s="39" t="n"/>
+      <c r="K73" s="39" t="n"/>
+      <c r="L73" s="39" t="n"/>
+      <c r="M73" s="39" t="n"/>
+      <c r="N73" s="39" t="n"/>
+      <c r="O73" s="39" t="n"/>
+      <c r="P73" s="39" t="n"/>
+      <c r="Q73" s="39" t="n"/>
+      <c r="R73" s="39" t="n"/>
+      <c r="S73" s="39" t="n"/>
+      <c r="T73" s="39" t="n"/>
+      <c r="U73" s="39" t="n"/>
+      <c r="V73" s="39" t="n"/>
+      <c r="W73" s="39" t="n"/>
+      <c r="X73" s="75" t="n"/>
+      <c r="Y73" s="39" t="n"/>
+      <c r="Z73" s="39" t="n"/>
+      <c r="AA73" s="39" t="n"/>
+      <c r="AB73" s="75" t="n"/>
+      <c r="AC73" s="39" t="n"/>
+      <c r="AD73" s="39" t="n"/>
+      <c r="AE73" s="39" t="n"/>
+      <c r="AF73" s="39" t="n"/>
+    </row>
+    <row r="87">
+      <c r="M87" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -9767,9 +9907,9 @@
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="A64:G64"/>
     <mergeCell ref="A65:G65"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A68:G68"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="O3:W3"/>
     <mergeCell ref="A2:AF2"/>
@@ -12413,11 +12553,11 @@
       </c>
       <c r="G34" s="241" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="H34" s="244" t="n">
-        <v>0</v>
+        <v>216006</v>
       </c>
       <c r="I34" s="241" t="inlineStr">
         <is>
@@ -12461,7 +12601,7 @@
         </is>
       </c>
       <c r="H35" s="244" t="n">
-        <v>0</v>
+        <v>174806</v>
       </c>
       <c r="I35" s="241" t="inlineStr">
         <is>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -24,14 +24,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0&quot;일&quot;"/>
     <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -193,8 +195,22 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -292,8 +308,23 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -429,11 +460,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="272">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1138,6 +1175,87 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="24" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="25" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="20" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1387,6 +1505,28 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>RNR 재무팀</author>
+  </authors>
+  <commentList>
+    <comment ref="N17" authorId="0" shapeId="0">
+      <text>
+        <t>은행 원금 상환 전표(원화 출금) 미수취
+전표 수취 후 상환환율과 KRW 확정 기입</t>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="0" shapeId="0">
+      <text>
+        <t>신한은행 원금 상환 전표(원화 출금액) 미수취
+수취 즉시 환율/KRW 기입 예정</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -17187,7 +17327,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="163" t="inlineStr">
         <is>
-          <t>기준일: 2026-06-10  |  미상환 건만 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
+          <t>기준일: 2026-06-10  |  상환 완료 건은 초록색 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
         </is>
       </c>
     </row>
@@ -17372,7 +17512,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="199" t="inlineStr">
         <is>
-          <t>&lt; 미상환 L/C 현황 &gt;</t>
+          <t>&lt; Usance L/C 현황 (상환완료 포함) &gt;</t>
         </is>
       </c>
       <c r="B14" s="148" t="n"/>
@@ -17534,70 +17674,70 @@
       <c r="P16" s="59" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="59" t="n">
+      <c r="A17" s="245" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="245" t="inlineStr">
         <is>
           <t>GPO-446-2</t>
         </is>
       </c>
-      <c r="C17" s="74" t="inlineStr">
+      <c r="C17" s="246" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D17" s="60" t="n">
+      <c r="D17" s="247" t="n">
         <v>190470</v>
       </c>
-      <c r="E17" s="59" t="inlineStr">
+      <c r="E17" s="245" t="inlineStr">
         <is>
           <t>신한은행</t>
         </is>
       </c>
-      <c r="F17" s="59" t="inlineStr">
+      <c r="F17" s="245" t="inlineStr">
         <is>
           <t>M88JX2511NU00018</t>
         </is>
       </c>
-      <c r="G17" s="59" t="inlineStr">
+      <c r="G17" s="245" t="inlineStr">
         <is>
           <t>2025-11-11</t>
         </is>
       </c>
-      <c r="H17" s="59" t="inlineStr">
+      <c r="H17" s="245" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="I17" s="59" t="inlineStr">
+      <c r="I17" s="245" t="inlineStr">
         <is>
           <t>180 Days</t>
         </is>
       </c>
-      <c r="J17" s="59" t="inlineStr">
+      <c r="J17" s="245" t="inlineStr">
         <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="K17" s="59" t="inlineStr">
+      <c r="K17" s="245" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="L17" s="200" t="n">
-        <v>60</v>
-      </c>
-      <c r="M17" s="59" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="N17" s="201" t="n"/>
-      <c r="O17" s="63" t="n"/>
-      <c r="P17" s="59" t="inlineStr">
-        <is>
-          <t>6/9 만기 상환 완료 (USD 190,470)</t>
+      <c r="L17" s="248" t="inlineStr">
+        <is>
+          <t>상환완료</t>
+        </is>
+      </c>
+      <c r="M17" s="249" t="n">
+        <v>46182</v>
+      </c>
+      <c r="N17" s="250" t="n"/>
+      <c r="O17" s="251" t="n"/>
+      <c r="P17" s="245" t="inlineStr">
+        <is>
+          <t>6/9 만기 상환 완료, 하단 정산 명세 참조</t>
         </is>
       </c>
     </row>
@@ -17855,7 +17995,11 @@
       <c r="P24" s="65" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="65" t="n"/>
+      <c r="A25" s="252" t="inlineStr">
+        <is>
+          <t>&lt; GPO-446-2 상환 정산 및 수수료 명세 (신한은행, 출처: 은행 수수료 내역서 2026-06-09 조회) &gt;</t>
+        </is>
+      </c>
       <c r="B25" s="65" t="n"/>
       <c r="C25" s="66" t="n"/>
       <c r="D25" s="65" t="n"/>
@@ -17873,12 +18017,36 @@
       <c r="P25" s="65" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="65" t="n"/>
-      <c r="B26" s="65" t="n"/>
-      <c r="C26" s="66" t="n"/>
-      <c r="D26" s="65" t="n"/>
-      <c r="E26" s="65" t="n"/>
-      <c r="F26" s="65" t="n"/>
+      <c r="A26" s="253" t="inlineStr">
+        <is>
+          <t>상환일</t>
+        </is>
+      </c>
+      <c r="B26" s="253" t="inlineStr">
+        <is>
+          <t>상환원금(USD)</t>
+        </is>
+      </c>
+      <c r="C26" s="253" t="inlineStr">
+        <is>
+          <t>상환환율(₩)</t>
+        </is>
+      </c>
+      <c r="D26" s="253" t="inlineStr">
+        <is>
+          <t>상환금액(KRW)</t>
+        </is>
+      </c>
+      <c r="E26" s="253" t="inlineStr">
+        <is>
+          <t>L/C No.</t>
+        </is>
+      </c>
+      <c r="F26" s="253" t="inlineStr">
+        <is>
+          <t>회계처리(권장)</t>
+        </is>
+      </c>
       <c r="G26" s="65" t="n"/>
       <c r="H26" s="65" t="n"/>
       <c r="I26" s="65" t="n"/>
@@ -17891,12 +18059,32 @@
       <c r="P26" s="65" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="65" t="n"/>
-      <c r="B27" s="65" t="n"/>
-      <c r="C27" s="66" t="n"/>
-      <c r="D27" s="65" t="n"/>
-      <c r="E27" s="65" t="n"/>
-      <c r="F27" s="70" t="n"/>
+      <c r="A27" s="254" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B27" s="255" t="n">
+        <v>190470</v>
+      </c>
+      <c r="C27" s="256" t="inlineStr">
+        <is>
+          <t>전표 확인 필요</t>
+        </is>
+      </c>
+      <c r="D27" s="256" t="inlineStr">
+        <is>
+          <t>전표 확인 필요</t>
+        </is>
+      </c>
+      <c r="E27" s="257" t="inlineStr">
+        <is>
+          <t>M88JX2511NU00018</t>
+        </is>
+      </c>
+      <c r="F27" s="258" t="inlineStr">
+        <is>
+          <t>차변 외화매입채무 190,470 USD, 대변 보통예금(상환환율), 차액 외환차손익</t>
+        </is>
+      </c>
       <c r="G27" s="71" t="n"/>
       <c r="H27" s="65" t="n"/>
       <c r="I27" s="65" t="n"/>
@@ -17927,16 +18115,56 @@
       <c r="P28" s="65" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="65" t="n"/>
-      <c r="B29" s="65" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="65" t="n"/>
-      <c r="E29" s="65" t="n"/>
-      <c r="F29" s="70" t="n"/>
-      <c r="G29" s="71" t="n"/>
-      <c r="H29" s="65" t="n"/>
-      <c r="I29" s="65" t="n"/>
-      <c r="J29" s="65" t="n"/>
+      <c r="A29" s="253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B29" s="253" t="inlineStr">
+        <is>
+          <t>징수일</t>
+        </is>
+      </c>
+      <c r="C29" s="253" t="inlineStr">
+        <is>
+          <t>수수료 구분</t>
+        </is>
+      </c>
+      <c r="D29" s="253" t="inlineStr">
+        <is>
+          <t>이율(%)</t>
+        </is>
+      </c>
+      <c r="E29" s="253" t="inlineStr">
+        <is>
+          <t>수수료 기간</t>
+        </is>
+      </c>
+      <c r="F29" s="259" t="inlineStr">
+        <is>
+          <t>일수</t>
+        </is>
+      </c>
+      <c r="G29" s="260" t="inlineStr">
+        <is>
+          <t>대상금액(USD)</t>
+        </is>
+      </c>
+      <c r="H29" s="253" t="inlineStr">
+        <is>
+          <t>USD 상당액</t>
+        </is>
+      </c>
+      <c r="I29" s="253" t="inlineStr">
+        <is>
+          <t>징수액(KRW)</t>
+        </is>
+      </c>
+      <c r="J29" s="253" t="inlineStr">
+        <is>
+          <t>회계처리(권장)</t>
+        </is>
+      </c>
       <c r="K29" s="65" t="n"/>
       <c r="L29" s="65" t="n"/>
       <c r="M29" s="65" t="n"/>
@@ -17945,16 +18173,42 @@
       <c r="P29" s="65" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="65" t="n"/>
-      <c r="B30" s="65" t="n"/>
-      <c r="C30" s="66" t="n"/>
-      <c r="D30" s="65" t="n"/>
-      <c r="E30" s="65" t="n"/>
-      <c r="F30" s="70" t="n"/>
-      <c r="G30" s="71" t="n"/>
-      <c r="H30" s="65" t="n"/>
-      <c r="I30" s="65" t="n"/>
-      <c r="J30" s="65" t="n"/>
+      <c r="A30" s="257" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="254" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C30" s="261" t="inlineStr">
+        <is>
+          <t>수입신용장 기간수수료(발행수수료, 360일 단위)</t>
+        </is>
+      </c>
+      <c r="D30" s="262" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E30" s="257" t="inlineStr">
+        <is>
+          <t>2025-11-10 ~ 2025-12-26</t>
+        </is>
+      </c>
+      <c r="F30" s="263" t="n">
+        <v>47</v>
+      </c>
+      <c r="G30" s="255" t="n">
+        <v>190470</v>
+      </c>
+      <c r="H30" s="255" t="n">
+        <v>198.94</v>
+      </c>
+      <c r="I30" s="264" t="n">
+        <v>289132</v>
+      </c>
+      <c r="J30" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="K30" s="65" t="n"/>
       <c r="L30" s="65" t="n"/>
       <c r="M30" s="65" t="n"/>
@@ -17963,16 +18217,32 @@
       <c r="P30" s="65" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="65" t="n"/>
-      <c r="B31" s="65" t="n"/>
-      <c r="C31" s="66" t="n"/>
-      <c r="D31" s="65" t="n"/>
-      <c r="E31" s="65" t="n"/>
-      <c r="F31" s="70" t="n"/>
-      <c r="G31" s="71" t="n"/>
-      <c r="H31" s="65" t="n"/>
-      <c r="I31" s="65" t="n"/>
-      <c r="J31" s="65" t="n"/>
+      <c r="A31" s="257" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="254" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C31" s="261" t="inlineStr">
+        <is>
+          <t>전신료(일반신용장 USANCE)</t>
+        </is>
+      </c>
+      <c r="D31" s="262" t="n"/>
+      <c r="E31" s="257" t="inlineStr"/>
+      <c r="F31" s="263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="255" t="n"/>
+      <c r="H31" s="255" t="n"/>
+      <c r="I31" s="264" t="n">
+        <v>13750</v>
+      </c>
+      <c r="J31" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="K31" s="65" t="n"/>
       <c r="L31" s="65" t="n"/>
       <c r="M31" s="65" t="n"/>
@@ -17981,16 +18251,32 @@
       <c r="P31" s="65" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="65" t="n"/>
-      <c r="B32" s="65" t="n"/>
-      <c r="C32" s="66" t="n"/>
-      <c r="D32" s="65" t="n"/>
-      <c r="E32" s="65" t="n"/>
-      <c r="F32" s="70" t="n"/>
-      <c r="G32" s="71" t="n"/>
-      <c r="H32" s="65" t="n"/>
-      <c r="I32" s="65" t="n"/>
-      <c r="J32" s="65" t="n"/>
+      <c r="A32" s="257" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="254" t="n">
+        <v>45980</v>
+      </c>
+      <c r="C32" s="261" t="inlineStr">
+        <is>
+          <t>수입화물선취보증서(L/G) 발급수수료</t>
+        </is>
+      </c>
+      <c r="D32" s="262" t="n"/>
+      <c r="E32" s="257" t="inlineStr"/>
+      <c r="F32" s="263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="255" t="n"/>
+      <c r="H32" s="255" t="n"/>
+      <c r="I32" s="264" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J32" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="K32" s="65" t="n"/>
       <c r="L32" s="65" t="n"/>
       <c r="M32" s="65" t="n"/>
@@ -17999,16 +18285,42 @@
       <c r="P32" s="65" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="65" t="n"/>
-      <c r="B33" s="65" t="n"/>
-      <c r="C33" s="66" t="n"/>
-      <c r="D33" s="65" t="n"/>
-      <c r="E33" s="65" t="n"/>
-      <c r="F33" s="70" t="n"/>
-      <c r="G33" s="71" t="n"/>
-      <c r="H33" s="65" t="n"/>
-      <c r="I33" s="65" t="n"/>
-      <c r="J33" s="65" t="n"/>
+      <c r="A33" s="257" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="254" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C33" s="261" t="inlineStr">
+        <is>
+          <t>수입화물선취보증료(외화)</t>
+        </is>
+      </c>
+      <c r="D33" s="262" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="257" t="inlineStr">
+        <is>
+          <t>2025-11-19 ~ 2025-12-07</t>
+        </is>
+      </c>
+      <c r="F33" s="263" t="n">
+        <v>19</v>
+      </c>
+      <c r="G33" s="255" t="n">
+        <v>190470</v>
+      </c>
+      <c r="H33" s="255" t="n">
+        <v>301.58</v>
+      </c>
+      <c r="I33" s="264" t="n">
+        <v>442866</v>
+      </c>
+      <c r="J33" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
       <c r="K33" s="65" t="n"/>
       <c r="L33" s="65" t="n"/>
       <c r="M33" s="65" t="n"/>
@@ -18017,16 +18329,42 @@
       <c r="P33" s="65" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="65" t="n"/>
-      <c r="B34" s="65" t="n"/>
-      <c r="C34" s="66" t="n"/>
-      <c r="D34" s="65" t="n"/>
-      <c r="E34" s="65" t="n"/>
-      <c r="F34" s="70" t="n"/>
-      <c r="G34" s="71" t="n"/>
-      <c r="H34" s="65" t="n"/>
-      <c r="I34" s="65" t="n"/>
-      <c r="J34" s="65" t="n"/>
+      <c r="A34" s="257" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="254" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C34" s="261" t="inlineStr">
+        <is>
+          <t>수입인수수수료(360일 단위)</t>
+        </is>
+      </c>
+      <c r="D34" s="262" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E34" s="257" t="inlineStr">
+        <is>
+          <t>2025-12-08 ~ 2026-05-31</t>
+        </is>
+      </c>
+      <c r="F34" s="263" t="n">
+        <v>175</v>
+      </c>
+      <c r="G34" s="255" t="n">
+        <v>190470</v>
+      </c>
+      <c r="H34" s="255" t="n">
+        <v>1111.08</v>
+      </c>
+      <c r="I34" s="264" t="n">
+        <v>1631613</v>
+      </c>
+      <c r="J34" s="257" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
       <c r="K34" s="65" t="n"/>
       <c r="L34" s="65" t="n"/>
       <c r="M34" s="65" t="n"/>
@@ -18035,16 +18373,42 @@
       <c r="P34" s="65" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="65" t="n"/>
-      <c r="B35" s="65" t="n"/>
-      <c r="C35" s="66" t="n"/>
-      <c r="D35" s="65" t="n"/>
-      <c r="E35" s="65" t="n"/>
-      <c r="F35" s="70" t="n"/>
-      <c r="G35" s="71" t="n"/>
-      <c r="H35" s="65" t="n"/>
-      <c r="I35" s="65" t="n"/>
-      <c r="J35" s="65" t="n"/>
+      <c r="A35" s="257" t="n">
+        <v>6</v>
+      </c>
+      <c r="B35" s="254" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C35" s="261" t="inlineStr">
+        <is>
+          <t>수입기간수수료 환급(-)</t>
+        </is>
+      </c>
+      <c r="D35" s="262" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E35" s="257" t="inlineStr">
+        <is>
+          <t>2025-12-08 ~ 2025-12-26</t>
+        </is>
+      </c>
+      <c r="F35" s="263" t="n">
+        <v>19</v>
+      </c>
+      <c r="G35" s="255" t="n">
+        <v>190470</v>
+      </c>
+      <c r="H35" s="255" t="n">
+        <v>-80.42</v>
+      </c>
+      <c r="I35" s="264" t="n">
+        <v>-116883</v>
+      </c>
+      <c r="J35" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료 차감</t>
+        </is>
+      </c>
       <c r="K35" s="65" t="n"/>
       <c r="L35" s="65" t="n"/>
       <c r="M35" s="65" t="n"/>
@@ -18053,16 +18417,42 @@
       <c r="P35" s="65" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="65" t="n"/>
-      <c r="B36" s="65" t="n"/>
-      <c r="C36" s="66" t="n"/>
-      <c r="D36" s="65" t="n"/>
-      <c r="E36" s="65" t="n"/>
-      <c r="F36" s="70" t="n"/>
-      <c r="G36" s="71" t="n"/>
-      <c r="H36" s="65" t="n"/>
-      <c r="I36" s="65" t="n"/>
-      <c r="J36" s="65" t="n"/>
+      <c r="A36" s="257" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" s="254" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C36" s="261" t="inlineStr">
+        <is>
+          <t>수입인수수수료(만기연장 8일분)</t>
+        </is>
+      </c>
+      <c r="D36" s="262" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E36" s="257" t="inlineStr">
+        <is>
+          <t>2026-06-01 ~ 2026-06-08</t>
+        </is>
+      </c>
+      <c r="F36" s="263" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="255" t="n">
+        <v>190470</v>
+      </c>
+      <c r="H36" s="255" t="n">
+        <v>50.79</v>
+      </c>
+      <c r="I36" s="264" t="n">
+        <v>77732</v>
+      </c>
+      <c r="J36" s="257" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
       <c r="K36" s="65" t="n"/>
       <c r="L36" s="65" t="n"/>
       <c r="M36" s="65" t="n"/>
@@ -18071,16 +18461,28 @@
       <c r="P36" s="65" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="65" t="n"/>
-      <c r="B37" s="65" t="n"/>
-      <c r="C37" s="66" t="n"/>
-      <c r="D37" s="65" t="n"/>
-      <c r="E37" s="65" t="n"/>
-      <c r="F37" s="70" t="n"/>
-      <c r="G37" s="71" t="n"/>
-      <c r="H37" s="65" t="n"/>
-      <c r="I37" s="65" t="n"/>
-      <c r="J37" s="65" t="n"/>
+      <c r="A37" s="253" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B37" s="265" t="n"/>
+      <c r="C37" s="266" t="n"/>
+      <c r="D37" s="265" t="n"/>
+      <c r="E37" s="265" t="n"/>
+      <c r="F37" s="267" t="n"/>
+      <c r="G37" s="268" t="n"/>
+      <c r="H37" s="269" t="n">
+        <v>1581.97</v>
+      </c>
+      <c r="I37" s="270" t="n">
+        <v>2343210</v>
+      </c>
+      <c r="J37" s="253" t="inlineStr">
+        <is>
+          <t>이자비용 1,709,345 + 지급수수료 633,865</t>
+        </is>
+      </c>
       <c r="K37" s="65" t="n"/>
       <c r="L37" s="65" t="n"/>
       <c r="M37" s="65" t="n"/>
@@ -18089,7 +18491,11 @@
       <c r="P37" s="65" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="65" t="n"/>
+      <c r="A38" s="271" t="inlineStr">
+        <is>
+          <t>주1: USD 상당액 = 대상금액 x 이율 x 일수/360 (정액 항목인 전신료, 발급수수료는 KRW 정액 징수로 USD 산식 없음)</t>
+        </is>
+      </c>
       <c r="B38" s="65" t="n"/>
       <c r="C38" s="66" t="n"/>
       <c r="D38" s="65" t="n"/>
@@ -18107,7 +18513,11 @@
       <c r="P38" s="65" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="65" t="n"/>
+      <c r="A39" s="271" t="inlineStr">
+        <is>
+          <t>주2: 수수료는 전액 KRW로 기징수됨 (징수일 기준). 회계처리 시 징수일자 전표로 계상</t>
+        </is>
+      </c>
       <c r="B39" s="65" t="n"/>
       <c r="C39" s="66" t="n"/>
       <c r="D39" s="65" t="n"/>
@@ -18125,7 +18535,11 @@
       <c r="P39" s="65" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="65" t="n"/>
+      <c r="A40" s="271" t="inlineStr">
+        <is>
+          <t>주3: 원금 상환(6/9) 전표 수취 후 상환환율, KRW 확정 기입 예정. 회계처리는 외화매입채무 제거 및 외환차손익 인식</t>
+        </is>
+      </c>
       <c r="B40" s="65" t="n"/>
       <c r="C40" s="66" t="n"/>
       <c r="D40" s="65" t="n"/>
@@ -19133,6 +19547,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -32,6 +32,7 @@
     <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="0.00000"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -324,7 +325,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -466,11 +467,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1257,6 +1259,16 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="24" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1505,28 +1517,6 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>RNR 재무팀</author>
-  </authors>
-  <commentList>
-    <comment ref="N17" authorId="0" shapeId="0">
-      <text>
-        <t>은행 원금 상환 전표(원화 출금) 미수취
-전표 수취 후 상환환율과 KRW 확정 기입</t>
-      </text>
-    </comment>
-    <comment ref="C27" authorId="0" shapeId="0">
-      <text>
-        <t>신한은행 원금 상환 전표(원화 출금액) 미수취
-수취 즉시 환율/KRW 기입 예정</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -17733,11 +17723,15 @@
       <c r="M17" s="249" t="n">
         <v>46182</v>
       </c>
-      <c r="N17" s="250" t="n"/>
-      <c r="O17" s="251" t="n"/>
+      <c r="N17" s="247" t="n">
+        <v>1535.1</v>
+      </c>
+      <c r="O17" s="272" t="n">
+        <v>292390497</v>
+      </c>
       <c r="P17" s="245" t="inlineStr">
         <is>
-          <t>6/9 만기 상환 완료, 하단 정산 명세 참조</t>
+          <t>6/9 만기 상환 완료 (전표 2026-06-09, 승인 402875686), 하단 정산 명세 참조</t>
         </is>
       </c>
     </row>
@@ -18065,15 +18059,11 @@
       <c r="B27" s="255" t="n">
         <v>190470</v>
       </c>
-      <c r="C27" s="256" t="inlineStr">
-        <is>
-          <t>전표 확인 필요</t>
-        </is>
-      </c>
-      <c r="D27" s="256" t="inlineStr">
-        <is>
-          <t>전표 확인 필요</t>
-        </is>
+      <c r="C27" s="255" t="n">
+        <v>1535.1</v>
+      </c>
+      <c r="D27" s="264" t="n">
+        <v>292390497</v>
       </c>
       <c r="E27" s="257" t="inlineStr">
         <is>
@@ -18082,7 +18072,7 @@
       </c>
       <c r="F27" s="258" t="inlineStr">
         <is>
-          <t>차변 외화매입채무 190,470 USD, 대변 보통예금(상환환율), 차액 외환차손익</t>
+          <t>차변 외화매입채무(USANCE) 190,470 USD 제거 + 외환차손익, 대변 보통예금 292,390,497</t>
         </is>
       </c>
       <c r="G27" s="71" t="n"/>
@@ -18461,26 +18451,36 @@
       <c r="P36" s="65" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="253" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B37" s="265" t="n"/>
-      <c r="C37" s="266" t="n"/>
-      <c r="D37" s="265" t="n"/>
-      <c r="E37" s="265" t="n"/>
-      <c r="F37" s="267" t="n"/>
-      <c r="G37" s="268" t="n"/>
-      <c r="H37" s="269" t="n">
-        <v>1581.97</v>
-      </c>
-      <c r="I37" s="270" t="n">
-        <v>2343210</v>
-      </c>
-      <c r="J37" s="253" t="inlineStr">
-        <is>
-          <t>이자비용 1,709,345 + 지급수수료 633,865</t>
+      <c r="A37" s="257" t="n">
+        <v>8</v>
+      </c>
+      <c r="B37" s="254" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C37" s="261" t="inlineStr">
+        <is>
+          <t>지체료 (인수수수료 연체이자 7%, 8일)</t>
+        </is>
+      </c>
+      <c r="D37" s="262" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="257" t="inlineStr">
+        <is>
+          <t>2026-06-01 ~ 2026-06-08</t>
+        </is>
+      </c>
+      <c r="F37" s="263" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" s="255" t="n"/>
+      <c r="H37" s="255" t="n"/>
+      <c r="I37" s="264" t="n">
+        <v>119</v>
+      </c>
+      <c r="J37" s="257" t="inlineStr">
+        <is>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="K37" s="65" t="n"/>
@@ -18491,20 +18491,42 @@
       <c r="P37" s="65" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="271" t="inlineStr">
-        <is>
-          <t>주1: USD 상당액 = 대상금액 x 이율 x 일수/360 (정액 항목인 전신료, 발급수수료는 KRW 정액 징수로 USD 산식 없음)</t>
-        </is>
-      </c>
-      <c r="B38" s="65" t="n"/>
-      <c r="C38" s="66" t="n"/>
-      <c r="D38" s="65" t="n"/>
-      <c r="E38" s="65" t="n"/>
-      <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="H38" s="65" t="n"/>
-      <c r="I38" s="65" t="n"/>
-      <c r="J38" s="65" t="n"/>
+      <c r="A38" s="257" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" s="254" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C38" s="261" t="inlineStr">
+        <is>
+          <t>해외수수료 (해외은행 인수금융 이자 5.57788%, 180일)</t>
+        </is>
+      </c>
+      <c r="D38" s="273" t="n">
+        <v>5.57788</v>
+      </c>
+      <c r="E38" s="257" t="inlineStr">
+        <is>
+          <t>2025-12-11 ~ 2026-06-09</t>
+        </is>
+      </c>
+      <c r="F38" s="263" t="n">
+        <v>180</v>
+      </c>
+      <c r="G38" s="255" t="n">
+        <v>190400</v>
+      </c>
+      <c r="H38" s="255" t="n">
+        <v>5310.14</v>
+      </c>
+      <c r="I38" s="264" t="n">
+        <v>8154250</v>
+      </c>
+      <c r="J38" s="257" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
       <c r="K38" s="65" t="n"/>
       <c r="L38" s="65" t="n"/>
       <c r="M38" s="65" t="n"/>
@@ -18513,20 +18535,28 @@
       <c r="P38" s="65" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="271" t="inlineStr">
-        <is>
-          <t>주2: 수수료는 전액 KRW로 기징수됨 (징수일 기준). 회계처리 시 징수일자 전표로 계상</t>
-        </is>
-      </c>
-      <c r="B39" s="65" t="n"/>
-      <c r="C39" s="66" t="n"/>
-      <c r="D39" s="65" t="n"/>
-      <c r="E39" s="65" t="n"/>
-      <c r="F39" s="65" t="n"/>
-      <c r="G39" s="71" t="n"/>
-      <c r="H39" s="65" t="n"/>
-      <c r="I39" s="65" t="n"/>
-      <c r="J39" s="65" t="n"/>
+      <c r="A39" s="253" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B39" s="265" t="n"/>
+      <c r="C39" s="266" t="n"/>
+      <c r="D39" s="265" t="n"/>
+      <c r="E39" s="265" t="n"/>
+      <c r="F39" s="265" t="n"/>
+      <c r="G39" s="268" t="n"/>
+      <c r="H39" s="269" t="n">
+        <v>6892.11</v>
+      </c>
+      <c r="I39" s="270" t="n">
+        <v>10497579</v>
+      </c>
+      <c r="J39" s="253" t="inlineStr">
+        <is>
+          <t>이자비용 9,863,714 + 지급수수료 633,865</t>
+        </is>
+      </c>
       <c r="K39" s="65" t="n"/>
       <c r="L39" s="65" t="n"/>
       <c r="M39" s="65" t="n"/>
@@ -18535,9 +18565,9 @@
       <c r="P39" s="65" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="271" t="inlineStr">
-        <is>
-          <t>주3: 원금 상환(6/9) 전표 수취 후 상환환율, KRW 확정 기입 예정. 회계처리는 외화매입채무 제거 및 외환차손익 인식</t>
+      <c r="A40" s="274" t="inlineStr">
+        <is>
+          <t>주1: USD 상당액 = 대상금액 x 이율 x 일수/360 (전신료, 발급수수료, 지체료는 KRW 정액 또는 KRW 기준 산출)</t>
         </is>
       </c>
       <c r="B40" s="65" t="n"/>
@@ -18557,7 +18587,11 @@
       <c r="P40" s="65" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="65" t="n"/>
+      <c r="A41" s="274" t="inlineStr">
+        <is>
+          <t>주2: No.1~6 수수료는 징수일에 KRW 기징수, No.7~9는 상환일(6/9) 출금. 회계처리는 각 징수일자 전표로 계상</t>
+        </is>
+      </c>
       <c r="B41" s="65" t="n"/>
       <c r="C41" s="66" t="n"/>
       <c r="D41" s="65" t="n"/>
@@ -18574,8 +18608,20 @@
       <c r="O41" s="65" t="n"/>
       <c r="P41" s="65" t="n"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="275" t="inlineStr">
+        <is>
+          <t>주3: 원금 상환 확정 (외국환 거래계산서 2026-06-09, 승인번호 402875686, REF M88JX2511NU00018): 원금 USD 190,470.00 x 1,535.10 = 292,390,497원</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="275" t="inlineStr">
+        <is>
+          <t>주4: 6/9 실제 출금 합계 300,622,598원 = 원금분 292,468,348 (원금 + 인수수수료 77,732 + 지체료 119) + 해외수수료분 8,154,250</t>
+        </is>
+      </c>
+    </row>
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1"/>
@@ -19547,7 +19593,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" tabRatio="500" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PO별 개당 수입원가" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="라이센스_워런티" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="합배송_비용안분" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="외화송금내역" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Usance_LC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="환율" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PO별 개당 수입원가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라이센스_워런티" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="합배송_비용안분" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화송금내역" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usance_LC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$40</definedName>
     <definedName name="RemitTable2">'외화송금내역'!$A$43:$L$91</definedName>
-    <definedName name="FxRateTable">'환율'!$A$7:$D$42</definedName>
+    <definedName name="FxRateTable">환율!$A$7:$D$43</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="276">
+  <cellXfs count="283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1269,6 +1269,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="24" fillId="18" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="18" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="18" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="18" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1767,7 +1788,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-06-10  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-06-16  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="148" t="n"/>
@@ -2055,24 +2076,20 @@
       <c r="H5" s="7" t="n">
         <v>6800</v>
       </c>
-      <c r="I5" s="33">
-        <f>IFERROR(VLOOKUP(B5,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I5" s="33" t="n">
+        <v>1475.2</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="9">
-        <f>IFERROR(ROUND(H5*I5,0),0)</f>
-        <v/>
-      </c>
-      <c r="L5" s="9">
-        <f>IFERROR(VLOOKUP(B5,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M5" s="9">
-        <f>IFERROR(VLOOKUP(B5,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>10031360</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>10031360</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>8000</v>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
@@ -2184,24 +2201,20 @@
       <c r="H6" s="7" t="n">
         <v>139083</v>
       </c>
-      <c r="I6" s="33">
-        <f>IFERROR(VLOOKUP(B6,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I6" s="33" t="n">
+        <v>1479.7</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>212471386</v>
-      </c>
-      <c r="K6" s="9">
-        <f>IFERROR(ROUND(H6*I6,0),0)</f>
-        <v/>
-      </c>
-      <c r="L6" s="9">
-        <f>IFERROR(VLOOKUP(B6,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M6" s="9">
-        <f>IFERROR(VLOOKUP(B6,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>205801115</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>205801115</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>12110</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>7751</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -2315,24 +2328,20 @@
       <c r="H7" s="7" t="n">
         <v>9060</v>
       </c>
-      <c r="I7" s="33">
-        <f>IFERROR(VLOOKUP(B7,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I7" s="33" t="n">
+        <v>1439.1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>18264679</v>
-      </c>
-      <c r="K7" s="9">
-        <f>IFERROR(ROUND(H7*I7,0),0)</f>
-        <v/>
-      </c>
-      <c r="L7" s="9">
-        <f>IFERROR(VLOOKUP(B7,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M7" s="9">
-        <f>IFERROR(VLOOKUP(B7,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>13038246</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>13038246</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>6537</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>5229</v>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
@@ -2446,24 +2455,20 @@
       <c r="H8" s="7" t="n">
         <v>4474</v>
       </c>
-      <c r="I8" s="33">
-        <f>IFERROR(VLOOKUP(B8,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I8" s="33" t="n">
+        <v>1479.7</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>212471386</v>
-      </c>
-      <c r="K8" s="9">
-        <f>IFERROR(ROUND(H8*I8,0),0)</f>
-        <v/>
-      </c>
-      <c r="L8" s="9">
-        <f>IFERROR(VLOOKUP(B8,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="9">
-        <f>IFERROR(VLOOKUP(B8,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>6620178</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>6620178</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>390</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>249</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -2692,24 +2697,20 @@
       <c r="H10" s="7" t="n">
         <v>252</v>
       </c>
-      <c r="I10" s="33">
-        <f>IFERROR(VLOOKUP(B10,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I10" s="33" t="n">
+        <v>1479</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>412788</v>
-      </c>
-      <c r="K10" s="9">
-        <f>IFERROR(ROUND(H10*I10,0),0)</f>
-        <v/>
-      </c>
-      <c r="L10" s="9">
-        <f>IFERROR(VLOOKUP(B10,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M10" s="9">
-        <f>IFERROR(VLOOKUP(B10,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>372708</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>372708</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>8000</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -2823,24 +2824,20 @@
       <c r="H11" s="7" t="n">
         <v>2710</v>
       </c>
-      <c r="I11" s="33">
-        <f>IFERROR(VLOOKUP(B11,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I11" s="33" t="n">
+        <v>1475.7</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>5505104</v>
-      </c>
-      <c r="K11" s="9">
-        <f>IFERROR(ROUND(H11*I11,0),0)</f>
-        <v/>
-      </c>
-      <c r="L11" s="9">
-        <f>IFERROR(VLOOKUP(B11,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M11" s="9">
-        <f>IFERROR(VLOOKUP(B11,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>3999147</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>3999147</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>5493</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>5859</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
@@ -2954,24 +2951,20 @@
       <c r="H12" s="7" t="n">
         <v>5056.8</v>
       </c>
-      <c r="I12" s="33">
-        <f>IFERROR(VLOOKUP(B12,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I12" s="33" t="n">
+        <v>1445.5</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>7356514</v>
-      </c>
-      <c r="K12" s="9">
-        <f>IFERROR(ROUND(H12*I12,0),0)</f>
-        <v/>
-      </c>
-      <c r="L12" s="9">
-        <f>IFERROR(VLOOKUP(B12,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M12" s="9">
-        <f>IFERROR(VLOOKUP(B12,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>7309604</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>7309604</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>8000</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -3085,24 +3078,20 @@
       <c r="H13" s="7" t="n">
         <v>137850</v>
       </c>
-      <c r="I13" s="33">
-        <f>IFERROR(VLOOKUP(B13,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I13" s="33" t="n">
+        <v>1477.6</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>203737212</v>
-      </c>
-      <c r="K13" s="9">
-        <f>IFERROR(ROUND(H13*I13,0),0)</f>
-        <v/>
-      </c>
-      <c r="L13" s="9">
-        <f>IFERROR(VLOOKUP(B13,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M13" s="9">
-        <f>IFERROR(VLOOKUP(B13,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>203687160</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>203687160</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>12500</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>8000</v>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
@@ -3216,24 +3205,20 @@
       <c r="H14" s="7" t="n">
         <v>20174</v>
       </c>
-      <c r="I14" s="33">
-        <f>IFERROR(VLOOKUP(B14,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I14" s="33" t="n">
+        <v>1454.7</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>36117425</v>
-      </c>
-      <c r="K14" s="9">
-        <f>IFERROR(ROUND(H14*I14,0),0)</f>
-        <v/>
-      </c>
-      <c r="L14" s="9">
-        <f>IFERROR(VLOOKUP(B14,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M14" s="9">
-        <f>IFERROR(VLOOKUP(B14,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>29347118</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>29347118</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>10171</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>6509</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -3347,24 +3332,20 @@
       <c r="H15" s="7" t="n">
         <v>4620</v>
       </c>
-      <c r="I15" s="33">
-        <f>IFERROR(VLOOKUP(B15,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I15" s="33" t="n">
+        <v>1454.7</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>36117425</v>
-      </c>
-      <c r="K15" s="9">
-        <f>IFERROR(ROUND(H15*I15,0),0)</f>
-        <v/>
-      </c>
-      <c r="L15" s="9">
-        <f>IFERROR(VLOOKUP(B15,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M15" s="9">
-        <f>IFERROR(VLOOKUP(B15,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>6720714</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>6720714</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>2329</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>1491</v>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
@@ -3478,24 +3459,20 @@
       <c r="H16" s="7" t="n">
         <v>9626.35</v>
       </c>
-      <c r="I16" s="33">
-        <f>IFERROR(VLOOKUP(B16,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I16" s="33" t="n">
+        <v>1476</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>14256012</v>
-      </c>
-      <c r="K16" s="9">
-        <f>IFERROR(ROUND(H16*I16,0),0)</f>
-        <v/>
-      </c>
-      <c r="L16" s="9">
-        <f>IFERROR(VLOOKUP(B16,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M16" s="9">
-        <f>IFERROR(VLOOKUP(B16,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>14208493</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>14208493</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>8000</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -3609,24 +3586,20 @@
       <c r="H17" s="7" t="n">
         <v>4936</v>
       </c>
-      <c r="I17" s="33">
-        <f>IFERROR(VLOOKUP(B17,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I17" s="33" t="n">
+        <v>1480</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>22306800</v>
-      </c>
-      <c r="K17" s="9">
-        <f>IFERROR(ROUND(H17*I17,0),0)</f>
-        <v/>
-      </c>
-      <c r="L17" s="9">
-        <f>IFERROR(VLOOKUP(B17,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M17" s="9">
-        <f>IFERROR(VLOOKUP(B17,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>7305280</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>7305280</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>3282</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>2626</v>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
@@ -3740,24 +3713,20 @@
       <c r="H18" s="7" t="n">
         <v>2745</v>
       </c>
-      <c r="I18" s="33">
-        <f>IFERROR(VLOOKUP(B18,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I18" s="33" t="n">
+        <v>1451.7</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>25506948</v>
-      </c>
-      <c r="K18" s="9">
-        <f>IFERROR(ROUND(H18*I18,0),0)</f>
-        <v/>
-      </c>
-      <c r="L18" s="9">
-        <f>IFERROR(VLOOKUP(B18,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M18" s="9">
-        <f>IFERROR(VLOOKUP(B18,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>3984917</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>3984917</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>1565</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>1252</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -3871,24 +3840,20 @@
       <c r="H19" s="7" t="n">
         <v>1700</v>
       </c>
-      <c r="I19" s="33">
-        <f>IFERROR(VLOOKUP(B19,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I19" s="33" t="n">
+        <v>1506.4</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>9919642</v>
-      </c>
-      <c r="K19" s="9">
-        <f>IFERROR(ROUND(H19*I19,0),0)</f>
-        <v/>
-      </c>
-      <c r="L19" s="9">
-        <f>IFERROR(VLOOKUP(B19,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="9">
-        <f>IFERROR(VLOOKUP(B19,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>2560880</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>2560880</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>2594</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>2075</v>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
@@ -4131,10 +4096,10 @@
         <v>1482.8</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>424990980</v>
+        <v>424940824</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>424990980</v>
+        <v>424940824</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>12038</v>
@@ -4252,24 +4217,20 @@
       <c r="H22" s="7" t="n">
         <v>9740</v>
       </c>
-      <c r="I22" s="33">
-        <f>IFERROR(VLOOKUP(B22,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I22" s="33" t="n">
+        <v>1505.7</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>51777431</v>
-      </c>
-      <c r="K22" s="9">
-        <f>IFERROR(ROUND(H22*I22,0),0)</f>
-        <v/>
-      </c>
-      <c r="L22" s="9">
-        <f>IFERROR(VLOOKUP(B22,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="9">
-        <f>IFERROR(VLOOKUP(B22,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>14665518</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>14665518</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>3544</v>
+      </c>
+      <c r="M22" s="9" t="n">
+        <v>2268</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -4498,24 +4459,20 @@
       <c r="H24" s="7" t="n">
         <v>36190</v>
       </c>
-      <c r="I24" s="33">
-        <f>IFERROR(VLOOKUP(B24,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I24" s="33" t="n">
+        <v>1481.9</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="9">
-        <f>IFERROR(ROUND(H24*I24,0),0)</f>
-        <v/>
-      </c>
-      <c r="L24" s="9">
-        <f>IFERROR(VLOOKUP(B24,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M24" s="9">
-        <f>IFERROR(VLOOKUP(B24,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>53629961</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>53629961</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>7847</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>5022</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -4629,24 +4586,20 @@
       <c r="H25" s="7" t="n">
         <v>180</v>
       </c>
-      <c r="I25" s="33">
-        <f>IFERROR(VLOOKUP(B25,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I25" s="33" t="n">
+        <v>1481.9</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="9">
-        <f>IFERROR(ROUND(H25*I25,0),0)</f>
-        <v/>
-      </c>
-      <c r="L25" s="9">
-        <f>IFERROR(VLOOKUP(B25,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M25" s="9">
-        <f>IFERROR(VLOOKUP(B25,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>266742</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>266742</v>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
@@ -4760,24 +4713,20 @@
       <c r="H26" s="7" t="n">
         <v>21280</v>
       </c>
-      <c r="I26" s="33">
-        <f>IFERROR(VLOOKUP(B26,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I26" s="33" t="n">
+        <v>1481.9</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="9">
-        <f>IFERROR(ROUND(H26*I26,0),0)</f>
-        <v/>
-      </c>
-      <c r="L26" s="9">
-        <f>IFERROR(VLOOKUP(B26,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M26" s="9">
-        <f>IFERROR(VLOOKUP(B26,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>31534832</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>31534832</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>4614</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>2953</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -4891,24 +4840,20 @@
       <c r="H27" s="7" t="n">
         <v>2058</v>
       </c>
-      <c r="I27" s="33">
-        <f>IFERROR(VLOOKUP(B27,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I27" s="33" t="n">
+        <v>1474.9</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="9">
-        <f>IFERROR(ROUND(H27*I27,0),0)</f>
-        <v/>
-      </c>
-      <c r="L27" s="9">
-        <f>IFERROR(VLOOKUP(B27,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M27" s="9">
-        <f>IFERROR(VLOOKUP(B27,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>3035344</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>3035344</v>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>768</v>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
@@ -5022,24 +4967,20 @@
       <c r="H28" s="7" t="n">
         <v>1977</v>
       </c>
-      <c r="I28" s="33">
-        <f>IFERROR(VLOOKUP(B28,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I28" s="33" t="n">
+        <v>1474.9</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="9">
-        <f>IFERROR(ROUND(H28*I28,0),0)</f>
-        <v/>
-      </c>
-      <c r="L28" s="9">
-        <f>IFERROR(VLOOKUP(B28,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M28" s="9">
-        <f>IFERROR(VLOOKUP(B28,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>2915877</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>2915877</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>1153</v>
+      </c>
+      <c r="M28" s="9" t="n">
+        <v>738</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -5153,22 +5094,20 @@
       <c r="H29" s="7" t="n">
         <v>4290</v>
       </c>
-      <c r="I29" s="33">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9">
-        <f>IFERROR(ROUND(H29*I29,0),0)</f>
-        <v/>
-      </c>
-      <c r="L29" s="9">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M29" s="9">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+      <c r="I29" s="33" t="n">
+        <v>1510.6</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>6480474</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>6480474</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>7500</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>8000</v>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
@@ -5270,24 +5209,20 @@
       <c r="H30" s="80" t="n">
         <v>78209</v>
       </c>
-      <c r="I30" s="180">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I30" s="180" t="n">
+        <v>1502.7</v>
       </c>
       <c r="J30" s="82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="82">
-        <f>IFERROR(ROUND(H30*I30,0),0)</f>
-        <v/>
-      </c>
-      <c r="L30" s="82">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M30" s="82">
-        <f>IFERROR(VLOOKUP(B30,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>117524664</v>
+      </c>
+      <c r="K30" s="82" t="n">
+        <v>117524664</v>
+      </c>
+      <c r="L30" s="82" t="n">
+        <v>9619</v>
+      </c>
+      <c r="M30" s="82" t="n">
+        <v>6156</v>
       </c>
       <c r="N30" s="78" t="inlineStr">
         <is>
@@ -5389,24 +5324,20 @@
       <c r="H31" s="80" t="n">
         <v>8140</v>
       </c>
-      <c r="I31" s="180">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+      <c r="I31" s="180" t="n">
+        <v>1502.7</v>
       </c>
       <c r="J31" s="82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="82">
-        <f>IFERROR(ROUND(H31*I31,0),0)</f>
-        <v/>
-      </c>
-      <c r="L31" s="82">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M31" s="82">
-        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>12231978</v>
+      </c>
+      <c r="K31" s="82" t="n">
+        <v>12231978</v>
+      </c>
+      <c r="L31" s="82" t="n">
+        <v>1001</v>
+      </c>
+      <c r="M31" s="82" t="n">
+        <v>641</v>
       </c>
       <c r="N31" s="78" t="inlineStr">
         <is>
@@ -5512,10 +5443,10 @@
         <v>1741.08</v>
       </c>
       <c r="J32" s="82" t="n">
-        <v>7702082</v>
+        <v>7640555</v>
       </c>
       <c r="K32" s="82" t="n">
-        <v>7702082</v>
+        <v>7640555</v>
       </c>
       <c r="L32" s="82" t="n">
         <v>10000</v>
@@ -5845,24 +5776,20 @@
       <c r="H35" s="126" t="n">
         <v>98800</v>
       </c>
-      <c r="I35" s="126">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I35" s="126" t="n">
+        <v>1502.8</v>
       </c>
       <c r="J35" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="128">
-        <f>IFERROR(ROUND(H35*I35,0),0)</f>
-        <v/>
-      </c>
-      <c r="L35" s="128">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M35" s="128">
-        <f>IFERROR(VLOOKUP(B35,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>148476640</v>
+      </c>
+      <c r="K35" s="128" t="n">
+        <v>148476640</v>
+      </c>
+      <c r="L35" s="128" t="n">
+        <v>12457</v>
+      </c>
+      <c r="M35" s="128" t="n">
+        <v>7973</v>
       </c>
       <c r="N35" s="129" t="n"/>
       <c r="O35" s="182" t="n">
@@ -5960,24 +5887,20 @@
       <c r="H36" s="126" t="n">
         <v>90</v>
       </c>
-      <c r="I36" s="126">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I36" s="126" t="n">
+        <v>1502.8</v>
       </c>
       <c r="J36" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="128">
-        <f>IFERROR(ROUND(H36*I36,0),0)</f>
-        <v/>
-      </c>
-      <c r="L36" s="128">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M36" s="128">
-        <f>IFERROR(VLOOKUP(B36,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>135252</v>
+      </c>
+      <c r="K36" s="128" t="n">
+        <v>135252</v>
+      </c>
+      <c r="L36" s="128" t="n">
+        <v>11</v>
+      </c>
+      <c r="M36" s="128" t="n">
+        <v>7</v>
       </c>
       <c r="N36" s="129" t="n"/>
       <c r="O36" s="129" t="n"/>
@@ -6061,24 +5984,20 @@
       <c r="H37" s="211" t="n">
         <v>69160</v>
       </c>
-      <c r="I37" s="212">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I37" s="212" t="n">
+        <v>1525.3</v>
       </c>
       <c r="J37" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="213">
-        <f>IFERROR(ROUND(H37*I37,0),0)</f>
-        <v/>
-      </c>
-      <c r="L37" s="213">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M37" s="213">
-        <f>IFERROR(VLOOKUP(B37,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>105489748</v>
+      </c>
+      <c r="K37" s="213" t="n">
+        <v>105489748</v>
+      </c>
+      <c r="L37" s="213" t="n">
+        <v>7261</v>
+      </c>
+      <c r="M37" s="213" t="n">
+        <v>4647</v>
       </c>
       <c r="N37" s="207" t="inlineStr">
         <is>
@@ -6180,24 +6099,20 @@
       <c r="H38" s="211" t="n">
         <v>49400</v>
       </c>
-      <c r="I38" s="212">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I38" s="212" t="n">
+        <v>1525.3</v>
       </c>
       <c r="J38" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="213">
-        <f>IFERROR(ROUND(H38*I38,0),0)</f>
-        <v/>
-      </c>
-      <c r="L38" s="213">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M38" s="213">
-        <f>IFERROR(VLOOKUP(B38,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>75349820</v>
+      </c>
+      <c r="K38" s="213" t="n">
+        <v>75349820</v>
+      </c>
+      <c r="L38" s="213" t="n">
+        <v>5186</v>
+      </c>
+      <c r="M38" s="213" t="n">
+        <v>3319</v>
       </c>
       <c r="N38" s="207" t="inlineStr">
         <is>
@@ -6420,24 +6335,20 @@
       <c r="H40" s="24" t="n">
         <v>5673</v>
       </c>
-      <c r="I40" s="185">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I40" s="185" t="n">
+        <v>1441.6</v>
       </c>
       <c r="J40" s="26" t="n">
-        <v>205028994</v>
-      </c>
-      <c r="K40" s="26">
-        <f>IFERROR(ROUND(H40*I40,0),0)</f>
-        <v/>
-      </c>
-      <c r="L40" s="26">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M40" s="26">
-        <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>8178197</v>
+      </c>
+      <c r="K40" s="26" t="n">
+        <v>8178197</v>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>499</v>
+      </c>
+      <c r="M40" s="26" t="n">
+        <v>319</v>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
@@ -6551,24 +6462,20 @@
       <c r="H41" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="I41" s="185">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I41" s="185" t="n">
+        <v>1439.1</v>
       </c>
       <c r="J41" s="26" t="n">
-        <v>18264679</v>
-      </c>
-      <c r="K41" s="26">
-        <f>IFERROR(ROUND(H41*I41,0),0)</f>
-        <v/>
-      </c>
-      <c r="L41" s="26">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M41" s="26">
-        <f>IFERROR(VLOOKUP(B41,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>503685</v>
+      </c>
+      <c r="K41" s="26" t="n">
+        <v>503685</v>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>253</v>
+      </c>
+      <c r="M41" s="26" t="n">
+        <v>202</v>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
@@ -6682,24 +6589,20 @@
       <c r="H42" s="24" t="n">
         <v>26358</v>
       </c>
-      <c r="I42" s="185">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I42" s="185" t="n">
+        <v>1460.7</v>
       </c>
       <c r="J42" s="26" t="n">
-        <v>38550844</v>
-      </c>
-      <c r="K42" s="26">
-        <f>IFERROR(ROUND(H42*I42,0),0)</f>
-        <v/>
-      </c>
-      <c r="L42" s="26">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M42" s="26">
-        <f>IFERROR(VLOOKUP(B42,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>38501131</v>
+      </c>
+      <c r="K42" s="26" t="n">
+        <v>38501131</v>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>12500</v>
+      </c>
+      <c r="M42" s="26" t="n">
+        <v>8000</v>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
@@ -6813,24 +6716,20 @@
       <c r="H43" s="24" t="n">
         <v>450</v>
       </c>
-      <c r="I43" s="185">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I43" s="185" t="n">
+        <v>1475.7</v>
       </c>
       <c r="J43" s="26" t="n">
-        <v>5505104</v>
-      </c>
-      <c r="K43" s="26">
-        <f>IFERROR(ROUND(H43*I43,0),0)</f>
-        <v/>
-      </c>
-      <c r="L43" s="26">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M43" s="26">
-        <f>IFERROR(VLOOKUP(B43,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>664065</v>
+      </c>
+      <c r="K43" s="26" t="n">
+        <v>664065</v>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>912</v>
+      </c>
+      <c r="M43" s="26" t="n">
+        <v>973</v>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
@@ -6944,24 +6843,20 @@
       <c r="H44" s="24" t="n">
         <v>540</v>
       </c>
-      <c r="I44" s="185">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I44" s="185" t="n">
+        <v>1475.7</v>
       </c>
       <c r="J44" s="26" t="n">
-        <v>5505104</v>
-      </c>
-      <c r="K44" s="26">
-        <f>IFERROR(ROUND(H44*I44,0),0)</f>
-        <v/>
-      </c>
-      <c r="L44" s="26">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M44" s="26">
-        <f>IFERROR(VLOOKUP(B44,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>796878</v>
+      </c>
+      <c r="K44" s="26" t="n">
+        <v>796878</v>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>1095</v>
+      </c>
+      <c r="M44" s="26" t="n">
+        <v>1168</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
@@ -7075,24 +6970,20 @@
       <c r="H45" s="24" t="n">
         <v>136516</v>
       </c>
-      <c r="I45" s="185">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I45" s="185" t="n">
+        <v>1441.6</v>
       </c>
       <c r="J45" s="26" t="n">
-        <v>205028994</v>
-      </c>
-      <c r="K45" s="26">
-        <f>IFERROR(ROUND(H45*I45,0),0)</f>
-        <v/>
-      </c>
-      <c r="L45" s="26">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M45" s="26">
-        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>196801466</v>
+      </c>
+      <c r="K45" s="26" t="n">
+        <v>196801466</v>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>12001</v>
+      </c>
+      <c r="M45" s="26" t="n">
+        <v>7681</v>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
@@ -7339,24 +7230,20 @@
       <c r="H47" s="24" t="n">
         <v>14793</v>
       </c>
-      <c r="I47" s="185">
-        <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I47" s="185" t="n">
+        <v>1451.7</v>
       </c>
       <c r="J47" s="26" t="n">
-        <v>25506948</v>
-      </c>
-      <c r="K47" s="26">
-        <f>IFERROR(ROUND(H47*I47,0),0)</f>
-        <v/>
-      </c>
-      <c r="L47" s="26">
-        <f>IFERROR(VLOOKUP(B47,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M47" s="26">
-        <f>IFERROR(VLOOKUP(B47,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>21474998</v>
+      </c>
+      <c r="K47" s="26" t="n">
+        <v>21474998</v>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>8435</v>
+      </c>
+      <c r="M47" s="26" t="n">
+        <v>6748</v>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
@@ -7603,24 +7490,20 @@
       <c r="H49" s="24" t="n">
         <v>1440</v>
       </c>
-      <c r="I49" s="185">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I49" s="185" t="n">
+        <v>1453.6</v>
       </c>
       <c r="J49" s="26" t="n">
-        <v>16908206</v>
-      </c>
-      <c r="K49" s="26">
-        <f>IFERROR(ROUND(H49*I49,0),0)</f>
-        <v/>
-      </c>
-      <c r="L49" s="26">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M49" s="26">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>2093184</v>
+      </c>
+      <c r="K49" s="26" t="n">
+        <v>2093184</v>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>1241</v>
+      </c>
+      <c r="M49" s="26" t="n">
+        <v>993</v>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
@@ -7734,24 +7617,20 @@
       <c r="H50" s="24" t="n">
         <v>4489</v>
       </c>
-      <c r="I50" s="185">
-        <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I50" s="185" t="n">
+        <v>1453.6</v>
       </c>
       <c r="J50" s="26" t="n">
-        <v>16908206</v>
-      </c>
-      <c r="K50" s="26">
-        <f>IFERROR(ROUND(H50*I50,0),0)</f>
-        <v/>
-      </c>
-      <c r="L50" s="26">
-        <f>IFERROR(VLOOKUP(B50,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M50" s="26">
-        <f>IFERROR(VLOOKUP(B50,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>6525210</v>
+      </c>
+      <c r="K50" s="26" t="n">
+        <v>6525210</v>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>3870</v>
+      </c>
+      <c r="M50" s="26" t="n">
+        <v>3096</v>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
@@ -7865,24 +7744,20 @@
       <c r="H51" s="24" t="n">
         <v>5670.57</v>
       </c>
-      <c r="I51" s="185">
-        <f>IFERROR(VLOOKUP(B51,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I51" s="185" t="n">
+        <v>1453.6</v>
       </c>
       <c r="J51" s="26" t="n">
-        <v>16908206</v>
-      </c>
-      <c r="K51" s="26">
-        <f>IFERROR(ROUND(H51*I51,0),0)</f>
-        <v/>
-      </c>
-      <c r="L51" s="26">
-        <f>IFERROR(VLOOKUP(B51,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="26">
-        <f>IFERROR(VLOOKUP(B51,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>8242741</v>
+      </c>
+      <c r="K51" s="26" t="n">
+        <v>8242741</v>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>4889</v>
+      </c>
+      <c r="M51" s="26" t="n">
+        <v>3911</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
@@ -7996,24 +7871,20 @@
       <c r="H52" s="24" t="n">
         <v>24614</v>
       </c>
-      <c r="I52" s="185">
-        <f>IFERROR(VLOOKUP(B52,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I52" s="185" t="n">
+        <v>1505.7</v>
       </c>
       <c r="J52" s="26" t="n">
-        <v>51777431</v>
-      </c>
-      <c r="K52" s="26">
-        <f>IFERROR(ROUND(H52*I52,0),0)</f>
-        <v/>
-      </c>
-      <c r="L52" s="26">
-        <f>IFERROR(VLOOKUP(B52,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M52" s="26">
-        <f>IFERROR(VLOOKUP(B52,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>37061300</v>
+      </c>
+      <c r="K52" s="26" t="n">
+        <v>37061300</v>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>8956</v>
+      </c>
+      <c r="M52" s="26" t="n">
+        <v>5732</v>
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
@@ -8127,24 +7998,20 @@
       <c r="H53" s="24" t="n">
         <v>3993.05</v>
       </c>
-      <c r="I53" s="185">
-        <f>IFERROR(VLOOKUP(B53,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I53" s="185" t="n">
+        <v>1506.4</v>
       </c>
       <c r="J53" s="26" t="n">
-        <v>9919642</v>
-      </c>
-      <c r="K53" s="26">
-        <f>IFERROR(ROUND(H53*I53,0),0)</f>
-        <v/>
-      </c>
-      <c r="L53" s="26">
-        <f>IFERROR(VLOOKUP(B53,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M53" s="26">
-        <f>IFERROR(VLOOKUP(B53,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>6015131</v>
+      </c>
+      <c r="K53" s="26" t="n">
+        <v>6015131</v>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>6093</v>
+      </c>
+      <c r="M53" s="26" t="n">
+        <v>4875</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
@@ -8258,24 +8125,20 @@
       <c r="H54" s="24" t="n">
         <v>360</v>
       </c>
-      <c r="I54" s="185">
-        <f>IFERROR(VLOOKUP(B54,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I54" s="185" t="n">
+        <v>1506.4</v>
       </c>
       <c r="J54" s="26" t="n">
-        <v>9919642</v>
-      </c>
-      <c r="K54" s="26">
-        <f>IFERROR(ROUND(H54*I54,0),0)</f>
-        <v/>
-      </c>
-      <c r="L54" s="26">
-        <f>IFERROR(VLOOKUP(B54,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M54" s="26">
-        <f>IFERROR(VLOOKUP(B54,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>542304</v>
+      </c>
+      <c r="K54" s="26" t="n">
+        <v>542304</v>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>549</v>
+      </c>
+      <c r="M54" s="26" t="n">
+        <v>439</v>
       </c>
       <c r="N54" s="20" t="inlineStr">
         <is>
@@ -8389,24 +8252,20 @@
       <c r="H55" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="I55" s="185">
-        <f>IFERROR(VLOOKUP(B55,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I55" s="185" t="n">
+        <v>1506.4</v>
       </c>
       <c r="J55" s="26" t="n">
-        <v>9919642</v>
-      </c>
-      <c r="K55" s="26">
-        <f>IFERROR(ROUND(H55*I55,0),0)</f>
-        <v/>
-      </c>
-      <c r="L55" s="26">
-        <f>IFERROR(VLOOKUP(B55,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M55" s="26">
-        <f>IFERROR(VLOOKUP(B55,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>753200</v>
+      </c>
+      <c r="K55" s="26" t="n">
+        <v>753200</v>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>763</v>
+      </c>
+      <c r="M55" s="26" t="n">
+        <v>610</v>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
@@ -8520,24 +8379,20 @@
       <c r="H56" s="24" t="n">
         <v>17404</v>
       </c>
-      <c r="I56" s="185">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I56" s="185" t="n">
+        <v>1474.9</v>
       </c>
       <c r="J56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="26">
-        <f>IFERROR(ROUND(H56*I56,0),0)</f>
-        <v/>
-      </c>
-      <c r="L56" s="26">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M56" s="26">
-        <f>IFERROR(VLOOKUP(B56,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>25669160</v>
+      </c>
+      <c r="K56" s="26" t="n">
+        <v>25669160</v>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>10147</v>
+      </c>
+      <c r="M56" s="26" t="n">
+        <v>6494</v>
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
@@ -8651,24 +8506,20 @@
       <c r="H57" s="87" t="n">
         <v>15289</v>
       </c>
-      <c r="I57" s="187">
-        <f>IFERROR(VLOOKUP(B57,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I57" s="187" t="n">
+        <v>1502.7</v>
       </c>
       <c r="J57" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="89">
-        <f>IFERROR(ROUND(H57*I57,0),0)</f>
-        <v/>
-      </c>
-      <c r="L57" s="89">
-        <f>IFERROR(VLOOKUP(B57,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M57" s="89">
-        <f>IFERROR(VLOOKUP(B57,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>22974780</v>
+      </c>
+      <c r="K57" s="89" t="n">
+        <v>22974780</v>
+      </c>
+      <c r="L57" s="89" t="n">
+        <v>1880</v>
+      </c>
+      <c r="M57" s="89" t="n">
+        <v>1203</v>
       </c>
       <c r="N57" s="85" t="inlineStr">
         <is>
@@ -8903,24 +8754,20 @@
       <c r="H59" s="134" t="n">
         <v>180</v>
       </c>
-      <c r="I59" s="134">
-        <f>IFERROR(VLOOKUP(B59,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I59" s="134" t="n">
+        <v>1518.9</v>
       </c>
       <c r="J59" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="136">
-        <f>IFERROR(ROUND(H59*I59,0),0)</f>
-        <v/>
-      </c>
-      <c r="L59" s="136">
-        <f>IFERROR(VLOOKUP(B59,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M59" s="136">
-        <f>IFERROR(VLOOKUP(B59,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>273402</v>
+      </c>
+      <c r="K59" s="136" t="n">
+        <v>273402</v>
+      </c>
+      <c r="L59" s="136" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M59" s="136" t="n">
+        <v>8000</v>
       </c>
       <c r="N59" s="137" t="n"/>
       <c r="O59" s="137" t="n"/>
@@ -9012,24 +8859,20 @@
       <c r="H60" s="134" t="n">
         <v>250</v>
       </c>
-      <c r="I60" s="134">
-        <f>IFERROR(VLOOKUP(B60,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I60" s="134" t="n">
+        <v>1502.8</v>
       </c>
       <c r="J60" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="136">
-        <f>IFERROR(ROUND(H60*I60,0),0)</f>
-        <v/>
-      </c>
-      <c r="L60" s="136">
-        <f>IFERROR(VLOOKUP(B60,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M60" s="136">
-        <f>IFERROR(VLOOKUP(B60,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>375700</v>
+      </c>
+      <c r="K60" s="136" t="n">
+        <v>375700</v>
+      </c>
+      <c r="L60" s="136" t="n">
+        <v>32</v>
+      </c>
+      <c r="M60" s="136" t="n">
+        <v>20</v>
       </c>
       <c r="N60" s="137" t="n"/>
       <c r="O60" s="137" t="n"/>
@@ -9121,24 +8964,20 @@
       <c r="H61" s="134" t="n">
         <v>500</v>
       </c>
-      <c r="I61" s="134">
-        <f>IFERROR(VLOOKUP(B61,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I61" s="134" t="n">
+        <v>1525.3</v>
       </c>
       <c r="J61" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="136">
-        <f>IFERROR(ROUND(H61*I61,0),0)</f>
-        <v/>
-      </c>
-      <c r="L61" s="136">
-        <f>IFERROR(VLOOKUP(B61,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M61" s="136">
-        <f>IFERROR(VLOOKUP(B61,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>762650</v>
+      </c>
+      <c r="K61" s="136" t="n">
+        <v>762650</v>
+      </c>
+      <c r="L61" s="136" t="n">
+        <v>52</v>
+      </c>
+      <c r="M61" s="136" t="n">
+        <v>34</v>
       </c>
       <c r="N61" s="137" t="n"/>
       <c r="O61" s="137" t="n"/>
@@ -9491,19 +9330,16 @@
         <v/>
       </c>
       <c r="J64" s="222" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="222">
-        <f>IFERROR(ROUND(H64*I64,0),0)</f>
-        <v/>
-      </c>
-      <c r="L64" s="222">
-        <f>IFERROR(VLOOKUP(B64,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M64" s="222">
-        <f>IFERROR(VLOOKUP(B64,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>75818749</v>
+      </c>
+      <c r="K64" s="222" t="n">
+        <v>75818749</v>
+      </c>
+      <c r="L64" s="222" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M64" s="222" t="n">
+        <v>16000</v>
       </c>
       <c r="N64" s="216" t="inlineStr">
         <is>
@@ -14744,33 +14580,26 @@
       <c r="E43" s="118" t="n">
         <v>143557</v>
       </c>
-      <c r="F43" s="122">
-        <f>D43/E43</f>
-        <v/>
-      </c>
-      <c r="G43" s="118">
-        <f>F10</f>
-        <v/>
-      </c>
-      <c r="H43" s="120">
-        <f>ROUND(D43*G43,0)</f>
-        <v/>
-      </c>
-      <c r="I43" s="120">
-        <f>ROUND(G10*F43*G43,0)</f>
-        <v/>
-      </c>
-      <c r="J43" s="120">
-        <f>ROUND(H10*F43,0)</f>
-        <v/>
-      </c>
-      <c r="K43" s="120">
-        <f>ROUND(I10*F43,0)</f>
-        <v/>
-      </c>
-      <c r="L43" s="121">
-        <f>H43+I43+J43+K43</f>
-        <v/>
+      <c r="F43" s="122" t="n">
+        <v>0.968835</v>
+      </c>
+      <c r="G43" s="118" t="n">
+        <v>1479.7</v>
+      </c>
+      <c r="H43" s="120" t="n">
+        <v>205801115</v>
+      </c>
+      <c r="I43" s="120" t="n">
+        <v>28672</v>
+      </c>
+      <c r="J43" s="120" t="n">
+        <v>12110</v>
+      </c>
+      <c r="K43" s="120" t="n">
+        <v>7751</v>
+      </c>
+      <c r="L43" s="121" t="n">
+        <v>205849648</v>
       </c>
       <c r="M43" s="115" t="n"/>
     </row>
@@ -14796,33 +14625,26 @@
       <c r="E44" s="118" t="n">
         <v>143557</v>
       </c>
-      <c r="F44" s="122">
-        <f>D44/E44</f>
-        <v/>
-      </c>
-      <c r="G44" s="118">
-        <f>F10</f>
-        <v/>
-      </c>
-      <c r="H44" s="120">
-        <f>ROUND(D44*G44,0)</f>
-        <v/>
-      </c>
-      <c r="I44" s="120">
-        <f>ROUND(G10*F44*G44,0)</f>
-        <v/>
-      </c>
-      <c r="J44" s="120">
-        <f>ROUND(H10*F44,0)</f>
-        <v/>
-      </c>
-      <c r="K44" s="120">
-        <f>ROUND(I10*F44,0)</f>
-        <v/>
-      </c>
-      <c r="L44" s="121">
-        <f>H44+I44+J44+K44</f>
-        <v/>
+      <c r="F44" s="122" t="n">
+        <v>0.031165</v>
+      </c>
+      <c r="G44" s="118" t="n">
+        <v>1479.7</v>
+      </c>
+      <c r="H44" s="120" t="n">
+        <v>6620178</v>
+      </c>
+      <c r="I44" s="120" t="n">
+        <v>922</v>
+      </c>
+      <c r="J44" s="120" t="n">
+        <v>390</v>
+      </c>
+      <c r="K44" s="120" t="n">
+        <v>249</v>
+      </c>
+      <c r="L44" s="121" t="n">
+        <v>6621739</v>
       </c>
       <c r="M44" s="115" t="n"/>
     </row>
@@ -14848,33 +14670,26 @@
       <c r="E45" s="118" t="n">
         <v>15040</v>
       </c>
-      <c r="F45" s="122">
-        <f>D45/E45</f>
-        <v/>
-      </c>
-      <c r="G45" s="118">
-        <f>F9</f>
-        <v/>
-      </c>
-      <c r="H45" s="120">
-        <f>ROUND(D45*G45,0)</f>
-        <v/>
-      </c>
-      <c r="I45" s="120">
-        <f>ROUND(G9*F45*G45,0)</f>
-        <v/>
-      </c>
-      <c r="J45" s="120">
-        <f>ROUND(H9*F45,0)</f>
-        <v/>
-      </c>
-      <c r="K45" s="120">
-        <f>ROUND(I9*F45,0)</f>
-        <v/>
-      </c>
-      <c r="L45" s="121">
-        <f>H45+I45+J45+K45</f>
-        <v/>
+      <c r="F45" s="122" t="n">
+        <v>0.328191</v>
+      </c>
+      <c r="G45" s="118" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H45" s="120" t="n">
+        <v>7305280</v>
+      </c>
+      <c r="I45" s="120" t="n">
+        <v>9714</v>
+      </c>
+      <c r="J45" s="120" t="n">
+        <v>3282</v>
+      </c>
+      <c r="K45" s="120" t="n">
+        <v>2626</v>
+      </c>
+      <c r="L45" s="121" t="n">
+        <v>7320902</v>
       </c>
       <c r="M45" s="115" t="n"/>
     </row>
@@ -14900,33 +14715,26 @@
       <c r="E46" s="118" t="n">
         <v>13860</v>
       </c>
-      <c r="F46" s="122">
-        <f>D46/E46</f>
-        <v/>
-      </c>
-      <c r="G46" s="118">
-        <f>F12</f>
-        <v/>
-      </c>
-      <c r="H46" s="120">
-        <f>ROUND(D46*G46,0)</f>
-        <v/>
-      </c>
-      <c r="I46" s="120">
-        <f>ROUND(G12*F46*G46,0)</f>
-        <v/>
-      </c>
-      <c r="J46" s="120">
-        <f>ROUND(H12*F46,0)</f>
-        <v/>
-      </c>
-      <c r="K46" s="120">
-        <f>ROUND(I12*F46,0)</f>
-        <v/>
-      </c>
-      <c r="L46" s="121">
-        <f>H46+I46+J46+K46</f>
-        <v/>
+      <c r="F46" s="122" t="n">
+        <v>0.65368</v>
+      </c>
+      <c r="G46" s="118" t="n">
+        <v>1439.1</v>
+      </c>
+      <c r="H46" s="120" t="n">
+        <v>13038246</v>
+      </c>
+      <c r="I46" s="120" t="n">
+        <v>18814</v>
+      </c>
+      <c r="J46" s="120" t="n">
+        <v>6537</v>
+      </c>
+      <c r="K46" s="120" t="n">
+        <v>5229</v>
+      </c>
+      <c r="L46" s="121" t="n">
+        <v>13068826</v>
       </c>
       <c r="M46" s="115" t="n"/>
     </row>
@@ -14952,33 +14760,26 @@
       <c r="E47" s="118" t="n">
         <v>13860</v>
       </c>
-      <c r="F47" s="122">
-        <f>D47/E47</f>
-        <v/>
-      </c>
-      <c r="G47" s="118">
-        <f>F12</f>
-        <v/>
-      </c>
-      <c r="H47" s="120">
-        <f>ROUND(D47*G47,0)</f>
-        <v/>
-      </c>
-      <c r="I47" s="120">
-        <f>ROUND(G12*F47*G47,0)</f>
-        <v/>
-      </c>
-      <c r="J47" s="120">
-        <f>ROUND(H12*F47,0)</f>
-        <v/>
-      </c>
-      <c r="K47" s="120">
-        <f>ROUND(I12*F47,0)</f>
-        <v/>
-      </c>
-      <c r="L47" s="121">
-        <f>H47+I47+J47+K47</f>
-        <v/>
+      <c r="F47" s="122" t="n">
+        <v>0.025253</v>
+      </c>
+      <c r="G47" s="118" t="n">
+        <v>1439.1</v>
+      </c>
+      <c r="H47" s="120" t="n">
+        <v>503685</v>
+      </c>
+      <c r="I47" s="120" t="n">
+        <v>727</v>
+      </c>
+      <c r="J47" s="120" t="n">
+        <v>253</v>
+      </c>
+      <c r="K47" s="120" t="n">
+        <v>202</v>
+      </c>
+      <c r="L47" s="121" t="n">
+        <v>504867</v>
       </c>
       <c r="M47" s="115" t="n"/>
     </row>
@@ -15004,33 +14805,26 @@
       <c r="E48" s="118" t="n">
         <v>252</v>
       </c>
-      <c r="F48" s="122">
-        <f>D48/E48</f>
-        <v/>
-      </c>
-      <c r="G48" s="118">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="H48" s="120">
-        <f>ROUND(D48*G48,0)</f>
-        <v/>
-      </c>
-      <c r="I48" s="120">
-        <f>ROUND(G14*F48*G48,0)</f>
-        <v/>
-      </c>
-      <c r="J48" s="120">
-        <f>ROUND(H14*F48,0)</f>
-        <v/>
-      </c>
-      <c r="K48" s="120">
-        <f>ROUND(I14*F48,0)</f>
-        <v/>
-      </c>
-      <c r="L48" s="121">
-        <f>H48+I48+J48+K48</f>
-        <v/>
+      <c r="F48" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="118" t="n">
+        <v>1479</v>
+      </c>
+      <c r="H48" s="120" t="n">
+        <v>372708</v>
+      </c>
+      <c r="I48" s="120" t="n">
+        <v>29580</v>
+      </c>
+      <c r="J48" s="120" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K48" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L48" s="121" t="n">
+        <v>412788</v>
       </c>
       <c r="M48" s="115" t="n"/>
     </row>
@@ -15056,33 +14850,26 @@
       <c r="E49" s="118" t="n">
         <v>3700</v>
       </c>
-      <c r="F49" s="122">
-        <f>D49/E49</f>
-        <v/>
-      </c>
-      <c r="G49" s="118">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="H49" s="120">
-        <f>ROUND(D49*G49,0)</f>
-        <v/>
-      </c>
-      <c r="I49" s="120">
-        <f>ROUND(G15*F49*G49,0)</f>
-        <v/>
-      </c>
-      <c r="J49" s="120">
-        <f>ROUND(H15*F49,0)</f>
-        <v/>
-      </c>
-      <c r="K49" s="120">
-        <f>ROUND(I15*F49,0)</f>
-        <v/>
-      </c>
-      <c r="L49" s="121">
-        <f>H49+I49+J49+K49</f>
-        <v/>
+      <c r="F49" s="122" t="n">
+        <v>0.121622</v>
+      </c>
+      <c r="G49" s="118" t="n">
+        <v>1475.7</v>
+      </c>
+      <c r="H49" s="120" t="n">
+        <v>664065</v>
+      </c>
+      <c r="I49" s="120" t="n">
+        <v>3590</v>
+      </c>
+      <c r="J49" s="120" t="n">
+        <v>912</v>
+      </c>
+      <c r="K49" s="120" t="n">
+        <v>973</v>
+      </c>
+      <c r="L49" s="121" t="n">
+        <v>669540</v>
       </c>
       <c r="M49" s="115" t="n"/>
     </row>
@@ -15108,33 +14895,26 @@
       <c r="E50" s="118" t="n">
         <v>3700</v>
       </c>
-      <c r="F50" s="122">
-        <f>D50/E50</f>
-        <v/>
-      </c>
-      <c r="G50" s="118">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="H50" s="120">
-        <f>ROUND(D50*G50,0)</f>
-        <v/>
-      </c>
-      <c r="I50" s="120">
-        <f>ROUND(G15*F50*G50,0)</f>
-        <v/>
-      </c>
-      <c r="J50" s="120">
-        <f>ROUND(H15*F50,0)</f>
-        <v/>
-      </c>
-      <c r="K50" s="120">
-        <f>ROUND(I15*F50,0)</f>
-        <v/>
-      </c>
-      <c r="L50" s="121">
-        <f>H50+I50+J50+K50</f>
-        <v/>
+      <c r="F50" s="122" t="n">
+        <v>0.732432</v>
+      </c>
+      <c r="G50" s="118" t="n">
+        <v>1475.7</v>
+      </c>
+      <c r="H50" s="120" t="n">
+        <v>3999147</v>
+      </c>
+      <c r="I50" s="120" t="n">
+        <v>21617</v>
+      </c>
+      <c r="J50" s="120" t="n">
+        <v>5493</v>
+      </c>
+      <c r="K50" s="120" t="n">
+        <v>5859</v>
+      </c>
+      <c r="L50" s="121" t="n">
+        <v>4032116</v>
       </c>
       <c r="M50" s="115" t="n"/>
     </row>
@@ -15160,33 +14940,26 @@
       <c r="E51" s="118" t="n">
         <v>3700</v>
       </c>
-      <c r="F51" s="122">
-        <f>D51/E51</f>
-        <v/>
-      </c>
-      <c r="G51" s="118">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="H51" s="120">
-        <f>ROUND(D51*G51,0)</f>
-        <v/>
-      </c>
-      <c r="I51" s="120">
-        <f>ROUND(G15*F51*G51,0)</f>
-        <v/>
-      </c>
-      <c r="J51" s="120">
-        <f>ROUND(H15*F51,0)</f>
-        <v/>
-      </c>
-      <c r="K51" s="120">
-        <f>ROUND(I15*F51,0)</f>
-        <v/>
-      </c>
-      <c r="L51" s="121">
-        <f>H51+I51+J51+K51</f>
-        <v/>
+      <c r="F51" s="122" t="n">
+        <v>0.145946</v>
+      </c>
+      <c r="G51" s="118" t="n">
+        <v>1475.7</v>
+      </c>
+      <c r="H51" s="120" t="n">
+        <v>796878</v>
+      </c>
+      <c r="I51" s="120" t="n">
+        <v>4307</v>
+      </c>
+      <c r="J51" s="120" t="n">
+        <v>1095</v>
+      </c>
+      <c r="K51" s="120" t="n">
+        <v>1168</v>
+      </c>
+      <c r="L51" s="121" t="n">
+        <v>803448</v>
       </c>
       <c r="M51" s="115" t="n"/>
     </row>
@@ -15212,33 +14985,26 @@
       <c r="E52" s="118" t="n">
         <v>9626.35</v>
       </c>
-      <c r="F52" s="122">
-        <f>D52/E52</f>
-        <v/>
-      </c>
-      <c r="G52" s="118">
-        <f>F16</f>
-        <v/>
-      </c>
-      <c r="H52" s="120">
-        <f>ROUND(D52*G52,0)</f>
-        <v/>
-      </c>
-      <c r="I52" s="120">
-        <f>ROUND(G16*F52*G52,0)</f>
-        <v/>
-      </c>
-      <c r="J52" s="120">
-        <f>ROUND(H16*F52,0)</f>
-        <v/>
-      </c>
-      <c r="K52" s="120">
-        <f>ROUND(I16*F52,0)</f>
-        <v/>
-      </c>
-      <c r="L52" s="121">
-        <f>H52+I52+J52+K52</f>
-        <v/>
+      <c r="F52" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="118" t="n">
+        <v>1476</v>
+      </c>
+      <c r="H52" s="120" t="n">
+        <v>14208493</v>
+      </c>
+      <c r="I52" s="120" t="n">
+        <v>29520</v>
+      </c>
+      <c r="J52" s="120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K52" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L52" s="121" t="n">
+        <v>14256013</v>
       </c>
       <c r="M52" s="115" t="n"/>
     </row>
@@ -15264,33 +15030,26 @@
       <c r="E53" s="118" t="n">
         <v>5056.8</v>
       </c>
-      <c r="F53" s="122">
-        <f>D53/E53</f>
-        <v/>
-      </c>
-      <c r="G53" s="118">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="H53" s="120">
-        <f>ROUND(D53*G53,0)</f>
-        <v/>
-      </c>
-      <c r="I53" s="120">
-        <f>ROUND(G17*F53*G53,0)</f>
-        <v/>
-      </c>
-      <c r="J53" s="120">
-        <f>ROUND(H17*F53,0)</f>
-        <v/>
-      </c>
-      <c r="K53" s="120">
-        <f>ROUND(I17*F53,0)</f>
-        <v/>
-      </c>
-      <c r="L53" s="121">
-        <f>H53+I53+J53+K53</f>
-        <v/>
+      <c r="F53" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="118" t="n">
+        <v>1445.5</v>
+      </c>
+      <c r="H53" s="120" t="n">
+        <v>7309604</v>
+      </c>
+      <c r="I53" s="120" t="n">
+        <v>28910</v>
+      </c>
+      <c r="J53" s="120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K53" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L53" s="121" t="n">
+        <v>7356514</v>
       </c>
       <c r="M53" s="115" t="n"/>
     </row>
@@ -15316,33 +15075,26 @@
       <c r="E54" s="118" t="n">
         <v>24794</v>
       </c>
-      <c r="F54" s="122">
-        <f>D54/E54</f>
-        <v/>
-      </c>
-      <c r="G54" s="118">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="H54" s="120">
-        <f>ROUND(D54*G54,0)</f>
-        <v/>
-      </c>
-      <c r="I54" s="120">
-        <f>ROUND(G19*F54*G54,0)</f>
-        <v/>
-      </c>
-      <c r="J54" s="120">
-        <f>ROUND(H19*F54,0)</f>
-        <v/>
-      </c>
-      <c r="K54" s="120">
-        <f>ROUND(I19*F54,0)</f>
-        <v/>
-      </c>
-      <c r="L54" s="121">
-        <f>H54+I54+J54+K54</f>
-        <v/>
+      <c r="F54" s="122" t="n">
+        <v>0.813665</v>
+      </c>
+      <c r="G54" s="118" t="n">
+        <v>1454.7</v>
+      </c>
+      <c r="H54" s="120" t="n">
+        <v>29347118</v>
+      </c>
+      <c r="I54" s="120" t="n">
+        <v>23673</v>
+      </c>
+      <c r="J54" s="120" t="n">
+        <v>10171</v>
+      </c>
+      <c r="K54" s="120" t="n">
+        <v>6509</v>
+      </c>
+      <c r="L54" s="121" t="n">
+        <v>29387471</v>
       </c>
       <c r="M54" s="115" t="n"/>
     </row>
@@ -15368,33 +15120,26 @@
       <c r="E55" s="118" t="n">
         <v>24794</v>
       </c>
-      <c r="F55" s="122">
-        <f>D55/E55</f>
-        <v/>
-      </c>
-      <c r="G55" s="118">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="H55" s="120">
-        <f>ROUND(D55*G55,0)</f>
-        <v/>
-      </c>
-      <c r="I55" s="120">
-        <f>ROUND(G19*F55*G55,0)</f>
-        <v/>
-      </c>
-      <c r="J55" s="120">
-        <f>ROUND(H19*F55,0)</f>
-        <v/>
-      </c>
-      <c r="K55" s="120">
-        <f>ROUND(I19*F55,0)</f>
-        <v/>
-      </c>
-      <c r="L55" s="121">
-        <f>H55+I55+J55+K55</f>
-        <v/>
+      <c r="F55" s="122" t="n">
+        <v>0.186335</v>
+      </c>
+      <c r="G55" s="118" t="n">
+        <v>1454.7</v>
+      </c>
+      <c r="H55" s="120" t="n">
+        <v>6720714</v>
+      </c>
+      <c r="I55" s="120" t="n">
+        <v>5421</v>
+      </c>
+      <c r="J55" s="120" t="n">
+        <v>2329</v>
+      </c>
+      <c r="K55" s="120" t="n">
+        <v>1491</v>
+      </c>
+      <c r="L55" s="121" t="n">
+        <v>6729955</v>
       </c>
       <c r="M55" s="115" t="n"/>
     </row>
@@ -15420,33 +15165,26 @@
       <c r="E56" s="118" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F56" s="122">
-        <f>D56/E56</f>
-        <v/>
-      </c>
-      <c r="G56" s="118">
-        <f>F20</f>
-        <v/>
-      </c>
-      <c r="H56" s="120">
-        <f>ROUND(D56*G56,0)</f>
-        <v/>
-      </c>
-      <c r="I56" s="120">
-        <f>ROUND(G20*F56*G56,0)</f>
-        <v/>
-      </c>
-      <c r="J56" s="120">
-        <f>ROUND(H20*F56,0)</f>
-        <v/>
-      </c>
-      <c r="K56" s="120">
-        <f>ROUND(I20*F56,0)</f>
-        <v/>
-      </c>
-      <c r="L56" s="121">
-        <f>H56+I56+J56+K56</f>
-        <v/>
+      <c r="F56" s="122" t="n">
+        <v>0.124143</v>
+      </c>
+      <c r="G56" s="118" t="n">
+        <v>1453.6</v>
+      </c>
+      <c r="H56" s="120" t="n">
+        <v>2093184</v>
+      </c>
+      <c r="I56" s="120" t="n">
+        <v>3609</v>
+      </c>
+      <c r="J56" s="120" t="n">
+        <v>1241</v>
+      </c>
+      <c r="K56" s="120" t="n">
+        <v>993</v>
+      </c>
+      <c r="L56" s="121" t="n">
+        <v>2099027</v>
       </c>
       <c r="M56" s="115" t="n"/>
     </row>
@@ -15472,33 +15210,26 @@
       <c r="E57" s="118" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F57" s="122">
-        <f>D57/E57</f>
-        <v/>
-      </c>
-      <c r="G57" s="118">
-        <f>F20</f>
-        <v/>
-      </c>
-      <c r="H57" s="120">
-        <f>ROUND(D57*G57,0)</f>
-        <v/>
-      </c>
-      <c r="I57" s="120">
-        <f>ROUND(G20*F57*G57,0)</f>
-        <v/>
-      </c>
-      <c r="J57" s="120">
-        <f>ROUND(H20*F57,0)</f>
-        <v/>
-      </c>
-      <c r="K57" s="120">
-        <f>ROUND(I20*F57,0)</f>
-        <v/>
-      </c>
-      <c r="L57" s="121">
-        <f>H57+I57+J57+K57</f>
-        <v/>
+      <c r="F57" s="122" t="n">
+        <v>0.386997</v>
+      </c>
+      <c r="G57" s="118" t="n">
+        <v>1453.6</v>
+      </c>
+      <c r="H57" s="120" t="n">
+        <v>6525210</v>
+      </c>
+      <c r="I57" s="120" t="n">
+        <v>11251</v>
+      </c>
+      <c r="J57" s="120" t="n">
+        <v>3870</v>
+      </c>
+      <c r="K57" s="120" t="n">
+        <v>3096</v>
+      </c>
+      <c r="L57" s="121" t="n">
+        <v>6543427</v>
       </c>
       <c r="M57" s="115" t="n"/>
     </row>
@@ -15524,33 +15255,26 @@
       <c r="E58" s="118" t="n">
         <v>11599.57</v>
       </c>
-      <c r="F58" s="122">
-        <f>D58/E58</f>
-        <v/>
-      </c>
-      <c r="G58" s="118">
-        <f>F20</f>
-        <v/>
-      </c>
-      <c r="H58" s="120">
-        <f>ROUND(D58*G58,0)</f>
-        <v/>
-      </c>
-      <c r="I58" s="120">
-        <f>ROUND(G20*F58*G58,0)</f>
-        <v/>
-      </c>
-      <c r="J58" s="120">
-        <f>ROUND(H20*F58,0)</f>
-        <v/>
-      </c>
-      <c r="K58" s="120">
-        <f>ROUND(I20*F58,0)</f>
-        <v/>
-      </c>
-      <c r="L58" s="121">
-        <f>H58+I58+J58+K58</f>
-        <v/>
+      <c r="F58" s="122" t="n">
+        <v>0.48886</v>
+      </c>
+      <c r="G58" s="118" t="n">
+        <v>1453.6</v>
+      </c>
+      <c r="H58" s="120" t="n">
+        <v>8242741</v>
+      </c>
+      <c r="I58" s="120" t="n">
+        <v>14212</v>
+      </c>
+      <c r="J58" s="120" t="n">
+        <v>4889</v>
+      </c>
+      <c r="K58" s="120" t="n">
+        <v>3911</v>
+      </c>
+      <c r="L58" s="121" t="n">
+        <v>8265753</v>
       </c>
       <c r="M58" s="115" t="n"/>
     </row>
@@ -15576,33 +15300,26 @@
       <c r="E59" s="118" t="n">
         <v>26358</v>
       </c>
-      <c r="F59" s="122">
-        <f>D59/E59</f>
-        <v/>
-      </c>
-      <c r="G59" s="118">
-        <f>F21</f>
-        <v/>
-      </c>
-      <c r="H59" s="120">
-        <f>ROUND(D59*G59,0)</f>
-        <v/>
-      </c>
-      <c r="I59" s="120">
-        <f>ROUND(G21*F59*G59,0)</f>
-        <v/>
-      </c>
-      <c r="J59" s="120">
-        <f>ROUND(H21*F59,0)</f>
-        <v/>
-      </c>
-      <c r="K59" s="120">
-        <f>ROUND(I21*F59,0)</f>
-        <v/>
-      </c>
-      <c r="L59" s="121">
-        <f>H59+I59+J59+K59</f>
-        <v/>
+      <c r="F59" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="118" t="n">
+        <v>1460.7</v>
+      </c>
+      <c r="H59" s="120" t="n">
+        <v>38501131</v>
+      </c>
+      <c r="I59" s="120" t="n">
+        <v>29214</v>
+      </c>
+      <c r="J59" s="120" t="n">
+        <v>12500</v>
+      </c>
+      <c r="K59" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L59" s="121" t="n">
+        <v>38550845</v>
       </c>
       <c r="M59" s="115" t="n"/>
     </row>
@@ -15628,33 +15345,26 @@
       <c r="E60" s="118" t="n">
         <v>17538</v>
       </c>
-      <c r="F60" s="122">
-        <f>D60/E60</f>
-        <v/>
-      </c>
-      <c r="G60" s="118">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H60" s="120">
-        <f>ROUND(D60*G60,0)</f>
-        <v/>
-      </c>
-      <c r="I60" s="120">
-        <f>ROUND(G22*F60*G60,0)</f>
-        <v/>
-      </c>
-      <c r="J60" s="120">
-        <f>ROUND(H22*F60,0)</f>
-        <v/>
-      </c>
-      <c r="K60" s="120">
-        <f>ROUND(I22*F60,0)</f>
-        <v/>
-      </c>
-      <c r="L60" s="121">
-        <f>H60+I60+J60+K60</f>
-        <v/>
+      <c r="F60" s="122" t="n">
+        <v>0.843483</v>
+      </c>
+      <c r="G60" s="118" t="n">
+        <v>1451.7</v>
+      </c>
+      <c r="H60" s="120" t="n">
+        <v>21474998</v>
+      </c>
+      <c r="I60" s="120" t="n">
+        <v>24490</v>
+      </c>
+      <c r="J60" s="120" t="n">
+        <v>8435</v>
+      </c>
+      <c r="K60" s="120" t="n">
+        <v>6748</v>
+      </c>
+      <c r="L60" s="121" t="n">
+        <v>21514671</v>
       </c>
       <c r="M60" s="115" t="n"/>
     </row>
@@ -15680,33 +15390,26 @@
       <c r="E61" s="118" t="n">
         <v>17538</v>
       </c>
-      <c r="F61" s="122">
-        <f>D61/E61</f>
-        <v/>
-      </c>
-      <c r="G61" s="118">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H61" s="120">
-        <f>ROUND(D61*G61,0)</f>
-        <v/>
-      </c>
-      <c r="I61" s="120">
-        <f>ROUND(G22*F61*G61,0)</f>
-        <v/>
-      </c>
-      <c r="J61" s="120">
-        <f>ROUND(H22*F61,0)</f>
-        <v/>
-      </c>
-      <c r="K61" s="120">
-        <f>ROUND(I22*F61,0)</f>
-        <v/>
-      </c>
-      <c r="L61" s="121">
-        <f>H61+I61+J61+K61</f>
-        <v/>
+      <c r="F61" s="122" t="n">
+        <v>0.156517</v>
+      </c>
+      <c r="G61" s="118" t="n">
+        <v>1451.7</v>
+      </c>
+      <c r="H61" s="120" t="n">
+        <v>3984917</v>
+      </c>
+      <c r="I61" s="120" t="n">
+        <v>4544</v>
+      </c>
+      <c r="J61" s="120" t="n">
+        <v>1565</v>
+      </c>
+      <c r="K61" s="120" t="n">
+        <v>1252</v>
+      </c>
+      <c r="L61" s="121" t="n">
+        <v>3992278</v>
       </c>
       <c r="M61" s="115" t="n"/>
     </row>
@@ -15732,33 +15435,26 @@
       <c r="E62" s="118" t="n">
         <v>142189</v>
       </c>
-      <c r="F62" s="122">
-        <f>D62/E62</f>
-        <v/>
-      </c>
-      <c r="G62" s="118">
-        <f>F23</f>
-        <v/>
-      </c>
-      <c r="H62" s="120">
-        <f>ROUND(D62*G62,0)</f>
-        <v/>
-      </c>
-      <c r="I62" s="120">
-        <f>ROUND(G23*F62*G62,0)</f>
-        <v/>
-      </c>
-      <c r="J62" s="120">
-        <f>ROUND(H23*F62,0)</f>
-        <v/>
-      </c>
-      <c r="K62" s="120">
-        <f>ROUND(I23*F62,0)</f>
-        <v/>
-      </c>
-      <c r="L62" s="121">
-        <f>H62+I62+J62+K62</f>
-        <v/>
+      <c r="F62" s="122" t="n">
+        <v>0.039898</v>
+      </c>
+      <c r="G62" s="118" t="n">
+        <v>1441.6</v>
+      </c>
+      <c r="H62" s="120" t="n">
+        <v>8178197</v>
+      </c>
+      <c r="I62" s="120" t="n">
+        <v>1150</v>
+      </c>
+      <c r="J62" s="120" t="n">
+        <v>499</v>
+      </c>
+      <c r="K62" s="120" t="n">
+        <v>319</v>
+      </c>
+      <c r="L62" s="121" t="n">
+        <v>8180165</v>
       </c>
       <c r="M62" s="115" t="n"/>
     </row>
@@ -15784,33 +15480,26 @@
       <c r="E63" s="118" t="n">
         <v>142189</v>
       </c>
-      <c r="F63" s="122">
-        <f>D63/E63</f>
-        <v/>
-      </c>
-      <c r="G63" s="118">
-        <f>F23</f>
-        <v/>
-      </c>
-      <c r="H63" s="120">
-        <f>ROUND(D63*G63,0)</f>
-        <v/>
-      </c>
-      <c r="I63" s="120">
-        <f>ROUND(G23*F63*G63,0)</f>
-        <v/>
-      </c>
-      <c r="J63" s="120">
-        <f>ROUND(H23*F63,0)</f>
-        <v/>
-      </c>
-      <c r="K63" s="120">
-        <f>ROUND(I23*F63,0)</f>
-        <v/>
-      </c>
-      <c r="L63" s="121">
-        <f>H63+I63+J63+K63</f>
-        <v/>
+      <c r="F63" s="122" t="n">
+        <v>0.960102</v>
+      </c>
+      <c r="G63" s="118" t="n">
+        <v>1441.6</v>
+      </c>
+      <c r="H63" s="120" t="n">
+        <v>196801466</v>
+      </c>
+      <c r="I63" s="120" t="n">
+        <v>27682</v>
+      </c>
+      <c r="J63" s="120" t="n">
+        <v>12001</v>
+      </c>
+      <c r="K63" s="120" t="n">
+        <v>7681</v>
+      </c>
+      <c r="L63" s="121" t="n">
+        <v>196848830</v>
       </c>
       <c r="M63" s="115" t="n"/>
     </row>
@@ -15836,33 +15525,26 @@
       <c r="E64" s="118" t="n">
         <v>137850</v>
       </c>
-      <c r="F64" s="122">
-        <f>D64/E64</f>
-        <v/>
-      </c>
-      <c r="G64" s="118">
-        <f>F24</f>
-        <v/>
-      </c>
-      <c r="H64" s="120">
-        <f>ROUND(D64*G64,0)</f>
-        <v/>
-      </c>
-      <c r="I64" s="120">
-        <f>ROUND(G24*F64*G64,0)</f>
-        <v/>
-      </c>
-      <c r="J64" s="120">
-        <f>ROUND(H24*F64,0)</f>
-        <v/>
-      </c>
-      <c r="K64" s="120">
-        <f>ROUND(I24*F64,0)</f>
-        <v/>
-      </c>
-      <c r="L64" s="121">
-        <f>H64+I64+J64+K64</f>
-        <v/>
+      <c r="F64" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="118" t="n">
+        <v>1477.6</v>
+      </c>
+      <c r="H64" s="120" t="n">
+        <v>203687160</v>
+      </c>
+      <c r="I64" s="120" t="n">
+        <v>29552</v>
+      </c>
+      <c r="J64" s="120" t="n">
+        <v>12500</v>
+      </c>
+      <c r="K64" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L64" s="121" t="n">
+        <v>203737212</v>
       </c>
       <c r="M64" s="115" t="n"/>
     </row>
@@ -15888,33 +15570,26 @@
       <c r="E65" s="118" t="n">
         <v>34354</v>
       </c>
-      <c r="F65" s="122">
-        <f>D65/E65</f>
-        <v/>
-      </c>
-      <c r="G65" s="118">
-        <f>F25</f>
-        <v/>
-      </c>
-      <c r="H65" s="120">
-        <f>ROUND(D65*G65,0)</f>
-        <v/>
-      </c>
-      <c r="I65" s="120">
-        <f>ROUND(G25*F65*G65,0)</f>
-        <v/>
-      </c>
-      <c r="J65" s="120">
-        <f>ROUND(H25*F65,0)</f>
-        <v/>
-      </c>
-      <c r="K65" s="120">
-        <f>ROUND(I25*F65,0)</f>
-        <v/>
-      </c>
-      <c r="L65" s="121">
-        <f>H65+I65+J65+K65</f>
-        <v/>
+      <c r="F65" s="122" t="n">
+        <v>0.283519</v>
+      </c>
+      <c r="G65" s="118" t="n">
+        <v>1505.7</v>
+      </c>
+      <c r="H65" s="120" t="n">
+        <v>14665518</v>
+      </c>
+      <c r="I65" s="120" t="n">
+        <v>8538</v>
+      </c>
+      <c r="J65" s="120" t="n">
+        <v>3544</v>
+      </c>
+      <c r="K65" s="120" t="n">
+        <v>2268</v>
+      </c>
+      <c r="L65" s="121" t="n">
+        <v>14679868</v>
       </c>
       <c r="M65" s="115" t="n"/>
     </row>
@@ -15940,33 +15615,26 @@
       <c r="E66" s="118" t="n">
         <v>34354</v>
       </c>
-      <c r="F66" s="122">
-        <f>D66/E66</f>
-        <v/>
-      </c>
-      <c r="G66" s="118">
-        <f>F25</f>
-        <v/>
-      </c>
-      <c r="H66" s="120">
-        <f>ROUND(D66*G66,0)</f>
-        <v/>
-      </c>
-      <c r="I66" s="120">
-        <f>ROUND(G25*F66*G66,0)</f>
-        <v/>
-      </c>
-      <c r="J66" s="120">
-        <f>ROUND(H25*F66,0)</f>
-        <v/>
-      </c>
-      <c r="K66" s="120">
-        <f>ROUND(I25*F66,0)</f>
-        <v/>
-      </c>
-      <c r="L66" s="121">
-        <f>H66+I66+J66+K66</f>
-        <v/>
+      <c r="F66" s="122" t="n">
+        <v>0.716481</v>
+      </c>
+      <c r="G66" s="118" t="n">
+        <v>1505.7</v>
+      </c>
+      <c r="H66" s="120" t="n">
+        <v>37061300</v>
+      </c>
+      <c r="I66" s="120" t="n">
+        <v>21576</v>
+      </c>
+      <c r="J66" s="120" t="n">
+        <v>8956</v>
+      </c>
+      <c r="K66" s="120" t="n">
+        <v>5732</v>
+      </c>
+      <c r="L66" s="121" t="n">
+        <v>37097564</v>
       </c>
       <c r="M66" s="115" t="n"/>
     </row>
@@ -15992,33 +15660,26 @@
       <c r="E67" s="118" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F67" s="122">
-        <f>D67/E67</f>
-        <v/>
-      </c>
-      <c r="G67" s="118">
-        <f>F26</f>
-        <v/>
-      </c>
-      <c r="H67" s="120">
-        <f>ROUND(D67*G67,0)</f>
-        <v/>
-      </c>
-      <c r="I67" s="120">
-        <f>ROUND(G26*F67*G67,0)</f>
-        <v/>
-      </c>
-      <c r="J67" s="120">
-        <f>ROUND(H26*F67,0)</f>
-        <v/>
-      </c>
-      <c r="K67" s="120">
-        <f>ROUND(I26*F67,0)</f>
-        <v/>
-      </c>
-      <c r="L67" s="121">
-        <f>H67+I67+J67+K67</f>
-        <v/>
+      <c r="F67" s="122" t="n">
+        <v>0.259421</v>
+      </c>
+      <c r="G67" s="118" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="H67" s="120" t="n">
+        <v>2560880</v>
+      </c>
+      <c r="I67" s="120" t="n">
+        <v>7816</v>
+      </c>
+      <c r="J67" s="120" t="n">
+        <v>2594</v>
+      </c>
+      <c r="K67" s="120" t="n">
+        <v>2075</v>
+      </c>
+      <c r="L67" s="121" t="n">
+        <v>2573365</v>
       </c>
       <c r="M67" s="115" t="n"/>
     </row>
@@ -16044,33 +15705,26 @@
       <c r="E68" s="118" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F68" s="122">
-        <f>D68/E68</f>
-        <v/>
-      </c>
-      <c r="G68" s="118">
-        <f>F26</f>
-        <v/>
-      </c>
-      <c r="H68" s="120">
-        <f>ROUND(D68*G68,0)</f>
-        <v/>
-      </c>
-      <c r="I68" s="120">
-        <f>ROUND(G26*F68*G68,0)</f>
-        <v/>
-      </c>
-      <c r="J68" s="120">
-        <f>ROUND(H26*F68,0)</f>
-        <v/>
-      </c>
-      <c r="K68" s="120">
-        <f>ROUND(I26*F68,0)</f>
-        <v/>
-      </c>
-      <c r="L68" s="121">
-        <f>H68+I68+J68+K68</f>
-        <v/>
+      <c r="F68" s="122" t="n">
+        <v>0.6093420000000001</v>
+      </c>
+      <c r="G68" s="118" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="H68" s="120" t="n">
+        <v>6015131</v>
+      </c>
+      <c r="I68" s="120" t="n">
+        <v>18358</v>
+      </c>
+      <c r="J68" s="120" t="n">
+        <v>6093</v>
+      </c>
+      <c r="K68" s="120" t="n">
+        <v>4875</v>
+      </c>
+      <c r="L68" s="121" t="n">
+        <v>6044457</v>
       </c>
       <c r="M68" s="115" t="n"/>
     </row>
@@ -16096,33 +15750,26 @@
       <c r="E69" s="118" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F69" s="122">
-        <f>D69/E69</f>
-        <v/>
-      </c>
-      <c r="G69" s="118">
-        <f>F26</f>
-        <v/>
-      </c>
-      <c r="H69" s="120">
-        <f>ROUND(D69*G69,0)</f>
-        <v/>
-      </c>
-      <c r="I69" s="120">
-        <f>ROUND(G26*F69*G69,0)</f>
-        <v/>
-      </c>
-      <c r="J69" s="120">
-        <f>ROUND(H26*F69,0)</f>
-        <v/>
-      </c>
-      <c r="K69" s="120">
-        <f>ROUND(I26*F69,0)</f>
-        <v/>
-      </c>
-      <c r="L69" s="121">
-        <f>H69+I69+J69+K69</f>
-        <v/>
+      <c r="F69" s="122" t="n">
+        <v>0.054936</v>
+      </c>
+      <c r="G69" s="118" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="H69" s="120" t="n">
+        <v>542304</v>
+      </c>
+      <c r="I69" s="120" t="n">
+        <v>1655</v>
+      </c>
+      <c r="J69" s="120" t="n">
+        <v>549</v>
+      </c>
+      <c r="K69" s="120" t="n">
+        <v>439</v>
+      </c>
+      <c r="L69" s="121" t="n">
+        <v>544947</v>
       </c>
       <c r="M69" s="115" t="n"/>
     </row>
@@ -16148,33 +15795,26 @@
       <c r="E70" s="118" t="n">
         <v>6553.05</v>
       </c>
-      <c r="F70" s="122">
-        <f>D70/E70</f>
-        <v/>
-      </c>
-      <c r="G70" s="118">
-        <f>F26</f>
-        <v/>
-      </c>
-      <c r="H70" s="120">
-        <f>ROUND(D70*G70,0)</f>
-        <v/>
-      </c>
-      <c r="I70" s="120">
-        <f>ROUND(G26*F70*G70,0)</f>
-        <v/>
-      </c>
-      <c r="J70" s="120">
-        <f>ROUND(H26*F70,0)</f>
-        <v/>
-      </c>
-      <c r="K70" s="120">
-        <f>ROUND(I26*F70,0)</f>
-        <v/>
-      </c>
-      <c r="L70" s="121">
-        <f>H70+I70+J70+K70</f>
-        <v/>
+      <c r="F70" s="122" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="G70" s="118" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="H70" s="120" t="n">
+        <v>753200</v>
+      </c>
+      <c r="I70" s="120" t="n">
+        <v>2299</v>
+      </c>
+      <c r="J70" s="120" t="n">
+        <v>763</v>
+      </c>
+      <c r="K70" s="120" t="n">
+        <v>610</v>
+      </c>
+      <c r="L70" s="121" t="n">
+        <v>756872</v>
       </c>
       <c r="M70" s="115" t="n"/>
     </row>
@@ -16200,33 +15840,26 @@
       <c r="E71" s="118" t="n">
         <v>57650</v>
       </c>
-      <c r="F71" s="122">
-        <f>D71/E71</f>
-        <v/>
-      </c>
-      <c r="G71" s="118">
-        <f>F27</f>
-        <v/>
-      </c>
-      <c r="H71" s="120">
-        <f>ROUND(D71*G71,0)</f>
-        <v/>
-      </c>
-      <c r="I71" s="120">
-        <f>ROUND(G27*F71*G71,0)</f>
-        <v/>
-      </c>
-      <c r="J71" s="120">
-        <f>ROUND(H27*F71,0)</f>
-        <v/>
-      </c>
-      <c r="K71" s="120">
-        <f>ROUND(I27*F71,0)</f>
-        <v/>
-      </c>
-      <c r="L71" s="121">
-        <f>H71+I71+J71+K71</f>
-        <v/>
+      <c r="F71" s="122" t="n">
+        <v>0.627754</v>
+      </c>
+      <c r="G71" s="118" t="n">
+        <v>1481.9</v>
+      </c>
+      <c r="H71" s="120" t="n">
+        <v>53629961</v>
+      </c>
+      <c r="I71" s="120" t="n">
+        <v>18605</v>
+      </c>
+      <c r="J71" s="120" t="n">
+        <v>7847</v>
+      </c>
+      <c r="K71" s="120" t="n">
+        <v>5022</v>
+      </c>
+      <c r="L71" s="121" t="n">
+        <v>53661435</v>
       </c>
       <c r="M71" s="115" t="n"/>
     </row>
@@ -16252,33 +15885,26 @@
       <c r="E72" s="118" t="n">
         <v>57650</v>
       </c>
-      <c r="F72" s="122">
-        <f>D72/E72</f>
-        <v/>
-      </c>
-      <c r="G72" s="118">
-        <f>F27</f>
-        <v/>
-      </c>
-      <c r="H72" s="120">
-        <f>ROUND(D72*G72,0)</f>
-        <v/>
-      </c>
-      <c r="I72" s="120">
-        <f>ROUND(G27*F72*G72,0)</f>
-        <v/>
-      </c>
-      <c r="J72" s="120">
-        <f>ROUND(H27*F72,0)</f>
-        <v/>
-      </c>
-      <c r="K72" s="120">
-        <f>ROUND(I27*F72,0)</f>
-        <v/>
-      </c>
-      <c r="L72" s="121">
-        <f>H72+I72+J72+K72</f>
-        <v/>
+      <c r="F72" s="122" t="n">
+        <v>0.003122</v>
+      </c>
+      <c r="G72" s="118" t="n">
+        <v>1481.9</v>
+      </c>
+      <c r="H72" s="120" t="n">
+        <v>266742</v>
+      </c>
+      <c r="I72" s="120" t="n">
+        <v>93</v>
+      </c>
+      <c r="J72" s="120" t="n">
+        <v>39</v>
+      </c>
+      <c r="K72" s="120" t="n">
+        <v>25</v>
+      </c>
+      <c r="L72" s="121" t="n">
+        <v>266899</v>
       </c>
       <c r="M72" s="115" t="n"/>
     </row>
@@ -16304,33 +15930,26 @@
       <c r="E73" s="118" t="n">
         <v>57650</v>
       </c>
-      <c r="F73" s="122">
-        <f>D73/E73</f>
-        <v/>
-      </c>
-      <c r="G73" s="118">
-        <f>F27</f>
-        <v/>
-      </c>
-      <c r="H73" s="120">
-        <f>ROUND(D73*G73,0)</f>
-        <v/>
-      </c>
-      <c r="I73" s="120">
-        <f>ROUND(G27*F73*G73,0)</f>
-        <v/>
-      </c>
-      <c r="J73" s="120">
-        <f>ROUND(H27*F73,0)</f>
-        <v/>
-      </c>
-      <c r="K73" s="120">
-        <f>ROUND(I27*F73,0)</f>
-        <v/>
-      </c>
-      <c r="L73" s="121">
-        <f>H73+I73+J73+K73</f>
-        <v/>
+      <c r="F73" s="122" t="n">
+        <v>0.369124</v>
+      </c>
+      <c r="G73" s="118" t="n">
+        <v>1481.9</v>
+      </c>
+      <c r="H73" s="120" t="n">
+        <v>31534832</v>
+      </c>
+      <c r="I73" s="120" t="n">
+        <v>10940</v>
+      </c>
+      <c r="J73" s="120" t="n">
+        <v>4614</v>
+      </c>
+      <c r="K73" s="120" t="n">
+        <v>2953</v>
+      </c>
+      <c r="L73" s="121" t="n">
+        <v>31553339</v>
       </c>
       <c r="M73" s="115" t="n"/>
     </row>
@@ -16356,33 +15975,26 @@
       <c r="E74" s="118" t="n">
         <v>297580</v>
       </c>
-      <c r="F74" s="122">
-        <f>D74/E74</f>
-        <v/>
-      </c>
-      <c r="G74" s="118">
-        <f>F31</f>
-        <v/>
-      </c>
-      <c r="H74" s="120">
-        <f>ROUND(D74*G74,0)</f>
-        <v/>
-      </c>
-      <c r="I74" s="120">
-        <f>ROUND(G31*F74*G74,0)</f>
-        <v/>
-      </c>
-      <c r="J74" s="120">
-        <f>ROUND(H31*F74,0)</f>
-        <v/>
-      </c>
-      <c r="K74" s="120">
-        <f>ROUND(I31*F74,0)</f>
-        <v/>
-      </c>
-      <c r="L74" s="121">
-        <f>H74+I74+J74+K74</f>
-        <v/>
+      <c r="F74" s="122" t="n">
+        <v>0.036965</v>
+      </c>
+      <c r="G74" s="118" t="n">
+        <v>1482.8</v>
+      </c>
+      <c r="H74" s="120" t="n">
+        <v>16310800</v>
+      </c>
+      <c r="I74" s="120" t="n">
+        <v>1096</v>
+      </c>
+      <c r="J74" s="120" t="n">
+        <v>462</v>
+      </c>
+      <c r="K74" s="120" t="n">
+        <v>296</v>
+      </c>
+      <c r="L74" s="121" t="n">
+        <v>16312654</v>
       </c>
       <c r="M74" s="115" t="n"/>
     </row>
@@ -16408,33 +16020,26 @@
       <c r="E75" s="118" t="n">
         <v>297580</v>
       </c>
-      <c r="F75" s="122">
-        <f>D75/E75</f>
-        <v/>
-      </c>
-      <c r="G75" s="118">
-        <f>F31</f>
-        <v/>
-      </c>
-      <c r="H75" s="120">
-        <f>ROUND(D75*G75,0)</f>
-        <v/>
-      </c>
-      <c r="I75" s="120">
-        <f>ROUND(G31*F75*G75,0)</f>
-        <v/>
-      </c>
-      <c r="J75" s="120">
-        <f>ROUND(H31*F75,0)</f>
-        <v/>
-      </c>
-      <c r="K75" s="120">
-        <f>ROUND(I31*F75,0)</f>
-        <v/>
-      </c>
-      <c r="L75" s="121">
-        <f>H75+I75+J75+K75</f>
-        <v/>
+      <c r="F75" s="122" t="n">
+        <v>0.963035</v>
+      </c>
+      <c r="G75" s="118" t="n">
+        <v>1482.8</v>
+      </c>
+      <c r="H75" s="120" t="n">
+        <v>424940824</v>
+      </c>
+      <c r="I75" s="120" t="n">
+        <v>28560</v>
+      </c>
+      <c r="J75" s="120" t="n">
+        <v>12038</v>
+      </c>
+      <c r="K75" s="120" t="n">
+        <v>7704</v>
+      </c>
+      <c r="L75" s="121" t="n">
+        <v>424989126</v>
       </c>
       <c r="M75" s="115" t="n"/>
     </row>
@@ -16460,33 +16065,26 @@
       <c r="E76" s="118" t="n">
         <v>4388.4</v>
       </c>
-      <c r="F76" s="122">
-        <f>D76/E76</f>
-        <v/>
-      </c>
-      <c r="G76" s="118">
-        <f>F32</f>
-        <v/>
-      </c>
-      <c r="H76" s="120">
-        <f>ROUND(D76*G76,0)</f>
-        <v/>
-      </c>
-      <c r="I76" s="120">
-        <f>ROUND(G32*F76*G76,0)</f>
-        <v/>
-      </c>
-      <c r="J76" s="120">
-        <f>ROUND(H32*F76,0)</f>
-        <v/>
-      </c>
-      <c r="K76" s="120">
-        <f>ROUND(I32*F76,0)</f>
-        <v/>
-      </c>
-      <c r="L76" s="121">
-        <f>H76+I76+J76+K76</f>
-        <v/>
+      <c r="F76" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="118" t="n">
+        <v>1741.08</v>
+      </c>
+      <c r="H76" s="120" t="n">
+        <v>7640555</v>
+      </c>
+      <c r="I76" s="120" t="n">
+        <v>43527</v>
+      </c>
+      <c r="J76" s="120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K76" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L76" s="121" t="n">
+        <v>7702082</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
@@ -16511,33 +16109,26 @@
       <c r="E77" s="118" t="n">
         <v>21439</v>
       </c>
-      <c r="F77" s="122">
-        <f>D77/E77</f>
-        <v/>
-      </c>
-      <c r="G77" s="118">
-        <f>F33</f>
-        <v/>
-      </c>
-      <c r="H77" s="120">
-        <f>ROUND(D77*G77,0)</f>
-        <v/>
-      </c>
-      <c r="I77" s="120">
-        <f>ROUND(G33*F77*G77,0)</f>
-        <v/>
-      </c>
-      <c r="J77" s="120">
-        <f>ROUND(H33*F77,0)</f>
-        <v/>
-      </c>
-      <c r="K77" s="120">
-        <f>ROUND(I33*F77,0)</f>
-        <v/>
-      </c>
-      <c r="L77" s="121">
-        <f>H77+I77+J77+K77</f>
-        <v/>
+      <c r="F77" s="122" t="n">
+        <v>0.811792</v>
+      </c>
+      <c r="G77" s="118" t="n">
+        <v>1474.9</v>
+      </c>
+      <c r="H77" s="120" t="n">
+        <v>25669160</v>
+      </c>
+      <c r="I77" s="120" t="n">
+        <v>23946</v>
+      </c>
+      <c r="J77" s="120" t="n">
+        <v>10147</v>
+      </c>
+      <c r="K77" s="120" t="n">
+        <v>6494</v>
+      </c>
+      <c r="L77" s="121" t="n">
+        <v>25709747</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
@@ -16562,33 +16153,26 @@
       <c r="E78" s="118" t="n">
         <v>21439</v>
       </c>
-      <c r="F78" s="122">
-        <f>D78/E78</f>
-        <v/>
-      </c>
-      <c r="G78" s="118">
-        <f>F33</f>
-        <v/>
-      </c>
-      <c r="H78" s="120">
-        <f>ROUND(D78*G78,0)</f>
-        <v/>
-      </c>
-      <c r="I78" s="120">
-        <f>ROUND(G33*F78*G78,0)</f>
-        <v/>
-      </c>
-      <c r="J78" s="120">
-        <f>ROUND(H33*F78,0)</f>
-        <v/>
-      </c>
-      <c r="K78" s="120">
-        <f>ROUND(I33*F78,0)</f>
-        <v/>
-      </c>
-      <c r="L78" s="121">
-        <f>H78+I78+J78+K78</f>
-        <v/>
+      <c r="F78" s="122" t="n">
+        <v>0.09599299999999999</v>
+      </c>
+      <c r="G78" s="118" t="n">
+        <v>1474.9</v>
+      </c>
+      <c r="H78" s="120" t="n">
+        <v>3035344</v>
+      </c>
+      <c r="I78" s="120" t="n">
+        <v>2832</v>
+      </c>
+      <c r="J78" s="120" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K78" s="120" t="n">
+        <v>768</v>
+      </c>
+      <c r="L78" s="121" t="n">
+        <v>3040144</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
@@ -16613,33 +16197,26 @@
       <c r="E79" s="118" t="n">
         <v>21439</v>
       </c>
-      <c r="F79" s="122">
-        <f>D79/E79</f>
-        <v/>
-      </c>
-      <c r="G79" s="118">
-        <f>F33</f>
-        <v/>
-      </c>
-      <c r="H79" s="120">
-        <f>ROUND(D79*G79,0)</f>
-        <v/>
-      </c>
-      <c r="I79" s="120">
-        <f>ROUND(G33*F79*G79,0)</f>
-        <v/>
-      </c>
-      <c r="J79" s="120">
-        <f>ROUND(H33*F79,0)</f>
-        <v/>
-      </c>
-      <c r="K79" s="120">
-        <f>ROUND(I33*F79,0)</f>
-        <v/>
-      </c>
-      <c r="L79" s="121">
-        <f>H79+I79+J79+K79</f>
-        <v/>
+      <c r="F79" s="122" t="n">
+        <v>0.09221500000000001</v>
+      </c>
+      <c r="G79" s="118" t="n">
+        <v>1474.9</v>
+      </c>
+      <c r="H79" s="120" t="n">
+        <v>2915877</v>
+      </c>
+      <c r="I79" s="120" t="n">
+        <v>2720</v>
+      </c>
+      <c r="J79" s="120" t="n">
+        <v>1153</v>
+      </c>
+      <c r="K79" s="120" t="n">
+        <v>738</v>
+      </c>
+      <c r="L79" s="121" t="n">
+        <v>2920488</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
@@ -16664,33 +16241,26 @@
       <c r="E80" s="118" t="n">
         <v>6800</v>
       </c>
-      <c r="F80" s="122">
-        <f>D80/E80</f>
-        <v/>
-      </c>
-      <c r="G80" s="118">
-        <f>F34</f>
-        <v/>
-      </c>
-      <c r="H80" s="120">
-        <f>ROUND(D80*G80,0)</f>
-        <v/>
-      </c>
-      <c r="I80" s="120">
-        <f>ROUND(G34*F80*G80,0)</f>
-        <v/>
-      </c>
-      <c r="J80" s="120">
-        <f>ROUND(H34*F80,0)</f>
-        <v/>
-      </c>
-      <c r="K80" s="120">
-        <f>ROUND(I34*F80,0)</f>
-        <v/>
-      </c>
-      <c r="L80" s="121">
-        <f>H80+I80+J80+K80</f>
-        <v/>
+      <c r="F80" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="118" t="n">
+        <v>1475.2</v>
+      </c>
+      <c r="H80" s="120" t="n">
+        <v>10031360</v>
+      </c>
+      <c r="I80" s="120" t="n">
+        <v>29504</v>
+      </c>
+      <c r="J80" s="120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K80" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L80" s="121" t="n">
+        <v>10078864</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
@@ -16715,33 +16285,26 @@
       <c r="E81" s="118" t="n">
         <v>180</v>
       </c>
-      <c r="F81" s="122">
-        <f>D81/E81</f>
-        <v/>
-      </c>
-      <c r="G81" s="118">
-        <f>F36</f>
-        <v/>
-      </c>
-      <c r="H81" s="120">
-        <f>ROUND(D81*G81,0)</f>
-        <v/>
-      </c>
-      <c r="I81" s="120">
-        <f>ROUND(G36*F81*G81,0)</f>
-        <v/>
-      </c>
-      <c r="J81" s="120">
-        <f>ROUND(H36*F81,0)</f>
-        <v/>
-      </c>
-      <c r="K81" s="120">
-        <f>ROUND(I36*F81,0)</f>
-        <v/>
-      </c>
-      <c r="L81" s="121">
-        <f>H81+I81+J81+K81</f>
-        <v/>
+      <c r="F81" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="118" t="n">
+        <v>1518.9</v>
+      </c>
+      <c r="H81" s="120" t="n">
+        <v>273402</v>
+      </c>
+      <c r="I81" s="120" t="n">
+        <v>30378</v>
+      </c>
+      <c r="J81" s="120" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K81" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L81" s="121" t="n">
+        <v>314280</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
@@ -16766,33 +16329,26 @@
       <c r="E82" s="118" t="n">
         <v>4290</v>
       </c>
-      <c r="F82" s="122">
-        <f>D82/E82</f>
-        <v/>
-      </c>
-      <c r="G82" s="118">
-        <f>F37</f>
-        <v/>
-      </c>
-      <c r="H82" s="120">
-        <f>ROUND(D82*G82,0)</f>
-        <v/>
-      </c>
-      <c r="I82" s="120">
-        <f>ROUND(G37*F82*G82,0)</f>
-        <v/>
-      </c>
-      <c r="J82" s="120">
-        <f>ROUND(H37*F82,0)</f>
-        <v/>
-      </c>
-      <c r="K82" s="120">
-        <f>ROUND(I37*F82,0)</f>
-        <v/>
-      </c>
-      <c r="L82" s="121">
-        <f>H82+I82+J82+K82</f>
-        <v/>
+      <c r="F82" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="118" t="n">
+        <v>1510.6</v>
+      </c>
+      <c r="H82" s="120" t="n">
+        <v>6480474</v>
+      </c>
+      <c r="I82" s="120" t="n">
+        <v>30212</v>
+      </c>
+      <c r="J82" s="120" t="n">
+        <v>7500</v>
+      </c>
+      <c r="K82" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L82" s="121" t="n">
+        <v>6526186</v>
       </c>
       <c r="M82" s="40" t="n"/>
     </row>
@@ -16818,33 +16374,26 @@
       <c r="E83" s="118" t="n">
         <v>99140</v>
       </c>
-      <c r="F83" s="122">
-        <f>D83/E83</f>
-        <v/>
-      </c>
-      <c r="G83" s="118">
-        <f>F38</f>
-        <v/>
-      </c>
-      <c r="H83" s="120">
-        <f>ROUND(D83*G83,0)</f>
-        <v/>
-      </c>
-      <c r="I83" s="120">
-        <f>ROUND(G38*F83*G83,0)</f>
-        <v/>
-      </c>
-      <c r="J83" s="120">
-        <f>ROUND(H38*F83,0)</f>
-        <v/>
-      </c>
-      <c r="K83" s="120">
-        <f>ROUND(I38*F83,0)</f>
-        <v/>
-      </c>
-      <c r="L83" s="121">
-        <f>H83+I83+J83+K83</f>
-        <v/>
+      <c r="F83" s="122" t="n">
+        <v>0.996571</v>
+      </c>
+      <c r="G83" s="118" t="n">
+        <v>1502.8</v>
+      </c>
+      <c r="H83" s="120" t="n">
+        <v>148476640</v>
+      </c>
+      <c r="I83" s="120" t="n">
+        <v>29953</v>
+      </c>
+      <c r="J83" s="120" t="n">
+        <v>12457</v>
+      </c>
+      <c r="K83" s="120" t="n">
+        <v>7973</v>
+      </c>
+      <c r="L83" s="121" t="n">
+        <v>148527023</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -16869,33 +16418,26 @@
       <c r="E84" s="118" t="n">
         <v>99140</v>
       </c>
-      <c r="F84" s="122">
-        <f>D84/E84</f>
-        <v/>
-      </c>
-      <c r="G84" s="118">
-        <f>F38</f>
-        <v/>
-      </c>
-      <c r="H84" s="120">
-        <f>ROUND(D84*G84,0)</f>
-        <v/>
-      </c>
-      <c r="I84" s="120">
-        <f>ROUND(G38*F84*G84,0)</f>
-        <v/>
-      </c>
-      <c r="J84" s="120">
-        <f>ROUND(H38*F84,0)</f>
-        <v/>
-      </c>
-      <c r="K84" s="120">
-        <f>ROUND(I38*F84,0)</f>
-        <v/>
-      </c>
-      <c r="L84" s="121">
-        <f>H84+I84+J84+K84</f>
-        <v/>
+      <c r="F84" s="122" t="n">
+        <v>0.002522</v>
+      </c>
+      <c r="G84" s="118" t="n">
+        <v>1502.8</v>
+      </c>
+      <c r="H84" s="120" t="n">
+        <v>375700</v>
+      </c>
+      <c r="I84" s="120" t="n">
+        <v>76</v>
+      </c>
+      <c r="J84" s="120" t="n">
+        <v>32</v>
+      </c>
+      <c r="K84" s="120" t="n">
+        <v>20</v>
+      </c>
+      <c r="L84" s="121" t="n">
+        <v>375828</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
@@ -16920,33 +16462,26 @@
       <c r="E85" s="118" t="n">
         <v>99140</v>
       </c>
-      <c r="F85" s="122">
-        <f>D85/E85</f>
-        <v/>
-      </c>
-      <c r="G85" s="118">
-        <f>F38</f>
-        <v/>
-      </c>
-      <c r="H85" s="120">
-        <f>ROUND(D85*G85,0)</f>
-        <v/>
-      </c>
-      <c r="I85" s="120">
-        <f>ROUND(G38*F85*G85,0)</f>
-        <v/>
-      </c>
-      <c r="J85" s="120">
-        <f>ROUND(H38*F85,0)</f>
-        <v/>
-      </c>
-      <c r="K85" s="120">
-        <f>ROUND(I38*F85,0)</f>
-        <v/>
-      </c>
-      <c r="L85" s="121">
-        <f>H85+I85+J85+K85</f>
-        <v/>
+      <c r="F85" s="122" t="n">
+        <v>0.000908</v>
+      </c>
+      <c r="G85" s="118" t="n">
+        <v>1502.8</v>
+      </c>
+      <c r="H85" s="120" t="n">
+        <v>135252</v>
+      </c>
+      <c r="I85" s="120" t="n">
+        <v>27</v>
+      </c>
+      <c r="J85" s="120" t="n">
+        <v>11</v>
+      </c>
+      <c r="K85" s="120" t="n">
+        <v>7</v>
+      </c>
+      <c r="L85" s="121" t="n">
+        <v>135297</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
@@ -16971,33 +16506,26 @@
       <c r="E86" s="118" t="n">
         <v>101638</v>
       </c>
-      <c r="F86" s="122">
-        <f>D86/E86</f>
-        <v/>
-      </c>
-      <c r="G86" s="118">
-        <f>F39</f>
-        <v/>
-      </c>
-      <c r="H86" s="120">
-        <f>ROUND(D86*G86,0)</f>
-        <v/>
-      </c>
-      <c r="I86" s="120">
-        <f>ROUND(G39*F86*G86,0)</f>
-        <v/>
-      </c>
-      <c r="J86" s="120">
-        <f>ROUND(H39*F86,0)</f>
-        <v/>
-      </c>
-      <c r="K86" s="120">
-        <f>ROUND(I39*F86,0)</f>
-        <v/>
-      </c>
-      <c r="L86" s="121">
-        <f>H86+I86+J86+K86</f>
-        <v/>
+      <c r="F86" s="122" t="n">
+        <v>0.150426</v>
+      </c>
+      <c r="G86" s="118" t="n">
+        <v>1502.7</v>
+      </c>
+      <c r="H86" s="120" t="n">
+        <v>22974780</v>
+      </c>
+      <c r="I86" s="120" t="n">
+        <v>4521</v>
+      </c>
+      <c r="J86" s="120" t="n">
+        <v>1880</v>
+      </c>
+      <c r="K86" s="120" t="n">
+        <v>1203</v>
+      </c>
+      <c r="L86" s="121" t="n">
+        <v>22982384</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
@@ -17022,33 +16550,26 @@
       <c r="E87" s="118" t="n">
         <v>101638</v>
       </c>
-      <c r="F87" s="122">
-        <f>D87/E87</f>
-        <v/>
-      </c>
-      <c r="G87" s="118">
-        <f>F39</f>
-        <v/>
-      </c>
-      <c r="H87" s="120">
-        <f>ROUND(D87*G87,0)</f>
-        <v/>
-      </c>
-      <c r="I87" s="120">
-        <f>ROUND(G39*F87*G87,0)</f>
-        <v/>
-      </c>
-      <c r="J87" s="120">
-        <f>ROUND(H39*F87,0)</f>
-        <v/>
-      </c>
-      <c r="K87" s="120">
-        <f>ROUND(I39*F87,0)</f>
-        <v/>
-      </c>
-      <c r="L87" s="121">
-        <f>H87+I87+J87+K87</f>
-        <v/>
+      <c r="F87" s="122" t="n">
+        <v>0.769486</v>
+      </c>
+      <c r="G87" s="118" t="n">
+        <v>1502.7</v>
+      </c>
+      <c r="H87" s="120" t="n">
+        <v>117524664</v>
+      </c>
+      <c r="I87" s="120" t="n">
+        <v>23126</v>
+      </c>
+      <c r="J87" s="120" t="n">
+        <v>9619</v>
+      </c>
+      <c r="K87" s="120" t="n">
+        <v>6156</v>
+      </c>
+      <c r="L87" s="121" t="n">
+        <v>117563565</v>
       </c>
     </row>
     <row r="88">
@@ -17073,33 +16594,26 @@
       <c r="E88" s="118" t="n">
         <v>101638</v>
       </c>
-      <c r="F88" s="122">
-        <f>D88/E88</f>
-        <v/>
-      </c>
-      <c r="G88" s="118">
-        <f>F39</f>
-        <v/>
-      </c>
-      <c r="H88" s="120">
-        <f>ROUND(D88*G88,0)</f>
-        <v/>
-      </c>
-      <c r="I88" s="120">
-        <f>ROUND(G39*F88*G88,0)</f>
-        <v/>
-      </c>
-      <c r="J88" s="120">
-        <f>ROUND(H39*F88,0)</f>
-        <v/>
-      </c>
-      <c r="K88" s="120">
-        <f>ROUND(I39*F88,0)</f>
-        <v/>
-      </c>
-      <c r="L88" s="121">
-        <f>H88+I88+J88+K88</f>
-        <v/>
+      <c r="F88" s="122" t="n">
+        <v>0.08008800000000001</v>
+      </c>
+      <c r="G88" s="118" t="n">
+        <v>1502.7</v>
+      </c>
+      <c r="H88" s="120" t="n">
+        <v>12231978</v>
+      </c>
+      <c r="I88" s="120" t="n">
+        <v>2407</v>
+      </c>
+      <c r="J88" s="120" t="n">
+        <v>1001</v>
+      </c>
+      <c r="K88" s="120" t="n">
+        <v>641</v>
+      </c>
+      <c r="L88" s="121" t="n">
+        <v>12236027</v>
       </c>
     </row>
     <row r="89">
@@ -17124,33 +16638,26 @@
       <c r="E89" s="236" t="n">
         <v>119060</v>
       </c>
-      <c r="F89" s="240">
-        <f>D89/E89</f>
-        <v/>
-      </c>
-      <c r="G89" s="236">
-        <f>F40</f>
-        <v/>
-      </c>
-      <c r="H89" s="238">
-        <f>ROUND(D89*G89,0)</f>
-        <v/>
-      </c>
-      <c r="I89" s="238">
-        <f>ROUND(G40*F89*G89,0)</f>
-        <v/>
-      </c>
-      <c r="J89" s="238">
-        <f>ROUND(H40*F89,0)</f>
-        <v/>
-      </c>
-      <c r="K89" s="238">
-        <f>ROUND(I40*F89,0)</f>
-        <v/>
-      </c>
-      <c r="L89" s="239">
-        <f>H89+I89+J89+K89</f>
-        <v/>
+      <c r="F89" s="240" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="G89" s="236" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="H89" s="238" t="n">
+        <v>762650</v>
+      </c>
+      <c r="I89" s="238" t="n">
+        <v>128</v>
+      </c>
+      <c r="J89" s="238" t="n">
+        <v>52</v>
+      </c>
+      <c r="K89" s="238" t="n">
+        <v>34</v>
+      </c>
+      <c r="L89" s="239" t="n">
+        <v>762864</v>
       </c>
     </row>
     <row r="90">
@@ -17175,33 +16682,26 @@
       <c r="E90" s="236" t="n">
         <v>119060</v>
       </c>
-      <c r="F90" s="240">
-        <f>D90/E90</f>
-        <v/>
-      </c>
-      <c r="G90" s="236">
-        <f>F40</f>
-        <v/>
-      </c>
-      <c r="H90" s="238">
-        <f>ROUND(D90*G90,0)</f>
-        <v/>
-      </c>
-      <c r="I90" s="238">
-        <f>ROUND(G40*F90*G90,0)</f>
-        <v/>
-      </c>
-      <c r="J90" s="238">
-        <f>ROUND(H40*F90,0)</f>
-        <v/>
-      </c>
-      <c r="K90" s="238">
-        <f>ROUND(I40*F90,0)</f>
-        <v/>
-      </c>
-      <c r="L90" s="239">
-        <f>H90+I90+J90+K90</f>
-        <v/>
+      <c r="F90" s="240" t="n">
+        <v>0.580884</v>
+      </c>
+      <c r="G90" s="236" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="H90" s="238" t="n">
+        <v>105489748</v>
+      </c>
+      <c r="I90" s="238" t="n">
+        <v>17720</v>
+      </c>
+      <c r="J90" s="238" t="n">
+        <v>7261</v>
+      </c>
+      <c r="K90" s="238" t="n">
+        <v>4647</v>
+      </c>
+      <c r="L90" s="239" t="n">
+        <v>105519376</v>
       </c>
     </row>
     <row r="91">
@@ -17226,33 +16726,26 @@
       <c r="E91" s="236" t="n">
         <v>119060</v>
       </c>
-      <c r="F91" s="240">
-        <f>D91/E91</f>
-        <v/>
-      </c>
-      <c r="G91" s="236">
-        <f>F40</f>
-        <v/>
-      </c>
-      <c r="H91" s="238">
-        <f>ROUND(D91*G91,0)</f>
-        <v/>
-      </c>
-      <c r="I91" s="238">
-        <f>ROUND(G40*F91*G91,0)</f>
-        <v/>
-      </c>
-      <c r="J91" s="238">
-        <f>ROUND(H40*F91,0)</f>
-        <v/>
-      </c>
-      <c r="K91" s="238">
-        <f>ROUND(I40*F91,0)</f>
-        <v/>
-      </c>
-      <c r="L91" s="239">
-        <f>H91+I91+J91+K91</f>
-        <v/>
+      <c r="F91" s="240" t="n">
+        <v>0.414917</v>
+      </c>
+      <c r="G91" s="236" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="H91" s="238" t="n">
+        <v>75349820</v>
+      </c>
+      <c r="I91" s="238" t="n">
+        <v>12657</v>
+      </c>
+      <c r="J91" s="238" t="n">
+        <v>5186</v>
+      </c>
+      <c r="K91" s="238" t="n">
+        <v>3319</v>
+      </c>
+      <c r="L91" s="239" t="n">
+        <v>75370982</v>
       </c>
     </row>
   </sheetData>
@@ -17317,7 +16810,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="163" t="inlineStr">
         <is>
-          <t>기준일: 2026-06-10  |  상환 완료 건은 초록색 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
+          <t>기준일: 2026-06-16  |  상환 완료 건은 초록색 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
         </is>
       </c>
     </row>
@@ -17604,64 +17097,76 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="59" t="n">
+      <c r="A16" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="276" t="inlineStr">
         <is>
           <t>CPO-672</t>
         </is>
       </c>
-      <c r="C16" s="74" t="inlineStr">
+      <c r="C16" s="277" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D16" s="60" t="n">
+      <c r="D16" s="278" t="n">
         <v>221868</v>
       </c>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="E16" s="276" t="inlineStr">
         <is>
           <t>신한은행</t>
         </is>
       </c>
-      <c r="F16" s="59" t="inlineStr">
+      <c r="F16" s="276" t="inlineStr">
         <is>
           <t>M88JX2510NU00018</t>
         </is>
       </c>
-      <c r="G16" s="59" t="inlineStr">
+      <c r="G16" s="276" t="inlineStr">
         <is>
           <t>2025-10-16</t>
         </is>
       </c>
-      <c r="H16" s="59" t="inlineStr">
+      <c r="H16" s="276" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="I16" s="59" t="inlineStr">
+      <c r="I16" s="276" t="inlineStr">
         <is>
           <t>180 Days</t>
         </is>
       </c>
-      <c r="J16" s="59" t="inlineStr">
+      <c r="J16" s="276" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="K16" s="59" t="inlineStr">
+      <c r="K16" s="276" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="L16" s="200" t="n">
-        <v>67</v>
-      </c>
-      <c r="M16" s="59" t="n"/>
-      <c r="N16" s="201" t="n"/>
-      <c r="O16" s="63" t="n"/>
-      <c r="P16" s="59" t="n"/>
+      <c r="L16" s="279" t="inlineStr">
+        <is>
+          <t>상환완료</t>
+        </is>
+      </c>
+      <c r="M16" s="280" t="n">
+        <v>46189</v>
+      </c>
+      <c r="N16" s="278" t="n">
+        <v>1517.2</v>
+      </c>
+      <c r="O16" s="281" t="n">
+        <v>336629315</v>
+      </c>
+      <c r="P16" s="276" t="inlineStr">
+        <is>
+          <t>6/16 만기 상환 완료 (외국환 거래표 2026-06-16, REF M88JX2510NU00018). 원금 USD 221,868.99 → 원화 336,629,315 (적용환율 1,517.20). 미결제잔액 USD 0.00</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="245" t="n">
@@ -19602,7 +19107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -19645,7 +19150,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="205" t="inlineStr">
         <is>
-          <t>업데이트: 2026-06-02 (관세청 고시환율)</t>
+          <t>업데이트: 2026-06-16 (관세청 고시환율)</t>
         </is>
       </c>
       <c r="B4" s="148" t="n"/>
@@ -20249,6 +19754,22 @@
       </c>
       <c r="D42" s="211" t="n">
         <v>1514.68</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="282" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B43" s="282" t="n">
+        <v>46193</v>
+      </c>
+      <c r="C43" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D43" s="211" t="n">
+        <v>1531.46</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -17157,14 +17157,14 @@
         <v>46189</v>
       </c>
       <c r="N16" s="278" t="n">
-        <v>1517.2</v>
+        <v>1517.25</v>
       </c>
       <c r="O16" s="281" t="n">
         <v>336629315</v>
       </c>
       <c r="P16" s="276" t="inlineStr">
         <is>
-          <t>6/16 만기 상환 완료 (외국환 거래표 2026-06-16, REF M88JX2510NU00018). 원금 USD 221,868.99 → 원화 336,629,315 (적용환율 1,517.20). 미결제잔액 USD 0.00</t>
+          <t>6/16 만기 상환 완료 (외국환 거래표 2026-06-16, REF M88JX2510NU00018). 원금 USD 221,868.00 → 원화 336,629,315 (적용환율 1,517.25, 은행 실제 출금액). 미결제잔액 USD 0.00, 하단 정산 명세 참조</t>
         </is>
       </c>
     </row>
@@ -18128,25 +18128,536 @@
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="50" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="51" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="52" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="53" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="54" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="55" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="56" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="57" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="58" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="59" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="60" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="61" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="62" ht="15.75" customFormat="1" customHeight="1" s="160"/>
-    <row r="63" ht="15.75" customFormat="1" customHeight="1" s="160"/>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="252" t="inlineStr">
+        <is>
+          <t>&lt; CPO-672 상환 정산 및 수수료 명세 (신한은행, 출처: 은행 수수료/인도 내역서 2026-06-16) &gt;</t>
+        </is>
+      </c>
+      <c r="B45" s="65" t="n"/>
+      <c r="C45" s="66" t="n"/>
+      <c r="D45" s="65" t="n"/>
+      <c r="E45" s="65" t="n"/>
+      <c r="F45" s="65" t="n"/>
+      <c r="G45" s="65" t="n"/>
+      <c r="H45" s="65" t="n"/>
+      <c r="I45" s="65" t="n"/>
+      <c r="J45" s="65" t="n"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="253" t="inlineStr">
+        <is>
+          <t>상환일</t>
+        </is>
+      </c>
+      <c r="B46" s="253" t="inlineStr">
+        <is>
+          <t>상환원금(USD)</t>
+        </is>
+      </c>
+      <c r="C46" s="253" t="inlineStr">
+        <is>
+          <t>상환환율(₩)</t>
+        </is>
+      </c>
+      <c r="D46" s="253" t="inlineStr">
+        <is>
+          <t>상환금액(KRW)</t>
+        </is>
+      </c>
+      <c r="E46" s="253" t="inlineStr">
+        <is>
+          <t>L/C No.</t>
+        </is>
+      </c>
+      <c r="F46" s="253" t="inlineStr">
+        <is>
+          <t>회계처리(권장)</t>
+        </is>
+      </c>
+      <c r="G46" s="65" t="n"/>
+      <c r="H46" s="65" t="n"/>
+      <c r="I46" s="65" t="n"/>
+      <c r="J46" s="65" t="n"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="254" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B47" s="255" t="n">
+        <v>221868</v>
+      </c>
+      <c r="C47" s="255" t="n">
+        <v>1517.25</v>
+      </c>
+      <c r="D47" s="264" t="n">
+        <v>336629315</v>
+      </c>
+      <c r="E47" s="257" t="inlineStr">
+        <is>
+          <t>M88JX2510NU00018</t>
+        </is>
+      </c>
+      <c r="F47" s="258" t="inlineStr">
+        <is>
+          <t>차변 외화매입채무(USANCE) 221,868 USD 제거 + 외환차손익, 대변 보통예금 336,629,315</t>
+        </is>
+      </c>
+      <c r="G47" s="71" t="n"/>
+      <c r="H47" s="65" t="n"/>
+      <c r="I47" s="65" t="n"/>
+      <c r="J47" s="65" t="n"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="65" t="n"/>
+      <c r="B48" s="65" t="n"/>
+      <c r="C48" s="66" t="n"/>
+      <c r="D48" s="65" t="n"/>
+      <c r="E48" s="65" t="n"/>
+      <c r="F48" s="70" t="n"/>
+      <c r="G48" s="71" t="n"/>
+      <c r="H48" s="65" t="n"/>
+      <c r="I48" s="65" t="n"/>
+      <c r="J48" s="65" t="n"/>
+    </row>
+    <row r="49" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A49" s="253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B49" s="253" t="inlineStr">
+        <is>
+          <t>징수일</t>
+        </is>
+      </c>
+      <c r="C49" s="253" t="inlineStr">
+        <is>
+          <t>수수료 구분</t>
+        </is>
+      </c>
+      <c r="D49" s="253" t="inlineStr">
+        <is>
+          <t>이율(%)</t>
+        </is>
+      </c>
+      <c r="E49" s="253" t="inlineStr">
+        <is>
+          <t>수수료 기간</t>
+        </is>
+      </c>
+      <c r="F49" s="259" t="inlineStr">
+        <is>
+          <t>일수</t>
+        </is>
+      </c>
+      <c r="G49" s="260" t="inlineStr">
+        <is>
+          <t>대상금액(USD)</t>
+        </is>
+      </c>
+      <c r="H49" s="253" t="inlineStr">
+        <is>
+          <t>USD 상당액</t>
+        </is>
+      </c>
+      <c r="I49" s="253" t="inlineStr">
+        <is>
+          <t>징수액(KRW)</t>
+        </is>
+      </c>
+      <c r="J49" s="253" t="inlineStr">
+        <is>
+          <t>회계처리(권장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A50" s="257" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="254" t="n">
+        <v>45946</v>
+      </c>
+      <c r="C50" s="261" t="inlineStr">
+        <is>
+          <t>수입신용장 기간수수료(발행수수료, 360일 단위)</t>
+        </is>
+      </c>
+      <c r="D50" s="262" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E50" s="257" t="inlineStr">
+        <is>
+          <t>2025-10-16 ~ 2025-12-19</t>
+        </is>
+      </c>
+      <c r="F50" s="263" t="n">
+        <v>65</v>
+      </c>
+      <c r="G50" s="255" t="n">
+        <v>221868</v>
+      </c>
+      <c r="H50" s="255" t="n">
+        <v>320.46</v>
+      </c>
+      <c r="I50" s="264" t="n">
+        <v>454691</v>
+      </c>
+      <c r="J50" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A51" s="257" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" s="254" t="n">
+        <v>45946</v>
+      </c>
+      <c r="C51" s="261" t="inlineStr">
+        <is>
+          <t>전신료(일반신용장 USANCE)</t>
+        </is>
+      </c>
+      <c r="D51" s="262" t="n"/>
+      <c r="E51" s="257" t="inlineStr"/>
+      <c r="F51" s="263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="255" t="n"/>
+      <c r="H51" s="255" t="n"/>
+      <c r="I51" s="264" t="n">
+        <v>13750</v>
+      </c>
+      <c r="J51" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A52" s="257" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" s="254" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C52" s="261" t="inlineStr">
+        <is>
+          <t>수입화물선취보증서(L/G) 발급수수료</t>
+        </is>
+      </c>
+      <c r="D52" s="262" t="n"/>
+      <c r="E52" s="257" t="inlineStr"/>
+      <c r="F52" s="263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="255" t="n"/>
+      <c r="H52" s="255" t="n"/>
+      <c r="I52" s="264" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J52" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A53" s="257" t="n">
+        <v>4</v>
+      </c>
+      <c r="B53" s="254" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C53" s="261" t="inlineStr">
+        <is>
+          <t>수입화물선취보증료(외화)</t>
+        </is>
+      </c>
+      <c r="D53" s="262" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="257" t="inlineStr">
+        <is>
+          <t>2025-10-31 ~ 2025-12-15</t>
+        </is>
+      </c>
+      <c r="F53" s="263" t="n">
+        <v>46</v>
+      </c>
+      <c r="G53" s="255" t="n">
+        <v>221868</v>
+      </c>
+      <c r="H53" s="255" t="n">
+        <v>850.55</v>
+      </c>
+      <c r="I53" s="264" t="n">
+        <v>1255244</v>
+      </c>
+      <c r="J53" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A54" s="257" t="n">
+        <v>5</v>
+      </c>
+      <c r="B54" s="254" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C54" s="261" t="inlineStr">
+        <is>
+          <t>수입인수수수료(360일 단위)</t>
+        </is>
+      </c>
+      <c r="D54" s="262" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E54" s="257" t="inlineStr">
+        <is>
+          <t>2025-12-16 ~ 2026-06-14</t>
+        </is>
+      </c>
+      <c r="F54" s="263" t="n">
+        <v>181</v>
+      </c>
+      <c r="G54" s="255" t="n">
+        <v>221868</v>
+      </c>
+      <c r="H54" s="255" t="n">
+        <v>1338.62</v>
+      </c>
+      <c r="I54" s="264" t="n">
+        <v>1975645</v>
+      </c>
+      <c r="J54" s="257" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A55" s="257" t="n">
+        <v>6</v>
+      </c>
+      <c r="B55" s="254" t="n">
+        <v>46007</v>
+      </c>
+      <c r="C55" s="261" t="inlineStr">
+        <is>
+          <t>수입기간수수료 환급(-)</t>
+        </is>
+      </c>
+      <c r="D55" s="262" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E55" s="257" t="inlineStr">
+        <is>
+          <t>2025-12-16 ~ 2025-12-19</t>
+        </is>
+      </c>
+      <c r="F55" s="263" t="n">
+        <v>4</v>
+      </c>
+      <c r="G55" s="255" t="n">
+        <v>221868</v>
+      </c>
+      <c r="H55" s="255" t="n">
+        <v>-19.72</v>
+      </c>
+      <c r="I55" s="264" t="n">
+        <v>-27981</v>
+      </c>
+      <c r="J55" s="257" t="inlineStr">
+        <is>
+          <t>지급수수료 차감</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A56" s="257" t="n">
+        <v>7</v>
+      </c>
+      <c r="B56" s="254" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C56" s="261" t="inlineStr">
+        <is>
+          <t>수입인수수수료(만기연장 1일분)</t>
+        </is>
+      </c>
+      <c r="D56" s="262" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E56" s="257" t="inlineStr">
+        <is>
+          <t>2026-06-15 ~ 2026-06-15</t>
+        </is>
+      </c>
+      <c r="F56" s="263" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="255" t="n">
+        <v>221868</v>
+      </c>
+      <c r="H56" s="255" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I56" s="264" t="n">
+        <v>11186</v>
+      </c>
+      <c r="J56" s="257" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A57" s="257" t="n">
+        <v>8</v>
+      </c>
+      <c r="B57" s="254" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C57" s="261" t="inlineStr">
+        <is>
+          <t>해외수수료(해외은행 인수금융 이자)</t>
+        </is>
+      </c>
+      <c r="D57" s="262" t="n"/>
+      <c r="E57" s="257" t="inlineStr">
+        <is>
+          <t>2025-12-19 인도 ~ 2026-06-16</t>
+        </is>
+      </c>
+      <c r="F57" s="263" t="n">
+        <v>180</v>
+      </c>
+      <c r="G57" s="255" t="n">
+        <v>221868</v>
+      </c>
+      <c r="H57" s="255" t="n">
+        <v>6124.77</v>
+      </c>
+      <c r="I57" s="264" t="n">
+        <v>9292540</v>
+      </c>
+      <c r="J57" s="257" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A58" s="253" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B58" s="265" t="n"/>
+      <c r="C58" s="266" t="n"/>
+      <c r="D58" s="265" t="n"/>
+      <c r="E58" s="265" t="n"/>
+      <c r="F58" s="265" t="n"/>
+      <c r="G58" s="268" t="n"/>
+      <c r="H58" s="269" t="n">
+        <v>8622.08</v>
+      </c>
+      <c r="I58" s="270" t="n">
+        <v>12980075</v>
+      </c>
+      <c r="J58" s="253" t="inlineStr">
+        <is>
+          <t>이자비용 11,279,371 + 지급수수료 1,700,704</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A59" s="274" t="inlineStr">
+        <is>
+          <t>주1: USD 상당액 = 대상금액 x 이율 x 일수/360 (전신료, L/G 발급료는 KRW 정액)</t>
+        </is>
+      </c>
+      <c r="B59" s="65" t="n"/>
+      <c r="C59" s="66" t="n"/>
+      <c r="D59" s="65" t="n"/>
+      <c r="E59" s="65" t="n"/>
+      <c r="F59" s="65" t="n"/>
+      <c r="G59" s="71" t="n"/>
+      <c r="H59" s="65" t="n"/>
+      <c r="I59" s="65" t="n"/>
+      <c r="J59" s="65" t="n"/>
+    </row>
+    <row r="60" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A60" s="274" t="inlineStr">
+        <is>
+          <t>주2: No.1~6 수수료는 징수일에 KRW 기징수, No.7(만기연장)·해외수수료는 상환일(6/16) 출금. 회계처리는 각 징수일자 전표로 계상</t>
+        </is>
+      </c>
+      <c r="B60" s="65" t="n"/>
+      <c r="C60" s="66" t="n"/>
+      <c r="D60" s="65" t="n"/>
+      <c r="E60" s="65" t="n"/>
+      <c r="F60" s="65" t="n"/>
+      <c r="G60" s="71" t="n"/>
+      <c r="H60" s="65" t="n"/>
+      <c r="I60" s="65" t="n"/>
+      <c r="J60" s="65" t="n"/>
+    </row>
+    <row r="61" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A61" s="274" t="inlineStr">
+        <is>
+          <t>주3: 원금 상환 (외국환 거래표 2026-06-16, REF M88JX2510NU00018): 원금 USD 221,868.00 x 적용환율 1,517.25 = 원화 336,629,315 (은행 실제 출금액)</t>
+        </is>
+      </c>
+      <c r="B61" s="65" t="n"/>
+      <c r="C61" s="66" t="n"/>
+      <c r="D61" s="65" t="n"/>
+      <c r="E61" s="65" t="n"/>
+      <c r="F61" s="65" t="n"/>
+      <c r="G61" s="71" t="n"/>
+      <c r="H61" s="65" t="n"/>
+      <c r="I61" s="65" t="n"/>
+      <c r="J61" s="65" t="n"/>
+    </row>
+    <row r="62" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A62" s="274" t="inlineStr">
+        <is>
+          <t>주4: 6/16 실제 출금 합계 345,933,041원 = 원금 336,629,315 + 만기연장 인수수수료 11,186 + 해외수수료 9,292,540</t>
+        </is>
+      </c>
+      <c r="B62" s="65" t="n"/>
+      <c r="C62" s="66" t="n"/>
+      <c r="D62" s="65" t="n"/>
+      <c r="E62" s="65" t="n"/>
+      <c r="F62" s="65" t="n"/>
+      <c r="G62" s="71" t="n"/>
+      <c r="H62" s="65" t="n"/>
+      <c r="I62" s="65" t="n"/>
+      <c r="J62" s="65" t="n"/>
+    </row>
+    <row r="63" ht="15.75" customFormat="1" customHeight="1" s="160">
+      <c r="A63" s="274" t="inlineStr">
+        <is>
+          <t>주5: 해외수수료 KRW 9,292,540은 USD 6,124.77 x 1,517.20 환산 추정 (은행 명세상 KRW 미표기). lcCustomsData 해외수수료(USD 6,124.77)와 일치</t>
+        </is>
+      </c>
+      <c r="B63" s="65" t="n"/>
+      <c r="C63" s="66" t="n"/>
+      <c r="D63" s="65" t="n"/>
+      <c r="E63" s="65" t="n"/>
+      <c r="F63" s="65" t="n"/>
+      <c r="G63" s="71" t="n"/>
+      <c r="H63" s="65" t="n"/>
+      <c r="I63" s="65" t="n"/>
+      <c r="J63" s="65" t="n"/>
+    </row>
     <row r="64" ht="15.75" customFormat="1" customHeight="1" s="160"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" tabRatio="500" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PO별 개당 수입원가" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라이센스_워런티" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="합배송_비용안분" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화송금내역" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usance_LC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PO별 개당 수입원가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="라이센스_워런티" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="합배송_비용안분" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="외화송금내역" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Usance_LC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$40</definedName>
-    <definedName name="RemitTable2">'외화송금내역'!$A$43:$L$91</definedName>
+    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$44</definedName>
+    <definedName name="RemitTable2">'외화송금내역'!$A$47:$L$101</definedName>
     <definedName name="FxRateTable">환율!$A$7:$D$43</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="283">
+  <cellXfs count="296">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1289,6 +1289,45 @@
     </xf>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,6 +1409,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>RNR 재무팀</author>
+    <author>import-cost-calculator</author>
   </authors>
   <commentList>
     <comment ref="S5" authorId="0" shapeId="0">
@@ -1491,14 +1531,28 @@
 인보이스/송금/수입신고 미도래 - 미확정 건</t>
       </text>
     </comment>
-    <comment ref="S63" authorId="0" shapeId="0">
+    <comment ref="S41" authorId="1" shapeId="0">
+      <text>
+        <t>관세 0원 — 수입신고필증 세율구분 'C'(WTO협정/양허세율) 적용
+HS 8518 음향기기 (loudspeakers/amplifier)
+원산지: 우크라이나(UA-A)</t>
+      </text>
+    </comment>
+    <comment ref="S42" authorId="1" shapeId="0">
+      <text>
+        <t>관세 0원 — 수입신고필증 세율구분 'C'(WTO협정/양허세율) 적용
+HS 8518 음향기기 (loudspeakers/amplifier)
+원산지: 우크라이나(UA-A)</t>
+      </text>
+    </comment>
+    <comment ref="S68" authorId="0" shapeId="0">
       <text>
         <t>관세율 0.00% - 세율구분 C(가가, WTO/ITA 양허)
 수리반환 재수입 건, 부가세만 과세
 (신고필증 2235626351613M)</t>
       </text>
     </comment>
-    <comment ref="Y63" authorId="0" shapeId="0">
+    <comment ref="Y68" authorId="0" shapeId="0">
       <text>
         <t>DHL 2026-05월 인보이스 (AWB 5094871784 = 수입신고필증 B/L 일치)
 GDC RMA 수리반환 건, 지출결의 2026-1344, 6/9 집행</t>
@@ -1722,7 +1776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF87"/>
+  <dimension ref="A1:AF93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" style="160" min="1" max="1"/>
@@ -1788,7 +1842,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-06-16  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-06-18  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="148" t="n"/>
@@ -2269,7 +2323,7 @@
         <v/>
       </c>
       <c r="AA6" s="10">
-        <f>K6+L6+M6+IFERROR(VLOOKUP(B6,RemitTable2,9,FALSE()),0)+Y6+Z6</f>
+        <f>K6+L6+M6+IFERROR(VLOOKUP(B6,RemitTable2,9,FALSE),0)+Y6+Z6</f>
         <v/>
       </c>
       <c r="AB6" s="11" t="n">
@@ -2396,7 +2450,7 @@
         <v/>
       </c>
       <c r="AA7" s="10">
-        <f>K7+L7+M7+IFERROR(VLOOKUP(B7,RemitTable2,9,FALSE()),0)+Y7+Z7</f>
+        <f>K7+L7+M7+IFERROR(VLOOKUP(B7,RemitTable2,9,FALSE),0)+Y7+Z7</f>
         <v/>
       </c>
       <c r="AB7" s="11" t="n">
@@ -2523,7 +2577,7 @@
         <v/>
       </c>
       <c r="AA8" s="10">
-        <f>K8+L8+M8+IFERROR(VLOOKUP(B8,RemitTable2,9,FALSE()),0)+Y8+Z8</f>
+        <f>K8+L8+M8+IFERROR(VLOOKUP(B8,RemitTable2,9,FALSE),0)+Y8+Z8</f>
         <v/>
       </c>
       <c r="AB8" s="11" t="n">
@@ -2585,7 +2639,7 @@
         <v>362.25</v>
       </c>
       <c r="I9" s="178">
-        <f>IFERROR(VLOOKUP(B9,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B9,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J9" s="18" t="n">
@@ -2596,11 +2650,11 @@
         <v/>
       </c>
       <c r="L9" s="18">
-        <f>IFERROR(VLOOKUP(B9,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B9,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M9" s="18">
-        <f>IFERROR(VLOOKUP(B9,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B9,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N9" s="12" t="inlineStr">
@@ -2610,8 +2664,14 @@
       </c>
       <c r="O9" s="12" t="n"/>
       <c r="P9" s="12" t="n"/>
-      <c r="Q9" s="18" t="n"/>
-      <c r="R9" s="18" t="n"/>
+      <c r="Q9" s="18">
+        <f>IF(P9="","",IFERROR(VLOOKUP(O9,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R9" s="18">
+        <f>IF(P9="","",H9)</f>
+        <v/>
+      </c>
       <c r="S9" s="18" t="n">
         <v>0</v>
       </c>
@@ -2642,7 +2702,7 @@
         <v/>
       </c>
       <c r="AA9" s="18">
-        <f>K9+L9+M9+IFERROR(VLOOKUP(B9,RemitTable2,9,FALSE()),0)+Y9+Z9</f>
+        <f>K9+L9+M9+IFERROR(VLOOKUP(B9,RemitTable2,9,FALSE),0)+Y9+Z9</f>
         <v/>
       </c>
       <c r="AB9" s="19" t="n">
@@ -2765,7 +2825,7 @@
         <v/>
       </c>
       <c r="AA10" s="10">
-        <f>K10+L10+M10+IFERROR(VLOOKUP(B10,RemitTable2,9,FALSE()),0)+Y10+Z10</f>
+        <f>K10+L10+M10+IFERROR(VLOOKUP(B10,RemitTable2,9,FALSE),0)+Y10+Z10</f>
         <v/>
       </c>
       <c r="AB10" s="11" t="n">
@@ -2892,7 +2952,7 @@
         <v/>
       </c>
       <c r="AA11" s="10">
-        <f>K11+L11+M11+IFERROR(VLOOKUP(B11,RemitTable2,9,FALSE()),0)+Y11+Z11</f>
+        <f>K11+L11+M11+IFERROR(VLOOKUP(B11,RemitTable2,9,FALSE),0)+Y11+Z11</f>
         <v/>
       </c>
       <c r="AB11" s="11" t="n">
@@ -3019,7 +3079,7 @@
         <v/>
       </c>
       <c r="AA12" s="10">
-        <f>K12+L12+M12+IFERROR(VLOOKUP(B12,RemitTable2,9,FALSE()),0)+Y12+Z12</f>
+        <f>K12+L12+M12+IFERROR(VLOOKUP(B12,RemitTable2,9,FALSE),0)+Y12+Z12</f>
         <v/>
       </c>
       <c r="AB12" s="11" t="n">
@@ -3146,7 +3206,7 @@
         <v/>
       </c>
       <c r="AA13" s="10">
-        <f>K13+L13+M13+IFERROR(VLOOKUP(B13,RemitTable2,9,FALSE()),0)+Y13+Z13</f>
+        <f>K13+L13+M13+IFERROR(VLOOKUP(B13,RemitTable2,9,FALSE),0)+Y13+Z13</f>
         <v/>
       </c>
       <c r="AB13" s="11" t="n">
@@ -3273,7 +3333,7 @@
         <v/>
       </c>
       <c r="AA14" s="10">
-        <f>K14+L14+M14+IFERROR(VLOOKUP(B14,RemitTable2,9,FALSE()),0)+Y14+Z14</f>
+        <f>K14+L14+M14+IFERROR(VLOOKUP(B14,RemitTable2,9,FALSE),0)+Y14+Z14</f>
         <v/>
       </c>
       <c r="AB14" s="11" t="n">
@@ -3400,7 +3460,7 @@
         <v/>
       </c>
       <c r="AA15" s="10">
-        <f>K15+L15+M15+IFERROR(VLOOKUP(B15,RemitTable2,9,FALSE()),0)+Y15+Z15</f>
+        <f>K15+L15+M15+IFERROR(VLOOKUP(B15,RemitTable2,9,FALSE),0)+Y15+Z15</f>
         <v/>
       </c>
       <c r="AB15" s="11" t="n">
@@ -3527,7 +3587,7 @@
         <v/>
       </c>
       <c r="AA16" s="10">
-        <f>K16+L16+M16+IFERROR(VLOOKUP(B16,RemitTable2,9,FALSE()),0)+Y16+Z16</f>
+        <f>K16+L16+M16+IFERROR(VLOOKUP(B16,RemitTable2,9,FALSE),0)+Y16+Z16</f>
         <v/>
       </c>
       <c r="AB16" s="11" t="n">
@@ -3654,7 +3714,7 @@
         <v/>
       </c>
       <c r="AA17" s="10">
-        <f>K17+L17+M17+IFERROR(VLOOKUP(B17,RemitTable2,9,FALSE()),0)+Y17+Z17</f>
+        <f>K17+L17+M17+IFERROR(VLOOKUP(B17,RemitTable2,9,FALSE),0)+Y17+Z17</f>
         <v/>
       </c>
       <c r="AB17" s="11" t="n">
@@ -3781,7 +3841,7 @@
         <v/>
       </c>
       <c r="AA18" s="10">
-        <f>K18+L18+M18+IFERROR(VLOOKUP(B18,RemitTable2,9,FALSE()),0)+Y18+Z18</f>
+        <f>K18+L18+M18+IFERROR(VLOOKUP(B18,RemitTable2,9,FALSE),0)+Y18+Z18</f>
         <v/>
       </c>
       <c r="AB18" s="11" t="n">
@@ -3908,7 +3968,7 @@
         <v/>
       </c>
       <c r="AA19" s="10">
-        <f>K19+L19+M19+IFERROR(VLOOKUP(B19,RemitTable2,9,FALSE()),0)+Y19+Z19</f>
+        <f>K19+L19+M19+IFERROR(VLOOKUP(B19,RemitTable2,9,FALSE),0)+Y19+Z19</f>
         <v/>
       </c>
       <c r="AB19" s="11" t="n">
@@ -4034,14 +4094,16 @@
         <f>S20+T20+W20</f>
         <v/>
       </c>
-      <c r="AA20" s="10" t="n">
-        <v>20915590</v>
+      <c r="AA20" s="10">
+        <f>K20+L20+M20+IFERROR(VLOOKUP(B20,RemitTable2,9,FALSE),0)+Y20+Z20</f>
+        <v/>
       </c>
       <c r="AB20" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="AC20" s="10" t="n">
-        <v>10457795</v>
+      <c r="AC20" s="10">
+        <f>ROUND(AA20/AB20,0)</f>
+        <v/>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
@@ -4159,14 +4221,16 @@
         <f>S21+T21+W21</f>
         <v/>
       </c>
-      <c r="AA21" s="10" t="n">
-        <v>473718807</v>
+      <c r="AA21" s="10">
+        <f>K21+L21+M21+IFERROR(VLOOKUP(B21,RemitTable2,9,FALSE),0)+Y21+Z21</f>
+        <v/>
       </c>
       <c r="AB21" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="AC21" s="10" t="n">
-        <v>16918529</v>
+      <c r="AC21" s="10">
+        <f>ROUND(AA21/AB21,0)</f>
+        <v/>
       </c>
       <c r="AD21" s="3" t="inlineStr">
         <is>
@@ -4285,7 +4349,7 @@
         <v/>
       </c>
       <c r="AA22" s="10">
-        <f>K22+L22+M22+IFERROR(VLOOKUP(B22,RemitTable2,9,FALSE()),0)+Y22+Z22</f>
+        <f>K22+L22+M22+IFERROR(VLOOKUP(B22,RemitTable2,9,FALSE),0)+Y22+Z22</f>
         <v/>
       </c>
       <c r="AB22" s="11" t="n">
@@ -4347,7 +4411,7 @@
         <v>35674</v>
       </c>
       <c r="I23" s="178">
-        <f>IFERROR(VLOOKUP(B23,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B23,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J23" s="18" t="n">
@@ -4358,11 +4422,11 @@
         <v/>
       </c>
       <c r="L23" s="18">
-        <f>IFERROR(VLOOKUP(B23,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B23,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M23" s="18">
-        <f>IFERROR(VLOOKUP(B23,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B23,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N23" s="12" t="inlineStr">
@@ -4372,8 +4436,14 @@
       </c>
       <c r="O23" s="12" t="n"/>
       <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="18" t="n"/>
-      <c r="R23" s="18" t="n"/>
+      <c r="Q23" s="18">
+        <f>IF(P23="","",IFERROR(VLOOKUP(O23,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R23" s="18">
+        <f>IF(P23="","",H23)</f>
+        <v/>
+      </c>
       <c r="S23" s="18" t="n">
         <v>0</v>
       </c>
@@ -4404,7 +4474,7 @@
         <v/>
       </c>
       <c r="AA23" s="18">
-        <f>K23+L23+M23+IFERROR(VLOOKUP(B23,RemitTable2,9,FALSE()),0)+Y23+Z23</f>
+        <f>K23+L23+M23+IFERROR(VLOOKUP(B23,RemitTable2,9,FALSE),0)+Y23+Z23</f>
         <v/>
       </c>
       <c r="AB23" s="19" t="n">
@@ -4527,7 +4597,7 @@
         <v/>
       </c>
       <c r="AA24" s="10">
-        <f>K24+L24+M24+IFERROR(VLOOKUP(B24,RemitTable2,9,FALSE()),0)+Y24+Z24</f>
+        <f>K24+L24+M24+IFERROR(VLOOKUP(B24,RemitTable2,9,FALSE),0)+Y24+Z24</f>
         <v/>
       </c>
       <c r="AB24" s="11" t="n">
@@ -4654,7 +4724,7 @@
         <v/>
       </c>
       <c r="AA25" s="10">
-        <f>K25+L25+M25+IFERROR(VLOOKUP(B25,RemitTable2,9,FALSE()),0)+Y25+Z25</f>
+        <f>K25+L25+M25+IFERROR(VLOOKUP(B25,RemitTable2,9,FALSE),0)+Y25+Z25</f>
         <v/>
       </c>
       <c r="AB25" s="11" t="n">
@@ -4781,7 +4851,7 @@
         <v/>
       </c>
       <c r="AA26" s="10">
-        <f>K26+L26+M26+IFERROR(VLOOKUP(B26,RemitTable2,9,FALSE()),0)+Y26+Z26</f>
+        <f>K26+L26+M26+IFERROR(VLOOKUP(B26,RemitTable2,9,FALSE),0)+Y26+Z26</f>
         <v/>
       </c>
       <c r="AB26" s="11" t="n">
@@ -4908,7 +4978,7 @@
         <v/>
       </c>
       <c r="AA27" s="10">
-        <f>K27+L27+M27+IFERROR(VLOOKUP(B27,RemitTable2,9,FALSE()),0)+Y27+Z27</f>
+        <f>K27+L27+M27+IFERROR(VLOOKUP(B27,RemitTable2,9,FALSE),0)+Y27+Z27</f>
         <v/>
       </c>
       <c r="AB27" s="11" t="n">
@@ -5035,7 +5105,7 @@
         <v/>
       </c>
       <c r="AA28" s="10">
-        <f>K28+L28+M28+IFERROR(VLOOKUP(B28,RemitTable2,9,FALSE()),0)+Y28+Z28</f>
+        <f>K28+L28+M28+IFERROR(VLOOKUP(B28,RemitTable2,9,FALSE),0)+Y28+Z28</f>
         <v/>
       </c>
       <c r="AB28" s="11" t="n">
@@ -5158,7 +5228,7 @@
         <v/>
       </c>
       <c r="AA29" s="10">
-        <f>K29+L29+M29+IFERROR(VLOOKUP(B29,RemitTable2,9,FALSE()),0)+Y29+Z29</f>
+        <f>K29+L29+M29+IFERROR(VLOOKUP(B29,RemitTable2,9,FALSE),0)+Y29+Z29</f>
         <v/>
       </c>
       <c r="AB29" s="11" t="n">
@@ -5273,7 +5343,7 @@
         <v/>
       </c>
       <c r="AA30" s="83">
-        <f>K30+L30+M30+IFERROR(VLOOKUP(B30,RemitTable2,9,FALSE()),0)+Y30+Z30</f>
+        <f>K30+L30+M30+IFERROR(VLOOKUP(B30,RemitTable2,9,FALSE),0)+Y30+Z30</f>
         <v/>
       </c>
       <c r="AB30" s="84" t="n">
@@ -5388,7 +5458,7 @@
         <v/>
       </c>
       <c r="AA31" s="83">
-        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
+        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE),0)+Y31+Z31</f>
         <v/>
       </c>
       <c r="AB31" s="84" t="n">
@@ -5496,14 +5566,16 @@
         <f>S32+T32+W32</f>
         <v/>
       </c>
-      <c r="AA32" s="83" t="n">
-        <v>7763609</v>
+      <c r="AA32" s="83">
+        <f>K32+L32+M32+IFERROR(VLOOKUP(B32,RemitTable2,9,FALSE),0)+Y32+Z32</f>
+        <v/>
       </c>
       <c r="AB32" s="84" t="n">
         <v>60</v>
       </c>
-      <c r="AC32" s="83" t="n">
-        <v>129393</v>
+      <c r="AC32" s="83">
+        <f>ROUND(AA32/AB32,0)</f>
+        <v/>
       </c>
       <c r="AD32" s="78" t="n"/>
       <c r="AE32" s="78" t="n"/>
@@ -5536,32 +5608,26 @@
       <c r="F33" s="181" t="n">
         <v>46127</v>
       </c>
-      <c r="G33" s="124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G33" s="283" t="n">
+        <v>46190</v>
       </c>
       <c r="H33" s="126" t="n">
         <v>351274</v>
       </c>
-      <c r="I33" s="126">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I33" s="126" t="n">
+        <v>1518</v>
       </c>
       <c r="J33" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="128">
-        <f>IFERROR(ROUND(H33*I33,0),0)</f>
-        <v/>
-      </c>
-      <c r="L33" s="128">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M33" s="128">
-        <f>IFERROR(VLOOKUP(B33,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>533233932</v>
+      </c>
+      <c r="K33" s="128" t="n">
+        <v>533233932</v>
+      </c>
+      <c r="L33" s="128" t="n">
+        <v>12500</v>
+      </c>
+      <c r="M33" s="128" t="n">
+        <v>8000</v>
       </c>
       <c r="N33" s="129" t="n"/>
       <c r="O33" s="182" t="n">
@@ -6303,530 +6369,474 @@
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="20" t="n">
+      <c r="A40" s="124" t="n">
+        <v>61</v>
+      </c>
+      <c r="B40" s="124" t="inlineStr">
+        <is>
+          <t>CPO696-5</t>
+        </is>
+      </c>
+      <c r="C40" s="124" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D40" s="124" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E40" s="124" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F40" s="181" t="n">
+        <v>46163</v>
+      </c>
+      <c r="G40" s="283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" s="126" t="n">
+        <v>346792</v>
+      </c>
+      <c r="I40" s="126">
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J40" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="128">
+        <f>IFERROR(ROUND(H40*I40,0),0)</f>
+        <v/>
+      </c>
+      <c r="L40" s="128">
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M40" s="128">
+        <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N40" s="129" t="inlineStr">
+        <is>
+          <t>CP4420-RGB 4K Projector 8대 + TPC Touch 8 (롯데 렌탈 4차)</t>
+        </is>
+      </c>
+      <c r="O40" s="182" t="n">
+        <v>46177</v>
+      </c>
+      <c r="P40" s="129" t="inlineStr">
+        <is>
+          <t>14008-26-101227M</t>
+        </is>
+      </c>
+      <c r="Q40" s="126">
+        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R40" s="126">
+        <f>IF(P40="","",H40)</f>
+        <v/>
+      </c>
+      <c r="S40" s="128" t="n">
+        <v>533676</v>
+      </c>
+      <c r="T40" s="128" t="n">
+        <v>52536040</v>
+      </c>
+      <c r="U40" s="129" t="n"/>
+      <c r="V40" s="129" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W40" s="128" t="n">
+        <v>286000</v>
+      </c>
+      <c r="X40" s="124" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="Y40" s="128" t="n">
+        <v>2898404</v>
+      </c>
+      <c r="Z40" s="128">
+        <f>S40+T40+W40</f>
+        <v/>
+      </c>
+      <c r="AA40" s="131">
+        <f>K40+L40+M40+IFERROR(VLOOKUP(B40,RemitTable2,9,FALSE),0)+Y40+Z40</f>
+        <v/>
+      </c>
+      <c r="AB40" s="167" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC40" s="131">
+        <f>ROUND(AA40/AB40,0)</f>
+        <v/>
+      </c>
+      <c r="AD40" s="129" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AE40" s="129" t="n"/>
+      <c r="AF40" s="129" t="n"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="124" t="n">
+        <v>62</v>
+      </c>
+      <c r="B41" s="124" t="inlineStr">
+        <is>
+          <t>MPO67</t>
+        </is>
+      </c>
+      <c r="C41" s="124" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D41" s="124" t="inlineStr">
+        <is>
+          <t>T/T</t>
+        </is>
+      </c>
+      <c r="E41" s="124" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F41" s="181" t="n">
+        <v>46154</v>
+      </c>
+      <c r="G41" s="283" t="n">
+        <v>46190</v>
+      </c>
+      <c r="H41" s="126" t="n">
+        <v>49138.8</v>
+      </c>
+      <c r="I41" s="126" t="n">
+        <v>1517.3</v>
+      </c>
+      <c r="J41" s="128" t="n">
+        <v>74558330</v>
+      </c>
+      <c r="K41" s="128" t="n">
+        <v>74558330</v>
+      </c>
+      <c r="L41" s="128" t="n">
+        <v>10115</v>
+      </c>
+      <c r="M41" s="128" t="n">
+        <v>6473</v>
+      </c>
+      <c r="N41" s="129" t="inlineStr">
+        <is>
+          <t>MAG 음향장비 loudspeakers 108EA (롯데컬처웍스)</t>
+        </is>
+      </c>
+      <c r="O41" s="182" t="n">
+        <v>46188</v>
+      </c>
+      <c r="P41" s="129" t="inlineStr">
+        <is>
+          <t>14008-26-101275M</t>
+        </is>
+      </c>
+      <c r="Q41" s="126">
+        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R41" s="126">
+        <f>IF(P41="","",H41)</f>
+        <v/>
+      </c>
+      <c r="S41" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="128" t="n">
+        <v>8891915</v>
+      </c>
+      <c r="U41" s="129" t="n"/>
+      <c r="V41" s="129" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W41" s="128" t="n">
+        <v>204725</v>
+      </c>
+      <c r="X41" s="124" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="Y41" s="128" t="n">
+        <v>14471173</v>
+      </c>
+      <c r="Z41" s="128">
+        <f>S41+T41+W41</f>
+        <v/>
+      </c>
+      <c r="AA41" s="131">
+        <f>K41+L41+M41+IFERROR(VLOOKUP(B41,RemitTable2,9,FALSE),0)+Y41+Z41</f>
+        <v/>
+      </c>
+      <c r="AB41" s="167" t="n">
+        <v>108</v>
+      </c>
+      <c r="AC41" s="131">
+        <f>ROUND(AA41/AB41,0)</f>
+        <v/>
+      </c>
+      <c r="AD41" s="129" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AE41" s="129" t="n"/>
+      <c r="AF41" s="129" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="124" t="n">
+        <v>63</v>
+      </c>
+      <c r="B42" s="124" t="inlineStr">
+        <is>
+          <t>MPO68</t>
+        </is>
+      </c>
+      <c r="C42" s="124" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D42" s="124" t="inlineStr">
+        <is>
+          <t>T/T</t>
+        </is>
+      </c>
+      <c r="E42" s="124" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F42" s="181" t="n">
+        <v>46154</v>
+      </c>
+      <c r="G42" s="283" t="n">
+        <v>46190</v>
+      </c>
+      <c r="H42" s="126" t="n">
+        <v>11587.2</v>
+      </c>
+      <c r="I42" s="126" t="n">
+        <v>1517.3</v>
+      </c>
+      <c r="J42" s="128" t="n">
+        <v>17582284</v>
+      </c>
+      <c r="K42" s="128" t="n">
+        <v>17582284</v>
+      </c>
+      <c r="L42" s="128" t="n">
+        <v>2385</v>
+      </c>
+      <c r="M42" s="128" t="n">
+        <v>1527</v>
+      </c>
+      <c r="N42" s="129" t="inlineStr">
+        <is>
+          <t>MAG 음향장비 loudspeakers 29EA (CJ 미래원)</t>
+        </is>
+      </c>
+      <c r="O42" s="182" t="n">
+        <v>46188</v>
+      </c>
+      <c r="P42" s="129" t="inlineStr">
+        <is>
+          <t>14008-26-101275M</t>
+        </is>
+      </c>
+      <c r="Q42" s="126">
+        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R42" s="126">
+        <f>IF(P42="","",H42)</f>
+        <v/>
+      </c>
+      <c r="S42" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="128" t="n">
+        <v>2096763</v>
+      </c>
+      <c r="U42" s="129" t="n"/>
+      <c r="V42" s="129" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W42" s="128" t="n">
+        <v>48275</v>
+      </c>
+      <c r="X42" s="124" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="Y42" s="128" t="n">
+        <v>3412382</v>
+      </c>
+      <c r="Z42" s="128">
+        <f>S42+T42+W42</f>
+        <v/>
+      </c>
+      <c r="AA42" s="131">
+        <f>K42+L42+M42+IFERROR(VLOOKUP(B42,RemitTable2,9,FALSE),0)+Y42+Z42</f>
+        <v/>
+      </c>
+      <c r="AB42" s="167" t="n">
         <v>29</v>
       </c>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>CPO667</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E40" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F40" s="183" t="n">
-        <v>45925</v>
-      </c>
-      <c r="G40" s="184" t="n">
-        <v>46080</v>
-      </c>
-      <c r="H40" s="24" t="n">
-        <v>5673</v>
-      </c>
-      <c r="I40" s="185" t="n">
-        <v>1441.6</v>
-      </c>
-      <c r="J40" s="26" t="n">
-        <v>8178197</v>
-      </c>
-      <c r="K40" s="26" t="n">
-        <v>8178197</v>
-      </c>
-      <c r="L40" s="26" t="n">
-        <v>499</v>
-      </c>
-      <c r="M40" s="26" t="n">
-        <v>319</v>
-      </c>
-      <c r="N40" s="20" t="inlineStr">
-        <is>
-          <t>EW CP2220</t>
-        </is>
-      </c>
-      <c r="O40" s="20" t="inlineStr">
+      <c r="AC42" s="131">
+        <f>ROUND(AA42/AB42,0)</f>
+        <v/>
+      </c>
+      <c r="AD42" s="129" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AE42" s="129" t="n"/>
+      <c r="AF42" s="129" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="124" t="n">
+        <v>64</v>
+      </c>
+      <c r="B43" s="124" t="inlineStr">
+        <is>
+          <t>APO001</t>
+        </is>
+      </c>
+      <c r="C43" s="124" t="inlineStr">
+        <is>
+          <t>Appotronics</t>
+        </is>
+      </c>
+      <c r="D43" s="124" t="inlineStr">
+        <is>
+          <t>100% TT in advance</t>
+        </is>
+      </c>
+      <c r="E43" s="124" t="inlineStr">
+        <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="F43" s="181" t="n">
+        <v>46163</v>
+      </c>
+      <c r="G43" s="283" t="n">
+        <v>46190</v>
+      </c>
+      <c r="H43" s="126" t="n">
+        <v>12400</v>
+      </c>
+      <c r="I43" s="126" t="n">
+        <v>1517.1</v>
+      </c>
+      <c r="J43" s="128" t="n">
+        <v>18812040</v>
+      </c>
+      <c r="K43" s="128" t="n">
+        <v>18812040</v>
+      </c>
+      <c r="L43" s="128" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M43" s="128" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N43" s="129" t="inlineStr">
+        <is>
+          <t>S20-C2220-BEAB 레이저모듈 2set (CP2220)</t>
+        </is>
+      </c>
+      <c r="O43" s="182" t="n"/>
+      <c r="P43" s="129" t="n"/>
+      <c r="Q43" s="126">
+        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R43" s="126">
+        <f>IF(P43="","",H43)</f>
+        <v/>
+      </c>
+      <c r="S43" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="129" t="n"/>
+      <c r="V43" s="129" t="n"/>
+      <c r="W43" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P40" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q40" s="24">
-        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R40" s="26">
-        <f>IF(P40="","",H40)</f>
-        <v/>
-      </c>
-      <c r="S40" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W40" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y40" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="26">
-        <f>S40+T40+W40</f>
-        <v/>
-      </c>
-      <c r="AA40" s="26">
-        <f>K40+L40+M40+IFERROR(VLOOKUP(B40,RemitTable2,9,FALSE),0)+Y40+Z40</f>
-        <v/>
-      </c>
-      <c r="AB40" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="26">
-        <f>ROUND(AA40/AB40,0)</f>
-        <v/>
-      </c>
-      <c r="AD40" s="20" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="AE40" s="184" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AF40" s="183" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="B41" s="20" t="inlineStr">
-        <is>
-          <t>GPO458</t>
-        </is>
-      </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F41" s="183" t="n">
-        <v>45982</v>
-      </c>
-      <c r="G41" s="184" t="n">
-        <v>46020</v>
-      </c>
-      <c r="H41" s="24" t="n">
-        <v>350</v>
-      </c>
-      <c r="I41" s="185" t="n">
-        <v>1439.1</v>
-      </c>
-      <c r="J41" s="26" t="n">
-        <v>503685</v>
-      </c>
-      <c r="K41" s="26" t="n">
-        <v>503685</v>
-      </c>
-      <c r="L41" s="26" t="n">
-        <v>253</v>
-      </c>
-      <c r="M41" s="26" t="n">
-        <v>202</v>
-      </c>
-      <c r="N41" s="20" t="inlineStr">
-        <is>
-          <t>HFR License</t>
-        </is>
-      </c>
-      <c r="O41" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P41" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q41" s="24">
-        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R41" s="26">
-        <f>IF(P41="","",H41)</f>
-        <v/>
-      </c>
-      <c r="S41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="26">
-        <f>S41+T41+W41</f>
-        <v/>
-      </c>
-      <c r="AA41" s="26">
-        <f>K41+L41+M41+IFERROR(VLOOKUP(B41,RemitTable2,9,FALSE),0)+Y41+Z41</f>
-        <v/>
-      </c>
-      <c r="AB41" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="26">
-        <f>ROUND(AA41/AB41,0)</f>
-        <v/>
-      </c>
-      <c r="AD41" s="20" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AE41" s="184" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AF41" s="183" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="20" t="n">
-        <v>31</v>
-      </c>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>CPO681</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F42" s="183" t="n">
-        <v>45993</v>
-      </c>
-      <c r="G42" s="184" t="n">
-        <v>46064</v>
-      </c>
-      <c r="H42" s="24" t="n">
-        <v>26358</v>
-      </c>
-      <c r="I42" s="185" t="n">
-        <v>1460.7</v>
-      </c>
-      <c r="J42" s="26" t="n">
-        <v>38501131</v>
-      </c>
-      <c r="K42" s="26" t="n">
-        <v>38501131</v>
-      </c>
-      <c r="L42" s="26" t="n">
-        <v>12500</v>
-      </c>
-      <c r="M42" s="26" t="n">
-        <v>8000</v>
-      </c>
-      <c r="N42" s="20" t="inlineStr">
-        <is>
-          <t>EW CP2309/2315/2320-RGB</t>
-        </is>
-      </c>
-      <c r="O42" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P42" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q42" s="24">
-        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R42" s="26">
-        <f>IF(P42="","",H42)</f>
-        <v/>
-      </c>
-      <c r="S42" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W42" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y42" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="26">
-        <f>S42+T42+W42</f>
-        <v/>
-      </c>
-      <c r="AA42" s="26">
-        <f>K42+L42+M42+IFERROR(VLOOKUP(B42,RemitTable2,9,FALSE),0)+Y42+Z42</f>
-        <v/>
-      </c>
-      <c r="AB42" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="26">
-        <f>ROUND(AA42/AB42,0)</f>
-        <v/>
-      </c>
-      <c r="AD42" s="20" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AE42" s="184" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AF42" s="183" t="inlineStr">
-        <is>
-          <t>2026-12-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>GPO459</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E43" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F43" s="183" t="n">
-        <v>46007</v>
-      </c>
-      <c r="G43" s="184" t="n">
-        <v>46043</v>
-      </c>
-      <c r="H43" s="24" t="n">
-        <v>450</v>
-      </c>
-      <c r="I43" s="185" t="n">
-        <v>1475.7</v>
-      </c>
-      <c r="J43" s="26" t="n">
-        <v>664065</v>
-      </c>
-      <c r="K43" s="26" t="n">
-        <v>664065</v>
-      </c>
-      <c r="L43" s="26" t="n">
-        <v>912</v>
-      </c>
-      <c r="M43" s="26" t="n">
-        <v>973</v>
-      </c>
-      <c r="N43" s="20" t="inlineStr">
-        <is>
-          <t>TMS-2000 EW</t>
-        </is>
-      </c>
-      <c r="O43" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P43" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q43" s="24">
-        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R43" s="26">
-        <f>IF(P43="","",H43)</f>
-        <v/>
-      </c>
-      <c r="S43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="26">
+      <c r="Y43" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="128">
         <f>S43+T43+W43</f>
         <v/>
       </c>
-      <c r="AA43" s="26">
+      <c r="AA43" s="131">
         <f>K43+L43+M43+IFERROR(VLOOKUP(B43,RemitTable2,9,FALSE),0)+Y43+Z43</f>
         <v/>
       </c>
-      <c r="AB43" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC43" s="26">
+      <c r="AB43" s="167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC43" s="131">
         <f>ROUND(AA43/AB43,0)</f>
         <v/>
       </c>
-      <c r="AD43" s="20" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="AE43" s="184" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF43" s="183" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
+      <c r="AD43" s="129" t="n"/>
+      <c r="AE43" s="129" t="n"/>
+      <c r="AF43" s="129" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="20" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E44" s="21" t="inlineStr">
@@ -6835,32 +6845,32 @@
         </is>
       </c>
       <c r="F44" s="183" t="n">
-        <v>46007</v>
+        <v>45925</v>
       </c>
       <c r="G44" s="184" t="n">
-        <v>46043</v>
+        <v>46080</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>540</v>
+        <v>5673</v>
       </c>
       <c r="I44" s="185" t="n">
-        <v>1475.7</v>
+        <v>1441.6</v>
       </c>
       <c r="J44" s="26" t="n">
-        <v>796878</v>
+        <v>8178197</v>
       </c>
       <c r="K44" s="26" t="n">
-        <v>796878</v>
+        <v>8178197</v>
       </c>
       <c r="L44" s="26" t="n">
-        <v>1095</v>
+        <v>499</v>
       </c>
       <c r="M44" s="26" t="n">
-        <v>1168</v>
+        <v>319</v>
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 EW</t>
+          <t>EW CP2220</t>
         </is>
       </c>
       <c r="O44" s="20" t="inlineStr">
@@ -6923,71 +6933,71 @@
       </c>
       <c r="AD44" s="20" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="AE44" s="184" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AF44" s="183" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="20" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F45" s="183" t="n">
-        <v>46010</v>
+        <v>45982</v>
       </c>
       <c r="G45" s="184" t="n">
-        <v>46080</v>
+        <v>46020</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>136516</v>
+        <v>350</v>
       </c>
       <c r="I45" s="185" t="n">
-        <v>1441.6</v>
+        <v>1439.1</v>
       </c>
       <c r="J45" s="26" t="n">
-        <v>196801466</v>
+        <v>503685</v>
       </c>
       <c r="K45" s="26" t="n">
-        <v>196801466</v>
+        <v>503685</v>
       </c>
       <c r="L45" s="26" t="n">
-        <v>12001</v>
+        <v>253</v>
       </c>
       <c r="M45" s="26" t="n">
-        <v>7681</v>
+        <v>202</v>
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (CP2208~CP4450)</t>
+          <t>HFR License</t>
         </is>
       </c>
       <c r="O45" s="20" t="inlineStr">
@@ -7050,37 +7060,37 @@
       </c>
       <c r="AD45" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE45" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AF45" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="20" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>GPO465</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E46" s="21" t="inlineStr">
@@ -7089,38 +7099,32 @@
         </is>
       </c>
       <c r="F46" s="183" t="n">
-        <v>46015</v>
-      </c>
-      <c r="G46" s="184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>45993</v>
+      </c>
+      <c r="G46" s="184" t="n">
+        <v>46064</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>76054</v>
-      </c>
-      <c r="I46" s="185">
-        <f>IFERROR(VLOOKUP(B46,RemitTable2,7,FALSE),0)</f>
-        <v/>
+        <v>26358</v>
+      </c>
+      <c r="I46" s="185" t="n">
+        <v>1460.7</v>
       </c>
       <c r="J46" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="26">
-        <f>IFERROR(ROUND(H46*I46,0),0)</f>
-        <v/>
-      </c>
-      <c r="L46" s="26">
-        <f>IFERROR(VLOOKUP(B46,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M46" s="26">
-        <f>IFERROR(VLOOKUP(B46,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>38501131</v>
+      </c>
+      <c r="K46" s="26" t="n">
+        <v>38501131</v>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>12500</v>
+      </c>
+      <c r="M46" s="26" t="n">
+        <v>8000</v>
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (SR/SX/TMS)</t>
+          <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
       <c r="O46" s="20" t="inlineStr">
@@ -7183,37 +7187,37 @@
       </c>
       <c r="AD46" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE46" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AF46" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-21</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E47" s="21" t="inlineStr">
@@ -7222,32 +7226,32 @@
         </is>
       </c>
       <c r="F47" s="183" t="n">
-        <v>46029</v>
+        <v>46007</v>
       </c>
       <c r="G47" s="184" t="n">
-        <v>46072</v>
+        <v>46043</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>14793</v>
+        <v>450</v>
       </c>
       <c r="I47" s="185" t="n">
-        <v>1451.7</v>
+        <v>1475.7</v>
       </c>
       <c r="J47" s="26" t="n">
-        <v>21474998</v>
+        <v>664065</v>
       </c>
       <c r="K47" s="26" t="n">
-        <v>21474998</v>
+        <v>664065</v>
       </c>
       <c r="L47" s="26" t="n">
-        <v>8435</v>
+        <v>912</v>
       </c>
       <c r="M47" s="26" t="n">
-        <v>6748</v>
+        <v>973</v>
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
-          <t>EW CP2315/CP4440-RGB</t>
+          <t>TMS-2000 EW</t>
         </is>
       </c>
       <c r="O47" s="20" t="inlineStr">
@@ -7315,32 +7319,32 @@
       </c>
       <c r="AE47" s="184" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF47" s="183" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="20" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>CPO687</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E48" s="21" t="inlineStr">
@@ -7349,38 +7353,32 @@
         </is>
       </c>
       <c r="F48" s="183" t="n">
-        <v>46029</v>
-      </c>
-      <c r="G48" s="184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46007</v>
+      </c>
+      <c r="G48" s="184" t="n">
+        <v>46043</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>26656</v>
-      </c>
-      <c r="I48" s="185">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE),0)</f>
-        <v/>
+        <v>540</v>
+      </c>
+      <c r="I48" s="185" t="n">
+        <v>1475.7</v>
       </c>
       <c r="J48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="26">
-        <f>IFERROR(ROUND(H48*I48,0),0)</f>
-        <v/>
-      </c>
-      <c r="L48" s="26">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M48" s="26">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>796878</v>
+      </c>
+      <c r="K48" s="26" t="n">
+        <v>796878</v>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>1095</v>
+      </c>
+      <c r="M48" s="26" t="n">
+        <v>1168</v>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>EW (홀딩)</t>
+          <t>TMS-1000 EW</t>
         </is>
       </c>
       <c r="O48" s="20" t="inlineStr">
@@ -7443,71 +7441,71 @@
       </c>
       <c r="AD48" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="AE48" s="184" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AF48" s="183" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F49" s="183" t="n">
-        <v>46042</v>
+        <v>46010</v>
       </c>
       <c r="G49" s="184" t="n">
-        <v>46057</v>
+        <v>46080</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>1440</v>
+        <v>136516</v>
       </c>
       <c r="I49" s="185" t="n">
-        <v>1453.6</v>
+        <v>1441.6</v>
       </c>
       <c r="J49" s="26" t="n">
-        <v>2093184</v>
+        <v>196801466</v>
       </c>
       <c r="K49" s="26" t="n">
-        <v>2093184</v>
+        <v>196801466</v>
       </c>
       <c r="L49" s="26" t="n">
-        <v>1241</v>
+        <v>12001</v>
       </c>
       <c r="M49" s="26" t="n">
-        <v>993</v>
+        <v>7681</v>
       </c>
       <c r="N49" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 License</t>
+          <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
       <c r="O49" s="20" t="inlineStr">
@@ -7586,11 +7584,11 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="20" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>GPO465</t>
         </is>
       </c>
       <c r="C50" s="21" t="inlineStr">
@@ -7609,32 +7607,38 @@
         </is>
       </c>
       <c r="F50" s="183" t="n">
-        <v>46042</v>
-      </c>
-      <c r="G50" s="184" t="n">
-        <v>46057</v>
+        <v>46015</v>
+      </c>
+      <c r="G50" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H50" s="24" t="n">
-        <v>4489</v>
-      </c>
-      <c r="I50" s="185" t="n">
-        <v>1453.6</v>
+        <v>76054</v>
+      </c>
+      <c r="I50" s="185">
+        <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE),0)</f>
+        <v/>
       </c>
       <c r="J50" s="26" t="n">
-        <v>6525210</v>
-      </c>
-      <c r="K50" s="26" t="n">
-        <v>6525210</v>
-      </c>
-      <c r="L50" s="26" t="n">
-        <v>3870</v>
-      </c>
-      <c r="M50" s="26" t="n">
-        <v>3096</v>
+        <v>0</v>
+      </c>
+      <c r="K50" s="26">
+        <f>IFERROR(ROUND(H50*I50,0),0)</f>
+        <v/>
+      </c>
+      <c r="L50" s="26">
+        <f>IFERROR(VLOOKUP(B50,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M50" s="26">
+        <f>IFERROR(VLOOKUP(B50,RemitTable2,11,FALSE),0)</f>
+        <v/>
       </c>
       <c r="N50" s="20" t="inlineStr">
         <is>
-          <t>SX/SR EW (CGV/Lotte)</t>
+          <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
       <c r="O50" s="20" t="inlineStr">
@@ -7713,21 +7717,21 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="20" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E51" s="21" t="inlineStr">
@@ -7736,32 +7740,32 @@
         </is>
       </c>
       <c r="F51" s="183" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="G51" s="184" t="n">
-        <v>46057</v>
+        <v>46072</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>5670.57</v>
+        <v>14793</v>
       </c>
       <c r="I51" s="185" t="n">
-        <v>1453.6</v>
+        <v>1451.7</v>
       </c>
       <c r="J51" s="26" t="n">
-        <v>8242741</v>
+        <v>21474998</v>
       </c>
       <c r="K51" s="26" t="n">
-        <v>8242741</v>
+        <v>21474998</v>
       </c>
       <c r="L51" s="26" t="n">
-        <v>4889</v>
+        <v>8435</v>
       </c>
       <c r="M51" s="26" t="n">
-        <v>3911</v>
+        <v>6748</v>
       </c>
       <c r="N51" s="20" t="inlineStr">
         <is>
-          <t>SR-1000/SX-3000 EW</t>
+          <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
       <c r="O51" s="20" t="inlineStr">
@@ -7829,22 +7833,22 @@
       </c>
       <c r="AE51" s="184" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AF51" s="183" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-29</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="20" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>CPO687</t>
         </is>
       </c>
       <c r="C52" s="21" t="inlineStr">
@@ -7863,32 +7867,38 @@
         </is>
       </c>
       <c r="F52" s="183" t="n">
-        <v>46057</v>
-      </c>
-      <c r="G52" s="184" t="n">
-        <v>46113</v>
+        <v>46029</v>
+      </c>
+      <c r="G52" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H52" s="24" t="n">
-        <v>24614</v>
-      </c>
-      <c r="I52" s="185" t="n">
-        <v>1505.7</v>
+        <v>26656</v>
+      </c>
+      <c r="I52" s="185">
+        <f>IFERROR(VLOOKUP(B52,RemitTable2,7,FALSE),0)</f>
+        <v/>
       </c>
       <c r="J52" s="26" t="n">
-        <v>37061300</v>
-      </c>
-      <c r="K52" s="26" t="n">
-        <v>37061300</v>
-      </c>
-      <c r="L52" s="26" t="n">
-        <v>8956</v>
-      </c>
-      <c r="M52" s="26" t="n">
-        <v>5732</v>
+        <v>0</v>
+      </c>
+      <c r="K52" s="26">
+        <f>IFERROR(ROUND(H52*I52,0),0)</f>
+        <v/>
+      </c>
+      <c r="L52" s="26">
+        <f>IFERROR(VLOOKUP(B52,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M52" s="26">
+        <f>IFERROR(VLOOKUP(B52,RemitTable2,11,FALSE),0)</f>
+        <v/>
       </c>
       <c r="N52" s="20" t="inlineStr">
         <is>
-          <t>EW (메가박스 외)</t>
+          <t>EW (홀딩)</t>
         </is>
       </c>
       <c r="O52" s="20" t="inlineStr">
@@ -7951,27 +7961,27 @@
       </c>
       <c r="AD52" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE52" s="184" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AF52" s="183" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="20" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="C53" s="21" t="inlineStr">
@@ -7986,36 +7996,36 @@
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F53" s="183" t="n">
-        <v>46060</v>
+        <v>46042</v>
       </c>
       <c r="G53" s="184" t="n">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="H53" s="24" t="n">
-        <v>3993.05</v>
+        <v>1440</v>
       </c>
       <c r="I53" s="185" t="n">
-        <v>1506.4</v>
+        <v>1453.6</v>
       </c>
       <c r="J53" s="26" t="n">
-        <v>6015131</v>
+        <v>2093184</v>
       </c>
       <c r="K53" s="26" t="n">
-        <v>6015131</v>
+        <v>2093184</v>
       </c>
       <c r="L53" s="26" t="n">
-        <v>6093</v>
+        <v>1241</v>
       </c>
       <c r="M53" s="26" t="n">
-        <v>4875</v>
+        <v>993</v>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
-          <t>SR/SX EW (하남미사 외)</t>
+          <t>TMS-2000 License</t>
         </is>
       </c>
       <c r="O53" s="20" t="inlineStr">
@@ -8088,17 +8098,17 @@
       </c>
       <c r="AF53" s="183" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="20" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="C54" s="21" t="inlineStr">
@@ -8113,36 +8123,36 @@
       </c>
       <c r="E54" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F54" s="183" t="n">
-        <v>46080</v>
+        <v>46042</v>
       </c>
       <c r="G54" s="184" t="n">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>360</v>
+        <v>4489</v>
       </c>
       <c r="I54" s="185" t="n">
-        <v>1506.4</v>
+        <v>1453.6</v>
       </c>
       <c r="J54" s="26" t="n">
-        <v>542304</v>
+        <v>6525210</v>
       </c>
       <c r="K54" s="26" t="n">
-        <v>542304</v>
+        <v>6525210</v>
       </c>
       <c r="L54" s="26" t="n">
-        <v>549</v>
+        <v>3870</v>
       </c>
       <c r="M54" s="26" t="n">
-        <v>439</v>
+        <v>3096</v>
       </c>
       <c r="N54" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 License</t>
+          <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
       <c r="O54" s="20" t="inlineStr">
@@ -8205,27 +8215,27 @@
       </c>
       <c r="AD54" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE54" s="184" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF54" s="183" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="C55" s="21" t="inlineStr">
@@ -8240,36 +8250,36 @@
       </c>
       <c r="E55" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F55" s="183" t="n">
-        <v>46088</v>
+        <v>46042</v>
       </c>
       <c r="G55" s="184" t="n">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>500</v>
+        <v>5670.57</v>
       </c>
       <c r="I55" s="185" t="n">
-        <v>1506.4</v>
+        <v>1453.6</v>
       </c>
       <c r="J55" s="26" t="n">
-        <v>753200</v>
+        <v>8242741</v>
       </c>
       <c r="K55" s="26" t="n">
-        <v>753200</v>
+        <v>8242741</v>
       </c>
       <c r="L55" s="26" t="n">
-        <v>763</v>
+        <v>4889</v>
       </c>
       <c r="M55" s="26" t="n">
-        <v>610</v>
+        <v>3911</v>
       </c>
       <c r="N55" s="20" t="inlineStr">
         <is>
-          <t>Dolby Atmos License</t>
+          <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
       <c r="O55" s="20" t="inlineStr">
@@ -8332,27 +8342,27 @@
       </c>
       <c r="AD55" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE55" s="184" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF55" s="183" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="20" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="C56" s="21" t="inlineStr">
@@ -8371,32 +8381,32 @@
         </is>
       </c>
       <c r="F56" s="183" t="n">
-        <v>46109</v>
+        <v>46057</v>
       </c>
       <c r="G56" s="184" t="n">
-        <v>46146</v>
+        <v>46113</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>17404</v>
+        <v>24614</v>
       </c>
       <c r="I56" s="185" t="n">
-        <v>1474.9</v>
+        <v>1505.7</v>
       </c>
       <c r="J56" s="26" t="n">
-        <v>25669160</v>
+        <v>37061300</v>
       </c>
       <c r="K56" s="26" t="n">
-        <v>25669160</v>
+        <v>37061300</v>
       </c>
       <c r="L56" s="26" t="n">
-        <v>10147</v>
+        <v>8956</v>
       </c>
       <c r="M56" s="26" t="n">
-        <v>6494</v>
+        <v>5732</v>
       </c>
       <c r="N56" s="20" t="inlineStr">
         <is>
-          <t>EW (CGV 동백 외)</t>
+          <t>EW (메가박스 외)</t>
         </is>
       </c>
       <c r="O56" s="20" t="inlineStr">
@@ -8459,1423 +8469,2154 @@
       </c>
       <c r="AD56" s="20" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE56" s="184" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AF56" s="183" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>GPO469</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E57" s="21" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F57" s="183" t="n">
+        <v>46060</v>
+      </c>
+      <c r="G57" s="184" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H57" s="24" t="n">
+        <v>3993.05</v>
+      </c>
+      <c r="I57" s="185" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="J57" s="26" t="n">
+        <v>6015131</v>
+      </c>
+      <c r="K57" s="26" t="n">
+        <v>6015131</v>
+      </c>
+      <c r="L57" s="26" t="n">
+        <v>6093</v>
+      </c>
+      <c r="M57" s="26" t="n">
+        <v>4875</v>
+      </c>
+      <c r="N57" s="20" t="inlineStr">
+        <is>
+          <t>SR/SX EW (하남미사 외)</t>
+        </is>
+      </c>
+      <c r="O57" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P57" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q57" s="24">
+        <f>IF(P57="","",IFERROR(VLOOKUP(O57,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R57" s="26">
+        <f>IF(P57="","",H57)</f>
+        <v/>
+      </c>
+      <c r="S57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="26">
+        <f>S57+T57+W57</f>
+        <v/>
+      </c>
+      <c r="AA57" s="26">
+        <f>K57+L57+M57+IFERROR(VLOOKUP(B57,RemitTable2,9,FALSE),0)+Y57+Z57</f>
+        <v/>
+      </c>
+      <c r="AB57" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="26">
+        <f>ROUND(AA57/AB57,0)</f>
+        <v/>
+      </c>
+      <c r="AD57" s="20" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AE57" s="184" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AF57" s="183" t="inlineStr">
+        <is>
+          <t>2027-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>GPO470</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F58" s="183" t="n">
+        <v>46080</v>
+      </c>
+      <c r="G58" s="184" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H58" s="24" t="n">
+        <v>360</v>
+      </c>
+      <c r="I58" s="185" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="J58" s="26" t="n">
+        <v>542304</v>
+      </c>
+      <c r="K58" s="26" t="n">
+        <v>542304</v>
+      </c>
+      <c r="L58" s="26" t="n">
+        <v>549</v>
+      </c>
+      <c r="M58" s="26" t="n">
+        <v>439</v>
+      </c>
+      <c r="N58" s="20" t="inlineStr">
+        <is>
+          <t>TMS-1000 License</t>
+        </is>
+      </c>
+      <c r="O58" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P58" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q58" s="24">
+        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R58" s="26">
+        <f>IF(P58="","",H58)</f>
+        <v/>
+      </c>
+      <c r="S58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="26">
+        <f>S58+T58+W58</f>
+        <v/>
+      </c>
+      <c r="AA58" s="26">
+        <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
+        <v/>
+      </c>
+      <c r="AB58" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="26">
+        <f>ROUND(AA58/AB58,0)</f>
+        <v/>
+      </c>
+      <c r="AD58" s="20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE58" s="184" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AF58" s="183" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>GPO471</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E59" s="21" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F59" s="183" t="n">
+        <v>46088</v>
+      </c>
+      <c r="G59" s="184" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H59" s="24" t="n">
+        <v>500</v>
+      </c>
+      <c r="I59" s="185" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="J59" s="26" t="n">
+        <v>753200</v>
+      </c>
+      <c r="K59" s="26" t="n">
+        <v>753200</v>
+      </c>
+      <c r="L59" s="26" t="n">
+        <v>763</v>
+      </c>
+      <c r="M59" s="26" t="n">
+        <v>610</v>
+      </c>
+      <c r="N59" s="20" t="inlineStr">
+        <is>
+          <t>Dolby Atmos License</t>
+        </is>
+      </c>
+      <c r="O59" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P59" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q59" s="24">
+        <f>IF(P59="","",IFERROR(VLOOKUP(O59,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R59" s="26">
+        <f>IF(P59="","",H59)</f>
+        <v/>
+      </c>
+      <c r="S59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="26">
+        <f>S59+T59+W59</f>
+        <v/>
+      </c>
+      <c r="AA59" s="26">
+        <f>K59+L59+M59+IFERROR(VLOOKUP(B59,RemitTable2,9,FALSE),0)+Y59+Z59</f>
+        <v/>
+      </c>
+      <c r="AB59" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="26">
+        <f>ROUND(AA59/AB59,0)</f>
+        <v/>
+      </c>
+      <c r="AD59" s="20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE59" s="184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF59" s="183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>CPO694</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F60" s="183" t="n">
+        <v>46109</v>
+      </c>
+      <c r="G60" s="184" t="n">
+        <v>46146</v>
+      </c>
+      <c r="H60" s="24" t="n">
+        <v>17404</v>
+      </c>
+      <c r="I60" s="185" t="n">
+        <v>1474.9</v>
+      </c>
+      <c r="J60" s="26" t="n">
+        <v>25669160</v>
+      </c>
+      <c r="K60" s="26" t="n">
+        <v>25669160</v>
+      </c>
+      <c r="L60" s="26" t="n">
+        <v>10147</v>
+      </c>
+      <c r="M60" s="26" t="n">
+        <v>6494</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
+        <is>
+          <t>EW (CGV 동백 외)</t>
+        </is>
+      </c>
+      <c r="O60" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P60" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q60" s="24">
+        <f>IF(P60="","",IFERROR(VLOOKUP(O60,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R60" s="26">
+        <f>IF(P60="","",H60)</f>
+        <v/>
+      </c>
+      <c r="S60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="26">
+        <f>S60+T60+W60</f>
+        <v/>
+      </c>
+      <c r="AA60" s="26">
+        <f>K60+L60+M60+IFERROR(VLOOKUP(B60,RemitTable2,9,FALSE),0)+Y60+Z60</f>
+        <v/>
+      </c>
+      <c r="AB60" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC60" s="26">
+        <f>ROUND(AA60/AB60,0)</f>
+        <v/>
+      </c>
+      <c r="AD60" s="20" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE56" s="184" t="inlineStr">
+      <c r="AE60" s="184" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AF56" s="183" t="inlineStr">
+      <c r="AF60" s="183" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="85" t="n">
+    <row r="61">
+      <c r="A61" s="85" t="n">
         <v>46</v>
       </c>
-      <c r="B57" s="85" t="inlineStr">
+      <c r="B61" s="85" t="inlineStr">
         <is>
           <t>CPO697</t>
         </is>
       </c>
-      <c r="C57" s="85" t="inlineStr">
+      <c r="C61" s="85" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D57" s="85" t="inlineStr">
+      <c r="D61" s="85" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E57" s="85" t="inlineStr">
+      <c r="E61" s="85" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F57" s="186" t="n">
+      <c r="F61" s="186" t="n">
         <v>46136</v>
       </c>
-      <c r="G57" s="186" t="n">
+      <c r="G61" s="186" t="n">
         <v>46171</v>
       </c>
-      <c r="H57" s="87" t="n">
+      <c r="H61" s="87" t="n">
         <v>15289</v>
       </c>
-      <c r="I57" s="187" t="n">
+      <c r="I61" s="187" t="n">
         <v>1502.7</v>
       </c>
-      <c r="J57" s="89" t="n">
+      <c r="J61" s="89" t="n">
         <v>22974780</v>
       </c>
-      <c r="K57" s="89" t="n">
+      <c r="K61" s="89" t="n">
         <v>22974780</v>
       </c>
-      <c r="L57" s="89" t="n">
+      <c r="L61" s="89" t="n">
         <v>1880</v>
       </c>
-      <c r="M57" s="89" t="n">
+      <c r="M61" s="89" t="n">
         <v>1203</v>
       </c>
-      <c r="N57" s="85" t="inlineStr">
+      <c r="N61" s="85" t="inlineStr">
         <is>
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O57" s="186" t="inlineStr">
+      <c r="O61" s="186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P57" s="85" t="inlineStr">
+      <c r="P61" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q57" s="87">
-        <f>IF(P57="","",IFERROR(VLOOKUP(O57,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R57" s="87">
-        <f>IF(P57="","",H57)</f>
-        <v/>
-      </c>
-      <c r="S57" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="186" t="n"/>
-      <c r="V57" s="85" t="inlineStr">
+      <c r="Q61" s="87">
+        <f>IF(P61="","",IFERROR(VLOOKUP(O61,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R61" s="87">
+        <f>IF(P61="","",H61)</f>
+        <v/>
+      </c>
+      <c r="S61" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="186" t="n"/>
+      <c r="V61" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W57" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" s="85" t="inlineStr">
+      <c r="W61" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y57" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="89">
-        <f>S57+T57+W57</f>
-        <v/>
-      </c>
-      <c r="AA57" s="89">
-        <f>K57+L57+M57+IFERROR(VLOOKUP(B57,RemitTable2,9,FALSE),0)+Y57+Z57</f>
-        <v/>
-      </c>
-      <c r="AB57" s="90" t="n">
+      <c r="Y61" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="89">
+        <f>S61+T61+W61</f>
+        <v/>
+      </c>
+      <c r="AA61" s="89">
+        <f>K61+L61+M61+IFERROR(VLOOKUP(B61,RemitTable2,9,FALSE),0)+Y61+Z61</f>
+        <v/>
+      </c>
+      <c r="AB61" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="AC57" s="89">
-        <f>ROUND(AA57/AB57,0)</f>
-        <v/>
-      </c>
-      <c r="AD57" s="85" t="inlineStr">
+      <c r="AC61" s="89">
+        <f>ROUND(AA61/AB61,0)</f>
+        <v/>
+      </c>
+      <c r="AD61" s="85" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE57" s="186" t="n">
+      <c r="AE61" s="186" t="n">
         <v>46168</v>
       </c>
-      <c r="AF57" s="186" t="n">
+      <c r="AF61" s="186" t="n">
         <v>46532</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="85" t="n">
+    <row r="62">
+      <c r="A62" s="85" t="n">
         <v>47</v>
       </c>
-      <c r="B58" s="85" t="inlineStr">
+      <c r="B62" s="85" t="inlineStr">
         <is>
           <t>CPO693-2</t>
         </is>
       </c>
-      <c r="C58" s="85" t="inlineStr">
+      <c r="C62" s="85" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D58" s="85" t="inlineStr">
+      <c r="D62" s="85" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E58" s="85" t="inlineStr">
+      <c r="E62" s="85" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F58" s="186" t="n">
+      <c r="F62" s="186" t="n">
         <v>46133</v>
       </c>
-      <c r="G58" s="186" t="inlineStr">
+      <c r="G62" s="186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H58" s="87" t="n">
+      <c r="H62" s="87" t="n">
         <v>2550</v>
       </c>
-      <c r="I58" s="187">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J58" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="89">
-        <f>IFERROR(ROUND(H58*I58,0),0)</f>
-        <v/>
-      </c>
-      <c r="L58" s="89">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M58" s="89">
-        <f>IFERROR(VLOOKUP(B58,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N58" s="85" t="inlineStr">
+      <c r="I62" s="187">
+        <f>IFERROR(VLOOKUP(B62,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J62" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="89">
+        <f>IFERROR(ROUND(H62*I62,0),0)</f>
+        <v/>
+      </c>
+      <c r="L62" s="89">
+        <f>IFERROR(VLOOKUP(B62,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M62" s="89">
+        <f>IFERROR(VLOOKUP(B62,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N62" s="85" t="inlineStr">
         <is>
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O58" s="186" t="inlineStr">
+      <c r="O62" s="186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P58" s="85" t="inlineStr">
+      <c r="P62" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q58" s="87">
-        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R58" s="87">
-        <f>IF(P58="","",H58)</f>
-        <v/>
-      </c>
-      <c r="S58" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="186" t="n"/>
-      <c r="V58" s="85" t="inlineStr">
+      <c r="Q62" s="87">
+        <f>IF(P62="","",IFERROR(VLOOKUP(O62,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R62" s="87">
+        <f>IF(P62="","",H62)</f>
+        <v/>
+      </c>
+      <c r="S62" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="186" t="n"/>
+      <c r="V62" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W58" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" s="85" t="inlineStr">
+      <c r="W62" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y58" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="89">
-        <f>S58+T58+W58</f>
-        <v/>
-      </c>
-      <c r="AA58" s="89">
-        <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
-        <v/>
-      </c>
-      <c r="AB58" s="90" t="n">
+      <c r="Y62" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="89">
+        <f>S62+T62+W62</f>
+        <v/>
+      </c>
+      <c r="AA62" s="89">
+        <f>K62+L62+M62+IFERROR(VLOOKUP(B62,RemitTable2,9,FALSE),0)+Y62+Z62</f>
+        <v/>
+      </c>
+      <c r="AB62" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="AC58" s="89">
-        <f>ROUND(AA58/AB58,0)</f>
-        <v/>
-      </c>
-      <c r="AD58" s="85" t="inlineStr">
+      <c r="AC62" s="89">
+        <f>ROUND(AA62/AB62,0)</f>
+        <v/>
+      </c>
+      <c r="AD62" s="85" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE58" s="186" t="n">
+      <c r="AE62" s="186" t="n">
         <v>46142</v>
       </c>
-      <c r="AF58" s="186" t="n">
+      <c r="AF62" s="186" t="n">
         <v>46872</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="132" t="n">
+    <row r="63">
+      <c r="A63" s="132" t="n">
         <v>54</v>
       </c>
-      <c r="B59" s="132" t="inlineStr">
+      <c r="B63" s="132" t="inlineStr">
         <is>
           <t>GPO478</t>
         </is>
       </c>
-      <c r="C59" s="132" t="inlineStr">
+      <c r="C63" s="132" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D59" s="132" t="inlineStr">
+      <c r="D63" s="132" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E59" s="132" t="inlineStr">
+      <c r="E63" s="132" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F59" s="188" t="n">
+      <c r="F63" s="188" t="n">
         <v>46127</v>
       </c>
-      <c r="G59" s="188" t="n">
+      <c r="G63" s="188" t="n">
         <v>46161</v>
       </c>
-      <c r="H59" s="134" t="n">
+      <c r="H63" s="134" t="n">
         <v>180</v>
       </c>
-      <c r="I59" s="134" t="n">
+      <c r="I63" s="134" t="n">
         <v>1518.9</v>
       </c>
-      <c r="J59" s="136" t="n">
+      <c r="J63" s="136" t="n">
         <v>273402</v>
       </c>
-      <c r="K59" s="136" t="n">
+      <c r="K63" s="136" t="n">
         <v>273402</v>
       </c>
-      <c r="L59" s="136" t="n">
+      <c r="L63" s="136" t="n">
         <v>2500</v>
       </c>
-      <c r="M59" s="136" t="n">
+      <c r="M63" s="136" t="n">
         <v>8000</v>
       </c>
-      <c r="N59" s="137" t="n"/>
-      <c r="O59" s="137" t="n"/>
-      <c r="P59" s="137" t="n"/>
-      <c r="Q59" s="134">
-        <f>IF(P59="","",IFERROR(VLOOKUP(O59,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R59" s="134">
-        <f>IF(P59="","",H59)</f>
-        <v/>
-      </c>
-      <c r="S59" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="137" t="n"/>
-      <c r="V59" s="137" t="n"/>
-      <c r="W59" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" s="132" t="inlineStr">
+      <c r="N63" s="137" t="n"/>
+      <c r="O63" s="137" t="n"/>
+      <c r="P63" s="137" t="n"/>
+      <c r="Q63" s="134">
+        <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R63" s="134">
+        <f>IF(P63="","",H63)</f>
+        <v/>
+      </c>
+      <c r="S63" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="137" t="n"/>
+      <c r="V63" s="137" t="n"/>
+      <c r="W63" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y59" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="136">
-        <f>S59+T59+W59</f>
-        <v/>
-      </c>
-      <c r="AA59" s="136">
-        <f>K59+L59+M59+IFERROR(VLOOKUP(B59,RemitTable2,9,FALSE),0)+Y59+Z59</f>
-        <v/>
-      </c>
-      <c r="AB59" s="168" t="n">
+      <c r="Y63" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="136">
+        <f>S63+T63+W63</f>
+        <v/>
+      </c>
+      <c r="AA63" s="136">
+        <f>K63+L63+M63+IFERROR(VLOOKUP(B63,RemitTable2,9,FALSE),0)+Y63+Z63</f>
+        <v/>
+      </c>
+      <c r="AB63" s="168" t="n">
         <v>2</v>
       </c>
-      <c r="AC59" s="136">
-        <f>ROUND(AA59/AB59,0)</f>
-        <v/>
-      </c>
-      <c r="AD59" s="137" t="inlineStr">
+      <c r="AC63" s="136">
+        <f>ROUND(AA63/AB63,0)</f>
+        <v/>
+      </c>
+      <c r="AD63" s="137" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE59" s="189" t="n">
+      <c r="AE63" s="189" t="n">
         <v>46143</v>
       </c>
-      <c r="AF59" s="189" t="n">
+      <c r="AF63" s="189" t="n">
         <v>46507</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="132" t="n">
+    <row r="64">
+      <c r="A64" s="132" t="n">
         <v>55</v>
       </c>
-      <c r="B60" s="132" t="inlineStr">
+      <c r="B64" s="132" t="inlineStr">
         <is>
           <t>GPO480</t>
         </is>
       </c>
-      <c r="C60" s="132" t="inlineStr">
+      <c r="C64" s="132" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D60" s="132" t="inlineStr">
+      <c r="D64" s="132" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E60" s="132" t="inlineStr">
+      <c r="E64" s="132" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F60" s="188" t="n">
+      <c r="F64" s="188" t="n">
         <v>46137</v>
       </c>
-      <c r="G60" s="188" t="n">
+      <c r="G64" s="188" t="n">
         <v>46171</v>
       </c>
-      <c r="H60" s="134" t="n">
+      <c r="H64" s="134" t="n">
         <v>250</v>
       </c>
-      <c r="I60" s="134" t="n">
+      <c r="I64" s="134" t="n">
         <v>1502.8</v>
       </c>
-      <c r="J60" s="136" t="n">
+      <c r="J64" s="136" t="n">
         <v>375700</v>
       </c>
-      <c r="K60" s="136" t="n">
+      <c r="K64" s="136" t="n">
         <v>375700</v>
       </c>
-      <c r="L60" s="136" t="n">
+      <c r="L64" s="136" t="n">
         <v>32</v>
       </c>
-      <c r="M60" s="136" t="n">
+      <c r="M64" s="136" t="n">
         <v>20</v>
       </c>
-      <c r="N60" s="137" t="n"/>
-      <c r="O60" s="137" t="n"/>
-      <c r="P60" s="137" t="n"/>
-      <c r="Q60" s="134">
-        <f>IF(P60="","",IFERROR(VLOOKUP(O60,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R60" s="134">
-        <f>IF(P60="","",H60)</f>
-        <v/>
-      </c>
-      <c r="S60" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="137" t="n"/>
-      <c r="V60" s="137" t="n"/>
-      <c r="W60" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="132" t="inlineStr">
+      <c r="N64" s="137" t="n"/>
+      <c r="O64" s="137" t="n"/>
+      <c r="P64" s="137" t="n"/>
+      <c r="Q64" s="134">
+        <f>IF(P64="","",IFERROR(VLOOKUP(O64,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R64" s="134">
+        <f>IF(P64="","",H64)</f>
+        <v/>
+      </c>
+      <c r="S64" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="137" t="n"/>
+      <c r="V64" s="137" t="n"/>
+      <c r="W64" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y60" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="136">
-        <f>S60+T60+W60</f>
-        <v/>
-      </c>
-      <c r="AA60" s="136">
-        <f>K60+L60+M60+IFERROR(VLOOKUP(B60,RemitTable2,9,FALSE),0)+Y60+Z60</f>
-        <v/>
-      </c>
-      <c r="AB60" s="168" t="n">
+      <c r="Y64" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="136">
+        <f>S64+T64+W64</f>
+        <v/>
+      </c>
+      <c r="AA64" s="136">
+        <f>K64+L64+M64+IFERROR(VLOOKUP(B64,RemitTable2,9,FALSE),0)+Y64+Z64</f>
+        <v/>
+      </c>
+      <c r="AB64" s="168" t="n">
         <v>1</v>
       </c>
-      <c r="AC60" s="136">
-        <f>ROUND(AA60/AB60,0)</f>
-        <v/>
-      </c>
-      <c r="AD60" s="137" t="inlineStr">
+      <c r="AC64" s="136">
+        <f>ROUND(AA64/AB64,0)</f>
+        <v/>
+      </c>
+      <c r="AD64" s="137" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE60" s="189" t="n">
+      <c r="AE64" s="189" t="n">
         <v>46143</v>
       </c>
-      <c r="AF60" s="189" t="n">
+      <c r="AF64" s="189" t="n">
         <v>49795</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="132" t="n">
+    <row r="65">
+      <c r="A65" s="132" t="n">
         <v>56</v>
       </c>
-      <c r="B61" s="132" t="inlineStr">
+      <c r="B65" s="132" t="inlineStr">
         <is>
           <t>GPO481</t>
         </is>
       </c>
-      <c r="C61" s="132" t="inlineStr">
+      <c r="C65" s="132" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D61" s="132" t="inlineStr">
+      <c r="D65" s="132" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E61" s="132" t="inlineStr">
+      <c r="E65" s="132" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F61" s="188" t="n">
+      <c r="F65" s="188" t="n">
         <v>46152</v>
       </c>
-      <c r="G61" s="233" t="n">
+      <c r="G65" s="233" t="n">
         <v>46183</v>
       </c>
-      <c r="H61" s="134" t="n">
+      <c r="H65" s="134" t="n">
         <v>500</v>
       </c>
-      <c r="I61" s="134" t="n">
+      <c r="I65" s="134" t="n">
         <v>1525.3</v>
       </c>
-      <c r="J61" s="136" t="n">
+      <c r="J65" s="136" t="n">
         <v>762650</v>
       </c>
-      <c r="K61" s="136" t="n">
+      <c r="K65" s="136" t="n">
         <v>762650</v>
       </c>
-      <c r="L61" s="136" t="n">
+      <c r="L65" s="136" t="n">
         <v>52</v>
       </c>
-      <c r="M61" s="136" t="n">
+      <c r="M65" s="136" t="n">
         <v>34</v>
       </c>
-      <c r="N61" s="137" t="n"/>
-      <c r="O61" s="137" t="n"/>
-      <c r="P61" s="137" t="n"/>
-      <c r="Q61" s="134">
-        <f>IF(P61="","",IFERROR(VLOOKUP(O61,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R61" s="134">
-        <f>IF(P61="","",H61)</f>
-        <v/>
-      </c>
-      <c r="S61" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="137" t="n"/>
-      <c r="V61" s="137" t="n"/>
-      <c r="W61" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" s="132" t="inlineStr">
+      <c r="N65" s="137" t="n"/>
+      <c r="O65" s="137" t="n"/>
+      <c r="P65" s="137" t="n"/>
+      <c r="Q65" s="134">
+        <f>IF(P65="","",IFERROR(VLOOKUP(O65,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R65" s="134">
+        <f>IF(P65="","",H65)</f>
+        <v/>
+      </c>
+      <c r="S65" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="137" t="n"/>
+      <c r="V65" s="137" t="n"/>
+      <c r="W65" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y61" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="136">
-        <f>S61+T61+W61</f>
-        <v/>
-      </c>
-      <c r="AA61" s="136">
-        <f>K61+L61+M61+IFERROR(VLOOKUP(B61,RemitTable2,9,FALSE),0)+Y61+Z61</f>
-        <v/>
-      </c>
-      <c r="AB61" s="168" t="n">
+      <c r="Y65" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="136">
+        <f>S65+T65+W65</f>
+        <v/>
+      </c>
+      <c r="AA65" s="136">
+        <f>K65+L65+M65+IFERROR(VLOOKUP(B65,RemitTable2,9,FALSE),0)+Y65+Z65</f>
+        <v/>
+      </c>
+      <c r="AB65" s="168" t="n">
         <v>1</v>
       </c>
-      <c r="AC61" s="136">
-        <f>ROUND(AA61/AB61,0)</f>
-        <v/>
-      </c>
-      <c r="AD61" s="137" t="inlineStr">
+      <c r="AC65" s="136">
+        <f>ROUND(AA65/AB65,0)</f>
+        <v/>
+      </c>
+      <c r="AD65" s="137" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE61" s="137" t="inlineStr">
+      <c r="AE65" s="137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF61" s="137" t="inlineStr">
+      <c r="AF65" s="137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="12" t="n">
+    <row r="66">
+      <c r="A66" s="132" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="132" t="inlineStr">
+        <is>
+          <t>GPO475</t>
+        </is>
+      </c>
+      <c r="C66" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D66" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E66" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F66" s="188" t="n">
+        <v>46127</v>
+      </c>
+      <c r="G66" s="188" t="n">
+        <v>46190</v>
+      </c>
+      <c r="H66" s="134" t="n">
+        <v>540</v>
+      </c>
+      <c r="I66" s="134" t="n">
+        <v>1516.8</v>
+      </c>
+      <c r="J66" s="136" t="n">
+        <v>819072</v>
+      </c>
+      <c r="K66" s="136" t="n">
+        <v>819072</v>
+      </c>
+      <c r="L66" s="136" t="n">
+        <v>1985</v>
+      </c>
+      <c r="M66" s="136" t="n">
+        <v>2118</v>
+      </c>
+      <c r="N66" s="137" t="inlineStr">
+        <is>
+          <t>TMS-1000 License 6 screens (CGV 안동)</t>
+        </is>
+      </c>
+      <c r="O66" s="137" t="n"/>
+      <c r="P66" s="137" t="n"/>
+      <c r="Q66" s="134">
+        <f>IF(P66="","",IFERROR(VLOOKUP(O66,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R66" s="134">
+        <f>IF(P66="","",H66)</f>
+        <v/>
+      </c>
+      <c r="S66" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="137" t="n"/>
+      <c r="V66" s="137" t="n"/>
+      <c r="W66" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y66" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="136">
+        <f>S66+T66+W66</f>
+        <v/>
+      </c>
+      <c r="AA66" s="136">
+        <f>K66+L66+M66+IFERROR(VLOOKUP(B66,RemitTable2,9,FALSE),0)+Y66+Z66</f>
+        <v/>
+      </c>
+      <c r="AB66" s="168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC66" s="136">
+        <f>ROUND(AA66/AB66,0)</f>
+        <v/>
+      </c>
+      <c r="AD66" s="137" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE66" s="189" t="n">
+        <v>46143</v>
+      </c>
+      <c r="AF66" s="189" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>CPO688</t>
         </is>
       </c>
-      <c r="C62" s="13" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="F62" s="176" t="n">
+      <c r="F67" s="176" t="n">
         <v>46037</v>
       </c>
-      <c r="G62" s="177" t="inlineStr">
+      <c r="G67" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H62" s="16" t="n">
+      <c r="H67" s="16" t="n">
         <v>4180</v>
       </c>
-      <c r="I62" s="178">
-        <f>IFERROR(VLOOKUP(B62,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J62" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="18">
-        <f>IFERROR(ROUND(H62*I62,0),0)</f>
-        <v/>
-      </c>
-      <c r="L62" s="18">
-        <f>IFERROR(VLOOKUP(B62,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M62" s="18">
-        <f>IFERROR(VLOOKUP(B62,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N62" s="12" t="inlineStr">
+      <c r="I67" s="178">
+        <f>IFERROR(VLOOKUP(B67,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J67" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="18">
+        <f>IFERROR(ROUND(H67*I67,0),0)</f>
+        <v/>
+      </c>
+      <c r="L67" s="18">
+        <f>IFERROR(VLOOKUP(B67,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M67" s="18">
+        <f>IFERROR(VLOOKUP(B67,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N67" s="12" t="inlineStr">
         <is>
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O62" s="12" t="inlineStr">
+      <c r="O67" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P62" s="12" t="inlineStr">
+      <c r="P67" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q62" s="16">
-        <f>IF(P62="","",IFERROR(VLOOKUP(O62,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R62" s="18">
-        <f>IF(P62="","",H62)</f>
-        <v/>
-      </c>
-      <c r="S62" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="12" t="inlineStr">
+      <c r="Q67" s="16">
+        <f>IF(P67="","",IFERROR(VLOOKUP(O67,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R67" s="18">
+        <f>IF(P67="","",H67)</f>
+        <v/>
+      </c>
+      <c r="S67" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W62" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="13" t="inlineStr">
+      <c r="W67" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y62" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="18">
-        <f>S62+T62+W62</f>
-        <v/>
-      </c>
-      <c r="AA62" s="18">
-        <f>K62+L62+M62+IFERROR(VLOOKUP(B62,RemitTable2,9,FALSE),0)+Y62+Z62</f>
-        <v/>
-      </c>
-      <c r="AB62" s="19" t="n">
+      <c r="Y67" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="18">
+        <f>S67+T67+W67</f>
+        <v/>
+      </c>
+      <c r="AA67" s="18">
+        <f>K67+L67+M67+IFERROR(VLOOKUP(B67,RemitTable2,9,FALSE),0)+Y67+Z67</f>
+        <v/>
+      </c>
+      <c r="AB67" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="AC62" s="18">
-        <f>ROUND(AA62/AB62,0)</f>
-        <v/>
-      </c>
-      <c r="AD62" s="12" t="inlineStr">
+      <c r="AC67" s="18">
+        <f>ROUND(AA67/AB67,0)</f>
+        <v/>
+      </c>
+      <c r="AD67" s="12" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE62" s="177" t="inlineStr">
+      <c r="AE67" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF62" s="176" t="inlineStr">
+      <c r="AF67" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="12" t="n">
+    <row r="68">
+      <c r="A68" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>SX3000수리</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>수리반환</t>
         </is>
       </c>
-      <c r="F63" s="176" t="n"/>
-      <c r="G63" s="177" t="inlineStr">
+      <c r="F68" s="176" t="n"/>
+      <c r="G68" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="16" t="n">
+      <c r="H68" s="16" t="n">
         <v>400</v>
       </c>
-      <c r="I63" s="178">
-        <f>IFERROR(VLOOKUP(B63,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J63" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="18">
-        <f>IFERROR(ROUND(H63*I63,0),0)</f>
-        <v/>
-      </c>
-      <c r="L63" s="18">
-        <f>IFERROR(VLOOKUP(B63,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M63" s="18">
-        <f>IFERROR(VLOOKUP(B63,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N63" s="12" t="inlineStr">
+      <c r="I68" s="178">
+        <f>IFERROR(VLOOKUP(B68,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J68" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="18">
+        <f>IFERROR(ROUND(H68*I68,0),0)</f>
+        <v/>
+      </c>
+      <c r="L68" s="18">
+        <f>IFERROR(VLOOKUP(B68,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M68" s="18">
+        <f>IFERROR(VLOOKUP(B68,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N68" s="12" t="inlineStr">
         <is>
           <t>Display Card (수리반환 5PCS)</t>
         </is>
       </c>
-      <c r="O63" s="177" t="n">
+      <c r="O68" s="177" t="n">
         <v>46125</v>
       </c>
-      <c r="P63" s="12" t="inlineStr">
+      <c r="P68" s="12" t="inlineStr">
         <is>
           <t>22356-26-351613M</t>
         </is>
       </c>
-      <c r="Q63" s="16">
-        <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R63" s="18">
-        <f>IF(P63="","",H63)</f>
-        <v/>
-      </c>
-      <c r="S63" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="18" t="n">
+      <c r="Q68" s="16">
+        <f>IF(P68="","",IFERROR(VLOOKUP(O68,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R68" s="18">
+        <f>IF(P68="","",H68)</f>
+        <v/>
+      </c>
+      <c r="S68" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="18" t="n">
         <v>67750</v>
       </c>
-      <c r="U63" s="13" t="n"/>
-      <c r="V63" s="12" t="inlineStr">
+      <c r="U68" s="13" t="n"/>
+      <c r="V68" s="12" t="inlineStr">
         <is>
           <t>운서합동</t>
         </is>
       </c>
-      <c r="W63" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" s="13" t="inlineStr">
+      <c r="W68" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" s="13" t="inlineStr">
         <is>
           <t>DHL</t>
         </is>
       </c>
-      <c r="Y63" s="18" t="n">
+      <c r="Y68" s="18" t="n">
         <v>216006</v>
       </c>
-      <c r="Z63" s="18">
-        <f>S63+T63+W63</f>
-        <v/>
-      </c>
-      <c r="AA63" s="18">
-        <f>K63+L63+M63+IFERROR(VLOOKUP(B63,RemitTable2,9,FALSE),0)+Y63+Z63</f>
-        <v/>
-      </c>
-      <c r="AB63" s="19" t="n">
+      <c r="Z68" s="18">
+        <f>S68+T68+W68</f>
+        <v/>
+      </c>
+      <c r="AA68" s="18">
+        <f>K68+L68+M68+IFERROR(VLOOKUP(B68,RemitTable2,9,FALSE),0)+Y68+Z68</f>
+        <v/>
+      </c>
+      <c r="AB68" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="AC63" s="18">
-        <f>ROUND(AA63/AB63,0)</f>
-        <v/>
-      </c>
-      <c r="AD63" s="12" t="inlineStr">
+      <c r="AC68" s="18">
+        <f>ROUND(AA68/AB68,0)</f>
+        <v/>
+      </c>
+      <c r="AD68" s="12" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE63" s="177" t="n"/>
-      <c r="AF63" s="176" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="216" t="n">
+      <c r="AE68" s="177" t="n"/>
+      <c r="AF68" s="176" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="216" t="n">
         <v>59</v>
       </c>
-      <c r="B64" s="216" t="inlineStr">
+      <c r="B69" s="216" t="inlineStr">
         <is>
           <t>FRC-MONOPLEX26</t>
         </is>
       </c>
-      <c r="C64" s="217" t="inlineStr">
+      <c r="C69" s="217" t="inlineStr">
         <is>
           <t>Ferco</t>
         </is>
       </c>
-      <c r="D64" s="216" t="inlineStr">
+      <c r="D69" s="216" t="inlineStr">
         <is>
           <t>50% TT advance + 50% balance</t>
         </is>
       </c>
-      <c r="E64" s="217" t="inlineStr">
+      <c r="E69" s="217" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="F64" s="218" t="n">
+      <c r="F69" s="218" t="n">
         <v>46048</v>
       </c>
-      <c r="G64" s="219" t="n">
+      <c r="G69" s="219" t="n">
         <v>46133</v>
       </c>
-      <c r="H64" s="220" t="n">
+      <c r="H69" s="220" t="n">
         <v>51952</v>
       </c>
-      <c r="I64" s="221">
-        <f>IFERROR(VLOOKUP(B64,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J64" s="222" t="n">
+      <c r="I69" s="221">
+        <f>IFERROR(VLOOKUP(B69,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J69" s="222" t="n">
         <v>75818749</v>
       </c>
-      <c r="K64" s="222" t="n">
+      <c r="K69" s="222" t="n">
         <v>75818749</v>
       </c>
-      <c r="L64" s="222" t="n">
+      <c r="L69" s="222" t="n">
         <v>25000</v>
       </c>
-      <c r="M64" s="222" t="n">
+      <c r="M69" s="222" t="n">
         <v>16000</v>
       </c>
-      <c r="N64" s="216" t="inlineStr">
+      <c r="N69" s="216" t="inlineStr">
         <is>
           <t>Cinema Seat (Recliner) / 44 EA / Monoplex DH Bangbae</t>
         </is>
       </c>
-      <c r="O64" s="219" t="n">
+      <c r="O69" s="219" t="n">
         <v>46153</v>
       </c>
-      <c r="P64" s="216" t="inlineStr">
+      <c r="P69" s="216" t="inlineStr">
         <is>
           <t>14008-26-101147M</t>
         </is>
       </c>
-      <c r="Q64" s="220">
-        <f>IF(P64="","",IFERROR(VLOOKUP(O64,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R64" s="220">
-        <f>IF(P64="","",H64)</f>
-        <v/>
-      </c>
-      <c r="S64" s="222" t="n">
+      <c r="Q69" s="220">
+        <f>IF(P69="","",IFERROR(VLOOKUP(O69,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R69" s="220">
+        <f>IF(P69="","",H69)</f>
+        <v/>
+      </c>
+      <c r="S69" s="222" t="n">
         <v>31050</v>
       </c>
-      <c r="T64" s="222" t="n">
+      <c r="T69" s="222" t="n">
         <v>7959560</v>
       </c>
-      <c r="U64" s="218" t="n"/>
-      <c r="V64" s="216" t="inlineStr">
+      <c r="U69" s="218" t="n"/>
+      <c r="V69" s="216" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
       </c>
-      <c r="W64" s="222" t="n">
+      <c r="W69" s="222" t="n">
         <v>250000</v>
       </c>
-      <c r="X64" s="217" t="inlineStr">
+      <c r="X69" s="217" t="inlineStr">
         <is>
           <t>진로직스</t>
         </is>
       </c>
-      <c r="Y64" s="222" t="n">
+      <c r="Y69" s="222" t="n">
         <v>5002612</v>
       </c>
-      <c r="Z64" s="222">
-        <f>S64+T64+W64</f>
-        <v/>
-      </c>
-      <c r="AA64" s="222">
-        <f>K64+L64+M64+IFERROR(VLOOKUP(B64,RemitTable2,9,FALSE),0)+Y64+Z64</f>
-        <v/>
-      </c>
-      <c r="AB64" s="223" t="n">
+      <c r="Z69" s="222">
+        <f>S69+T69+W69</f>
+        <v/>
+      </c>
+      <c r="AA69" s="222">
+        <f>K69+L69+M69+IFERROR(VLOOKUP(B69,RemitTable2,9,FALSE),0)+Y69+Z69</f>
+        <v/>
+      </c>
+      <c r="AB69" s="223" t="n">
         <v>44</v>
       </c>
-      <c r="AC64" s="222">
-        <f>ROUND(AA64/AB64,0)</f>
-        <v/>
-      </c>
-      <c r="AD64" s="216" t="inlineStr">
+      <c r="AC69" s="222">
+        <f>ROUND(AA69/AB69,0)</f>
+        <v/>
+      </c>
+      <c r="AD69" s="216" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE64" s="216" t="n"/>
-      <c r="AF64" s="217" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="147" t="inlineStr">
+      <c r="AE69" s="216" t="n"/>
+      <c r="AF69" s="217" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="284" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="284" t="inlineStr">
+        <is>
+          <t>GPO475-수리</t>
+        </is>
+      </c>
+      <c r="C70" s="285" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D70" s="284" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E70" s="285" t="inlineStr">
+        <is>
+          <t>수리</t>
+        </is>
+      </c>
+      <c r="F70" s="286" t="n">
+        <v>46126</v>
+      </c>
+      <c r="G70" s="287" t="n">
+        <v>46190</v>
+      </c>
+      <c r="H70" s="288" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I70" s="289" t="n">
+        <v>1516.8</v>
+      </c>
+      <c r="J70" s="290" t="n">
+        <v>2275200</v>
+      </c>
+      <c r="K70" s="290" t="n">
+        <v>2275200</v>
+      </c>
+      <c r="L70" s="290" t="n">
+        <v>5515</v>
+      </c>
+      <c r="M70" s="290" t="n">
+        <v>5882</v>
+      </c>
+      <c r="N70" s="284" t="inlineStr">
+        <is>
+          <t>SR-1000 IMB Inspection+Repair (SN A78267)</t>
+        </is>
+      </c>
+      <c r="O70" s="287" t="n"/>
+      <c r="P70" s="284" t="n"/>
+      <c r="Q70" s="288">
+        <f>IF(P70="","",IFERROR(VLOOKUP(O70,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R70" s="290">
+        <f>IF(P70="","",H70)</f>
+        <v/>
+      </c>
+      <c r="S70" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="285" t="n"/>
+      <c r="V70" s="284" t="n"/>
+      <c r="W70" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y70" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="290">
+        <f>S70+T70+W70</f>
+        <v/>
+      </c>
+      <c r="AA70" s="290">
+        <f>K70+L70+M70+IFERROR(VLOOKUP(B70,RemitTable2,9,FALSE),0)+Y70+Z70</f>
+        <v/>
+      </c>
+      <c r="AB70" s="291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC70" s="290">
+        <f>ROUND(AA70/AB70,0)</f>
+        <v/>
+      </c>
+      <c r="AD70" s="284" t="n"/>
+      <c r="AE70" s="287" t="n"/>
+      <c r="AF70" s="286" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="147" t="inlineStr">
         <is>
           <t>장비/부품 합계</t>
         </is>
       </c>
-      <c r="B65" s="148" t="n"/>
-      <c r="C65" s="148" t="n"/>
-      <c r="D65" s="148" t="n"/>
-      <c r="E65" s="148" t="n"/>
-      <c r="F65" s="148" t="n"/>
-      <c r="G65" s="149" t="n"/>
-      <c r="H65" s="142">
-        <f>SUBTOTAL(9,H5:H39)</f>
-        <v/>
-      </c>
-      <c r="I65" s="141" t="n"/>
-      <c r="J65" s="142">
+      <c r="B71" s="148" t="n"/>
+      <c r="C71" s="148" t="n"/>
+      <c r="D71" s="148" t="n"/>
+      <c r="E71" s="148" t="n"/>
+      <c r="F71" s="148" t="n"/>
+      <c r="G71" s="149" t="n"/>
+      <c r="H71" s="142">
+        <f>SUBTOTAL(9,H5:H43)</f>
+        <v/>
+      </c>
+      <c r="I71" s="141" t="n"/>
+      <c r="J71" s="142">
         <f>SUBTOTAL(9,J5:J39)</f>
         <v/>
       </c>
-      <c r="K65" s="142">
-        <f>SUBTOTAL(9,K5:K39)</f>
-        <v/>
-      </c>
-      <c r="L65" s="142">
-        <f>SUBTOTAL(9,L5:L39)</f>
-        <v/>
-      </c>
-      <c r="M65" s="142">
-        <f>SUBTOTAL(9,M5:M39)</f>
-        <v/>
-      </c>
-      <c r="N65" s="141" t="n"/>
-      <c r="O65" s="141" t="n"/>
-      <c r="P65" s="141" t="n"/>
-      <c r="Q65" s="142" t="n"/>
-      <c r="R65" s="140" t="n"/>
-      <c r="S65" s="142">
-        <f>SUBTOTAL(9,S5:S39)</f>
-        <v/>
-      </c>
-      <c r="T65" s="142">
-        <f>SUBTOTAL(9,T5:T39)</f>
-        <v/>
-      </c>
-      <c r="U65" s="141" t="n"/>
-      <c r="V65" s="141" t="n"/>
-      <c r="W65" s="142">
-        <f>SUBTOTAL(9,W5:W39)</f>
-        <v/>
-      </c>
-      <c r="X65" s="147" t="n"/>
-      <c r="Y65" s="142">
-        <f>SUBTOTAL(9,Y5:Y39)</f>
-        <v/>
-      </c>
-      <c r="Z65" s="142">
-        <f>SUBTOTAL(9,Z5:Z39)</f>
-        <v/>
-      </c>
-      <c r="AA65" s="142">
-        <f>SUBTOTAL(9,AA5:AA39)</f>
-        <v/>
-      </c>
-      <c r="AB65" s="147" t="n"/>
-      <c r="AC65" s="141" t="n"/>
-      <c r="AD65" s="141" t="n"/>
-      <c r="AE65" s="141" t="n"/>
-      <c r="AF65" s="141" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="147" t="inlineStr">
+      <c r="K71" s="142">
+        <f>SUBTOTAL(9,K5:K43)</f>
+        <v/>
+      </c>
+      <c r="L71" s="142">
+        <f>SUBTOTAL(9,L5:L43)</f>
+        <v/>
+      </c>
+      <c r="M71" s="142">
+        <f>SUBTOTAL(9,M5:M43)</f>
+        <v/>
+      </c>
+      <c r="N71" s="141" t="n"/>
+      <c r="O71" s="141" t="n"/>
+      <c r="P71" s="141" t="n"/>
+      <c r="Q71" s="142" t="n"/>
+      <c r="R71" s="140" t="n"/>
+      <c r="S71" s="142">
+        <f>SUBTOTAL(9,S5:S43)</f>
+        <v/>
+      </c>
+      <c r="T71" s="142">
+        <f>SUBTOTAL(9,T5:T43)</f>
+        <v/>
+      </c>
+      <c r="U71" s="141" t="n"/>
+      <c r="V71" s="141" t="n"/>
+      <c r="W71" s="142">
+        <f>SUBTOTAL(9,W5:W43)</f>
+        <v/>
+      </c>
+      <c r="X71" s="147" t="n"/>
+      <c r="Y71" s="142">
+        <f>SUBTOTAL(9,Y5:Y43)</f>
+        <v/>
+      </c>
+      <c r="Z71" s="142">
+        <f>SUBTOTAL(9,Z5:Z43)</f>
+        <v/>
+      </c>
+      <c r="AA71" s="142">
+        <f>SUBTOTAL(9,AA5:AA43)</f>
+        <v/>
+      </c>
+      <c r="AB71" s="147" t="n"/>
+      <c r="AC71" s="141" t="n"/>
+      <c r="AD71" s="141" t="n"/>
+      <c r="AE71" s="141" t="n"/>
+      <c r="AF71" s="141" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="147" t="inlineStr">
         <is>
           <t>라이센스/워런티 합계</t>
         </is>
       </c>
-      <c r="B66" s="148" t="n"/>
-      <c r="C66" s="148" t="n"/>
-      <c r="D66" s="148" t="n"/>
-      <c r="E66" s="148" t="n"/>
-      <c r="F66" s="148" t="n"/>
-      <c r="G66" s="149" t="n"/>
-      <c r="H66" s="142">
-        <f>SUBTOTAL(9,H40:H61)</f>
-        <v/>
-      </c>
-      <c r="I66" s="141" t="n"/>
-      <c r="J66" s="142">
+      <c r="B72" s="148" t="n"/>
+      <c r="C72" s="148" t="n"/>
+      <c r="D72" s="148" t="n"/>
+      <c r="E72" s="148" t="n"/>
+      <c r="F72" s="148" t="n"/>
+      <c r="G72" s="149" t="n"/>
+      <c r="H72" s="142">
+        <f>SUBTOTAL(9,H44:H66)</f>
+        <v/>
+      </c>
+      <c r="I72" s="141" t="n"/>
+      <c r="J72" s="142">
         <f>SUBTOTAL(9,J40:J61)</f>
         <v/>
       </c>
-      <c r="K66" s="142">
-        <f>SUBTOTAL(9,K40:K61)</f>
-        <v/>
-      </c>
-      <c r="L66" s="142">
-        <f>SUBTOTAL(9,L40:L61)</f>
-        <v/>
-      </c>
-      <c r="M66" s="142">
-        <f>SUBTOTAL(9,M40:M61)</f>
-        <v/>
-      </c>
-      <c r="N66" s="141" t="n"/>
-      <c r="O66" s="141" t="n"/>
-      <c r="P66" s="141" t="n"/>
-      <c r="Q66" s="142" t="n"/>
-      <c r="R66" s="140" t="n"/>
-      <c r="S66" s="142">
-        <f>SUBTOTAL(9,S40:S61)</f>
-        <v/>
-      </c>
-      <c r="T66" s="142">
-        <f>SUBTOTAL(9,T40:T61)</f>
-        <v/>
-      </c>
-      <c r="U66" s="141" t="n"/>
-      <c r="V66" s="141" t="n"/>
-      <c r="W66" s="142">
-        <f>SUBTOTAL(9,W40:W61)</f>
-        <v/>
-      </c>
-      <c r="X66" s="147" t="n"/>
-      <c r="Y66" s="142">
-        <f>SUBTOTAL(9,Y40:Y61)</f>
-        <v/>
-      </c>
-      <c r="Z66" s="142">
-        <f>SUBTOTAL(9,Z40:Z61)</f>
-        <v/>
-      </c>
-      <c r="AA66" s="142">
-        <f>SUBTOTAL(9,AA40:AA61)</f>
-        <v/>
-      </c>
-      <c r="AB66" s="147" t="n"/>
-      <c r="AC66" s="141" t="n"/>
-      <c r="AD66" s="141" t="n"/>
-      <c r="AE66" s="141" t="n"/>
-      <c r="AF66" s="141" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="147" t="inlineStr">
+      <c r="K72" s="142">
+        <f>SUBTOTAL(9,K44:K66)</f>
+        <v/>
+      </c>
+      <c r="L72" s="142">
+        <f>SUBTOTAL(9,L44:L66)</f>
+        <v/>
+      </c>
+      <c r="M72" s="142">
+        <f>SUBTOTAL(9,M44:M66)</f>
+        <v/>
+      </c>
+      <c r="N72" s="141" t="n"/>
+      <c r="O72" s="141" t="n"/>
+      <c r="P72" s="141" t="n"/>
+      <c r="Q72" s="142" t="n"/>
+      <c r="R72" s="140" t="n"/>
+      <c r="S72" s="142">
+        <f>SUBTOTAL(9,S44:S66)</f>
+        <v/>
+      </c>
+      <c r="T72" s="142">
+        <f>SUBTOTAL(9,T44:T66)</f>
+        <v/>
+      </c>
+      <c r="U72" s="141" t="n"/>
+      <c r="V72" s="141" t="n"/>
+      <c r="W72" s="142">
+        <f>SUBTOTAL(9,W44:W66)</f>
+        <v/>
+      </c>
+      <c r="X72" s="147" t="n"/>
+      <c r="Y72" s="142">
+        <f>SUBTOTAL(9,Y44:Y66)</f>
+        <v/>
+      </c>
+      <c r="Z72" s="142">
+        <f>SUBTOTAL(9,Z44:Z66)</f>
+        <v/>
+      </c>
+      <c r="AA72" s="142">
+        <f>SUBTOTAL(9,AA44:AA66)</f>
+        <v/>
+      </c>
+      <c r="AB72" s="147" t="n"/>
+      <c r="AC72" s="141" t="n"/>
+      <c r="AD72" s="141" t="n"/>
+      <c r="AE72" s="141" t="n"/>
+      <c r="AF72" s="141" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="147" t="inlineStr">
         <is>
           <t>기타 합계</t>
         </is>
       </c>
-      <c r="B67" s="148" t="n"/>
-      <c r="C67" s="148" t="n"/>
-      <c r="D67" s="148" t="n"/>
-      <c r="E67" s="148" t="n"/>
-      <c r="F67" s="148" t="n"/>
-      <c r="G67" s="149" t="n"/>
-      <c r="H67" s="142">
-        <f>SUBTOTAL(9,H62:H64)</f>
-        <v/>
-      </c>
-      <c r="I67" s="141" t="n"/>
-      <c r="J67" s="142">
+      <c r="B73" s="148" t="n"/>
+      <c r="C73" s="148" t="n"/>
+      <c r="D73" s="148" t="n"/>
+      <c r="E73" s="148" t="n"/>
+      <c r="F73" s="148" t="n"/>
+      <c r="G73" s="149" t="n"/>
+      <c r="H73" s="142">
+        <f>SUBTOTAL(9,H67:H70)</f>
+        <v/>
+      </c>
+      <c r="I73" s="141" t="n"/>
+      <c r="J73" s="142">
         <f>SUBTOTAL(9,J62:J64)</f>
         <v/>
       </c>
-      <c r="K67" s="142">
-        <f>SUBTOTAL(9,K62:K64)</f>
-        <v/>
-      </c>
-      <c r="L67" s="142">
-        <f>SUBTOTAL(9,L62:L64)</f>
-        <v/>
-      </c>
-      <c r="M67" s="142">
-        <f>SUBTOTAL(9,M62:M64)</f>
-        <v/>
-      </c>
-      <c r="N67" s="141" t="n"/>
-      <c r="O67" s="141" t="n"/>
-      <c r="P67" s="141" t="n"/>
-      <c r="Q67" s="142" t="n"/>
-      <c r="R67" s="140" t="n"/>
-      <c r="S67" s="142">
-        <f>SUBTOTAL(9,S62:S64)</f>
-        <v/>
-      </c>
-      <c r="T67" s="142">
-        <f>SUBTOTAL(9,T62:T64)</f>
-        <v/>
-      </c>
-      <c r="U67" s="141" t="n"/>
-      <c r="V67" s="141" t="n"/>
-      <c r="W67" s="142">
-        <f>SUBTOTAL(9,W62:W64)</f>
-        <v/>
-      </c>
-      <c r="X67" s="147" t="n"/>
-      <c r="Y67" s="142">
-        <f>SUBTOTAL(9,Y62:Y64)</f>
-        <v/>
-      </c>
-      <c r="Z67" s="142">
-        <f>SUBTOTAL(9,Z62:Z64)</f>
-        <v/>
-      </c>
-      <c r="AA67" s="142">
-        <f>SUBTOTAL(9,AA62:AA64)</f>
-        <v/>
-      </c>
-      <c r="AB67" s="147" t="n"/>
-      <c r="AC67" s="141" t="n"/>
-      <c r="AD67" s="141" t="n"/>
-      <c r="AE67" s="141" t="n"/>
-      <c r="AF67" s="141" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="154" t="inlineStr">
+      <c r="K73" s="142">
+        <f>SUBTOTAL(9,K67:K70)</f>
+        <v/>
+      </c>
+      <c r="L73" s="142">
+        <f>SUBTOTAL(9,L67:L70)</f>
+        <v/>
+      </c>
+      <c r="M73" s="142">
+        <f>SUBTOTAL(9,M67:M70)</f>
+        <v/>
+      </c>
+      <c r="N73" s="141" t="n"/>
+      <c r="O73" s="141" t="n"/>
+      <c r="P73" s="141" t="n"/>
+      <c r="Q73" s="142" t="n"/>
+      <c r="R73" s="140" t="n"/>
+      <c r="S73" s="142">
+        <f>SUBTOTAL(9,S67:S70)</f>
+        <v/>
+      </c>
+      <c r="T73" s="142">
+        <f>SUBTOTAL(9,T67:T70)</f>
+        <v/>
+      </c>
+      <c r="U73" s="141" t="n"/>
+      <c r="V73" s="141" t="n"/>
+      <c r="W73" s="142">
+        <f>SUBTOTAL(9,W67:W70)</f>
+        <v/>
+      </c>
+      <c r="X73" s="147" t="n"/>
+      <c r="Y73" s="142">
+        <f>SUBTOTAL(9,Y67:Y70)</f>
+        <v/>
+      </c>
+      <c r="Z73" s="142">
+        <f>SUBTOTAL(9,Z67:Z70)</f>
+        <v/>
+      </c>
+      <c r="AA73" s="142">
+        <f>SUBTOTAL(9,AA67:AA70)</f>
+        <v/>
+      </c>
+      <c r="AB73" s="147" t="n"/>
+      <c r="AC73" s="141" t="n"/>
+      <c r="AD73" s="141" t="n"/>
+      <c r="AE73" s="141" t="n"/>
+      <c r="AF73" s="141" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="154" t="inlineStr">
         <is>
           <t>총 합계</t>
         </is>
       </c>
-      <c r="B68" s="148" t="n"/>
-      <c r="C68" s="148" t="n"/>
-      <c r="D68" s="148" t="n"/>
-      <c r="E68" s="148" t="n"/>
-      <c r="F68" s="148" t="n"/>
-      <c r="G68" s="149" t="n"/>
-      <c r="H68" s="146">
-        <f>SUBTOTAL(9,H5:H64)</f>
-        <v/>
-      </c>
-      <c r="I68" s="145" t="n"/>
-      <c r="J68" s="146">
+      <c r="B74" s="148" t="n"/>
+      <c r="C74" s="148" t="n"/>
+      <c r="D74" s="148" t="n"/>
+      <c r="E74" s="148" t="n"/>
+      <c r="F74" s="148" t="n"/>
+      <c r="G74" s="149" t="n"/>
+      <c r="H74" s="146">
+        <f>SUBTOTAL(9,H5:H70)</f>
+        <v/>
+      </c>
+      <c r="I74" s="145" t="n"/>
+      <c r="J74" s="146">
         <f>SUBTOTAL(9,J5:J64)</f>
         <v/>
       </c>
-      <c r="K68" s="146">
-        <f>SUBTOTAL(9,K5:K64)</f>
-        <v/>
-      </c>
-      <c r="L68" s="146">
-        <f>SUBTOTAL(9,L5:L64)</f>
-        <v/>
-      </c>
-      <c r="M68" s="146">
-        <f>SUBTOTAL(9,M5:M64)</f>
-        <v/>
-      </c>
-      <c r="N68" s="145" t="n"/>
-      <c r="O68" s="145" t="n"/>
-      <c r="P68" s="145" t="n"/>
-      <c r="Q68" s="146" t="n"/>
-      <c r="R68" s="144" t="n"/>
-      <c r="S68" s="146">
-        <f>SUBTOTAL(9,S5:S64)</f>
-        <v/>
-      </c>
-      <c r="T68" s="146">
-        <f>SUBTOTAL(9,T5:T64)</f>
-        <v/>
-      </c>
-      <c r="U68" s="145" t="n"/>
-      <c r="V68" s="145" t="n"/>
-      <c r="W68" s="146">
-        <f>SUBTOTAL(9,W5:W64)</f>
-        <v/>
-      </c>
-      <c r="X68" s="154" t="n"/>
-      <c r="Y68" s="146">
-        <f>SUBTOTAL(9,Y5:Y64)</f>
-        <v/>
-      </c>
-      <c r="Z68" s="146">
-        <f>SUBTOTAL(9,Z5:Z64)</f>
-        <v/>
-      </c>
-      <c r="AA68" s="146">
-        <f>SUBTOTAL(9,AA5:AA64)</f>
-        <v/>
-      </c>
-      <c r="AB68" s="154" t="n"/>
-      <c r="AC68" s="145" t="n"/>
-      <c r="AD68" s="145" t="n"/>
-      <c r="AE68" s="145" t="n"/>
-      <c r="AF68" s="145" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="39" t="n"/>
-      <c r="B69" s="39" t="n"/>
-      <c r="C69" s="39" t="n"/>
-      <c r="D69" s="39" t="n"/>
-      <c r="E69" s="39" t="n"/>
-      <c r="F69" s="39" t="n"/>
-      <c r="G69" s="39" t="n"/>
-      <c r="H69" s="39" t="n"/>
-      <c r="I69" s="39" t="n"/>
-      <c r="J69" s="39" t="n"/>
-      <c r="K69" s="39" t="n"/>
-      <c r="L69" s="39" t="n"/>
-      <c r="M69" s="39" t="n"/>
-      <c r="N69" s="39" t="n"/>
-      <c r="O69" s="39" t="n"/>
-      <c r="P69" s="39" t="n"/>
-      <c r="Q69" s="39" t="n"/>
-      <c r="R69" s="39" t="n"/>
-      <c r="S69" s="39" t="n"/>
-      <c r="T69" s="39" t="n"/>
-      <c r="U69" s="39" t="n"/>
-      <c r="V69" s="39" t="n"/>
-      <c r="W69" s="39" t="n"/>
-      <c r="X69" s="75" t="n"/>
-      <c r="Y69" s="39" t="n"/>
-      <c r="Z69" s="39" t="n"/>
-      <c r="AA69" s="39" t="n"/>
-      <c r="AB69" s="75" t="n"/>
-      <c r="AC69" s="39" t="n"/>
-      <c r="AD69" s="39" t="n"/>
-      <c r="AE69" s="39" t="n"/>
-      <c r="AF69" s="39" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="39" t="n"/>
-      <c r="B70" s="39" t="n"/>
-      <c r="C70" s="39" t="n"/>
-      <c r="D70" s="39" t="n"/>
-      <c r="E70" s="39" t="n"/>
-      <c r="F70" s="39" t="n"/>
-      <c r="G70" s="39" t="n"/>
-      <c r="H70" s="39" t="n"/>
-      <c r="I70" s="39" t="n"/>
-      <c r="J70" s="39" t="n"/>
-      <c r="K70" s="39" t="n"/>
-      <c r="L70" s="39" t="n"/>
-      <c r="M70" s="39" t="n"/>
-      <c r="N70" s="39" t="n"/>
-      <c r="O70" s="39" t="n"/>
-      <c r="P70" s="39" t="n"/>
-      <c r="Q70" s="39" t="n"/>
-      <c r="R70" s="39" t="n"/>
-      <c r="S70" s="39" t="n"/>
-      <c r="T70" s="39" t="n"/>
-      <c r="U70" s="39" t="n"/>
-      <c r="V70" s="39" t="n"/>
-      <c r="W70" s="39" t="n"/>
-      <c r="X70" s="75" t="n"/>
-      <c r="Y70" s="39" t="n"/>
-      <c r="Z70" s="39" t="n"/>
-      <c r="AA70" s="39" t="n"/>
-      <c r="AB70" s="75" t="n"/>
-      <c r="AC70" s="39" t="n"/>
-      <c r="AD70" s="39" t="n"/>
-      <c r="AE70" s="39" t="n"/>
-      <c r="AF70" s="39" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="39" t="n"/>
-      <c r="B71" s="39" t="n"/>
-      <c r="C71" s="39" t="n"/>
-      <c r="D71" s="39" t="n"/>
-      <c r="E71" s="39" t="n"/>
-      <c r="F71" s="39" t="n"/>
-      <c r="G71" s="39" t="n"/>
-      <c r="H71" s="39" t="n"/>
-      <c r="I71" s="39" t="n"/>
-      <c r="J71" s="39" t="n"/>
-      <c r="K71" s="39" t="n"/>
-      <c r="L71" s="39" t="n"/>
-      <c r="M71" s="39" t="n"/>
-      <c r="N71" s="39" t="n"/>
-      <c r="O71" s="39" t="n"/>
-      <c r="P71" s="39" t="n"/>
-      <c r="Q71" s="39" t="n"/>
-      <c r="R71" s="39" t="n"/>
-      <c r="S71" s="39" t="n"/>
-      <c r="T71" s="39" t="n"/>
-      <c r="U71" s="39" t="n"/>
-      <c r="V71" s="39" t="n"/>
-      <c r="W71" s="39" t="n"/>
-      <c r="X71" s="75" t="n"/>
-      <c r="Y71" s="39" t="n"/>
-      <c r="Z71" s="39" t="n"/>
-      <c r="AA71" s="39" t="n"/>
-      <c r="AB71" s="75" t="n"/>
-      <c r="AC71" s="39" t="n"/>
-      <c r="AD71" s="39" t="n"/>
-      <c r="AE71" s="39" t="n"/>
-      <c r="AF71" s="39" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="39" t="n"/>
-      <c r="B72" s="39" t="n"/>
-      <c r="C72" s="39" t="n"/>
-      <c r="D72" s="39" t="n"/>
-      <c r="E72" s="39" t="n"/>
-      <c r="F72" s="39" t="n"/>
-      <c r="G72" s="39" t="n"/>
-      <c r="H72" s="39" t="n"/>
-      <c r="I72" s="39" t="n"/>
-      <c r="J72" s="39" t="n"/>
-      <c r="K72" s="39" t="n"/>
-      <c r="L72" s="39" t="n"/>
-      <c r="M72" s="39" t="n"/>
-      <c r="N72" s="39" t="n"/>
-      <c r="O72" s="39" t="n"/>
-      <c r="P72" s="39" t="n"/>
-      <c r="Q72" s="39" t="n"/>
-      <c r="R72" s="39" t="n"/>
-      <c r="S72" s="39" t="n"/>
-      <c r="T72" s="39" t="n"/>
-      <c r="U72" s="39" t="n"/>
-      <c r="V72" s="39" t="n"/>
-      <c r="W72" s="39" t="n"/>
-      <c r="X72" s="75" t="n"/>
-      <c r="Y72" s="39" t="n"/>
-      <c r="Z72" s="39" t="n"/>
-      <c r="AA72" s="39" t="n"/>
-      <c r="AB72" s="75" t="n"/>
-      <c r="AC72" s="39" t="n"/>
-      <c r="AD72" s="39" t="n"/>
-      <c r="AE72" s="39" t="n"/>
-      <c r="AF72" s="39" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="39" t="n"/>
-      <c r="B73" s="39" t="n"/>
-      <c r="C73" s="39" t="n"/>
-      <c r="D73" s="39" t="n"/>
-      <c r="E73" s="39" t="n"/>
-      <c r="F73" s="39" t="n"/>
-      <c r="G73" s="39" t="n"/>
-      <c r="H73" s="39" t="n"/>
-      <c r="I73" s="39" t="n"/>
-      <c r="J73" s="39" t="n"/>
-      <c r="K73" s="39" t="n"/>
-      <c r="L73" s="39" t="n"/>
-      <c r="M73" s="39" t="n"/>
-      <c r="N73" s="39" t="n"/>
-      <c r="O73" s="39" t="n"/>
-      <c r="P73" s="39" t="n"/>
-      <c r="Q73" s="39" t="n"/>
-      <c r="R73" s="39" t="n"/>
-      <c r="S73" s="39" t="n"/>
-      <c r="T73" s="39" t="n"/>
-      <c r="U73" s="39" t="n"/>
-      <c r="V73" s="39" t="n"/>
-      <c r="W73" s="39" t="n"/>
-      <c r="X73" s="75" t="n"/>
-      <c r="Y73" s="39" t="n"/>
-      <c r="Z73" s="39" t="n"/>
-      <c r="AA73" s="39" t="n"/>
-      <c r="AB73" s="75" t="n"/>
-      <c r="AC73" s="39" t="n"/>
-      <c r="AD73" s="39" t="n"/>
-      <c r="AE73" s="39" t="n"/>
-      <c r="AF73" s="39" t="n"/>
-    </row>
-    <row r="87">
-      <c r="M87" s="40" t="n"/>
+      <c r="K74" s="146">
+        <f>SUBTOTAL(9,K5:K70)</f>
+        <v/>
+      </c>
+      <c r="L74" s="146">
+        <f>SUBTOTAL(9,L5:L70)</f>
+        <v/>
+      </c>
+      <c r="M74" s="146">
+        <f>SUBTOTAL(9,M5:M70)</f>
+        <v/>
+      </c>
+      <c r="N74" s="145" t="n"/>
+      <c r="O74" s="145" t="n"/>
+      <c r="P74" s="145" t="n"/>
+      <c r="Q74" s="146" t="n"/>
+      <c r="R74" s="144" t="n"/>
+      <c r="S74" s="146">
+        <f>SUBTOTAL(9,S5:S70)</f>
+        <v/>
+      </c>
+      <c r="T74" s="146">
+        <f>SUBTOTAL(9,T5:T70)</f>
+        <v/>
+      </c>
+      <c r="U74" s="145" t="n"/>
+      <c r="V74" s="145" t="n"/>
+      <c r="W74" s="146">
+        <f>SUBTOTAL(9,W5:W70)</f>
+        <v/>
+      </c>
+      <c r="X74" s="154" t="n"/>
+      <c r="Y74" s="146">
+        <f>SUBTOTAL(9,Y5:Y70)</f>
+        <v/>
+      </c>
+      <c r="Z74" s="146">
+        <f>SUBTOTAL(9,Z5:Z70)</f>
+        <v/>
+      </c>
+      <c r="AA74" s="146">
+        <f>SUBTOTAL(9,AA5:AA70)</f>
+        <v/>
+      </c>
+      <c r="AB74" s="154" t="n"/>
+      <c r="AC74" s="145" t="n"/>
+      <c r="AD74" s="145" t="n"/>
+      <c r="AE74" s="145" t="n"/>
+      <c r="AF74" s="145" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="39" t="n"/>
+      <c r="B75" s="39" t="n"/>
+      <c r="C75" s="39" t="n"/>
+      <c r="D75" s="39" t="n"/>
+      <c r="E75" s="39" t="n"/>
+      <c r="F75" s="39" t="n"/>
+      <c r="G75" s="39" t="n"/>
+      <c r="H75" s="39" t="n"/>
+      <c r="I75" s="39" t="n"/>
+      <c r="J75" s="39" t="n"/>
+      <c r="K75" s="39" t="n"/>
+      <c r="L75" s="39" t="n"/>
+      <c r="M75" s="39" t="n"/>
+      <c r="N75" s="39" t="n"/>
+      <c r="O75" s="39" t="n"/>
+      <c r="P75" s="39" t="n"/>
+      <c r="Q75" s="39" t="n"/>
+      <c r="R75" s="39" t="n"/>
+      <c r="S75" s="39" t="n"/>
+      <c r="T75" s="39" t="n"/>
+      <c r="U75" s="39" t="n"/>
+      <c r="V75" s="39" t="n"/>
+      <c r="W75" s="39" t="n"/>
+      <c r="X75" s="75" t="n"/>
+      <c r="Y75" s="39" t="n"/>
+      <c r="Z75" s="39" t="n"/>
+      <c r="AA75" s="39" t="n"/>
+      <c r="AB75" s="75" t="n"/>
+      <c r="AC75" s="39" t="n"/>
+      <c r="AD75" s="39" t="n"/>
+      <c r="AE75" s="39" t="n"/>
+      <c r="AF75" s="39" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="39" t="n"/>
+      <c r="B76" s="39" t="n"/>
+      <c r="C76" s="39" t="n"/>
+      <c r="D76" s="39" t="n"/>
+      <c r="E76" s="39" t="n"/>
+      <c r="F76" s="39" t="n"/>
+      <c r="G76" s="39" t="n"/>
+      <c r="H76" s="39" t="n"/>
+      <c r="I76" s="39" t="n"/>
+      <c r="J76" s="39" t="n"/>
+      <c r="K76" s="39" t="n"/>
+      <c r="L76" s="39" t="n"/>
+      <c r="M76" s="39" t="n"/>
+      <c r="N76" s="39" t="n"/>
+      <c r="O76" s="39" t="n"/>
+      <c r="P76" s="39" t="n"/>
+      <c r="Q76" s="39" t="n"/>
+      <c r="R76" s="39" t="n"/>
+      <c r="S76" s="39" t="n"/>
+      <c r="T76" s="39" t="n"/>
+      <c r="U76" s="39" t="n"/>
+      <c r="V76" s="39" t="n"/>
+      <c r="W76" s="39" t="n"/>
+      <c r="X76" s="75" t="n"/>
+      <c r="Y76" s="39" t="n"/>
+      <c r="Z76" s="39" t="n"/>
+      <c r="AA76" s="39" t="n"/>
+      <c r="AB76" s="75" t="n"/>
+      <c r="AC76" s="39" t="n"/>
+      <c r="AD76" s="39" t="n"/>
+      <c r="AE76" s="39" t="n"/>
+      <c r="AF76" s="39" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="39" t="n"/>
+      <c r="B77" s="39" t="n"/>
+      <c r="C77" s="39" t="n"/>
+      <c r="D77" s="39" t="n"/>
+      <c r="E77" s="39" t="n"/>
+      <c r="F77" s="39" t="n"/>
+      <c r="G77" s="39" t="n"/>
+      <c r="H77" s="39" t="n"/>
+      <c r="I77" s="39" t="n"/>
+      <c r="J77" s="39" t="n"/>
+      <c r="K77" s="39" t="n"/>
+      <c r="L77" s="39" t="n"/>
+      <c r="M77" s="39" t="n"/>
+      <c r="N77" s="39" t="n"/>
+      <c r="O77" s="39" t="n"/>
+      <c r="P77" s="39" t="n"/>
+      <c r="Q77" s="39" t="n"/>
+      <c r="R77" s="39" t="n"/>
+      <c r="S77" s="39" t="n"/>
+      <c r="T77" s="39" t="n"/>
+      <c r="U77" s="39" t="n"/>
+      <c r="V77" s="39" t="n"/>
+      <c r="W77" s="39" t="n"/>
+      <c r="X77" s="75" t="n"/>
+      <c r="Y77" s="39" t="n"/>
+      <c r="Z77" s="39" t="n"/>
+      <c r="AA77" s="39" t="n"/>
+      <c r="AB77" s="75" t="n"/>
+      <c r="AC77" s="39" t="n"/>
+      <c r="AD77" s="39" t="n"/>
+      <c r="AE77" s="39" t="n"/>
+      <c r="AF77" s="39" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="39" t="n"/>
+      <c r="B78" s="39" t="n"/>
+      <c r="C78" s="39" t="n"/>
+      <c r="D78" s="39" t="n"/>
+      <c r="E78" s="39" t="n"/>
+      <c r="F78" s="39" t="n"/>
+      <c r="G78" s="39" t="n"/>
+      <c r="H78" s="39" t="n"/>
+      <c r="I78" s="39" t="n"/>
+      <c r="J78" s="39" t="n"/>
+      <c r="K78" s="39" t="n"/>
+      <c r="L78" s="39" t="n"/>
+      <c r="M78" s="39" t="n"/>
+      <c r="N78" s="39" t="n"/>
+      <c r="O78" s="39" t="n"/>
+      <c r="P78" s="39" t="n"/>
+      <c r="Q78" s="39" t="n"/>
+      <c r="R78" s="39" t="n"/>
+      <c r="S78" s="39" t="n"/>
+      <c r="T78" s="39" t="n"/>
+      <c r="U78" s="39" t="n"/>
+      <c r="V78" s="39" t="n"/>
+      <c r="W78" s="39" t="n"/>
+      <c r="X78" s="75" t="n"/>
+      <c r="Y78" s="39" t="n"/>
+      <c r="Z78" s="39" t="n"/>
+      <c r="AA78" s="39" t="n"/>
+      <c r="AB78" s="75" t="n"/>
+      <c r="AC78" s="39" t="n"/>
+      <c r="AD78" s="39" t="n"/>
+      <c r="AE78" s="39" t="n"/>
+      <c r="AF78" s="39" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="39" t="n"/>
+      <c r="B79" s="39" t="n"/>
+      <c r="C79" s="39" t="n"/>
+      <c r="D79" s="39" t="n"/>
+      <c r="E79" s="39" t="n"/>
+      <c r="F79" s="39" t="n"/>
+      <c r="G79" s="39" t="n"/>
+      <c r="H79" s="39" t="n"/>
+      <c r="I79" s="39" t="n"/>
+      <c r="J79" s="39" t="n"/>
+      <c r="K79" s="39" t="n"/>
+      <c r="L79" s="39" t="n"/>
+      <c r="M79" s="39" t="n"/>
+      <c r="N79" s="39" t="n"/>
+      <c r="O79" s="39" t="n"/>
+      <c r="P79" s="39" t="n"/>
+      <c r="Q79" s="39" t="n"/>
+      <c r="R79" s="39" t="n"/>
+      <c r="S79" s="39" t="n"/>
+      <c r="T79" s="39" t="n"/>
+      <c r="U79" s="39" t="n"/>
+      <c r="V79" s="39" t="n"/>
+      <c r="W79" s="39" t="n"/>
+      <c r="X79" s="75" t="n"/>
+      <c r="Y79" s="39" t="n"/>
+      <c r="Z79" s="39" t="n"/>
+      <c r="AA79" s="39" t="n"/>
+      <c r="AB79" s="75" t="n"/>
+      <c r="AC79" s="39" t="n"/>
+      <c r="AD79" s="39" t="n"/>
+      <c r="AE79" s="39" t="n"/>
+      <c r="AF79" s="39" t="n"/>
+    </row>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93">
+      <c r="M93" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A66:G66"/>
     <mergeCell ref="G3:N3"/>
-    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="A65:G65"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A71:G71"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="O3:W3"/>
     <mergeCell ref="A2:AF2"/>
@@ -11040,6 +11781,96 @@
       <c r="L24" s="228" t="n"/>
       <c r="M24" s="228" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="224" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="224" t="inlineStr">
+        <is>
+          <t>GPO475</t>
+        </is>
+      </c>
+      <c r="C25" s="225" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D25" s="225" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="E25" s="226" t="n">
+        <v>540</v>
+      </c>
+      <c r="F25" s="224" t="inlineStr">
+        <is>
+          <t>TMS-1000 License 6 screens (CGV 안동)</t>
+        </is>
+      </c>
+      <c r="G25" s="227" t="n">
+        <v>46127</v>
+      </c>
+      <c r="H25" s="227" t="n">
+        <v>46190</v>
+      </c>
+      <c r="I25" s="227" t="n">
+        <v>46143</v>
+      </c>
+      <c r="J25" s="227" t="n">
+        <v>46507</v>
+      </c>
+      <c r="K25" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="L25" s="228" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
     <row r="70">
       <c r="M70" s="40" t="n"/>
     </row>
@@ -12579,6 +13410,165 @@
       <c r="L35" s="228" t="n"/>
       <c r="M35" s="228" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="241" t="inlineStr">
+        <is>
+          <t>14008-26-101227M</t>
+        </is>
+      </c>
+      <c r="B36" s="241" t="inlineStr">
+        <is>
+          <t>CPO696-5</t>
+        </is>
+      </c>
+      <c r="C36" s="242" t="n">
+        <v>346792</v>
+      </c>
+      <c r="D36" s="243">
+        <f>C36/C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F36" s="244" t="n">
+        <v>286000</v>
+      </c>
+      <c r="G36" s="241" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="H36" s="244" t="n">
+        <v>2898404</v>
+      </c>
+      <c r="I36" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J36" s="241" t="inlineStr"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="292" t="inlineStr">
+        <is>
+          <t>14008-26-101275M</t>
+        </is>
+      </c>
+      <c r="B37" s="292" t="inlineStr">
+        <is>
+          <t>MPO67</t>
+        </is>
+      </c>
+      <c r="C37" s="293" t="n">
+        <v>49138.8</v>
+      </c>
+      <c r="D37" s="294">
+        <f>C37/(C37+C38)</f>
+        <v/>
+      </c>
+      <c r="E37" s="292" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F37" s="295">
+        <f>ROUND(253000*D37,0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="292" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="H37" s="295">
+        <f>ROUND(17883555*D37,0)</f>
+        <v/>
+      </c>
+      <c r="I37" s="292" t="inlineStr">
+        <is>
+          <t>합배송</t>
+        </is>
+      </c>
+      <c r="J37" s="292" t="inlineStr">
+        <is>
+          <t>2건 합산(롯데/CJ미래원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="292" t="inlineStr"/>
+      <c r="B38" s="292" t="inlineStr">
+        <is>
+          <t>MPO68</t>
+        </is>
+      </c>
+      <c r="C38" s="293" t="n">
+        <v>11587.2</v>
+      </c>
+      <c r="D38" s="294">
+        <f>C38/(C37+C38)</f>
+        <v/>
+      </c>
+      <c r="E38" s="292" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F38" s="295">
+        <f>253000-F37</f>
+        <v/>
+      </c>
+      <c r="G38" s="292" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="H38" s="295">
+        <f>17883555-H37</f>
+        <v/>
+      </c>
+      <c r="I38" s="292" t="inlineStr">
+        <is>
+          <t>합배송</t>
+        </is>
+      </c>
+      <c r="J38" s="292" t="inlineStr"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
     <row r="71">
       <c r="M71" s="40" t="n"/>
     </row>
@@ -12598,7 +13588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="160" min="1" max="1"/>
@@ -14477,321 +15467,325 @@
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="169" t="inlineStr">
+      <c r="A41" s="234" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C41" s="235" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D41" s="234" t="inlineStr">
+        <is>
+          <t>CPO696-3</t>
+        </is>
+      </c>
+      <c r="E41" s="236" t="n">
+        <v>351274</v>
+      </c>
+      <c r="F41" s="237" t="n">
+        <v>1518</v>
+      </c>
+      <c r="G41" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I41" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J41" s="238" t="n">
+        <v>533284792</v>
+      </c>
+      <c r="K41" s="238">
+        <f>ROUND((E41+G41)*F41+H41+I41,0)</f>
+        <v/>
+      </c>
+      <c r="L41" s="239">
+        <f>J41-K41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="234" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C42" s="235" t="inlineStr">
+        <is>
+          <t>Appotronics</t>
+        </is>
+      </c>
+      <c r="D42" s="234" t="inlineStr">
+        <is>
+          <t>APO001 (S20-C2220-BEAB)</t>
+        </is>
+      </c>
+      <c r="E42" s="236" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F42" s="237" t="n">
+        <v>1517.1</v>
+      </c>
+      <c r="G42" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" s="238" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I42" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J42" s="238" t="n">
+        <v>18860382</v>
+      </c>
+      <c r="K42" s="238">
+        <f>ROUND((E42+G42)*F42+H42+I42,0)</f>
+        <v/>
+      </c>
+      <c r="L42" s="239">
+        <f>J42-K42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="234" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C43" s="235" t="inlineStr">
+        <is>
+          <t>MMK Europe</t>
+        </is>
+      </c>
+      <c r="D43" s="234" t="inlineStr">
+        <is>
+          <t>MPO67, MPO68</t>
+        </is>
+      </c>
+      <c r="E43" s="236" t="n">
+        <v>60726</v>
+      </c>
+      <c r="F43" s="237" t="n">
+        <v>1517.3</v>
+      </c>
+      <c r="G43" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H43" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I43" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J43" s="238" t="n">
+        <v>92190405</v>
+      </c>
+      <c r="K43" s="238">
+        <f>ROUND((E43+G43)*F43+H43+I43,0)</f>
+        <v/>
+      </c>
+      <c r="L43" s="239">
+        <f>J43-K43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="234" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C44" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D44" s="234" t="inlineStr">
+        <is>
+          <t>GPO475, SR-1000수리</t>
+        </is>
+      </c>
+      <c r="E44" s="236" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F44" s="237" t="n">
+        <v>1516.8</v>
+      </c>
+      <c r="G44" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H44" s="238" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I44" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J44" s="238" t="n">
+        <v>3140108</v>
+      </c>
+      <c r="K44" s="238">
+        <f>ROUND((E44+G44)*F44+H44+I44,0)</f>
+        <v/>
+      </c>
+      <c r="L44" s="239">
+        <f>J44-K44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="169" t="inlineStr">
         <is>
           <t>② PO별 비용 안분 내역</t>
         </is>
       </c>
-      <c r="B41" s="148" t="n"/>
-      <c r="C41" s="148" t="n"/>
-      <c r="D41" s="148" t="n"/>
-      <c r="E41" s="148" t="n"/>
-      <c r="F41" s="148" t="n"/>
-      <c r="G41" s="148" t="n"/>
-      <c r="H41" s="148" t="n"/>
-      <c r="I41" s="148" t="n"/>
-      <c r="J41" s="148" t="n"/>
-      <c r="K41" s="148" t="n"/>
-      <c r="L41" s="149" t="n"/>
-      <c r="M41" s="115" t="n"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="150" t="inlineStr">
+      <c r="B45" s="148" t="n"/>
+      <c r="C45" s="148" t="n"/>
+      <c r="D45" s="148" t="n"/>
+      <c r="E45" s="148" t="n"/>
+      <c r="F45" s="148" t="n"/>
+      <c r="G45" s="148" t="n"/>
+      <c r="H45" s="148" t="n"/>
+      <c r="I45" s="148" t="n"/>
+      <c r="J45" s="148" t="n"/>
+      <c r="K45" s="148" t="n"/>
+      <c r="L45" s="149" t="n"/>
+      <c r="M45" s="115" t="n"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="150" t="inlineStr">
         <is>
           <t>PO No.</t>
         </is>
       </c>
-      <c r="B42" s="150" t="inlineStr">
+      <c r="B46" s="150" t="inlineStr">
         <is>
           <t>송금일</t>
         </is>
       </c>
-      <c r="C42" s="150" t="inlineStr">
+      <c r="C46" s="150" t="inlineStr">
         <is>
           <t>업체</t>
         </is>
       </c>
-      <c r="D42" s="150" t="inlineStr">
+      <c r="D46" s="150" t="inlineStr">
         <is>
           <t>PO USD</t>
         </is>
       </c>
-      <c r="E42" s="150" t="inlineStr">
+      <c r="E46" s="150" t="inlineStr">
         <is>
           <t>그룹총USD</t>
         </is>
       </c>
-      <c r="F42" s="150" t="inlineStr">
+      <c r="F46" s="150" t="inlineStr">
         <is>
           <t>배부비율</t>
         </is>
       </c>
-      <c r="G42" s="150" t="inlineStr">
+      <c r="G46" s="150" t="inlineStr">
         <is>
           <t>적용환율</t>
         </is>
       </c>
-      <c r="H42" s="150" t="inlineStr">
+      <c r="H46" s="150" t="inlineStr">
         <is>
           <t>원화환산액</t>
         </is>
       </c>
-      <c r="I42" s="150" t="inlineStr">
+      <c r="I46" s="150" t="inlineStr">
         <is>
           <t>중개수수료안분</t>
         </is>
       </c>
-      <c r="J42" s="150" t="inlineStr">
+      <c r="J46" s="150" t="inlineStr">
         <is>
           <t>수수료안분</t>
         </is>
       </c>
-      <c r="K42" s="150" t="inlineStr">
+      <c r="K46" s="150" t="inlineStr">
         <is>
           <t>전신료안분</t>
         </is>
       </c>
-      <c r="L42" s="150" t="inlineStr">
+      <c r="L46" s="150" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
-      </c>
-      <c r="M42" s="115" t="n"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="116" t="inlineStr">
-        <is>
-          <t>CPO678-1</t>
-        </is>
-      </c>
-      <c r="B43" s="116" t="inlineStr">
-        <is>
-          <t>2025.12.16</t>
-        </is>
-      </c>
-      <c r="C43" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D43" s="118" t="n">
-        <v>139083</v>
-      </c>
-      <c r="E43" s="118" t="n">
-        <v>143557</v>
-      </c>
-      <c r="F43" s="122" t="n">
-        <v>0.968835</v>
-      </c>
-      <c r="G43" s="118" t="n">
-        <v>1479.7</v>
-      </c>
-      <c r="H43" s="120" t="n">
-        <v>205801115</v>
-      </c>
-      <c r="I43" s="120" t="n">
-        <v>28672</v>
-      </c>
-      <c r="J43" s="120" t="n">
-        <v>12110</v>
-      </c>
-      <c r="K43" s="120" t="n">
-        <v>7751</v>
-      </c>
-      <c r="L43" s="121" t="n">
-        <v>205849648</v>
-      </c>
-      <c r="M43" s="115" t="n"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="116" t="inlineStr">
-        <is>
-          <t>CPO679</t>
-        </is>
-      </c>
-      <c r="B44" s="116" t="inlineStr">
-        <is>
-          <t>2025.12.16</t>
-        </is>
-      </c>
-      <c r="C44" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D44" s="118" t="n">
-        <v>4474</v>
-      </c>
-      <c r="E44" s="118" t="n">
-        <v>143557</v>
-      </c>
-      <c r="F44" s="122" t="n">
-        <v>0.031165</v>
-      </c>
-      <c r="G44" s="118" t="n">
-        <v>1479.7</v>
-      </c>
-      <c r="H44" s="120" t="n">
-        <v>6620178</v>
-      </c>
-      <c r="I44" s="120" t="n">
-        <v>922</v>
-      </c>
-      <c r="J44" s="120" t="n">
-        <v>390</v>
-      </c>
-      <c r="K44" s="120" t="n">
-        <v>249</v>
-      </c>
-      <c r="L44" s="121" t="n">
-        <v>6621739</v>
-      </c>
-      <c r="M44" s="115" t="n"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="116" t="inlineStr">
-        <is>
-          <t>MPO65</t>
-        </is>
-      </c>
-      <c r="B45" s="116" t="inlineStr">
-        <is>
-          <t>2025.12.16</t>
-        </is>
-      </c>
-      <c r="C45" s="117" t="inlineStr">
-        <is>
-          <t>MAG</t>
-        </is>
-      </c>
-      <c r="D45" s="118" t="n">
-        <v>4936</v>
-      </c>
-      <c r="E45" s="118" t="n">
-        <v>15040</v>
-      </c>
-      <c r="F45" s="122" t="n">
-        <v>0.328191</v>
-      </c>
-      <c r="G45" s="118" t="n">
-        <v>1480</v>
-      </c>
-      <c r="H45" s="120" t="n">
-        <v>7305280</v>
-      </c>
-      <c r="I45" s="120" t="n">
-        <v>9714</v>
-      </c>
-      <c r="J45" s="120" t="n">
-        <v>3282</v>
-      </c>
-      <c r="K45" s="120" t="n">
-        <v>2626</v>
-      </c>
-      <c r="L45" s="121" t="n">
-        <v>7320902</v>
-      </c>
-      <c r="M45" s="115" t="n"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="116" t="inlineStr">
-        <is>
-          <t>GPO451</t>
-        </is>
-      </c>
-      <c r="B46" s="116" t="inlineStr">
-        <is>
-          <t>2025.12.29</t>
-        </is>
-      </c>
-      <c r="C46" s="117" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D46" s="118" t="n">
-        <v>9060</v>
-      </c>
-      <c r="E46" s="118" t="n">
-        <v>13860</v>
-      </c>
-      <c r="F46" s="122" t="n">
-        <v>0.65368</v>
-      </c>
-      <c r="G46" s="118" t="n">
-        <v>1439.1</v>
-      </c>
-      <c r="H46" s="120" t="n">
-        <v>13038246</v>
-      </c>
-      <c r="I46" s="120" t="n">
-        <v>18814</v>
-      </c>
-      <c r="J46" s="120" t="n">
-        <v>6537</v>
-      </c>
-      <c r="K46" s="120" t="n">
-        <v>5229</v>
-      </c>
-      <c r="L46" s="121" t="n">
-        <v>13068826</v>
       </c>
       <c r="M46" s="115" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="116" t="inlineStr">
         <is>
-          <t>GPO458</t>
+          <t>CPO678-1</t>
         </is>
       </c>
       <c r="B47" s="116" t="inlineStr">
         <is>
-          <t>2025.12.29</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="C47" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D47" s="118" t="n">
-        <v>350</v>
+        <v>139083</v>
       </c>
       <c r="E47" s="118" t="n">
-        <v>13860</v>
+        <v>143557</v>
       </c>
       <c r="F47" s="122" t="n">
-        <v>0.025253</v>
+        <v>0.968835</v>
       </c>
       <c r="G47" s="118" t="n">
-        <v>1439.1</v>
+        <v>1479.7</v>
       </c>
       <c r="H47" s="120" t="n">
-        <v>503685</v>
+        <v>205801115</v>
       </c>
       <c r="I47" s="120" t="n">
-        <v>727</v>
+        <v>28672</v>
       </c>
       <c r="J47" s="120" t="n">
-        <v>253</v>
+        <v>12110</v>
       </c>
       <c r="K47" s="120" t="n">
-        <v>202</v>
+        <v>7751</v>
       </c>
       <c r="L47" s="121" t="n">
-        <v>504867</v>
+        <v>205849648</v>
       </c>
       <c r="M47" s="115" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="116" t="inlineStr">
         <is>
-          <t>CPO680</t>
+          <t>CPO679</t>
         </is>
       </c>
       <c r="B48" s="116" t="inlineStr">
         <is>
-          <t>2026.01.13</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="C48" s="117" t="inlineStr">
@@ -14800,88 +15794,88 @@
         </is>
       </c>
       <c r="D48" s="118" t="n">
-        <v>252</v>
+        <v>4474</v>
       </c>
       <c r="E48" s="118" t="n">
-        <v>252</v>
+        <v>143557</v>
       </c>
       <c r="F48" s="122" t="n">
-        <v>1</v>
+        <v>0.031165</v>
       </c>
       <c r="G48" s="118" t="n">
-        <v>1479</v>
+        <v>1479.7</v>
       </c>
       <c r="H48" s="120" t="n">
-        <v>372708</v>
+        <v>6620178</v>
       </c>
       <c r="I48" s="120" t="n">
-        <v>29580</v>
+        <v>922</v>
       </c>
       <c r="J48" s="120" t="n">
-        <v>2500</v>
+        <v>390</v>
       </c>
       <c r="K48" s="120" t="n">
-        <v>8000</v>
+        <v>249</v>
       </c>
       <c r="L48" s="121" t="n">
-        <v>412788</v>
+        <v>6621739</v>
       </c>
       <c r="M48" s="115" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="116" t="inlineStr">
         <is>
-          <t>GPO459</t>
+          <t>MPO65</t>
         </is>
       </c>
       <c r="B49" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="C49" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D49" s="118" t="n">
-        <v>450</v>
+        <v>4936</v>
       </c>
       <c r="E49" s="118" t="n">
-        <v>3700</v>
+        <v>15040</v>
       </c>
       <c r="F49" s="122" t="n">
-        <v>0.121622</v>
+        <v>0.328191</v>
       </c>
       <c r="G49" s="118" t="n">
-        <v>1475.7</v>
+        <v>1480</v>
       </c>
       <c r="H49" s="120" t="n">
-        <v>664065</v>
+        <v>7305280</v>
       </c>
       <c r="I49" s="120" t="n">
-        <v>3590</v>
+        <v>9714</v>
       </c>
       <c r="J49" s="120" t="n">
-        <v>912</v>
+        <v>3282</v>
       </c>
       <c r="K49" s="120" t="n">
-        <v>973</v>
+        <v>2626</v>
       </c>
       <c r="L49" s="121" t="n">
-        <v>669540</v>
+        <v>7320902</v>
       </c>
       <c r="M49" s="115" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="116" t="inlineStr">
         <is>
-          <t>GPO460</t>
+          <t>GPO451</t>
         </is>
       </c>
       <c r="B50" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2025.12.29</t>
         </is>
       </c>
       <c r="C50" s="117" t="inlineStr">
@@ -14890,43 +15884,43 @@
         </is>
       </c>
       <c r="D50" s="118" t="n">
-        <v>2710</v>
+        <v>9060</v>
       </c>
       <c r="E50" s="118" t="n">
-        <v>3700</v>
+        <v>13860</v>
       </c>
       <c r="F50" s="122" t="n">
-        <v>0.732432</v>
+        <v>0.65368</v>
       </c>
       <c r="G50" s="118" t="n">
-        <v>1475.7</v>
+        <v>1439.1</v>
       </c>
       <c r="H50" s="120" t="n">
-        <v>3999147</v>
+        <v>13038246</v>
       </c>
       <c r="I50" s="120" t="n">
-        <v>21617</v>
+        <v>18814</v>
       </c>
       <c r="J50" s="120" t="n">
-        <v>5493</v>
+        <v>6537</v>
       </c>
       <c r="K50" s="120" t="n">
-        <v>5859</v>
+        <v>5229</v>
       </c>
       <c r="L50" s="121" t="n">
-        <v>4032116</v>
+        <v>13068826</v>
       </c>
       <c r="M50" s="115" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="116" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="B51" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2025.12.29</t>
         </is>
       </c>
       <c r="C51" s="117" t="inlineStr">
@@ -14935,308 +15929,308 @@
         </is>
       </c>
       <c r="D51" s="118" t="n">
-        <v>540</v>
+        <v>350</v>
       </c>
       <c r="E51" s="118" t="n">
-        <v>3700</v>
+        <v>13860</v>
       </c>
       <c r="F51" s="122" t="n">
-        <v>0.145946</v>
+        <v>0.025253</v>
       </c>
       <c r="G51" s="118" t="n">
-        <v>1475.7</v>
+        <v>1439.1</v>
       </c>
       <c r="H51" s="120" t="n">
-        <v>796878</v>
+        <v>503685</v>
       </c>
       <c r="I51" s="120" t="n">
-        <v>4307</v>
+        <v>727</v>
       </c>
       <c r="J51" s="120" t="n">
-        <v>1095</v>
+        <v>253</v>
       </c>
       <c r="K51" s="120" t="n">
-        <v>1168</v>
+        <v>202</v>
       </c>
       <c r="L51" s="121" t="n">
-        <v>803448</v>
+        <v>504867</v>
       </c>
       <c r="M51" s="115" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="116" t="inlineStr">
         <is>
-          <t>MPO66</t>
+          <t>CPO680</t>
         </is>
       </c>
       <c r="B52" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.01.13</t>
         </is>
       </c>
       <c r="C52" s="117" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D52" s="118" t="n">
-        <v>9626.35</v>
+        <v>252</v>
       </c>
       <c r="E52" s="118" t="n">
-        <v>9626.35</v>
+        <v>252</v>
       </c>
       <c r="F52" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="118" t="n">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="H52" s="120" t="n">
-        <v>14208493</v>
+        <v>372708</v>
       </c>
       <c r="I52" s="120" t="n">
-        <v>29520</v>
+        <v>29580</v>
       </c>
       <c r="J52" s="120" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="K52" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="L52" s="121" t="n">
-        <v>14256013</v>
+        <v>412788</v>
       </c>
       <c r="M52" s="115" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="116" t="inlineStr">
         <is>
-          <t>LPO001</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="B53" s="116" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C53" s="117" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D53" s="118" t="n">
-        <v>5056.8</v>
+        <v>450</v>
       </c>
       <c r="E53" s="118" t="n">
-        <v>5056.8</v>
+        <v>3700</v>
       </c>
       <c r="F53" s="122" t="n">
-        <v>1</v>
+        <v>0.121622</v>
       </c>
       <c r="G53" s="118" t="n">
-        <v>1445.5</v>
+        <v>1475.7</v>
       </c>
       <c r="H53" s="120" t="n">
-        <v>7309604</v>
+        <v>664065</v>
       </c>
       <c r="I53" s="120" t="n">
-        <v>28910</v>
+        <v>3590</v>
       </c>
       <c r="J53" s="120" t="n">
-        <v>10000</v>
+        <v>912</v>
       </c>
       <c r="K53" s="120" t="n">
-        <v>8000</v>
+        <v>973</v>
       </c>
       <c r="L53" s="121" t="n">
-        <v>7356514</v>
+        <v>669540</v>
       </c>
       <c r="M53" s="115" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="116" t="inlineStr">
         <is>
-          <t>CPO682</t>
+          <t>GPO460</t>
         </is>
       </c>
       <c r="B54" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C54" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D54" s="118" t="n">
-        <v>20174</v>
+        <v>2710</v>
       </c>
       <c r="E54" s="118" t="n">
-        <v>24794</v>
+        <v>3700</v>
       </c>
       <c r="F54" s="122" t="n">
-        <v>0.813665</v>
+        <v>0.732432</v>
       </c>
       <c r="G54" s="118" t="n">
-        <v>1454.7</v>
+        <v>1475.7</v>
       </c>
       <c r="H54" s="120" t="n">
-        <v>29347118</v>
+        <v>3999147</v>
       </c>
       <c r="I54" s="120" t="n">
-        <v>23673</v>
+        <v>21617</v>
       </c>
       <c r="J54" s="120" t="n">
-        <v>10171</v>
+        <v>5493</v>
       </c>
       <c r="K54" s="120" t="n">
-        <v>6509</v>
+        <v>5859</v>
       </c>
       <c r="L54" s="121" t="n">
-        <v>29387471</v>
+        <v>4032116</v>
       </c>
       <c r="M54" s="115" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="116" t="inlineStr">
         <is>
-          <t>CPO683</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="B55" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C55" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D55" s="118" t="n">
-        <v>4620</v>
+        <v>540</v>
       </c>
       <c r="E55" s="118" t="n">
-        <v>24794</v>
+        <v>3700</v>
       </c>
       <c r="F55" s="122" t="n">
-        <v>0.186335</v>
+        <v>0.145946</v>
       </c>
       <c r="G55" s="118" t="n">
-        <v>1454.7</v>
+        <v>1475.7</v>
       </c>
       <c r="H55" s="120" t="n">
-        <v>6720714</v>
+        <v>796878</v>
       </c>
       <c r="I55" s="120" t="n">
-        <v>5421</v>
+        <v>4307</v>
       </c>
       <c r="J55" s="120" t="n">
-        <v>2329</v>
+        <v>1095</v>
       </c>
       <c r="K55" s="120" t="n">
-        <v>1491</v>
+        <v>1168</v>
       </c>
       <c r="L55" s="121" t="n">
-        <v>6729955</v>
+        <v>803448</v>
       </c>
       <c r="M55" s="115" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="116" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>MPO66</t>
         </is>
       </c>
       <c r="B56" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C56" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D56" s="118" t="n">
-        <v>1440</v>
+        <v>9626.35</v>
       </c>
       <c r="E56" s="118" t="n">
-        <v>11599.57</v>
+        <v>9626.35</v>
       </c>
       <c r="F56" s="122" t="n">
-        <v>0.124143</v>
+        <v>1</v>
       </c>
       <c r="G56" s="118" t="n">
-        <v>1453.6</v>
+        <v>1476</v>
       </c>
       <c r="H56" s="120" t="n">
-        <v>2093184</v>
+        <v>14208493</v>
       </c>
       <c r="I56" s="120" t="n">
-        <v>3609</v>
+        <v>29520</v>
       </c>
       <c r="J56" s="120" t="n">
-        <v>1241</v>
+        <v>10000</v>
       </c>
       <c r="K56" s="120" t="n">
-        <v>993</v>
+        <v>8000</v>
       </c>
       <c r="L56" s="121" t="n">
-        <v>2099027</v>
+        <v>14256013</v>
       </c>
       <c r="M56" s="115" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="116" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>LPO001</t>
         </is>
       </c>
       <c r="B57" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="C57" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D57" s="118" t="n">
-        <v>4489</v>
+        <v>5056.8</v>
       </c>
       <c r="E57" s="118" t="n">
-        <v>11599.57</v>
+        <v>5056.8</v>
       </c>
       <c r="F57" s="122" t="n">
-        <v>0.386997</v>
+        <v>1</v>
       </c>
       <c r="G57" s="118" t="n">
-        <v>1453.6</v>
+        <v>1445.5</v>
       </c>
       <c r="H57" s="120" t="n">
-        <v>6525210</v>
+        <v>7309604</v>
       </c>
       <c r="I57" s="120" t="n">
-        <v>11251</v>
+        <v>28910</v>
       </c>
       <c r="J57" s="120" t="n">
-        <v>3870</v>
+        <v>10000</v>
       </c>
       <c r="K57" s="120" t="n">
-        <v>3096</v>
+        <v>8000</v>
       </c>
       <c r="L57" s="121" t="n">
-        <v>6543427</v>
+        <v>7356514</v>
       </c>
       <c r="M57" s="115" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="116" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>CPO682</t>
         </is>
       </c>
       <c r="B58" s="116" t="inlineStr">
@@ -15246,47 +16240,47 @@
       </c>
       <c r="C58" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D58" s="118" t="n">
-        <v>5670.57</v>
+        <v>20174</v>
       </c>
       <c r="E58" s="118" t="n">
-        <v>11599.57</v>
+        <v>24794</v>
       </c>
       <c r="F58" s="122" t="n">
-        <v>0.48886</v>
+        <v>0.813665</v>
       </c>
       <c r="G58" s="118" t="n">
-        <v>1453.6</v>
+        <v>1454.7</v>
       </c>
       <c r="H58" s="120" t="n">
-        <v>8242741</v>
+        <v>29347118</v>
       </c>
       <c r="I58" s="120" t="n">
-        <v>14212</v>
+        <v>23673</v>
       </c>
       <c r="J58" s="120" t="n">
-        <v>4889</v>
+        <v>10171</v>
       </c>
       <c r="K58" s="120" t="n">
-        <v>3911</v>
+        <v>6509</v>
       </c>
       <c r="L58" s="121" t="n">
-        <v>8265753</v>
+        <v>29387471</v>
       </c>
       <c r="M58" s="115" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="116" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>CPO683</t>
         </is>
       </c>
       <c r="B59" s="116" t="inlineStr">
         <is>
-          <t>2026.02.11</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C59" s="117" t="inlineStr">
@@ -15295,178 +16289,178 @@
         </is>
       </c>
       <c r="D59" s="118" t="n">
-        <v>26358</v>
+        <v>4620</v>
       </c>
       <c r="E59" s="118" t="n">
-        <v>26358</v>
+        <v>24794</v>
       </c>
       <c r="F59" s="122" t="n">
-        <v>1</v>
+        <v>0.186335</v>
       </c>
       <c r="G59" s="118" t="n">
-        <v>1460.7</v>
+        <v>1454.7</v>
       </c>
       <c r="H59" s="120" t="n">
-        <v>38501131</v>
+        <v>6720714</v>
       </c>
       <c r="I59" s="120" t="n">
-        <v>29214</v>
+        <v>5421</v>
       </c>
       <c r="J59" s="120" t="n">
-        <v>12500</v>
+        <v>2329</v>
       </c>
       <c r="K59" s="120" t="n">
-        <v>8000</v>
+        <v>1491</v>
       </c>
       <c r="L59" s="121" t="n">
-        <v>38550845</v>
+        <v>6729955</v>
       </c>
       <c r="M59" s="115" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="116" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="B60" s="116" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C60" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D60" s="118" t="n">
-        <v>14793</v>
+        <v>1440</v>
       </c>
       <c r="E60" s="118" t="n">
-        <v>17538</v>
+        <v>11599.57</v>
       </c>
       <c r="F60" s="122" t="n">
-        <v>0.843483</v>
+        <v>0.124143</v>
       </c>
       <c r="G60" s="118" t="n">
-        <v>1451.7</v>
+        <v>1453.6</v>
       </c>
       <c r="H60" s="120" t="n">
-        <v>21474998</v>
+        <v>2093184</v>
       </c>
       <c r="I60" s="120" t="n">
-        <v>24490</v>
+        <v>3609</v>
       </c>
       <c r="J60" s="120" t="n">
-        <v>8435</v>
+        <v>1241</v>
       </c>
       <c r="K60" s="120" t="n">
-        <v>6748</v>
+        <v>993</v>
       </c>
       <c r="L60" s="121" t="n">
-        <v>21514671</v>
+        <v>2099027</v>
       </c>
       <c r="M60" s="115" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="116" t="inlineStr">
         <is>
-          <t>CPO689</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="B61" s="116" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C61" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D61" s="118" t="n">
-        <v>2745</v>
+        <v>4489</v>
       </c>
       <c r="E61" s="118" t="n">
-        <v>17538</v>
+        <v>11599.57</v>
       </c>
       <c r="F61" s="122" t="n">
-        <v>0.156517</v>
+        <v>0.386997</v>
       </c>
       <c r="G61" s="118" t="n">
-        <v>1451.7</v>
+        <v>1453.6</v>
       </c>
       <c r="H61" s="120" t="n">
-        <v>3984917</v>
+        <v>6525210</v>
       </c>
       <c r="I61" s="120" t="n">
-        <v>4544</v>
+        <v>11251</v>
       </c>
       <c r="J61" s="120" t="n">
-        <v>1565</v>
+        <v>3870</v>
       </c>
       <c r="K61" s="120" t="n">
-        <v>1252</v>
+        <v>3096</v>
       </c>
       <c r="L61" s="121" t="n">
-        <v>3992278</v>
+        <v>6543427</v>
       </c>
       <c r="M61" s="115" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="116" t="inlineStr">
         <is>
-          <t>CPO667</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="B62" s="116" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C62" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D62" s="118" t="n">
-        <v>5673</v>
+        <v>5670.57</v>
       </c>
       <c r="E62" s="118" t="n">
-        <v>142189</v>
+        <v>11599.57</v>
       </c>
       <c r="F62" s="122" t="n">
-        <v>0.039898</v>
+        <v>0.48886</v>
       </c>
       <c r="G62" s="118" t="n">
-        <v>1441.6</v>
+        <v>1453.6</v>
       </c>
       <c r="H62" s="120" t="n">
-        <v>8178197</v>
+        <v>8242741</v>
       </c>
       <c r="I62" s="120" t="n">
-        <v>1150</v>
+        <v>14212</v>
       </c>
       <c r="J62" s="120" t="n">
-        <v>499</v>
+        <v>4889</v>
       </c>
       <c r="K62" s="120" t="n">
-        <v>319</v>
+        <v>3911</v>
       </c>
       <c r="L62" s="121" t="n">
-        <v>8180165</v>
+        <v>8265753</v>
       </c>
       <c r="M62" s="115" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="116" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="B63" s="116" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.02.11</t>
         </is>
       </c>
       <c r="C63" s="117" t="inlineStr">
@@ -15475,43 +16469,43 @@
         </is>
       </c>
       <c r="D63" s="118" t="n">
-        <v>136516</v>
+        <v>26358</v>
       </c>
       <c r="E63" s="118" t="n">
-        <v>142189</v>
+        <v>26358</v>
       </c>
       <c r="F63" s="122" t="n">
-        <v>0.960102</v>
+        <v>1</v>
       </c>
       <c r="G63" s="118" t="n">
-        <v>1441.6</v>
+        <v>1460.7</v>
       </c>
       <c r="H63" s="120" t="n">
-        <v>196801466</v>
+        <v>38501131</v>
       </c>
       <c r="I63" s="120" t="n">
-        <v>27682</v>
+        <v>29214</v>
       </c>
       <c r="J63" s="120" t="n">
-        <v>12001</v>
+        <v>12500</v>
       </c>
       <c r="K63" s="120" t="n">
-        <v>7681</v>
+        <v>8000</v>
       </c>
       <c r="L63" s="121" t="n">
-        <v>196848830</v>
+        <v>38550845</v>
       </c>
       <c r="M63" s="115" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="116" t="inlineStr">
         <is>
-          <t>CPO678-2</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="B64" s="116" t="inlineStr">
         <is>
-          <t>2026.03.06</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C64" s="117" t="inlineStr">
@@ -15520,43 +16514,43 @@
         </is>
       </c>
       <c r="D64" s="118" t="n">
-        <v>137850</v>
+        <v>14793</v>
       </c>
       <c r="E64" s="118" t="n">
-        <v>137850</v>
+        <v>17538</v>
       </c>
       <c r="F64" s="122" t="n">
-        <v>1</v>
+        <v>0.843483</v>
       </c>
       <c r="G64" s="118" t="n">
-        <v>1477.6</v>
+        <v>1451.7</v>
       </c>
       <c r="H64" s="120" t="n">
-        <v>203687160</v>
+        <v>21474998</v>
       </c>
       <c r="I64" s="120" t="n">
-        <v>29552</v>
+        <v>24490</v>
       </c>
       <c r="J64" s="120" t="n">
-        <v>12500</v>
+        <v>8435</v>
       </c>
       <c r="K64" s="120" t="n">
-        <v>8000</v>
+        <v>6748</v>
       </c>
       <c r="L64" s="121" t="n">
-        <v>203737212</v>
+        <v>21514671</v>
       </c>
       <c r="M64" s="115" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="116" t="inlineStr">
         <is>
-          <t>CPO690</t>
+          <t>CPO689</t>
         </is>
       </c>
       <c r="B65" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C65" s="117" t="inlineStr">
@@ -15565,43 +16559,43 @@
         </is>
       </c>
       <c r="D65" s="118" t="n">
-        <v>9740</v>
+        <v>2745</v>
       </c>
       <c r="E65" s="118" t="n">
-        <v>34354</v>
+        <v>17538</v>
       </c>
       <c r="F65" s="122" t="n">
-        <v>0.283519</v>
+        <v>0.156517</v>
       </c>
       <c r="G65" s="118" t="n">
-        <v>1505.7</v>
+        <v>1451.7</v>
       </c>
       <c r="H65" s="120" t="n">
-        <v>14665518</v>
+        <v>3984917</v>
       </c>
       <c r="I65" s="120" t="n">
-        <v>8538</v>
+        <v>4544</v>
       </c>
       <c r="J65" s="120" t="n">
-        <v>3544</v>
+        <v>1565</v>
       </c>
       <c r="K65" s="120" t="n">
-        <v>2268</v>
+        <v>1252</v>
       </c>
       <c r="L65" s="121" t="n">
-        <v>14679868</v>
+        <v>3992278</v>
       </c>
       <c r="M65" s="115" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="116" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="B66" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C66" s="117" t="inlineStr">
@@ -15610,128 +16604,128 @@
         </is>
       </c>
       <c r="D66" s="118" t="n">
-        <v>24614</v>
+        <v>5673</v>
       </c>
       <c r="E66" s="118" t="n">
-        <v>34354</v>
+        <v>142189</v>
       </c>
       <c r="F66" s="122" t="n">
-        <v>0.716481</v>
+        <v>0.039898</v>
       </c>
       <c r="G66" s="118" t="n">
-        <v>1505.7</v>
+        <v>1441.6</v>
       </c>
       <c r="H66" s="120" t="n">
-        <v>37061300</v>
+        <v>8178197</v>
       </c>
       <c r="I66" s="120" t="n">
-        <v>21576</v>
+        <v>1150</v>
       </c>
       <c r="J66" s="120" t="n">
-        <v>8956</v>
+        <v>499</v>
       </c>
       <c r="K66" s="120" t="n">
-        <v>5732</v>
+        <v>319</v>
       </c>
       <c r="L66" s="121" t="n">
-        <v>37097564</v>
+        <v>8180165</v>
       </c>
       <c r="M66" s="115" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="116" t="inlineStr">
         <is>
-          <t>GPO467</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="B67" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C67" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D67" s="118" t="n">
-        <v>1700</v>
+        <v>136516</v>
       </c>
       <c r="E67" s="118" t="n">
-        <v>6553.05</v>
+        <v>142189</v>
       </c>
       <c r="F67" s="122" t="n">
-        <v>0.259421</v>
+        <v>0.960102</v>
       </c>
       <c r="G67" s="118" t="n">
-        <v>1506.4</v>
+        <v>1441.6</v>
       </c>
       <c r="H67" s="120" t="n">
-        <v>2560880</v>
+        <v>196801466</v>
       </c>
       <c r="I67" s="120" t="n">
-        <v>7816</v>
+        <v>27682</v>
       </c>
       <c r="J67" s="120" t="n">
-        <v>2594</v>
+        <v>12001</v>
       </c>
       <c r="K67" s="120" t="n">
-        <v>2075</v>
+        <v>7681</v>
       </c>
       <c r="L67" s="121" t="n">
-        <v>2573365</v>
+        <v>196848830</v>
       </c>
       <c r="M67" s="115" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="116" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>CPO678-2</t>
         </is>
       </c>
       <c r="B68" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.03.06</t>
         </is>
       </c>
       <c r="C68" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D68" s="118" t="n">
-        <v>3993.05</v>
+        <v>137850</v>
       </c>
       <c r="E68" s="118" t="n">
-        <v>6553.05</v>
+        <v>137850</v>
       </c>
       <c r="F68" s="122" t="n">
-        <v>0.6093420000000001</v>
+        <v>1</v>
       </c>
       <c r="G68" s="118" t="n">
-        <v>1506.4</v>
+        <v>1477.6</v>
       </c>
       <c r="H68" s="120" t="n">
-        <v>6015131</v>
+        <v>203687160</v>
       </c>
       <c r="I68" s="120" t="n">
-        <v>18358</v>
+        <v>29552</v>
       </c>
       <c r="J68" s="120" t="n">
-        <v>6093</v>
+        <v>12500</v>
       </c>
       <c r="K68" s="120" t="n">
-        <v>4875</v>
+        <v>8000</v>
       </c>
       <c r="L68" s="121" t="n">
-        <v>6044457</v>
+        <v>203737212</v>
       </c>
       <c r="M68" s="115" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="116" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>CPO690</t>
         </is>
       </c>
       <c r="B69" s="116" t="inlineStr">
@@ -15741,42 +16735,42 @@
       </c>
       <c r="C69" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D69" s="118" t="n">
-        <v>360</v>
+        <v>9740</v>
       </c>
       <c r="E69" s="118" t="n">
-        <v>6553.05</v>
+        <v>34354</v>
       </c>
       <c r="F69" s="122" t="n">
-        <v>0.054936</v>
+        <v>0.283519</v>
       </c>
       <c r="G69" s="118" t="n">
-        <v>1506.4</v>
+        <v>1505.7</v>
       </c>
       <c r="H69" s="120" t="n">
-        <v>542304</v>
+        <v>14665518</v>
       </c>
       <c r="I69" s="120" t="n">
-        <v>1655</v>
+        <v>8538</v>
       </c>
       <c r="J69" s="120" t="n">
-        <v>549</v>
+        <v>3544</v>
       </c>
       <c r="K69" s="120" t="n">
-        <v>439</v>
+        <v>2268</v>
       </c>
       <c r="L69" s="121" t="n">
-        <v>544947</v>
+        <v>14679868</v>
       </c>
       <c r="M69" s="115" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="116" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="B70" s="116" t="inlineStr">
@@ -15786,47 +16780,47 @@
       </c>
       <c r="C70" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D70" s="118" t="n">
-        <v>500</v>
+        <v>24614</v>
       </c>
       <c r="E70" s="118" t="n">
-        <v>6553.05</v>
+        <v>34354</v>
       </c>
       <c r="F70" s="122" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.716481</v>
       </c>
       <c r="G70" s="118" t="n">
-        <v>1506.4</v>
+        <v>1505.7</v>
       </c>
       <c r="H70" s="120" t="n">
-        <v>753200</v>
+        <v>37061300</v>
       </c>
       <c r="I70" s="120" t="n">
-        <v>2299</v>
+        <v>21576</v>
       </c>
       <c r="J70" s="120" t="n">
-        <v>763</v>
+        <v>8956</v>
       </c>
       <c r="K70" s="120" t="n">
-        <v>610</v>
+        <v>5732</v>
       </c>
       <c r="L70" s="121" t="n">
-        <v>756872</v>
+        <v>37097564</v>
       </c>
       <c r="M70" s="115" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="116" t="inlineStr">
         <is>
-          <t>GPO468-1</t>
+          <t>GPO467</t>
         </is>
       </c>
       <c r="B71" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C71" s="117" t="inlineStr">
@@ -15835,43 +16829,43 @@
         </is>
       </c>
       <c r="D71" s="118" t="n">
-        <v>36190</v>
+        <v>1700</v>
       </c>
       <c r="E71" s="118" t="n">
-        <v>57650</v>
+        <v>6553.05</v>
       </c>
       <c r="F71" s="122" t="n">
-        <v>0.627754</v>
+        <v>0.259421</v>
       </c>
       <c r="G71" s="118" t="n">
-        <v>1481.9</v>
+        <v>1506.4</v>
       </c>
       <c r="H71" s="120" t="n">
-        <v>53629961</v>
+        <v>2560880</v>
       </c>
       <c r="I71" s="120" t="n">
-        <v>18605</v>
+        <v>7816</v>
       </c>
       <c r="J71" s="120" t="n">
-        <v>7847</v>
+        <v>2594</v>
       </c>
       <c r="K71" s="120" t="n">
-        <v>5022</v>
+        <v>2075</v>
       </c>
       <c r="L71" s="121" t="n">
-        <v>53661435</v>
+        <v>2573365</v>
       </c>
       <c r="M71" s="115" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="116" t="inlineStr">
         <is>
-          <t>GPO472</t>
+          <t>GPO469</t>
         </is>
       </c>
       <c r="B72" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C72" s="117" t="inlineStr">
@@ -15880,43 +16874,43 @@
         </is>
       </c>
       <c r="D72" s="118" t="n">
-        <v>180</v>
+        <v>3993.05</v>
       </c>
       <c r="E72" s="118" t="n">
-        <v>57650</v>
+        <v>6553.05</v>
       </c>
       <c r="F72" s="122" t="n">
-        <v>0.003122</v>
+        <v>0.6093420000000001</v>
       </c>
       <c r="G72" s="118" t="n">
-        <v>1481.9</v>
+        <v>1506.4</v>
       </c>
       <c r="H72" s="120" t="n">
-        <v>266742</v>
+        <v>6015131</v>
       </c>
       <c r="I72" s="120" t="n">
-        <v>93</v>
+        <v>18358</v>
       </c>
       <c r="J72" s="120" t="n">
-        <v>39</v>
+        <v>6093</v>
       </c>
       <c r="K72" s="120" t="n">
-        <v>25</v>
+        <v>4875</v>
       </c>
       <c r="L72" s="121" t="n">
-        <v>266899</v>
+        <v>6044457</v>
       </c>
       <c r="M72" s="115" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="116" t="inlineStr">
         <is>
-          <t>GPO468-2</t>
+          <t>GPO470</t>
         </is>
       </c>
       <c r="B73" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C73" s="117" t="inlineStr">
@@ -15925,221 +16919,223 @@
         </is>
       </c>
       <c r="D73" s="118" t="n">
-        <v>21280</v>
+        <v>360</v>
       </c>
       <c r="E73" s="118" t="n">
-        <v>57650</v>
+        <v>6553.05</v>
       </c>
       <c r="F73" s="122" t="n">
-        <v>0.369124</v>
+        <v>0.054936</v>
       </c>
       <c r="G73" s="118" t="n">
-        <v>1481.9</v>
+        <v>1506.4</v>
       </c>
       <c r="H73" s="120" t="n">
-        <v>31534832</v>
+        <v>542304</v>
       </c>
       <c r="I73" s="120" t="n">
-        <v>10940</v>
+        <v>1655</v>
       </c>
       <c r="J73" s="120" t="n">
-        <v>4614</v>
+        <v>549</v>
       </c>
       <c r="K73" s="120" t="n">
-        <v>2953</v>
+        <v>439</v>
       </c>
       <c r="L73" s="121" t="n">
-        <v>31553339</v>
+        <v>544947</v>
       </c>
       <c r="M73" s="115" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="116" t="inlineStr">
         <is>
-          <t>CPO692-1</t>
+          <t>GPO471</t>
         </is>
       </c>
       <c r="B74" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C74" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D74" s="118" t="n">
-        <v>11000</v>
+        <v>500</v>
       </c>
       <c r="E74" s="118" t="n">
-        <v>297580</v>
+        <v>6553.05</v>
       </c>
       <c r="F74" s="122" t="n">
-        <v>0.036965</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G74" s="118" t="n">
-        <v>1482.8</v>
+        <v>1506.4</v>
       </c>
       <c r="H74" s="120" t="n">
-        <v>16310800</v>
+        <v>753200</v>
       </c>
       <c r="I74" s="120" t="n">
-        <v>1096</v>
+        <v>2299</v>
       </c>
       <c r="J74" s="120" t="n">
-        <v>462</v>
+        <v>763</v>
       </c>
       <c r="K74" s="120" t="n">
-        <v>296</v>
+        <v>610</v>
       </c>
       <c r="L74" s="121" t="n">
-        <v>16312654</v>
+        <v>756872</v>
       </c>
       <c r="M74" s="115" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="116" t="inlineStr">
         <is>
-          <t>CPO692-2</t>
+          <t>GPO468-1</t>
         </is>
       </c>
       <c r="B75" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C75" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D75" s="118" t="n">
-        <v>286580</v>
+        <v>36190</v>
       </c>
       <c r="E75" s="118" t="n">
-        <v>297580</v>
+        <v>57650</v>
       </c>
       <c r="F75" s="122" t="n">
-        <v>0.963035</v>
+        <v>0.627754</v>
       </c>
       <c r="G75" s="118" t="n">
-        <v>1482.8</v>
+        <v>1481.9</v>
       </c>
       <c r="H75" s="120" t="n">
-        <v>424940824</v>
+        <v>53629961</v>
       </c>
       <c r="I75" s="120" t="n">
-        <v>28560</v>
+        <v>18605</v>
       </c>
       <c r="J75" s="120" t="n">
-        <v>12038</v>
+        <v>7847</v>
       </c>
       <c r="K75" s="120" t="n">
-        <v>7704</v>
+        <v>5022</v>
       </c>
       <c r="L75" s="121" t="n">
-        <v>424989126</v>
+        <v>53661435</v>
       </c>
       <c r="M75" s="115" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="116" t="inlineStr">
         <is>
-          <t>EPO18</t>
+          <t>GPO472</t>
         </is>
       </c>
       <c r="B76" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C76" s="117" t="inlineStr">
         <is>
-          <t>MAICO Italia</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D76" s="118" t="n">
-        <v>4388.4</v>
+        <v>180</v>
       </c>
       <c r="E76" s="118" t="n">
-        <v>4388.4</v>
+        <v>57650</v>
       </c>
       <c r="F76" s="122" t="n">
-        <v>1</v>
+        <v>0.003122</v>
       </c>
       <c r="G76" s="118" t="n">
-        <v>1741.08</v>
+        <v>1481.9</v>
       </c>
       <c r="H76" s="120" t="n">
-        <v>7640555</v>
+        <v>266742</v>
       </c>
       <c r="I76" s="120" t="n">
-        <v>43527</v>
+        <v>93</v>
       </c>
       <c r="J76" s="120" t="n">
-        <v>10000</v>
+        <v>39</v>
       </c>
       <c r="K76" s="120" t="n">
-        <v>8000</v>
+        <v>25</v>
       </c>
       <c r="L76" s="121" t="n">
-        <v>7702082</v>
-      </c>
+        <v>266899</v>
+      </c>
+      <c r="M76" s="115" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="116" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>GPO468-2</t>
         </is>
       </c>
       <c r="B77" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C77" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D77" s="118" t="n">
-        <v>17404</v>
+        <v>21280</v>
       </c>
       <c r="E77" s="118" t="n">
-        <v>21439</v>
+        <v>57650</v>
       </c>
       <c r="F77" s="122" t="n">
-        <v>0.811792</v>
+        <v>0.369124</v>
       </c>
       <c r="G77" s="118" t="n">
-        <v>1474.9</v>
+        <v>1481.9</v>
       </c>
       <c r="H77" s="120" t="n">
-        <v>25669160</v>
+        <v>31534832</v>
       </c>
       <c r="I77" s="120" t="n">
-        <v>23946</v>
+        <v>10940</v>
       </c>
       <c r="J77" s="120" t="n">
-        <v>10147</v>
+        <v>4614</v>
       </c>
       <c r="K77" s="120" t="n">
-        <v>6494</v>
+        <v>2953</v>
       </c>
       <c r="L77" s="121" t="n">
-        <v>25709747</v>
-      </c>
+        <v>31553339</v>
+      </c>
+      <c r="M77" s="115" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="116" t="inlineStr">
         <is>
-          <t>CPO695-1</t>
+          <t>CPO692-1</t>
         </is>
       </c>
       <c r="B78" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C78" s="117" t="inlineStr">
@@ -16148,42 +17144,43 @@
         </is>
       </c>
       <c r="D78" s="118" t="n">
-        <v>2058</v>
+        <v>11000</v>
       </c>
       <c r="E78" s="118" t="n">
-        <v>21439</v>
+        <v>297580</v>
       </c>
       <c r="F78" s="122" t="n">
-        <v>0.09599299999999999</v>
+        <v>0.036965</v>
       </c>
       <c r="G78" s="118" t="n">
-        <v>1474.9</v>
+        <v>1482.8</v>
       </c>
       <c r="H78" s="120" t="n">
-        <v>3035344</v>
+        <v>16310800</v>
       </c>
       <c r="I78" s="120" t="n">
-        <v>2832</v>
+        <v>1096</v>
       </c>
       <c r="J78" s="120" t="n">
-        <v>1200</v>
+        <v>462</v>
       </c>
       <c r="K78" s="120" t="n">
-        <v>768</v>
+        <v>296</v>
       </c>
       <c r="L78" s="121" t="n">
-        <v>3040144</v>
-      </c>
+        <v>16312654</v>
+      </c>
+      <c r="M78" s="115" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="116" t="inlineStr">
         <is>
-          <t>CPO695-2</t>
+          <t>CPO692-2</t>
         </is>
       </c>
       <c r="B79" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C79" s="117" t="inlineStr">
@@ -16192,66 +17189,67 @@
         </is>
       </c>
       <c r="D79" s="118" t="n">
-        <v>1977</v>
+        <v>286580</v>
       </c>
       <c r="E79" s="118" t="n">
-        <v>21439</v>
+        <v>297580</v>
       </c>
       <c r="F79" s="122" t="n">
-        <v>0.09221500000000001</v>
+        <v>0.963035</v>
       </c>
       <c r="G79" s="118" t="n">
-        <v>1474.9</v>
+        <v>1482.8</v>
       </c>
       <c r="H79" s="120" t="n">
-        <v>2915877</v>
+        <v>424940824</v>
       </c>
       <c r="I79" s="120" t="n">
-        <v>2720</v>
+        <v>28560</v>
       </c>
       <c r="J79" s="120" t="n">
-        <v>1153</v>
+        <v>12038</v>
       </c>
       <c r="K79" s="120" t="n">
-        <v>738</v>
+        <v>7704</v>
       </c>
       <c r="L79" s="121" t="n">
-        <v>2920488</v>
-      </c>
+        <v>424989126</v>
+      </c>
+      <c r="M79" s="115" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="116" t="inlineStr">
         <is>
-          <t>IPO016</t>
+          <t>EPO18</t>
         </is>
       </c>
       <c r="B80" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C80" s="117" t="inlineStr">
         <is>
-          <t>Integ</t>
+          <t>MAICO Italia</t>
         </is>
       </c>
       <c r="D80" s="118" t="n">
-        <v>6800</v>
+        <v>4388.4</v>
       </c>
       <c r="E80" s="118" t="n">
-        <v>6800</v>
+        <v>4388.4</v>
       </c>
       <c r="F80" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="118" t="n">
-        <v>1475.2</v>
+        <v>1741.08</v>
       </c>
       <c r="H80" s="120" t="n">
-        <v>10031360</v>
+        <v>7640555</v>
       </c>
       <c r="I80" s="120" t="n">
-        <v>29504</v>
+        <v>43527</v>
       </c>
       <c r="J80" s="120" t="n">
         <v>10000</v>
@@ -16260,62 +17258,62 @@
         <v>8000</v>
       </c>
       <c r="L80" s="121" t="n">
-        <v>10078864</v>
+        <v>7702082</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="116" t="inlineStr">
         <is>
-          <t>GPO478</t>
+          <t>CPO694</t>
         </is>
       </c>
       <c r="B81" s="116" t="inlineStr">
         <is>
-          <t>2026.05.19</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C81" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D81" s="118" t="n">
-        <v>180</v>
+        <v>17404</v>
       </c>
       <c r="E81" s="118" t="n">
-        <v>180</v>
+        <v>21439</v>
       </c>
       <c r="F81" s="122" t="n">
-        <v>1</v>
+        <v>0.811792</v>
       </c>
       <c r="G81" s="118" t="n">
-        <v>1518.9</v>
+        <v>1474.9</v>
       </c>
       <c r="H81" s="120" t="n">
-        <v>273402</v>
+        <v>25669160</v>
       </c>
       <c r="I81" s="120" t="n">
-        <v>30378</v>
+        <v>23946</v>
       </c>
       <c r="J81" s="120" t="n">
-        <v>2500</v>
+        <v>10147</v>
       </c>
       <c r="K81" s="120" t="n">
-        <v>8000</v>
+        <v>6494</v>
       </c>
       <c r="L81" s="121" t="n">
-        <v>314280</v>
+        <v>25709747</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="116" t="inlineStr">
         <is>
-          <t>CPO698</t>
+          <t>CPO695-1</t>
         </is>
       </c>
       <c r="B82" s="116" t="inlineStr">
         <is>
-          <t>2026.05.20</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C82" s="117" t="inlineStr">
@@ -16324,131 +17322,130 @@
         </is>
       </c>
       <c r="D82" s="118" t="n">
-        <v>4290</v>
+        <v>2058</v>
       </c>
       <c r="E82" s="118" t="n">
-        <v>4290</v>
+        <v>21439</v>
       </c>
       <c r="F82" s="122" t="n">
-        <v>1</v>
+        <v>0.09599299999999999</v>
       </c>
       <c r="G82" s="118" t="n">
-        <v>1510.6</v>
+        <v>1474.9</v>
       </c>
       <c r="H82" s="120" t="n">
-        <v>6480474</v>
+        <v>3035344</v>
       </c>
       <c r="I82" s="120" t="n">
-        <v>30212</v>
+        <v>2832</v>
       </c>
       <c r="J82" s="120" t="n">
-        <v>7500</v>
+        <v>1200</v>
       </c>
       <c r="K82" s="120" t="n">
-        <v>8000</v>
+        <v>768</v>
       </c>
       <c r="L82" s="121" t="n">
-        <v>6526186</v>
-      </c>
-      <c r="M82" s="40" t="n"/>
+        <v>3040144</v>
+      </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="116" t="inlineStr">
         <is>
-          <t>GPO473-1</t>
+          <t>CPO695-2</t>
         </is>
       </c>
       <c r="B83" s="116" t="inlineStr">
         <is>
-          <t>2026.05.29</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C83" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D83" s="118" t="n">
-        <v>98800</v>
+        <v>1977</v>
       </c>
       <c r="E83" s="118" t="n">
-        <v>99140</v>
+        <v>21439</v>
       </c>
       <c r="F83" s="122" t="n">
-        <v>0.996571</v>
+        <v>0.09221500000000001</v>
       </c>
       <c r="G83" s="118" t="n">
-        <v>1502.8</v>
+        <v>1474.9</v>
       </c>
       <c r="H83" s="120" t="n">
-        <v>148476640</v>
+        <v>2915877</v>
       </c>
       <c r="I83" s="120" t="n">
-        <v>29953</v>
+        <v>2720</v>
       </c>
       <c r="J83" s="120" t="n">
-        <v>12457</v>
+        <v>1153</v>
       </c>
       <c r="K83" s="120" t="n">
-        <v>7973</v>
+        <v>738</v>
       </c>
       <c r="L83" s="121" t="n">
-        <v>148527023</v>
+        <v>2920488</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="116" t="inlineStr">
         <is>
-          <t>GPO480</t>
+          <t>IPO016</t>
         </is>
       </c>
       <c r="B84" s="116" t="inlineStr">
         <is>
-          <t>2026.05.29</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C84" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Integ</t>
         </is>
       </c>
       <c r="D84" s="118" t="n">
-        <v>250</v>
+        <v>6800</v>
       </c>
       <c r="E84" s="118" t="n">
-        <v>99140</v>
+        <v>6800</v>
       </c>
       <c r="F84" s="122" t="n">
-        <v>0.002522</v>
+        <v>1</v>
       </c>
       <c r="G84" s="118" t="n">
-        <v>1502.8</v>
+        <v>1475.2</v>
       </c>
       <c r="H84" s="120" t="n">
-        <v>375700</v>
+        <v>10031360</v>
       </c>
       <c r="I84" s="120" t="n">
-        <v>76</v>
+        <v>29504</v>
       </c>
       <c r="J84" s="120" t="n">
-        <v>32</v>
+        <v>10000</v>
       </c>
       <c r="K84" s="120" t="n">
-        <v>20</v>
+        <v>8000</v>
       </c>
       <c r="L84" s="121" t="n">
-        <v>375828</v>
+        <v>10078864</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="116" t="inlineStr">
         <is>
-          <t>GPO479</t>
+          <t>GPO478</t>
         </is>
       </c>
       <c r="B85" s="116" t="inlineStr">
         <is>
-          <t>2026.05.29</t>
+          <t>2026.05.19</t>
         </is>
       </c>
       <c r="C85" s="117" t="inlineStr">
@@ -16457,42 +17454,42 @@
         </is>
       </c>
       <c r="D85" s="118" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E85" s="118" t="n">
-        <v>99140</v>
+        <v>180</v>
       </c>
       <c r="F85" s="122" t="n">
-        <v>0.000908</v>
+        <v>1</v>
       </c>
       <c r="G85" s="118" t="n">
-        <v>1502.8</v>
+        <v>1518.9</v>
       </c>
       <c r="H85" s="120" t="n">
-        <v>135252</v>
+        <v>273402</v>
       </c>
       <c r="I85" s="120" t="n">
-        <v>27</v>
+        <v>30378</v>
       </c>
       <c r="J85" s="120" t="n">
-        <v>11</v>
+        <v>2500</v>
       </c>
       <c r="K85" s="120" t="n">
-        <v>7</v>
+        <v>8000</v>
       </c>
       <c r="L85" s="121" t="n">
-        <v>135297</v>
+        <v>314280</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="116" t="inlineStr">
         <is>
-          <t>CPO697</t>
+          <t>CPO698</t>
         </is>
       </c>
       <c r="B86" s="116" t="inlineStr">
         <is>
-          <t>2026.05.29</t>
+          <t>2026.05.20</t>
         </is>
       </c>
       <c r="C86" s="117" t="inlineStr">
@@ -16501,37 +17498,38 @@
         </is>
       </c>
       <c r="D86" s="118" t="n">
-        <v>15289</v>
+        <v>4290</v>
       </c>
       <c r="E86" s="118" t="n">
-        <v>101638</v>
+        <v>4290</v>
       </c>
       <c r="F86" s="122" t="n">
-        <v>0.150426</v>
+        <v>1</v>
       </c>
       <c r="G86" s="118" t="n">
-        <v>1502.7</v>
+        <v>1510.6</v>
       </c>
       <c r="H86" s="120" t="n">
-        <v>22974780</v>
+        <v>6480474</v>
       </c>
       <c r="I86" s="120" t="n">
-        <v>4521</v>
+        <v>30212</v>
       </c>
       <c r="J86" s="120" t="n">
-        <v>1880</v>
+        <v>7500</v>
       </c>
       <c r="K86" s="120" t="n">
-        <v>1203</v>
+        <v>8000</v>
       </c>
       <c r="L86" s="121" t="n">
-        <v>22982384</v>
-      </c>
+        <v>6526186</v>
+      </c>
+      <c r="M86" s="40" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="116" t="inlineStr">
         <is>
-          <t>CPO696-1</t>
+          <t>GPO473-1</t>
         </is>
       </c>
       <c r="B87" s="116" t="inlineStr">
@@ -16541,216 +17539,668 @@
       </c>
       <c r="C87" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D87" s="118" t="n">
-        <v>78209</v>
+        <v>98800</v>
       </c>
       <c r="E87" s="118" t="n">
-        <v>101638</v>
+        <v>99140</v>
       </c>
       <c r="F87" s="122" t="n">
-        <v>0.769486</v>
+        <v>0.996571</v>
       </c>
       <c r="G87" s="118" t="n">
-        <v>1502.7</v>
+        <v>1502.8</v>
       </c>
       <c r="H87" s="120" t="n">
-        <v>117524664</v>
+        <v>148476640</v>
       </c>
       <c r="I87" s="120" t="n">
-        <v>23126</v>
+        <v>29953</v>
       </c>
       <c r="J87" s="120" t="n">
-        <v>9619</v>
+        <v>12457</v>
       </c>
       <c r="K87" s="120" t="n">
-        <v>6156</v>
+        <v>7973</v>
       </c>
       <c r="L87" s="121" t="n">
-        <v>117563565</v>
+        <v>148527023</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="116" t="inlineStr">
         <is>
+          <t>GPO480</t>
+        </is>
+      </c>
+      <c r="B88" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C88" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D88" s="118" t="n">
+        <v>250</v>
+      </c>
+      <c r="E88" s="118" t="n">
+        <v>99140</v>
+      </c>
+      <c r="F88" s="122" t="n">
+        <v>0.002522</v>
+      </c>
+      <c r="G88" s="118" t="n">
+        <v>1502.8</v>
+      </c>
+      <c r="H88" s="120" t="n">
+        <v>375700</v>
+      </c>
+      <c r="I88" s="120" t="n">
+        <v>76</v>
+      </c>
+      <c r="J88" s="120" t="n">
+        <v>32</v>
+      </c>
+      <c r="K88" s="120" t="n">
+        <v>20</v>
+      </c>
+      <c r="L88" s="121" t="n">
+        <v>375828</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="116" t="inlineStr">
+        <is>
+          <t>GPO479</t>
+        </is>
+      </c>
+      <c r="B89" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C89" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D89" s="118" t="n">
+        <v>90</v>
+      </c>
+      <c r="E89" s="118" t="n">
+        <v>99140</v>
+      </c>
+      <c r="F89" s="122" t="n">
+        <v>0.000908</v>
+      </c>
+      <c r="G89" s="118" t="n">
+        <v>1502.8</v>
+      </c>
+      <c r="H89" s="120" t="n">
+        <v>135252</v>
+      </c>
+      <c r="I89" s="120" t="n">
+        <v>27</v>
+      </c>
+      <c r="J89" s="120" t="n">
+        <v>11</v>
+      </c>
+      <c r="K89" s="120" t="n">
+        <v>7</v>
+      </c>
+      <c r="L89" s="121" t="n">
+        <v>135297</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="116" t="inlineStr">
+        <is>
+          <t>CPO697</t>
+        </is>
+      </c>
+      <c r="B90" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C90" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D90" s="118" t="n">
+        <v>15289</v>
+      </c>
+      <c r="E90" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F90" s="122" t="n">
+        <v>0.150426</v>
+      </c>
+      <c r="G90" s="118" t="n">
+        <v>1502.7</v>
+      </c>
+      <c r="H90" s="120" t="n">
+        <v>22974780</v>
+      </c>
+      <c r="I90" s="120" t="n">
+        <v>4521</v>
+      </c>
+      <c r="J90" s="120" t="n">
+        <v>1880</v>
+      </c>
+      <c r="K90" s="120" t="n">
+        <v>1203</v>
+      </c>
+      <c r="L90" s="121" t="n">
+        <v>22982384</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="116" t="inlineStr">
+        <is>
+          <t>CPO696-1</t>
+        </is>
+      </c>
+      <c r="B91" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C91" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D91" s="118" t="n">
+        <v>78209</v>
+      </c>
+      <c r="E91" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F91" s="122" t="n">
+        <v>0.769486</v>
+      </c>
+      <c r="G91" s="118" t="n">
+        <v>1502.7</v>
+      </c>
+      <c r="H91" s="120" t="n">
+        <v>117524664</v>
+      </c>
+      <c r="I91" s="120" t="n">
+        <v>23126</v>
+      </c>
+      <c r="J91" s="120" t="n">
+        <v>9619</v>
+      </c>
+      <c r="K91" s="120" t="n">
+        <v>6156</v>
+      </c>
+      <c r="L91" s="121" t="n">
+        <v>117563565</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="116" t="inlineStr">
+        <is>
           <t>CPO696-2</t>
         </is>
       </c>
-      <c r="B88" s="116" t="inlineStr">
+      <c r="B92" s="116" t="inlineStr">
         <is>
           <t>2026.05.29</t>
         </is>
       </c>
-      <c r="C88" s="117" t="inlineStr">
+      <c r="C92" s="117" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D88" s="118" t="n">
+      <c r="D92" s="118" t="n">
         <v>8140</v>
       </c>
-      <c r="E88" s="118" t="n">
+      <c r="E92" s="118" t="n">
         <v>101638</v>
       </c>
-      <c r="F88" s="122" t="n">
+      <c r="F92" s="122" t="n">
         <v>0.08008800000000001</v>
       </c>
-      <c r="G88" s="118" t="n">
+      <c r="G92" s="118" t="n">
         <v>1502.7</v>
       </c>
-      <c r="H88" s="120" t="n">
+      <c r="H92" s="120" t="n">
         <v>12231978</v>
       </c>
-      <c r="I88" s="120" t="n">
+      <c r="I92" s="120" t="n">
         <v>2407</v>
       </c>
-      <c r="J88" s="120" t="n">
+      <c r="J92" s="120" t="n">
         <v>1001</v>
       </c>
-      <c r="K88" s="120" t="n">
+      <c r="K92" s="120" t="n">
         <v>641</v>
       </c>
-      <c r="L88" s="121" t="n">
+      <c r="L92" s="121" t="n">
         <v>12236027</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="234" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="234" t="inlineStr">
         <is>
           <t>GPO481</t>
         </is>
       </c>
-      <c r="B89" s="234" t="inlineStr">
+      <c r="B93" s="234" t="inlineStr">
         <is>
           <t>2026.06.10</t>
         </is>
       </c>
-      <c r="C89" s="235" t="inlineStr">
+      <c r="C93" s="235" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D89" s="236" t="n">
+      <c r="D93" s="236" t="n">
         <v>500</v>
       </c>
-      <c r="E89" s="236" t="n">
+      <c r="E93" s="236" t="n">
         <v>119060</v>
       </c>
-      <c r="F89" s="240" t="n">
+      <c r="F93" s="240" t="n">
         <v>0.0042</v>
       </c>
-      <c r="G89" s="236" t="n">
+      <c r="G93" s="236" t="n">
         <v>1525.3</v>
       </c>
-      <c r="H89" s="238" t="n">
+      <c r="H93" s="238" t="n">
         <v>762650</v>
       </c>
-      <c r="I89" s="238" t="n">
+      <c r="I93" s="238" t="n">
         <v>128</v>
       </c>
-      <c r="J89" s="238" t="n">
+      <c r="J93" s="238" t="n">
         <v>52</v>
       </c>
-      <c r="K89" s="238" t="n">
+      <c r="K93" s="238" t="n">
         <v>34</v>
       </c>
-      <c r="L89" s="239" t="n">
+      <c r="L93" s="239" t="n">
         <v>762864</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="234" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="234" t="inlineStr">
         <is>
           <t>GPO473-2</t>
         </is>
       </c>
-      <c r="B90" s="234" t="inlineStr">
+      <c r="B94" s="234" t="inlineStr">
         <is>
           <t>2026.06.10</t>
         </is>
       </c>
-      <c r="C90" s="235" t="inlineStr">
+      <c r="C94" s="235" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D90" s="236" t="n">
+      <c r="D94" s="236" t="n">
         <v>69160</v>
       </c>
-      <c r="E90" s="236" t="n">
+      <c r="E94" s="236" t="n">
         <v>119060</v>
       </c>
-      <c r="F90" s="240" t="n">
+      <c r="F94" s="240" t="n">
         <v>0.580884</v>
       </c>
-      <c r="G90" s="236" t="n">
+      <c r="G94" s="236" t="n">
         <v>1525.3</v>
       </c>
-      <c r="H90" s="238" t="n">
+      <c r="H94" s="238" t="n">
         <v>105489748</v>
       </c>
-      <c r="I90" s="238" t="n">
+      <c r="I94" s="238" t="n">
         <v>17720</v>
       </c>
-      <c r="J90" s="238" t="n">
+      <c r="J94" s="238" t="n">
         <v>7261</v>
       </c>
-      <c r="K90" s="238" t="n">
+      <c r="K94" s="238" t="n">
         <v>4647</v>
       </c>
-      <c r="L90" s="239" t="n">
+      <c r="L94" s="239" t="n">
         <v>105519376</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="234" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="234" t="inlineStr">
         <is>
           <t>GPO473-3</t>
         </is>
       </c>
-      <c r="B91" s="234" t="inlineStr">
+      <c r="B95" s="234" t="inlineStr">
         <is>
           <t>2026.06.10</t>
         </is>
       </c>
-      <c r="C91" s="235" t="inlineStr">
+      <c r="C95" s="235" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D91" s="236" t="n">
+      <c r="D95" s="236" t="n">
         <v>49400</v>
       </c>
-      <c r="E91" s="236" t="n">
+      <c r="E95" s="236" t="n">
         <v>119060</v>
       </c>
-      <c r="F91" s="240" t="n">
+      <c r="F95" s="240" t="n">
         <v>0.414917</v>
       </c>
-      <c r="G91" s="236" t="n">
+      <c r="G95" s="236" t="n">
         <v>1525.3</v>
       </c>
-      <c r="H91" s="238" t="n">
+      <c r="H95" s="238" t="n">
         <v>75349820</v>
       </c>
-      <c r="I91" s="238" t="n">
+      <c r="I95" s="238" t="n">
         <v>12657</v>
       </c>
-      <c r="J91" s="238" t="n">
+      <c r="J95" s="238" t="n">
         <v>5186</v>
       </c>
-      <c r="K91" s="238" t="n">
+      <c r="K95" s="238" t="n">
         <v>3319</v>
       </c>
-      <c r="L91" s="239" t="n">
+      <c r="L95" s="239" t="n">
         <v>75370982</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="234" t="inlineStr">
+        <is>
+          <t>CPO696-3</t>
+        </is>
+      </c>
+      <c r="B96" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C96" s="235" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D96" s="236" t="n">
+        <v>351274</v>
+      </c>
+      <c r="E96" s="236" t="n">
+        <v>351274</v>
+      </c>
+      <c r="F96" s="240">
+        <f>IFERROR(D96/E96,0)</f>
+        <v/>
+      </c>
+      <c r="G96" s="236" t="n">
+        <v>1518</v>
+      </c>
+      <c r="H96" s="238" t="n">
+        <v>533233932</v>
+      </c>
+      <c r="I96" s="238" t="n">
+        <v>30360</v>
+      </c>
+      <c r="J96" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="K96" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L96" s="239">
+        <f>H96+I96+J96+K96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="234" t="inlineStr">
+        <is>
+          <t>APO001</t>
+        </is>
+      </c>
+      <c r="B97" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C97" s="235" t="inlineStr">
+        <is>
+          <t>Appotronics</t>
+        </is>
+      </c>
+      <c r="D97" s="236" t="n">
+        <v>12400</v>
+      </c>
+      <c r="E97" s="236" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F97" s="240">
+        <f>IFERROR(D97/E97,0)</f>
+        <v/>
+      </c>
+      <c r="G97" s="236" t="n">
+        <v>1517.1</v>
+      </c>
+      <c r="H97" s="238" t="n">
+        <v>18812040</v>
+      </c>
+      <c r="I97" s="238" t="n">
+        <v>30342</v>
+      </c>
+      <c r="J97" s="238" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K97" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L97" s="239">
+        <f>H97+I97+J97+K97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="234" t="inlineStr">
+        <is>
+          <t>MPO67</t>
+        </is>
+      </c>
+      <c r="B98" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C98" s="235" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D98" s="236" t="n">
+        <v>49138.8</v>
+      </c>
+      <c r="E98" s="236" t="n">
+        <v>60726</v>
+      </c>
+      <c r="F98" s="240">
+        <f>IFERROR(D98/E98,0)</f>
+        <v/>
+      </c>
+      <c r="G98" s="236" t="n">
+        <v>1517.3</v>
+      </c>
+      <c r="H98" s="238" t="n">
+        <v>74558330</v>
+      </c>
+      <c r="I98" s="238" t="n">
+        <v>24555</v>
+      </c>
+      <c r="J98" s="238" t="n">
+        <v>10115</v>
+      </c>
+      <c r="K98" s="238" t="n">
+        <v>6473</v>
+      </c>
+      <c r="L98" s="239">
+        <f>H98+I98+J98+K98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="234" t="inlineStr">
+        <is>
+          <t>MPO68</t>
+        </is>
+      </c>
+      <c r="B99" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C99" s="235" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D99" s="236" t="n">
+        <v>11587.2</v>
+      </c>
+      <c r="E99" s="236" t="n">
+        <v>60726</v>
+      </c>
+      <c r="F99" s="240">
+        <f>IFERROR(D99/E99,0)</f>
+        <v/>
+      </c>
+      <c r="G99" s="236" t="n">
+        <v>1517.3</v>
+      </c>
+      <c r="H99" s="238" t="n">
+        <v>17582284</v>
+      </c>
+      <c r="I99" s="238" t="n">
+        <v>5791</v>
+      </c>
+      <c r="J99" s="238" t="n">
+        <v>2385</v>
+      </c>
+      <c r="K99" s="238" t="n">
+        <v>1527</v>
+      </c>
+      <c r="L99" s="239">
+        <f>H99+I99+J99+K99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="234" t="inlineStr">
+        <is>
+          <t>GPO475</t>
+        </is>
+      </c>
+      <c r="B100" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C100" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D100" s="236" t="n">
+        <v>540</v>
+      </c>
+      <c r="E100" s="236" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F100" s="240">
+        <f>IFERROR(D100/E100,0)</f>
+        <v/>
+      </c>
+      <c r="G100" s="236" t="n">
+        <v>1516.8</v>
+      </c>
+      <c r="H100" s="238" t="n">
+        <v>819072</v>
+      </c>
+      <c r="I100" s="238" t="n">
+        <v>8030</v>
+      </c>
+      <c r="J100" s="238" t="n">
+        <v>1985</v>
+      </c>
+      <c r="K100" s="238" t="n">
+        <v>2118</v>
+      </c>
+      <c r="L100" s="239">
+        <f>H100+I100+J100+K100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="234" t="inlineStr">
+        <is>
+          <t>GPO475-수리</t>
+        </is>
+      </c>
+      <c r="B101" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C101" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D101" s="236" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E101" s="236" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F101" s="240">
+        <f>IFERROR(D101/E101,0)</f>
+        <v/>
+      </c>
+      <c r="G101" s="236" t="n">
+        <v>1516.8</v>
+      </c>
+      <c r="H101" s="238" t="n">
+        <v>2275200</v>
+      </c>
+      <c r="I101" s="238" t="n">
+        <v>22306</v>
+      </c>
+      <c r="J101" s="238" t="n">
+        <v>5515</v>
+      </c>
+      <c r="K101" s="238" t="n">
+        <v>5882</v>
+      </c>
+      <c r="L101" s="239">
+        <f>H101+I101+J101+K101</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A45:L45"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -14,9 +14,9 @@
     <sheet name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$44</definedName>
-    <definedName name="RemitTable2">'외화송금내역'!$A$47:$L$101</definedName>
     <definedName name="FxRateTable">환율!$A$7:$D$43</definedName>
+    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$40</definedName>
+    <definedName name="RemitTable2">'외화송금내역'!$A$43:$L$97</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1580,11 +1580,6 @@
     </comment>
     <comment ref="D5" authorId="0" shapeId="0">
       <text>
-        <t>출금내역만 확인. PO/송금확인서 미확인</t>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="0" shapeId="0">
-      <text>
         <t>출금내역만 확인. 송금확인서 미확인</t>
       </text>
     </comment>
@@ -10590,19 +10585,6 @@
       <c r="AE79" s="39" t="n"/>
       <c r="AF79" s="39" t="n"/>
     </row>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
     <row r="93">
       <c r="M93" s="40" t="n"/>
     </row>
@@ -11827,50 +11809,6 @@
       </c>
       <c r="L25" s="228" t="n"/>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
     <row r="70">
       <c r="M70" s="40" t="n"/>
     </row>
@@ -13537,38 +13475,6 @@
       </c>
       <c r="J38" s="292" t="inlineStr"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
     <row r="71">
       <c r="M71" s="40" t="n"/>
     </row>
@@ -13588,7 +13494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="160" min="1" max="1"/>
@@ -13791,16 +13697,16 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Thali Consulting</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>(PO미기재)</t>
+          <t>CPO-669</t>
         </is>
       </c>
       <c r="E5" s="33" t="n">
-        <v>9247.690000000001</v>
+        <v>7410</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>0</v>
@@ -13833,7 +13739,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2025.12.02</t>
+          <t>2025.12.09</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -13843,26 +13749,26 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>CPO-669</t>
+          <t>CPO675,677,CPO-664-2</t>
         </is>
       </c>
       <c r="E6" s="33" t="n">
-        <v>7410</v>
+        <v>6024</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0</v>
+        <v>1473.3</v>
       </c>
       <c r="G6" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0</v>
+        <v>8922625</v>
       </c>
       <c r="K6" s="9">
         <f>ROUND((E6+G6)*F6+H6+I6,0)</f>
@@ -13885,19 +13791,19 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>CPO675,677,CPO-664-2</t>
+          <t>GPO449,450,452,453,454</t>
         </is>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6024</v>
+        <v>7862</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1473.3</v>
+        <v>1473.2</v>
       </c>
       <c r="G7" s="33" t="n">
         <v>20</v>
@@ -13909,7 +13815,7 @@
         <v>8000</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>8922625</v>
+        <v>11629762</v>
       </c>
       <c r="K7" s="9">
         <f>ROUND((E7+G7)*F7+H7+I7,0)</f>
@@ -13927,24 +13833,24 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2025.12.09</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>GPO449,450,452,453,454</t>
+          <t>MPO-65,64</t>
         </is>
       </c>
       <c r="E8" s="33" t="n">
-        <v>7862</v>
+        <v>15040</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1473.2</v>
+        <v>1480</v>
       </c>
       <c r="G8" s="33" t="n">
         <v>20</v>
@@ -13956,7 +13862,7 @@
         <v>8000</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>11629762</v>
+        <v>22306800</v>
       </c>
       <c r="K8" s="9">
         <f>ROUND((E8+G8)*F8+H8+I8,0)</f>
@@ -13979,31 +13885,31 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>MPO-65,64</t>
+          <t>CPO-679,CPO-678-1</t>
         </is>
       </c>
       <c r="E9" s="33" t="n">
-        <v>15040</v>
+        <v>143557</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1480</v>
+        <v>1479.7</v>
       </c>
       <c r="G9" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>22306800</v>
+        <v>212471386</v>
       </c>
       <c r="K9" s="9">
         <f>ROUND((E9+G9)*F9+H9+I9,0)</f>
@@ -14021,36 +13927,36 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2025.12.29</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>CPO-679,CPO-678-1</t>
+          <t>GPO451,458,455,456,457</t>
         </is>
       </c>
       <c r="E10" s="33" t="n">
-        <v>143557</v>
+        <v>13860</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1479.7</v>
+        <v>1439.1</v>
       </c>
       <c r="G10" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>212471386</v>
+        <v>18264679</v>
       </c>
       <c r="K10" s="9">
         <f>ROUND((E10+G10)*F10+H10+I10,0)</f>
@@ -14068,36 +13974,36 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2025.12.19</t>
+          <t>2025.12.30</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>GDC(라이센스)</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>/ROC/라이센스</t>
+          <t>CPO676</t>
         </is>
       </c>
       <c r="E11" s="33" t="n">
-        <v>1200</v>
+        <v>36060</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1464.9</v>
+        <v>1442.7</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
+        <v>52073116</v>
       </c>
       <c r="K11" s="9">
         <f>ROUND((E11+G11)*F11+H11+I11,0)</f>
@@ -14115,36 +14021,36 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2025.12.29</t>
+          <t>2026.01.13</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>GPO451,458,455,456,457</t>
+          <t>CPO680</t>
         </is>
       </c>
       <c r="E12" s="33" t="n">
-        <v>13860</v>
+        <v>252</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1439.1</v>
+        <v>1479</v>
       </c>
       <c r="G12" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>18264679</v>
+        <v>412788</v>
       </c>
       <c r="K12" s="9">
         <f>ROUND((E12+G12)*F12+H12+I12,0)</f>
@@ -14162,36 +14068,36 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2025.12.30</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>CPO676</t>
+          <t>GPO459,460,461</t>
         </is>
       </c>
       <c r="E13" s="33" t="n">
-        <v>36060</v>
+        <v>3700</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1442.7</v>
+        <v>1475.7</v>
       </c>
       <c r="G13" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>52073116</v>
+        <v>5505104</v>
       </c>
       <c r="K13" s="9">
         <f>ROUND((E13+G13)*F13+H13+I13,0)</f>
@@ -14209,36 +14115,36 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026.01.13</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>CPO680</t>
+          <t>MPO-66</t>
         </is>
       </c>
       <c r="E14" s="33" t="n">
-        <v>252</v>
+        <v>9626.35</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="G14" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>412788</v>
+        <v>14256012</v>
       </c>
       <c r="K14" s="9">
         <f>ROUND((E14+G14)*F14+H14+I14,0)</f>
@@ -14256,36 +14162,36 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>GPO459,460,461</t>
+          <t>LPO-001</t>
         </is>
       </c>
       <c r="E15" s="33" t="n">
-        <v>3700</v>
+        <v>5056.8</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1475.7</v>
+        <v>1445.5</v>
       </c>
       <c r="G15" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5505104</v>
+        <v>7356514</v>
       </c>
       <c r="K15" s="9">
         <f>ROUND((E15+G15)*F15+H15+I15,0)</f>
@@ -14303,36 +14209,36 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>Monoplex</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>MPO-66</t>
+          <t>MONOPLEX20260126-01</t>
         </is>
       </c>
       <c r="E16" s="33" t="n">
-        <v>9626.35</v>
+        <v>25976</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>1476</v>
+        <v>1445.5</v>
       </c>
       <c r="G16" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>14256012</v>
+        <v>37597718</v>
       </c>
       <c r="K16" s="9">
         <f>ROUND((E16+G16)*F16+H16+I16,0)</f>
@@ -14350,36 +14256,36 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>LPO-001</t>
+          <t>CPO-682,683</t>
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>5056.8</v>
+        <v>24794</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>1445.5</v>
+        <v>1454.7</v>
       </c>
       <c r="G17" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>7356514</v>
+        <v>36117425</v>
       </c>
       <c r="K17" s="9">
         <f>ROUND((E17+G17)*F17+H17+I17,0)</f>
@@ -14397,36 +14303,36 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Monoplex</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>MONOPLEX20260126-01</t>
+          <t>GPO462,463,464</t>
         </is>
       </c>
       <c r="E18" s="33" t="n">
-        <v>25976</v>
+        <v>11599.57</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>1445.5</v>
+        <v>1453.6</v>
       </c>
       <c r="G18" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>37597718</v>
+        <v>16908206</v>
       </c>
       <c r="K18" s="9">
         <f>ROUND((E18+G18)*F18+H18+I18,0)</f>
@@ -14444,7 +14350,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.11</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -14454,14 +14360,14 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>CPO-682,683</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>24794</v>
+        <v>26358</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>1454.7</v>
+        <v>1460.7</v>
       </c>
       <c r="G19" s="33" t="n">
         <v>20</v>
@@ -14473,7 +14379,7 @@
         <v>8000</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>36117425</v>
+        <v>38550844</v>
       </c>
       <c r="K19" s="9">
         <f>ROUND((E19+G19)*F19+H19+I19,0)</f>
@@ -14491,24 +14397,24 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>GPO462,463,464</t>
+          <t>CPO686,CPO689</t>
         </is>
       </c>
       <c r="E20" s="33" t="n">
-        <v>11599.57</v>
+        <v>17538</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>1453.6</v>
+        <v>1451.7</v>
       </c>
       <c r="G20" s="33" t="n">
         <v>20</v>
@@ -14520,7 +14426,7 @@
         <v>8000</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>16908206</v>
+        <v>25506948</v>
       </c>
       <c r="K20" s="9">
         <f>ROUND((E20+G20)*F20+H20+I20,0)</f>
@@ -14538,7 +14444,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2026.02.11</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -14548,14 +14454,14 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>CPO685,667</t>
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>26358</v>
+        <v>142189</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>1460.7</v>
+        <v>1441.6</v>
       </c>
       <c r="G21" s="33" t="n">
         <v>20</v>
@@ -14567,7 +14473,7 @@
         <v>8000</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>38550844</v>
+        <v>205028994</v>
       </c>
       <c r="K21" s="9">
         <f>ROUND((E21+G21)*F21+H21+I21,0)</f>
@@ -14585,7 +14491,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.03.06</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -14595,26 +14501,26 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>CPO686,CPO689</t>
+          <t>CPO678-2</t>
         </is>
       </c>
       <c r="E22" s="33" t="n">
-        <v>17538</v>
+        <v>137850</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>1451.7</v>
+        <v>1477.6</v>
       </c>
       <c r="G22" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>25506948</v>
+        <v>203737212</v>
       </c>
       <c r="K22" s="9">
         <f>ROUND((E22+G22)*F22+H22+I22,0)</f>
@@ -14632,7 +14538,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -14642,14 +14548,14 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>CPO685,667</t>
+          <t>CPO690,691</t>
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>142189</v>
+        <v>34354</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1441.6</v>
+        <v>1505.7</v>
       </c>
       <c r="G23" s="33" t="n">
         <v>20</v>
@@ -14661,7 +14567,7 @@
         <v>8000</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>205028994</v>
+        <v>51777431</v>
       </c>
       <c r="K23" s="9">
         <f>ROUND((E23+G23)*F23+H23+I23,0)</f>
@@ -14679,36 +14585,36 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2026.03.06</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>CPO678-2</t>
+          <t>GPO469,467,470,471</t>
         </is>
       </c>
       <c r="E24" s="33" t="n">
-        <v>137850</v>
+        <v>6553.05</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>1477.6</v>
+        <v>1506.4</v>
       </c>
       <c r="G24" s="33" t="n">
         <v>20</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>12500</v>
+        <v>10000</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>203737212</v>
+        <v>9919642</v>
       </c>
       <c r="K24" s="9">
         <f>ROUND((E24+G24)*F24+H24+I24,0)</f>
@@ -14726,24 +14632,24 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>CPO690,691</t>
+          <t>GPO468-1, 472, 468-2</t>
         </is>
       </c>
       <c r="E25" s="33" t="n">
-        <v>34354</v>
+        <v>57650</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>1505.7</v>
+        <v>1481.9</v>
       </c>
       <c r="G25" s="33" t="n">
         <v>20</v>
@@ -14755,7 +14661,7 @@
         <v>8000</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>51777431</v>
+        <v>85481673</v>
       </c>
       <c r="K25" s="9">
         <f>ROUND((E25+G25)*F25+H25+I25,0)</f>
@@ -14768,94 +14674,94 @@
       <c r="M25" s="115" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="96" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.01</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>GPO469,467,470,471</t>
-        </is>
-      </c>
-      <c r="E26" s="33" t="n">
-        <v>6553.05</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1506.4</v>
-      </c>
-      <c r="G26" s="33" t="n">
+      <c r="B26" s="96" t="inlineStr">
+        <is>
+          <t>2026.04.21</t>
+        </is>
+      </c>
+      <c r="C26" s="97" t="inlineStr">
+        <is>
+          <t>Ferco</t>
+        </is>
+      </c>
+      <c r="D26" s="96" t="inlineStr">
+        <is>
+          <t>MONOPLEX20260126-01</t>
+        </is>
+      </c>
+      <c r="E26" s="98" t="n">
+        <v>25976</v>
+      </c>
+      <c r="F26" s="196" t="n">
+        <v>1473.3</v>
+      </c>
+      <c r="G26" s="98" t="n">
         <v>20</v>
       </c>
-      <c r="H26" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I26" s="9" t="n">
+      <c r="H26" s="99" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I26" s="99" t="n">
         <v>8000</v>
       </c>
-      <c r="J26" s="9" t="n">
-        <v>9919642</v>
-      </c>
-      <c r="K26" s="9">
+      <c r="J26" s="99" t="n">
+        <v>38320406</v>
+      </c>
+      <c r="K26" s="99">
         <f>ROUND((E26+G26)*F26+H26+I26,0)</f>
         <v/>
       </c>
-      <c r="L26" s="35">
+      <c r="L26" s="100">
         <f>J26-K26</f>
         <v/>
       </c>
       <c r="M26" s="115" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="96" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>2026.04.14</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>GPO468-1, 472, 468-2</t>
-        </is>
-      </c>
-      <c r="E27" s="33" t="n">
-        <v>57650</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>1481.9</v>
-      </c>
-      <c r="G27" s="33" t="n">
+      <c r="B27" s="96" t="inlineStr">
+        <is>
+          <t>2026.04.22</t>
+        </is>
+      </c>
+      <c r="C27" s="97" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D27" s="96" t="inlineStr">
+        <is>
+          <t>CPO692(692-1, 692-2)</t>
+        </is>
+      </c>
+      <c r="E27" s="98" t="n">
+        <v>297580</v>
+      </c>
+      <c r="F27" s="196" t="n">
+        <v>1482.8</v>
+      </c>
+      <c r="G27" s="98" t="n">
         <v>20</v>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="H27" s="99" t="n">
         <v>12500</v>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I27" s="99" t="n">
         <v>8000</v>
       </c>
-      <c r="J27" s="9" t="n">
-        <v>85481673</v>
-      </c>
-      <c r="K27" s="9">
+      <c r="J27" s="99" t="n">
+        <v>441301780</v>
+      </c>
+      <c r="K27" s="99">
         <f>ROUND((E27+G27)*F27+H27+I27,0)</f>
         <v/>
       </c>
-      <c r="L27" s="35">
+      <c r="L27" s="100">
         <f>J27-K27</f>
         <v/>
       </c>
@@ -14867,36 +14773,36 @@
       </c>
       <c r="B28" s="96" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C28" s="97" t="inlineStr">
         <is>
-          <t>Swank</t>
+          <t>MAICO Italia (EUR)</t>
         </is>
       </c>
       <c r="D28" s="96" t="inlineStr">
         <is>
-          <t>(영화 라이센스)</t>
+          <t>EPO18</t>
         </is>
       </c>
       <c r="E28" s="98" t="n">
-        <v>814</v>
+        <v>4388.4</v>
       </c>
       <c r="F28" s="196" t="n">
-        <v>1505</v>
+        <v>1741.08</v>
       </c>
       <c r="G28" s="98" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H28" s="99" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="I28" s="99" t="n">
         <v>8000</v>
       </c>
       <c r="J28" s="99" t="n">
-        <v>1268170</v>
+        <v>7702082</v>
       </c>
       <c r="K28" s="99">
         <f>ROUND((E28+G28)*F28+H28+I28,0)</f>
@@ -14909,192 +14815,190 @@
       <c r="M28" s="115" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="96" t="n">
+      <c r="A29" s="116" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.02</t>
-        </is>
-      </c>
-      <c r="C29" s="97" t="inlineStr">
-        <is>
-          <t>Monoplex</t>
-        </is>
-      </c>
-      <c r="D29" s="96" t="inlineStr">
-        <is>
-          <t>(영업)</t>
-        </is>
-      </c>
-      <c r="E29" s="98" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F29" s="196" t="n">
-        <v>1520.1</v>
-      </c>
-      <c r="G29" s="98" t="n">
+      <c r="B29" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.04</t>
+        </is>
+      </c>
+      <c r="C29" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D29" s="116" t="inlineStr">
+        <is>
+          <t>CPO694, CPO695-1, CPO695-2</t>
+        </is>
+      </c>
+      <c r="E29" s="118" t="n">
+        <v>21439</v>
+      </c>
+      <c r="F29" s="197" t="n">
+        <v>1474.9</v>
+      </c>
+      <c r="G29" s="118" t="n">
         <v>20</v>
       </c>
-      <c r="H29" s="99" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I29" s="99" t="n">
+      <c r="H29" s="120" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I29" s="120" t="n">
         <v>8000</v>
       </c>
-      <c r="J29" s="99" t="n">
-        <v>45666402</v>
-      </c>
-      <c r="K29" s="99">
+      <c r="J29" s="120" t="n">
+        <v>31670379</v>
+      </c>
+      <c r="K29" s="120">
         <f>ROUND((E29+G29)*F29+H29+I29,0)</f>
         <v/>
       </c>
-      <c r="L29" s="100">
+      <c r="L29" s="121">
         <f>J29-K29</f>
         <v/>
       </c>
-      <c r="M29" s="115" t="n"/>
+      <c r="M29" s="114" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="96" t="n">
+      <c r="A30" s="116" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.21</t>
-        </is>
-      </c>
-      <c r="C30" s="97" t="inlineStr">
+      <c r="B30" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.04</t>
+        </is>
+      </c>
+      <c r="C30" s="117" t="inlineStr">
+        <is>
+          <t>Integ Process Group</t>
+        </is>
+      </c>
+      <c r="D30" s="116" t="inlineStr">
+        <is>
+          <t>IPO016 (JNR-410)</t>
+        </is>
+      </c>
+      <c r="E30" s="118" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F30" s="197" t="n">
+        <v>1475.2</v>
+      </c>
+      <c r="G30" s="118" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" s="120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I30" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J30" s="120" t="n">
+        <v>10078864</v>
+      </c>
+      <c r="K30" s="120">
+        <f>ROUND((E30+G30)*F30+H30+I30,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="121">
+        <f>J30-K30</f>
+        <v/>
+      </c>
+      <c r="M30" s="114" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="116" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.12</t>
+        </is>
+      </c>
+      <c r="C31" s="117" t="inlineStr">
         <is>
           <t>Ferco</t>
         </is>
       </c>
-      <c r="D30" s="96" t="inlineStr">
-        <is>
-          <t>MONOPLEX20260126-01</t>
-        </is>
-      </c>
-      <c r="E30" s="98" t="n">
-        <v>25976</v>
-      </c>
-      <c r="F30" s="196" t="n">
-        <v>1473.3</v>
-      </c>
-      <c r="G30" s="98" t="n">
+      <c r="D31" s="116" t="inlineStr">
+        <is>
+          <t>PI44133-1</t>
+        </is>
+      </c>
+      <c r="E31" s="118" t="n">
+        <v>4416</v>
+      </c>
+      <c r="F31" s="197" t="n">
+        <v>1755.24</v>
+      </c>
+      <c r="G31" s="118" t="n">
+        <v>25</v>
+      </c>
+      <c r="H31" s="120" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I31" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J31" s="120" t="n">
+        <v>7813020</v>
+      </c>
+      <c r="K31" s="120">
+        <f>ROUND((E31+G31)*F31+H31+I31,0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="121">
+        <f>J31-K31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="116" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.19</t>
+        </is>
+      </c>
+      <c r="C32" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D32" s="116" t="inlineStr">
+        <is>
+          <t>GPO478</t>
+        </is>
+      </c>
+      <c r="E32" s="118" t="n">
+        <v>180</v>
+      </c>
+      <c r="F32" s="197" t="n">
+        <v>1518.9</v>
+      </c>
+      <c r="G32" s="118" t="n">
         <v>20</v>
       </c>
-      <c r="H30" s="99" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I30" s="99" t="n">
+      <c r="H32" s="120" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I32" s="120" t="n">
         <v>8000</v>
       </c>
-      <c r="J30" s="99" t="n">
-        <v>38320406</v>
-      </c>
-      <c r="K30" s="99">
-        <f>ROUND((E30+G30)*F30+H30+I30,0)</f>
-        <v/>
-      </c>
-      <c r="L30" s="100">
-        <f>J30-K30</f>
-        <v/>
-      </c>
-      <c r="M30" s="115" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="96" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C31" s="97" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D31" s="96" t="inlineStr">
-        <is>
-          <t>CPO692(692-1, 692-2)</t>
-        </is>
-      </c>
-      <c r="E31" s="98" t="n">
-        <v>297580</v>
-      </c>
-      <c r="F31" s="196" t="n">
-        <v>1482.8</v>
-      </c>
-      <c r="G31" s="98" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" s="99" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I31" s="99" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J31" s="99" t="n">
-        <v>441301780</v>
-      </c>
-      <c r="K31" s="99">
-        <f>ROUND((E31+G31)*F31+H31+I31,0)</f>
-        <v/>
-      </c>
-      <c r="L31" s="100">
-        <f>J31-K31</f>
-        <v/>
-      </c>
-      <c r="M31" s="115" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="96" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="96" t="inlineStr">
-        <is>
-          <t>2026.04.22</t>
-        </is>
-      </c>
-      <c r="C32" s="97" t="inlineStr">
-        <is>
-          <t>MAICO Italia (EUR)</t>
-        </is>
-      </c>
-      <c r="D32" s="96" t="inlineStr">
-        <is>
-          <t>EPO18</t>
-        </is>
-      </c>
-      <c r="E32" s="98" t="n">
-        <v>4388.4</v>
-      </c>
-      <c r="F32" s="196" t="n">
-        <v>1741.08</v>
-      </c>
-      <c r="G32" s="98" t="n">
-        <v>25</v>
-      </c>
-      <c r="H32" s="99" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I32" s="99" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J32" s="99" t="n">
-        <v>7702082</v>
-      </c>
-      <c r="K32" s="99">
+      <c r="J32" s="120" t="n">
+        <v>314280</v>
+      </c>
+      <c r="K32" s="120">
         <f>ROUND((E32+G32)*F32+H32+I32,0)</f>
         <v/>
       </c>
-      <c r="L32" s="100">
+      <c r="L32" s="121">
         <f>J32-K32</f>
         <v/>
       </c>
-      <c r="M32" s="115" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="116" t="n">
@@ -15102,7 +15006,7 @@
       </c>
       <c r="B33" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.20</t>
         </is>
       </c>
       <c r="C33" s="117" t="inlineStr">
@@ -15112,26 +15016,26 @@
       </c>
       <c r="D33" s="116" t="inlineStr">
         <is>
-          <t>CPO694, CPO695-1, CPO695-2</t>
+          <t>CPO698</t>
         </is>
       </c>
       <c r="E33" s="118" t="n">
-        <v>21439</v>
+        <v>4290</v>
       </c>
       <c r="F33" s="197" t="n">
-        <v>1474.9</v>
+        <v>1510.6</v>
       </c>
       <c r="G33" s="118" t="n">
         <v>20</v>
       </c>
       <c r="H33" s="120" t="n">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="I33" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="J33" s="120" t="n">
-        <v>31670379</v>
+        <v>6526186</v>
       </c>
       <c r="K33" s="120">
         <f>ROUND((E33+G33)*F33+H33+I33,0)</f>
@@ -15141,7 +15045,6 @@
         <f>J33-K33</f>
         <v/>
       </c>
-      <c r="M33" s="114" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="116" t="n">
@@ -15149,36 +15052,36 @@
       </c>
       <c r="B34" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C34" s="117" t="inlineStr">
         <is>
-          <t>Integ Process Group</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D34" s="116" t="inlineStr">
         <is>
-          <t>IPO016 (JNR-410)</t>
+          <t>GPO480, GPO479, GPO473-1</t>
         </is>
       </c>
       <c r="E34" s="118" t="n">
-        <v>6800</v>
+        <v>99140</v>
       </c>
       <c r="F34" s="197" t="n">
-        <v>1475.2</v>
+        <v>1502.8</v>
       </c>
       <c r="G34" s="118" t="n">
         <v>20</v>
       </c>
       <c r="H34" s="120" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I34" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="J34" s="120" t="n">
-        <v>10078864</v>
+        <v>149038148</v>
       </c>
       <c r="K34" s="120">
         <f>ROUND((E34+G34)*F34+H34+I34,0)</f>
@@ -15188,7 +15091,6 @@
         <f>J34-K34</f>
         <v/>
       </c>
-      <c r="M34" s="114" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="116" t="n">
@@ -15196,36 +15098,36 @@
       </c>
       <c r="B35" s="116" t="inlineStr">
         <is>
-          <t>2026.05.12</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C35" s="117" t="inlineStr">
         <is>
-          <t>Ferco</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D35" s="116" t="inlineStr">
         <is>
-          <t>PI44133-1</t>
+          <t>CPO697, CPO696-1, CPO696-2</t>
         </is>
       </c>
       <c r="E35" s="118" t="n">
-        <v>4416</v>
+        <v>101638</v>
       </c>
       <c r="F35" s="197" t="n">
-        <v>1755.24</v>
+        <v>1502.7</v>
       </c>
       <c r="G35" s="118" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H35" s="120" t="n">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="I35" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="J35" s="120" t="n">
-        <v>7813020</v>
+        <v>152781976</v>
       </c>
       <c r="K35" s="120">
         <f>ROUND((E35+G35)*F35+H35+I35,0)</f>
@@ -15237,185 +15139,185 @@
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="116" t="n">
+      <c r="A36" s="234" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.19</t>
-        </is>
-      </c>
-      <c r="C36" s="117" t="inlineStr">
+      <c r="B36" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C36" s="235" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D36" s="116" t="inlineStr">
-        <is>
-          <t>GPO478</t>
-        </is>
-      </c>
-      <c r="E36" s="118" t="n">
-        <v>180</v>
-      </c>
-      <c r="F36" s="197" t="n">
-        <v>1518.9</v>
-      </c>
-      <c r="G36" s="118" t="n">
+      <c r="D36" s="234" t="inlineStr">
+        <is>
+          <t>GPO481, GPO473-2, GPO473-3</t>
+        </is>
+      </c>
+      <c r="E36" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F36" s="237" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="G36" s="236" t="n">
         <v>20</v>
       </c>
-      <c r="H36" s="120" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I36" s="120" t="n">
+      <c r="H36" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I36" s="238" t="n">
         <v>8000</v>
       </c>
-      <c r="J36" s="120" t="n">
-        <v>314280</v>
-      </c>
-      <c r="K36" s="120">
+      <c r="J36" s="238" t="n">
+        <v>181653224</v>
+      </c>
+      <c r="K36" s="238">
         <f>ROUND((E36+G36)*F36+H36+I36,0)</f>
         <v/>
       </c>
-      <c r="L36" s="121">
+      <c r="L36" s="239">
         <f>J36-K36</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="116" t="n">
+      <c r="A37" s="234" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.20</t>
-        </is>
-      </c>
-      <c r="C37" s="117" t="inlineStr">
+      <c r="B37" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C37" s="235" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D37" s="116" t="inlineStr">
-        <is>
-          <t>CPO698</t>
-        </is>
-      </c>
-      <c r="E37" s="118" t="n">
-        <v>4290</v>
-      </c>
-      <c r="F37" s="197" t="n">
-        <v>1510.6</v>
-      </c>
-      <c r="G37" s="118" t="n">
+      <c r="D37" s="234" t="inlineStr">
+        <is>
+          <t>CPO696-3</t>
+        </is>
+      </c>
+      <c r="E37" s="236" t="n">
+        <v>351274</v>
+      </c>
+      <c r="F37" s="237" t="n">
+        <v>1518</v>
+      </c>
+      <c r="G37" s="236" t="n">
         <v>20</v>
       </c>
-      <c r="H37" s="120" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I37" s="120" t="n">
+      <c r="H37" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I37" s="238" t="n">
         <v>8000</v>
       </c>
-      <c r="J37" s="120" t="n">
-        <v>6526186</v>
-      </c>
-      <c r="K37" s="120">
+      <c r="J37" s="238" t="n">
+        <v>533284792</v>
+      </c>
+      <c r="K37" s="238">
         <f>ROUND((E37+G37)*F37+H37+I37,0)</f>
         <v/>
       </c>
-      <c r="L37" s="121">
+      <c r="L37" s="239">
         <f>J37-K37</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="116" t="n">
+      <c r="A38" s="234" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C38" s="117" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D38" s="116" t="inlineStr">
-        <is>
-          <t>GPO480, GPO479, GPO473-1</t>
-        </is>
-      </c>
-      <c r="E38" s="118" t="n">
-        <v>99140</v>
-      </c>
-      <c r="F38" s="197" t="n">
-        <v>1502.8</v>
-      </c>
-      <c r="G38" s="118" t="n">
+      <c r="B38" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C38" s="235" t="inlineStr">
+        <is>
+          <t>Appotronics</t>
+        </is>
+      </c>
+      <c r="D38" s="234" t="inlineStr">
+        <is>
+          <t>APO001 (S20-C2220-BEAB)</t>
+        </is>
+      </c>
+      <c r="E38" s="236" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F38" s="237" t="n">
+        <v>1517.1</v>
+      </c>
+      <c r="G38" s="236" t="n">
         <v>20</v>
       </c>
-      <c r="H38" s="120" t="n">
+      <c r="H38" s="238" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I38" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J38" s="238" t="n">
+        <v>18860382</v>
+      </c>
+      <c r="K38" s="238">
+        <f>ROUND((E38+G38)*F38+H38+I38,0)</f>
+        <v/>
+      </c>
+      <c r="L38" s="239">
+        <f>J38-K38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="234" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C39" s="235" t="inlineStr">
+        <is>
+          <t>MMK Europe</t>
+        </is>
+      </c>
+      <c r="D39" s="234" t="inlineStr">
+        <is>
+          <t>MPO67, MPO68</t>
+        </is>
+      </c>
+      <c r="E39" s="236" t="n">
+        <v>60726</v>
+      </c>
+      <c r="F39" s="237" t="n">
+        <v>1517.3</v>
+      </c>
+      <c r="G39" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" s="238" t="n">
         <v>12500</v>
       </c>
-      <c r="I38" s="120" t="n">
+      <c r="I39" s="238" t="n">
         <v>8000</v>
       </c>
-      <c r="J38" s="120" t="n">
-        <v>149038148</v>
-      </c>
-      <c r="K38" s="120">
-        <f>ROUND((E38+G38)*F38+H38+I38,0)</f>
-        <v/>
-      </c>
-      <c r="L38" s="121">
-        <f>J38-K38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="116" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C39" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D39" s="116" t="inlineStr">
-        <is>
-          <t>CPO697, CPO696-1, CPO696-2</t>
-        </is>
-      </c>
-      <c r="E39" s="118" t="n">
-        <v>101638</v>
-      </c>
-      <c r="F39" s="197" t="n">
-        <v>1502.7</v>
-      </c>
-      <c r="G39" s="118" t="n">
-        <v>20</v>
-      </c>
-      <c r="H39" s="120" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I39" s="120" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J39" s="120" t="n">
-        <v>152781976</v>
-      </c>
-      <c r="K39" s="120">
+      <c r="J39" s="238" t="n">
+        <v>92190405</v>
+      </c>
+      <c r="K39" s="238">
         <f>ROUND((E39+G39)*F39+H39+I39,0)</f>
         <v/>
       </c>
-      <c r="L39" s="121">
+      <c r="L39" s="239">
         <f>J39-K39</f>
         <v/>
       </c>
@@ -15426,7 +15328,7 @@
       </c>
       <c r="B40" s="234" t="inlineStr">
         <is>
-          <t>2026.06.10</t>
+          <t>2026.06.17</t>
         </is>
       </c>
       <c r="C40" s="235" t="inlineStr">
@@ -15436,26 +15338,26 @@
       </c>
       <c r="D40" s="234" t="inlineStr">
         <is>
-          <t>GPO481, GPO473-2, GPO473-3</t>
+          <t>GPO475, SR-1000수리</t>
         </is>
       </c>
       <c r="E40" s="236" t="n">
-        <v>119060</v>
+        <v>2040</v>
       </c>
       <c r="F40" s="237" t="n">
-        <v>1525.3</v>
+        <v>1516.8</v>
       </c>
       <c r="G40" s="236" t="n">
         <v>20</v>
       </c>
       <c r="H40" s="238" t="n">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="I40" s="238" t="n">
         <v>8000</v>
       </c>
       <c r="J40" s="238" t="n">
-        <v>181653224</v>
+        <v>3140108</v>
       </c>
       <c r="K40" s="238">
         <f>ROUND((E40+G40)*F40+H40+I40,0)</f>
@@ -15467,325 +15369,321 @@
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="234" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C41" s="235" t="inlineStr">
+      <c r="A41" s="169" t="inlineStr">
+        <is>
+          <t>② PO별 비용 안분 내역</t>
+        </is>
+      </c>
+      <c r="B41" s="148" t="n"/>
+      <c r="C41" s="148" t="n"/>
+      <c r="D41" s="148" t="n"/>
+      <c r="E41" s="148" t="n"/>
+      <c r="F41" s="148" t="n"/>
+      <c r="G41" s="148" t="n"/>
+      <c r="H41" s="148" t="n"/>
+      <c r="I41" s="148" t="n"/>
+      <c r="J41" s="148" t="n"/>
+      <c r="K41" s="148" t="n"/>
+      <c r="L41" s="149" t="n"/>
+      <c r="M41" s="115" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="150" t="inlineStr">
+        <is>
+          <t>PO No.</t>
+        </is>
+      </c>
+      <c r="B42" s="150" t="inlineStr">
+        <is>
+          <t>송금일</t>
+        </is>
+      </c>
+      <c r="C42" s="150" t="inlineStr">
+        <is>
+          <t>업체</t>
+        </is>
+      </c>
+      <c r="D42" s="150" t="inlineStr">
+        <is>
+          <t>PO USD</t>
+        </is>
+      </c>
+      <c r="E42" s="150" t="inlineStr">
+        <is>
+          <t>그룹총USD</t>
+        </is>
+      </c>
+      <c r="F42" s="150" t="inlineStr">
+        <is>
+          <t>배부비율</t>
+        </is>
+      </c>
+      <c r="G42" s="150" t="inlineStr">
+        <is>
+          <t>적용환율</t>
+        </is>
+      </c>
+      <c r="H42" s="150" t="inlineStr">
+        <is>
+          <t>원화환산액</t>
+        </is>
+      </c>
+      <c r="I42" s="150" t="inlineStr">
+        <is>
+          <t>중개수수료안분</t>
+        </is>
+      </c>
+      <c r="J42" s="150" t="inlineStr">
+        <is>
+          <t>수수료안분</t>
+        </is>
+      </c>
+      <c r="K42" s="150" t="inlineStr">
+        <is>
+          <t>전신료안분</t>
+        </is>
+      </c>
+      <c r="L42" s="150" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="M42" s="115" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="116" t="inlineStr">
+        <is>
+          <t>CPO678-1</t>
+        </is>
+      </c>
+      <c r="B43" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.16</t>
+        </is>
+      </c>
+      <c r="C43" s="117" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D41" s="234" t="inlineStr">
-        <is>
-          <t>CPO696-3</t>
-        </is>
-      </c>
-      <c r="E41" s="236" t="n">
-        <v>351274</v>
-      </c>
-      <c r="F41" s="237" t="n">
-        <v>1518</v>
-      </c>
-      <c r="G41" s="236" t="n">
-        <v>20</v>
-      </c>
-      <c r="H41" s="238" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I41" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J41" s="238" t="n">
-        <v>533284792</v>
-      </c>
-      <c r="K41" s="238">
-        <f>ROUND((E41+G41)*F41+H41+I41,0)</f>
-        <v/>
-      </c>
-      <c r="L41" s="239">
-        <f>J41-K41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="234" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C42" s="235" t="inlineStr">
-        <is>
-          <t>Appotronics</t>
-        </is>
-      </c>
-      <c r="D42" s="234" t="inlineStr">
-        <is>
-          <t>APO001 (S20-C2220-BEAB)</t>
-        </is>
-      </c>
-      <c r="E42" s="236" t="n">
-        <v>12400</v>
-      </c>
-      <c r="F42" s="237" t="n">
-        <v>1517.1</v>
-      </c>
-      <c r="G42" s="236" t="n">
-        <v>20</v>
-      </c>
-      <c r="H42" s="238" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I42" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J42" s="238" t="n">
-        <v>18860382</v>
-      </c>
-      <c r="K42" s="238">
-        <f>ROUND((E42+G42)*F42+H42+I42,0)</f>
-        <v/>
-      </c>
-      <c r="L42" s="239">
-        <f>J42-K42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="234" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C43" s="235" t="inlineStr">
-        <is>
-          <t>MMK Europe</t>
-        </is>
-      </c>
-      <c r="D43" s="234" t="inlineStr">
-        <is>
-          <t>MPO67, MPO68</t>
-        </is>
-      </c>
-      <c r="E43" s="236" t="n">
-        <v>60726</v>
-      </c>
-      <c r="F43" s="237" t="n">
-        <v>1517.3</v>
-      </c>
-      <c r="G43" s="236" t="n">
-        <v>20</v>
-      </c>
-      <c r="H43" s="238" t="n">
-        <v>12500</v>
-      </c>
-      <c r="I43" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J43" s="238" t="n">
-        <v>92190405</v>
-      </c>
-      <c r="K43" s="238">
-        <f>ROUND((E43+G43)*F43+H43+I43,0)</f>
-        <v/>
-      </c>
-      <c r="L43" s="239">
-        <f>J43-K43</f>
-        <v/>
-      </c>
+      <c r="D43" s="118" t="n">
+        <v>139083</v>
+      </c>
+      <c r="E43" s="118" t="n">
+        <v>143557</v>
+      </c>
+      <c r="F43" s="122" t="n">
+        <v>0.968835</v>
+      </c>
+      <c r="G43" s="118" t="n">
+        <v>1479.7</v>
+      </c>
+      <c r="H43" s="120" t="n">
+        <v>205801115</v>
+      </c>
+      <c r="I43" s="120" t="n">
+        <v>28672</v>
+      </c>
+      <c r="J43" s="120" t="n">
+        <v>12110</v>
+      </c>
+      <c r="K43" s="120" t="n">
+        <v>7751</v>
+      </c>
+      <c r="L43" s="121" t="n">
+        <v>205849648</v>
+      </c>
+      <c r="M43" s="115" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="234" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C44" s="235" t="inlineStr">
+      <c r="A44" s="116" t="inlineStr">
+        <is>
+          <t>CPO679</t>
+        </is>
+      </c>
+      <c r="B44" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.16</t>
+        </is>
+      </c>
+      <c r="C44" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D44" s="118" t="n">
+        <v>4474</v>
+      </c>
+      <c r="E44" s="118" t="n">
+        <v>143557</v>
+      </c>
+      <c r="F44" s="122" t="n">
+        <v>0.031165</v>
+      </c>
+      <c r="G44" s="118" t="n">
+        <v>1479.7</v>
+      </c>
+      <c r="H44" s="120" t="n">
+        <v>6620178</v>
+      </c>
+      <c r="I44" s="120" t="n">
+        <v>922</v>
+      </c>
+      <c r="J44" s="120" t="n">
+        <v>390</v>
+      </c>
+      <c r="K44" s="120" t="n">
+        <v>249</v>
+      </c>
+      <c r="L44" s="121" t="n">
+        <v>6621739</v>
+      </c>
+      <c r="M44" s="115" t="n"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="116" t="inlineStr">
+        <is>
+          <t>MPO65</t>
+        </is>
+      </c>
+      <c r="B45" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.16</t>
+        </is>
+      </c>
+      <c r="C45" s="117" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D45" s="118" t="n">
+        <v>4936</v>
+      </c>
+      <c r="E45" s="118" t="n">
+        <v>15040</v>
+      </c>
+      <c r="F45" s="122" t="n">
+        <v>0.328191</v>
+      </c>
+      <c r="G45" s="118" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H45" s="120" t="n">
+        <v>7305280</v>
+      </c>
+      <c r="I45" s="120" t="n">
+        <v>9714</v>
+      </c>
+      <c r="J45" s="120" t="n">
+        <v>3282</v>
+      </c>
+      <c r="K45" s="120" t="n">
+        <v>2626</v>
+      </c>
+      <c r="L45" s="121" t="n">
+        <v>7320902</v>
+      </c>
+      <c r="M45" s="115" t="n"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="116" t="inlineStr">
+        <is>
+          <t>GPO451</t>
+        </is>
+      </c>
+      <c r="B46" s="116" t="inlineStr">
+        <is>
+          <t>2025.12.29</t>
+        </is>
+      </c>
+      <c r="C46" s="117" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D44" s="234" t="inlineStr">
-        <is>
-          <t>GPO475, SR-1000수리</t>
-        </is>
-      </c>
-      <c r="E44" s="236" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F44" s="237" t="n">
-        <v>1516.8</v>
-      </c>
-      <c r="G44" s="236" t="n">
-        <v>20</v>
-      </c>
-      <c r="H44" s="238" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I44" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J44" s="238" t="n">
-        <v>3140108</v>
-      </c>
-      <c r="K44" s="238">
-        <f>ROUND((E44+G44)*F44+H44+I44,0)</f>
-        <v/>
-      </c>
-      <c r="L44" s="239">
-        <f>J44-K44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="169" t="inlineStr">
-        <is>
-          <t>② PO별 비용 안분 내역</t>
-        </is>
-      </c>
-      <c r="B45" s="148" t="n"/>
-      <c r="C45" s="148" t="n"/>
-      <c r="D45" s="148" t="n"/>
-      <c r="E45" s="148" t="n"/>
-      <c r="F45" s="148" t="n"/>
-      <c r="G45" s="148" t="n"/>
-      <c r="H45" s="148" t="n"/>
-      <c r="I45" s="148" t="n"/>
-      <c r="J45" s="148" t="n"/>
-      <c r="K45" s="148" t="n"/>
-      <c r="L45" s="149" t="n"/>
-      <c r="M45" s="115" t="n"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="150" t="inlineStr">
-        <is>
-          <t>PO No.</t>
-        </is>
-      </c>
-      <c r="B46" s="150" t="inlineStr">
-        <is>
-          <t>송금일</t>
-        </is>
-      </c>
-      <c r="C46" s="150" t="inlineStr">
-        <is>
-          <t>업체</t>
-        </is>
-      </c>
-      <c r="D46" s="150" t="inlineStr">
-        <is>
-          <t>PO USD</t>
-        </is>
-      </c>
-      <c r="E46" s="150" t="inlineStr">
-        <is>
-          <t>그룹총USD</t>
-        </is>
-      </c>
-      <c r="F46" s="150" t="inlineStr">
-        <is>
-          <t>배부비율</t>
-        </is>
-      </c>
-      <c r="G46" s="150" t="inlineStr">
-        <is>
-          <t>적용환율</t>
-        </is>
-      </c>
-      <c r="H46" s="150" t="inlineStr">
-        <is>
-          <t>원화환산액</t>
-        </is>
-      </c>
-      <c r="I46" s="150" t="inlineStr">
-        <is>
-          <t>중개수수료안분</t>
-        </is>
-      </c>
-      <c r="J46" s="150" t="inlineStr">
-        <is>
-          <t>수수료안분</t>
-        </is>
-      </c>
-      <c r="K46" s="150" t="inlineStr">
-        <is>
-          <t>전신료안분</t>
-        </is>
-      </c>
-      <c r="L46" s="150" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
+      <c r="D46" s="118" t="n">
+        <v>9060</v>
+      </c>
+      <c r="E46" s="118" t="n">
+        <v>13860</v>
+      </c>
+      <c r="F46" s="122" t="n">
+        <v>0.65368</v>
+      </c>
+      <c r="G46" s="118" t="n">
+        <v>1439.1</v>
+      </c>
+      <c r="H46" s="120" t="n">
+        <v>13038246</v>
+      </c>
+      <c r="I46" s="120" t="n">
+        <v>18814</v>
+      </c>
+      <c r="J46" s="120" t="n">
+        <v>6537</v>
+      </c>
+      <c r="K46" s="120" t="n">
+        <v>5229</v>
+      </c>
+      <c r="L46" s="121" t="n">
+        <v>13068826</v>
       </c>
       <c r="M46" s="115" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="116" t="inlineStr">
         <is>
-          <t>CPO678-1</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="B47" s="116" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2025.12.29</t>
         </is>
       </c>
       <c r="C47" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D47" s="118" t="n">
-        <v>139083</v>
+        <v>350</v>
       </c>
       <c r="E47" s="118" t="n">
-        <v>143557</v>
+        <v>13860</v>
       </c>
       <c r="F47" s="122" t="n">
-        <v>0.968835</v>
+        <v>0.025253</v>
       </c>
       <c r="G47" s="118" t="n">
-        <v>1479.7</v>
+        <v>1439.1</v>
       </c>
       <c r="H47" s="120" t="n">
-        <v>205801115</v>
+        <v>503685</v>
       </c>
       <c r="I47" s="120" t="n">
-        <v>28672</v>
+        <v>727</v>
       </c>
       <c r="J47" s="120" t="n">
-        <v>12110</v>
+        <v>253</v>
       </c>
       <c r="K47" s="120" t="n">
-        <v>7751</v>
+        <v>202</v>
       </c>
       <c r="L47" s="121" t="n">
-        <v>205849648</v>
+        <v>504867</v>
       </c>
       <c r="M47" s="115" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="116" t="inlineStr">
         <is>
-          <t>CPO679</t>
+          <t>CPO680</t>
         </is>
       </c>
       <c r="B48" s="116" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2026.01.13</t>
         </is>
       </c>
       <c r="C48" s="117" t="inlineStr">
@@ -15794,88 +15692,88 @@
         </is>
       </c>
       <c r="D48" s="118" t="n">
-        <v>4474</v>
+        <v>252</v>
       </c>
       <c r="E48" s="118" t="n">
-        <v>143557</v>
+        <v>252</v>
       </c>
       <c r="F48" s="122" t="n">
-        <v>0.031165</v>
+        <v>1</v>
       </c>
       <c r="G48" s="118" t="n">
-        <v>1479.7</v>
+        <v>1479</v>
       </c>
       <c r="H48" s="120" t="n">
-        <v>6620178</v>
+        <v>372708</v>
       </c>
       <c r="I48" s="120" t="n">
-        <v>922</v>
+        <v>29580</v>
       </c>
       <c r="J48" s="120" t="n">
-        <v>390</v>
+        <v>2500</v>
       </c>
       <c r="K48" s="120" t="n">
-        <v>249</v>
+        <v>8000</v>
       </c>
       <c r="L48" s="121" t="n">
-        <v>6621739</v>
+        <v>412788</v>
       </c>
       <c r="M48" s="115" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="116" t="inlineStr">
         <is>
-          <t>MPO65</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="B49" s="116" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C49" s="117" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D49" s="118" t="n">
-        <v>4936</v>
+        <v>450</v>
       </c>
       <c r="E49" s="118" t="n">
-        <v>15040</v>
+        <v>3700</v>
       </c>
       <c r="F49" s="122" t="n">
-        <v>0.328191</v>
+        <v>0.121622</v>
       </c>
       <c r="G49" s="118" t="n">
-        <v>1480</v>
+        <v>1475.7</v>
       </c>
       <c r="H49" s="120" t="n">
-        <v>7305280</v>
+        <v>664065</v>
       </c>
       <c r="I49" s="120" t="n">
-        <v>9714</v>
+        <v>3590</v>
       </c>
       <c r="J49" s="120" t="n">
-        <v>3282</v>
+        <v>912</v>
       </c>
       <c r="K49" s="120" t="n">
-        <v>2626</v>
+        <v>973</v>
       </c>
       <c r="L49" s="121" t="n">
-        <v>7320902</v>
+        <v>669540</v>
       </c>
       <c r="M49" s="115" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="116" t="inlineStr">
         <is>
-          <t>GPO451</t>
+          <t>GPO460</t>
         </is>
       </c>
       <c r="B50" s="116" t="inlineStr">
         <is>
-          <t>2025.12.29</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C50" s="117" t="inlineStr">
@@ -15884,43 +15782,43 @@
         </is>
       </c>
       <c r="D50" s="118" t="n">
-        <v>9060</v>
+        <v>2710</v>
       </c>
       <c r="E50" s="118" t="n">
-        <v>13860</v>
+        <v>3700</v>
       </c>
       <c r="F50" s="122" t="n">
-        <v>0.65368</v>
+        <v>0.732432</v>
       </c>
       <c r="G50" s="118" t="n">
-        <v>1439.1</v>
+        <v>1475.7</v>
       </c>
       <c r="H50" s="120" t="n">
-        <v>13038246</v>
+        <v>3999147</v>
       </c>
       <c r="I50" s="120" t="n">
-        <v>18814</v>
+        <v>21617</v>
       </c>
       <c r="J50" s="120" t="n">
-        <v>6537</v>
+        <v>5493</v>
       </c>
       <c r="K50" s="120" t="n">
-        <v>5229</v>
+        <v>5859</v>
       </c>
       <c r="L50" s="121" t="n">
-        <v>13068826</v>
+        <v>4032116</v>
       </c>
       <c r="M50" s="115" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="116" t="inlineStr">
         <is>
-          <t>GPO458</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="B51" s="116" t="inlineStr">
         <is>
-          <t>2025.12.29</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C51" s="117" t="inlineStr">
@@ -15929,308 +15827,308 @@
         </is>
       </c>
       <c r="D51" s="118" t="n">
-        <v>350</v>
+        <v>540</v>
       </c>
       <c r="E51" s="118" t="n">
-        <v>13860</v>
+        <v>3700</v>
       </c>
       <c r="F51" s="122" t="n">
-        <v>0.025253</v>
+        <v>0.145946</v>
       </c>
       <c r="G51" s="118" t="n">
-        <v>1439.1</v>
+        <v>1475.7</v>
       </c>
       <c r="H51" s="120" t="n">
-        <v>503685</v>
+        <v>796878</v>
       </c>
       <c r="I51" s="120" t="n">
-        <v>727</v>
+        <v>4307</v>
       </c>
       <c r="J51" s="120" t="n">
-        <v>253</v>
+        <v>1095</v>
       </c>
       <c r="K51" s="120" t="n">
-        <v>202</v>
+        <v>1168</v>
       </c>
       <c r="L51" s="121" t="n">
-        <v>504867</v>
+        <v>803448</v>
       </c>
       <c r="M51" s="115" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="116" t="inlineStr">
         <is>
-          <t>CPO680</t>
+          <t>MPO66</t>
         </is>
       </c>
       <c r="B52" s="116" t="inlineStr">
         <is>
-          <t>2026.01.13</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C52" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D52" s="118" t="n">
-        <v>252</v>
+        <v>9626.35</v>
       </c>
       <c r="E52" s="118" t="n">
-        <v>252</v>
+        <v>9626.35</v>
       </c>
       <c r="F52" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="118" t="n">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="H52" s="120" t="n">
-        <v>372708</v>
+        <v>14208493</v>
       </c>
       <c r="I52" s="120" t="n">
-        <v>29580</v>
+        <v>29520</v>
       </c>
       <c r="J52" s="120" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="K52" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="L52" s="121" t="n">
-        <v>412788</v>
+        <v>14256013</v>
       </c>
       <c r="M52" s="115" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="116" t="inlineStr">
         <is>
-          <t>GPO459</t>
+          <t>LPO001</t>
         </is>
       </c>
       <c r="B53" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="C53" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D53" s="118" t="n">
-        <v>450</v>
+        <v>5056.8</v>
       </c>
       <c r="E53" s="118" t="n">
-        <v>3700</v>
+        <v>5056.8</v>
       </c>
       <c r="F53" s="122" t="n">
-        <v>0.121622</v>
+        <v>1</v>
       </c>
       <c r="G53" s="118" t="n">
-        <v>1475.7</v>
+        <v>1445.5</v>
       </c>
       <c r="H53" s="120" t="n">
-        <v>664065</v>
+        <v>7309604</v>
       </c>
       <c r="I53" s="120" t="n">
-        <v>3590</v>
+        <v>28910</v>
       </c>
       <c r="J53" s="120" t="n">
-        <v>912</v>
+        <v>10000</v>
       </c>
       <c r="K53" s="120" t="n">
-        <v>973</v>
+        <v>8000</v>
       </c>
       <c r="L53" s="121" t="n">
-        <v>669540</v>
+        <v>7356514</v>
       </c>
       <c r="M53" s="115" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="116" t="inlineStr">
         <is>
-          <t>GPO460</t>
+          <t>CPO682</t>
         </is>
       </c>
       <c r="B54" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C54" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D54" s="118" t="n">
-        <v>2710</v>
+        <v>20174</v>
       </c>
       <c r="E54" s="118" t="n">
-        <v>3700</v>
+        <v>24794</v>
       </c>
       <c r="F54" s="122" t="n">
-        <v>0.732432</v>
+        <v>0.813665</v>
       </c>
       <c r="G54" s="118" t="n">
-        <v>1475.7</v>
+        <v>1454.7</v>
       </c>
       <c r="H54" s="120" t="n">
-        <v>3999147</v>
+        <v>29347118</v>
       </c>
       <c r="I54" s="120" t="n">
-        <v>21617</v>
+        <v>23673</v>
       </c>
       <c r="J54" s="120" t="n">
-        <v>5493</v>
+        <v>10171</v>
       </c>
       <c r="K54" s="120" t="n">
-        <v>5859</v>
+        <v>6509</v>
       </c>
       <c r="L54" s="121" t="n">
-        <v>4032116</v>
+        <v>29387471</v>
       </c>
       <c r="M54" s="115" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="116" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>CPO683</t>
         </is>
       </c>
       <c r="B55" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C55" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D55" s="118" t="n">
-        <v>540</v>
+        <v>4620</v>
       </c>
       <c r="E55" s="118" t="n">
-        <v>3700</v>
+        <v>24794</v>
       </c>
       <c r="F55" s="122" t="n">
-        <v>0.145946</v>
+        <v>0.186335</v>
       </c>
       <c r="G55" s="118" t="n">
-        <v>1475.7</v>
+        <v>1454.7</v>
       </c>
       <c r="H55" s="120" t="n">
-        <v>796878</v>
+        <v>6720714</v>
       </c>
       <c r="I55" s="120" t="n">
-        <v>4307</v>
+        <v>5421</v>
       </c>
       <c r="J55" s="120" t="n">
-        <v>1095</v>
+        <v>2329</v>
       </c>
       <c r="K55" s="120" t="n">
-        <v>1168</v>
+        <v>1491</v>
       </c>
       <c r="L55" s="121" t="n">
-        <v>803448</v>
+        <v>6729955</v>
       </c>
       <c r="M55" s="115" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="116" t="inlineStr">
         <is>
-          <t>MPO66</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="B56" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C56" s="117" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D56" s="118" t="n">
-        <v>9626.35</v>
+        <v>1440</v>
       </c>
       <c r="E56" s="118" t="n">
-        <v>9626.35</v>
+        <v>11599.57</v>
       </c>
       <c r="F56" s="122" t="n">
-        <v>1</v>
+        <v>0.124143</v>
       </c>
       <c r="G56" s="118" t="n">
-        <v>1476</v>
+        <v>1453.6</v>
       </c>
       <c r="H56" s="120" t="n">
-        <v>14208493</v>
+        <v>2093184</v>
       </c>
       <c r="I56" s="120" t="n">
-        <v>29520</v>
+        <v>3609</v>
       </c>
       <c r="J56" s="120" t="n">
-        <v>10000</v>
+        <v>1241</v>
       </c>
       <c r="K56" s="120" t="n">
-        <v>8000</v>
+        <v>993</v>
       </c>
       <c r="L56" s="121" t="n">
-        <v>14256013</v>
+        <v>2099027</v>
       </c>
       <c r="M56" s="115" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="116" t="inlineStr">
         <is>
-          <t>LPO001</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="B57" s="116" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C57" s="117" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D57" s="118" t="n">
-        <v>5056.8</v>
+        <v>4489</v>
       </c>
       <c r="E57" s="118" t="n">
-        <v>5056.8</v>
+        <v>11599.57</v>
       </c>
       <c r="F57" s="122" t="n">
-        <v>1</v>
+        <v>0.386997</v>
       </c>
       <c r="G57" s="118" t="n">
-        <v>1445.5</v>
+        <v>1453.6</v>
       </c>
       <c r="H57" s="120" t="n">
-        <v>7309604</v>
+        <v>6525210</v>
       </c>
       <c r="I57" s="120" t="n">
-        <v>28910</v>
+        <v>11251</v>
       </c>
       <c r="J57" s="120" t="n">
-        <v>10000</v>
+        <v>3870</v>
       </c>
       <c r="K57" s="120" t="n">
-        <v>8000</v>
+        <v>3096</v>
       </c>
       <c r="L57" s="121" t="n">
-        <v>7356514</v>
+        <v>6543427</v>
       </c>
       <c r="M57" s="115" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="116" t="inlineStr">
         <is>
-          <t>CPO682</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="B58" s="116" t="inlineStr">
@@ -16240,47 +16138,47 @@
       </c>
       <c r="C58" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D58" s="118" t="n">
-        <v>20174</v>
+        <v>5670.57</v>
       </c>
       <c r="E58" s="118" t="n">
-        <v>24794</v>
+        <v>11599.57</v>
       </c>
       <c r="F58" s="122" t="n">
-        <v>0.813665</v>
+        <v>0.48886</v>
       </c>
       <c r="G58" s="118" t="n">
-        <v>1454.7</v>
+        <v>1453.6</v>
       </c>
       <c r="H58" s="120" t="n">
-        <v>29347118</v>
+        <v>8242741</v>
       </c>
       <c r="I58" s="120" t="n">
-        <v>23673</v>
+        <v>14212</v>
       </c>
       <c r="J58" s="120" t="n">
-        <v>10171</v>
+        <v>4889</v>
       </c>
       <c r="K58" s="120" t="n">
-        <v>6509</v>
+        <v>3911</v>
       </c>
       <c r="L58" s="121" t="n">
-        <v>29387471</v>
+        <v>8265753</v>
       </c>
       <c r="M58" s="115" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="116" t="inlineStr">
         <is>
-          <t>CPO683</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="B59" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.11</t>
         </is>
       </c>
       <c r="C59" s="117" t="inlineStr">
@@ -16289,178 +16187,178 @@
         </is>
       </c>
       <c r="D59" s="118" t="n">
-        <v>4620</v>
+        <v>26358</v>
       </c>
       <c r="E59" s="118" t="n">
-        <v>24794</v>
+        <v>26358</v>
       </c>
       <c r="F59" s="122" t="n">
-        <v>0.186335</v>
+        <v>1</v>
       </c>
       <c r="G59" s="118" t="n">
-        <v>1454.7</v>
+        <v>1460.7</v>
       </c>
       <c r="H59" s="120" t="n">
-        <v>6720714</v>
+        <v>38501131</v>
       </c>
       <c r="I59" s="120" t="n">
-        <v>5421</v>
+        <v>29214</v>
       </c>
       <c r="J59" s="120" t="n">
-        <v>2329</v>
+        <v>12500</v>
       </c>
       <c r="K59" s="120" t="n">
-        <v>1491</v>
+        <v>8000</v>
       </c>
       <c r="L59" s="121" t="n">
-        <v>6729955</v>
+        <v>38550845</v>
       </c>
       <c r="M59" s="115" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="116" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="B60" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C60" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D60" s="118" t="n">
-        <v>1440</v>
+        <v>14793</v>
       </c>
       <c r="E60" s="118" t="n">
-        <v>11599.57</v>
+        <v>17538</v>
       </c>
       <c r="F60" s="122" t="n">
-        <v>0.124143</v>
+        <v>0.843483</v>
       </c>
       <c r="G60" s="118" t="n">
-        <v>1453.6</v>
+        <v>1451.7</v>
       </c>
       <c r="H60" s="120" t="n">
-        <v>2093184</v>
+        <v>21474998</v>
       </c>
       <c r="I60" s="120" t="n">
-        <v>3609</v>
+        <v>24490</v>
       </c>
       <c r="J60" s="120" t="n">
-        <v>1241</v>
+        <v>8435</v>
       </c>
       <c r="K60" s="120" t="n">
-        <v>993</v>
+        <v>6748</v>
       </c>
       <c r="L60" s="121" t="n">
-        <v>2099027</v>
+        <v>21514671</v>
       </c>
       <c r="M60" s="115" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="116" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>CPO689</t>
         </is>
       </c>
       <c r="B61" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C61" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D61" s="118" t="n">
-        <v>4489</v>
+        <v>2745</v>
       </c>
       <c r="E61" s="118" t="n">
-        <v>11599.57</v>
+        <v>17538</v>
       </c>
       <c r="F61" s="122" t="n">
-        <v>0.386997</v>
+        <v>0.156517</v>
       </c>
       <c r="G61" s="118" t="n">
-        <v>1453.6</v>
+        <v>1451.7</v>
       </c>
       <c r="H61" s="120" t="n">
-        <v>6525210</v>
+        <v>3984917</v>
       </c>
       <c r="I61" s="120" t="n">
-        <v>11251</v>
+        <v>4544</v>
       </c>
       <c r="J61" s="120" t="n">
-        <v>3870</v>
+        <v>1565</v>
       </c>
       <c r="K61" s="120" t="n">
-        <v>3096</v>
+        <v>1252</v>
       </c>
       <c r="L61" s="121" t="n">
-        <v>6543427</v>
+        <v>3992278</v>
       </c>
       <c r="M61" s="115" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="116" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="B62" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C62" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D62" s="118" t="n">
-        <v>5670.57</v>
+        <v>5673</v>
       </c>
       <c r="E62" s="118" t="n">
-        <v>11599.57</v>
+        <v>142189</v>
       </c>
       <c r="F62" s="122" t="n">
-        <v>0.48886</v>
+        <v>0.039898</v>
       </c>
       <c r="G62" s="118" t="n">
-        <v>1453.6</v>
+        <v>1441.6</v>
       </c>
       <c r="H62" s="120" t="n">
-        <v>8242741</v>
+        <v>8178197</v>
       </c>
       <c r="I62" s="120" t="n">
-        <v>14212</v>
+        <v>1150</v>
       </c>
       <c r="J62" s="120" t="n">
-        <v>4889</v>
+        <v>499</v>
       </c>
       <c r="K62" s="120" t="n">
-        <v>3911</v>
+        <v>319</v>
       </c>
       <c r="L62" s="121" t="n">
-        <v>8265753</v>
+        <v>8180165</v>
       </c>
       <c r="M62" s="115" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="116" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="B63" s="116" t="inlineStr">
         <is>
-          <t>2026.02.11</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C63" s="117" t="inlineStr">
@@ -16469,43 +16367,43 @@
         </is>
       </c>
       <c r="D63" s="118" t="n">
-        <v>26358</v>
+        <v>136516</v>
       </c>
       <c r="E63" s="118" t="n">
-        <v>26358</v>
+        <v>142189</v>
       </c>
       <c r="F63" s="122" t="n">
-        <v>1</v>
+        <v>0.960102</v>
       </c>
       <c r="G63" s="118" t="n">
-        <v>1460.7</v>
+        <v>1441.6</v>
       </c>
       <c r="H63" s="120" t="n">
-        <v>38501131</v>
+        <v>196801466</v>
       </c>
       <c r="I63" s="120" t="n">
-        <v>29214</v>
+        <v>27682</v>
       </c>
       <c r="J63" s="120" t="n">
-        <v>12500</v>
+        <v>12001</v>
       </c>
       <c r="K63" s="120" t="n">
-        <v>8000</v>
+        <v>7681</v>
       </c>
       <c r="L63" s="121" t="n">
-        <v>38550845</v>
+        <v>196848830</v>
       </c>
       <c r="M63" s="115" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="116" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>CPO678-2</t>
         </is>
       </c>
       <c r="B64" s="116" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.03.06</t>
         </is>
       </c>
       <c r="C64" s="117" t="inlineStr">
@@ -16514,43 +16412,43 @@
         </is>
       </c>
       <c r="D64" s="118" t="n">
-        <v>14793</v>
+        <v>137850</v>
       </c>
       <c r="E64" s="118" t="n">
-        <v>17538</v>
+        <v>137850</v>
       </c>
       <c r="F64" s="122" t="n">
-        <v>0.843483</v>
+        <v>1</v>
       </c>
       <c r="G64" s="118" t="n">
-        <v>1451.7</v>
+        <v>1477.6</v>
       </c>
       <c r="H64" s="120" t="n">
-        <v>21474998</v>
+        <v>203687160</v>
       </c>
       <c r="I64" s="120" t="n">
-        <v>24490</v>
+        <v>29552</v>
       </c>
       <c r="J64" s="120" t="n">
-        <v>8435</v>
+        <v>12500</v>
       </c>
       <c r="K64" s="120" t="n">
-        <v>6748</v>
+        <v>8000</v>
       </c>
       <c r="L64" s="121" t="n">
-        <v>21514671</v>
+        <v>203737212</v>
       </c>
       <c r="M64" s="115" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="116" t="inlineStr">
         <is>
-          <t>CPO689</t>
+          <t>CPO690</t>
         </is>
       </c>
       <c r="B65" s="116" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C65" s="117" t="inlineStr">
@@ -16559,43 +16457,43 @@
         </is>
       </c>
       <c r="D65" s="118" t="n">
-        <v>2745</v>
+        <v>9740</v>
       </c>
       <c r="E65" s="118" t="n">
-        <v>17538</v>
+        <v>34354</v>
       </c>
       <c r="F65" s="122" t="n">
-        <v>0.156517</v>
+        <v>0.283519</v>
       </c>
       <c r="G65" s="118" t="n">
-        <v>1451.7</v>
+        <v>1505.7</v>
       </c>
       <c r="H65" s="120" t="n">
-        <v>3984917</v>
+        <v>14665518</v>
       </c>
       <c r="I65" s="120" t="n">
-        <v>4544</v>
+        <v>8538</v>
       </c>
       <c r="J65" s="120" t="n">
-        <v>1565</v>
+        <v>3544</v>
       </c>
       <c r="K65" s="120" t="n">
-        <v>1252</v>
+        <v>2268</v>
       </c>
       <c r="L65" s="121" t="n">
-        <v>3992278</v>
+        <v>14679868</v>
       </c>
       <c r="M65" s="115" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="116" t="inlineStr">
         <is>
-          <t>CPO667</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="B66" s="116" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C66" s="117" t="inlineStr">
@@ -16604,128 +16502,128 @@
         </is>
       </c>
       <c r="D66" s="118" t="n">
-        <v>5673</v>
+        <v>24614</v>
       </c>
       <c r="E66" s="118" t="n">
-        <v>142189</v>
+        <v>34354</v>
       </c>
       <c r="F66" s="122" t="n">
-        <v>0.039898</v>
+        <v>0.716481</v>
       </c>
       <c r="G66" s="118" t="n">
-        <v>1441.6</v>
+        <v>1505.7</v>
       </c>
       <c r="H66" s="120" t="n">
-        <v>8178197</v>
+        <v>37061300</v>
       </c>
       <c r="I66" s="120" t="n">
-        <v>1150</v>
+        <v>21576</v>
       </c>
       <c r="J66" s="120" t="n">
-        <v>499</v>
+        <v>8956</v>
       </c>
       <c r="K66" s="120" t="n">
-        <v>319</v>
+        <v>5732</v>
       </c>
       <c r="L66" s="121" t="n">
-        <v>8180165</v>
+        <v>37097564</v>
       </c>
       <c r="M66" s="115" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="116" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>GPO467</t>
         </is>
       </c>
       <c r="B67" s="116" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C67" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D67" s="118" t="n">
-        <v>136516</v>
+        <v>1700</v>
       </c>
       <c r="E67" s="118" t="n">
-        <v>142189</v>
+        <v>6553.05</v>
       </c>
       <c r="F67" s="122" t="n">
-        <v>0.960102</v>
+        <v>0.259421</v>
       </c>
       <c r="G67" s="118" t="n">
-        <v>1441.6</v>
+        <v>1506.4</v>
       </c>
       <c r="H67" s="120" t="n">
-        <v>196801466</v>
+        <v>2560880</v>
       </c>
       <c r="I67" s="120" t="n">
-        <v>27682</v>
+        <v>7816</v>
       </c>
       <c r="J67" s="120" t="n">
-        <v>12001</v>
+        <v>2594</v>
       </c>
       <c r="K67" s="120" t="n">
-        <v>7681</v>
+        <v>2075</v>
       </c>
       <c r="L67" s="121" t="n">
-        <v>196848830</v>
+        <v>2573365</v>
       </c>
       <c r="M67" s="115" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="116" t="inlineStr">
         <is>
-          <t>CPO678-2</t>
+          <t>GPO469</t>
         </is>
       </c>
       <c r="B68" s="116" t="inlineStr">
         <is>
-          <t>2026.03.06</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C68" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D68" s="118" t="n">
-        <v>137850</v>
+        <v>3993.05</v>
       </c>
       <c r="E68" s="118" t="n">
-        <v>137850</v>
+        <v>6553.05</v>
       </c>
       <c r="F68" s="122" t="n">
-        <v>1</v>
+        <v>0.6093420000000001</v>
       </c>
       <c r="G68" s="118" t="n">
-        <v>1477.6</v>
+        <v>1506.4</v>
       </c>
       <c r="H68" s="120" t="n">
-        <v>203687160</v>
+        <v>6015131</v>
       </c>
       <c r="I68" s="120" t="n">
-        <v>29552</v>
+        <v>18358</v>
       </c>
       <c r="J68" s="120" t="n">
-        <v>12500</v>
+        <v>6093</v>
       </c>
       <c r="K68" s="120" t="n">
-        <v>8000</v>
+        <v>4875</v>
       </c>
       <c r="L68" s="121" t="n">
-        <v>203737212</v>
+        <v>6044457</v>
       </c>
       <c r="M68" s="115" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="116" t="inlineStr">
         <is>
-          <t>CPO690</t>
+          <t>GPO470</t>
         </is>
       </c>
       <c r="B69" s="116" t="inlineStr">
@@ -16735,42 +16633,42 @@
       </c>
       <c r="C69" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D69" s="118" t="n">
-        <v>9740</v>
+        <v>360</v>
       </c>
       <c r="E69" s="118" t="n">
-        <v>34354</v>
+        <v>6553.05</v>
       </c>
       <c r="F69" s="122" t="n">
-        <v>0.283519</v>
+        <v>0.054936</v>
       </c>
       <c r="G69" s="118" t="n">
-        <v>1505.7</v>
+        <v>1506.4</v>
       </c>
       <c r="H69" s="120" t="n">
-        <v>14665518</v>
+        <v>542304</v>
       </c>
       <c r="I69" s="120" t="n">
-        <v>8538</v>
+        <v>1655</v>
       </c>
       <c r="J69" s="120" t="n">
-        <v>3544</v>
+        <v>549</v>
       </c>
       <c r="K69" s="120" t="n">
-        <v>2268</v>
+        <v>439</v>
       </c>
       <c r="L69" s="121" t="n">
-        <v>14679868</v>
+        <v>544947</v>
       </c>
       <c r="M69" s="115" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="116" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>GPO471</t>
         </is>
       </c>
       <c r="B70" s="116" t="inlineStr">
@@ -16780,47 +16678,47 @@
       </c>
       <c r="C70" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D70" s="118" t="n">
-        <v>24614</v>
+        <v>500</v>
       </c>
       <c r="E70" s="118" t="n">
-        <v>34354</v>
+        <v>6553.05</v>
       </c>
       <c r="F70" s="122" t="n">
-        <v>0.716481</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G70" s="118" t="n">
-        <v>1505.7</v>
+        <v>1506.4</v>
       </c>
       <c r="H70" s="120" t="n">
-        <v>37061300</v>
+        <v>753200</v>
       </c>
       <c r="I70" s="120" t="n">
-        <v>21576</v>
+        <v>2299</v>
       </c>
       <c r="J70" s="120" t="n">
-        <v>8956</v>
+        <v>763</v>
       </c>
       <c r="K70" s="120" t="n">
-        <v>5732</v>
+        <v>610</v>
       </c>
       <c r="L70" s="121" t="n">
-        <v>37097564</v>
+        <v>756872</v>
       </c>
       <c r="M70" s="115" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="116" t="inlineStr">
         <is>
-          <t>GPO467</t>
+          <t>GPO468-1</t>
         </is>
       </c>
       <c r="B71" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C71" s="117" t="inlineStr">
@@ -16829,43 +16727,43 @@
         </is>
       </c>
       <c r="D71" s="118" t="n">
-        <v>1700</v>
+        <v>36190</v>
       </c>
       <c r="E71" s="118" t="n">
-        <v>6553.05</v>
+        <v>57650</v>
       </c>
       <c r="F71" s="122" t="n">
-        <v>0.259421</v>
+        <v>0.627754</v>
       </c>
       <c r="G71" s="118" t="n">
-        <v>1506.4</v>
+        <v>1481.9</v>
       </c>
       <c r="H71" s="120" t="n">
-        <v>2560880</v>
+        <v>53629961</v>
       </c>
       <c r="I71" s="120" t="n">
-        <v>7816</v>
+        <v>18605</v>
       </c>
       <c r="J71" s="120" t="n">
-        <v>2594</v>
+        <v>7847</v>
       </c>
       <c r="K71" s="120" t="n">
-        <v>2075</v>
+        <v>5022</v>
       </c>
       <c r="L71" s="121" t="n">
-        <v>2573365</v>
+        <v>53661435</v>
       </c>
       <c r="M71" s="115" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="116" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>GPO472</t>
         </is>
       </c>
       <c r="B72" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C72" s="117" t="inlineStr">
@@ -16874,43 +16772,43 @@
         </is>
       </c>
       <c r="D72" s="118" t="n">
-        <v>3993.05</v>
+        <v>180</v>
       </c>
       <c r="E72" s="118" t="n">
-        <v>6553.05</v>
+        <v>57650</v>
       </c>
       <c r="F72" s="122" t="n">
-        <v>0.6093420000000001</v>
+        <v>0.003122</v>
       </c>
       <c r="G72" s="118" t="n">
-        <v>1506.4</v>
+        <v>1481.9</v>
       </c>
       <c r="H72" s="120" t="n">
-        <v>6015131</v>
+        <v>266742</v>
       </c>
       <c r="I72" s="120" t="n">
-        <v>18358</v>
+        <v>93</v>
       </c>
       <c r="J72" s="120" t="n">
-        <v>6093</v>
+        <v>39</v>
       </c>
       <c r="K72" s="120" t="n">
-        <v>4875</v>
+        <v>25</v>
       </c>
       <c r="L72" s="121" t="n">
-        <v>6044457</v>
+        <v>266899</v>
       </c>
       <c r="M72" s="115" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="116" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>GPO468-2</t>
         </is>
       </c>
       <c r="B73" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C73" s="117" t="inlineStr">
@@ -16919,223 +16817,221 @@
         </is>
       </c>
       <c r="D73" s="118" t="n">
-        <v>360</v>
+        <v>21280</v>
       </c>
       <c r="E73" s="118" t="n">
-        <v>6553.05</v>
+        <v>57650</v>
       </c>
       <c r="F73" s="122" t="n">
-        <v>0.054936</v>
+        <v>0.369124</v>
       </c>
       <c r="G73" s="118" t="n">
-        <v>1506.4</v>
+        <v>1481.9</v>
       </c>
       <c r="H73" s="120" t="n">
-        <v>542304</v>
+        <v>31534832</v>
       </c>
       <c r="I73" s="120" t="n">
-        <v>1655</v>
+        <v>10940</v>
       </c>
       <c r="J73" s="120" t="n">
-        <v>549</v>
+        <v>4614</v>
       </c>
       <c r="K73" s="120" t="n">
-        <v>439</v>
+        <v>2953</v>
       </c>
       <c r="L73" s="121" t="n">
-        <v>544947</v>
+        <v>31553339</v>
       </c>
       <c r="M73" s="115" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="116" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>CPO692-1</t>
         </is>
       </c>
       <c r="B74" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C74" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D74" s="118" t="n">
-        <v>500</v>
+        <v>11000</v>
       </c>
       <c r="E74" s="118" t="n">
-        <v>6553.05</v>
+        <v>297580</v>
       </c>
       <c r="F74" s="122" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.036965</v>
       </c>
       <c r="G74" s="118" t="n">
-        <v>1506.4</v>
+        <v>1482.8</v>
       </c>
       <c r="H74" s="120" t="n">
-        <v>753200</v>
+        <v>16310800</v>
       </c>
       <c r="I74" s="120" t="n">
-        <v>2299</v>
+        <v>1096</v>
       </c>
       <c r="J74" s="120" t="n">
-        <v>763</v>
+        <v>462</v>
       </c>
       <c r="K74" s="120" t="n">
-        <v>610</v>
+        <v>296</v>
       </c>
       <c r="L74" s="121" t="n">
-        <v>756872</v>
+        <v>16312654</v>
       </c>
       <c r="M74" s="115" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="116" t="inlineStr">
         <is>
-          <t>GPO468-1</t>
+          <t>CPO692-2</t>
         </is>
       </c>
       <c r="B75" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C75" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D75" s="118" t="n">
-        <v>36190</v>
+        <v>286580</v>
       </c>
       <c r="E75" s="118" t="n">
-        <v>57650</v>
+        <v>297580</v>
       </c>
       <c r="F75" s="122" t="n">
-        <v>0.627754</v>
+        <v>0.963035</v>
       </c>
       <c r="G75" s="118" t="n">
-        <v>1481.9</v>
+        <v>1482.8</v>
       </c>
       <c r="H75" s="120" t="n">
-        <v>53629961</v>
+        <v>424940824</v>
       </c>
       <c r="I75" s="120" t="n">
-        <v>18605</v>
+        <v>28560</v>
       </c>
       <c r="J75" s="120" t="n">
-        <v>7847</v>
+        <v>12038</v>
       </c>
       <c r="K75" s="120" t="n">
-        <v>5022</v>
+        <v>7704</v>
       </c>
       <c r="L75" s="121" t="n">
-        <v>53661435</v>
+        <v>424989126</v>
       </c>
       <c r="M75" s="115" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="116" t="inlineStr">
         <is>
-          <t>GPO472</t>
+          <t>EPO18</t>
         </is>
       </c>
       <c r="B76" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C76" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAICO Italia</t>
         </is>
       </c>
       <c r="D76" s="118" t="n">
-        <v>180</v>
+        <v>4388.4</v>
       </c>
       <c r="E76" s="118" t="n">
-        <v>57650</v>
+        <v>4388.4</v>
       </c>
       <c r="F76" s="122" t="n">
-        <v>0.003122</v>
+        <v>1</v>
       </c>
       <c r="G76" s="118" t="n">
-        <v>1481.9</v>
+        <v>1741.08</v>
       </c>
       <c r="H76" s="120" t="n">
-        <v>266742</v>
+        <v>7640555</v>
       </c>
       <c r="I76" s="120" t="n">
-        <v>93</v>
+        <v>43527</v>
       </c>
       <c r="J76" s="120" t="n">
-        <v>39</v>
+        <v>10000</v>
       </c>
       <c r="K76" s="120" t="n">
-        <v>25</v>
+        <v>8000</v>
       </c>
       <c r="L76" s="121" t="n">
-        <v>266899</v>
-      </c>
-      <c r="M76" s="115" t="n"/>
+        <v>7702082</v>
+      </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="116" t="inlineStr">
         <is>
-          <t>GPO468-2</t>
+          <t>CPO694</t>
         </is>
       </c>
       <c r="B77" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C77" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D77" s="118" t="n">
-        <v>21280</v>
+        <v>17404</v>
       </c>
       <c r="E77" s="118" t="n">
-        <v>57650</v>
+        <v>21439</v>
       </c>
       <c r="F77" s="122" t="n">
-        <v>0.369124</v>
+        <v>0.811792</v>
       </c>
       <c r="G77" s="118" t="n">
-        <v>1481.9</v>
+        <v>1474.9</v>
       </c>
       <c r="H77" s="120" t="n">
-        <v>31534832</v>
+        <v>25669160</v>
       </c>
       <c r="I77" s="120" t="n">
-        <v>10940</v>
+        <v>23946</v>
       </c>
       <c r="J77" s="120" t="n">
-        <v>4614</v>
+        <v>10147</v>
       </c>
       <c r="K77" s="120" t="n">
-        <v>2953</v>
+        <v>6494</v>
       </c>
       <c r="L77" s="121" t="n">
-        <v>31553339</v>
-      </c>
-      <c r="M77" s="115" t="n"/>
+        <v>25709747</v>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="116" t="inlineStr">
         <is>
-          <t>CPO692-1</t>
+          <t>CPO695-1</t>
         </is>
       </c>
       <c r="B78" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C78" s="117" t="inlineStr">
@@ -17144,43 +17040,42 @@
         </is>
       </c>
       <c r="D78" s="118" t="n">
-        <v>11000</v>
+        <v>2058</v>
       </c>
       <c r="E78" s="118" t="n">
-        <v>297580</v>
+        <v>21439</v>
       </c>
       <c r="F78" s="122" t="n">
-        <v>0.036965</v>
+        <v>0.09599299999999999</v>
       </c>
       <c r="G78" s="118" t="n">
-        <v>1482.8</v>
+        <v>1474.9</v>
       </c>
       <c r="H78" s="120" t="n">
-        <v>16310800</v>
+        <v>3035344</v>
       </c>
       <c r="I78" s="120" t="n">
-        <v>1096</v>
+        <v>2832</v>
       </c>
       <c r="J78" s="120" t="n">
-        <v>462</v>
+        <v>1200</v>
       </c>
       <c r="K78" s="120" t="n">
-        <v>296</v>
+        <v>768</v>
       </c>
       <c r="L78" s="121" t="n">
-        <v>16312654</v>
-      </c>
-      <c r="M78" s="115" t="n"/>
+        <v>3040144</v>
+      </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="116" t="inlineStr">
         <is>
-          <t>CPO692-2</t>
+          <t>CPO695-2</t>
         </is>
       </c>
       <c r="B79" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C79" s="117" t="inlineStr">
@@ -17189,67 +17084,66 @@
         </is>
       </c>
       <c r="D79" s="118" t="n">
-        <v>286580</v>
+        <v>1977</v>
       </c>
       <c r="E79" s="118" t="n">
-        <v>297580</v>
+        <v>21439</v>
       </c>
       <c r="F79" s="122" t="n">
-        <v>0.963035</v>
+        <v>0.09221500000000001</v>
       </c>
       <c r="G79" s="118" t="n">
-        <v>1482.8</v>
+        <v>1474.9</v>
       </c>
       <c r="H79" s="120" t="n">
-        <v>424940824</v>
+        <v>2915877</v>
       </c>
       <c r="I79" s="120" t="n">
-        <v>28560</v>
+        <v>2720</v>
       </c>
       <c r="J79" s="120" t="n">
-        <v>12038</v>
+        <v>1153</v>
       </c>
       <c r="K79" s="120" t="n">
-        <v>7704</v>
+        <v>738</v>
       </c>
       <c r="L79" s="121" t="n">
-        <v>424989126</v>
-      </c>
-      <c r="M79" s="115" t="n"/>
+        <v>2920488</v>
+      </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="116" t="inlineStr">
         <is>
-          <t>EPO18</t>
+          <t>IPO016</t>
         </is>
       </c>
       <c r="B80" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C80" s="117" t="inlineStr">
         <is>
-          <t>MAICO Italia</t>
+          <t>Integ</t>
         </is>
       </c>
       <c r="D80" s="118" t="n">
-        <v>4388.4</v>
+        <v>6800</v>
       </c>
       <c r="E80" s="118" t="n">
-        <v>4388.4</v>
+        <v>6800</v>
       </c>
       <c r="F80" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="118" t="n">
-        <v>1741.08</v>
+        <v>1475.2</v>
       </c>
       <c r="H80" s="120" t="n">
-        <v>7640555</v>
+        <v>10031360</v>
       </c>
       <c r="I80" s="120" t="n">
-        <v>43527</v>
+        <v>29504</v>
       </c>
       <c r="J80" s="120" t="n">
         <v>10000</v>
@@ -17258,62 +17152,62 @@
         <v>8000</v>
       </c>
       <c r="L80" s="121" t="n">
-        <v>7702082</v>
+        <v>10078864</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="116" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>GPO478</t>
         </is>
       </c>
       <c r="B81" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.19</t>
         </is>
       </c>
       <c r="C81" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D81" s="118" t="n">
-        <v>17404</v>
+        <v>180</v>
       </c>
       <c r="E81" s="118" t="n">
-        <v>21439</v>
+        <v>180</v>
       </c>
       <c r="F81" s="122" t="n">
-        <v>0.811792</v>
+        <v>1</v>
       </c>
       <c r="G81" s="118" t="n">
-        <v>1474.9</v>
+        <v>1518.9</v>
       </c>
       <c r="H81" s="120" t="n">
-        <v>25669160</v>
+        <v>273402</v>
       </c>
       <c r="I81" s="120" t="n">
-        <v>23946</v>
+        <v>30378</v>
       </c>
       <c r="J81" s="120" t="n">
-        <v>10147</v>
+        <v>2500</v>
       </c>
       <c r="K81" s="120" t="n">
-        <v>6494</v>
+        <v>8000</v>
       </c>
       <c r="L81" s="121" t="n">
-        <v>25709747</v>
+        <v>314280</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="116" t="inlineStr">
         <is>
-          <t>CPO695-1</t>
+          <t>CPO698</t>
         </is>
       </c>
       <c r="B82" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.20</t>
         </is>
       </c>
       <c r="C82" s="117" t="inlineStr">
@@ -17322,130 +17216,131 @@
         </is>
       </c>
       <c r="D82" s="118" t="n">
-        <v>2058</v>
+        <v>4290</v>
       </c>
       <c r="E82" s="118" t="n">
-        <v>21439</v>
+        <v>4290</v>
       </c>
       <c r="F82" s="122" t="n">
-        <v>0.09599299999999999</v>
+        <v>1</v>
       </c>
       <c r="G82" s="118" t="n">
-        <v>1474.9</v>
+        <v>1510.6</v>
       </c>
       <c r="H82" s="120" t="n">
-        <v>3035344</v>
+        <v>6480474</v>
       </c>
       <c r="I82" s="120" t="n">
-        <v>2832</v>
+        <v>30212</v>
       </c>
       <c r="J82" s="120" t="n">
-        <v>1200</v>
+        <v>7500</v>
       </c>
       <c r="K82" s="120" t="n">
-        <v>768</v>
+        <v>8000</v>
       </c>
       <c r="L82" s="121" t="n">
-        <v>3040144</v>
-      </c>
+        <v>6526186</v>
+      </c>
+      <c r="M82" s="40" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="116" t="inlineStr">
         <is>
-          <t>CPO695-2</t>
+          <t>GPO473-1</t>
         </is>
       </c>
       <c r="B83" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C83" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D83" s="118" t="n">
-        <v>1977</v>
+        <v>98800</v>
       </c>
       <c r="E83" s="118" t="n">
-        <v>21439</v>
+        <v>99140</v>
       </c>
       <c r="F83" s="122" t="n">
-        <v>0.09221500000000001</v>
+        <v>0.996571</v>
       </c>
       <c r="G83" s="118" t="n">
-        <v>1474.9</v>
+        <v>1502.8</v>
       </c>
       <c r="H83" s="120" t="n">
-        <v>2915877</v>
+        <v>148476640</v>
       </c>
       <c r="I83" s="120" t="n">
-        <v>2720</v>
+        <v>29953</v>
       </c>
       <c r="J83" s="120" t="n">
-        <v>1153</v>
+        <v>12457</v>
       </c>
       <c r="K83" s="120" t="n">
-        <v>738</v>
+        <v>7973</v>
       </c>
       <c r="L83" s="121" t="n">
-        <v>2920488</v>
+        <v>148527023</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="116" t="inlineStr">
         <is>
-          <t>IPO016</t>
+          <t>GPO480</t>
         </is>
       </c>
       <c r="B84" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C84" s="117" t="inlineStr">
         <is>
-          <t>Integ</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D84" s="118" t="n">
-        <v>6800</v>
+        <v>250</v>
       </c>
       <c r="E84" s="118" t="n">
-        <v>6800</v>
+        <v>99140</v>
       </c>
       <c r="F84" s="122" t="n">
-        <v>1</v>
+        <v>0.002522</v>
       </c>
       <c r="G84" s="118" t="n">
-        <v>1475.2</v>
+        <v>1502.8</v>
       </c>
       <c r="H84" s="120" t="n">
-        <v>10031360</v>
+        <v>375700</v>
       </c>
       <c r="I84" s="120" t="n">
-        <v>29504</v>
+        <v>76</v>
       </c>
       <c r="J84" s="120" t="n">
-        <v>10000</v>
+        <v>32</v>
       </c>
       <c r="K84" s="120" t="n">
-        <v>8000</v>
+        <v>20</v>
       </c>
       <c r="L84" s="121" t="n">
-        <v>10078864</v>
+        <v>375828</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="116" t="inlineStr">
         <is>
-          <t>GPO478</t>
+          <t>GPO479</t>
         </is>
       </c>
       <c r="B85" s="116" t="inlineStr">
         <is>
-          <t>2026.05.19</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C85" s="117" t="inlineStr">
@@ -17454,42 +17349,42 @@
         </is>
       </c>
       <c r="D85" s="118" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E85" s="118" t="n">
-        <v>180</v>
+        <v>99140</v>
       </c>
       <c r="F85" s="122" t="n">
-        <v>1</v>
+        <v>0.000908</v>
       </c>
       <c r="G85" s="118" t="n">
-        <v>1518.9</v>
+        <v>1502.8</v>
       </c>
       <c r="H85" s="120" t="n">
-        <v>273402</v>
+        <v>135252</v>
       </c>
       <c r="I85" s="120" t="n">
-        <v>30378</v>
+        <v>27</v>
       </c>
       <c r="J85" s="120" t="n">
-        <v>2500</v>
+        <v>11</v>
       </c>
       <c r="K85" s="120" t="n">
-        <v>8000</v>
+        <v>7</v>
       </c>
       <c r="L85" s="121" t="n">
-        <v>314280</v>
+        <v>135297</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="116" t="inlineStr">
         <is>
-          <t>CPO698</t>
+          <t>CPO697</t>
         </is>
       </c>
       <c r="B86" s="116" t="inlineStr">
         <is>
-          <t>2026.05.20</t>
+          <t>2026.05.29</t>
         </is>
       </c>
       <c r="C86" s="117" t="inlineStr">
@@ -17498,38 +17393,37 @@
         </is>
       </c>
       <c r="D86" s="118" t="n">
-        <v>4290</v>
+        <v>15289</v>
       </c>
       <c r="E86" s="118" t="n">
-        <v>4290</v>
+        <v>101638</v>
       </c>
       <c r="F86" s="122" t="n">
-        <v>1</v>
+        <v>0.150426</v>
       </c>
       <c r="G86" s="118" t="n">
-        <v>1510.6</v>
+        <v>1502.7</v>
       </c>
       <c r="H86" s="120" t="n">
-        <v>6480474</v>
+        <v>22974780</v>
       </c>
       <c r="I86" s="120" t="n">
-        <v>30212</v>
+        <v>4521</v>
       </c>
       <c r="J86" s="120" t="n">
-        <v>7500</v>
+        <v>1880</v>
       </c>
       <c r="K86" s="120" t="n">
-        <v>8000</v>
+        <v>1203</v>
       </c>
       <c r="L86" s="121" t="n">
-        <v>6526186</v>
-      </c>
-      <c r="M86" s="40" t="n"/>
+        <v>22982384</v>
+      </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="116" t="inlineStr">
         <is>
-          <t>GPO473-1</t>
+          <t>CPO696-1</t>
         </is>
       </c>
       <c r="B87" s="116" t="inlineStr">
@@ -17539,41 +17433,41 @@
       </c>
       <c r="C87" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D87" s="118" t="n">
-        <v>98800</v>
+        <v>78209</v>
       </c>
       <c r="E87" s="118" t="n">
-        <v>99140</v>
+        <v>101638</v>
       </c>
       <c r="F87" s="122" t="n">
-        <v>0.996571</v>
+        <v>0.769486</v>
       </c>
       <c r="G87" s="118" t="n">
-        <v>1502.8</v>
+        <v>1502.7</v>
       </c>
       <c r="H87" s="120" t="n">
-        <v>148476640</v>
+        <v>117524664</v>
       </c>
       <c r="I87" s="120" t="n">
-        <v>29953</v>
+        <v>23126</v>
       </c>
       <c r="J87" s="120" t="n">
-        <v>12457</v>
+        <v>9619</v>
       </c>
       <c r="K87" s="120" t="n">
-        <v>7973</v>
+        <v>6156</v>
       </c>
       <c r="L87" s="121" t="n">
-        <v>148527023</v>
+        <v>117563565</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="116" t="inlineStr">
         <is>
-          <t>GPO480</t>
+          <t>CPO696-2</t>
         </is>
       </c>
       <c r="B88" s="116" t="inlineStr">
@@ -17583,349 +17477,357 @@
       </c>
       <c r="C88" s="117" t="inlineStr">
         <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D88" s="118" t="n">
+        <v>8140</v>
+      </c>
+      <c r="E88" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F88" s="122" t="n">
+        <v>0.08008800000000001</v>
+      </c>
+      <c r="G88" s="118" t="n">
+        <v>1502.7</v>
+      </c>
+      <c r="H88" s="120" t="n">
+        <v>12231978</v>
+      </c>
+      <c r="I88" s="120" t="n">
+        <v>2407</v>
+      </c>
+      <c r="J88" s="120" t="n">
+        <v>1001</v>
+      </c>
+      <c r="K88" s="120" t="n">
+        <v>641</v>
+      </c>
+      <c r="L88" s="121" t="n">
+        <v>12236027</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="234" t="inlineStr">
+        <is>
+          <t>GPO481</t>
+        </is>
+      </c>
+      <c r="B89" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C89" s="235" t="inlineStr">
+        <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D88" s="118" t="n">
-        <v>250</v>
-      </c>
-      <c r="E88" s="118" t="n">
-        <v>99140</v>
-      </c>
-      <c r="F88" s="122" t="n">
-        <v>0.002522</v>
-      </c>
-      <c r="G88" s="118" t="n">
-        <v>1502.8</v>
-      </c>
-      <c r="H88" s="120" t="n">
-        <v>375700</v>
-      </c>
-      <c r="I88" s="120" t="n">
-        <v>76</v>
-      </c>
-      <c r="J88" s="120" t="n">
-        <v>32</v>
-      </c>
-      <c r="K88" s="120" t="n">
-        <v>20</v>
-      </c>
-      <c r="L88" s="121" t="n">
-        <v>375828</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="116" t="inlineStr">
-        <is>
-          <t>GPO479</t>
-        </is>
-      </c>
-      <c r="B89" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C89" s="117" t="inlineStr">
+      <c r="D89" s="236" t="n">
+        <v>500</v>
+      </c>
+      <c r="E89" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F89" s="240" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="G89" s="236" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="H89" s="238" t="n">
+        <v>762650</v>
+      </c>
+      <c r="I89" s="238" t="n">
+        <v>128</v>
+      </c>
+      <c r="J89" s="238" t="n">
+        <v>52</v>
+      </c>
+      <c r="K89" s="238" t="n">
+        <v>34</v>
+      </c>
+      <c r="L89" s="239" t="n">
+        <v>762864</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="234" t="inlineStr">
+        <is>
+          <t>GPO473-2</t>
+        </is>
+      </c>
+      <c r="B90" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C90" s="235" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D89" s="118" t="n">
-        <v>90</v>
-      </c>
-      <c r="E89" s="118" t="n">
-        <v>99140</v>
-      </c>
-      <c r="F89" s="122" t="n">
-        <v>0.000908</v>
-      </c>
-      <c r="G89" s="118" t="n">
-        <v>1502.8</v>
-      </c>
-      <c r="H89" s="120" t="n">
-        <v>135252</v>
-      </c>
-      <c r="I89" s="120" t="n">
-        <v>27</v>
-      </c>
-      <c r="J89" s="120" t="n">
-        <v>11</v>
-      </c>
-      <c r="K89" s="120" t="n">
-        <v>7</v>
-      </c>
-      <c r="L89" s="121" t="n">
-        <v>135297</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="116" t="inlineStr">
-        <is>
-          <t>CPO697</t>
-        </is>
-      </c>
-      <c r="B90" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C90" s="117" t="inlineStr">
+      <c r="D90" s="236" t="n">
+        <v>69160</v>
+      </c>
+      <c r="E90" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F90" s="240" t="n">
+        <v>0.580884</v>
+      </c>
+      <c r="G90" s="236" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="H90" s="238" t="n">
+        <v>105489748</v>
+      </c>
+      <c r="I90" s="238" t="n">
+        <v>17720</v>
+      </c>
+      <c r="J90" s="238" t="n">
+        <v>7261</v>
+      </c>
+      <c r="K90" s="238" t="n">
+        <v>4647</v>
+      </c>
+      <c r="L90" s="239" t="n">
+        <v>105519376</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="234" t="inlineStr">
+        <is>
+          <t>GPO473-3</t>
+        </is>
+      </c>
+      <c r="B91" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.10</t>
+        </is>
+      </c>
+      <c r="C91" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D91" s="236" t="n">
+        <v>49400</v>
+      </c>
+      <c r="E91" s="236" t="n">
+        <v>119060</v>
+      </c>
+      <c r="F91" s="240" t="n">
+        <v>0.414917</v>
+      </c>
+      <c r="G91" s="236" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="H91" s="238" t="n">
+        <v>75349820</v>
+      </c>
+      <c r="I91" s="238" t="n">
+        <v>12657</v>
+      </c>
+      <c r="J91" s="238" t="n">
+        <v>5186</v>
+      </c>
+      <c r="K91" s="238" t="n">
+        <v>3319</v>
+      </c>
+      <c r="L91" s="239" t="n">
+        <v>75370982</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="234" t="inlineStr">
+        <is>
+          <t>CPO696-3</t>
+        </is>
+      </c>
+      <c r="B92" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C92" s="235" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D90" s="118" t="n">
-        <v>15289</v>
-      </c>
-      <c r="E90" s="118" t="n">
-        <v>101638</v>
-      </c>
-      <c r="F90" s="122" t="n">
-        <v>0.150426</v>
-      </c>
-      <c r="G90" s="118" t="n">
-        <v>1502.7</v>
-      </c>
-      <c r="H90" s="120" t="n">
-        <v>22974780</v>
-      </c>
-      <c r="I90" s="120" t="n">
-        <v>4521</v>
-      </c>
-      <c r="J90" s="120" t="n">
-        <v>1880</v>
-      </c>
-      <c r="K90" s="120" t="n">
-        <v>1203</v>
-      </c>
-      <c r="L90" s="121" t="n">
-        <v>22982384</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="116" t="inlineStr">
-        <is>
-          <t>CPO696-1</t>
-        </is>
-      </c>
-      <c r="B91" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C91" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D91" s="118" t="n">
-        <v>78209</v>
-      </c>
-      <c r="E91" s="118" t="n">
-        <v>101638</v>
-      </c>
-      <c r="F91" s="122" t="n">
-        <v>0.769486</v>
-      </c>
-      <c r="G91" s="118" t="n">
-        <v>1502.7</v>
-      </c>
-      <c r="H91" s="120" t="n">
-        <v>117524664</v>
-      </c>
-      <c r="I91" s="120" t="n">
-        <v>23126</v>
-      </c>
-      <c r="J91" s="120" t="n">
-        <v>9619</v>
-      </c>
-      <c r="K91" s="120" t="n">
-        <v>6156</v>
-      </c>
-      <c r="L91" s="121" t="n">
-        <v>117563565</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="116" t="inlineStr">
-        <is>
-          <t>CPO696-2</t>
-        </is>
-      </c>
-      <c r="B92" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C92" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D92" s="118" t="n">
-        <v>8140</v>
-      </c>
-      <c r="E92" s="118" t="n">
-        <v>101638</v>
-      </c>
-      <c r="F92" s="122" t="n">
-        <v>0.08008800000000001</v>
-      </c>
-      <c r="G92" s="118" t="n">
-        <v>1502.7</v>
-      </c>
-      <c r="H92" s="120" t="n">
-        <v>12231978</v>
-      </c>
-      <c r="I92" s="120" t="n">
-        <v>2407</v>
-      </c>
-      <c r="J92" s="120" t="n">
-        <v>1001</v>
-      </c>
-      <c r="K92" s="120" t="n">
-        <v>641</v>
-      </c>
-      <c r="L92" s="121" t="n">
-        <v>12236027</v>
+      <c r="D92" s="236" t="n">
+        <v>351274</v>
+      </c>
+      <c r="E92" s="236" t="n">
+        <v>351274</v>
+      </c>
+      <c r="F92" s="240">
+        <f>IFERROR(D92/E92,0)</f>
+        <v/>
+      </c>
+      <c r="G92" s="236" t="n">
+        <v>1518</v>
+      </c>
+      <c r="H92" s="238" t="n">
+        <v>533233932</v>
+      </c>
+      <c r="I92" s="238" t="n">
+        <v>30360</v>
+      </c>
+      <c r="J92" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="K92" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L92" s="239">
+        <f>H92+I92+J92+K92</f>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="234" t="inlineStr">
         <is>
-          <t>GPO481</t>
+          <t>APO001</t>
         </is>
       </c>
       <c r="B93" s="234" t="inlineStr">
         <is>
-          <t>2026.06.10</t>
+          <t>2026.06.17</t>
         </is>
       </c>
       <c r="C93" s="235" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Appotronics</t>
         </is>
       </c>
       <c r="D93" s="236" t="n">
-        <v>500</v>
+        <v>12400</v>
       </c>
       <c r="E93" s="236" t="n">
-        <v>119060</v>
-      </c>
-      <c r="F93" s="240" t="n">
-        <v>0.0042</v>
+        <v>12400</v>
+      </c>
+      <c r="F93" s="240">
+        <f>IFERROR(D93/E93,0)</f>
+        <v/>
       </c>
       <c r="G93" s="236" t="n">
-        <v>1525.3</v>
+        <v>1517.1</v>
       </c>
       <c r="H93" s="238" t="n">
-        <v>762650</v>
+        <v>18812040</v>
       </c>
       <c r="I93" s="238" t="n">
-        <v>128</v>
+        <v>30342</v>
       </c>
       <c r="J93" s="238" t="n">
-        <v>52</v>
+        <v>10000</v>
       </c>
       <c r="K93" s="238" t="n">
-        <v>34</v>
-      </c>
-      <c r="L93" s="239" t="n">
-        <v>762864</v>
+        <v>8000</v>
+      </c>
+      <c r="L93" s="239">
+        <f>H93+I93+J93+K93</f>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="234" t="inlineStr">
         <is>
-          <t>GPO473-2</t>
+          <t>MPO67</t>
         </is>
       </c>
       <c r="B94" s="234" t="inlineStr">
         <is>
-          <t>2026.06.10</t>
+          <t>2026.06.17</t>
         </is>
       </c>
       <c r="C94" s="235" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D94" s="236" t="n">
-        <v>69160</v>
+        <v>49138.8</v>
       </c>
       <c r="E94" s="236" t="n">
-        <v>119060</v>
-      </c>
-      <c r="F94" s="240" t="n">
-        <v>0.580884</v>
+        <v>60726</v>
+      </c>
+      <c r="F94" s="240">
+        <f>IFERROR(D94/E94,0)</f>
+        <v/>
       </c>
       <c r="G94" s="236" t="n">
-        <v>1525.3</v>
+        <v>1517.3</v>
       </c>
       <c r="H94" s="238" t="n">
-        <v>105489748</v>
+        <v>74558330</v>
       </c>
       <c r="I94" s="238" t="n">
-        <v>17720</v>
+        <v>24555</v>
       </c>
       <c r="J94" s="238" t="n">
-        <v>7261</v>
+        <v>10115</v>
       </c>
       <c r="K94" s="238" t="n">
-        <v>4647</v>
-      </c>
-      <c r="L94" s="239" t="n">
-        <v>105519376</v>
+        <v>6473</v>
+      </c>
+      <c r="L94" s="239">
+        <f>H94+I94+J94+K94</f>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="234" t="inlineStr">
         <is>
-          <t>GPO473-3</t>
+          <t>MPO68</t>
         </is>
       </c>
       <c r="B95" s="234" t="inlineStr">
         <is>
-          <t>2026.06.10</t>
+          <t>2026.06.17</t>
         </is>
       </c>
       <c r="C95" s="235" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D95" s="236" t="n">
-        <v>49400</v>
+        <v>11587.2</v>
       </c>
       <c r="E95" s="236" t="n">
-        <v>119060</v>
-      </c>
-      <c r="F95" s="240" t="n">
-        <v>0.414917</v>
+        <v>60726</v>
+      </c>
+      <c r="F95" s="240">
+        <f>IFERROR(D95/E95,0)</f>
+        <v/>
       </c>
       <c r="G95" s="236" t="n">
-        <v>1525.3</v>
+        <v>1517.3</v>
       </c>
       <c r="H95" s="238" t="n">
-        <v>75349820</v>
+        <v>17582284</v>
       </c>
       <c r="I95" s="238" t="n">
-        <v>12657</v>
+        <v>5791</v>
       </c>
       <c r="J95" s="238" t="n">
-        <v>5186</v>
+        <v>2385</v>
       </c>
       <c r="K95" s="238" t="n">
-        <v>3319</v>
-      </c>
-      <c r="L95" s="239" t="n">
-        <v>75370982</v>
+        <v>1527</v>
+      </c>
+      <c r="L95" s="239">
+        <f>H95+I95+J95+K95</f>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="234" t="inlineStr">
         <is>
-          <t>CPO696-3</t>
+          <t>GPO475</t>
         </is>
       </c>
       <c r="B96" s="234" t="inlineStr">
@@ -17935,33 +17837,33 @@
       </c>
       <c r="C96" s="235" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D96" s="236" t="n">
-        <v>351274</v>
+        <v>540</v>
       </c>
       <c r="E96" s="236" t="n">
-        <v>351274</v>
+        <v>2040</v>
       </c>
       <c r="F96" s="240">
         <f>IFERROR(D96/E96,0)</f>
         <v/>
       </c>
       <c r="G96" s="236" t="n">
-        <v>1518</v>
+        <v>1516.8</v>
       </c>
       <c r="H96" s="238" t="n">
-        <v>533233932</v>
+        <v>819072</v>
       </c>
       <c r="I96" s="238" t="n">
-        <v>30360</v>
+        <v>8030</v>
       </c>
       <c r="J96" s="238" t="n">
-        <v>12500</v>
+        <v>1985</v>
       </c>
       <c r="K96" s="238" t="n">
-        <v>8000</v>
+        <v>2118</v>
       </c>
       <c r="L96" s="239">
         <f>H96+I96+J96+K96</f>
@@ -17971,7 +17873,7 @@
     <row r="97">
       <c r="A97" s="234" t="inlineStr">
         <is>
-          <t>APO001</t>
+          <t>GPO475-수리</t>
         </is>
       </c>
       <c r="B97" s="234" t="inlineStr">
@@ -17981,226 +17883,43 @@
       </c>
       <c r="C97" s="235" t="inlineStr">
         <is>
-          <t>Appotronics</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D97" s="236" t="n">
-        <v>12400</v>
+        <v>1500</v>
       </c>
       <c r="E97" s="236" t="n">
-        <v>12400</v>
+        <v>2040</v>
       </c>
       <c r="F97" s="240">
         <f>IFERROR(D97/E97,0)</f>
         <v/>
       </c>
       <c r="G97" s="236" t="n">
-        <v>1517.1</v>
+        <v>1516.8</v>
       </c>
       <c r="H97" s="238" t="n">
-        <v>18812040</v>
+        <v>2275200</v>
       </c>
       <c r="I97" s="238" t="n">
-        <v>30342</v>
+        <v>22306</v>
       </c>
       <c r="J97" s="238" t="n">
-        <v>10000</v>
+        <v>5515</v>
       </c>
       <c r="K97" s="238" t="n">
-        <v>8000</v>
+        <v>5882</v>
       </c>
       <c r="L97" s="239">
         <f>H97+I97+J97+K97</f>
         <v/>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="234" t="inlineStr">
-        <is>
-          <t>MPO67</t>
-        </is>
-      </c>
-      <c r="B98" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C98" s="235" t="inlineStr">
-        <is>
-          <t>MAG</t>
-        </is>
-      </c>
-      <c r="D98" s="236" t="n">
-        <v>49138.8</v>
-      </c>
-      <c r="E98" s="236" t="n">
-        <v>60726</v>
-      </c>
-      <c r="F98" s="240">
-        <f>IFERROR(D98/E98,0)</f>
-        <v/>
-      </c>
-      <c r="G98" s="236" t="n">
-        <v>1517.3</v>
-      </c>
-      <c r="H98" s="238" t="n">
-        <v>74558330</v>
-      </c>
-      <c r="I98" s="238" t="n">
-        <v>24555</v>
-      </c>
-      <c r="J98" s="238" t="n">
-        <v>10115</v>
-      </c>
-      <c r="K98" s="238" t="n">
-        <v>6473</v>
-      </c>
-      <c r="L98" s="239">
-        <f>H98+I98+J98+K98</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="234" t="inlineStr">
-        <is>
-          <t>MPO68</t>
-        </is>
-      </c>
-      <c r="B99" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C99" s="235" t="inlineStr">
-        <is>
-          <t>MAG</t>
-        </is>
-      </c>
-      <c r="D99" s="236" t="n">
-        <v>11587.2</v>
-      </c>
-      <c r="E99" s="236" t="n">
-        <v>60726</v>
-      </c>
-      <c r="F99" s="240">
-        <f>IFERROR(D99/E99,0)</f>
-        <v/>
-      </c>
-      <c r="G99" s="236" t="n">
-        <v>1517.3</v>
-      </c>
-      <c r="H99" s="238" t="n">
-        <v>17582284</v>
-      </c>
-      <c r="I99" s="238" t="n">
-        <v>5791</v>
-      </c>
-      <c r="J99" s="238" t="n">
-        <v>2385</v>
-      </c>
-      <c r="K99" s="238" t="n">
-        <v>1527</v>
-      </c>
-      <c r="L99" s="239">
-        <f>H99+I99+J99+K99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="234" t="inlineStr">
-        <is>
-          <t>GPO475</t>
-        </is>
-      </c>
-      <c r="B100" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C100" s="235" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D100" s="236" t="n">
-        <v>540</v>
-      </c>
-      <c r="E100" s="236" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F100" s="240">
-        <f>IFERROR(D100/E100,0)</f>
-        <v/>
-      </c>
-      <c r="G100" s="236" t="n">
-        <v>1516.8</v>
-      </c>
-      <c r="H100" s="238" t="n">
-        <v>819072</v>
-      </c>
-      <c r="I100" s="238" t="n">
-        <v>8030</v>
-      </c>
-      <c r="J100" s="238" t="n">
-        <v>1985</v>
-      </c>
-      <c r="K100" s="238" t="n">
-        <v>2118</v>
-      </c>
-      <c r="L100" s="239">
-        <f>H100+I100+J100+K100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="234" t="inlineStr">
-        <is>
-          <t>GPO475-수리</t>
-        </is>
-      </c>
-      <c r="B101" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C101" s="235" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D101" s="236" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E101" s="236" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F101" s="240">
-        <f>IFERROR(D101/E101,0)</f>
-        <v/>
-      </c>
-      <c r="G101" s="236" t="n">
-        <v>1516.8</v>
-      </c>
-      <c r="H101" s="238" t="n">
-        <v>2275200</v>
-      </c>
-      <c r="I101" s="238" t="n">
-        <v>22306</v>
-      </c>
-      <c r="J101" s="238" t="n">
-        <v>5515</v>
-      </c>
-      <c r="K101" s="238" t="n">
-        <v>5882</v>
-      </c>
-      <c r="L101" s="239">
-        <f>H101+I101+J101+K101</f>
-        <v/>
-      </c>
-    </row>
+    <row r="98"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A41:L41"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -2206,12 +2206,12 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr">
+      <c r="AE5" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AF5" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2333,12 +2333,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE6" s="3" t="inlineStr">
+      <c r="AE6" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AF6" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2460,12 +2460,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr">
+      <c r="AE7" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AF7" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2587,12 +2587,12 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="AE8" s="3" t="inlineStr">
+      <c r="AE8" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AF8" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2657,7 +2657,7 @@
           <t>Parts (국내)</t>
         </is>
       </c>
-      <c r="O9" s="12" t="n"/>
+      <c r="O9" s="177" t="n"/>
       <c r="P9" s="12" t="n"/>
       <c r="Q9" s="18">
         <f>IF(P9="","",IFERROR(VLOOKUP(O9,FxRateTable,4,TRUE),""))</f>
@@ -2673,7 +2673,7 @@
       <c r="T9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="13" t="n">
+      <c r="U9" s="176" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="12" t="inlineStr">
@@ -2708,12 +2708,12 @@
         <v/>
       </c>
       <c r="AD9" s="12" t="n"/>
-      <c r="AE9" s="12" t="inlineStr">
+      <c r="AE9" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF9" s="13" t="inlineStr">
+      <c r="AF9" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2835,12 +2835,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE10" s="3" t="inlineStr">
+      <c r="AE10" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AF10" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2962,12 +2962,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE11" s="3" t="inlineStr">
+      <c r="AE11" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AF11" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3089,12 +3089,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE12" s="3" t="inlineStr">
+      <c r="AE12" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AF12" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3216,12 +3216,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE13" s="3" t="inlineStr">
+      <c r="AE13" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AF13" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3343,12 +3343,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE14" s="3" t="inlineStr">
+      <c r="AE14" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AF14" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3470,12 +3470,12 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE15" s="3" t="inlineStr">
+      <c r="AE15" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AF15" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3597,12 +3597,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE16" s="3" t="inlineStr">
+      <c r="AE16" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AF16" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3724,12 +3724,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE17" s="3" t="inlineStr">
+      <c r="AE17" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AF17" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3851,12 +3851,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE18" s="3" t="inlineStr">
+      <c r="AE18" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AF18" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3978,12 +3978,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE19" s="3" t="inlineStr">
+      <c r="AE19" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AF19" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4105,12 +4105,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE20" s="3" t="inlineStr">
+      <c r="AE20" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF20" s="4" t="inlineStr">
+      <c r="AF20" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4232,12 +4232,12 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="AE21" s="3" t="inlineStr">
+      <c r="AE21" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AF21" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4359,12 +4359,12 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE22" s="3" t="inlineStr">
+      <c r="AE22" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AF22" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4429,7 +4429,7 @@
           <t>Projector (한국)</t>
         </is>
       </c>
-      <c r="O23" s="12" t="n"/>
+      <c r="O23" s="177" t="n"/>
       <c r="P23" s="12" t="n"/>
       <c r="Q23" s="18">
         <f>IF(P23="","",IFERROR(VLOOKUP(O23,FxRateTable,4,TRUE),""))</f>
@@ -4445,7 +4445,7 @@
       <c r="T23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="13" t="n">
+      <c r="U23" s="176" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="12" t="inlineStr">
@@ -4480,12 +4480,12 @@
         <v/>
       </c>
       <c r="AD23" s="12" t="n"/>
-      <c r="AE23" s="12" t="inlineStr">
+      <c r="AE23" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF23" s="13" t="inlineStr">
+      <c r="AF23" s="176" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4607,12 +4607,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE24" s="3" t="inlineStr">
+      <c r="AE24" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AF24" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4734,12 +4734,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE25" s="3" t="inlineStr">
+      <c r="AE25" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AF25" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4861,12 +4861,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE26" s="3" t="inlineStr">
+      <c r="AE26" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AF26" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4988,12 +4988,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE27" s="3" t="inlineStr">
+      <c r="AE27" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AF27" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5115,12 +5115,12 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE28" s="3" t="inlineStr">
+      <c r="AE28" s="175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AF28" s="174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5238,8 +5238,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE29" s="3" t="n"/>
-      <c r="AF29" s="4" t="n"/>
+      <c r="AE29" s="175" t="n"/>
+      <c r="AF29" s="174" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="78" t="n">
@@ -5353,8 +5353,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE30" s="78" t="n"/>
-      <c r="AF30" s="78" t="n"/>
+      <c r="AE30" s="179" t="n"/>
+      <c r="AF30" s="179" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="78" t="n">
@@ -5468,8 +5468,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE31" s="78" t="n"/>
-      <c r="AF31" s="78" t="n"/>
+      <c r="AE31" s="179" t="n"/>
+      <c r="AF31" s="179" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="78" t="n">
@@ -5573,8 +5573,8 @@
         <v/>
       </c>
       <c r="AD32" s="78" t="n"/>
-      <c r="AE32" s="78" t="n"/>
-      <c r="AF32" s="78" t="n"/>
+      <c r="AE32" s="179" t="n"/>
+      <c r="AF32" s="179" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="124" t="n">
@@ -5603,7 +5603,7 @@
       <c r="F33" s="181" t="n">
         <v>46127</v>
       </c>
-      <c r="G33" s="283" t="n">
+      <c r="G33" s="181" t="n">
         <v>46190</v>
       </c>
       <c r="H33" s="126" t="n">
@@ -5647,7 +5647,7 @@
       <c r="T33" s="128" t="n">
         <v>52140300</v>
       </c>
-      <c r="U33" s="129" t="n"/>
+      <c r="U33" s="182" t="n"/>
       <c r="V33" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5684,8 +5684,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE33" s="129" t="n"/>
-      <c r="AF33" s="129" t="n"/>
+      <c r="AE33" s="182" t="n"/>
+      <c r="AF33" s="182" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="124" t="n">
@@ -5714,7 +5714,7 @@
       <c r="F34" s="181" t="n">
         <v>46143</v>
       </c>
-      <c r="G34" s="124" t="inlineStr">
+      <c r="G34" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5764,7 +5764,7 @@
       <c r="T34" s="128" t="n">
         <v>118665800</v>
       </c>
-      <c r="U34" s="129" t="n"/>
+      <c r="U34" s="182" t="n"/>
       <c r="V34" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5801,8 +5801,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE34" s="129" t="n"/>
-      <c r="AF34" s="129" t="n"/>
+      <c r="AE34" s="182" t="n"/>
+      <c r="AF34" s="182" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="124" t="n">
@@ -5875,7 +5875,7 @@
       <c r="T35" s="128" t="n">
         <v>14902330</v>
       </c>
-      <c r="U35" s="129" t="n"/>
+      <c r="U35" s="182" t="n"/>
       <c r="V35" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5912,8 +5912,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE35" s="129" t="n"/>
-      <c r="AF35" s="129" t="n"/>
+      <c r="AE35" s="182" t="n"/>
+      <c r="AF35" s="182" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="124" t="n">
@@ -5964,7 +5964,7 @@
         <v>7</v>
       </c>
       <c r="N36" s="129" t="n"/>
-      <c r="O36" s="129" t="n"/>
+      <c r="O36" s="182" t="n"/>
       <c r="P36" s="129" t="n"/>
       <c r="Q36" s="126">
         <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
@@ -5980,7 +5980,7 @@
       <c r="T36" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="129" t="n"/>
+      <c r="U36" s="182" t="n"/>
       <c r="V36" s="129" t="n"/>
       <c r="W36" s="128" t="n">
         <v>0</v>
@@ -6009,8 +6009,8 @@
         <v/>
       </c>
       <c r="AD36" s="129" t="n"/>
-      <c r="AE36" s="129" t="n"/>
-      <c r="AF36" s="129" t="n"/>
+      <c r="AE36" s="182" t="n"/>
+      <c r="AF36" s="182" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="207" t="n">
@@ -6124,8 +6124,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE37" s="207" t="n"/>
-      <c r="AF37" s="208" t="n"/>
+      <c r="AE37" s="210" t="n"/>
+      <c r="AF37" s="209" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="207" t="n">
@@ -6239,8 +6239,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE38" s="207" t="n"/>
-      <c r="AF38" s="208" t="n"/>
+      <c r="AE38" s="210" t="n"/>
+      <c r="AF38" s="209" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="124" t="n">
@@ -6303,7 +6303,7 @@
           <t>JNIOR Model 410 (IPO017, FedEx 4/21 발송분)</t>
         </is>
       </c>
-      <c r="O39" s="129" t="n"/>
+      <c r="O39" s="182" t="n"/>
       <c r="P39" s="129" t="n"/>
       <c r="Q39" s="126">
         <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
@@ -6319,7 +6319,7 @@
       <c r="T39" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U39" s="129" t="n"/>
+      <c r="U39" s="182" t="n"/>
       <c r="V39" s="129" t="inlineStr">
         <is>
           <t>-</t>
@@ -6352,12 +6352,12 @@
         <v/>
       </c>
       <c r="AD39" s="129" t="n"/>
-      <c r="AE39" s="129" t="inlineStr">
+      <c r="AE39" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF39" s="129" t="inlineStr">
+      <c r="AF39" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6390,7 +6390,7 @@
       <c r="F40" s="181" t="n">
         <v>46163</v>
       </c>
-      <c r="G40" s="283" t="inlineStr">
+      <c r="G40" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6444,7 +6444,7 @@
       <c r="T40" s="128" t="n">
         <v>52536040</v>
       </c>
-      <c r="U40" s="129" t="n"/>
+      <c r="U40" s="182" t="n"/>
       <c r="V40" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6481,8 +6481,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE40" s="129" t="n"/>
-      <c r="AF40" s="129" t="n"/>
+      <c r="AE40" s="182" t="n"/>
+      <c r="AF40" s="182" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="124" t="n">
@@ -6511,7 +6511,7 @@
       <c r="F41" s="181" t="n">
         <v>46154</v>
       </c>
-      <c r="G41" s="283" t="n">
+      <c r="G41" s="181" t="n">
         <v>46190</v>
       </c>
       <c r="H41" s="126" t="n">
@@ -6559,7 +6559,7 @@
       <c r="T41" s="128" t="n">
         <v>8891915</v>
       </c>
-      <c r="U41" s="129" t="n"/>
+      <c r="U41" s="182" t="n"/>
       <c r="V41" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6596,8 +6596,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE41" s="129" t="n"/>
-      <c r="AF41" s="129" t="n"/>
+      <c r="AE41" s="182" t="n"/>
+      <c r="AF41" s="182" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="124" t="n">
@@ -6626,7 +6626,7 @@
       <c r="F42" s="181" t="n">
         <v>46154</v>
       </c>
-      <c r="G42" s="283" t="n">
+      <c r="G42" s="181" t="n">
         <v>46190</v>
       </c>
       <c r="H42" s="126" t="n">
@@ -6674,7 +6674,7 @@
       <c r="T42" s="128" t="n">
         <v>2096763</v>
       </c>
-      <c r="U42" s="129" t="n"/>
+      <c r="U42" s="182" t="n"/>
       <c r="V42" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6711,8 +6711,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE42" s="129" t="n"/>
-      <c r="AF42" s="129" t="n"/>
+      <c r="AE42" s="182" t="n"/>
+      <c r="AF42" s="182" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="124" t="n">
@@ -6741,7 +6741,7 @@
       <c r="F43" s="181" t="n">
         <v>46163</v>
       </c>
-      <c r="G43" s="283" t="n">
+      <c r="G43" s="181" t="n">
         <v>46190</v>
       </c>
       <c r="H43" s="126" t="n">
@@ -6783,7 +6783,7 @@
       <c r="T43" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U43" s="129" t="n"/>
+      <c r="U43" s="182" t="n"/>
       <c r="V43" s="129" t="n"/>
       <c r="W43" s="128" t="n">
         <v>0</v>
@@ -6812,8 +6812,8 @@
         <v/>
       </c>
       <c r="AD43" s="129" t="n"/>
-      <c r="AE43" s="129" t="n"/>
-      <c r="AF43" s="129" t="n"/>
+      <c r="AE43" s="182" t="n"/>
+      <c r="AF43" s="182" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="20" t="n">
@@ -6868,7 +6868,7 @@
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="O44" s="20" t="inlineStr">
+      <c r="O44" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6892,7 +6892,7 @@
       <c r="T44" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U44" s="21" t="n">
+      <c r="U44" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V44" s="20" t="inlineStr">
@@ -6995,7 +6995,7 @@
           <t>HFR License</t>
         </is>
       </c>
-      <c r="O45" s="20" t="inlineStr">
+      <c r="O45" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7019,7 +7019,7 @@
       <c r="T45" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="21" t="n">
+      <c r="U45" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V45" s="20" t="inlineStr">
@@ -7122,7 +7122,7 @@
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="O46" s="20" t="inlineStr">
+      <c r="O46" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7146,7 +7146,7 @@
       <c r="T46" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="21" t="n">
+      <c r="U46" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="20" t="inlineStr">
@@ -7249,7 +7249,7 @@
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="O47" s="20" t="inlineStr">
+      <c r="O47" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7273,7 +7273,7 @@
       <c r="T47" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="21" t="n">
+      <c r="U47" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V47" s="20" t="inlineStr">
@@ -7376,7 +7376,7 @@
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="O48" s="20" t="inlineStr">
+      <c r="O48" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7400,7 +7400,7 @@
       <c r="T48" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="21" t="n">
+      <c r="U48" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V48" s="20" t="inlineStr">
@@ -7503,7 +7503,7 @@
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="O49" s="20" t="inlineStr">
+      <c r="O49" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7527,7 +7527,7 @@
       <c r="T49" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="21" t="n">
+      <c r="U49" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V49" s="20" t="inlineStr">
@@ -7636,7 +7636,7 @@
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="O50" s="20" t="inlineStr">
+      <c r="O50" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7660,7 +7660,7 @@
       <c r="T50" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="21" t="n">
+      <c r="U50" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V50" s="20" t="inlineStr">
@@ -7763,7 +7763,7 @@
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="O51" s="20" t="inlineStr">
+      <c r="O51" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7787,7 +7787,7 @@
       <c r="T51" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U51" s="21" t="n">
+      <c r="U51" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V51" s="20" t="inlineStr">
@@ -7896,7 +7896,7 @@
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="O52" s="20" t="inlineStr">
+      <c r="O52" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7920,7 +7920,7 @@
       <c r="T52" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="21" t="n">
+      <c r="U52" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V52" s="20" t="inlineStr">
@@ -8023,7 +8023,7 @@
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="O53" s="20" t="inlineStr">
+      <c r="O53" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8047,7 +8047,7 @@
       <c r="T53" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U53" s="21" t="n">
+      <c r="U53" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V53" s="20" t="inlineStr">
@@ -8150,7 +8150,7 @@
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="O54" s="20" t="inlineStr">
+      <c r="O54" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8174,7 +8174,7 @@
       <c r="T54" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U54" s="21" t="n">
+      <c r="U54" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V54" s="20" t="inlineStr">
@@ -8277,7 +8277,7 @@
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="O55" s="20" t="inlineStr">
+      <c r="O55" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8301,7 +8301,7 @@
       <c r="T55" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U55" s="21" t="n">
+      <c r="U55" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V55" s="20" t="inlineStr">
@@ -8404,7 +8404,7 @@
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="O56" s="20" t="inlineStr">
+      <c r="O56" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8428,7 +8428,7 @@
       <c r="T56" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U56" s="21" t="n">
+      <c r="U56" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V56" s="20" t="inlineStr">
@@ -8531,7 +8531,7 @@
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="O57" s="20" t="inlineStr">
+      <c r="O57" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8555,7 +8555,7 @@
       <c r="T57" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U57" s="21" t="n">
+      <c r="U57" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V57" s="20" t="inlineStr">
@@ -8658,7 +8658,7 @@
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="O58" s="20" t="inlineStr">
+      <c r="O58" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8682,7 +8682,7 @@
       <c r="T58" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="21" t="n">
+      <c r="U58" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V58" s="20" t="inlineStr">
@@ -8785,7 +8785,7 @@
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="O59" s="20" t="inlineStr">
+      <c r="O59" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8809,7 +8809,7 @@
       <c r="T59" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="21" t="n">
+      <c r="U59" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V59" s="20" t="inlineStr">
@@ -8912,7 +8912,7 @@
           <t>EW (CGV 동백 외)</t>
         </is>
       </c>
-      <c r="O60" s="20" t="inlineStr">
+      <c r="O60" s="184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8936,7 +8936,7 @@
       <c r="T60" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="21" t="n">
+      <c r="U60" s="183" t="n">
         <v>0</v>
       </c>
       <c r="V60" s="20" t="inlineStr">
@@ -9283,7 +9283,7 @@
         <v>8000</v>
       </c>
       <c r="N63" s="137" t="n"/>
-      <c r="O63" s="137" t="n"/>
+      <c r="O63" s="189" t="n"/>
       <c r="P63" s="137" t="n"/>
       <c r="Q63" s="134">
         <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
@@ -9299,7 +9299,7 @@
       <c r="T63" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U63" s="137" t="n"/>
+      <c r="U63" s="189" t="n"/>
       <c r="V63" s="137" t="n"/>
       <c r="W63" s="136" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>20</v>
       </c>
       <c r="N64" s="137" t="n"/>
-      <c r="O64" s="137" t="n"/>
+      <c r="O64" s="189" t="n"/>
       <c r="P64" s="137" t="n"/>
       <c r="Q64" s="134">
         <f>IF(P64="","",IFERROR(VLOOKUP(O64,FxRateTable,4,TRUE),""))</f>
@@ -9404,7 +9404,7 @@
       <c r="T64" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U64" s="137" t="n"/>
+      <c r="U64" s="189" t="n"/>
       <c r="V64" s="137" t="n"/>
       <c r="W64" s="136" t="n">
         <v>0</v>
@@ -9471,7 +9471,7 @@
       <c r="F65" s="188" t="n">
         <v>46152</v>
       </c>
-      <c r="G65" s="233" t="n">
+      <c r="G65" s="188" t="n">
         <v>46183</v>
       </c>
       <c r="H65" s="134" t="n">
@@ -9493,7 +9493,7 @@
         <v>34</v>
       </c>
       <c r="N65" s="137" t="n"/>
-      <c r="O65" s="137" t="n"/>
+      <c r="O65" s="189" t="n"/>
       <c r="P65" s="137" t="n"/>
       <c r="Q65" s="134">
         <f>IF(P65="","",IFERROR(VLOOKUP(O65,FxRateTable,4,TRUE),""))</f>
@@ -9509,7 +9509,7 @@
       <c r="T65" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="137" t="n"/>
+      <c r="U65" s="189" t="n"/>
       <c r="V65" s="137" t="n"/>
       <c r="W65" s="136" t="n">
         <v>0</v>
@@ -9542,12 +9542,12 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE65" s="137" t="inlineStr">
+      <c r="AE65" s="189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF65" s="137" t="inlineStr">
+      <c r="AF65" s="189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9606,7 +9606,7 @@
           <t>TMS-1000 License 6 screens (CGV 안동)</t>
         </is>
       </c>
-      <c r="O66" s="137" t="n"/>
+      <c r="O66" s="189" t="n"/>
       <c r="P66" s="137" t="n"/>
       <c r="Q66" s="134">
         <f>IF(P66="","",IFERROR(VLOOKUP(O66,FxRateTable,4,TRUE),""))</f>
@@ -9622,7 +9622,7 @@
       <c r="T66" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U66" s="137" t="n"/>
+      <c r="U66" s="189" t="n"/>
       <c r="V66" s="137" t="n"/>
       <c r="W66" s="136" t="n">
         <v>0</v>
@@ -9721,7 +9721,7 @@
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O67" s="12" t="inlineStr">
+      <c r="O67" s="177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9745,7 +9745,7 @@
       <c r="T67" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U67" s="13" t="n">
+      <c r="U67" s="176" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="12" t="inlineStr">
@@ -9874,7 +9874,7 @@
       <c r="T68" s="18" t="n">
         <v>67750</v>
       </c>
-      <c r="U68" s="13" t="n"/>
+      <c r="U68" s="176" t="n"/>
       <c r="V68" s="12" t="inlineStr">
         <is>
           <t>운서합동</t>
@@ -10027,8 +10027,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE69" s="216" t="n"/>
-      <c r="AF69" s="217" t="n"/>
+      <c r="AE69" s="219" t="n"/>
+      <c r="AF69" s="218" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="284" t="n">
@@ -10099,7 +10099,7 @@
       <c r="T70" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="U70" s="285" t="n"/>
+      <c r="U70" s="286" t="n"/>
       <c r="V70" s="284" t="n"/>
       <c r="W70" s="290" t="n">
         <v>0</v>
@@ -13494,7 +13494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="160" min="1" max="1"/>
@@ -17916,7 +17916,6 @@
         <v/>
       </c>
     </row>
-    <row r="98"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A41:L41"/>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" tabRatio="500" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PO별 개당 수입원가" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="라이센스_워런티" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="합배송_비용안분" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="외화송금내역" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Usance_LC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="환율" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PO별 개당 수입원가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라이센스_워런티" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="합배송_비용안분" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화송금내역" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usance_LC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="FxRateTable">환율!$A$7:$D$43</definedName>
+    <definedName name="FxRateTable">'환율'!$A$7:$D$45</definedName>
     <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$40</definedName>
     <definedName name="RemitTable2">'외화송금내역'!$A$43:$L$97</definedName>
   </definedNames>
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="310">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1328,6 +1328,48 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1410,6 +1452,7 @@
   <authors>
     <author>RNR 재무팀</author>
     <author>import-cost-calculator</author>
+    <author>RNR</author>
   </authors>
   <commentList>
     <comment ref="S5" authorId="0" shapeId="0">
@@ -1545,6 +1588,14 @@
 원산지: 우크라이나(UA-A)</t>
       </text>
     </comment>
+    <comment ref="S43" authorId="2" shapeId="0">
+      <text>
+        <t>관세 0원 — 수입신고필증 세율구분 'C'(가가, WTO/ITA 양허) 적용
+HS 8529.90-6010 프로젝터 부품 (레이저광원모듈)
+원산지: 중국(CN-A)
+(신고번호 14008-26-101317M, 수리일 2026-06-29)</t>
+      </text>
+    </comment>
     <comment ref="S68" authorId="0" shapeId="0">
       <text>
         <t>관세율 0.00% - 세율구분 C(가가, WTO/ITA 양허)
@@ -1553,6 +1604,19 @@
       </text>
     </comment>
     <comment ref="Y68" authorId="0" shapeId="0">
+      <text>
+        <t>DHL 2026-05월 인보이스 (AWB 5094871784 = 수입신고필증 B/L 일치)
+GDC RMA 수리반환 건, 지출결의 2026-1344, 6/9 집행</t>
+      </text>
+    </comment>
+    <comment ref="S73" authorId="0" shapeId="0">
+      <text>
+        <t>관세율 0.00% - 세율구분 C(가가, WTO/ITA 양허)
+수리반환 재수입 건, 부가세만 과세
+(신고필증 2235626351613M)</t>
+      </text>
+    </comment>
+    <comment ref="Y73" authorId="0" shapeId="0">
       <text>
         <t>DHL 2026-05월 인보이스 (AWB 5094871784 = 수입신고필증 B/L 일치)
 GDC RMA 수리반환 건, 지출결의 2026-1344, 6/9 집행</t>
@@ -1837,7 +1901,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-06-18  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-07-02  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="148" t="n"/>
@@ -6767,8 +6831,14 @@
           <t>S20-C2220-BEAB 레이저모듈 2set (CP2220)</t>
         </is>
       </c>
-      <c r="O43" s="182" t="n"/>
-      <c r="P43" s="129" t="n"/>
+      <c r="O43" s="182" t="n">
+        <v>46202</v>
+      </c>
+      <c r="P43" s="129" t="inlineStr">
+        <is>
+          <t>14008-26-101317M</t>
+        </is>
+      </c>
       <c r="Q43" s="126">
         <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
         <v/>
@@ -6781,20 +6851,26 @@
         <v>0</v>
       </c>
       <c r="T43" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="182" t="n"/>
-      <c r="V43" s="129" t="n"/>
+        <v>1959600</v>
+      </c>
+      <c r="U43" s="182" t="n">
+        <v>46202</v>
+      </c>
+      <c r="V43" s="129" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
       <c r="W43" s="128" t="n">
-        <v>0</v>
+        <v>43010</v>
       </c>
       <c r="X43" s="124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y43" s="128" t="n">
-        <v>0</v>
+        <v>692650</v>
       </c>
       <c r="Z43" s="128">
         <f>S43+T43+W43</f>
@@ -6811,2581 +6887,2587 @@
         <f>ROUND(AA43/AB43,0)</f>
         <v/>
       </c>
-      <c r="AD43" s="129" t="n"/>
+      <c r="AD43" s="129" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
       <c r="AE43" s="182" t="n"/>
       <c r="AF43" s="182" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="20" t="n">
+      <c r="A44" s="124" t="n">
+        <v>67</v>
+      </c>
+      <c r="B44" s="124" t="inlineStr">
+        <is>
+          <t>GPO483</t>
+        </is>
+      </c>
+      <c r="C44" s="124" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D44" s="124" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E44" s="124" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F44" s="181" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G44" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="126" t="n">
+        <v>14730</v>
+      </c>
+      <c r="I44" s="126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="129" t="inlineStr">
+        <is>
+          <t>AIB-3000 Cinema Audio Processor 9EA (롯데 인천검단 6 / CJ미래원 1 / RNR 2)</t>
+        </is>
+      </c>
+      <c r="O44" s="182" t="n"/>
+      <c r="P44" s="129" t="n"/>
+      <c r="Q44" s="126">
+        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R44" s="126">
+        <f>IF(P44="","",H44)</f>
+        <v/>
+      </c>
+      <c r="S44" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="182" t="n"/>
+      <c r="V44" s="129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W44" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y44" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="128">
+        <f>S44+T44+W44</f>
+        <v/>
+      </c>
+      <c r="AA44" s="131">
+        <f>K44+L44+M44+IFERROR(VLOOKUP(B44,RemitTable2,9,FALSE),0)+Y44+Z44</f>
+        <v/>
+      </c>
+      <c r="AB44" s="167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC44" s="131">
+        <f>ROUND(AA44/AB44,0)</f>
+        <v/>
+      </c>
+      <c r="AD44" s="129" t="n"/>
+      <c r="AE44" s="182" t="n"/>
+      <c r="AF44" s="182" t="n"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="296" t="n">
         <v>29</v>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B45" s="296" t="inlineStr">
         <is>
           <t>CPO667</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
+      <c r="C45" s="297" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="D45" s="296" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E44" s="21" t="inlineStr">
+      <c r="E45" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F44" s="183" t="n">
+      <c r="F45" s="298" t="n">
         <v>45925</v>
       </c>
-      <c r="G44" s="184" t="n">
+      <c r="G45" s="299" t="n">
         <v>46080</v>
       </c>
-      <c r="H44" s="24" t="n">
+      <c r="H45" s="300" t="n">
         <v>5673</v>
       </c>
-      <c r="I44" s="185" t="n">
+      <c r="I45" s="301" t="n">
         <v>1441.6</v>
       </c>
-      <c r="J44" s="26" t="n">
+      <c r="J45" s="302" t="n">
         <v>8178197</v>
       </c>
-      <c r="K44" s="26" t="n">
+      <c r="K45" s="302" t="n">
         <v>8178197</v>
       </c>
-      <c r="L44" s="26" t="n">
+      <c r="L45" s="302" t="n">
         <v>499</v>
       </c>
-      <c r="M44" s="26" t="n">
+      <c r="M45" s="302" t="n">
         <v>319</v>
       </c>
-      <c r="N44" s="20" t="inlineStr">
+      <c r="N45" s="296" t="inlineStr">
         <is>
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="O44" s="184" t="inlineStr">
+      <c r="O45" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P44" s="20" t="inlineStr">
+      <c r="P45" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q44" s="24">
-        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R44" s="26">
-        <f>IF(P44="","",H44)</f>
-        <v/>
-      </c>
-      <c r="S44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="20" t="inlineStr">
+      <c r="Q45" s="300">
+        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R45" s="302">
+        <f>IF(P45="","",H45)</f>
+        <v/>
+      </c>
+      <c r="S45" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="21" t="inlineStr">
+      <c r="W45" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="26">
-        <f>S44+T44+W44</f>
-        <v/>
-      </c>
-      <c r="AA44" s="26">
-        <f>K44+L44+M44+IFERROR(VLOOKUP(B44,RemitTable2,9,FALSE),0)+Y44+Z44</f>
-        <v/>
-      </c>
-      <c r="AB44" s="27" t="n">
+      <c r="Y45" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="302">
+        <f>S45+T45+W45</f>
+        <v/>
+      </c>
+      <c r="AA45" s="302">
+        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE),0)+Y45+Z45</f>
+        <v/>
+      </c>
+      <c r="AB45" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC44" s="26">
-        <f>ROUND(AA44/AB44,0)</f>
-        <v/>
-      </c>
-      <c r="AD44" s="20" t="inlineStr">
+      <c r="AC45" s="302">
+        <f>ROUND(AA45/AB45,0)</f>
+        <v/>
+      </c>
+      <c r="AD45" s="296" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="AE44" s="184" t="inlineStr">
+      <c r="AE45" s="299" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="AF44" s="183" t="inlineStr">
+      <c r="AF45" s="298" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="20" t="n">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="296" t="n">
         <v>30</v>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B46" s="296" t="inlineStr">
         <is>
           <t>GPO458</t>
         </is>
       </c>
-      <c r="C45" s="21" t="inlineStr">
+      <c r="C46" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D46" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E45" s="21" t="inlineStr">
+      <c r="E46" s="297" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F45" s="183" t="n">
+      <c r="F46" s="298" t="n">
         <v>45982</v>
       </c>
-      <c r="G45" s="184" t="n">
+      <c r="G46" s="299" t="n">
         <v>46020</v>
       </c>
-      <c r="H45" s="24" t="n">
+      <c r="H46" s="300" t="n">
         <v>350</v>
       </c>
-      <c r="I45" s="185" t="n">
+      <c r="I46" s="301" t="n">
         <v>1439.1</v>
       </c>
-      <c r="J45" s="26" t="n">
+      <c r="J46" s="302" t="n">
         <v>503685</v>
       </c>
-      <c r="K45" s="26" t="n">
+      <c r="K46" s="302" t="n">
         <v>503685</v>
       </c>
-      <c r="L45" s="26" t="n">
+      <c r="L46" s="302" t="n">
         <v>253</v>
       </c>
-      <c r="M45" s="26" t="n">
+      <c r="M46" s="302" t="n">
         <v>202</v>
       </c>
-      <c r="N45" s="20" t="inlineStr">
+      <c r="N46" s="296" t="inlineStr">
         <is>
           <t>HFR License</t>
         </is>
       </c>
-      <c r="O45" s="184" t="inlineStr">
+      <c r="O46" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P45" s="20" t="inlineStr">
+      <c r="P46" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q45" s="24">
-        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R45" s="26">
-        <f>IF(P45="","",H45)</f>
-        <v/>
-      </c>
-      <c r="S45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="20" t="inlineStr">
+      <c r="Q46" s="300">
+        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R46" s="302">
+        <f>IF(P46="","",H46)</f>
+        <v/>
+      </c>
+      <c r="S46" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="21" t="inlineStr">
+      <c r="W46" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="26">
-        <f>S45+T45+W45</f>
-        <v/>
-      </c>
-      <c r="AA45" s="26">
-        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE),0)+Y45+Z45</f>
-        <v/>
-      </c>
-      <c r="AB45" s="27" t="n">
+      <c r="Y46" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="302">
+        <f>S46+T46+W46</f>
+        <v/>
+      </c>
+      <c r="AA46" s="302">
+        <f>K46+L46+M46+IFERROR(VLOOKUP(B46,RemitTable2,9,FALSE),0)+Y46+Z46</f>
+        <v/>
+      </c>
+      <c r="AB46" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC45" s="26">
-        <f>ROUND(AA45/AB45,0)</f>
-        <v/>
-      </c>
-      <c r="AD45" s="20" t="inlineStr">
+      <c r="AC46" s="302">
+        <f>ROUND(AA46/AB46,0)</f>
+        <v/>
+      </c>
+      <c r="AD46" s="296" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE45" s="184" t="inlineStr">
+      <c r="AE46" s="299" t="inlineStr">
         <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AF45" s="183" t="inlineStr">
+      <c r="AF46" s="298" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="20" t="n">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="296" t="n">
         <v>31</v>
       </c>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B47" s="296" t="inlineStr">
         <is>
           <t>CPO681</t>
         </is>
       </c>
-      <c r="C46" s="21" t="inlineStr">
+      <c r="C47" s="297" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D47" s="296" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E46" s="21" t="inlineStr">
+      <c r="E47" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F46" s="183" t="n">
+      <c r="F47" s="298" t="n">
         <v>45993</v>
       </c>
-      <c r="G46" s="184" t="n">
+      <c r="G47" s="299" t="n">
         <v>46064</v>
       </c>
-      <c r="H46" s="24" t="n">
+      <c r="H47" s="300" t="n">
         <v>26358</v>
       </c>
-      <c r="I46" s="185" t="n">
+      <c r="I47" s="301" t="n">
         <v>1460.7</v>
       </c>
-      <c r="J46" s="26" t="n">
+      <c r="J47" s="302" t="n">
         <v>38501131</v>
       </c>
-      <c r="K46" s="26" t="n">
+      <c r="K47" s="302" t="n">
         <v>38501131</v>
       </c>
-      <c r="L46" s="26" t="n">
+      <c r="L47" s="302" t="n">
         <v>12500</v>
       </c>
-      <c r="M46" s="26" t="n">
+      <c r="M47" s="302" t="n">
         <v>8000</v>
       </c>
-      <c r="N46" s="20" t="inlineStr">
+      <c r="N47" s="296" t="inlineStr">
         <is>
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="O46" s="184" t="inlineStr">
+      <c r="O47" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P46" s="20" t="inlineStr">
+      <c r="P47" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q46" s="24">
-        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R46" s="26">
-        <f>IF(P46="","",H46)</f>
-        <v/>
-      </c>
-      <c r="S46" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="20" t="inlineStr">
+      <c r="Q47" s="300">
+        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R47" s="302">
+        <f>IF(P47="","",H47)</f>
+        <v/>
+      </c>
+      <c r="S47" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W46" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="21" t="inlineStr">
+      <c r="W47" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y46" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="26">
-        <f>S46+T46+W46</f>
-        <v/>
-      </c>
-      <c r="AA46" s="26">
-        <f>K46+L46+M46+IFERROR(VLOOKUP(B46,RemitTable2,9,FALSE),0)+Y46+Z46</f>
-        <v/>
-      </c>
-      <c r="AB46" s="27" t="n">
+      <c r="Y47" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="302">
+        <f>S47+T47+W47</f>
+        <v/>
+      </c>
+      <c r="AA47" s="302">
+        <f>K47+L47+M47+IFERROR(VLOOKUP(B47,RemitTable2,9,FALSE),0)+Y47+Z47</f>
+        <v/>
+      </c>
+      <c r="AB47" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC46" s="26">
-        <f>ROUND(AA46/AB46,0)</f>
-        <v/>
-      </c>
-      <c r="AD46" s="20" t="inlineStr">
+      <c r="AC47" s="302">
+        <f>ROUND(AA47/AB47,0)</f>
+        <v/>
+      </c>
+      <c r="AD47" s="296" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE46" s="184" t="inlineStr">
+      <c r="AE47" s="299" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AF46" s="183" t="inlineStr">
+      <c r="AF47" s="298" t="inlineStr">
         <is>
           <t>2026-12-21</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="20" t="n">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="296" t="n">
         <v>32</v>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B48" s="296" t="inlineStr">
         <is>
           <t>GPO459</t>
         </is>
       </c>
-      <c r="C47" s="21" t="inlineStr">
+      <c r="C48" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D48" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E47" s="21" t="inlineStr">
+      <c r="E48" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F47" s="183" t="n">
+      <c r="F48" s="298" t="n">
         <v>46007</v>
       </c>
-      <c r="G47" s="184" t="n">
+      <c r="G48" s="299" t="n">
         <v>46043</v>
       </c>
-      <c r="H47" s="24" t="n">
+      <c r="H48" s="300" t="n">
         <v>450</v>
       </c>
-      <c r="I47" s="185" t="n">
+      <c r="I48" s="301" t="n">
         <v>1475.7</v>
       </c>
-      <c r="J47" s="26" t="n">
+      <c r="J48" s="302" t="n">
         <v>664065</v>
       </c>
-      <c r="K47" s="26" t="n">
+      <c r="K48" s="302" t="n">
         <v>664065</v>
       </c>
-      <c r="L47" s="26" t="n">
+      <c r="L48" s="302" t="n">
         <v>912</v>
       </c>
-      <c r="M47" s="26" t="n">
+      <c r="M48" s="302" t="n">
         <v>973</v>
       </c>
-      <c r="N47" s="20" t="inlineStr">
+      <c r="N48" s="296" t="inlineStr">
         <is>
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="O47" s="184" t="inlineStr">
+      <c r="O48" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P47" s="20" t="inlineStr">
+      <c r="P48" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q47" s="24">
-        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R47" s="26">
-        <f>IF(P47="","",H47)</f>
-        <v/>
-      </c>
-      <c r="S47" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="20" t="inlineStr">
+      <c r="Q48" s="300">
+        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R48" s="302">
+        <f>IF(P48="","",H48)</f>
+        <v/>
+      </c>
+      <c r="S48" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W47" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="21" t="inlineStr">
+      <c r="W48" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y47" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="26">
-        <f>S47+T47+W47</f>
-        <v/>
-      </c>
-      <c r="AA47" s="26">
-        <f>K47+L47+M47+IFERROR(VLOOKUP(B47,RemitTable2,9,FALSE),0)+Y47+Z47</f>
-        <v/>
-      </c>
-      <c r="AB47" s="27" t="n">
+      <c r="Y48" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="302">
+        <f>S48+T48+W48</f>
+        <v/>
+      </c>
+      <c r="AA48" s="302">
+        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE),0)+Y48+Z48</f>
+        <v/>
+      </c>
+      <c r="AB48" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC47" s="26">
-        <f>ROUND(AA47/AB47,0)</f>
-        <v/>
-      </c>
-      <c r="AD47" s="20" t="inlineStr">
+      <c r="AC48" s="302">
+        <f>ROUND(AA48/AB48,0)</f>
+        <v/>
+      </c>
+      <c r="AD48" s="296" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE47" s="184" t="inlineStr">
+      <c r="AE48" s="299" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF47" s="183" t="inlineStr">
+      <c r="AF48" s="298" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="20" t="n">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="296" t="n">
         <v>33</v>
       </c>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B49" s="296" t="inlineStr">
         <is>
           <t>GPO461</t>
         </is>
       </c>
-      <c r="C48" s="21" t="inlineStr">
+      <c r="C49" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D49" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E48" s="21" t="inlineStr">
+      <c r="E49" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F48" s="183" t="n">
+      <c r="F49" s="298" t="n">
         <v>46007</v>
       </c>
-      <c r="G48" s="184" t="n">
+      <c r="G49" s="299" t="n">
         <v>46043</v>
       </c>
-      <c r="H48" s="24" t="n">
+      <c r="H49" s="300" t="n">
         <v>540</v>
       </c>
-      <c r="I48" s="185" t="n">
+      <c r="I49" s="301" t="n">
         <v>1475.7</v>
       </c>
-      <c r="J48" s="26" t="n">
+      <c r="J49" s="302" t="n">
         <v>796878</v>
       </c>
-      <c r="K48" s="26" t="n">
+      <c r="K49" s="302" t="n">
         <v>796878</v>
       </c>
-      <c r="L48" s="26" t="n">
+      <c r="L49" s="302" t="n">
         <v>1095</v>
       </c>
-      <c r="M48" s="26" t="n">
+      <c r="M49" s="302" t="n">
         <v>1168</v>
       </c>
-      <c r="N48" s="20" t="inlineStr">
+      <c r="N49" s="296" t="inlineStr">
         <is>
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="O48" s="184" t="inlineStr">
+      <c r="O49" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P48" s="20" t="inlineStr">
+      <c r="P49" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q48" s="24">
-        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R48" s="26">
-        <f>IF(P48="","",H48)</f>
-        <v/>
-      </c>
-      <c r="S48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="20" t="inlineStr">
+      <c r="Q49" s="300">
+        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R49" s="302">
+        <f>IF(P49="","",H49)</f>
+        <v/>
+      </c>
+      <c r="S49" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="21" t="inlineStr">
+      <c r="W49" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="26">
-        <f>S48+T48+W48</f>
-        <v/>
-      </c>
-      <c r="AA48" s="26">
-        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE),0)+Y48+Z48</f>
-        <v/>
-      </c>
-      <c r="AB48" s="27" t="n">
+      <c r="Y49" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="302">
+        <f>S49+T49+W49</f>
+        <v/>
+      </c>
+      <c r="AA49" s="302">
+        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE),0)+Y49+Z49</f>
+        <v/>
+      </c>
+      <c r="AB49" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC48" s="26">
-        <f>ROUND(AA48/AB48,0)</f>
-        <v/>
-      </c>
-      <c r="AD48" s="20" t="inlineStr">
+      <c r="AC49" s="302">
+        <f>ROUND(AA49/AB49,0)</f>
+        <v/>
+      </c>
+      <c r="AD49" s="296" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="AE48" s="184" t="inlineStr">
+      <c r="AE49" s="299" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="AF48" s="183" t="inlineStr">
+      <c r="AF49" s="298" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="20" t="n">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="296" t="n">
         <v>34</v>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B50" s="296" t="inlineStr">
         <is>
           <t>CPO685</t>
         </is>
       </c>
-      <c r="C49" s="21" t="inlineStr">
+      <c r="C50" s="297" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D50" s="296" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E49" s="21" t="inlineStr">
+      <c r="E50" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F49" s="183" t="n">
+      <c r="F50" s="298" t="n">
         <v>46010</v>
       </c>
-      <c r="G49" s="184" t="n">
+      <c r="G50" s="299" t="n">
         <v>46080</v>
       </c>
-      <c r="H49" s="24" t="n">
+      <c r="H50" s="300" t="n">
         <v>136516</v>
       </c>
-      <c r="I49" s="185" t="n">
+      <c r="I50" s="301" t="n">
         <v>1441.6</v>
       </c>
-      <c r="J49" s="26" t="n">
+      <c r="J50" s="302" t="n">
         <v>196801466</v>
       </c>
-      <c r="K49" s="26" t="n">
+      <c r="K50" s="302" t="n">
         <v>196801466</v>
       </c>
-      <c r="L49" s="26" t="n">
+      <c r="L50" s="302" t="n">
         <v>12001</v>
       </c>
-      <c r="M49" s="26" t="n">
+      <c r="M50" s="302" t="n">
         <v>7681</v>
       </c>
-      <c r="N49" s="20" t="inlineStr">
+      <c r="N50" s="296" t="inlineStr">
         <is>
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="O49" s="184" t="inlineStr">
+      <c r="O50" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P49" s="20" t="inlineStr">
+      <c r="P50" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q49" s="24">
-        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R49" s="26">
-        <f>IF(P49="","",H49)</f>
-        <v/>
-      </c>
-      <c r="S49" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="20" t="inlineStr">
+      <c r="Q50" s="300">
+        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R50" s="302">
+        <f>IF(P50="","",H50)</f>
+        <v/>
+      </c>
+      <c r="S50" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W49" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="21" t="inlineStr">
+      <c r="W50" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y49" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="26">
-        <f>S49+T49+W49</f>
-        <v/>
-      </c>
-      <c r="AA49" s="26">
-        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE),0)+Y49+Z49</f>
-        <v/>
-      </c>
-      <c r="AB49" s="27" t="n">
+      <c r="Y50" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="302">
+        <f>S50+T50+W50</f>
+        <v/>
+      </c>
+      <c r="AA50" s="302">
+        <f>K50+L50+M50+IFERROR(VLOOKUP(B50,RemitTable2,9,FALSE),0)+Y50+Z50</f>
+        <v/>
+      </c>
+      <c r="AB50" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC49" s="26">
-        <f>ROUND(AA49/AB49,0)</f>
-        <v/>
-      </c>
-      <c r="AD49" s="20" t="inlineStr">
+      <c r="AC50" s="302">
+        <f>ROUND(AA50/AB50,0)</f>
+        <v/>
+      </c>
+      <c r="AD50" s="296" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE49" s="184" t="inlineStr">
+      <c r="AE50" s="299" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF49" s="183" t="inlineStr">
+      <c r="AF50" s="298" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="20" t="n">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="296" t="n">
         <v>35</v>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B51" s="296" t="inlineStr">
         <is>
           <t>GPO465</t>
         </is>
       </c>
-      <c r="C50" s="21" t="inlineStr">
+      <c r="C51" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D50" s="20" t="inlineStr">
+      <c r="D51" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E50" s="21" t="inlineStr">
+      <c r="E51" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F50" s="183" t="n">
+      <c r="F51" s="298" t="n">
         <v>46015</v>
       </c>
-      <c r="G50" s="184" t="inlineStr">
+      <c r="G51" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H50" s="24" t="n">
+      <c r="H51" s="300" t="n">
         <v>76054</v>
       </c>
-      <c r="I50" s="185">
+      <c r="I51" s="301">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
-      <c r="J50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="26">
+      <c r="J51" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="302">
         <f>IFERROR(ROUND(H50*I50,0),0)</f>
         <v/>
       </c>
-      <c r="L50" s="26">
+      <c r="L51" s="302">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
-      <c r="M50" s="26">
+      <c r="M51" s="302">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N50" s="20" t="inlineStr">
+      <c r="N51" s="296" t="inlineStr">
         <is>
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="O50" s="184" t="inlineStr">
+      <c r="O51" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P50" s="20" t="inlineStr">
+      <c r="P51" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q50" s="24">
-        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R50" s="26">
-        <f>IF(P50="","",H50)</f>
-        <v/>
-      </c>
-      <c r="S50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="20" t="inlineStr">
+      <c r="Q51" s="300">
+        <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R51" s="302">
+        <f>IF(P51="","",H51)</f>
+        <v/>
+      </c>
+      <c r="S51" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="21" t="inlineStr">
+      <c r="W51" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y50" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="26">
-        <f>S50+T50+W50</f>
-        <v/>
-      </c>
-      <c r="AA50" s="26">
-        <f>K50+L50+M50+IFERROR(VLOOKUP(B50,RemitTable2,9,FALSE),0)+Y50+Z50</f>
-        <v/>
-      </c>
-      <c r="AB50" s="27" t="n">
+      <c r="Y51" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="302">
+        <f>S51+T51+W51</f>
+        <v/>
+      </c>
+      <c r="AA51" s="302">
+        <f>K51+L51+M51+IFERROR(VLOOKUP(B51,RemitTable2,9,FALSE),0)+Y51+Z51</f>
+        <v/>
+      </c>
+      <c r="AB51" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC50" s="26">
-        <f>ROUND(AA50/AB50,0)</f>
-        <v/>
-      </c>
-      <c r="AD50" s="20" t="inlineStr">
+      <c r="AC51" s="302">
+        <f>ROUND(AA51/AB51,0)</f>
+        <v/>
+      </c>
+      <c r="AD51" s="296" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE50" s="184" t="inlineStr">
+      <c r="AE51" s="299" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF50" s="183" t="inlineStr">
+      <c r="AF51" s="298" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="20" t="n">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="296" t="n">
         <v>36</v>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B52" s="296" t="inlineStr">
         <is>
           <t>CPO686</t>
         </is>
       </c>
-      <c r="C51" s="21" t="inlineStr">
+      <c r="C52" s="297" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D52" s="296" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E51" s="21" t="inlineStr">
+      <c r="E52" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F51" s="183" t="n">
+      <c r="F52" s="298" t="n">
         <v>46029</v>
       </c>
-      <c r="G51" s="184" t="n">
+      <c r="G52" s="299" t="n">
         <v>46072</v>
       </c>
-      <c r="H51" s="24" t="n">
+      <c r="H52" s="300" t="n">
         <v>14793</v>
       </c>
-      <c r="I51" s="185" t="n">
+      <c r="I52" s="301" t="n">
         <v>1451.7</v>
       </c>
-      <c r="J51" s="26" t="n">
+      <c r="J52" s="302" t="n">
         <v>21474998</v>
       </c>
-      <c r="K51" s="26" t="n">
+      <c r="K52" s="302" t="n">
         <v>21474998</v>
       </c>
-      <c r="L51" s="26" t="n">
+      <c r="L52" s="302" t="n">
         <v>8435</v>
       </c>
-      <c r="M51" s="26" t="n">
+      <c r="M52" s="302" t="n">
         <v>6748</v>
       </c>
-      <c r="N51" s="20" t="inlineStr">
+      <c r="N52" s="296" t="inlineStr">
         <is>
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="O51" s="184" t="inlineStr">
+      <c r="O52" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P51" s="20" t="inlineStr">
+      <c r="P52" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q51" s="24">
-        <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R51" s="26">
-        <f>IF(P51="","",H51)</f>
-        <v/>
-      </c>
-      <c r="S51" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="20" t="inlineStr">
+      <c r="Q52" s="300">
+        <f>IF(P52="","",IFERROR(VLOOKUP(O52,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R52" s="302">
+        <f>IF(P52="","",H52)</f>
+        <v/>
+      </c>
+      <c r="S52" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W51" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="21" t="inlineStr">
+      <c r="W52" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y51" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="26">
-        <f>S51+T51+W51</f>
-        <v/>
-      </c>
-      <c r="AA51" s="26">
-        <f>K51+L51+M51+IFERROR(VLOOKUP(B51,RemitTable2,9,FALSE),0)+Y51+Z51</f>
-        <v/>
-      </c>
-      <c r="AB51" s="27" t="n">
+      <c r="Y52" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="302">
+        <f>S52+T52+W52</f>
+        <v/>
+      </c>
+      <c r="AA52" s="302">
+        <f>K52+L52+M52+IFERROR(VLOOKUP(B52,RemitTable2,9,FALSE),0)+Y52+Z52</f>
+        <v/>
+      </c>
+      <c r="AB52" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC51" s="26">
-        <f>ROUND(AA51/AB51,0)</f>
-        <v/>
-      </c>
-      <c r="AD51" s="20" t="inlineStr">
+      <c r="AC52" s="302">
+        <f>ROUND(AA52/AB52,0)</f>
+        <v/>
+      </c>
+      <c r="AD52" s="296" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE51" s="184" t="inlineStr">
+      <c r="AE52" s="299" t="inlineStr">
         <is>
           <t>2026-01-30</t>
         </is>
       </c>
-      <c r="AF51" s="183" t="inlineStr">
+      <c r="AF52" s="298" t="inlineStr">
         <is>
           <t>2027-01-29</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="20" t="n">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="296" t="n">
         <v>37</v>
       </c>
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B53" s="296" t="inlineStr">
         <is>
           <t>CPO687</t>
         </is>
       </c>
-      <c r="C52" s="21" t="inlineStr">
+      <c r="C53" s="297" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D52" s="20" t="inlineStr">
+      <c r="D53" s="296" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E52" s="21" t="inlineStr">
+      <c r="E53" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F52" s="183" t="n">
+      <c r="F53" s="298" t="n">
         <v>46029</v>
       </c>
-      <c r="G52" s="184" t="inlineStr">
+      <c r="G53" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="24" t="n">
+      <c r="H53" s="300" t="n">
         <v>26656</v>
       </c>
-      <c r="I52" s="185">
+      <c r="I53" s="301">
         <f>IFERROR(VLOOKUP(B52,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
-      <c r="J52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="26">
+      <c r="J53" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="302">
         <f>IFERROR(ROUND(H52*I52,0),0)</f>
         <v/>
       </c>
-      <c r="L52" s="26">
+      <c r="L53" s="302">
         <f>IFERROR(VLOOKUP(B52,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
-      <c r="M52" s="26">
+      <c r="M53" s="302">
         <f>IFERROR(VLOOKUP(B52,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N52" s="20" t="inlineStr">
+      <c r="N53" s="296" t="inlineStr">
         <is>
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="O52" s="184" t="inlineStr">
+      <c r="O53" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P52" s="20" t="inlineStr">
+      <c r="P53" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q52" s="24">
-        <f>IF(P52="","",IFERROR(VLOOKUP(O52,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R52" s="26">
-        <f>IF(P52="","",H52)</f>
-        <v/>
-      </c>
-      <c r="S52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="20" t="inlineStr">
+      <c r="Q53" s="300">
+        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R53" s="302">
+        <f>IF(P53="","",H53)</f>
+        <v/>
+      </c>
+      <c r="S53" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" s="21" t="inlineStr">
+      <c r="W53" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="26">
-        <f>S52+T52+W52</f>
-        <v/>
-      </c>
-      <c r="AA52" s="26">
-        <f>K52+L52+M52+IFERROR(VLOOKUP(B52,RemitTable2,9,FALSE),0)+Y52+Z52</f>
-        <v/>
-      </c>
-      <c r="AB52" s="27" t="n">
+      <c r="Y53" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="302">
+        <f>S53+T53+W53</f>
+        <v/>
+      </c>
+      <c r="AA53" s="302">
+        <f>K53+L53+M53+IFERROR(VLOOKUP(B53,RemitTable2,9,FALSE),0)+Y53+Z53</f>
+        <v/>
+      </c>
+      <c r="AB53" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC52" s="26">
-        <f>ROUND(AA52/AB52,0)</f>
-        <v/>
-      </c>
-      <c r="AD52" s="20" t="inlineStr">
+      <c r="AC53" s="302">
+        <f>ROUND(AA53/AB53,0)</f>
+        <v/>
+      </c>
+      <c r="AD53" s="296" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE52" s="184" t="inlineStr">
+      <c r="AE53" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF52" s="183" t="inlineStr">
+      <c r="AF53" s="298" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="20" t="n">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="296" t="n">
         <v>38</v>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B54" s="296" t="inlineStr">
         <is>
           <t>GPO462</t>
         </is>
       </c>
-      <c r="C53" s="21" t="inlineStr">
+      <c r="C54" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="D54" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E54" s="297" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F53" s="183" t="n">
+      <c r="F54" s="298" t="n">
         <v>46042</v>
       </c>
-      <c r="G53" s="184" t="n">
+      <c r="G54" s="299" t="n">
         <v>46057</v>
       </c>
-      <c r="H53" s="24" t="n">
+      <c r="H54" s="300" t="n">
         <v>1440</v>
       </c>
-      <c r="I53" s="185" t="n">
+      <c r="I54" s="301" t="n">
         <v>1453.6</v>
       </c>
-      <c r="J53" s="26" t="n">
+      <c r="J54" s="302" t="n">
         <v>2093184</v>
       </c>
-      <c r="K53" s="26" t="n">
+      <c r="K54" s="302" t="n">
         <v>2093184</v>
       </c>
-      <c r="L53" s="26" t="n">
+      <c r="L54" s="302" t="n">
         <v>1241</v>
       </c>
-      <c r="M53" s="26" t="n">
+      <c r="M54" s="302" t="n">
         <v>993</v>
       </c>
-      <c r="N53" s="20" t="inlineStr">
+      <c r="N54" s="296" t="inlineStr">
         <is>
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="O53" s="184" t="inlineStr">
+      <c r="O54" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P53" s="20" t="inlineStr">
+      <c r="P54" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q53" s="24">
-        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R53" s="26">
-        <f>IF(P53="","",H53)</f>
-        <v/>
-      </c>
-      <c r="S53" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="20" t="inlineStr">
+      <c r="Q54" s="300">
+        <f>IF(P54="","",IFERROR(VLOOKUP(O54,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R54" s="302">
+        <f>IF(P54="","",H54)</f>
+        <v/>
+      </c>
+      <c r="S54" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W53" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="21" t="inlineStr">
+      <c r="W54" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y53" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="26">
-        <f>S53+T53+W53</f>
-        <v/>
-      </c>
-      <c r="AA53" s="26">
-        <f>K53+L53+M53+IFERROR(VLOOKUP(B53,RemitTable2,9,FALSE),0)+Y53+Z53</f>
-        <v/>
-      </c>
-      <c r="AB53" s="27" t="n">
+      <c r="Y54" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="302">
+        <f>S54+T54+W54</f>
+        <v/>
+      </c>
+      <c r="AA54" s="302">
+        <f>K54+L54+M54+IFERROR(VLOOKUP(B54,RemitTable2,9,FALSE),0)+Y54+Z54</f>
+        <v/>
+      </c>
+      <c r="AB54" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC53" s="26">
-        <f>ROUND(AA53/AB53,0)</f>
-        <v/>
-      </c>
-      <c r="AD53" s="20" t="inlineStr">
+      <c r="AC54" s="302">
+        <f>ROUND(AA54/AB54,0)</f>
+        <v/>
+      </c>
+      <c r="AD54" s="296" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE53" s="184" t="inlineStr">
+      <c r="AE54" s="299" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF53" s="183" t="inlineStr">
+      <c r="AF54" s="298" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="20" t="n">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="296" t="n">
         <v>39</v>
       </c>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B55" s="296" t="inlineStr">
         <is>
           <t>GPO463</t>
         </is>
       </c>
-      <c r="C54" s="21" t="inlineStr">
+      <c r="C55" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D55" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
+      <c r="E55" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F54" s="183" t="n">
+      <c r="F55" s="298" t="n">
         <v>46042</v>
       </c>
-      <c r="G54" s="184" t="n">
+      <c r="G55" s="299" t="n">
         <v>46057</v>
       </c>
-      <c r="H54" s="24" t="n">
+      <c r="H55" s="300" t="n">
         <v>4489</v>
       </c>
-      <c r="I54" s="185" t="n">
+      <c r="I55" s="301" t="n">
         <v>1453.6</v>
       </c>
-      <c r="J54" s="26" t="n">
+      <c r="J55" s="302" t="n">
         <v>6525210</v>
       </c>
-      <c r="K54" s="26" t="n">
+      <c r="K55" s="302" t="n">
         <v>6525210</v>
       </c>
-      <c r="L54" s="26" t="n">
+      <c r="L55" s="302" t="n">
         <v>3870</v>
       </c>
-      <c r="M54" s="26" t="n">
+      <c r="M55" s="302" t="n">
         <v>3096</v>
       </c>
-      <c r="N54" s="20" t="inlineStr">
+      <c r="N55" s="296" t="inlineStr">
         <is>
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="O54" s="184" t="inlineStr">
+      <c r="O55" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P54" s="20" t="inlineStr">
+      <c r="P55" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q54" s="24">
-        <f>IF(P54="","",IFERROR(VLOOKUP(O54,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R54" s="26">
-        <f>IF(P54="","",H54)</f>
-        <v/>
-      </c>
-      <c r="S54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="20" t="inlineStr">
+      <c r="Q55" s="300">
+        <f>IF(P55="","",IFERROR(VLOOKUP(O55,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R55" s="302">
+        <f>IF(P55="","",H55)</f>
+        <v/>
+      </c>
+      <c r="S55" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" s="21" t="inlineStr">
+      <c r="W55" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y54" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="26">
-        <f>S54+T54+W54</f>
-        <v/>
-      </c>
-      <c r="AA54" s="26">
-        <f>K54+L54+M54+IFERROR(VLOOKUP(B54,RemitTable2,9,FALSE),0)+Y54+Z54</f>
-        <v/>
-      </c>
-      <c r="AB54" s="27" t="n">
+      <c r="Y55" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="302">
+        <f>S55+T55+W55</f>
+        <v/>
+      </c>
+      <c r="AA55" s="302">
+        <f>K55+L55+M55+IFERROR(VLOOKUP(B55,RemitTable2,9,FALSE),0)+Y55+Z55</f>
+        <v/>
+      </c>
+      <c r="AB55" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC54" s="26">
-        <f>ROUND(AA54/AB54,0)</f>
-        <v/>
-      </c>
-      <c r="AD54" s="20" t="inlineStr">
+      <c r="AC55" s="302">
+        <f>ROUND(AA55/AB55,0)</f>
+        <v/>
+      </c>
+      <c r="AD55" s="296" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE54" s="184" t="inlineStr">
+      <c r="AE55" s="299" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF54" s="183" t="inlineStr">
+      <c r="AF55" s="298" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="20" t="n">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="296" t="n">
         <v>40</v>
       </c>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B56" s="296" t="inlineStr">
         <is>
           <t>GPO464</t>
         </is>
       </c>
-      <c r="C55" s="21" t="inlineStr">
+      <c r="C56" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D55" s="20" t="inlineStr">
+      <c r="D56" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E55" s="21" t="inlineStr">
+      <c r="E56" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F55" s="183" t="n">
+      <c r="F56" s="298" t="n">
         <v>46042</v>
       </c>
-      <c r="G55" s="184" t="n">
+      <c r="G56" s="299" t="n">
         <v>46057</v>
       </c>
-      <c r="H55" s="24" t="n">
+      <c r="H56" s="300" t="n">
         <v>5670.57</v>
       </c>
-      <c r="I55" s="185" t="n">
+      <c r="I56" s="301" t="n">
         <v>1453.6</v>
       </c>
-      <c r="J55" s="26" t="n">
+      <c r="J56" s="302" t="n">
         <v>8242741</v>
       </c>
-      <c r="K55" s="26" t="n">
+      <c r="K56" s="302" t="n">
         <v>8242741</v>
       </c>
-      <c r="L55" s="26" t="n">
+      <c r="L56" s="302" t="n">
         <v>4889</v>
       </c>
-      <c r="M55" s="26" t="n">
+      <c r="M56" s="302" t="n">
         <v>3911</v>
       </c>
-      <c r="N55" s="20" t="inlineStr">
+      <c r="N56" s="296" t="inlineStr">
         <is>
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="O55" s="184" t="inlineStr">
+      <c r="O56" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P55" s="20" t="inlineStr">
+      <c r="P56" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q55" s="24">
-        <f>IF(P55="","",IFERROR(VLOOKUP(O55,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R55" s="26">
-        <f>IF(P55="","",H55)</f>
-        <v/>
-      </c>
-      <c r="S55" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="20" t="inlineStr">
+      <c r="Q56" s="300">
+        <f>IF(P56="","",IFERROR(VLOOKUP(O56,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R56" s="302">
+        <f>IF(P56="","",H56)</f>
+        <v/>
+      </c>
+      <c r="S56" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W55" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" s="21" t="inlineStr">
+      <c r="W56" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y55" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="26">
-        <f>S55+T55+W55</f>
-        <v/>
-      </c>
-      <c r="AA55" s="26">
-        <f>K55+L55+M55+IFERROR(VLOOKUP(B55,RemitTable2,9,FALSE),0)+Y55+Z55</f>
-        <v/>
-      </c>
-      <c r="AB55" s="27" t="n">
+      <c r="Y56" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="302">
+        <f>S56+T56+W56</f>
+        <v/>
+      </c>
+      <c r="AA56" s="302">
+        <f>K56+L56+M56+IFERROR(VLOOKUP(B56,RemitTable2,9,FALSE),0)+Y56+Z56</f>
+        <v/>
+      </c>
+      <c r="AB56" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC55" s="26">
-        <f>ROUND(AA55/AB55,0)</f>
-        <v/>
-      </c>
-      <c r="AD55" s="20" t="inlineStr">
+      <c r="AC56" s="302">
+        <f>ROUND(AA56/AB56,0)</f>
+        <v/>
+      </c>
+      <c r="AD56" s="296" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE55" s="184" t="inlineStr">
+      <c r="AE56" s="299" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF55" s="183" t="inlineStr">
+      <c r="AF56" s="298" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="20" t="n">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="296" t="n">
         <v>41</v>
       </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B57" s="296" t="inlineStr">
         <is>
           <t>CPO691</t>
         </is>
       </c>
-      <c r="C56" s="21" t="inlineStr">
+      <c r="C57" s="297" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D56" s="20" t="inlineStr">
+      <c r="D57" s="296" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E56" s="21" t="inlineStr">
+      <c r="E57" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F56" s="183" t="n">
+      <c r="F57" s="298" t="n">
         <v>46057</v>
       </c>
-      <c r="G56" s="184" t="n">
+      <c r="G57" s="299" t="n">
         <v>46113</v>
       </c>
-      <c r="H56" s="24" t="n">
+      <c r="H57" s="300" t="n">
         <v>24614</v>
       </c>
-      <c r="I56" s="185" t="n">
+      <c r="I57" s="301" t="n">
         <v>1505.7</v>
       </c>
-      <c r="J56" s="26" t="n">
+      <c r="J57" s="302" t="n">
         <v>37061300</v>
       </c>
-      <c r="K56" s="26" t="n">
+      <c r="K57" s="302" t="n">
         <v>37061300</v>
       </c>
-      <c r="L56" s="26" t="n">
+      <c r="L57" s="302" t="n">
         <v>8956</v>
       </c>
-      <c r="M56" s="26" t="n">
+      <c r="M57" s="302" t="n">
         <v>5732</v>
       </c>
-      <c r="N56" s="20" t="inlineStr">
+      <c r="N57" s="296" t="inlineStr">
         <is>
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="O56" s="184" t="inlineStr">
+      <c r="O57" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P56" s="20" t="inlineStr">
+      <c r="P57" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q56" s="24">
-        <f>IF(P56="","",IFERROR(VLOOKUP(O56,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R56" s="26">
-        <f>IF(P56="","",H56)</f>
-        <v/>
-      </c>
-      <c r="S56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="20" t="inlineStr">
+      <c r="Q57" s="300">
+        <f>IF(P57="","",IFERROR(VLOOKUP(O57,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R57" s="302">
+        <f>IF(P57="","",H57)</f>
+        <v/>
+      </c>
+      <c r="S57" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" s="21" t="inlineStr">
+      <c r="W57" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y56" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="26">
-        <f>S56+T56+W56</f>
-        <v/>
-      </c>
-      <c r="AA56" s="26">
-        <f>K56+L56+M56+IFERROR(VLOOKUP(B56,RemitTable2,9,FALSE),0)+Y56+Z56</f>
-        <v/>
-      </c>
-      <c r="AB56" s="27" t="n">
+      <c r="Y57" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="302">
+        <f>S57+T57+W57</f>
+        <v/>
+      </c>
+      <c r="AA57" s="302">
+        <f>K57+L57+M57+IFERROR(VLOOKUP(B57,RemitTable2,9,FALSE),0)+Y57+Z57</f>
+        <v/>
+      </c>
+      <c r="AB57" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC56" s="26">
-        <f>ROUND(AA56/AB56,0)</f>
-        <v/>
-      </c>
-      <c r="AD56" s="20" t="inlineStr">
+      <c r="AC57" s="302">
+        <f>ROUND(AA57/AB57,0)</f>
+        <v/>
+      </c>
+      <c r="AD57" s="296" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE56" s="184" t="inlineStr">
+      <c r="AE57" s="299" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AF56" s="183" t="inlineStr">
+      <c r="AF57" s="298" t="inlineStr">
         <is>
           <t>2027-02-28</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="20" t="n">
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="296" t="n">
         <v>42</v>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B58" s="296" t="inlineStr">
         <is>
           <t>GPO469</t>
         </is>
       </c>
-      <c r="C57" s="21" t="inlineStr">
+      <c r="C58" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D57" s="20" t="inlineStr">
+      <c r="D58" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E57" s="21" t="inlineStr">
+      <c r="E58" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F57" s="183" t="n">
+      <c r="F58" s="298" t="n">
         <v>46060</v>
       </c>
-      <c r="G57" s="184" t="n">
+      <c r="G58" s="299" t="n">
         <v>46113</v>
       </c>
-      <c r="H57" s="24" t="n">
+      <c r="H58" s="300" t="n">
         <v>3993.05</v>
       </c>
-      <c r="I57" s="185" t="n">
+      <c r="I58" s="301" t="n">
         <v>1506.4</v>
       </c>
-      <c r="J57" s="26" t="n">
+      <c r="J58" s="302" t="n">
         <v>6015131</v>
       </c>
-      <c r="K57" s="26" t="n">
+      <c r="K58" s="302" t="n">
         <v>6015131</v>
       </c>
-      <c r="L57" s="26" t="n">
+      <c r="L58" s="302" t="n">
         <v>6093</v>
       </c>
-      <c r="M57" s="26" t="n">
+      <c r="M58" s="302" t="n">
         <v>4875</v>
       </c>
-      <c r="N57" s="20" t="inlineStr">
+      <c r="N58" s="296" t="inlineStr">
         <is>
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="O57" s="184" t="inlineStr">
+      <c r="O58" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P57" s="20" t="inlineStr">
+      <c r="P58" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q57" s="24">
-        <f>IF(P57="","",IFERROR(VLOOKUP(O57,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R57" s="26">
-        <f>IF(P57="","",H57)</f>
-        <v/>
-      </c>
-      <c r="S57" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="20" t="inlineStr">
+      <c r="Q58" s="300">
+        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R58" s="302">
+        <f>IF(P58="","",H58)</f>
+        <v/>
+      </c>
+      <c r="S58" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W57" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" s="21" t="inlineStr">
+      <c r="W58" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y57" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="26">
-        <f>S57+T57+W57</f>
-        <v/>
-      </c>
-      <c r="AA57" s="26">
-        <f>K57+L57+M57+IFERROR(VLOOKUP(B57,RemitTable2,9,FALSE),0)+Y57+Z57</f>
-        <v/>
-      </c>
-      <c r="AB57" s="27" t="n">
+      <c r="Y58" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="302">
+        <f>S58+T58+W58</f>
+        <v/>
+      </c>
+      <c r="AA58" s="302">
+        <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
+        <v/>
+      </c>
+      <c r="AB58" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC57" s="26">
-        <f>ROUND(AA57/AB57,0)</f>
-        <v/>
-      </c>
-      <c r="AD57" s="20" t="inlineStr">
+      <c r="AC58" s="302">
+        <f>ROUND(AA58/AB58,0)</f>
+        <v/>
+      </c>
+      <c r="AD58" s="296" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE57" s="184" t="inlineStr">
+      <c r="AE58" s="299" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="AF57" s="183" t="inlineStr">
+      <c r="AF58" s="298" t="inlineStr">
         <is>
           <t>2027-02-22</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="20" t="n">
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="296" t="n">
         <v>43</v>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B59" s="296" t="inlineStr">
         <is>
           <t>GPO470</t>
         </is>
       </c>
-      <c r="C58" s="21" t="inlineStr">
+      <c r="C59" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D58" s="20" t="inlineStr">
+      <c r="D59" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E58" s="21" t="inlineStr">
+      <c r="E59" s="297" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F58" s="183" t="n">
+      <c r="F59" s="298" t="n">
         <v>46080</v>
       </c>
-      <c r="G58" s="184" t="n">
+      <c r="G59" s="299" t="n">
         <v>46113</v>
       </c>
-      <c r="H58" s="24" t="n">
+      <c r="H59" s="300" t="n">
         <v>360</v>
       </c>
-      <c r="I58" s="185" t="n">
+      <c r="I59" s="301" t="n">
         <v>1506.4</v>
       </c>
-      <c r="J58" s="26" t="n">
+      <c r="J59" s="302" t="n">
         <v>542304</v>
       </c>
-      <c r="K58" s="26" t="n">
+      <c r="K59" s="302" t="n">
         <v>542304</v>
       </c>
-      <c r="L58" s="26" t="n">
+      <c r="L59" s="302" t="n">
         <v>549</v>
       </c>
-      <c r="M58" s="26" t="n">
+      <c r="M59" s="302" t="n">
         <v>439</v>
       </c>
-      <c r="N58" s="20" t="inlineStr">
+      <c r="N59" s="296" t="inlineStr">
         <is>
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="O58" s="184" t="inlineStr">
+      <c r="O59" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P58" s="20" t="inlineStr">
+      <c r="P59" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q58" s="24">
-        <f>IF(P58="","",IFERROR(VLOOKUP(O58,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R58" s="26">
-        <f>IF(P58="","",H58)</f>
-        <v/>
-      </c>
-      <c r="S58" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="20" t="inlineStr">
+      <c r="Q59" s="300">
+        <f>IF(P59="","",IFERROR(VLOOKUP(O59,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R59" s="302">
+        <f>IF(P59="","",H59)</f>
+        <v/>
+      </c>
+      <c r="S59" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W58" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" s="21" t="inlineStr">
+      <c r="W59" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y58" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="26">
-        <f>S58+T58+W58</f>
-        <v/>
-      </c>
-      <c r="AA58" s="26">
-        <f>K58+L58+M58+IFERROR(VLOOKUP(B58,RemitTable2,9,FALSE),0)+Y58+Z58</f>
-        <v/>
-      </c>
-      <c r="AB58" s="27" t="n">
+      <c r="Y59" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="302">
+        <f>S59+T59+W59</f>
+        <v/>
+      </c>
+      <c r="AA59" s="302">
+        <f>K59+L59+M59+IFERROR(VLOOKUP(B59,RemitTable2,9,FALSE),0)+Y59+Z59</f>
+        <v/>
+      </c>
+      <c r="AB59" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC58" s="26">
-        <f>ROUND(AA58/AB58,0)</f>
-        <v/>
-      </c>
-      <c r="AD58" s="20" t="inlineStr">
+      <c r="AC59" s="302">
+        <f>ROUND(AA59/AB59,0)</f>
+        <v/>
+      </c>
+      <c r="AD59" s="296" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE58" s="184" t="inlineStr">
+      <c r="AE59" s="299" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AF58" s="183" t="inlineStr">
+      <c r="AF59" s="298" t="inlineStr">
         <is>
           <t>2027-02-28</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="20" t="n">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="296" t="n">
         <v>44</v>
       </c>
-      <c r="B59" s="20" t="inlineStr">
+      <c r="B60" s="296" t="inlineStr">
         <is>
           <t>GPO471</t>
         </is>
       </c>
-      <c r="C59" s="21" t="inlineStr">
+      <c r="C60" s="297" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D59" s="20" t="inlineStr">
+      <c r="D60" s="296" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E59" s="21" t="inlineStr">
+      <c r="E60" s="297" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F59" s="183" t="n">
+      <c r="F60" s="298" t="n">
         <v>46088</v>
       </c>
-      <c r="G59" s="184" t="n">
+      <c r="G60" s="299" t="n">
         <v>46113</v>
       </c>
-      <c r="H59" s="24" t="n">
+      <c r="H60" s="300" t="n">
         <v>500</v>
       </c>
-      <c r="I59" s="185" t="n">
+      <c r="I60" s="301" t="n">
         <v>1506.4</v>
       </c>
-      <c r="J59" s="26" t="n">
+      <c r="J60" s="302" t="n">
         <v>753200</v>
       </c>
-      <c r="K59" s="26" t="n">
+      <c r="K60" s="302" t="n">
         <v>753200</v>
       </c>
-      <c r="L59" s="26" t="n">
+      <c r="L60" s="302" t="n">
         <v>763</v>
       </c>
-      <c r="M59" s="26" t="n">
+      <c r="M60" s="302" t="n">
         <v>610</v>
       </c>
-      <c r="N59" s="20" t="inlineStr">
+      <c r="N60" s="296" t="inlineStr">
         <is>
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="O59" s="184" t="inlineStr">
+      <c r="O60" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P59" s="20" t="inlineStr">
+      <c r="P60" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q59" s="24">
-        <f>IF(P59="","",IFERROR(VLOOKUP(O59,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R59" s="26">
-        <f>IF(P59="","",H59)</f>
-        <v/>
-      </c>
-      <c r="S59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="20" t="inlineStr">
+      <c r="Q60" s="300">
+        <f>IF(P60="","",IFERROR(VLOOKUP(O60,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R60" s="302">
+        <f>IF(P60="","",H60)</f>
+        <v/>
+      </c>
+      <c r="S60" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" s="21" t="inlineStr">
+      <c r="W60" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="26">
-        <f>S59+T59+W59</f>
-        <v/>
-      </c>
-      <c r="AA59" s="26">
-        <f>K59+L59+M59+IFERROR(VLOOKUP(B59,RemitTable2,9,FALSE),0)+Y59+Z59</f>
-        <v/>
-      </c>
-      <c r="AB59" s="27" t="n">
+      <c r="Y60" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="302">
+        <f>S60+T60+W60</f>
+        <v/>
+      </c>
+      <c r="AA60" s="302">
+        <f>K60+L60+M60+IFERROR(VLOOKUP(B60,RemitTable2,9,FALSE),0)+Y60+Z60</f>
+        <v/>
+      </c>
+      <c r="AB60" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC59" s="26">
-        <f>ROUND(AA59/AB59,0)</f>
-        <v/>
-      </c>
-      <c r="AD59" s="20" t="inlineStr">
+      <c r="AC60" s="302">
+        <f>ROUND(AA60/AB60,0)</f>
+        <v/>
+      </c>
+      <c r="AD60" s="296" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE59" s="184" t="inlineStr">
+      <c r="AE60" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF59" s="183" t="inlineStr">
+      <c r="AF60" s="298" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="20" t="n">
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="296" t="n">
         <v>45</v>
       </c>
-      <c r="B60" s="20" t="inlineStr">
+      <c r="B61" s="296" t="inlineStr">
         <is>
           <t>CPO694</t>
         </is>
       </c>
-      <c r="C60" s="21" t="inlineStr">
+      <c r="C61" s="297" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D60" s="20" t="inlineStr">
+      <c r="D61" s="296" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E60" s="21" t="inlineStr">
+      <c r="E61" s="297" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F60" s="183" t="n">
+      <c r="F61" s="298" t="n">
         <v>46109</v>
       </c>
-      <c r="G60" s="184" t="n">
+      <c r="G61" s="299" t="n">
         <v>46146</v>
       </c>
-      <c r="H60" s="24" t="n">
+      <c r="H61" s="300" t="n">
         <v>17404</v>
       </c>
-      <c r="I60" s="185" t="n">
+      <c r="I61" s="301" t="n">
         <v>1474.9</v>
       </c>
-      <c r="J60" s="26" t="n">
+      <c r="J61" s="302" t="n">
         <v>25669160</v>
       </c>
-      <c r="K60" s="26" t="n">
+      <c r="K61" s="302" t="n">
         <v>25669160</v>
       </c>
-      <c r="L60" s="26" t="n">
+      <c r="L61" s="302" t="n">
         <v>10147</v>
       </c>
-      <c r="M60" s="26" t="n">
+      <c r="M61" s="302" t="n">
         <v>6494</v>
       </c>
-      <c r="N60" s="20" t="inlineStr">
+      <c r="N61" s="296" t="inlineStr">
         <is>
           <t>EW (CGV 동백 외)</t>
         </is>
       </c>
-      <c r="O60" s="184" t="inlineStr">
+      <c r="O61" s="299" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P60" s="20" t="inlineStr">
+      <c r="P61" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q60" s="24">
-        <f>IF(P60="","",IFERROR(VLOOKUP(O60,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R60" s="26">
-        <f>IF(P60="","",H60)</f>
-        <v/>
-      </c>
-      <c r="S60" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="20" t="inlineStr">
+      <c r="Q61" s="300">
+        <f>IF(P61="","",IFERROR(VLOOKUP(O61,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R61" s="302">
+        <f>IF(P61="","",H61)</f>
+        <v/>
+      </c>
+      <c r="S61" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="298" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W60" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="21" t="inlineStr">
+      <c r="W61" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y60" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="26">
-        <f>S60+T60+W60</f>
-        <v/>
-      </c>
-      <c r="AA60" s="26">
-        <f>K60+L60+M60+IFERROR(VLOOKUP(B60,RemitTable2,9,FALSE),0)+Y60+Z60</f>
-        <v/>
-      </c>
-      <c r="AB60" s="27" t="n">
+      <c r="Y61" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="302">
+        <f>S61+T61+W61</f>
+        <v/>
+      </c>
+      <c r="AA61" s="302">
+        <f>K61+L61+M61+IFERROR(VLOOKUP(B61,RemitTable2,9,FALSE),0)+Y61+Z61</f>
+        <v/>
+      </c>
+      <c r="AB61" s="303" t="n">
         <v>1</v>
       </c>
-      <c r="AC60" s="26">
-        <f>ROUND(AA60/AB60,0)</f>
-        <v/>
-      </c>
-      <c r="AD60" s="20" t="inlineStr">
+      <c r="AC61" s="302">
+        <f>ROUND(AA61/AB61,0)</f>
+        <v/>
+      </c>
+      <c r="AD61" s="296" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE60" s="184" t="inlineStr">
+      <c r="AE61" s="299" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AF60" s="183" t="inlineStr">
+      <c r="AF61" s="298" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="85" t="n">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="304" t="n">
         <v>46</v>
       </c>
-      <c r="B61" s="85" t="inlineStr">
+      <c r="B62" s="304" t="inlineStr">
         <is>
           <t>CPO697</t>
         </is>
       </c>
-      <c r="C61" s="85" t="inlineStr">
+      <c r="C62" s="304" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D61" s="85" t="inlineStr">
+      <c r="D62" s="304" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E61" s="85" t="inlineStr">
+      <c r="E62" s="304" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F61" s="186" t="n">
+      <c r="F62" s="305" t="n">
         <v>46136</v>
       </c>
-      <c r="G61" s="186" t="n">
+      <c r="G62" s="305" t="n">
         <v>46171</v>
       </c>
-      <c r="H61" s="87" t="n">
+      <c r="H62" s="306" t="n">
         <v>15289</v>
       </c>
-      <c r="I61" s="187" t="n">
+      <c r="I62" s="307" t="n">
         <v>1502.7</v>
       </c>
-      <c r="J61" s="89" t="n">
+      <c r="J62" s="308" t="n">
         <v>22974780</v>
       </c>
-      <c r="K61" s="89" t="n">
+      <c r="K62" s="308" t="n">
         <v>22974780</v>
       </c>
-      <c r="L61" s="89" t="n">
+      <c r="L62" s="308" t="n">
         <v>1880</v>
       </c>
-      <c r="M61" s="89" t="n">
+      <c r="M62" s="308" t="n">
         <v>1203</v>
       </c>
-      <c r="N61" s="85" t="inlineStr">
+      <c r="N62" s="304" t="inlineStr">
         <is>
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O61" s="186" t="inlineStr">
+      <c r="O62" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P61" s="85" t="inlineStr">
+      <c r="P62" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q61" s="87">
-        <f>IF(P61="","",IFERROR(VLOOKUP(O61,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R61" s="87">
-        <f>IF(P61="","",H61)</f>
-        <v/>
-      </c>
-      <c r="S61" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="186" t="n"/>
-      <c r="V61" s="85" t="inlineStr">
+      <c r="Q62" s="306">
+        <f>IF(P62="","",IFERROR(VLOOKUP(O62,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R62" s="306">
+        <f>IF(P62="","",H62)</f>
+        <v/>
+      </c>
+      <c r="S62" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="305" t="n"/>
+      <c r="V62" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W61" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" s="85" t="inlineStr">
+      <c r="W62" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y61" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="89">
-        <f>S61+T61+W61</f>
-        <v/>
-      </c>
-      <c r="AA61" s="89">
-        <f>K61+L61+M61+IFERROR(VLOOKUP(B61,RemitTable2,9,FALSE),0)+Y61+Z61</f>
-        <v/>
-      </c>
-      <c r="AB61" s="90" t="n">
+      <c r="Y62" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="308">
+        <f>S62+T62+W62</f>
+        <v/>
+      </c>
+      <c r="AA62" s="308">
+        <f>K62+L62+M62+IFERROR(VLOOKUP(B62,RemitTable2,9,FALSE),0)+Y62+Z62</f>
+        <v/>
+      </c>
+      <c r="AB62" s="309" t="n">
         <v>1</v>
       </c>
-      <c r="AC61" s="89">
-        <f>ROUND(AA61/AB61,0)</f>
-        <v/>
-      </c>
-      <c r="AD61" s="85" t="inlineStr">
+      <c r="AC62" s="308">
+        <f>ROUND(AA62/AB62,0)</f>
+        <v/>
+      </c>
+      <c r="AD62" s="304" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE61" s="186" t="n">
+      <c r="AE62" s="305" t="n">
         <v>46168</v>
       </c>
-      <c r="AF61" s="186" t="n">
+      <c r="AF62" s="305" t="n">
         <v>46532</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="85" t="n">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="304" t="n">
         <v>47</v>
       </c>
-      <c r="B62" s="85" t="inlineStr">
+      <c r="B63" s="304" t="inlineStr">
         <is>
           <t>CPO693-2</t>
         </is>
       </c>
-      <c r="C62" s="85" t="inlineStr">
+      <c r="C63" s="304" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D62" s="85" t="inlineStr">
+      <c r="D63" s="304" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E62" s="85" t="inlineStr">
+      <c r="E63" s="304" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F62" s="186" t="n">
+      <c r="F63" s="305" t="n">
         <v>46133</v>
       </c>
-      <c r="G62" s="186" t="inlineStr">
+      <c r="G63" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H62" s="87" t="n">
+      <c r="H63" s="306" t="n">
         <v>2550</v>
       </c>
-      <c r="I62" s="187">
+      <c r="I63" s="307">
         <f>IFERROR(VLOOKUP(B62,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
-      <c r="J62" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="89">
+      <c r="J63" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="308">
         <f>IFERROR(ROUND(H62*I62,0),0)</f>
         <v/>
       </c>
-      <c r="L62" s="89">
+      <c r="L63" s="308">
         <f>IFERROR(VLOOKUP(B62,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
-      <c r="M62" s="89">
+      <c r="M63" s="308">
         <f>IFERROR(VLOOKUP(B62,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N62" s="85" t="inlineStr">
+      <c r="N63" s="304" t="inlineStr">
         <is>
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O62" s="186" t="inlineStr">
+      <c r="O63" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P62" s="85" t="inlineStr">
+      <c r="P63" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q62" s="87">
-        <f>IF(P62="","",IFERROR(VLOOKUP(O62,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R62" s="87">
-        <f>IF(P62="","",H62)</f>
-        <v/>
-      </c>
-      <c r="S62" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="186" t="n"/>
-      <c r="V62" s="85" t="inlineStr">
+      <c r="Q63" s="306">
+        <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R63" s="306">
+        <f>IF(P63="","",H63)</f>
+        <v/>
+      </c>
+      <c r="S63" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="305" t="n"/>
+      <c r="V63" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W62" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="85" t="inlineStr">
+      <c r="W63" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y62" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="89">
-        <f>S62+T62+W62</f>
-        <v/>
-      </c>
-      <c r="AA62" s="89">
-        <f>K62+L62+M62+IFERROR(VLOOKUP(B62,RemitTable2,9,FALSE),0)+Y62+Z62</f>
-        <v/>
-      </c>
-      <c r="AB62" s="90" t="n">
+      <c r="Y63" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="308">
+        <f>S63+T63+W63</f>
+        <v/>
+      </c>
+      <c r="AA63" s="308">
+        <f>K63+L63+M63+IFERROR(VLOOKUP(B63,RemitTable2,9,FALSE),0)+Y63+Z63</f>
+        <v/>
+      </c>
+      <c r="AB63" s="309" t="n">
         <v>1</v>
       </c>
-      <c r="AC62" s="89">
-        <f>ROUND(AA62/AB62,0)</f>
-        <v/>
-      </c>
-      <c r="AD62" s="85" t="inlineStr">
+      <c r="AC63" s="308">
+        <f>ROUND(AA63/AB63,0)</f>
+        <v/>
+      </c>
+      <c r="AD63" s="304" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE62" s="186" t="n">
+      <c r="AE63" s="305" t="n">
         <v>46142</v>
       </c>
-      <c r="AF62" s="186" t="n">
+      <c r="AF63" s="305" t="n">
         <v>46872</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="132" t="n">
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="132" t="n">
         <v>54</v>
       </c>
-      <c r="B63" s="132" t="inlineStr">
+      <c r="B64" s="132" t="inlineStr">
         <is>
           <t>GPO478</t>
         </is>
       </c>
-      <c r="C63" s="132" t="inlineStr">
+      <c r="C64" s="132" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D63" s="132" t="inlineStr">
+      <c r="D64" s="132" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E63" s="132" t="inlineStr">
+      <c r="E64" s="132" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
       </c>
-      <c r="F63" s="188" t="n">
+      <c r="F64" s="188" t="n">
         <v>46127</v>
       </c>
-      <c r="G63" s="188" t="n">
+      <c r="G64" s="188" t="n">
         <v>46161</v>
       </c>
-      <c r="H63" s="134" t="n">
+      <c r="H64" s="134" t="n">
         <v>180</v>
       </c>
-      <c r="I63" s="134" t="n">
+      <c r="I64" s="134" t="n">
         <v>1518.9</v>
       </c>
-      <c r="J63" s="136" t="n">
+      <c r="J64" s="136" t="n">
         <v>273402</v>
       </c>
-      <c r="K63" s="136" t="n">
+      <c r="K64" s="136" t="n">
         <v>273402</v>
       </c>
-      <c r="L63" s="136" t="n">
+      <c r="L64" s="136" t="n">
         <v>2500</v>
       </c>
-      <c r="M63" s="136" t="n">
+      <c r="M64" s="136" t="n">
         <v>8000</v>
-      </c>
-      <c r="N63" s="137" t="n"/>
-      <c r="O63" s="189" t="n"/>
-      <c r="P63" s="137" t="n"/>
-      <c r="Q63" s="134">
-        <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R63" s="134">
-        <f>IF(P63="","",H63)</f>
-        <v/>
-      </c>
-      <c r="S63" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="189" t="n"/>
-      <c r="V63" s="137" t="n"/>
-      <c r="W63" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y63" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="136">
-        <f>S63+T63+W63</f>
-        <v/>
-      </c>
-      <c r="AA63" s="136">
-        <f>K63+L63+M63+IFERROR(VLOOKUP(B63,RemitTable2,9,FALSE),0)+Y63+Z63</f>
-        <v/>
-      </c>
-      <c r="AB63" s="168" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC63" s="136">
-        <f>ROUND(AA63/AB63,0)</f>
-        <v/>
-      </c>
-      <c r="AD63" s="137" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="AE63" s="189" t="n">
-        <v>46143</v>
-      </c>
-      <c r="AF63" s="189" t="n">
-        <v>46507</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="132" t="n">
-        <v>55</v>
-      </c>
-      <c r="B64" s="132" t="inlineStr">
-        <is>
-          <t>GPO480</t>
-        </is>
-      </c>
-      <c r="C64" s="132" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D64" s="132" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E64" s="132" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F64" s="188" t="n">
-        <v>46137</v>
-      </c>
-      <c r="G64" s="188" t="n">
-        <v>46171</v>
-      </c>
-      <c r="H64" s="134" t="n">
-        <v>250</v>
-      </c>
-      <c r="I64" s="134" t="n">
-        <v>1502.8</v>
-      </c>
-      <c r="J64" s="136" t="n">
-        <v>375700</v>
-      </c>
-      <c r="K64" s="136" t="n">
-        <v>375700</v>
-      </c>
-      <c r="L64" s="136" t="n">
-        <v>32</v>
-      </c>
-      <c r="M64" s="136" t="n">
-        <v>20</v>
       </c>
       <c r="N64" s="137" t="n"/>
       <c r="O64" s="189" t="n"/>
@@ -9426,7 +9508,7 @@
         <v/>
       </c>
       <c r="AB64" s="168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC64" s="136">
         <f>ROUND(AA64/AB64,0)</f>
@@ -9441,16 +9523,16 @@
         <v>46143</v>
       </c>
       <c r="AF64" s="189" t="n">
-        <v>49795</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="132" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B65" s="132" t="inlineStr">
         <is>
-          <t>GPO481</t>
+          <t>GPO480</t>
         </is>
       </c>
       <c r="C65" s="132" t="inlineStr">
@@ -9469,28 +9551,28 @@
         </is>
       </c>
       <c r="F65" s="188" t="n">
-        <v>46152</v>
+        <v>46137</v>
       </c>
       <c r="G65" s="188" t="n">
-        <v>46183</v>
+        <v>46171</v>
       </c>
       <c r="H65" s="134" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I65" s="134" t="n">
-        <v>1525.3</v>
+        <v>1502.8</v>
       </c>
       <c r="J65" s="136" t="n">
-        <v>762650</v>
+        <v>375700</v>
       </c>
       <c r="K65" s="136" t="n">
-        <v>762650</v>
+        <v>375700</v>
       </c>
       <c r="L65" s="136" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="M65" s="136" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="N65" s="137" t="n"/>
       <c r="O65" s="189" t="n"/>
@@ -9539,27 +9621,23 @@
       </c>
       <c r="AD65" s="137" t="inlineStr">
         <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="AE65" s="189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF65" s="189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE65" s="189" t="n">
+        <v>46143</v>
+      </c>
+      <c r="AF65" s="189" t="n">
+        <v>49795</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="132" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B66" s="132" t="inlineStr">
         <is>
-          <t>GPO475</t>
+          <t>GPO481</t>
         </is>
       </c>
       <c r="C66" s="132" t="inlineStr">
@@ -9578,34 +9656,30 @@
         </is>
       </c>
       <c r="F66" s="188" t="n">
-        <v>46127</v>
+        <v>46152</v>
       </c>
       <c r="G66" s="188" t="n">
-        <v>46190</v>
+        <v>46183</v>
       </c>
       <c r="H66" s="134" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="I66" s="134" t="n">
-        <v>1516.8</v>
+        <v>1525.3</v>
       </c>
       <c r="J66" s="136" t="n">
-        <v>819072</v>
+        <v>762650</v>
       </c>
       <c r="K66" s="136" t="n">
-        <v>819072</v>
+        <v>762650</v>
       </c>
       <c r="L66" s="136" t="n">
-        <v>1985</v>
+        <v>52</v>
       </c>
       <c r="M66" s="136" t="n">
-        <v>2118</v>
-      </c>
-      <c r="N66" s="137" t="inlineStr">
-        <is>
-          <t>TMS-1000 License 6 screens (CGV 안동)</t>
-        </is>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="N66" s="137" t="n"/>
       <c r="O66" s="189" t="n"/>
       <c r="P66" s="137" t="n"/>
       <c r="Q66" s="134">
@@ -9644,7 +9718,7 @@
         <v/>
       </c>
       <c r="AB66" s="168" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC66" s="136">
         <f>ROUND(AA66/AB66,0)</f>
@@ -9652,938 +9726,1341 @@
       </c>
       <c r="AD66" s="137" t="inlineStr">
         <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AE66" s="189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF66" s="189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="132" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="132" t="inlineStr">
+        <is>
+          <t>GPO475</t>
+        </is>
+      </c>
+      <c r="C67" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D67" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E67" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F67" s="188" t="n">
+        <v>46127</v>
+      </c>
+      <c r="G67" s="188" t="n">
+        <v>46190</v>
+      </c>
+      <c r="H67" s="134" t="n">
+        <v>540</v>
+      </c>
+      <c r="I67" s="134" t="n">
+        <v>1516.8</v>
+      </c>
+      <c r="J67" s="136" t="n">
+        <v>819072</v>
+      </c>
+      <c r="K67" s="136" t="n">
+        <v>819072</v>
+      </c>
+      <c r="L67" s="136" t="n">
+        <v>1985</v>
+      </c>
+      <c r="M67" s="136" t="n">
+        <v>2118</v>
+      </c>
+      <c r="N67" s="137" t="inlineStr">
+        <is>
+          <t>TMS-1000 License 6 screens (CGV 안동)</t>
+        </is>
+      </c>
+      <c r="O67" s="189" t="n"/>
+      <c r="P67" s="137" t="n"/>
+      <c r="Q67" s="134">
+        <f>IF(P67="","",IFERROR(VLOOKUP(O67,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R67" s="134">
+        <f>IF(P67="","",H67)</f>
+        <v/>
+      </c>
+      <c r="S67" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="189" t="n"/>
+      <c r="V67" s="137" t="n"/>
+      <c r="W67" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y67" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="136">
+        <f>S67+T67+W67</f>
+        <v/>
+      </c>
+      <c r="AA67" s="136">
+        <f>K67+L67+M67+IFERROR(VLOOKUP(B67,RemitTable2,9,FALSE),0)+Y67+Z67</f>
+        <v/>
+      </c>
+      <c r="AB67" s="168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC67" s="136">
+        <f>ROUND(AA67/AB67,0)</f>
+        <v/>
+      </c>
+      <c r="AD67" s="137" t="inlineStr">
+        <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE66" s="189" t="n">
+      <c r="AE67" s="189" t="n">
         <v>46143</v>
       </c>
-      <c r="AF66" s="189" t="n">
+      <c r="AF67" s="189" t="n">
         <v>46507</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="12" t="n">
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="132" t="n">
+        <v>68</v>
+      </c>
+      <c r="B68" s="132" t="inlineStr">
+        <is>
+          <t>CPO702</t>
+        </is>
+      </c>
+      <c r="C68" s="132" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D68" s="132" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E68" s="132" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F68" s="188" t="n">
+        <v>46181</v>
+      </c>
+      <c r="G68" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" s="134" t="n">
+        <v>32715</v>
+      </c>
+      <c r="I68" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="137" t="inlineStr">
+        <is>
+          <t>EW CP2215/CP2309-RGB 24대 (롯데 영천/CineQ 청라/CGV 동두천 외)</t>
+        </is>
+      </c>
+      <c r="O68" s="189" t="n"/>
+      <c r="P68" s="137" t="n"/>
+      <c r="Q68" s="134">
+        <f>IF(P68="","",IFERROR(VLOOKUP(O68,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R68" s="134">
+        <f>IF(P68="","",H68)</f>
+        <v/>
+      </c>
+      <c r="S68" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="189" t="n"/>
+      <c r="V68" s="137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W68" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y68" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="136">
+        <f>S68+T68+W68</f>
+        <v/>
+      </c>
+      <c r="AA68" s="136">
+        <f>K68+L68+M68+IFERROR(VLOOKUP(B68,RemitTable2,9,FALSE),0)+Y68+Z68</f>
+        <v/>
+      </c>
+      <c r="AB68" s="168" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC68" s="136">
+        <f>ROUND(AA68/AB68,0)</f>
+        <v/>
+      </c>
+      <c r="AD68" s="137" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AE68" s="189" t="n">
+        <v>46192</v>
+      </c>
+      <c r="AF68" s="189" t="n">
+        <v>46752</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="132" t="n">
+        <v>69</v>
+      </c>
+      <c r="B69" s="132" t="inlineStr">
+        <is>
+          <t>GPO486</t>
+        </is>
+      </c>
+      <c r="C69" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D69" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E69" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F69" s="188" t="n">
+        <v>46182</v>
+      </c>
+      <c r="G69" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="134" t="n">
+        <v>450</v>
+      </c>
+      <c r="I69" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="137" t="inlineStr">
+        <is>
+          <t>TMS-1000 License Extension 5screens (메가박스 경산 하양)</t>
+        </is>
+      </c>
+      <c r="O69" s="189" t="n"/>
+      <c r="P69" s="137" t="n"/>
+      <c r="Q69" s="134">
+        <f>IF(P69="","",IFERROR(VLOOKUP(O69,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R69" s="134">
+        <f>IF(P69="","",H69)</f>
+        <v/>
+      </c>
+      <c r="S69" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="189" t="n"/>
+      <c r="V69" s="137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W69" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y69" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="136">
+        <f>S69+T69+W69</f>
+        <v/>
+      </c>
+      <c r="AA69" s="136">
+        <f>K69+L69+M69+IFERROR(VLOOKUP(B69,RemitTable2,9,FALSE),0)+Y69+Z69</f>
+        <v/>
+      </c>
+      <c r="AB69" s="168" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC69" s="136">
+        <f>ROUND(AA69/AB69,0)</f>
+        <v/>
+      </c>
+      <c r="AD69" s="137" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE69" s="189" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AF69" s="189" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="132" t="n">
+        <v>70</v>
+      </c>
+      <c r="B70" s="132" t="inlineStr">
+        <is>
+          <t>GPO484</t>
+        </is>
+      </c>
+      <c r="C70" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D70" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E70" s="132" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F70" s="188" t="n">
+        <v>46183</v>
+      </c>
+      <c r="G70" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="134" t="n">
+        <v>7407.81</v>
+      </c>
+      <c r="I70" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="137" t="inlineStr">
+        <is>
+          <t>SR-1000/SX-4000 Warranty Ext 11대 (CGV 진주혁신/합천/구례)</t>
+        </is>
+      </c>
+      <c r="O70" s="189" t="n"/>
+      <c r="P70" s="137" t="n"/>
+      <c r="Q70" s="134">
+        <f>IF(P70="","",IFERROR(VLOOKUP(O70,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R70" s="134">
+        <f>IF(P70="","",H70)</f>
+        <v/>
+      </c>
+      <c r="S70" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="189" t="n"/>
+      <c r="V70" s="137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W70" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y70" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="136">
+        <f>S70+T70+W70</f>
+        <v/>
+      </c>
+      <c r="AA70" s="136">
+        <f>K70+L70+M70+IFERROR(VLOOKUP(B70,RemitTable2,9,FALSE),0)+Y70+Z70</f>
+        <v/>
+      </c>
+      <c r="AB70" s="168" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC70" s="136">
+        <f>ROUND(AA70/AB70,0)</f>
+        <v/>
+      </c>
+      <c r="AD70" s="137" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE70" s="189" t="n">
+        <v>46156</v>
+      </c>
+      <c r="AF70" s="189" t="n">
+        <v>46752</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="132" t="n">
+        <v>71</v>
+      </c>
+      <c r="B71" s="132" t="inlineStr">
+        <is>
+          <t>GPO489</t>
+        </is>
+      </c>
+      <c r="C71" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D71" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E71" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F71" s="188" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G71" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" s="134" t="n">
+        <v>3320</v>
+      </c>
+      <c r="I71" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="137" t="inlineStr">
+        <is>
+          <t>TMS License 7사이트 32screens (메가박스 삼천포/CGV 대구수성 외)</t>
+        </is>
+      </c>
+      <c r="O71" s="189" t="n"/>
+      <c r="P71" s="137" t="n"/>
+      <c r="Q71" s="134">
+        <f>IF(P71="","",IFERROR(VLOOKUP(O71,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R71" s="134">
+        <f>IF(P71="","",H71)</f>
+        <v/>
+      </c>
+      <c r="S71" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="189" t="n"/>
+      <c r="V71" s="137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W71" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y71" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="136">
+        <f>S71+T71+W71</f>
+        <v/>
+      </c>
+      <c r="AA71" s="136">
+        <f>K71+L71+M71+IFERROR(VLOOKUP(B71,RemitTable2,9,FALSE),0)+Y71+Z71</f>
+        <v/>
+      </c>
+      <c r="AB71" s="168" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC71" s="136">
+        <f>ROUND(AA71/AB71,0)</f>
+        <v/>
+      </c>
+      <c r="AD71" s="137" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE71" s="189" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AF71" s="189" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="284" t="n">
         <v>48</v>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B72" s="284" t="inlineStr">
         <is>
           <t>CPO688</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C72" s="285" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D72" s="284" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="E72" s="285" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="F67" s="176" t="n">
+      <c r="F72" s="286" t="n">
         <v>46037</v>
       </c>
-      <c r="G67" s="177" t="inlineStr">
+      <c r="G72" s="287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="16" t="n">
+      <c r="H72" s="288" t="n">
         <v>4180</v>
       </c>
-      <c r="I67" s="178">
+      <c r="I72" s="289">
         <f>IFERROR(VLOOKUP(B67,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
-      <c r="J67" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="18">
+      <c r="J72" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="290">
         <f>IFERROR(ROUND(H67*I67,0),0)</f>
         <v/>
       </c>
-      <c r="L67" s="18">
+      <c r="L72" s="290">
         <f>IFERROR(VLOOKUP(B67,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
-      <c r="M67" s="18">
+      <c r="M72" s="290">
         <f>IFERROR(VLOOKUP(B67,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N67" s="12" t="inlineStr">
+      <c r="N72" s="284" t="inlineStr">
         <is>
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O67" s="177" t="inlineStr">
+      <c r="O72" s="287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P67" s="12" t="inlineStr">
+      <c r="P72" s="284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q67" s="16">
-        <f>IF(P67="","",IFERROR(VLOOKUP(O67,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R67" s="18">
-        <f>IF(P67="","",H67)</f>
-        <v/>
-      </c>
-      <c r="S67" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="176" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="12" t="inlineStr">
+      <c r="Q72" s="288">
+        <f>IF(P72="","",IFERROR(VLOOKUP(O72,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R72" s="290">
+        <f>IF(P72="","",H72)</f>
+        <v/>
+      </c>
+      <c r="S72" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="286" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W67" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" s="13" t="inlineStr">
+      <c r="W72" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y67" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" s="18">
-        <f>S67+T67+W67</f>
-        <v/>
-      </c>
-      <c r="AA67" s="18">
-        <f>K67+L67+M67+IFERROR(VLOOKUP(B67,RemitTable2,9,FALSE),0)+Y67+Z67</f>
-        <v/>
-      </c>
-      <c r="AB67" s="19" t="n">
+      <c r="Y72" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="290">
+        <f>S72+T72+W72</f>
+        <v/>
+      </c>
+      <c r="AA72" s="290">
+        <f>K72+L72+M72+IFERROR(VLOOKUP(B72,RemitTable2,9,FALSE),0)+Y72+Z72</f>
+        <v/>
+      </c>
+      <c r="AB72" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="AC67" s="18">
-        <f>ROUND(AA67/AB67,0)</f>
-        <v/>
-      </c>
-      <c r="AD67" s="12" t="inlineStr">
+      <c r="AC72" s="290">
+        <f>ROUND(AA72/AB72,0)</f>
+        <v/>
+      </c>
+      <c r="AD72" s="284" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE67" s="177" t="inlineStr">
+      <c r="AE72" s="287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF67" s="176" t="inlineStr">
+      <c r="AF72" s="286" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="12" t="n">
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="284" t="n">
         <v>49</v>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B73" s="284" t="inlineStr">
         <is>
           <t>SX3000수리</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C73" s="285" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D73" s="284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E68" s="13" t="inlineStr">
+      <c r="E73" s="285" t="inlineStr">
         <is>
           <t>수리반환</t>
         </is>
       </c>
-      <c r="F68" s="176" t="n"/>
-      <c r="G68" s="177" t="inlineStr">
+      <c r="F73" s="286" t="n"/>
+      <c r="G73" s="287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H68" s="16" t="n">
+      <c r="H73" s="288" t="n">
         <v>400</v>
       </c>
-      <c r="I68" s="178">
+      <c r="I73" s="289">
         <f>IFERROR(VLOOKUP(B68,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
-      <c r="J68" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="18">
+      <c r="J73" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="290">
         <f>IFERROR(ROUND(H68*I68,0),0)</f>
         <v/>
       </c>
-      <c r="L68" s="18">
+      <c r="L73" s="290">
         <f>IFERROR(VLOOKUP(B68,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
-      <c r="M68" s="18">
+      <c r="M73" s="290">
         <f>IFERROR(VLOOKUP(B68,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N68" s="12" t="inlineStr">
+      <c r="N73" s="284" t="inlineStr">
         <is>
           <t>Display Card (수리반환 5PCS)</t>
         </is>
       </c>
-      <c r="O68" s="177" t="n">
+      <c r="O73" s="287" t="n">
         <v>46125</v>
       </c>
-      <c r="P68" s="12" t="inlineStr">
+      <c r="P73" s="284" t="inlineStr">
         <is>
           <t>22356-26-351613M</t>
         </is>
       </c>
-      <c r="Q68" s="16">
-        <f>IF(P68="","",IFERROR(VLOOKUP(O68,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R68" s="18">
-        <f>IF(P68="","",H68)</f>
-        <v/>
-      </c>
-      <c r="S68" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="18" t="n">
+      <c r="Q73" s="288">
+        <f>IF(P73="","",IFERROR(VLOOKUP(O73,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R73" s="290">
+        <f>IF(P73="","",H73)</f>
+        <v/>
+      </c>
+      <c r="S73" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="290" t="n">
         <v>67750</v>
       </c>
-      <c r="U68" s="176" t="n"/>
-      <c r="V68" s="12" t="inlineStr">
+      <c r="U73" s="286" t="n"/>
+      <c r="V73" s="284" t="inlineStr">
         <is>
           <t>운서합동</t>
         </is>
       </c>
-      <c r="W68" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" s="13" t="inlineStr">
+      <c r="W73" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" s="285" t="inlineStr">
         <is>
           <t>DHL</t>
         </is>
       </c>
-      <c r="Y68" s="18" t="n">
+      <c r="Y73" s="290" t="n">
         <v>216006</v>
       </c>
-      <c r="Z68" s="18">
-        <f>S68+T68+W68</f>
-        <v/>
-      </c>
-      <c r="AA68" s="18">
-        <f>K68+L68+M68+IFERROR(VLOOKUP(B68,RemitTable2,9,FALSE),0)+Y68+Z68</f>
-        <v/>
-      </c>
-      <c r="AB68" s="19" t="n">
+      <c r="Z73" s="290">
+        <f>S73+T73+W73</f>
+        <v/>
+      </c>
+      <c r="AA73" s="290">
+        <f>K73+L73+M73+IFERROR(VLOOKUP(B73,RemitTable2,9,FALSE),0)+Y73+Z73</f>
+        <v/>
+      </c>
+      <c r="AB73" s="291" t="n">
         <v>5</v>
       </c>
-      <c r="AC68" s="18">
-        <f>ROUND(AA68/AB68,0)</f>
-        <v/>
-      </c>
-      <c r="AD68" s="12" t="inlineStr">
+      <c r="AC73" s="290">
+        <f>ROUND(AA73/AB73,0)</f>
+        <v/>
+      </c>
+      <c r="AD73" s="284" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE68" s="177" t="n"/>
-      <c r="AF68" s="176" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="216" t="n">
+      <c r="AE73" s="287" t="n"/>
+      <c r="AF73" s="286" t="n"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="216" t="n">
         <v>59</v>
       </c>
-      <c r="B69" s="216" t="inlineStr">
+      <c r="B74" s="216" t="inlineStr">
         <is>
           <t>FRC-MONOPLEX26</t>
         </is>
       </c>
-      <c r="C69" s="217" t="inlineStr">
+      <c r="C74" s="217" t="inlineStr">
         <is>
           <t>Ferco</t>
         </is>
       </c>
-      <c r="D69" s="216" t="inlineStr">
+      <c r="D74" s="216" t="inlineStr">
         <is>
           <t>50% TT advance + 50% balance</t>
         </is>
       </c>
-      <c r="E69" s="217" t="inlineStr">
+      <c r="E74" s="217" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="F69" s="218" t="n">
+      <c r="F74" s="218" t="n">
         <v>46048</v>
       </c>
-      <c r="G69" s="219" t="n">
+      <c r="G74" s="219" t="n">
         <v>46133</v>
       </c>
-      <c r="H69" s="220" t="n">
+      <c r="H74" s="220" t="n">
         <v>51952</v>
       </c>
-      <c r="I69" s="221">
+      <c r="I74" s="221">
         <f>IFERROR(VLOOKUP(B69,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
-      <c r="J69" s="222" t="n">
+      <c r="J74" s="222" t="n">
         <v>75818749</v>
       </c>
-      <c r="K69" s="222" t="n">
+      <c r="K74" s="222" t="n">
         <v>75818749</v>
       </c>
-      <c r="L69" s="222" t="n">
+      <c r="L74" s="222" t="n">
         <v>25000</v>
       </c>
-      <c r="M69" s="222" t="n">
+      <c r="M74" s="222" t="n">
         <v>16000</v>
       </c>
-      <c r="N69" s="216" t="inlineStr">
+      <c r="N74" s="216" t="inlineStr">
         <is>
           <t>Cinema Seat (Recliner) / 44 EA / Monoplex DH Bangbae</t>
         </is>
       </c>
-      <c r="O69" s="219" t="n">
+      <c r="O74" s="219" t="n">
         <v>46153</v>
       </c>
-      <c r="P69" s="216" t="inlineStr">
+      <c r="P74" s="216" t="inlineStr">
         <is>
           <t>14008-26-101147M</t>
         </is>
       </c>
-      <c r="Q69" s="220">
-        <f>IF(P69="","",IFERROR(VLOOKUP(O69,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R69" s="220">
-        <f>IF(P69="","",H69)</f>
-        <v/>
-      </c>
-      <c r="S69" s="222" t="n">
+      <c r="Q74" s="220">
+        <f>IF(P74="","",IFERROR(VLOOKUP(O74,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R74" s="220">
+        <f>IF(P74="","",H74)</f>
+        <v/>
+      </c>
+      <c r="S74" s="222" t="n">
         <v>31050</v>
       </c>
-      <c r="T69" s="222" t="n">
+      <c r="T74" s="222" t="n">
         <v>7959560</v>
       </c>
-      <c r="U69" s="218" t="n"/>
-      <c r="V69" s="216" t="inlineStr">
+      <c r="U74" s="218" t="n"/>
+      <c r="V74" s="216" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
       </c>
-      <c r="W69" s="222" t="n">
+      <c r="W74" s="222" t="n">
         <v>250000</v>
       </c>
-      <c r="X69" s="217" t="inlineStr">
+      <c r="X74" s="217" t="inlineStr">
         <is>
           <t>진로직스</t>
         </is>
       </c>
-      <c r="Y69" s="222" t="n">
+      <c r="Y74" s="222" t="n">
         <v>5002612</v>
       </c>
-      <c r="Z69" s="222">
-        <f>S69+T69+W69</f>
-        <v/>
-      </c>
-      <c r="AA69" s="222">
-        <f>K69+L69+M69+IFERROR(VLOOKUP(B69,RemitTable2,9,FALSE),0)+Y69+Z69</f>
-        <v/>
-      </c>
-      <c r="AB69" s="223" t="n">
+      <c r="Z74" s="222">
+        <f>S74+T74+W74</f>
+        <v/>
+      </c>
+      <c r="AA74" s="222">
+        <f>K74+L74+M74+IFERROR(VLOOKUP(B74,RemitTable2,9,FALSE),0)+Y74+Z74</f>
+        <v/>
+      </c>
+      <c r="AB74" s="223" t="n">
         <v>44</v>
       </c>
-      <c r="AC69" s="222">
-        <f>ROUND(AA69/AB69,0)</f>
-        <v/>
-      </c>
-      <c r="AD69" s="216" t="inlineStr">
+      <c r="AC74" s="222">
+        <f>ROUND(AA74/AB74,0)</f>
+        <v/>
+      </c>
+      <c r="AD74" s="216" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE69" s="219" t="n"/>
-      <c r="AF69" s="218" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="284" t="n">
+      <c r="AE74" s="219" t="n"/>
+      <c r="AF74" s="218" t="n"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="284" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="284" t="inlineStr">
+      <c r="B75" s="284" t="inlineStr">
         <is>
           <t>GPO475-수리</t>
         </is>
       </c>
-      <c r="C70" s="285" t="inlineStr">
+      <c r="C75" s="285" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D70" s="284" t="inlineStr">
+      <c r="D75" s="284" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E70" s="285" t="inlineStr">
+      <c r="E75" s="285" t="inlineStr">
         <is>
           <t>수리</t>
         </is>
       </c>
-      <c r="F70" s="286" t="n">
+      <c r="F75" s="286" t="n">
         <v>46126</v>
       </c>
-      <c r="G70" s="287" t="n">
+      <c r="G75" s="287" t="n">
         <v>46190</v>
       </c>
-      <c r="H70" s="288" t="n">
+      <c r="H75" s="288" t="n">
         <v>1500</v>
       </c>
-      <c r="I70" s="289" t="n">
+      <c r="I75" s="289" t="n">
         <v>1516.8</v>
       </c>
-      <c r="J70" s="290" t="n">
+      <c r="J75" s="290" t="n">
         <v>2275200</v>
       </c>
-      <c r="K70" s="290" t="n">
+      <c r="K75" s="290" t="n">
         <v>2275200</v>
       </c>
-      <c r="L70" s="290" t="n">
+      <c r="L75" s="290" t="n">
         <v>5515</v>
       </c>
-      <c r="M70" s="290" t="n">
+      <c r="M75" s="290" t="n">
         <v>5882</v>
       </c>
-      <c r="N70" s="284" t="inlineStr">
+      <c r="N75" s="284" t="inlineStr">
         <is>
           <t>SR-1000 IMB Inspection+Repair (SN A78267)</t>
         </is>
       </c>
-      <c r="O70" s="287" t="n"/>
-      <c r="P70" s="284" t="n"/>
-      <c r="Q70" s="288">
-        <f>IF(P70="","",IFERROR(VLOOKUP(O70,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R70" s="290">
-        <f>IF(P70="","",H70)</f>
-        <v/>
-      </c>
-      <c r="S70" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" s="286" t="n"/>
-      <c r="V70" s="284" t="n"/>
-      <c r="W70" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" s="285" t="inlineStr">
+      <c r="O75" s="287" t="n"/>
+      <c r="P75" s="284" t="n"/>
+      <c r="Q75" s="288">
+        <f>IF(P75="","",IFERROR(VLOOKUP(O75,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R75" s="290">
+        <f>IF(P75="","",H75)</f>
+        <v/>
+      </c>
+      <c r="S75" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" s="286" t="n"/>
+      <c r="V75" s="284" t="n"/>
+      <c r="W75" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y70" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" s="290">
-        <f>S70+T70+W70</f>
-        <v/>
-      </c>
-      <c r="AA70" s="290">
-        <f>K70+L70+M70+IFERROR(VLOOKUP(B70,RemitTable2,9,FALSE),0)+Y70+Z70</f>
-        <v/>
-      </c>
-      <c r="AB70" s="291" t="n">
+      <c r="Y75" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="290">
+        <f>S75+T75+W75</f>
+        <v/>
+      </c>
+      <c r="AA75" s="290">
+        <f>K75+L75+M75+IFERROR(VLOOKUP(B75,RemitTable2,9,FALSE),0)+Y75+Z75</f>
+        <v/>
+      </c>
+      <c r="AB75" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="AC70" s="290">
-        <f>ROUND(AA70/AB70,0)</f>
-        <v/>
-      </c>
-      <c r="AD70" s="284" t="n"/>
-      <c r="AE70" s="287" t="n"/>
-      <c r="AF70" s="286" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="147" t="inlineStr">
+      <c r="AC75" s="290">
+        <f>ROUND(AA75/AB75,0)</f>
+        <v/>
+      </c>
+      <c r="AD75" s="284" t="n"/>
+      <c r="AE75" s="287" t="n"/>
+      <c r="AF75" s="286" t="n"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="147" t="inlineStr">
         <is>
           <t>장비/부품 합계</t>
         </is>
       </c>
-      <c r="B71" s="148" t="n"/>
-      <c r="C71" s="148" t="n"/>
-      <c r="D71" s="148" t="n"/>
-      <c r="E71" s="148" t="n"/>
-      <c r="F71" s="148" t="n"/>
-      <c r="G71" s="149" t="n"/>
-      <c r="H71" s="142">
-        <f>SUBTOTAL(9,H5:H43)</f>
-        <v/>
-      </c>
-      <c r="I71" s="141" t="n"/>
-      <c r="J71" s="142">
-        <f>SUBTOTAL(9,J5:J39)</f>
-        <v/>
-      </c>
-      <c r="K71" s="142">
-        <f>SUBTOTAL(9,K5:K43)</f>
-        <v/>
-      </c>
-      <c r="L71" s="142">
-        <f>SUBTOTAL(9,L5:L43)</f>
-        <v/>
-      </c>
-      <c r="M71" s="142">
-        <f>SUBTOTAL(9,M5:M43)</f>
-        <v/>
-      </c>
-      <c r="N71" s="141" t="n"/>
-      <c r="O71" s="141" t="n"/>
-      <c r="P71" s="141" t="n"/>
-      <c r="Q71" s="142" t="n"/>
-      <c r="R71" s="140" t="n"/>
-      <c r="S71" s="142">
-        <f>SUBTOTAL(9,S5:S43)</f>
-        <v/>
-      </c>
-      <c r="T71" s="142">
-        <f>SUBTOTAL(9,T5:T43)</f>
-        <v/>
-      </c>
-      <c r="U71" s="141" t="n"/>
-      <c r="V71" s="141" t="n"/>
-      <c r="W71" s="142">
-        <f>SUBTOTAL(9,W5:W43)</f>
-        <v/>
-      </c>
-      <c r="X71" s="147" t="n"/>
-      <c r="Y71" s="142">
-        <f>SUBTOTAL(9,Y5:Y43)</f>
-        <v/>
-      </c>
-      <c r="Z71" s="142">
-        <f>SUBTOTAL(9,Z5:Z43)</f>
-        <v/>
-      </c>
-      <c r="AA71" s="142">
-        <f>SUBTOTAL(9,AA5:AA43)</f>
-        <v/>
-      </c>
-      <c r="AB71" s="147" t="n"/>
-      <c r="AC71" s="141" t="n"/>
-      <c r="AD71" s="141" t="n"/>
-      <c r="AE71" s="141" t="n"/>
-      <c r="AF71" s="141" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="147" t="inlineStr">
+      <c r="B76" s="148" t="n"/>
+      <c r="C76" s="148" t="n"/>
+      <c r="D76" s="148" t="n"/>
+      <c r="E76" s="148" t="n"/>
+      <c r="F76" s="148" t="n"/>
+      <c r="G76" s="149" t="n"/>
+      <c r="H76" s="142">
+        <f>SUBTOTAL(9,H5:H44)</f>
+        <v/>
+      </c>
+      <c r="I76" s="141" t="n"/>
+      <c r="J76" s="142">
+        <f>SUBTOTAL(9,J5:J44)</f>
+        <v/>
+      </c>
+      <c r="K76" s="142">
+        <f>SUBTOTAL(9,K5:K44)</f>
+        <v/>
+      </c>
+      <c r="L76" s="142">
+        <f>SUBTOTAL(9,L5:L44)</f>
+        <v/>
+      </c>
+      <c r="M76" s="142">
+        <f>SUBTOTAL(9,M5:M44)</f>
+        <v/>
+      </c>
+      <c r="N76" s="141" t="n"/>
+      <c r="O76" s="141" t="n"/>
+      <c r="P76" s="141" t="n"/>
+      <c r="Q76" s="142" t="n"/>
+      <c r="R76" s="140" t="n"/>
+      <c r="S76" s="142">
+        <f>SUBTOTAL(9,S5:S44)</f>
+        <v/>
+      </c>
+      <c r="T76" s="142">
+        <f>SUBTOTAL(9,T5:T44)</f>
+        <v/>
+      </c>
+      <c r="U76" s="141" t="n"/>
+      <c r="V76" s="141" t="n"/>
+      <c r="W76" s="142">
+        <f>SUBTOTAL(9,W5:W44)</f>
+        <v/>
+      </c>
+      <c r="X76" s="147" t="n"/>
+      <c r="Y76" s="142">
+        <f>SUBTOTAL(9,Y5:Y44)</f>
+        <v/>
+      </c>
+      <c r="Z76" s="142">
+        <f>SUBTOTAL(9,Z5:Z44)</f>
+        <v/>
+      </c>
+      <c r="AA76" s="142">
+        <f>SUBTOTAL(9,AA5:AA44)</f>
+        <v/>
+      </c>
+      <c r="AB76" s="147" t="n"/>
+      <c r="AC76" s="141" t="n"/>
+      <c r="AD76" s="141" t="n"/>
+      <c r="AE76" s="141" t="n"/>
+      <c r="AF76" s="141" t="n"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="147" t="inlineStr">
         <is>
           <t>라이센스/워런티 합계</t>
         </is>
       </c>
-      <c r="B72" s="148" t="n"/>
-      <c r="C72" s="148" t="n"/>
-      <c r="D72" s="148" t="n"/>
-      <c r="E72" s="148" t="n"/>
-      <c r="F72" s="148" t="n"/>
-      <c r="G72" s="149" t="n"/>
-      <c r="H72" s="142">
-        <f>SUBTOTAL(9,H44:H66)</f>
-        <v/>
-      </c>
-      <c r="I72" s="141" t="n"/>
-      <c r="J72" s="142">
-        <f>SUBTOTAL(9,J40:J61)</f>
-        <v/>
-      </c>
-      <c r="K72" s="142">
-        <f>SUBTOTAL(9,K44:K66)</f>
-        <v/>
-      </c>
-      <c r="L72" s="142">
-        <f>SUBTOTAL(9,L44:L66)</f>
-        <v/>
-      </c>
-      <c r="M72" s="142">
-        <f>SUBTOTAL(9,M44:M66)</f>
-        <v/>
-      </c>
-      <c r="N72" s="141" t="n"/>
-      <c r="O72" s="141" t="n"/>
-      <c r="P72" s="141" t="n"/>
-      <c r="Q72" s="142" t="n"/>
-      <c r="R72" s="140" t="n"/>
-      <c r="S72" s="142">
-        <f>SUBTOTAL(9,S44:S66)</f>
-        <v/>
-      </c>
-      <c r="T72" s="142">
-        <f>SUBTOTAL(9,T44:T66)</f>
-        <v/>
-      </c>
-      <c r="U72" s="141" t="n"/>
-      <c r="V72" s="141" t="n"/>
-      <c r="W72" s="142">
-        <f>SUBTOTAL(9,W44:W66)</f>
-        <v/>
-      </c>
-      <c r="X72" s="147" t="n"/>
-      <c r="Y72" s="142">
-        <f>SUBTOTAL(9,Y44:Y66)</f>
-        <v/>
-      </c>
-      <c r="Z72" s="142">
-        <f>SUBTOTAL(9,Z44:Z66)</f>
-        <v/>
-      </c>
-      <c r="AA72" s="142">
-        <f>SUBTOTAL(9,AA44:AA66)</f>
-        <v/>
-      </c>
-      <c r="AB72" s="147" t="n"/>
-      <c r="AC72" s="141" t="n"/>
-      <c r="AD72" s="141" t="n"/>
-      <c r="AE72" s="141" t="n"/>
-      <c r="AF72" s="141" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="147" t="inlineStr">
+      <c r="B77" s="148" t="n"/>
+      <c r="C77" s="148" t="n"/>
+      <c r="D77" s="148" t="n"/>
+      <c r="E77" s="148" t="n"/>
+      <c r="F77" s="148" t="n"/>
+      <c r="G77" s="149" t="n"/>
+      <c r="H77" s="142">
+        <f>SUBTOTAL(9,H45:H71)</f>
+        <v/>
+      </c>
+      <c r="I77" s="141" t="n"/>
+      <c r="J77" s="142">
+        <f>SUBTOTAL(9,J45:J71)</f>
+        <v/>
+      </c>
+      <c r="K77" s="142">
+        <f>SUBTOTAL(9,K45:K71)</f>
+        <v/>
+      </c>
+      <c r="L77" s="142">
+        <f>SUBTOTAL(9,L45:L71)</f>
+        <v/>
+      </c>
+      <c r="M77" s="142">
+        <f>SUBTOTAL(9,M45:M71)</f>
+        <v/>
+      </c>
+      <c r="N77" s="141" t="n"/>
+      <c r="O77" s="141" t="n"/>
+      <c r="P77" s="141" t="n"/>
+      <c r="Q77" s="142" t="n"/>
+      <c r="R77" s="140" t="n"/>
+      <c r="S77" s="142">
+        <f>SUBTOTAL(9,S45:S71)</f>
+        <v/>
+      </c>
+      <c r="T77" s="142">
+        <f>SUBTOTAL(9,T45:T71)</f>
+        <v/>
+      </c>
+      <c r="U77" s="141" t="n"/>
+      <c r="V77" s="141" t="n"/>
+      <c r="W77" s="142">
+        <f>SUBTOTAL(9,W45:W71)</f>
+        <v/>
+      </c>
+      <c r="X77" s="147" t="n"/>
+      <c r="Y77" s="142">
+        <f>SUBTOTAL(9,Y45:Y71)</f>
+        <v/>
+      </c>
+      <c r="Z77" s="142">
+        <f>SUBTOTAL(9,Z45:Z71)</f>
+        <v/>
+      </c>
+      <c r="AA77" s="142">
+        <f>SUBTOTAL(9,AA45:AA71)</f>
+        <v/>
+      </c>
+      <c r="AB77" s="147" t="n"/>
+      <c r="AC77" s="141" t="n"/>
+      <c r="AD77" s="141" t="n"/>
+      <c r="AE77" s="141" t="n"/>
+      <c r="AF77" s="141" t="n"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="147" t="inlineStr">
         <is>
           <t>기타 합계</t>
         </is>
       </c>
-      <c r="B73" s="148" t="n"/>
-      <c r="C73" s="148" t="n"/>
-      <c r="D73" s="148" t="n"/>
-      <c r="E73" s="148" t="n"/>
-      <c r="F73" s="148" t="n"/>
-      <c r="G73" s="149" t="n"/>
-      <c r="H73" s="142">
-        <f>SUBTOTAL(9,H67:H70)</f>
-        <v/>
-      </c>
-      <c r="I73" s="141" t="n"/>
-      <c r="J73" s="142">
-        <f>SUBTOTAL(9,J62:J64)</f>
-        <v/>
-      </c>
-      <c r="K73" s="142">
-        <f>SUBTOTAL(9,K67:K70)</f>
-        <v/>
-      </c>
-      <c r="L73" s="142">
-        <f>SUBTOTAL(9,L67:L70)</f>
-        <v/>
-      </c>
-      <c r="M73" s="142">
-        <f>SUBTOTAL(9,M67:M70)</f>
-        <v/>
-      </c>
-      <c r="N73" s="141" t="n"/>
-      <c r="O73" s="141" t="n"/>
-      <c r="P73" s="141" t="n"/>
-      <c r="Q73" s="142" t="n"/>
-      <c r="R73" s="140" t="n"/>
-      <c r="S73" s="142">
-        <f>SUBTOTAL(9,S67:S70)</f>
-        <v/>
-      </c>
-      <c r="T73" s="142">
-        <f>SUBTOTAL(9,T67:T70)</f>
-        <v/>
-      </c>
-      <c r="U73" s="141" t="n"/>
-      <c r="V73" s="141" t="n"/>
-      <c r="W73" s="142">
-        <f>SUBTOTAL(9,W67:W70)</f>
-        <v/>
-      </c>
-      <c r="X73" s="147" t="n"/>
-      <c r="Y73" s="142">
-        <f>SUBTOTAL(9,Y67:Y70)</f>
-        <v/>
-      </c>
-      <c r="Z73" s="142">
-        <f>SUBTOTAL(9,Z67:Z70)</f>
-        <v/>
-      </c>
-      <c r="AA73" s="142">
-        <f>SUBTOTAL(9,AA67:AA70)</f>
-        <v/>
-      </c>
-      <c r="AB73" s="147" t="n"/>
-      <c r="AC73" s="141" t="n"/>
-      <c r="AD73" s="141" t="n"/>
-      <c r="AE73" s="141" t="n"/>
-      <c r="AF73" s="141" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="154" t="inlineStr">
+      <c r="B78" s="148" t="n"/>
+      <c r="C78" s="148" t="n"/>
+      <c r="D78" s="148" t="n"/>
+      <c r="E78" s="148" t="n"/>
+      <c r="F78" s="148" t="n"/>
+      <c r="G78" s="149" t="n"/>
+      <c r="H78" s="142">
+        <f>SUBTOTAL(9,H72:H75)</f>
+        <v/>
+      </c>
+      <c r="I78" s="141" t="n"/>
+      <c r="J78" s="142">
+        <f>SUBTOTAL(9,J72:J75)</f>
+        <v/>
+      </c>
+      <c r="K78" s="142">
+        <f>SUBTOTAL(9,K72:K75)</f>
+        <v/>
+      </c>
+      <c r="L78" s="142">
+        <f>SUBTOTAL(9,L72:L75)</f>
+        <v/>
+      </c>
+      <c r="M78" s="142">
+        <f>SUBTOTAL(9,M72:M75)</f>
+        <v/>
+      </c>
+      <c r="N78" s="141" t="n"/>
+      <c r="O78" s="141" t="n"/>
+      <c r="P78" s="141" t="n"/>
+      <c r="Q78" s="142" t="n"/>
+      <c r="R78" s="140" t="n"/>
+      <c r="S78" s="142">
+        <f>SUBTOTAL(9,S72:S75)</f>
+        <v/>
+      </c>
+      <c r="T78" s="142">
+        <f>SUBTOTAL(9,T72:T75)</f>
+        <v/>
+      </c>
+      <c r="U78" s="141" t="n"/>
+      <c r="V78" s="141" t="n"/>
+      <c r="W78" s="142">
+        <f>SUBTOTAL(9,W72:W75)</f>
+        <v/>
+      </c>
+      <c r="X78" s="147" t="n"/>
+      <c r="Y78" s="142">
+        <f>SUBTOTAL(9,Y72:Y75)</f>
+        <v/>
+      </c>
+      <c r="Z78" s="142">
+        <f>SUBTOTAL(9,Z72:Z75)</f>
+        <v/>
+      </c>
+      <c r="AA78" s="142">
+        <f>SUBTOTAL(9,AA72:AA75)</f>
+        <v/>
+      </c>
+      <c r="AB78" s="147" t="n"/>
+      <c r="AC78" s="141" t="n"/>
+      <c r="AD78" s="141" t="n"/>
+      <c r="AE78" s="141" t="n"/>
+      <c r="AF78" s="141" t="n"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="154" t="inlineStr">
         <is>
           <t>총 합계</t>
         </is>
       </c>
-      <c r="B74" s="148" t="n"/>
-      <c r="C74" s="148" t="n"/>
-      <c r="D74" s="148" t="n"/>
-      <c r="E74" s="148" t="n"/>
-      <c r="F74" s="148" t="n"/>
-      <c r="G74" s="149" t="n"/>
-      <c r="H74" s="146">
-        <f>SUBTOTAL(9,H5:H70)</f>
-        <v/>
-      </c>
-      <c r="I74" s="145" t="n"/>
-      <c r="J74" s="146">
-        <f>SUBTOTAL(9,J5:J64)</f>
-        <v/>
-      </c>
-      <c r="K74" s="146">
-        <f>SUBTOTAL(9,K5:K70)</f>
-        <v/>
-      </c>
-      <c r="L74" s="146">
-        <f>SUBTOTAL(9,L5:L70)</f>
-        <v/>
-      </c>
-      <c r="M74" s="146">
-        <f>SUBTOTAL(9,M5:M70)</f>
-        <v/>
-      </c>
-      <c r="N74" s="145" t="n"/>
-      <c r="O74" s="145" t="n"/>
-      <c r="P74" s="145" t="n"/>
-      <c r="Q74" s="146" t="n"/>
-      <c r="R74" s="144" t="n"/>
-      <c r="S74" s="146">
-        <f>SUBTOTAL(9,S5:S70)</f>
-        <v/>
-      </c>
-      <c r="T74" s="146">
-        <f>SUBTOTAL(9,T5:T70)</f>
-        <v/>
-      </c>
-      <c r="U74" s="145" t="n"/>
-      <c r="V74" s="145" t="n"/>
-      <c r="W74" s="146">
-        <f>SUBTOTAL(9,W5:W70)</f>
-        <v/>
-      </c>
-      <c r="X74" s="154" t="n"/>
-      <c r="Y74" s="146">
-        <f>SUBTOTAL(9,Y5:Y70)</f>
-        <v/>
-      </c>
-      <c r="Z74" s="146">
-        <f>SUBTOTAL(9,Z5:Z70)</f>
-        <v/>
-      </c>
-      <c r="AA74" s="146">
-        <f>SUBTOTAL(9,AA5:AA70)</f>
-        <v/>
-      </c>
-      <c r="AB74" s="154" t="n"/>
-      <c r="AC74" s="145" t="n"/>
-      <c r="AD74" s="145" t="n"/>
-      <c r="AE74" s="145" t="n"/>
-      <c r="AF74" s="145" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="39" t="n"/>
-      <c r="B75" s="39" t="n"/>
-      <c r="C75" s="39" t="n"/>
-      <c r="D75" s="39" t="n"/>
-      <c r="E75" s="39" t="n"/>
-      <c r="F75" s="39" t="n"/>
-      <c r="G75" s="39" t="n"/>
-      <c r="H75" s="39" t="n"/>
-      <c r="I75" s="39" t="n"/>
-      <c r="J75" s="39" t="n"/>
-      <c r="K75" s="39" t="n"/>
-      <c r="L75" s="39" t="n"/>
-      <c r="M75" s="39" t="n"/>
-      <c r="N75" s="39" t="n"/>
-      <c r="O75" s="39" t="n"/>
-      <c r="P75" s="39" t="n"/>
-      <c r="Q75" s="39" t="n"/>
-      <c r="R75" s="39" t="n"/>
-      <c r="S75" s="39" t="n"/>
-      <c r="T75" s="39" t="n"/>
-      <c r="U75" s="39" t="n"/>
-      <c r="V75" s="39" t="n"/>
-      <c r="W75" s="39" t="n"/>
-      <c r="X75" s="75" t="n"/>
-      <c r="Y75" s="39" t="n"/>
-      <c r="Z75" s="39" t="n"/>
-      <c r="AA75" s="39" t="n"/>
-      <c r="AB75" s="75" t="n"/>
-      <c r="AC75" s="39" t="n"/>
-      <c r="AD75" s="39" t="n"/>
-      <c r="AE75" s="39" t="n"/>
-      <c r="AF75" s="39" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="39" t="n"/>
-      <c r="B76" s="39" t="n"/>
-      <c r="C76" s="39" t="n"/>
-      <c r="D76" s="39" t="n"/>
-      <c r="E76" s="39" t="n"/>
-      <c r="F76" s="39" t="n"/>
-      <c r="G76" s="39" t="n"/>
-      <c r="H76" s="39" t="n"/>
-      <c r="I76" s="39" t="n"/>
-      <c r="J76" s="39" t="n"/>
-      <c r="K76" s="39" t="n"/>
-      <c r="L76" s="39" t="n"/>
-      <c r="M76" s="39" t="n"/>
-      <c r="N76" s="39" t="n"/>
-      <c r="O76" s="39" t="n"/>
-      <c r="P76" s="39" t="n"/>
-      <c r="Q76" s="39" t="n"/>
-      <c r="R76" s="39" t="n"/>
-      <c r="S76" s="39" t="n"/>
-      <c r="T76" s="39" t="n"/>
-      <c r="U76" s="39" t="n"/>
-      <c r="V76" s="39" t="n"/>
-      <c r="W76" s="39" t="n"/>
-      <c r="X76" s="75" t="n"/>
-      <c r="Y76" s="39" t="n"/>
-      <c r="Z76" s="39" t="n"/>
-      <c r="AA76" s="39" t="n"/>
-      <c r="AB76" s="75" t="n"/>
-      <c r="AC76" s="39" t="n"/>
-      <c r="AD76" s="39" t="n"/>
-      <c r="AE76" s="39" t="n"/>
-      <c r="AF76" s="39" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="39" t="n"/>
-      <c r="B77" s="39" t="n"/>
-      <c r="C77" s="39" t="n"/>
-      <c r="D77" s="39" t="n"/>
-      <c r="E77" s="39" t="n"/>
-      <c r="F77" s="39" t="n"/>
-      <c r="G77" s="39" t="n"/>
-      <c r="H77" s="39" t="n"/>
-      <c r="I77" s="39" t="n"/>
-      <c r="J77" s="39" t="n"/>
-      <c r="K77" s="39" t="n"/>
-      <c r="L77" s="39" t="n"/>
-      <c r="M77" s="39" t="n"/>
-      <c r="N77" s="39" t="n"/>
-      <c r="O77" s="39" t="n"/>
-      <c r="P77" s="39" t="n"/>
-      <c r="Q77" s="39" t="n"/>
-      <c r="R77" s="39" t="n"/>
-      <c r="S77" s="39" t="n"/>
-      <c r="T77" s="39" t="n"/>
-      <c r="U77" s="39" t="n"/>
-      <c r="V77" s="39" t="n"/>
-      <c r="W77" s="39" t="n"/>
-      <c r="X77" s="75" t="n"/>
-      <c r="Y77" s="39" t="n"/>
-      <c r="Z77" s="39" t="n"/>
-      <c r="AA77" s="39" t="n"/>
-      <c r="AB77" s="75" t="n"/>
-      <c r="AC77" s="39" t="n"/>
-      <c r="AD77" s="39" t="n"/>
-      <c r="AE77" s="39" t="n"/>
-      <c r="AF77" s="39" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="39" t="n"/>
-      <c r="B78" s="39" t="n"/>
-      <c r="C78" s="39" t="n"/>
-      <c r="D78" s="39" t="n"/>
-      <c r="E78" s="39" t="n"/>
-      <c r="F78" s="39" t="n"/>
-      <c r="G78" s="39" t="n"/>
-      <c r="H78" s="39" t="n"/>
-      <c r="I78" s="39" t="n"/>
-      <c r="J78" s="39" t="n"/>
-      <c r="K78" s="39" t="n"/>
-      <c r="L78" s="39" t="n"/>
-      <c r="M78" s="39" t="n"/>
-      <c r="N78" s="39" t="n"/>
-      <c r="O78" s="39" t="n"/>
-      <c r="P78" s="39" t="n"/>
-      <c r="Q78" s="39" t="n"/>
-      <c r="R78" s="39" t="n"/>
-      <c r="S78" s="39" t="n"/>
-      <c r="T78" s="39" t="n"/>
-      <c r="U78" s="39" t="n"/>
-      <c r="V78" s="39" t="n"/>
-      <c r="W78" s="39" t="n"/>
-      <c r="X78" s="75" t="n"/>
-      <c r="Y78" s="39" t="n"/>
-      <c r="Z78" s="39" t="n"/>
-      <c r="AA78" s="39" t="n"/>
-      <c r="AB78" s="75" t="n"/>
-      <c r="AC78" s="39" t="n"/>
-      <c r="AD78" s="39" t="n"/>
-      <c r="AE78" s="39" t="n"/>
-      <c r="AF78" s="39" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="39" t="n"/>
-      <c r="B79" s="39" t="n"/>
-      <c r="C79" s="39" t="n"/>
-      <c r="D79" s="39" t="n"/>
-      <c r="E79" s="39" t="n"/>
-      <c r="F79" s="39" t="n"/>
-      <c r="G79" s="39" t="n"/>
-      <c r="H79" s="39" t="n"/>
-      <c r="I79" s="39" t="n"/>
-      <c r="J79" s="39" t="n"/>
-      <c r="K79" s="39" t="n"/>
-      <c r="L79" s="39" t="n"/>
-      <c r="M79" s="39" t="n"/>
-      <c r="N79" s="39" t="n"/>
-      <c r="O79" s="39" t="n"/>
-      <c r="P79" s="39" t="n"/>
-      <c r="Q79" s="39" t="n"/>
-      <c r="R79" s="39" t="n"/>
-      <c r="S79" s="39" t="n"/>
-      <c r="T79" s="39" t="n"/>
-      <c r="U79" s="39" t="n"/>
-      <c r="V79" s="39" t="n"/>
-      <c r="W79" s="39" t="n"/>
-      <c r="X79" s="75" t="n"/>
-      <c r="Y79" s="39" t="n"/>
-      <c r="Z79" s="39" t="n"/>
-      <c r="AA79" s="39" t="n"/>
-      <c r="AB79" s="75" t="n"/>
-      <c r="AC79" s="39" t="n"/>
-      <c r="AD79" s="39" t="n"/>
-      <c r="AE79" s="39" t="n"/>
-      <c r="AF79" s="39" t="n"/>
+      <c r="B79" s="148" t="n"/>
+      <c r="C79" s="148" t="n"/>
+      <c r="D79" s="148" t="n"/>
+      <c r="E79" s="148" t="n"/>
+      <c r="F79" s="148" t="n"/>
+      <c r="G79" s="149" t="n"/>
+      <c r="H79" s="146">
+        <f>SUBTOTAL(9,H5:H75)</f>
+        <v/>
+      </c>
+      <c r="I79" s="145" t="n"/>
+      <c r="J79" s="146">
+        <f>SUBTOTAL(9,J5:J75)</f>
+        <v/>
+      </c>
+      <c r="K79" s="146">
+        <f>SUBTOTAL(9,K5:K75)</f>
+        <v/>
+      </c>
+      <c r="L79" s="146">
+        <f>SUBTOTAL(9,L5:L75)</f>
+        <v/>
+      </c>
+      <c r="M79" s="146">
+        <f>SUBTOTAL(9,M5:M75)</f>
+        <v/>
+      </c>
+      <c r="N79" s="145" t="n"/>
+      <c r="O79" s="145" t="n"/>
+      <c r="P79" s="145" t="n"/>
+      <c r="Q79" s="146" t="n"/>
+      <c r="R79" s="144" t="n"/>
+      <c r="S79" s="146">
+        <f>SUBTOTAL(9,S5:S75)</f>
+        <v/>
+      </c>
+      <c r="T79" s="146">
+        <f>SUBTOTAL(9,T5:T75)</f>
+        <v/>
+      </c>
+      <c r="U79" s="145" t="n"/>
+      <c r="V79" s="145" t="n"/>
+      <c r="W79" s="146">
+        <f>SUBTOTAL(9,W5:W75)</f>
+        <v/>
+      </c>
+      <c r="X79" s="154" t="n"/>
+      <c r="Y79" s="146">
+        <f>SUBTOTAL(9,Y5:Y75)</f>
+        <v/>
+      </c>
+      <c r="Z79" s="146">
+        <f>SUBTOTAL(9,Z5:Z75)</f>
+        <v/>
+      </c>
+      <c r="AA79" s="146">
+        <f>SUBTOTAL(9,AA5:AA75)</f>
+        <v/>
+      </c>
+      <c r="AB79" s="154" t="n"/>
+      <c r="AC79" s="145" t="n"/>
+      <c r="AD79" s="145" t="n"/>
+      <c r="AE79" s="145" t="n"/>
+      <c r="AF79" s="145" t="n"/>
     </row>
     <row r="93">
       <c r="M93" s="40" t="n"/>
@@ -10591,14 +11068,14 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="G3:N3"/>
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A79:G79"/>
     <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A78:G78"/>
     <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="A72:G72"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A76:G76"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="O3:W3"/>
     <mergeCell ref="A2:AF2"/>
@@ -11809,6 +12286,202 @@
       </c>
       <c r="L25" s="228" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="224" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="224" t="inlineStr">
+        <is>
+          <t>CPO702</t>
+        </is>
+      </c>
+      <c r="C26" s="225" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D26" s="225" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="E26" s="226" t="n">
+        <v>32715</v>
+      </c>
+      <c r="F26" s="224" t="inlineStr">
+        <is>
+          <t>EW CP2215/CP2309-RGB 24대 (롯데 영천 외 8개소)</t>
+        </is>
+      </c>
+      <c r="G26" s="227" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H26" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="227" t="n">
+        <v>46192</v>
+      </c>
+      <c r="J26" s="227" t="n">
+        <v>46752</v>
+      </c>
+      <c r="K26" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="L26" s="228" t="n"/>
+      <c r="M26" s="160" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="224" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="224" t="inlineStr">
+        <is>
+          <t>GPO486</t>
+        </is>
+      </c>
+      <c r="C27" s="225" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D27" s="225" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="E27" s="226" t="n">
+        <v>450</v>
+      </c>
+      <c r="F27" s="224" t="inlineStr">
+        <is>
+          <t>TMS-1000 License Ext 5screens (메가박스 경산 하양)</t>
+        </is>
+      </c>
+      <c r="G27" s="227" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H27" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="227" t="n">
+        <v>46204</v>
+      </c>
+      <c r="J27" s="227" t="n">
+        <v>46568</v>
+      </c>
+      <c r="K27" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="L27" s="228" t="n"/>
+      <c r="M27" s="160" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="224" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="224" t="inlineStr">
+        <is>
+          <t>GPO484</t>
+        </is>
+      </c>
+      <c r="C28" s="225" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D28" s="225" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="E28" s="226" t="n">
+        <v>7407.81</v>
+      </c>
+      <c r="F28" s="224" t="inlineStr">
+        <is>
+          <t>SR-1000/SX-4000 Warranty Ext 11대 (CGV 진주혁신 외)</t>
+        </is>
+      </c>
+      <c r="G28" s="227" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H28" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="227" t="n">
+        <v>46156</v>
+      </c>
+      <c r="J28" s="227" t="n">
+        <v>46752</v>
+      </c>
+      <c r="K28" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="L28" s="228" t="n"/>
+      <c r="M28" s="160" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="224" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="224" t="inlineStr">
+        <is>
+          <t>GPO489</t>
+        </is>
+      </c>
+      <c r="C29" s="225" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D29" s="225" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="E29" s="226" t="n">
+        <v>3320</v>
+      </c>
+      <c r="F29" s="224" t="inlineStr">
+        <is>
+          <t>TMS License 7사이트 32screens (메가박스 삼천포 외)</t>
+        </is>
+      </c>
+      <c r="G29" s="227" t="n">
+        <v>46196</v>
+      </c>
+      <c r="H29" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="227" t="n">
+        <v>46204</v>
+      </c>
+      <c r="J29" s="227" t="n">
+        <v>46568</v>
+      </c>
+      <c r="K29" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="L29" s="228" t="n"/>
+      <c r="M29" s="160" t="n"/>
+    </row>
     <row r="70">
       <c r="M70" s="40" t="n"/>
     </row>
@@ -13474,6 +14147,50 @@
         </is>
       </c>
       <c r="J38" s="292" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="241" t="inlineStr">
+        <is>
+          <t>14008-26-101317M</t>
+        </is>
+      </c>
+      <c r="B39" s="241" t="inlineStr">
+        <is>
+          <t>APO001</t>
+        </is>
+      </c>
+      <c r="C39" s="242" t="n">
+        <v>12400</v>
+      </c>
+      <c r="D39" s="243">
+        <f>C39/C39</f>
+        <v/>
+      </c>
+      <c r="E39" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F39" s="244" t="n">
+        <v>43010</v>
+      </c>
+      <c r="G39" s="241" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="H39" s="244" t="n">
+        <v>692650</v>
+      </c>
+      <c r="I39" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J39" s="241" t="n"/>
+      <c r="K39" s="160" t="n"/>
+      <c r="L39" s="160" t="n"/>
+      <c r="M39" s="160" t="n"/>
     </row>
     <row r="71">
       <c r="M71" s="40" t="n"/>
@@ -20786,7 +21503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -20829,7 +21546,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="205" t="inlineStr">
         <is>
-          <t>업데이트: 2026-06-16 (관세청 고시환율)</t>
+          <t>업데이트: 2026-07-02 (관세청 고시환율)</t>
         </is>
       </c>
       <c r="B4" s="148" t="n"/>
@@ -21449,6 +22166,38 @@
       </c>
       <c r="D43" s="211" t="n">
         <v>1531.46</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="282" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B44" s="282" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C44" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D44" s="211" t="n">
+        <v>1516.02</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="282" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B45" s="282" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C45" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D45" s="211" t="n">
+        <v>1538.3</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -1901,7 +1901,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-07-02  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-07-07  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="148" t="n"/>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="T4" s="155" t="inlineStr">
         <is>
-          <t>부가세(KRW)</t>
+          <t>부가세(KRW,참고)</t>
         </is>
       </c>
       <c r="U4" s="150" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="Z4" s="155" t="inlineStr">
         <is>
-          <t>소계:관부가세+통관(KRW)</t>
+          <t>소계:관세+통관(KRW)</t>
         </is>
       </c>
       <c r="AA4" s="155" t="inlineStr">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="9">
-        <f>S5+T5+W5</f>
+        <f>S5+W5</f>
         <v/>
       </c>
       <c r="AA5" s="123">
@@ -2378,7 +2378,7 @@
         <v>2470670</v>
       </c>
       <c r="Z6" s="9">
-        <f>S6+T6+W6</f>
+        <f>S6+W6</f>
         <v/>
       </c>
       <c r="AA6" s="10">
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="9">
-        <f>S7+T7+W7</f>
+        <f>S7+W7</f>
         <v/>
       </c>
       <c r="AA7" s="10">
@@ -2632,7 +2632,7 @@
         <v>590823</v>
       </c>
       <c r="Z8" s="9">
-        <f>S8+T8+W8</f>
+        <f>S8+W8</f>
         <v/>
       </c>
       <c r="AA8" s="10">
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="Z9" s="18">
-        <f>S9+T9+W9</f>
+        <f>S9+W9</f>
         <v/>
       </c>
       <c r="AA9" s="18">
@@ -2880,7 +2880,7 @@
         <v>4477</v>
       </c>
       <c r="Z10" s="9">
-        <f>S10+T10+W10</f>
+        <f>S10+W10</f>
         <v/>
       </c>
       <c r="AA10" s="10">
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="9">
-        <f>S11+T11+W11</f>
+        <f>S11+W11</f>
         <v/>
       </c>
       <c r="AA11" s="10">
@@ -3134,7 +3134,7 @@
         <v>581438</v>
       </c>
       <c r="Z12" s="9">
-        <f>S12+T12+W12</f>
+        <f>S12+W12</f>
         <v/>
       </c>
       <c r="AA12" s="10">
@@ -3261,7 +3261,7 @@
         <v>2385057</v>
       </c>
       <c r="Z13" s="9">
-        <f>S13+T13+W13</f>
+        <f>S13+W13</f>
         <v/>
       </c>
       <c r="AA13" s="10">
@@ -3388,7 +3388,7 @@
         <v>1864148</v>
       </c>
       <c r="Z14" s="9">
-        <f>S14+T14+W14</f>
+        <f>S14+W14</f>
         <v/>
       </c>
       <c r="AA14" s="10">
@@ -3515,7 +3515,7 @@
         <v>426904</v>
       </c>
       <c r="Z15" s="9">
-        <f>S15+T15+W15</f>
+        <f>S15+W15</f>
         <v/>
       </c>
       <c r="AA15" s="10">
@@ -3642,7 +3642,7 @@
         <v>2690702</v>
       </c>
       <c r="Z16" s="9">
-        <f>S16+T16+W16</f>
+        <f>S16+W16</f>
         <v/>
       </c>
       <c r="AA16" s="10">
@@ -3769,7 +3769,7 @@
         <v>1379682</v>
       </c>
       <c r="Z17" s="9">
-        <f>S17+T17+W17</f>
+        <f>S17+W17</f>
         <v/>
       </c>
       <c r="AA17" s="10">
@@ -3896,7 +3896,7 @@
         <v>162080</v>
       </c>
       <c r="Z18" s="9">
-        <f>S18+T18+W18</f>
+        <f>S18+W18</f>
         <v/>
       </c>
       <c r="AA18" s="10">
@@ -4023,7 +4023,7 @@
         <v>136050</v>
       </c>
       <c r="Z19" s="9">
-        <f>S19+T19+W19</f>
+        <f>S19+W19</f>
         <v/>
       </c>
       <c r="AA19" s="10">
@@ -4150,7 +4150,7 @@
         <v>1553086</v>
       </c>
       <c r="Z20" s="9">
-        <f>S20+T20+W20</f>
+        <f>S20+W20</f>
         <v/>
       </c>
       <c r="AA20" s="10">
@@ -4277,7 +4277,7 @@
         <v>2649525</v>
       </c>
       <c r="Z21" s="9">
-        <f>S21+T21+W21</f>
+        <f>S21+W21</f>
         <v/>
       </c>
       <c r="AA21" s="10">
@@ -4404,7 +4404,7 @@
         <v>1561040</v>
       </c>
       <c r="Z22" s="9">
-        <f>S22+T22+W22</f>
+        <f>S22+W22</f>
         <v/>
       </c>
       <c r="AA22" s="10">
@@ -4529,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="Z23" s="18">
-        <f>S23+T23+W23</f>
+        <f>S23+W23</f>
         <v/>
       </c>
       <c r="AA23" s="18">
@@ -4652,7 +4652,7 @@
         <v>1232133</v>
       </c>
       <c r="Z24" s="9">
-        <f>S24+T24+W24</f>
+        <f>S24+W24</f>
         <v/>
       </c>
       <c r="AA24" s="10">
@@ -4779,7 +4779,7 @@
         <v>6128</v>
       </c>
       <c r="Z25" s="9">
-        <f>S25+T25+W25</f>
+        <f>S25+W25</f>
         <v/>
       </c>
       <c r="AA25" s="10">
@@ -4906,7 +4906,7 @@
         <v>904960</v>
       </c>
       <c r="Z26" s="9">
-        <f>S26+T26+W26</f>
+        <f>S26+W26</f>
         <v/>
       </c>
       <c r="AA26" s="10">
@@ -5033,7 +5033,7 @@
         <v>6264783</v>
       </c>
       <c r="Z27" s="9">
-        <f>S27+T27+W27</f>
+        <f>S27+W27</f>
         <v/>
       </c>
       <c r="AA27" s="10">
@@ -5160,7 +5160,7 @@
         <v>1454605</v>
       </c>
       <c r="Z28" s="9">
-        <f>S28+T28+W28</f>
+        <f>S28+W28</f>
         <v/>
       </c>
       <c r="AA28" s="10">
@@ -5283,7 +5283,7 @@
         <v>174806</v>
       </c>
       <c r="Z29" s="9">
-        <f>S29+T29+W29</f>
+        <f>S29+W29</f>
         <v/>
       </c>
       <c r="AA29" s="10">
@@ -5398,7 +5398,7 @@
         <v>3909069</v>
       </c>
       <c r="Z30" s="82">
-        <f>S30+T30+W30</f>
+        <f>S30+W30</f>
         <v/>
       </c>
       <c r="AA30" s="83">
@@ -5513,7 +5513,7 @@
         <v>846621</v>
       </c>
       <c r="Z31" s="82">
-        <f>S31+T31+W31</f>
+        <f>S31+W31</f>
         <v/>
       </c>
       <c r="AA31" s="83">
@@ -5622,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="Z32" s="82">
-        <f>S32+T32+W32</f>
+        <f>S32+W32</f>
         <v/>
       </c>
       <c r="AA32" s="83">
@@ -5729,7 +5729,7 @@
         <v>3103207</v>
       </c>
       <c r="Z33" s="128">
-        <f>S33+T33+W33</f>
+        <f>S33+W33</f>
         <v/>
       </c>
       <c r="AA33" s="131">
@@ -5846,7 +5846,7 @@
         <v>3270326</v>
       </c>
       <c r="Z34" s="128">
-        <f>S34+T34+W34</f>
+        <f>S34+W34</f>
         <v/>
       </c>
       <c r="AA34" s="131">
@@ -5957,7 +5957,7 @@
         <v>3636072</v>
       </c>
       <c r="Z35" s="128">
-        <f>S35+T35+W35</f>
+        <f>S35+W35</f>
         <v/>
       </c>
       <c r="AA35" s="131">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="Z36" s="128">
-        <f>S36+T36+W36</f>
+        <f>S36+W36</f>
         <v/>
       </c>
       <c r="AA36" s="131">
@@ -6169,7 +6169,7 @@
         <v>3759954</v>
       </c>
       <c r="Z37" s="213">
-        <f>S37+T37+W37</f>
+        <f>S37+W37</f>
         <v/>
       </c>
       <c r="AA37" s="214">
@@ -6284,7 +6284,7 @@
         <v>2259958</v>
       </c>
       <c r="Z38" s="213">
-        <f>S38+T38+W38</f>
+        <f>S38+W38</f>
         <v/>
       </c>
       <c r="AA38" s="214">
@@ -6401,7 +6401,7 @@
         <v>159250</v>
       </c>
       <c r="Z39" s="128">
-        <f>S39+T39+W39</f>
+        <f>S39+W39</f>
         <v/>
       </c>
       <c r="AA39" s="131">
@@ -6526,7 +6526,7 @@
         <v>2898404</v>
       </c>
       <c r="Z40" s="128">
-        <f>S40+T40+W40</f>
+        <f>S40+W40</f>
         <v/>
       </c>
       <c r="AA40" s="131">
@@ -6641,7 +6641,7 @@
         <v>14471173</v>
       </c>
       <c r="Z41" s="128">
-        <f>S41+T41+W41</f>
+        <f>S41+W41</f>
         <v/>
       </c>
       <c r="AA41" s="131">
@@ -6756,7 +6756,7 @@
         <v>3412382</v>
       </c>
       <c r="Z42" s="128">
-        <f>S42+T42+W42</f>
+        <f>S42+W42</f>
         <v/>
       </c>
       <c r="AA42" s="131">
@@ -6873,7 +6873,7 @@
         <v>692650</v>
       </c>
       <c r="Z43" s="128">
-        <f>S43+T43+W43</f>
+        <f>S43+W43</f>
         <v/>
       </c>
       <c r="AA43" s="131">
@@ -6984,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="Z44" s="128">
-        <f>S44+T44+W44</f>
+        <f>S44+W44</f>
         <v/>
       </c>
       <c r="AA44" s="131">
@@ -7099,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="302">
-        <f>S45+T45+W45</f>
+        <f>S45+W45</f>
         <v/>
       </c>
       <c r="AA45" s="302">
@@ -7226,7 +7226,7 @@
         <v>0</v>
       </c>
       <c r="Z46" s="302">
-        <f>S46+T46+W46</f>
+        <f>S46+W46</f>
         <v/>
       </c>
       <c r="AA46" s="302">
@@ -7353,7 +7353,7 @@
         <v>0</v>
       </c>
       <c r="Z47" s="302">
-        <f>S47+T47+W47</f>
+        <f>S47+W47</f>
         <v/>
       </c>
       <c r="AA47" s="302">
@@ -7480,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="Z48" s="302">
-        <f>S48+T48+W48</f>
+        <f>S48+W48</f>
         <v/>
       </c>
       <c r="AA48" s="302">
@@ -7607,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="Z49" s="302">
-        <f>S49+T49+W49</f>
+        <f>S49+W49</f>
         <v/>
       </c>
       <c r="AA49" s="302">
@@ -7734,7 +7734,7 @@
         <v>0</v>
       </c>
       <c r="Z50" s="302">
-        <f>S50+T50+W50</f>
+        <f>S50+W50</f>
         <v/>
       </c>
       <c r="AA50" s="302">
@@ -7867,7 +7867,7 @@
         <v>0</v>
       </c>
       <c r="Z51" s="302">
-        <f>S51+T51+W51</f>
+        <f>S51+W51</f>
         <v/>
       </c>
       <c r="AA51" s="302">
@@ -7994,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="Z52" s="302">
-        <f>S52+T52+W52</f>
+        <f>S52+W52</f>
         <v/>
       </c>
       <c r="AA52" s="302">
@@ -8127,7 +8127,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="302">
-        <f>S53+T53+W53</f>
+        <f>S53+W53</f>
         <v/>
       </c>
       <c r="AA53" s="302">
@@ -8254,7 +8254,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="302">
-        <f>S54+T54+W54</f>
+        <f>S54+W54</f>
         <v/>
       </c>
       <c r="AA54" s="302">
@@ -8381,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="302">
-        <f>S55+T55+W55</f>
+        <f>S55+W55</f>
         <v/>
       </c>
       <c r="AA55" s="302">
@@ -8508,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="Z56" s="302">
-        <f>S56+T56+W56</f>
+        <f>S56+W56</f>
         <v/>
       </c>
       <c r="AA56" s="302">
@@ -8635,7 +8635,7 @@
         <v>0</v>
       </c>
       <c r="Z57" s="302">
-        <f>S57+T57+W57</f>
+        <f>S57+W57</f>
         <v/>
       </c>
       <c r="AA57" s="302">
@@ -8762,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="302">
-        <f>S58+T58+W58</f>
+        <f>S58+W58</f>
         <v/>
       </c>
       <c r="AA58" s="302">
@@ -8889,7 +8889,7 @@
         <v>0</v>
       </c>
       <c r="Z59" s="302">
-        <f>S59+T59+W59</f>
+        <f>S59+W59</f>
         <v/>
       </c>
       <c r="AA59" s="302">
@@ -9016,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="Z60" s="302">
-        <f>S60+T60+W60</f>
+        <f>S60+W60</f>
         <v/>
       </c>
       <c r="AA60" s="302">
@@ -9143,7 +9143,7 @@
         <v>0</v>
       </c>
       <c r="Z61" s="302">
-        <f>S61+T61+W61</f>
+        <f>S61+W61</f>
         <v/>
       </c>
       <c r="AA61" s="302">
@@ -9268,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="308">
-        <f>S62+T62+W62</f>
+        <f>S62+W62</f>
         <v/>
       </c>
       <c r="AA62" s="308">
@@ -9395,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="Z63" s="308">
-        <f>S63+T63+W63</f>
+        <f>S63+W63</f>
         <v/>
       </c>
       <c r="AA63" s="308">
@@ -9500,7 +9500,7 @@
         <v>0</v>
       </c>
       <c r="Z64" s="136">
-        <f>S64+T64+W64</f>
+        <f>S64+W64</f>
         <v/>
       </c>
       <c r="AA64" s="136">
@@ -9605,7 +9605,7 @@
         <v>0</v>
       </c>
       <c r="Z65" s="136">
-        <f>S65+T65+W65</f>
+        <f>S65+W65</f>
         <v/>
       </c>
       <c r="AA65" s="136">
@@ -9710,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="Z66" s="136">
-        <f>S66+T66+W66</f>
+        <f>S66+W66</f>
         <v/>
       </c>
       <c r="AA66" s="136">
@@ -9823,7 +9823,7 @@
         <v>0</v>
       </c>
       <c r="Z67" s="136">
-        <f>S67+T67+W67</f>
+        <f>S67+W67</f>
         <v/>
       </c>
       <c r="AA67" s="136">
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="Z68" s="136">
-        <f>S68+T68+W68</f>
+        <f>S68+W68</f>
         <v/>
       </c>
       <c r="AA68" s="136">
@@ -10053,7 +10053,7 @@
         <v>0</v>
       </c>
       <c r="Z69" s="136">
-        <f>S69+T69+W69</f>
+        <f>S69+W69</f>
         <v/>
       </c>
       <c r="AA69" s="136">
@@ -10168,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="Z70" s="136">
-        <f>S70+T70+W70</f>
+        <f>S70+W70</f>
         <v/>
       </c>
       <c r="AA70" s="136">
@@ -10283,7 +10283,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="136">
-        <f>S71+T71+W71</f>
+        <f>S71+W71</f>
         <v/>
       </c>
       <c r="AA71" s="136">
@@ -10412,7 +10412,7 @@
         <v>0</v>
       </c>
       <c r="Z72" s="290">
-        <f>S72+T72+W72</f>
+        <f>S72+W72</f>
         <v/>
       </c>
       <c r="AA72" s="290">
@@ -10539,7 +10539,7 @@
         <v>216006</v>
       </c>
       <c r="Z73" s="290">
-        <f>S73+T73+W73</f>
+        <f>S73+W73</f>
         <v/>
       </c>
       <c r="AA73" s="290">
@@ -10655,7 +10655,7 @@
         <v>5002612</v>
       </c>
       <c r="Z74" s="222">
-        <f>S74+T74+W74</f>
+        <f>S74+W74</f>
         <v/>
       </c>
       <c r="AA74" s="222">
@@ -10760,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="Z75" s="290">
-        <f>S75+T75+W75</f>
+        <f>S75+W75</f>
         <v/>
       </c>
       <c r="AA75" s="290">
@@ -11062,6 +11062,19 @@
       <c r="AE79" s="145" t="n"/>
       <c r="AF79" s="145" t="n"/>
     </row>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
     <row r="93">
       <c r="M93" s="40" t="n"/>
     </row>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -2356,10 +2356,8 @@
       <c r="T6" s="9" t="n">
         <v>20784342</v>
       </c>
-      <c r="U6" s="174" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
+      <c r="U6" s="174" t="n">
+        <v>46017</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -2483,10 +2481,8 @@
       <c r="T7" s="9" t="n">
         <v>1352610</v>
       </c>
-      <c r="U7" s="174" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
+      <c r="U7" s="174" t="n">
+        <v>46011</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -2610,10 +2606,8 @@
       <c r="T8" s="9" t="n">
         <v>756850</v>
       </c>
-      <c r="U8" s="174" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
+      <c r="U8" s="174" t="n">
+        <v>46004</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -2737,9 +2731,7 @@
       <c r="T9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="176" t="n">
-        <v>0</v>
-      </c>
+      <c r="U9" s="176" t="n"/>
       <c r="V9" s="12" t="inlineStr">
         <is>
           <t>-</t>
@@ -2858,10 +2850,8 @@
       <c r="T10" s="9" t="n">
         <v>37658</v>
       </c>
-      <c r="U10" s="174" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
+      <c r="U10" s="174" t="n">
+        <v>46017</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2985,10 +2975,8 @@
       <c r="T11" s="9" t="n">
         <v>399770</v>
       </c>
-      <c r="U11" s="174" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="U11" s="174" t="n">
+        <v>46038</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -3112,10 +3100,8 @@
       <c r="T12" s="9" t="n">
         <v>831820</v>
       </c>
-      <c r="U12" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
+      <c r="U12" s="174" t="n">
+        <v>46105</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -3239,10 +3225,8 @@
       <c r="T13" s="9" t="n">
         <v>19976300</v>
       </c>
-      <c r="U13" s="174" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="U13" s="174" t="n">
+        <v>46042</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -3366,10 +3350,8 @@
       <c r="T14" s="9" t="n">
         <v>3156262</v>
       </c>
-      <c r="U14" s="174" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
+      <c r="U14" s="174" t="n">
+        <v>46030</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -3493,10 +3475,8 @@
       <c r="T15" s="9" t="n">
         <v>722808</v>
       </c>
-      <c r="U15" s="174" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
+      <c r="U15" s="174" t="n">
+        <v>46030</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -3620,10 +3600,8 @@
       <c r="T16" s="9" t="n">
         <v>1704871</v>
       </c>
-      <c r="U16" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
+      <c r="U16" s="174" t="n">
+        <v>46087</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -3747,10 +3725,8 @@
       <c r="T17" s="9" t="n">
         <v>874189</v>
       </c>
-      <c r="U17" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
+      <c r="U17" s="174" t="n">
+        <v>46087</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -3874,10 +3850,8 @@
       <c r="T18" s="9" t="n">
         <v>409790</v>
       </c>
-      <c r="U18" s="174" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="U18" s="174" t="n">
+        <v>46057</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -4001,10 +3975,8 @@
       <c r="T19" s="9" t="n">
         <v>250080</v>
       </c>
-      <c r="U19" s="174" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
+      <c r="U19" s="174" t="n">
+        <v>46071</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -4128,10 +4100,8 @@
       <c r="T20" s="9" t="n">
         <v>1752040</v>
       </c>
-      <c r="U20" s="174" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
+      <c r="U20" s="174" t="n">
+        <v>46079</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -4255,10 +4225,8 @@
       <c r="T21" s="9" t="n">
         <v>42329590</v>
       </c>
-      <c r="U21" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
+      <c r="U21" s="174" t="n">
+        <v>46088</v>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
@@ -4382,10 +4350,8 @@
       <c r="T22" s="9" t="n">
         <v>1493440</v>
       </c>
-      <c r="U22" s="174" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
+      <c r="U22" s="174" t="n">
+        <v>46067</v>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
@@ -4509,9 +4475,7 @@
       <c r="T23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="176" t="n">
-        <v>0</v>
-      </c>
+      <c r="U23" s="176" t="n"/>
       <c r="V23" s="12" t="inlineStr">
         <is>
           <t>-</t>
@@ -4630,10 +4594,8 @@
       <c r="T24" s="9" t="n">
         <v>5395574</v>
       </c>
-      <c r="U24" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
+      <c r="U24" s="174" t="n">
+        <v>46110</v>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
@@ -4757,10 +4719,8 @@
       <c r="T25" s="9" t="n">
         <v>26836</v>
       </c>
-      <c r="U25" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
+      <c r="U25" s="174" t="n">
+        <v>46110</v>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
@@ -4884,10 +4844,8 @@
       <c r="T26" s="9" t="n">
         <v>4747530</v>
       </c>
-      <c r="U26" s="174" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
+      <c r="U26" s="174" t="n">
+        <v>46119</v>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
@@ -5011,10 +4969,8 @@
       <c r="T27" s="9" t="n">
         <v>350480</v>
       </c>
-      <c r="U27" s="174" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
+      <c r="U27" s="174" t="n">
+        <v>46120</v>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
@@ -5138,10 +5094,8 @@
       <c r="T28" s="9" t="n">
         <v>317310</v>
       </c>
-      <c r="U28" s="174" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
+      <c r="U28" s="174" t="n">
+        <v>46119</v>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
@@ -7079,9 +7033,7 @@
       <c r="T45" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U45" s="298" t="n"/>
       <c r="V45" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7206,9 +7158,7 @@
       <c r="T46" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U46" s="298" t="n"/>
       <c r="V46" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7333,9 +7283,7 @@
       <c r="T47" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U47" s="298" t="n"/>
       <c r="V47" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7460,9 +7408,7 @@
       <c r="T48" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U48" s="298" t="n"/>
       <c r="V48" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7587,9 +7533,7 @@
       <c r="T49" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U49" s="298" t="n"/>
       <c r="V49" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7714,9 +7658,7 @@
       <c r="T50" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U50" s="298" t="n"/>
       <c r="V50" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7847,9 +7789,7 @@
       <c r="T51" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U51" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U51" s="298" t="n"/>
       <c r="V51" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7974,9 +7914,7 @@
       <c r="T52" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U52" s="298" t="n"/>
       <c r="V52" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8107,9 +8045,7 @@
       <c r="T53" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U53" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U53" s="298" t="n"/>
       <c r="V53" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8234,9 +8170,7 @@
       <c r="T54" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U54" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U54" s="298" t="n"/>
       <c r="V54" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8361,9 +8295,7 @@
       <c r="T55" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U55" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U55" s="298" t="n"/>
       <c r="V55" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8488,9 +8420,7 @@
       <c r="T56" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U56" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U56" s="298" t="n"/>
       <c r="V56" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8615,9 +8545,7 @@
       <c r="T57" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U57" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U57" s="298" t="n"/>
       <c r="V57" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8742,9 +8670,7 @@
       <c r="T58" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U58" s="298" t="n"/>
       <c r="V58" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8869,9 +8795,7 @@
       <c r="T59" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U59" s="298" t="n"/>
       <c r="V59" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8996,9 +8920,7 @@
       <c r="T60" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U60" s="298" t="n"/>
       <c r="V60" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -9123,9 +9045,7 @@
       <c r="T61" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U61" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U61" s="298" t="n"/>
       <c r="V61" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -10392,9 +10312,7 @@
       <c r="T72" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="U72" s="286" t="n">
-        <v>0</v>
-      </c>
+      <c r="U72" s="286" t="n"/>
       <c r="V72" s="284" t="inlineStr">
         <is>
           <t>-</t>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -5665,7 +5665,7 @@
       <c r="T33" s="128" t="n">
         <v>52140300</v>
       </c>
-      <c r="U33" s="182" t="n"/>
+      <c r="U33" s="181" t="n"/>
       <c r="V33" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5782,7 +5782,7 @@
       <c r="T34" s="128" t="n">
         <v>118665800</v>
       </c>
-      <c r="U34" s="182" t="n"/>
+      <c r="U34" s="181" t="n"/>
       <c r="V34" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5893,7 +5893,7 @@
       <c r="T35" s="128" t="n">
         <v>14902330</v>
       </c>
-      <c r="U35" s="182" t="n"/>
+      <c r="U35" s="181" t="n"/>
       <c r="V35" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5998,7 +5998,7 @@
       <c r="T36" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="182" t="n"/>
+      <c r="U36" s="181" t="n"/>
       <c r="V36" s="129" t="n"/>
       <c r="W36" s="128" t="n">
         <v>0</v>
@@ -6337,7 +6337,7 @@
       <c r="T39" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U39" s="182" t="n"/>
+      <c r="U39" s="181" t="n"/>
       <c r="V39" s="129" t="inlineStr">
         <is>
           <t>-</t>
@@ -6462,7 +6462,7 @@
       <c r="T40" s="128" t="n">
         <v>52536040</v>
       </c>
-      <c r="U40" s="182" t="n"/>
+      <c r="U40" s="181" t="n"/>
       <c r="V40" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6577,7 +6577,7 @@
       <c r="T41" s="128" t="n">
         <v>8891915</v>
       </c>
-      <c r="U41" s="182" t="n"/>
+      <c r="U41" s="181" t="n"/>
       <c r="V41" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6692,7 +6692,7 @@
       <c r="T42" s="128" t="n">
         <v>2096763</v>
       </c>
-      <c r="U42" s="182" t="n"/>
+      <c r="U42" s="181" t="n"/>
       <c r="V42" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6807,7 +6807,7 @@
       <c r="T43" s="128" t="n">
         <v>1959600</v>
       </c>
-      <c r="U43" s="182" t="n">
+      <c r="U43" s="181" t="n">
         <v>46202</v>
       </c>
       <c r="V43" s="129" t="inlineStr">
@@ -6920,7 +6920,7 @@
       <c r="T44" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U44" s="182" t="n"/>
+      <c r="U44" s="181" t="n"/>
       <c r="V44" s="129" t="inlineStr">
         <is>
           <t>-</t>
@@ -9406,7 +9406,7 @@
       <c r="T64" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U64" s="189" t="n"/>
+      <c r="U64" s="188" t="n"/>
       <c r="V64" s="137" t="n"/>
       <c r="W64" s="136" t="n">
         <v>0</v>
@@ -9511,7 +9511,7 @@
       <c r="T65" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="189" t="n"/>
+      <c r="U65" s="188" t="n"/>
       <c r="V65" s="137" t="n"/>
       <c r="W65" s="136" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
       <c r="T66" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U66" s="189" t="n"/>
+      <c r="U66" s="188" t="n"/>
       <c r="V66" s="137" t="n"/>
       <c r="W66" s="136" t="n">
         <v>0</v>
@@ -9729,7 +9729,7 @@
       <c r="T67" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U67" s="189" t="n"/>
+      <c r="U67" s="188" t="n"/>
       <c r="V67" s="137" t="n"/>
       <c r="W67" s="136" t="n">
         <v>0</v>
@@ -9840,7 +9840,7 @@
       <c r="T68" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U68" s="189" t="n"/>
+      <c r="U68" s="188" t="n"/>
       <c r="V68" s="137" t="inlineStr">
         <is>
           <t>-</t>
@@ -9955,7 +9955,7 @@
       <c r="T69" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U69" s="189" t="n"/>
+      <c r="U69" s="188" t="n"/>
       <c r="V69" s="137" t="inlineStr">
         <is>
           <t>-</t>
@@ -10070,7 +10070,7 @@
       <c r="T70" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U70" s="189" t="n"/>
+      <c r="U70" s="188" t="n"/>
       <c r="V70" s="137" t="inlineStr">
         <is>
           <t>-</t>
@@ -10185,7 +10185,7 @@
       <c r="T71" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U71" s="189" t="n"/>
+      <c r="U71" s="188" t="n"/>
       <c r="V71" s="137" t="inlineStr">
         <is>
           <t>-</t>
@@ -10742,7 +10742,7 @@
         <f>SUBTOTAL(9,T5:T44)</f>
         <v/>
       </c>
-      <c r="U76" s="141" t="n"/>
+      <c r="U76" s="147" t="n"/>
       <c r="V76" s="141" t="n"/>
       <c r="W76" s="142">
         <f>SUBTOTAL(9,W5:W44)</f>
@@ -10813,7 +10813,7 @@
         <f>SUBTOTAL(9,T45:T71)</f>
         <v/>
       </c>
-      <c r="U77" s="141" t="n"/>
+      <c r="U77" s="147" t="n"/>
       <c r="V77" s="141" t="n"/>
       <c r="W77" s="142">
         <f>SUBTOTAL(9,W45:W71)</f>
@@ -10884,7 +10884,7 @@
         <f>SUBTOTAL(9,T72:T75)</f>
         <v/>
       </c>
-      <c r="U78" s="141" t="n"/>
+      <c r="U78" s="147" t="n"/>
       <c r="V78" s="141" t="n"/>
       <c r="W78" s="142">
         <f>SUBTOTAL(9,W72:W75)</f>
@@ -10955,7 +10955,7 @@
         <f>SUBTOTAL(9,T5:T75)</f>
         <v/>
       </c>
-      <c r="U79" s="145" t="n"/>
+      <c r="U79" s="154" t="n"/>
       <c r="V79" s="145" t="n"/>
       <c r="W79" s="146">
         <f>SUBTOTAL(9,W5:W75)</f>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="310">
+  <cellXfs count="312">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1370,6 +1370,12 @@
     </xf>
     <xf numFmtId="3" fontId="20" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5627,7 +5633,7 @@
       <c r="H33" s="126" t="n">
         <v>351274</v>
       </c>
-      <c r="I33" s="126" t="n">
+      <c r="I33" s="310" t="n">
         <v>1518</v>
       </c>
       <c r="J33" s="128" t="n">
@@ -5643,10 +5649,10 @@
         <v>8000</v>
       </c>
       <c r="N33" s="129" t="n"/>
-      <c r="O33" s="182" t="n">
+      <c r="O33" s="181" t="n">
         <v>46141</v>
       </c>
-      <c r="P33" s="129" t="inlineStr">
+      <c r="P33" s="124" t="inlineStr">
         <is>
           <t>14008-26-101140M</t>
         </is>
@@ -5666,7 +5672,7 @@
         <v>52140300</v>
       </c>
       <c r="U33" s="181" t="n"/>
-      <c r="V33" s="129" t="inlineStr">
+      <c r="V33" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -5697,7 +5703,7 @@
         <f>ROUND(AA33/AB33,0)</f>
         <v/>
       </c>
-      <c r="AD33" s="129" t="inlineStr">
+      <c r="AD33" s="124" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -5740,7 +5746,7 @@
       <c r="H34" s="126" t="n">
         <v>807233</v>
       </c>
-      <c r="I34" s="126">
+      <c r="I34" s="310">
         <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
@@ -5760,10 +5766,10 @@
         <v/>
       </c>
       <c r="N34" s="129" t="n"/>
-      <c r="O34" s="182" t="n">
+      <c r="O34" s="181" t="n">
         <v>46157</v>
       </c>
-      <c r="P34" s="129" t="inlineStr">
+      <c r="P34" s="124" t="inlineStr">
         <is>
           <t>14008-26-101168M</t>
         </is>
@@ -5783,7 +5789,7 @@
         <v>118665800</v>
       </c>
       <c r="U34" s="181" t="n"/>
-      <c r="V34" s="129" t="inlineStr">
+      <c r="V34" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -5814,7 +5820,7 @@
         <f>ROUND(AA34/AB34,0)</f>
         <v/>
       </c>
-      <c r="AD34" s="129" t="inlineStr">
+      <c r="AD34" s="124" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5855,7 +5861,7 @@
       <c r="H35" s="126" t="n">
         <v>98800</v>
       </c>
-      <c r="I35" s="126" t="n">
+      <c r="I35" s="310" t="n">
         <v>1502.8</v>
       </c>
       <c r="J35" s="128" t="n">
@@ -5871,10 +5877,10 @@
         <v>7973</v>
       </c>
       <c r="N35" s="129" t="n"/>
-      <c r="O35" s="182" t="n">
+      <c r="O35" s="181" t="n">
         <v>46146</v>
       </c>
-      <c r="P35" s="129" t="inlineStr">
+      <c r="P35" s="124" t="inlineStr">
         <is>
           <t>14008-26-101148M</t>
         </is>
@@ -5894,7 +5900,7 @@
         <v>14902330</v>
       </c>
       <c r="U35" s="181" t="n"/>
-      <c r="V35" s="129" t="inlineStr">
+      <c r="V35" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -5925,7 +5931,7 @@
         <f>ROUND(AA35/AB35,0)</f>
         <v/>
       </c>
-      <c r="AD35" s="129" t="inlineStr">
+      <c r="AD35" s="124" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5966,7 +5972,7 @@
       <c r="H36" s="126" t="n">
         <v>90</v>
       </c>
-      <c r="I36" s="126" t="n">
+      <c r="I36" s="310" t="n">
         <v>1502.8</v>
       </c>
       <c r="J36" s="128" t="n">
@@ -6297,7 +6303,7 @@
       <c r="H39" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="126">
+      <c r="I39" s="310">
         <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
@@ -6316,7 +6322,7 @@
         <f>IFERROR(VLOOKUP(B39,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N39" s="129" t="inlineStr">
+      <c r="N39" s="124" t="inlineStr">
         <is>
           <t>JNIOR Model 410 (IPO017, FedEx 4/21 발송분)</t>
         </is>
@@ -6338,7 +6344,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="181" t="n"/>
-      <c r="V39" s="129" t="inlineStr">
+      <c r="V39" s="124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6370,12 +6376,12 @@
         <v/>
       </c>
       <c r="AD39" s="129" t="n"/>
-      <c r="AE39" s="182" t="inlineStr">
+      <c r="AE39" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF39" s="182" t="inlineStr">
+      <c r="AF39" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6416,7 +6422,7 @@
       <c r="H40" s="126" t="n">
         <v>346792</v>
       </c>
-      <c r="I40" s="126">
+      <c r="I40" s="310">
         <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
@@ -6435,15 +6441,15 @@
         <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N40" s="129" t="inlineStr">
+      <c r="N40" s="124" t="inlineStr">
         <is>
           <t>CP4420-RGB 4K Projector 8대 + TPC Touch 8 (롯데 렌탈 4차)</t>
         </is>
       </c>
-      <c r="O40" s="182" t="n">
+      <c r="O40" s="181" t="n">
         <v>46177</v>
       </c>
-      <c r="P40" s="129" t="inlineStr">
+      <c r="P40" s="124" t="inlineStr">
         <is>
           <t>14008-26-101227M</t>
         </is>
@@ -6463,7 +6469,7 @@
         <v>52536040</v>
       </c>
       <c r="U40" s="181" t="n"/>
-      <c r="V40" s="129" t="inlineStr">
+      <c r="V40" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -6494,7 +6500,7 @@
         <f>ROUND(AA40/AB40,0)</f>
         <v/>
       </c>
-      <c r="AD40" s="129" t="inlineStr">
+      <c r="AD40" s="124" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6535,7 +6541,7 @@
       <c r="H41" s="126" t="n">
         <v>49138.8</v>
       </c>
-      <c r="I41" s="126" t="n">
+      <c r="I41" s="310" t="n">
         <v>1517.3</v>
       </c>
       <c r="J41" s="128" t="n">
@@ -6550,15 +6556,15 @@
       <c r="M41" s="128" t="n">
         <v>6473</v>
       </c>
-      <c r="N41" s="129" t="inlineStr">
+      <c r="N41" s="124" t="inlineStr">
         <is>
           <t>MAG 음향장비 loudspeakers 108EA (롯데컬처웍스)</t>
         </is>
       </c>
-      <c r="O41" s="182" t="n">
+      <c r="O41" s="181" t="n">
         <v>46188</v>
       </c>
-      <c r="P41" s="129" t="inlineStr">
+      <c r="P41" s="124" t="inlineStr">
         <is>
           <t>14008-26-101275M</t>
         </is>
@@ -6578,7 +6584,7 @@
         <v>8891915</v>
       </c>
       <c r="U41" s="181" t="n"/>
-      <c r="V41" s="129" t="inlineStr">
+      <c r="V41" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -6609,7 +6615,7 @@
         <f>ROUND(AA41/AB41,0)</f>
         <v/>
       </c>
-      <c r="AD41" s="129" t="inlineStr">
+      <c r="AD41" s="124" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6650,7 +6656,7 @@
       <c r="H42" s="126" t="n">
         <v>11587.2</v>
       </c>
-      <c r="I42" s="126" t="n">
+      <c r="I42" s="310" t="n">
         <v>1517.3</v>
       </c>
       <c r="J42" s="128" t="n">
@@ -6665,15 +6671,15 @@
       <c r="M42" s="128" t="n">
         <v>1527</v>
       </c>
-      <c r="N42" s="129" t="inlineStr">
+      <c r="N42" s="124" t="inlineStr">
         <is>
           <t>MAG 음향장비 loudspeakers 29EA (CJ 미래원)</t>
         </is>
       </c>
-      <c r="O42" s="182" t="n">
+      <c r="O42" s="181" t="n">
         <v>46188</v>
       </c>
-      <c r="P42" s="129" t="inlineStr">
+      <c r="P42" s="124" t="inlineStr">
         <is>
           <t>14008-26-101275M</t>
         </is>
@@ -6693,7 +6699,7 @@
         <v>2096763</v>
       </c>
       <c r="U42" s="181" t="n"/>
-      <c r="V42" s="129" t="inlineStr">
+      <c r="V42" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -6724,7 +6730,7 @@
         <f>ROUND(AA42/AB42,0)</f>
         <v/>
       </c>
-      <c r="AD42" s="129" t="inlineStr">
+      <c r="AD42" s="124" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6765,7 +6771,7 @@
       <c r="H43" s="126" t="n">
         <v>12400</v>
       </c>
-      <c r="I43" s="126" t="n">
+      <c r="I43" s="310" t="n">
         <v>1517.1</v>
       </c>
       <c r="J43" s="128" t="n">
@@ -6780,15 +6786,15 @@
       <c r="M43" s="128" t="n">
         <v>8000</v>
       </c>
-      <c r="N43" s="129" t="inlineStr">
+      <c r="N43" s="124" t="inlineStr">
         <is>
           <t>S20-C2220-BEAB 레이저모듈 2set (CP2220)</t>
         </is>
       </c>
-      <c r="O43" s="182" t="n">
+      <c r="O43" s="181" t="n">
         <v>46202</v>
       </c>
-      <c r="P43" s="129" t="inlineStr">
+      <c r="P43" s="124" t="inlineStr">
         <is>
           <t>14008-26-101317M</t>
         </is>
@@ -6810,7 +6816,7 @@
       <c r="U43" s="181" t="n">
         <v>46202</v>
       </c>
-      <c r="V43" s="129" t="inlineStr">
+      <c r="V43" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -6841,7 +6847,7 @@
         <f>ROUND(AA43/AB43,0)</f>
         <v/>
       </c>
-      <c r="AD43" s="129" t="inlineStr">
+      <c r="AD43" s="124" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6884,7 +6890,7 @@
       <c r="H44" s="126" t="n">
         <v>14730</v>
       </c>
-      <c r="I44" s="126" t="n">
+      <c r="I44" s="310" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="128" t="n">
@@ -6899,7 +6905,7 @@
       <c r="M44" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="N44" s="129" t="inlineStr">
+      <c r="N44" s="124" t="inlineStr">
         <is>
           <t>AIB-3000 Cinema Audio Processor 9EA (롯데 인천검단 6 / CJ미래원 1 / RNR 2)</t>
         </is>
@@ -6921,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="U44" s="181" t="n"/>
-      <c r="V44" s="129" t="inlineStr">
+      <c r="V44" s="124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9374,7 +9380,7 @@
       <c r="H64" s="134" t="n">
         <v>180</v>
       </c>
-      <c r="I64" s="134" t="n">
+      <c r="I64" s="311" t="n">
         <v>1518.9</v>
       </c>
       <c r="J64" s="136" t="n">
@@ -9434,15 +9440,15 @@
         <f>ROUND(AA64/AB64,0)</f>
         <v/>
       </c>
-      <c r="AD64" s="137" t="inlineStr">
+      <c r="AD64" s="132" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE64" s="189" t="n">
+      <c r="AE64" s="188" t="n">
         <v>46143</v>
       </c>
-      <c r="AF64" s="189" t="n">
+      <c r="AF64" s="188" t="n">
         <v>46507</v>
       </c>
     </row>
@@ -9479,7 +9485,7 @@
       <c r="H65" s="134" t="n">
         <v>250</v>
       </c>
-      <c r="I65" s="134" t="n">
+      <c r="I65" s="311" t="n">
         <v>1502.8</v>
       </c>
       <c r="J65" s="136" t="n">
@@ -9539,15 +9545,15 @@
         <f>ROUND(AA65/AB65,0)</f>
         <v/>
       </c>
-      <c r="AD65" s="137" t="inlineStr">
+      <c r="AD65" s="132" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE65" s="189" t="n">
+      <c r="AE65" s="188" t="n">
         <v>46143</v>
       </c>
-      <c r="AF65" s="189" t="n">
+      <c r="AF65" s="188" t="n">
         <v>49795</v>
       </c>
     </row>
@@ -9584,7 +9590,7 @@
       <c r="H66" s="134" t="n">
         <v>500</v>
       </c>
-      <c r="I66" s="134" t="n">
+      <c r="I66" s="311" t="n">
         <v>1525.3</v>
       </c>
       <c r="J66" s="136" t="n">
@@ -9644,17 +9650,17 @@
         <f>ROUND(AA66/AB66,0)</f>
         <v/>
       </c>
-      <c r="AD66" s="137" t="inlineStr">
+      <c r="AD66" s="132" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE66" s="189" t="inlineStr">
+      <c r="AE66" s="188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF66" s="189" t="inlineStr">
+      <c r="AF66" s="188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9693,7 +9699,7 @@
       <c r="H67" s="134" t="n">
         <v>540</v>
       </c>
-      <c r="I67" s="134" t="n">
+      <c r="I67" s="311" t="n">
         <v>1516.8</v>
       </c>
       <c r="J67" s="136" t="n">
@@ -9708,7 +9714,7 @@
       <c r="M67" s="136" t="n">
         <v>2118</v>
       </c>
-      <c r="N67" s="137" t="inlineStr">
+      <c r="N67" s="132" t="inlineStr">
         <is>
           <t>TMS-1000 License 6 screens (CGV 안동)</t>
         </is>
@@ -9757,15 +9763,15 @@
         <f>ROUND(AA67/AB67,0)</f>
         <v/>
       </c>
-      <c r="AD67" s="137" t="inlineStr">
+      <c r="AD67" s="132" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE67" s="189" t="n">
+      <c r="AE67" s="188" t="n">
         <v>46143</v>
       </c>
-      <c r="AF67" s="189" t="n">
+      <c r="AF67" s="188" t="n">
         <v>46507</v>
       </c>
     </row>
@@ -9804,7 +9810,7 @@
       <c r="H68" s="134" t="n">
         <v>32715</v>
       </c>
-      <c r="I68" s="134" t="n">
+      <c r="I68" s="311" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="136" t="n">
@@ -9819,7 +9825,7 @@
       <c r="M68" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N68" s="137" t="inlineStr">
+      <c r="N68" s="132" t="inlineStr">
         <is>
           <t>EW CP2215/CP2309-RGB 24대 (롯데 영천/CineQ 청라/CGV 동두천 외)</t>
         </is>
@@ -9841,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="188" t="n"/>
-      <c r="V68" s="137" t="inlineStr">
+      <c r="V68" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9872,15 +9878,15 @@
         <f>ROUND(AA68/AB68,0)</f>
         <v/>
       </c>
-      <c r="AD68" s="137" t="inlineStr">
+      <c r="AD68" s="132" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE68" s="189" t="n">
+      <c r="AE68" s="188" t="n">
         <v>46192</v>
       </c>
-      <c r="AF68" s="189" t="n">
+      <c r="AF68" s="188" t="n">
         <v>46752</v>
       </c>
     </row>
@@ -9919,7 +9925,7 @@
       <c r="H69" s="134" t="n">
         <v>450</v>
       </c>
-      <c r="I69" s="134" t="n">
+      <c r="I69" s="311" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="136" t="n">
@@ -9934,7 +9940,7 @@
       <c r="M69" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N69" s="137" t="inlineStr">
+      <c r="N69" s="132" t="inlineStr">
         <is>
           <t>TMS-1000 License Extension 5screens (메가박스 경산 하양)</t>
         </is>
@@ -9956,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="188" t="n"/>
-      <c r="V69" s="137" t="inlineStr">
+      <c r="V69" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9987,15 +9993,15 @@
         <f>ROUND(AA69/AB69,0)</f>
         <v/>
       </c>
-      <c r="AD69" s="137" t="inlineStr">
+      <c r="AD69" s="132" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="AE69" s="189" t="n">
+      <c r="AE69" s="188" t="n">
         <v>46204</v>
       </c>
-      <c r="AF69" s="189" t="n">
+      <c r="AF69" s="188" t="n">
         <v>46568</v>
       </c>
     </row>
@@ -10034,7 +10040,7 @@
       <c r="H70" s="134" t="n">
         <v>7407.81</v>
       </c>
-      <c r="I70" s="134" t="n">
+      <c r="I70" s="311" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="136" t="n">
@@ -10049,7 +10055,7 @@
       <c r="M70" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N70" s="137" t="inlineStr">
+      <c r="N70" s="132" t="inlineStr">
         <is>
           <t>SR-1000/SX-4000 Warranty Ext 11대 (CGV 진주혁신/합천/구례)</t>
         </is>
@@ -10071,7 +10077,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="188" t="n"/>
-      <c r="V70" s="137" t="inlineStr">
+      <c r="V70" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10102,15 +10108,15 @@
         <f>ROUND(AA70/AB70,0)</f>
         <v/>
       </c>
-      <c r="AD70" s="137" t="inlineStr">
+      <c r="AD70" s="132" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE70" s="189" t="n">
+      <c r="AE70" s="188" t="n">
         <v>46156</v>
       </c>
-      <c r="AF70" s="189" t="n">
+      <c r="AF70" s="188" t="n">
         <v>46752</v>
       </c>
     </row>
@@ -10149,7 +10155,7 @@
       <c r="H71" s="134" t="n">
         <v>3320</v>
       </c>
-      <c r="I71" s="134" t="n">
+      <c r="I71" s="311" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="136" t="n">
@@ -10164,7 +10170,7 @@
       <c r="M71" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N71" s="137" t="inlineStr">
+      <c r="N71" s="132" t="inlineStr">
         <is>
           <t>TMS License 7사이트 32screens (메가박스 삼천포/CGV 대구수성 외)</t>
         </is>
@@ -10186,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="188" t="n"/>
-      <c r="V71" s="137" t="inlineStr">
+      <c r="V71" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10217,15 +10223,15 @@
         <f>ROUND(AA71/AB71,0)</f>
         <v/>
       </c>
-      <c r="AD71" s="137" t="inlineStr">
+      <c r="AD71" s="132" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="AE71" s="189" t="n">
+      <c r="AE71" s="188" t="n">
         <v>46204</v>
       </c>
-      <c r="AF71" s="189" t="n">
+      <c r="AF71" s="188" t="n">
         <v>46568</v>
       </c>
     </row>
@@ -12413,6 +12419,46 @@
       <c r="L29" s="228" t="n"/>
       <c r="M29" s="160" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
     <row r="70">
       <c r="M70" s="40" t="n"/>
     </row>
@@ -14123,6 +14169,37 @@
       <c r="L39" s="160" t="n"/>
       <c r="M39" s="160" t="n"/>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
     <row r="71">
       <c r="M71" s="40" t="n"/>
     </row>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="FxRateTable">'환율'!$A$7:$D$45</definedName>
     <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$40</definedName>
     <definedName name="RemitTable2">'외화송금내역'!$A$43:$L$97</definedName>
+    <definedName name="FxRateTable">'환율'!$A$7:$D$50</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1457,8 +1457,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>RNR 재무팀</author>
-    <author>import-cost-calculator</author>
-    <author>RNR</author>
   </authors>
   <commentList>
     <comment ref="S5" authorId="0" shapeId="0">
@@ -1552,11 +1550,26 @@
 지출결의 2026-1344, 6/9 집행</t>
       </text>
     </comment>
+    <comment ref="Q32" authorId="0" shapeId="0">
+      <text>
+        <t>신고환율 1,686.20 = 신고필증 14008-26-101205M 56번 (EUR 기준). USD 주간 고시환율 미적용 건이라 값으로 직접 기입</t>
+      </text>
+    </comment>
+    <comment ref="S32" authorId="0" shapeId="0">
+      <text>
+        <t>관세 0원 — 한-EU FTA 협정세율(세율구분 FEU1 이가) 적용, HS 8414.59-9000 (신고필증 14008-26-101205M, 수리일 2026-07-27)</t>
+      </text>
+    </comment>
     <comment ref="S35" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8543 — 디지털시네마 서버/IMB
 (정보기술협정 양허품목)</t>
+      </text>
+    </comment>
+    <comment ref="Y36" authorId="0" shapeId="0">
+      <text>
+        <t>FedEx 2026-06월 인보이스 48,920원 (AWB 577262341268, 2026-05-04 GDC HK 발송) 지출결의 2026-1597</t>
       </text>
     </comment>
     <comment ref="S37" authorId="0" shapeId="0">
@@ -1580,21 +1593,21 @@
 인보이스/송금/수입신고 미도래 - 미확정 건</t>
       </text>
     </comment>
-    <comment ref="S41" authorId="1" shapeId="0">
+    <comment ref="S41" authorId="0" shapeId="0">
       <text>
         <t>관세 0원 — 수입신고필증 세율구분 'C'(WTO협정/양허세율) 적용
 HS 8518 음향기기 (loudspeakers/amplifier)
 원산지: 우크라이나(UA-A)</t>
       </text>
     </comment>
-    <comment ref="S42" authorId="1" shapeId="0">
+    <comment ref="S42" authorId="0" shapeId="0">
       <text>
         <t>관세 0원 — 수입신고필증 세율구분 'C'(WTO협정/양허세율) 적용
 HS 8518 음향기기 (loudspeakers/amplifier)
 원산지: 우크라이나(UA-A)</t>
       </text>
     </comment>
-    <comment ref="S43" authorId="2" shapeId="0">
+    <comment ref="S43" authorId="0" shapeId="0">
       <text>
         <t>관세 0원 — 수입신고필증 세율구분 'C'(가가, WTO/ITA 양허) 적용
 HS 8529.90-6010 프로젝터 부품 (레이저광원모듈)
@@ -1602,30 +1615,67 @@
 (신고번호 14008-26-101317M, 수리일 2026-06-29)</t>
       </text>
     </comment>
-    <comment ref="S68" authorId="0" shapeId="0">
+    <comment ref="S44" authorId="0" shapeId="0">
+      <text>
+        <t>ITA(정보기술협정) 관세면제 HS 8517.62-9020 / 8471.80-9000 — 시네마 오디오프로세서 및 HDMI 모듈 (신고필증 세율구분 C 가가)</t>
+      </text>
+    </comment>
+    <comment ref="T44" authorId="0" shapeId="0">
+      <text>
+        <t>수입신고 23176-26-472403M 결제금액 USD 15,870 (인보이스 GDC-INV-2606-005 USD 14,730 + HDMI Module 3EA USD 1,140). 납부고지서(2026-07-10 재발행) 기준 가산세(보정이자) 79,130원 별도 부과, 취득원가 제외</t>
+      </text>
+    </comment>
+    <comment ref="H45" authorId="0" shapeId="0">
+      <text>
+        <t>수입신고 23176-26-606930M 결제금액 USD 5,499 중 ASSY FAN 2EA 귀속분. 관세/부가세는 USD 비율 안분 (CPO701 54 : CPO703 5,445)</t>
+      </text>
+    </comment>
+    <comment ref="H46" authorId="0" shapeId="0">
+      <text>
+        <t>수입신고 23176-26-606930M 결제금액 USD 5,499 중 Lens 1EA 귀속분. 관세/부가세는 USD 비율 안분 (CPO701 54 : CPO703 5,445)</t>
+      </text>
+    </comment>
+    <comment ref="S48" authorId="0" shapeId="0">
+      <text>
+        <t>ITA(정보기술협정) 관세면제 HS 8529.90-6029 — 디지털시네마 서버 부품 (신고필증 세율구분 C 가가)</t>
+      </text>
+    </comment>
+    <comment ref="H49" authorId="0" shapeId="0">
+      <text>
+        <t>수입신고 총 결제금액 USD 335,110 중 지출결의 2026-1667 물량내역 기준 GPO482 귀속분. 물량내역 미기재 2개 란(Advertising Board USD 200, Coaxial Cable USD 126)은 GPO482에 합산 (총액 일치 목적)</t>
+      </text>
+    </comment>
+    <comment ref="S49" authorId="0" shapeId="0">
+      <text>
+        <t>관세 0원 — 신고필증 14008-26-101364M 세율구분 C(가가, WTO/ITA 양허) 및 FCN1(한중 FTA 협정세율) 적용</t>
+      </text>
+    </comment>
+    <comment ref="S50" authorId="0" shapeId="0">
+      <text>
+        <t>관세 0원 — 신고필증 14008-26-101364M 세율구분 FCN1(한중 FTA 협정세율) 적용, HS 9004.90-2000</t>
+      </text>
+    </comment>
+    <comment ref="H78" authorId="0" shapeId="0">
+      <text>
+        <t>GDC-INV-2606-025 : gross USD 33,309 차감 구형서버 보상판매 Credit GDC-CN-2604-001 USD 28,000 = 실지급 USD 5,309</t>
+      </text>
+    </comment>
+    <comment ref="S80" authorId="0" shapeId="0">
       <text>
         <t>관세율 0.00% - 세율구분 C(가가, WTO/ITA 양허)
 수리반환 재수입 건, 부가세만 과세
 (신고필증 2235626351613M)</t>
       </text>
     </comment>
-    <comment ref="Y68" authorId="0" shapeId="0">
+    <comment ref="Y80" authorId="0" shapeId="0">
       <text>
         <t>DHL 2026-05월 인보이스 (AWB 5094871784 = 수입신고필증 B/L 일치)
 GDC RMA 수리반환 건, 지출결의 2026-1344, 6/9 집행</t>
       </text>
     </comment>
-    <comment ref="S73" authorId="0" shapeId="0">
+    <comment ref="Y81" authorId="0" shapeId="0">
       <text>
-        <t>관세율 0.00% - 세율구분 C(가가, WTO/ITA 양허)
-수리반환 재수입 건, 부가세만 과세
-(신고필증 2235626351613M)</t>
-      </text>
-    </comment>
-    <comment ref="Y73" authorId="0" shapeId="0">
-      <text>
-        <t>DHL 2026-05월 인보이스 (AWB 5094871784 = 수입신고필증 B/L 일치)
-GDC RMA 수리반환 건, 지출결의 2026-1344, 6/9 집행</t>
+        <t>진로직스 운임 정정 추가정산금 230,890원 반영 (정정 전 4,827,602 → 정정 후 5,058,492, HFIKUO26401C, 입항지 부산 변경분) 지출결의 2026-1536</t>
       </text>
     </comment>
   </commentList>
@@ -1841,7 +1891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF93"/>
+  <dimension ref="A1:AF100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" style="160" min="1" max="1"/>
@@ -1907,7 +1957,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-07-07  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-08-04  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="148" t="n"/>
@@ -5548,11 +5598,16 @@
           <t>AXC 200 ELICENT VENTILATORE/FAN (60EA, EUR)</t>
         </is>
       </c>
-      <c r="O32" s="179" t="n"/>
-      <c r="P32" s="78" t="n"/>
-      <c r="Q32" s="80">
-        <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE),""))</f>
-        <v/>
+      <c r="O32" s="179" t="n">
+        <v>46230</v>
+      </c>
+      <c r="P32" s="78" t="inlineStr">
+        <is>
+          <t>14008-26-101205M</t>
+        </is>
+      </c>
+      <c r="Q32" s="80" t="n">
+        <v>1686.2</v>
       </c>
       <c r="R32" s="80">
         <f>IF(P32="","",H32)</f>
@@ -5562,12 +5617,12 @@
         <v>0</v>
       </c>
       <c r="T32" s="82" t="n">
-        <v>0</v>
+        <v>814230</v>
       </c>
       <c r="U32" s="179" t="n"/>
       <c r="V32" s="78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>조운관세사무소</t>
         </is>
       </c>
       <c r="W32" s="82" t="n">
@@ -5575,7 +5630,7 @@
       </c>
       <c r="X32" s="78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y32" s="82" t="n">
@@ -5596,13 +5651,17 @@
         <f>ROUND(AA32/AB32,0)</f>
         <v/>
       </c>
-      <c r="AD32" s="78" t="n"/>
+      <c r="AD32" s="78" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
       <c r="AE32" s="179" t="n"/>
       <c r="AF32" s="179" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="124" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B33" s="124" t="inlineStr">
         <is>
@@ -5713,7 +5772,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="124" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B34" s="124" t="inlineStr">
         <is>
@@ -5830,7 +5889,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="124" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B35" s="124" t="inlineStr">
         <is>
@@ -5941,7 +6000,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="124" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="B36" s="124" t="inlineStr">
         <is>
@@ -6011,11 +6070,11 @@
       </c>
       <c r="X36" s="124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="Y36" s="128" t="n">
-        <v>0</v>
+        <v>48920</v>
       </c>
       <c r="Z36" s="128">
         <f>S36+W36</f>
@@ -6038,7 +6097,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="207" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B37" s="207" t="inlineStr">
         <is>
@@ -6153,7 +6212,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="207" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B38" s="207" t="inlineStr">
         <is>
@@ -6268,7 +6327,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="124" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="B39" s="124" t="inlineStr">
         <is>
@@ -6389,7 +6448,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="124" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="B40" s="124" t="inlineStr">
         <is>
@@ -6510,7 +6569,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="124" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B41" s="124" t="inlineStr">
         <is>
@@ -6625,7 +6684,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="124" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="B42" s="124" t="inlineStr">
         <is>
@@ -6740,7 +6799,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="124" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B43" s="124" t="inlineStr">
         <is>
@@ -6857,7 +6916,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="124" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="B44" s="124" t="inlineStr">
         <is>
@@ -6910,8 +6969,14 @@
           <t>AIB-3000 Cinema Audio Processor 9EA (롯데 인천검단 6 / CJ미래원 1 / RNR 2)</t>
         </is>
       </c>
-      <c r="O44" s="182" t="n"/>
-      <c r="P44" s="129" t="n"/>
+      <c r="O44" s="182" t="n">
+        <v>46188</v>
+      </c>
+      <c r="P44" s="129" t="inlineStr">
+        <is>
+          <t>23176-26-472403M</t>
+        </is>
+      </c>
       <c r="Q44" s="126">
         <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
         <v/>
@@ -6924,12 +6989,12 @@
         <v>0</v>
       </c>
       <c r="T44" s="128" t="n">
-        <v>0</v>
+        <v>2457950</v>
       </c>
       <c r="U44" s="181" t="n"/>
       <c r="V44" s="124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>스타합동관세사무소</t>
         </is>
       </c>
       <c r="W44" s="128" t="n">
@@ -6937,7 +7002,7 @@
       </c>
       <c r="X44" s="124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fedex</t>
         </is>
       </c>
       <c r="Y44" s="128" t="n">
@@ -6958,777 +7023,817 @@
         <f>ROUND(AA44/AB44,0)</f>
         <v/>
       </c>
-      <c r="AD44" s="129" t="n"/>
+      <c r="AD44" s="129" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
       <c r="AE44" s="182" t="n"/>
       <c r="AF44" s="182" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="296" t="n">
-        <v>29</v>
-      </c>
-      <c r="B45" s="296" t="inlineStr">
-        <is>
-          <t>CPO667</t>
-        </is>
-      </c>
-      <c r="C45" s="297" t="inlineStr">
+      <c r="A45" s="124" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="124" t="inlineStr">
+        <is>
+          <t>CPO701</t>
+        </is>
+      </c>
+      <c r="C45" s="124" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D45" s="296" t="inlineStr">
+      <c r="D45" s="124" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E45" s="297" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F45" s="298" t="n">
-        <v>45925</v>
-      </c>
-      <c r="G45" s="299" t="n">
-        <v>46080</v>
-      </c>
-      <c r="H45" s="300" t="n">
-        <v>5673</v>
-      </c>
-      <c r="I45" s="301" t="n">
-        <v>1441.6</v>
-      </c>
-      <c r="J45" s="302" t="n">
-        <v>8178197</v>
-      </c>
-      <c r="K45" s="302" t="n">
-        <v>8178197</v>
-      </c>
-      <c r="L45" s="302" t="n">
-        <v>499</v>
-      </c>
-      <c r="M45" s="302" t="n">
-        <v>319</v>
-      </c>
-      <c r="N45" s="296" t="inlineStr">
-        <is>
-          <t>EW CP2220</t>
-        </is>
-      </c>
-      <c r="O45" s="299" t="inlineStr">
+      <c r="E45" s="124" t="inlineStr">
+        <is>
+          <t>부품(Fan)</t>
+        </is>
+      </c>
+      <c r="F45" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P45" s="296" t="inlineStr">
+      <c r="G45" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q45" s="300">
+      <c r="H45" s="126" t="n">
+        <v>54</v>
+      </c>
+      <c r="I45" s="310">
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J45" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="128">
+        <f>IFERROR(ROUND(H45*I45,0),0)</f>
+        <v/>
+      </c>
+      <c r="L45" s="128">
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M45" s="128">
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N45" s="124" t="inlineStr">
+        <is>
+          <t>ASSY FAN 12V 0.6A 4-Wire 92MM (2EA)</t>
+        </is>
+      </c>
+      <c r="O45" s="182" t="n">
+        <v>46216</v>
+      </c>
+      <c r="P45" s="129" t="inlineStr">
+        <is>
+          <t>23176-26-606930M</t>
+        </is>
+      </c>
+      <c r="Q45" s="126">
         <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R45" s="302">
+      <c r="R45" s="126">
         <f>IF(P45="","",H45)</f>
         <v/>
       </c>
-      <c r="S45" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="298" t="n"/>
-      <c r="V45" s="296" t="inlineStr">
+      <c r="S45" s="128" t="n">
+        <v>6631</v>
+      </c>
+      <c r="T45" s="128" t="n">
+        <v>8952</v>
+      </c>
+      <c r="U45" s="181" t="n"/>
+      <c r="V45" s="124" t="inlineStr">
+        <is>
+          <t>스타합동관세사무소</t>
+        </is>
+      </c>
+      <c r="W45" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="124" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="Y45" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="128">
+        <f>S45+W45</f>
+        <v/>
+      </c>
+      <c r="AA45" s="131">
+        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE),0)+Y45+Z45</f>
+        <v/>
+      </c>
+      <c r="AB45" s="167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC45" s="131">
+        <f>ROUND(AA45/AB45,0)</f>
+        <v/>
+      </c>
+      <c r="AD45" s="129" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE45" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W45" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="297" t="inlineStr">
+      <c r="AF45" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y45" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="302">
-        <f>S45+W45</f>
-        <v/>
-      </c>
-      <c r="AA45" s="302">
-        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE),0)+Y45+Z45</f>
-        <v/>
-      </c>
-      <c r="AB45" s="303" t="n">
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="124" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="124" t="inlineStr">
+        <is>
+          <t>CPO703</t>
+        </is>
+      </c>
+      <c r="C46" s="124" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D46" s="124" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E46" s="124" t="inlineStr">
+        <is>
+          <t>부품(렌즈)</t>
+        </is>
+      </c>
+      <c r="F46" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="126" t="n">
+        <v>5445</v>
+      </c>
+      <c r="I46" s="310">
+        <f>IFERROR(VLOOKUP(B46,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J46" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="128">
+        <f>IFERROR(ROUND(H46*I46,0),0)</f>
+        <v/>
+      </c>
+      <c r="L46" s="128">
+        <f>IFERROR(VLOOKUP(B46,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M46" s="128">
+        <f>IFERROR(VLOOKUP(B46,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N46" s="124" t="inlineStr">
+        <is>
+          <t>Lens 0.83-1.21 .69" DLPCine Zoom MT (1EA)</t>
+        </is>
+      </c>
+      <c r="O46" s="182" t="n">
+        <v>46216</v>
+      </c>
+      <c r="P46" s="129" t="inlineStr">
+        <is>
+          <t>23176-26-606930M</t>
+        </is>
+      </c>
+      <c r="Q46" s="126">
+        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R46" s="126">
+        <f>IF(P46="","",H46)</f>
+        <v/>
+      </c>
+      <c r="S46" s="128" t="n">
+        <v>668679</v>
+      </c>
+      <c r="T46" s="128" t="n">
+        <v>902728</v>
+      </c>
+      <c r="U46" s="181" t="n"/>
+      <c r="V46" s="124" t="inlineStr">
+        <is>
+          <t>스타합동관세사무소</t>
+        </is>
+      </c>
+      <c r="W46" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="124" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="Y46" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="128">
+        <f>S46+W46</f>
+        <v/>
+      </c>
+      <c r="AA46" s="131">
+        <f>K46+L46+M46+IFERROR(VLOOKUP(B46,RemitTable2,9,FALSE),0)+Y46+Z46</f>
+        <v/>
+      </c>
+      <c r="AB46" s="167" t="n">
         <v>1</v>
       </c>
-      <c r="AC45" s="302">
-        <f>ROUND(AA45/AB45,0)</f>
-        <v/>
-      </c>
-      <c r="AD45" s="296" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="AE45" s="299" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AF45" s="298" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="296" t="n">
-        <v>30</v>
-      </c>
-      <c r="B46" s="296" t="inlineStr">
-        <is>
-          <t>GPO458</t>
-        </is>
-      </c>
-      <c r="C46" s="297" t="inlineStr">
+      <c r="AC46" s="131">
+        <f>ROUND(AA46/AB46,0)</f>
+        <v/>
+      </c>
+      <c r="AD46" s="129" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE46" s="182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF46" s="182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="124" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="124" t="inlineStr">
+        <is>
+          <t>GPO488</t>
+        </is>
+      </c>
+      <c r="C47" s="124" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D46" s="296" t="inlineStr">
+      <c r="D47" s="124" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E46" s="297" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F46" s="298" t="n">
-        <v>45982</v>
-      </c>
-      <c r="G46" s="299" t="n">
-        <v>46020</v>
-      </c>
-      <c r="H46" s="300" t="n">
-        <v>350</v>
-      </c>
-      <c r="I46" s="301" t="n">
-        <v>1439.1</v>
-      </c>
-      <c r="J46" s="302" t="n">
-        <v>503685</v>
-      </c>
-      <c r="K46" s="302" t="n">
-        <v>503685</v>
-      </c>
-      <c r="L46" s="302" t="n">
-        <v>253</v>
-      </c>
-      <c r="M46" s="302" t="n">
-        <v>202</v>
-      </c>
-      <c r="N46" s="296" t="inlineStr">
-        <is>
-          <t>HFR License</t>
-        </is>
-      </c>
-      <c r="O46" s="299" t="inlineStr">
+      <c r="E47" s="124" t="inlineStr">
+        <is>
+          <t>부품(Fan)</t>
+        </is>
+      </c>
+      <c r="F47" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P46" s="296" t="inlineStr">
+      <c r="G47" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q46" s="300">
-        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R46" s="302">
-        <f>IF(P46="","",H46)</f>
-        <v/>
-      </c>
-      <c r="S46" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="298" t="n"/>
-      <c r="V46" s="296" t="inlineStr">
+      <c r="H47" s="126" t="n">
+        <v>180</v>
+      </c>
+      <c r="I47" s="310">
+        <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J47" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="128">
+        <f>IFERROR(ROUND(H47*I47,0),0)</f>
+        <v/>
+      </c>
+      <c r="L47" s="128">
+        <f>IFERROR(VLOOKUP(B47,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M47" s="128">
+        <f>IFERROR(VLOOKUP(B47,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N47" s="124" t="inlineStr">
+        <is>
+          <t>PSD-3000-U2 Rear Ventilation Fan (20EA)</t>
+        </is>
+      </c>
+      <c r="O47" s="182" t="n">
+        <v>46216</v>
+      </c>
+      <c r="P47" s="129" t="inlineStr">
+        <is>
+          <t>23176-26-605075M</t>
+        </is>
+      </c>
+      <c r="Q47" s="126">
+        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R47" s="126">
+        <f>IF(P47="","",H47)</f>
+        <v/>
+      </c>
+      <c r="S47" s="128" t="n">
+        <v>24140</v>
+      </c>
+      <c r="T47" s="128" t="n">
+        <v>32590</v>
+      </c>
+      <c r="U47" s="181" t="n"/>
+      <c r="V47" s="124" t="inlineStr">
+        <is>
+          <t>스타합동관세사무소</t>
+        </is>
+      </c>
+      <c r="W47" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="124" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="Y47" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="128">
+        <f>S47+W47</f>
+        <v/>
+      </c>
+      <c r="AA47" s="131">
+        <f>K47+L47+M47+IFERROR(VLOOKUP(B47,RemitTable2,9,FALSE),0)+Y47+Z47</f>
+        <v/>
+      </c>
+      <c r="AB47" s="167" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC47" s="131">
+        <f>ROUND(AA47/AB47,0)</f>
+        <v/>
+      </c>
+      <c r="AD47" s="129" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE47" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W46" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="297" t="inlineStr">
+      <c r="AF47" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y46" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="302">
-        <f>S46+W46</f>
-        <v/>
-      </c>
-      <c r="AA46" s="302">
-        <f>K46+L46+M46+IFERROR(VLOOKUP(B46,RemitTable2,9,FALSE),0)+Y46+Z46</f>
-        <v/>
-      </c>
-      <c r="AB46" s="303" t="n">
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="124" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="124" t="inlineStr">
+        <is>
+          <t>GPO493</t>
+        </is>
+      </c>
+      <c r="C48" s="124" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D48" s="124" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E48" s="124" t="inlineStr">
+        <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="F48" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="126" t="n">
+        <v>4470</v>
+      </c>
+      <c r="I48" s="310">
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J48" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="128">
+        <f>IFERROR(ROUND(H48*I48,0),0)</f>
+        <v/>
+      </c>
+      <c r="L48" s="128">
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M48" s="128">
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N48" s="124" t="inlineStr">
+        <is>
+          <t>SR-1000 Christie S2/S3 Faceplate (37EA) + Security Gate (45EA)</t>
+        </is>
+      </c>
+      <c r="O48" s="182" t="n">
+        <v>46218</v>
+      </c>
+      <c r="P48" s="129" t="inlineStr">
+        <is>
+          <t>23176-26-618473M</t>
+        </is>
+      </c>
+      <c r="Q48" s="126">
+        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R48" s="126">
+        <f>IF(P48="","",H48)</f>
+        <v/>
+      </c>
+      <c r="S48" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="128" t="n">
+        <v>692710</v>
+      </c>
+      <c r="U48" s="181" t="n"/>
+      <c r="V48" s="124" t="inlineStr">
+        <is>
+          <t>스타합동관세사무소</t>
+        </is>
+      </c>
+      <c r="W48" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="124" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="Y48" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="128">
+        <f>S48+W48</f>
+        <v/>
+      </c>
+      <c r="AA48" s="131">
+        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE),0)+Y48+Z48</f>
+        <v/>
+      </c>
+      <c r="AB48" s="167" t="n">
+        <v>82</v>
+      </c>
+      <c r="AC48" s="131">
+        <f>ROUND(AA48/AB48,0)</f>
+        <v/>
+      </c>
+      <c r="AD48" s="129" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE48" s="182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF48" s="182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="124" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="124" t="inlineStr">
+        <is>
+          <t>GPO482</t>
+        </is>
+      </c>
+      <c r="C49" s="124" t="inlineStr">
+        <is>
+          <t>GDC (Espedeo)</t>
+        </is>
+      </c>
+      <c r="D49" s="124" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E49" s="124" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F49" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="126" t="n">
+        <v>329510</v>
+      </c>
+      <c r="I49" s="310">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J49" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="128">
+        <f>IFERROR(ROUND(H49*I49,0),0)</f>
+        <v/>
+      </c>
+      <c r="L49" s="128">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M49" s="128">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N49" s="124" t="inlineStr">
+        <is>
+          <t>Tricorne Premium Cinema LED 1SET + Enterprise Storage 8TB (3EA) + Synchronization kit 1SET</t>
+        </is>
+      </c>
+      <c r="O49" s="182" t="n">
+        <v>46224</v>
+      </c>
+      <c r="P49" s="129" t="inlineStr">
+        <is>
+          <t>14008-26-101364M</t>
+        </is>
+      </c>
+      <c r="Q49" s="126">
+        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R49" s="126">
+        <f>IF(P49="","",H49)</f>
+        <v/>
+      </c>
+      <c r="S49" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="128" t="n">
+        <v>49543390</v>
+      </c>
+      <c r="U49" s="181" t="n"/>
+      <c r="V49" s="124" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W49" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="124" t="inlineStr">
+        <is>
+          <t>훼밀리익스프레스</t>
+        </is>
+      </c>
+      <c r="Y49" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="128">
+        <f>S49+W49</f>
+        <v/>
+      </c>
+      <c r="AA49" s="131">
+        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE),0)+Y49+Z49</f>
+        <v/>
+      </c>
+      <c r="AB49" s="167" t="n">
         <v>1</v>
       </c>
-      <c r="AC46" s="302">
-        <f>ROUND(AA46/AB46,0)</f>
-        <v/>
-      </c>
-      <c r="AD46" s="296" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AE46" s="299" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AF46" s="298" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="296" t="n">
-        <v>31</v>
-      </c>
-      <c r="B47" s="296" t="inlineStr">
-        <is>
-          <t>CPO681</t>
-        </is>
-      </c>
-      <c r="C47" s="297" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D47" s="296" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E47" s="297" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F47" s="298" t="n">
-        <v>45993</v>
-      </c>
-      <c r="G47" s="299" t="n">
-        <v>46064</v>
-      </c>
-      <c r="H47" s="300" t="n">
-        <v>26358</v>
-      </c>
-      <c r="I47" s="301" t="n">
-        <v>1460.7</v>
-      </c>
-      <c r="J47" s="302" t="n">
-        <v>38501131</v>
-      </c>
-      <c r="K47" s="302" t="n">
-        <v>38501131</v>
-      </c>
-      <c r="L47" s="302" t="n">
-        <v>12500</v>
-      </c>
-      <c r="M47" s="302" t="n">
-        <v>8000</v>
-      </c>
-      <c r="N47" s="296" t="inlineStr">
-        <is>
-          <t>EW CP2309/2315/2320-RGB</t>
-        </is>
-      </c>
-      <c r="O47" s="299" t="inlineStr">
+      <c r="AC49" s="131">
+        <f>ROUND(AA49/AB49,0)</f>
+        <v/>
+      </c>
+      <c r="AD49" s="129" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE49" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P47" s="296" t="inlineStr">
+      <c r="AF49" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q47" s="300">
-        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R47" s="302">
-        <f>IF(P47="","",H47)</f>
-        <v/>
-      </c>
-      <c r="S47" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="298" t="n"/>
-      <c r="V47" s="296" t="inlineStr">
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="124" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="124" t="inlineStr">
+        <is>
+          <t>GPO485</t>
+        </is>
+      </c>
+      <c r="C50" s="124" t="inlineStr">
+        <is>
+          <t>GDC (Espedeo)</t>
+        </is>
+      </c>
+      <c r="D50" s="124" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E50" s="124" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="F50" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W47" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="297" t="inlineStr">
+      <c r="G50" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y47" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="302">
-        <f>S47+W47</f>
-        <v/>
-      </c>
-      <c r="AA47" s="302">
-        <f>K47+L47+M47+IFERROR(VLOOKUP(B47,RemitTable2,9,FALSE),0)+Y47+Z47</f>
-        <v/>
-      </c>
-      <c r="AB47" s="303" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC47" s="302">
-        <f>ROUND(AA47/AB47,0)</f>
-        <v/>
-      </c>
-      <c r="AD47" s="296" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AE47" s="299" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AF47" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="296" t="n">
-        <v>32</v>
-      </c>
-      <c r="B48" s="296" t="inlineStr">
-        <is>
-          <t>GPO459</t>
-        </is>
-      </c>
-      <c r="C48" s="297" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D48" s="296" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E48" s="297" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F48" s="298" t="n">
-        <v>46007</v>
-      </c>
-      <c r="G48" s="299" t="n">
-        <v>46043</v>
-      </c>
-      <c r="H48" s="300" t="n">
-        <v>450</v>
-      </c>
-      <c r="I48" s="301" t="n">
-        <v>1475.7</v>
-      </c>
-      <c r="J48" s="302" t="n">
-        <v>664065</v>
-      </c>
-      <c r="K48" s="302" t="n">
-        <v>664065</v>
-      </c>
-      <c r="L48" s="302" t="n">
-        <v>912</v>
-      </c>
-      <c r="M48" s="302" t="n">
-        <v>973</v>
-      </c>
-      <c r="N48" s="296" t="inlineStr">
-        <is>
-          <t>TMS-2000 EW</t>
-        </is>
-      </c>
-      <c r="O48" s="299" t="inlineStr">
+      <c r="H50" s="126" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I50" s="310">
+        <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J50" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="128">
+        <f>IFERROR(ROUND(H50*I50,0),0)</f>
+        <v/>
+      </c>
+      <c r="L50" s="128">
+        <f>IFERROR(VLOOKUP(B50,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M50" s="128">
+        <f>IFERROR(VLOOKUP(B50,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N50" s="124" t="inlineStr">
+        <is>
+          <t>Active 3D system AL-1000T 1SET + 3D active glasses GL-110T (50EA)</t>
+        </is>
+      </c>
+      <c r="O50" s="182" t="n">
+        <v>46224</v>
+      </c>
+      <c r="P50" s="129" t="inlineStr">
+        <is>
+          <t>14008-26-101364M</t>
+        </is>
+      </c>
+      <c r="Q50" s="126">
+        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R50" s="126">
+        <f>IF(P50="","",H50)</f>
+        <v/>
+      </c>
+      <c r="S50" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="128" t="n">
+        <v>841980</v>
+      </c>
+      <c r="U50" s="181" t="n"/>
+      <c r="V50" s="124" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="W50" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="124" t="inlineStr">
+        <is>
+          <t>훼밀리익스프레스</t>
+        </is>
+      </c>
+      <c r="Y50" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="128">
+        <f>S50+W50</f>
+        <v/>
+      </c>
+      <c r="AA50" s="131">
+        <f>K50+L50+M50+IFERROR(VLOOKUP(B50,RemitTable2,9,FALSE),0)+Y50+Z50</f>
+        <v/>
+      </c>
+      <c r="AB50" s="167" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC50" s="131">
+        <f>ROUND(AA50/AB50,0)</f>
+        <v/>
+      </c>
+      <c r="AD50" s="129" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE50" s="182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P48" s="296" t="inlineStr">
+      <c r="AF50" s="182" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="Q48" s="300">
-        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R48" s="302">
-        <f>IF(P48="","",H48)</f>
-        <v/>
-      </c>
-      <c r="S48" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="298" t="n"/>
-      <c r="V48" s="296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W48" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y48" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="302">
-        <f>S48+W48</f>
-        <v/>
-      </c>
-      <c r="AA48" s="302">
-        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE),0)+Y48+Z48</f>
-        <v/>
-      </c>
-      <c r="AB48" s="303" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC48" s="302">
-        <f>ROUND(AA48/AB48,0)</f>
-        <v/>
-      </c>
-      <c r="AD48" s="296" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="AE48" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF48" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="296" t="n">
-        <v>33</v>
-      </c>
-      <c r="B49" s="296" t="inlineStr">
-        <is>
-          <t>GPO461</t>
-        </is>
-      </c>
-      <c r="C49" s="297" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D49" s="296" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E49" s="297" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F49" s="298" t="n">
-        <v>46007</v>
-      </c>
-      <c r="G49" s="299" t="n">
-        <v>46043</v>
-      </c>
-      <c r="H49" s="300" t="n">
-        <v>540</v>
-      </c>
-      <c r="I49" s="301" t="n">
-        <v>1475.7</v>
-      </c>
-      <c r="J49" s="302" t="n">
-        <v>796878</v>
-      </c>
-      <c r="K49" s="302" t="n">
-        <v>796878</v>
-      </c>
-      <c r="L49" s="302" t="n">
-        <v>1095</v>
-      </c>
-      <c r="M49" s="302" t="n">
-        <v>1168</v>
-      </c>
-      <c r="N49" s="296" t="inlineStr">
-        <is>
-          <t>TMS-1000 EW</t>
-        </is>
-      </c>
-      <c r="O49" s="299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q49" s="300">
-        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R49" s="302">
-        <f>IF(P49="","",H49)</f>
-        <v/>
-      </c>
-      <c r="S49" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="298" t="n"/>
-      <c r="V49" s="296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W49" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y49" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="302">
-        <f>S49+W49</f>
-        <v/>
-      </c>
-      <c r="AA49" s="302">
-        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE),0)+Y49+Z49</f>
-        <v/>
-      </c>
-      <c r="AB49" s="303" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC49" s="302">
-        <f>ROUND(AA49/AB49,0)</f>
-        <v/>
-      </c>
-      <c r="AD49" s="296" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="AE49" s="299" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AF49" s="298" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="296" t="n">
-        <v>34</v>
-      </c>
-      <c r="B50" s="296" t="inlineStr">
-        <is>
-          <t>CPO685</t>
-        </is>
-      </c>
-      <c r="C50" s="297" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D50" s="296" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E50" s="297" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F50" s="298" t="n">
-        <v>46010</v>
-      </c>
-      <c r="G50" s="299" t="n">
-        <v>46080</v>
-      </c>
-      <c r="H50" s="300" t="n">
-        <v>136516</v>
-      </c>
-      <c r="I50" s="301" t="n">
-        <v>1441.6</v>
-      </c>
-      <c r="J50" s="302" t="n">
-        <v>196801466</v>
-      </c>
-      <c r="K50" s="302" t="n">
-        <v>196801466</v>
-      </c>
-      <c r="L50" s="302" t="n">
-        <v>12001</v>
-      </c>
-      <c r="M50" s="302" t="n">
-        <v>7681</v>
-      </c>
-      <c r="N50" s="296" t="inlineStr">
-        <is>
-          <t>EW 대량 (CP2208~CP4450)</t>
-        </is>
-      </c>
-      <c r="O50" s="299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P50" s="296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q50" s="300">
-        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R50" s="302">
-        <f>IF(P50="","",H50)</f>
-        <v/>
-      </c>
-      <c r="S50" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="298" t="n"/>
-      <c r="V50" s="296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W50" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y50" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="302">
-        <f>S50+W50</f>
-        <v/>
-      </c>
-      <c r="AA50" s="302">
-        <f>K50+L50+M50+IFERROR(VLOOKUP(B50,RemitTable2,9,FALSE),0)+Y50+Z50</f>
-        <v/>
-      </c>
-      <c r="AB50" s="303" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC50" s="302">
-        <f>ROUND(AA50/AB50,0)</f>
-        <v/>
-      </c>
-      <c r="AD50" s="296" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="AE50" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF50" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="296" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B51" s="296" t="inlineStr">
         <is>
-          <t>GPO465</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="C51" s="297" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D51" s="296" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E51" s="297" t="inlineStr">
@@ -7737,38 +7842,32 @@
         </is>
       </c>
       <c r="F51" s="298" t="n">
-        <v>46015</v>
-      </c>
-      <c r="G51" s="299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>45925</v>
+      </c>
+      <c r="G51" s="299" t="n">
+        <v>46080</v>
       </c>
       <c r="H51" s="300" t="n">
-        <v>76054</v>
-      </c>
-      <c r="I51" s="301">
-        <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE),0)</f>
-        <v/>
+        <v>5673</v>
+      </c>
+      <c r="I51" s="301" t="n">
+        <v>1441.6</v>
       </c>
       <c r="J51" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="302">
-        <f>IFERROR(ROUND(H50*I50,0),0)</f>
-        <v/>
-      </c>
-      <c r="L51" s="302">
-        <f>IFERROR(VLOOKUP(B50,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="302">
-        <f>IFERROR(VLOOKUP(B50,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>8178197</v>
+      </c>
+      <c r="K51" s="302" t="n">
+        <v>8178197</v>
+      </c>
+      <c r="L51" s="302" t="n">
+        <v>499</v>
+      </c>
+      <c r="M51" s="302" t="n">
+        <v>319</v>
       </c>
       <c r="N51" s="296" t="inlineStr">
         <is>
-          <t>EW 대량 (SR/SX/TMS)</t>
+          <t>EW CP2220</t>
         </is>
       </c>
       <c r="O51" s="299" t="inlineStr">
@@ -7829,71 +7928,71 @@
       </c>
       <c r="AD51" s="296" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="AE51" s="299" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AF51" s="298" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="296" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B52" s="296" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="C52" s="297" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D52" s="296" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E52" s="297" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F52" s="298" t="n">
-        <v>46029</v>
+        <v>45982</v>
       </c>
       <c r="G52" s="299" t="n">
-        <v>46072</v>
+        <v>46020</v>
       </c>
       <c r="H52" s="300" t="n">
-        <v>14793</v>
+        <v>350</v>
       </c>
       <c r="I52" s="301" t="n">
-        <v>1451.7</v>
+        <v>1439.1</v>
       </c>
       <c r="J52" s="302" t="n">
-        <v>21474998</v>
+        <v>503685</v>
       </c>
       <c r="K52" s="302" t="n">
-        <v>21474998</v>
+        <v>503685</v>
       </c>
       <c r="L52" s="302" t="n">
-        <v>8435</v>
+        <v>253</v>
       </c>
       <c r="M52" s="302" t="n">
-        <v>6748</v>
+        <v>202</v>
       </c>
       <c r="N52" s="296" t="inlineStr">
         <is>
-          <t>EW CP2315/CP4440-RGB</t>
+          <t>HFR License</t>
         </is>
       </c>
       <c r="O52" s="299" t="inlineStr">
@@ -7954,27 +8053,27 @@
       </c>
       <c r="AD52" s="296" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE52" s="299" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AF52" s="298" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="296" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B53" s="296" t="inlineStr">
         <is>
-          <t>CPO687</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="C53" s="297" t="inlineStr">
@@ -7993,38 +8092,32 @@
         </is>
       </c>
       <c r="F53" s="298" t="n">
-        <v>46029</v>
-      </c>
-      <c r="G53" s="299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>45993</v>
+      </c>
+      <c r="G53" s="299" t="n">
+        <v>46064</v>
       </c>
       <c r="H53" s="300" t="n">
-        <v>26656</v>
-      </c>
-      <c r="I53" s="301">
-        <f>IFERROR(VLOOKUP(B52,RemitTable2,7,FALSE),0)</f>
-        <v/>
+        <v>26358</v>
+      </c>
+      <c r="I53" s="301" t="n">
+        <v>1460.7</v>
       </c>
       <c r="J53" s="302" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="302">
-        <f>IFERROR(ROUND(H52*I52,0),0)</f>
-        <v/>
-      </c>
-      <c r="L53" s="302">
-        <f>IFERROR(VLOOKUP(B52,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M53" s="302">
-        <f>IFERROR(VLOOKUP(B52,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>38501131</v>
+      </c>
+      <c r="K53" s="302" t="n">
+        <v>38501131</v>
+      </c>
+      <c r="L53" s="302" t="n">
+        <v>12500</v>
+      </c>
+      <c r="M53" s="302" t="n">
+        <v>8000</v>
       </c>
       <c r="N53" s="296" t="inlineStr">
         <is>
-          <t>EW (홀딩)</t>
+          <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
       <c r="O53" s="299" t="inlineStr">
@@ -8085,27 +8178,27 @@
       </c>
       <c r="AD53" s="296" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE53" s="299" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AF53" s="298" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-12-21</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="296" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B54" s="296" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="C54" s="297" t="inlineStr">
@@ -8120,36 +8213,36 @@
       </c>
       <c r="E54" s="297" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F54" s="298" t="n">
-        <v>46042</v>
+        <v>46007</v>
       </c>
       <c r="G54" s="299" t="n">
-        <v>46057</v>
+        <v>46043</v>
       </c>
       <c r="H54" s="300" t="n">
-        <v>1440</v>
+        <v>450</v>
       </c>
       <c r="I54" s="301" t="n">
-        <v>1453.6</v>
+        <v>1475.7</v>
       </c>
       <c r="J54" s="302" t="n">
-        <v>2093184</v>
+        <v>664065</v>
       </c>
       <c r="K54" s="302" t="n">
-        <v>2093184</v>
+        <v>664065</v>
       </c>
       <c r="L54" s="302" t="n">
-        <v>1241</v>
+        <v>912</v>
       </c>
       <c r="M54" s="302" t="n">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="N54" s="296" t="inlineStr">
         <is>
-          <t>TMS-2000 License</t>
+          <t>TMS-2000 EW</t>
         </is>
       </c>
       <c r="O54" s="299" t="inlineStr">
@@ -8226,11 +8319,11 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="296" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B55" s="296" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="C55" s="297" t="inlineStr">
@@ -8249,32 +8342,32 @@
         </is>
       </c>
       <c r="F55" s="298" t="n">
-        <v>46042</v>
+        <v>46007</v>
       </c>
       <c r="G55" s="299" t="n">
-        <v>46057</v>
+        <v>46043</v>
       </c>
       <c r="H55" s="300" t="n">
-        <v>4489</v>
+        <v>540</v>
       </c>
       <c r="I55" s="301" t="n">
-        <v>1453.6</v>
+        <v>1475.7</v>
       </c>
       <c r="J55" s="302" t="n">
-        <v>6525210</v>
+        <v>796878</v>
       </c>
       <c r="K55" s="302" t="n">
-        <v>6525210</v>
+        <v>796878</v>
       </c>
       <c r="L55" s="302" t="n">
-        <v>3870</v>
+        <v>1095</v>
       </c>
       <c r="M55" s="302" t="n">
-        <v>3096</v>
+        <v>1168</v>
       </c>
       <c r="N55" s="296" t="inlineStr">
         <is>
-          <t>SX/SR EW (CGV/Lotte)</t>
+          <t>TMS-1000 EW</t>
         </is>
       </c>
       <c r="O55" s="299" t="inlineStr">
@@ -8335,37 +8428,37 @@
       </c>
       <c r="AD55" s="296" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="AE55" s="299" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AF55" s="298" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="296" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B56" s="296" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="C56" s="297" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D56" s="296" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E56" s="297" t="inlineStr">
@@ -8374,32 +8467,32 @@
         </is>
       </c>
       <c r="F56" s="298" t="n">
-        <v>46042</v>
+        <v>46010</v>
       </c>
       <c r="G56" s="299" t="n">
-        <v>46057</v>
+        <v>46080</v>
       </c>
       <c r="H56" s="300" t="n">
-        <v>5670.57</v>
+        <v>136516</v>
       </c>
       <c r="I56" s="301" t="n">
-        <v>1453.6</v>
+        <v>1441.6</v>
       </c>
       <c r="J56" s="302" t="n">
-        <v>8242741</v>
+        <v>196801466</v>
       </c>
       <c r="K56" s="302" t="n">
-        <v>8242741</v>
+        <v>196801466</v>
       </c>
       <c r="L56" s="302" t="n">
-        <v>4889</v>
+        <v>12001</v>
       </c>
       <c r="M56" s="302" t="n">
-        <v>3911</v>
+        <v>7681</v>
       </c>
       <c r="N56" s="296" t="inlineStr">
         <is>
-          <t>SR-1000/SX-3000 EW</t>
+          <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
       <c r="O56" s="299" t="inlineStr">
@@ -8476,21 +8569,21 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="296" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B57" s="296" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>GPO465</t>
         </is>
       </c>
       <c r="C57" s="297" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D57" s="296" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E57" s="297" t="inlineStr">
@@ -8499,32 +8592,38 @@
         </is>
       </c>
       <c r="F57" s="298" t="n">
-        <v>46057</v>
-      </c>
-      <c r="G57" s="299" t="n">
-        <v>46113</v>
+        <v>46015</v>
+      </c>
+      <c r="G57" s="299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H57" s="300" t="n">
-        <v>24614</v>
-      </c>
-      <c r="I57" s="301" t="n">
-        <v>1505.7</v>
+        <v>76054</v>
+      </c>
+      <c r="I57" s="301">
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,7,FALSE),0)</f>
+        <v/>
       </c>
       <c r="J57" s="302" t="n">
-        <v>37061300</v>
-      </c>
-      <c r="K57" s="302" t="n">
-        <v>37061300</v>
-      </c>
-      <c r="L57" s="302" t="n">
-        <v>8956</v>
-      </c>
-      <c r="M57" s="302" t="n">
-        <v>5732</v>
+        <v>0</v>
+      </c>
+      <c r="K57" s="302">
+        <f>IFERROR(ROUND(H57*I57,0),0)</f>
+        <v/>
+      </c>
+      <c r="L57" s="302">
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M57" s="302">
+        <f>IFERROR(VLOOKUP(B57,RemitTable2,11,FALSE),0)</f>
+        <v/>
       </c>
       <c r="N57" s="296" t="inlineStr">
         <is>
-          <t>EW (메가박스 외)</t>
+          <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
       <c r="O57" s="299" t="inlineStr">
@@ -8585,37 +8684,37 @@
       </c>
       <c r="AD57" s="296" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE57" s="299" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF57" s="298" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="296" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B58" s="296" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="C58" s="297" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D58" s="296" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E58" s="297" t="inlineStr">
@@ -8624,32 +8723,32 @@
         </is>
       </c>
       <c r="F58" s="298" t="n">
-        <v>46060</v>
+        <v>46029</v>
       </c>
       <c r="G58" s="299" t="n">
-        <v>46113</v>
+        <v>46072</v>
       </c>
       <c r="H58" s="300" t="n">
-        <v>3993.05</v>
+        <v>14793</v>
       </c>
       <c r="I58" s="301" t="n">
-        <v>1506.4</v>
+        <v>1451.7</v>
       </c>
       <c r="J58" s="302" t="n">
-        <v>6015131</v>
+        <v>21474998</v>
       </c>
       <c r="K58" s="302" t="n">
-        <v>6015131</v>
+        <v>21474998</v>
       </c>
       <c r="L58" s="302" t="n">
-        <v>6093</v>
+        <v>8435</v>
       </c>
       <c r="M58" s="302" t="n">
-        <v>4875</v>
+        <v>6748</v>
       </c>
       <c r="N58" s="296" t="inlineStr">
         <is>
-          <t>SR/SX EW (하남미사 외)</t>
+          <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
       <c r="O58" s="299" t="inlineStr">
@@ -8715,66 +8814,72 @@
       </c>
       <c r="AE58" s="299" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AF58" s="298" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-01-29</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="296" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B59" s="296" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>CPO687</t>
         </is>
       </c>
       <c r="C59" s="297" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D59" s="296" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E59" s="297" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F59" s="298" t="n">
-        <v>46080</v>
-      </c>
-      <c r="G59" s="299" t="n">
-        <v>46113</v>
+        <v>46029</v>
+      </c>
+      <c r="G59" s="299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H59" s="300" t="n">
-        <v>360</v>
-      </c>
-      <c r="I59" s="301" t="n">
-        <v>1506.4</v>
+        <v>26656</v>
+      </c>
+      <c r="I59" s="301">
+        <f>IFERROR(VLOOKUP(B59,RemitTable2,7,FALSE),0)</f>
+        <v/>
       </c>
       <c r="J59" s="302" t="n">
-        <v>542304</v>
-      </c>
-      <c r="K59" s="302" t="n">
-        <v>542304</v>
-      </c>
-      <c r="L59" s="302" t="n">
-        <v>549</v>
-      </c>
-      <c r="M59" s="302" t="n">
-        <v>439</v>
+        <v>0</v>
+      </c>
+      <c r="K59" s="302">
+        <f>IFERROR(ROUND(H59*I59,0),0)</f>
+        <v/>
+      </c>
+      <c r="L59" s="302">
+        <f>IFERROR(VLOOKUP(B59,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M59" s="302">
+        <f>IFERROR(VLOOKUP(B59,RemitTable2,11,FALSE),0)</f>
+        <v/>
       </c>
       <c r="N59" s="296" t="inlineStr">
         <is>
-          <t>TMS-1000 License</t>
+          <t>EW (홀딩)</t>
         </is>
       </c>
       <c r="O59" s="299" t="inlineStr">
@@ -8835,27 +8940,27 @@
       </c>
       <c r="AD59" s="296" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE59" s="299" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AF59" s="298" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="296" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B60" s="296" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="C60" s="297" t="inlineStr">
@@ -8874,32 +8979,32 @@
         </is>
       </c>
       <c r="F60" s="298" t="n">
-        <v>46088</v>
+        <v>46042</v>
       </c>
       <c r="G60" s="299" t="n">
-        <v>46113</v>
+        <v>46057</v>
       </c>
       <c r="H60" s="300" t="n">
-        <v>500</v>
+        <v>1440</v>
       </c>
       <c r="I60" s="301" t="n">
-        <v>1506.4</v>
+        <v>1453.6</v>
       </c>
       <c r="J60" s="302" t="n">
-        <v>753200</v>
+        <v>2093184</v>
       </c>
       <c r="K60" s="302" t="n">
-        <v>753200</v>
+        <v>2093184</v>
       </c>
       <c r="L60" s="302" t="n">
-        <v>763</v>
+        <v>1241</v>
       </c>
       <c r="M60" s="302" t="n">
-        <v>610</v>
+        <v>993</v>
       </c>
       <c r="N60" s="296" t="inlineStr">
         <is>
-          <t>Dolby Atmos License</t>
+          <t>TMS-2000 License</t>
         </is>
       </c>
       <c r="O60" s="299" t="inlineStr">
@@ -8960,37 +9065,37 @@
       </c>
       <c r="AD60" s="296" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE60" s="299" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF60" s="298" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="296" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B61" s="296" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="C61" s="297" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D61" s="296" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E61" s="297" t="inlineStr">
@@ -8999,32 +9104,32 @@
         </is>
       </c>
       <c r="F61" s="298" t="n">
-        <v>46109</v>
+        <v>46042</v>
       </c>
       <c r="G61" s="299" t="n">
-        <v>46146</v>
+        <v>46057</v>
       </c>
       <c r="H61" s="300" t="n">
-        <v>17404</v>
+        <v>4489</v>
       </c>
       <c r="I61" s="301" t="n">
-        <v>1474.9</v>
+        <v>1453.6</v>
       </c>
       <c r="J61" s="302" t="n">
-        <v>25669160</v>
+        <v>6525210</v>
       </c>
       <c r="K61" s="302" t="n">
-        <v>25669160</v>
+        <v>6525210</v>
       </c>
       <c r="L61" s="302" t="n">
-        <v>10147</v>
+        <v>3870</v>
       </c>
       <c r="M61" s="302" t="n">
-        <v>6494</v>
+        <v>3096</v>
       </c>
       <c r="N61" s="296" t="inlineStr">
         <is>
-          <t>EW (CGV 동백 외)</t>
+          <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
       <c r="O61" s="299" t="inlineStr">
@@ -9085,933 +9190,1025 @@
       </c>
       <c r="AD61" s="296" t="inlineStr">
         <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AE61" s="299" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AF61" s="298" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="296" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="296" t="inlineStr">
+        <is>
+          <t>GPO464</t>
+        </is>
+      </c>
+      <c r="C62" s="297" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D62" s="296" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E62" s="297" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F62" s="298" t="n">
+        <v>46042</v>
+      </c>
+      <c r="G62" s="299" t="n">
+        <v>46057</v>
+      </c>
+      <c r="H62" s="300" t="n">
+        <v>5670.57</v>
+      </c>
+      <c r="I62" s="301" t="n">
+        <v>1453.6</v>
+      </c>
+      <c r="J62" s="302" t="n">
+        <v>8242741</v>
+      </c>
+      <c r="K62" s="302" t="n">
+        <v>8242741</v>
+      </c>
+      <c r="L62" s="302" t="n">
+        <v>4889</v>
+      </c>
+      <c r="M62" s="302" t="n">
+        <v>3911</v>
+      </c>
+      <c r="N62" s="296" t="inlineStr">
+        <is>
+          <t>SR-1000/SX-3000 EW</t>
+        </is>
+      </c>
+      <c r="O62" s="299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P62" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q62" s="300">
+        <f>IF(P62="","",IFERROR(VLOOKUP(O62,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R62" s="302">
+        <f>IF(P62="","",H62)</f>
+        <v/>
+      </c>
+      <c r="S62" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="298" t="n"/>
+      <c r="V62" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W62" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y62" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="302">
+        <f>S62+W62</f>
+        <v/>
+      </c>
+      <c r="AA62" s="302">
+        <f>K62+L62+M62+IFERROR(VLOOKUP(B62,RemitTable2,9,FALSE),0)+Y62+Z62</f>
+        <v/>
+      </c>
+      <c r="AB62" s="303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC62" s="302">
+        <f>ROUND(AA62/AB62,0)</f>
+        <v/>
+      </c>
+      <c r="AD62" s="296" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AE62" s="299" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AF62" s="298" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="296" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="296" t="inlineStr">
+        <is>
+          <t>CPO691</t>
+        </is>
+      </c>
+      <c r="C63" s="297" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D63" s="296" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E63" s="297" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F63" s="298" t="n">
+        <v>46057</v>
+      </c>
+      <c r="G63" s="299" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H63" s="300" t="n">
+        <v>24614</v>
+      </c>
+      <c r="I63" s="301" t="n">
+        <v>1505.7</v>
+      </c>
+      <c r="J63" s="302" t="n">
+        <v>37061300</v>
+      </c>
+      <c r="K63" s="302" t="n">
+        <v>37061300</v>
+      </c>
+      <c r="L63" s="302" t="n">
+        <v>8956</v>
+      </c>
+      <c r="M63" s="302" t="n">
+        <v>5732</v>
+      </c>
+      <c r="N63" s="296" t="inlineStr">
+        <is>
+          <t>EW (메가박스 외)</t>
+        </is>
+      </c>
+      <c r="O63" s="299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P63" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q63" s="300">
+        <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R63" s="302">
+        <f>IF(P63="","",H63)</f>
+        <v/>
+      </c>
+      <c r="S63" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="298" t="n"/>
+      <c r="V63" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W63" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y63" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="302">
+        <f>S63+W63</f>
+        <v/>
+      </c>
+      <c r="AA63" s="302">
+        <f>K63+L63+M63+IFERROR(VLOOKUP(B63,RemitTable2,9,FALSE),0)+Y63+Z63</f>
+        <v/>
+      </c>
+      <c r="AB63" s="303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="302">
+        <f>ROUND(AA63/AB63,0)</f>
+        <v/>
+      </c>
+      <c r="AD63" s="296" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE63" s="299" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AF63" s="298" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="296" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="296" t="inlineStr">
+        <is>
+          <t>GPO469</t>
+        </is>
+      </c>
+      <c r="C64" s="297" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D64" s="296" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E64" s="297" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F64" s="298" t="n">
+        <v>46060</v>
+      </c>
+      <c r="G64" s="299" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H64" s="300" t="n">
+        <v>3993.05</v>
+      </c>
+      <c r="I64" s="301" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="J64" s="302" t="n">
+        <v>6015131</v>
+      </c>
+      <c r="K64" s="302" t="n">
+        <v>6015131</v>
+      </c>
+      <c r="L64" s="302" t="n">
+        <v>6093</v>
+      </c>
+      <c r="M64" s="302" t="n">
+        <v>4875</v>
+      </c>
+      <c r="N64" s="296" t="inlineStr">
+        <is>
+          <t>SR/SX EW (하남미사 외)</t>
+        </is>
+      </c>
+      <c r="O64" s="299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P64" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q64" s="300">
+        <f>IF(P64="","",IFERROR(VLOOKUP(O64,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R64" s="302">
+        <f>IF(P64="","",H64)</f>
+        <v/>
+      </c>
+      <c r="S64" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="298" t="n"/>
+      <c r="V64" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W64" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y64" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="302">
+        <f>S64+W64</f>
+        <v/>
+      </c>
+      <c r="AA64" s="302">
+        <f>K64+L64+M64+IFERROR(VLOOKUP(B64,RemitTable2,9,FALSE),0)+Y64+Z64</f>
+        <v/>
+      </c>
+      <c r="AB64" s="303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="302">
+        <f>ROUND(AA64/AB64,0)</f>
+        <v/>
+      </c>
+      <c r="AD64" s="296" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AE64" s="299" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AF64" s="298" t="inlineStr">
+        <is>
+          <t>2027-02-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="296" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="296" t="inlineStr">
+        <is>
+          <t>GPO470</t>
+        </is>
+      </c>
+      <c r="C65" s="297" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D65" s="296" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E65" s="297" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F65" s="298" t="n">
+        <v>46080</v>
+      </c>
+      <c r="G65" s="299" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H65" s="300" t="n">
+        <v>360</v>
+      </c>
+      <c r="I65" s="301" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="J65" s="302" t="n">
+        <v>542304</v>
+      </c>
+      <c r="K65" s="302" t="n">
+        <v>542304</v>
+      </c>
+      <c r="L65" s="302" t="n">
+        <v>549</v>
+      </c>
+      <c r="M65" s="302" t="n">
+        <v>439</v>
+      </c>
+      <c r="N65" s="296" t="inlineStr">
+        <is>
+          <t>TMS-1000 License</t>
+        </is>
+      </c>
+      <c r="O65" s="299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P65" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q65" s="300">
+        <f>IF(P65="","",IFERROR(VLOOKUP(O65,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R65" s="302">
+        <f>IF(P65="","",H65)</f>
+        <v/>
+      </c>
+      <c r="S65" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="298" t="n"/>
+      <c r="V65" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W65" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" s="297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y65" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="302">
+        <f>S65+W65</f>
+        <v/>
+      </c>
+      <c r="AA65" s="302">
+        <f>K65+L65+M65+IFERROR(VLOOKUP(B65,RemitTable2,9,FALSE),0)+Y65+Z65</f>
+        <v/>
+      </c>
+      <c r="AB65" s="303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC65" s="302">
+        <f>ROUND(AA65/AB65,0)</f>
+        <v/>
+      </c>
+      <c r="AD65" s="296" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE65" s="299" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AF65" s="298" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="296" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="296" t="inlineStr">
+        <is>
+          <t>GPO471</t>
+        </is>
+      </c>
+      <c r="C66" s="297" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D66" s="296" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E66" s="297" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F66" s="298" t="n">
+        <v>46088</v>
+      </c>
+      <c r="G66" s="299" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H66" s="300" t="n">
+        <v>500</v>
+      </c>
+      <c r="I66" s="301" t="n">
+        <v>1506.4</v>
+      </c>
+      <c r="J66" s="302" t="n">
+        <v>753200</v>
+      </c>
+      <c r="K66" s="302" t="n">
+        <v>753200</v>
+      </c>
+      <c r="L66" s="302" t="n">
+        <v>763</v>
+      </c>
+      <c r="M66" s="302" t="n">
+        <v>610</v>
+      </c>
+      <c r="N66" s="296" t="inlineStr">
+        <is>
+          <t>Dolby Atmos License</t>
+        </is>
+      </c>
+      <c r="O66" s="299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P66" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q66" s="300">
+        <f>IF(P66="","",IFERROR(VLOOKUP(O66,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R66" s="302">
+        <f>IF(P66="","",H66)</f>
+        <v/>
+      </c>
+      <c r="S66" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="298" t="n"/>
+      <c r="V66" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W66" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y66" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="302">
+        <f>S66+W66</f>
+        <v/>
+      </c>
+      <c r="AA66" s="302">
+        <f>K66+L66+M66+IFERROR(VLOOKUP(B66,RemitTable2,9,FALSE),0)+Y66+Z66</f>
+        <v/>
+      </c>
+      <c r="AB66" s="303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="302">
+        <f>ROUND(AA66/AB66,0)</f>
+        <v/>
+      </c>
+      <c r="AD66" s="296" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE66" s="299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF66" s="298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="296" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="296" t="inlineStr">
+        <is>
+          <t>CPO694</t>
+        </is>
+      </c>
+      <c r="C67" s="297" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D67" s="296" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E67" s="297" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F67" s="298" t="n">
+        <v>46109</v>
+      </c>
+      <c r="G67" s="299" t="n">
+        <v>46146</v>
+      </c>
+      <c r="H67" s="300" t="n">
+        <v>17404</v>
+      </c>
+      <c r="I67" s="301" t="n">
+        <v>1474.9</v>
+      </c>
+      <c r="J67" s="302" t="n">
+        <v>25669160</v>
+      </c>
+      <c r="K67" s="302" t="n">
+        <v>25669160</v>
+      </c>
+      <c r="L67" s="302" t="n">
+        <v>10147</v>
+      </c>
+      <c r="M67" s="302" t="n">
+        <v>6494</v>
+      </c>
+      <c r="N67" s="296" t="inlineStr">
+        <is>
+          <t>EW (CGV 동백 외)</t>
+        </is>
+      </c>
+      <c r="O67" s="299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P67" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q67" s="300">
+        <f>IF(P67="","",IFERROR(VLOOKUP(O67,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R67" s="302">
+        <f>IF(P67="","",H67)</f>
+        <v/>
+      </c>
+      <c r="S67" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="298" t="n"/>
+      <c r="V67" s="296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W67" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" s="297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y67" s="302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="302">
+        <f>S67+W67</f>
+        <v/>
+      </c>
+      <c r="AA67" s="302">
+        <f>K67+L67+M67+IFERROR(VLOOKUP(B67,RemitTable2,9,FALSE),0)+Y67+Z67</f>
+        <v/>
+      </c>
+      <c r="AB67" s="303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC67" s="302">
+        <f>ROUND(AA67/AB67,0)</f>
+        <v/>
+      </c>
+      <c r="AD67" s="296" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE61" s="299" t="inlineStr">
+      <c r="AE67" s="299" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AF61" s="298" t="inlineStr">
+      <c r="AF67" s="298" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="304" t="n">
-        <v>46</v>
-      </c>
-      <c r="B62" s="304" t="inlineStr">
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="304" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="304" t="inlineStr">
         <is>
           <t>CPO697</t>
         </is>
       </c>
-      <c r="C62" s="304" t="inlineStr">
+      <c r="C68" s="304" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D62" s="304" t="inlineStr">
+      <c r="D68" s="304" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E62" s="304" t="inlineStr">
+      <c r="E68" s="304" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F62" s="305" t="n">
+      <c r="F68" s="305" t="n">
         <v>46136</v>
       </c>
-      <c r="G62" s="305" t="n">
+      <c r="G68" s="305" t="n">
         <v>46171</v>
       </c>
-      <c r="H62" s="306" t="n">
+      <c r="H68" s="306" t="n">
         <v>15289</v>
       </c>
-      <c r="I62" s="307" t="n">
+      <c r="I68" s="307" t="n">
         <v>1502.7</v>
       </c>
-      <c r="J62" s="308" t="n">
+      <c r="J68" s="308" t="n">
         <v>22974780</v>
       </c>
-      <c r="K62" s="308" t="n">
+      <c r="K68" s="308" t="n">
         <v>22974780</v>
       </c>
-      <c r="L62" s="308" t="n">
+      <c r="L68" s="308" t="n">
         <v>1880</v>
       </c>
-      <c r="M62" s="308" t="n">
+      <c r="M68" s="308" t="n">
         <v>1203</v>
       </c>
-      <c r="N62" s="304" t="inlineStr">
+      <c r="N68" s="304" t="inlineStr">
         <is>
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O62" s="305" t="inlineStr">
+      <c r="O68" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P62" s="304" t="inlineStr">
+      <c r="P68" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q62" s="306">
-        <f>IF(P62="","",IFERROR(VLOOKUP(O62,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R62" s="306">
-        <f>IF(P62="","",H62)</f>
-        <v/>
-      </c>
-      <c r="S62" s="308" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="308" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="305" t="n"/>
-      <c r="V62" s="304" t="inlineStr">
+      <c r="Q68" s="306">
+        <f>IF(P68="","",IFERROR(VLOOKUP(O68,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R68" s="306">
+        <f>IF(P68="","",H68)</f>
+        <v/>
+      </c>
+      <c r="S68" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="305" t="n"/>
+      <c r="V68" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W62" s="308" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="304" t="inlineStr">
+      <c r="W68" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y62" s="308" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="308">
-        <f>S62+W62</f>
-        <v/>
-      </c>
-      <c r="AA62" s="308">
-        <f>K62+L62+M62+IFERROR(VLOOKUP(B62,RemitTable2,9,FALSE),0)+Y62+Z62</f>
-        <v/>
-      </c>
-      <c r="AB62" s="309" t="n">
+      <c r="Y68" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="308">
+        <f>S68+W68</f>
+        <v/>
+      </c>
+      <c r="AA68" s="308">
+        <f>K68+L68+M68+IFERROR(VLOOKUP(B68,RemitTable2,9,FALSE),0)+Y68+Z68</f>
+        <v/>
+      </c>
+      <c r="AB68" s="309" t="n">
         <v>1</v>
       </c>
-      <c r="AC62" s="308">
-        <f>ROUND(AA62/AB62,0)</f>
-        <v/>
-      </c>
-      <c r="AD62" s="304" t="inlineStr">
+      <c r="AC68" s="308">
+        <f>ROUND(AA68/AB68,0)</f>
+        <v/>
+      </c>
+      <c r="AD68" s="304" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE62" s="305" t="n">
+      <c r="AE68" s="305" t="n">
         <v>46168</v>
       </c>
-      <c r="AF62" s="305" t="n">
+      <c r="AF68" s="305" t="n">
         <v>46532</v>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="304" t="n">
-        <v>47</v>
-      </c>
-      <c r="B63" s="304" t="inlineStr">
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="304" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="304" t="inlineStr">
         <is>
           <t>CPO693-2</t>
         </is>
       </c>
-      <c r="C63" s="304" t="inlineStr">
+      <c r="C69" s="304" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D63" s="304" t="inlineStr">
+      <c r="D69" s="304" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E63" s="304" t="inlineStr">
+      <c r="E69" s="304" t="inlineStr">
         <is>
           <t>워런티(EW)</t>
         </is>
       </c>
-      <c r="F63" s="305" t="n">
+      <c r="F69" s="305" t="n">
         <v>46133</v>
       </c>
-      <c r="G63" s="305" t="inlineStr">
+      <c r="G69" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="306" t="n">
+      <c r="H69" s="306" t="n">
         <v>2550</v>
       </c>
-      <c r="I63" s="307">
-        <f>IFERROR(VLOOKUP(B62,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J63" s="308" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="308">
-        <f>IFERROR(ROUND(H62*I62,0),0)</f>
-        <v/>
-      </c>
-      <c r="L63" s="308">
-        <f>IFERROR(VLOOKUP(B62,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M63" s="308">
-        <f>IFERROR(VLOOKUP(B62,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N63" s="304" t="inlineStr">
+      <c r="I69" s="307">
+        <f>IFERROR(VLOOKUP(B69,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J69" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="308">
+        <f>IFERROR(ROUND(H69*I69,0),0)</f>
+        <v/>
+      </c>
+      <c r="L69" s="308">
+        <f>IFERROR(VLOOKUP(B69,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M69" s="308">
+        <f>IFERROR(VLOOKUP(B69,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N69" s="304" t="inlineStr">
         <is>
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O63" s="305" t="inlineStr">
+      <c r="O69" s="305" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P63" s="304" t="inlineStr">
+      <c r="P69" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q63" s="306">
-        <f>IF(P63="","",IFERROR(VLOOKUP(O63,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R63" s="306">
-        <f>IF(P63="","",H63)</f>
-        <v/>
-      </c>
-      <c r="S63" s="308" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="308" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="305" t="n"/>
-      <c r="V63" s="304" t="inlineStr">
+      <c r="Q69" s="306">
+        <f>IF(P69="","",IFERROR(VLOOKUP(O69,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R69" s="306">
+        <f>IF(P69="","",H69)</f>
+        <v/>
+      </c>
+      <c r="S69" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="305" t="n"/>
+      <c r="V69" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W63" s="308" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" s="304" t="inlineStr">
+      <c r="W69" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" s="304" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y63" s="308" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="308">
-        <f>S63+W63</f>
-        <v/>
-      </c>
-      <c r="AA63" s="308">
-        <f>K63+L63+M63+IFERROR(VLOOKUP(B63,RemitTable2,9,FALSE),0)+Y63+Z63</f>
-        <v/>
-      </c>
-      <c r="AB63" s="309" t="n">
+      <c r="Y69" s="308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="308">
+        <f>S69+W69</f>
+        <v/>
+      </c>
+      <c r="AA69" s="308">
+        <f>K69+L69+M69+IFERROR(VLOOKUP(B69,RemitTable2,9,FALSE),0)+Y69+Z69</f>
+        <v/>
+      </c>
+      <c r="AB69" s="309" t="n">
         <v>1</v>
       </c>
-      <c r="AC63" s="308">
-        <f>ROUND(AA63/AB63,0)</f>
-        <v/>
-      </c>
-      <c r="AD63" s="304" t="inlineStr">
+      <c r="AC69" s="308">
+        <f>ROUND(AA69/AB69,0)</f>
+        <v/>
+      </c>
+      <c r="AD69" s="304" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE63" s="305" t="n">
+      <c r="AE69" s="305" t="n">
         <v>46142</v>
       </c>
-      <c r="AF63" s="305" t="n">
+      <c r="AF69" s="305" t="n">
         <v>46872</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="132" t="n">
-        <v>54</v>
-      </c>
-      <c r="B64" s="132" t="inlineStr">
-        <is>
-          <t>GPO478</t>
-        </is>
-      </c>
-      <c r="C64" s="132" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D64" s="132" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E64" s="132" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F64" s="188" t="n">
-        <v>46127</v>
-      </c>
-      <c r="G64" s="188" t="n">
-        <v>46161</v>
-      </c>
-      <c r="H64" s="134" t="n">
-        <v>180</v>
-      </c>
-      <c r="I64" s="311" t="n">
-        <v>1518.9</v>
-      </c>
-      <c r="J64" s="136" t="n">
-        <v>273402</v>
-      </c>
-      <c r="K64" s="136" t="n">
-        <v>273402</v>
-      </c>
-      <c r="L64" s="136" t="n">
-        <v>2500</v>
-      </c>
-      <c r="M64" s="136" t="n">
-        <v>8000</v>
-      </c>
-      <c r="N64" s="137" t="n"/>
-      <c r="O64" s="189" t="n"/>
-      <c r="P64" s="137" t="n"/>
-      <c r="Q64" s="134">
-        <f>IF(P64="","",IFERROR(VLOOKUP(O64,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R64" s="134">
-        <f>IF(P64="","",H64)</f>
-        <v/>
-      </c>
-      <c r="S64" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" s="188" t="n"/>
-      <c r="V64" s="137" t="n"/>
-      <c r="W64" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y64" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" s="136">
-        <f>S64+W64</f>
-        <v/>
-      </c>
-      <c r="AA64" s="136">
-        <f>K64+L64+M64+IFERROR(VLOOKUP(B64,RemitTable2,9,FALSE),0)+Y64+Z64</f>
-        <v/>
-      </c>
-      <c r="AB64" s="168" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC64" s="136">
-        <f>ROUND(AA64/AB64,0)</f>
-        <v/>
-      </c>
-      <c r="AD64" s="132" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="AE64" s="188" t="n">
-        <v>46143</v>
-      </c>
-      <c r="AF64" s="188" t="n">
-        <v>46507</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="132" t="n">
-        <v>55</v>
-      </c>
-      <c r="B65" s="132" t="inlineStr">
-        <is>
-          <t>GPO480</t>
-        </is>
-      </c>
-      <c r="C65" s="132" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D65" s="132" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E65" s="132" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F65" s="188" t="n">
-        <v>46137</v>
-      </c>
-      <c r="G65" s="188" t="n">
-        <v>46171</v>
-      </c>
-      <c r="H65" s="134" t="n">
-        <v>250</v>
-      </c>
-      <c r="I65" s="311" t="n">
-        <v>1502.8</v>
-      </c>
-      <c r="J65" s="136" t="n">
-        <v>375700</v>
-      </c>
-      <c r="K65" s="136" t="n">
-        <v>375700</v>
-      </c>
-      <c r="L65" s="136" t="n">
-        <v>32</v>
-      </c>
-      <c r="M65" s="136" t="n">
-        <v>20</v>
-      </c>
-      <c r="N65" s="137" t="n"/>
-      <c r="O65" s="189" t="n"/>
-      <c r="P65" s="137" t="n"/>
-      <c r="Q65" s="134">
-        <f>IF(P65="","",IFERROR(VLOOKUP(O65,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R65" s="134">
-        <f>IF(P65="","",H65)</f>
-        <v/>
-      </c>
-      <c r="S65" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="188" t="n"/>
-      <c r="V65" s="137" t="n"/>
-      <c r="W65" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y65" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" s="136">
-        <f>S65+W65</f>
-        <v/>
-      </c>
-      <c r="AA65" s="136">
-        <f>K65+L65+M65+IFERROR(VLOOKUP(B65,RemitTable2,9,FALSE),0)+Y65+Z65</f>
-        <v/>
-      </c>
-      <c r="AB65" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC65" s="136">
-        <f>ROUND(AA65/AB65,0)</f>
-        <v/>
-      </c>
-      <c r="AD65" s="132" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="AE65" s="188" t="n">
-        <v>46143</v>
-      </c>
-      <c r="AF65" s="188" t="n">
-        <v>49795</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="132" t="n">
-        <v>56</v>
-      </c>
-      <c r="B66" s="132" t="inlineStr">
-        <is>
-          <t>GPO481</t>
-        </is>
-      </c>
-      <c r="C66" s="132" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D66" s="132" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E66" s="132" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F66" s="188" t="n">
-        <v>46152</v>
-      </c>
-      <c r="G66" s="188" t="n">
-        <v>46183</v>
-      </c>
-      <c r="H66" s="134" t="n">
-        <v>500</v>
-      </c>
-      <c r="I66" s="311" t="n">
-        <v>1525.3</v>
-      </c>
-      <c r="J66" s="136" t="n">
-        <v>762650</v>
-      </c>
-      <c r="K66" s="136" t="n">
-        <v>762650</v>
-      </c>
-      <c r="L66" s="136" t="n">
-        <v>52</v>
-      </c>
-      <c r="M66" s="136" t="n">
-        <v>34</v>
-      </c>
-      <c r="N66" s="137" t="n"/>
-      <c r="O66" s="189" t="n"/>
-      <c r="P66" s="137" t="n"/>
-      <c r="Q66" s="134">
-        <f>IF(P66="","",IFERROR(VLOOKUP(O66,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R66" s="134">
-        <f>IF(P66="","",H66)</f>
-        <v/>
-      </c>
-      <c r="S66" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="188" t="n"/>
-      <c r="V66" s="137" t="n"/>
-      <c r="W66" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y66" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="136">
-        <f>S66+W66</f>
-        <v/>
-      </c>
-      <c r="AA66" s="136">
-        <f>K66+L66+M66+IFERROR(VLOOKUP(B66,RemitTable2,9,FALSE),0)+Y66+Z66</f>
-        <v/>
-      </c>
-      <c r="AB66" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC66" s="136">
-        <f>ROUND(AA66/AB66,0)</f>
-        <v/>
-      </c>
-      <c r="AD66" s="132" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="AE66" s="188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF66" s="188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="132" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="132" t="inlineStr">
-        <is>
-          <t>GPO475</t>
-        </is>
-      </c>
-      <c r="C67" s="132" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D67" s="132" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E67" s="132" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F67" s="188" t="n">
-        <v>46127</v>
-      </c>
-      <c r="G67" s="188" t="n">
-        <v>46190</v>
-      </c>
-      <c r="H67" s="134" t="n">
-        <v>540</v>
-      </c>
-      <c r="I67" s="311" t="n">
-        <v>1516.8</v>
-      </c>
-      <c r="J67" s="136" t="n">
-        <v>819072</v>
-      </c>
-      <c r="K67" s="136" t="n">
-        <v>819072</v>
-      </c>
-      <c r="L67" s="136" t="n">
-        <v>1985</v>
-      </c>
-      <c r="M67" s="136" t="n">
-        <v>2118</v>
-      </c>
-      <c r="N67" s="132" t="inlineStr">
-        <is>
-          <t>TMS-1000 License 6 screens (CGV 안동)</t>
-        </is>
-      </c>
-      <c r="O67" s="189" t="n"/>
-      <c r="P67" s="137" t="n"/>
-      <c r="Q67" s="134">
-        <f>IF(P67="","",IFERROR(VLOOKUP(O67,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R67" s="134">
-        <f>IF(P67="","",H67)</f>
-        <v/>
-      </c>
-      <c r="S67" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="188" t="n"/>
-      <c r="V67" s="137" t="n"/>
-      <c r="W67" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y67" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" s="136">
-        <f>S67+W67</f>
-        <v/>
-      </c>
-      <c r="AA67" s="136">
-        <f>K67+L67+M67+IFERROR(VLOOKUP(B67,RemitTable2,9,FALSE),0)+Y67+Z67</f>
-        <v/>
-      </c>
-      <c r="AB67" s="168" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC67" s="136">
-        <f>ROUND(AA67/AB67,0)</f>
-        <v/>
-      </c>
-      <c r="AD67" s="132" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="AE67" s="188" t="n">
-        <v>46143</v>
-      </c>
-      <c r="AF67" s="188" t="n">
-        <v>46507</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="132" t="n">
-        <v>68</v>
-      </c>
-      <c r="B68" s="132" t="inlineStr">
-        <is>
-          <t>CPO702</t>
-        </is>
-      </c>
-      <c r="C68" s="132" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D68" s="132" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E68" s="132" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F68" s="188" t="n">
-        <v>46181</v>
-      </c>
-      <c r="G68" s="188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="134" t="n">
-        <v>32715</v>
-      </c>
-      <c r="I68" s="311" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="132" t="inlineStr">
-        <is>
-          <t>EW CP2215/CP2309-RGB 24대 (롯데 영천/CineQ 청라/CGV 동두천 외)</t>
-        </is>
-      </c>
-      <c r="O68" s="189" t="n"/>
-      <c r="P68" s="137" t="n"/>
-      <c r="Q68" s="134">
-        <f>IF(P68="","",IFERROR(VLOOKUP(O68,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R68" s="134">
-        <f>IF(P68="","",H68)</f>
-        <v/>
-      </c>
-      <c r="S68" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="188" t="n"/>
-      <c r="V68" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W68" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y68" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="136">
-        <f>S68+W68</f>
-        <v/>
-      </c>
-      <c r="AA68" s="136">
-        <f>K68+L68+M68+IFERROR(VLOOKUP(B68,RemitTable2,9,FALSE),0)+Y68+Z68</f>
-        <v/>
-      </c>
-      <c r="AB68" s="168" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC68" s="136">
-        <f>ROUND(AA68/AB68,0)</f>
-        <v/>
-      </c>
-      <c r="AD68" s="132" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="AE68" s="188" t="n">
-        <v>46192</v>
-      </c>
-      <c r="AF68" s="188" t="n">
-        <v>46752</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="132" t="n">
-        <v>69</v>
-      </c>
-      <c r="B69" s="132" t="inlineStr">
-        <is>
-          <t>GPO486</t>
-        </is>
-      </c>
-      <c r="C69" s="132" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D69" s="132" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E69" s="132" t="inlineStr">
-        <is>
-          <t>라이센스</t>
-        </is>
-      </c>
-      <c r="F69" s="188" t="n">
-        <v>46182</v>
-      </c>
-      <c r="G69" s="188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="134" t="n">
-        <v>450</v>
-      </c>
-      <c r="I69" s="311" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="132" t="inlineStr">
-        <is>
-          <t>TMS-1000 License Extension 5screens (메가박스 경산 하양)</t>
-        </is>
-      </c>
-      <c r="O69" s="189" t="n"/>
-      <c r="P69" s="137" t="n"/>
-      <c r="Q69" s="134">
-        <f>IF(P69="","",IFERROR(VLOOKUP(O69,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R69" s="134">
-        <f>IF(P69="","",H69)</f>
-        <v/>
-      </c>
-      <c r="S69" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" s="188" t="n"/>
-      <c r="V69" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W69" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y69" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" s="136">
-        <f>S69+W69</f>
-        <v/>
-      </c>
-      <c r="AA69" s="136">
-        <f>K69+L69+M69+IFERROR(VLOOKUP(B69,RemitTable2,9,FALSE),0)+Y69+Z69</f>
-        <v/>
-      </c>
-      <c r="AB69" s="168" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC69" s="136">
-        <f>ROUND(AA69/AB69,0)</f>
-        <v/>
-      </c>
-      <c r="AD69" s="132" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="AE69" s="188" t="n">
-        <v>46204</v>
-      </c>
-      <c r="AF69" s="188" t="n">
-        <v>46568</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="132" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B70" s="132" t="inlineStr">
         <is>
-          <t>GPO484</t>
+          <t>GPO478</t>
         </is>
       </c>
       <c r="C70" s="132" t="inlineStr">
@@ -10026,40 +10223,34 @@
       </c>
       <c r="E70" s="132" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F70" s="188" t="n">
-        <v>46183</v>
-      </c>
-      <c r="G70" s="188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46127</v>
+      </c>
+      <c r="G70" s="188" t="n">
+        <v>46161</v>
       </c>
       <c r="H70" s="134" t="n">
-        <v>7407.81</v>
+        <v>180</v>
       </c>
       <c r="I70" s="311" t="n">
-        <v>0</v>
+        <v>1518.9</v>
       </c>
       <c r="J70" s="136" t="n">
-        <v>0</v>
+        <v>273402</v>
       </c>
       <c r="K70" s="136" t="n">
-        <v>0</v>
+        <v>273402</v>
       </c>
       <c r="L70" s="136" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="M70" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="132" t="inlineStr">
-        <is>
-          <t>SR-1000/SX-4000 Warranty Ext 11대 (CGV 진주혁신/합천/구례)</t>
-        </is>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="N70" s="137" t="n"/>
       <c r="O70" s="189" t="n"/>
       <c r="P70" s="137" t="n"/>
       <c r="Q70" s="134">
@@ -10077,11 +10268,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="188" t="n"/>
-      <c r="V70" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="V70" s="137" t="n"/>
       <c r="W70" s="136" t="n">
         <v>0</v>
       </c>
@@ -10102,7 +10289,7 @@
         <v/>
       </c>
       <c r="AB70" s="168" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AC70" s="136">
         <f>ROUND(AA70/AB70,0)</f>
@@ -10114,19 +10301,19 @@
         </is>
       </c>
       <c r="AE70" s="188" t="n">
-        <v>46156</v>
+        <v>46143</v>
       </c>
       <c r="AF70" s="188" t="n">
-        <v>46752</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="132" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B71" s="132" t="inlineStr">
         <is>
-          <t>GPO489</t>
+          <t>GPO480</t>
         </is>
       </c>
       <c r="C71" s="132" t="inlineStr">
@@ -10145,36 +10332,30 @@
         </is>
       </c>
       <c r="F71" s="188" t="n">
-        <v>46196</v>
-      </c>
-      <c r="G71" s="188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46137</v>
+      </c>
+      <c r="G71" s="188" t="n">
+        <v>46171</v>
       </c>
       <c r="H71" s="134" t="n">
-        <v>3320</v>
+        <v>250</v>
       </c>
       <c r="I71" s="311" t="n">
-        <v>0</v>
+        <v>1502.8</v>
       </c>
       <c r="J71" s="136" t="n">
-        <v>0</v>
+        <v>375700</v>
       </c>
       <c r="K71" s="136" t="n">
-        <v>0</v>
+        <v>375700</v>
       </c>
       <c r="L71" s="136" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M71" s="136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="132" t="inlineStr">
-        <is>
-          <t>TMS License 7사이트 32screens (메가박스 삼천포/CGV 대구수성 외)</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N71" s="137" t="n"/>
       <c r="O71" s="189" t="n"/>
       <c r="P71" s="137" t="n"/>
       <c r="Q71" s="134">
@@ -10192,11 +10373,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="188" t="n"/>
-      <c r="V71" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="V71" s="137" t="n"/>
       <c r="W71" s="136" t="n">
         <v>0</v>
       </c>
@@ -10217,7 +10394,7 @@
         <v/>
       </c>
       <c r="AB71" s="168" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AC71" s="136">
         <f>ROUND(AA71/AB71,0)</f>
@@ -10225,794 +10402,1588 @@
       </c>
       <c r="AD71" s="132" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE71" s="188" t="n">
+        <v>46143</v>
+      </c>
+      <c r="AF71" s="188" t="n">
+        <v>49795</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="132" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="132" t="inlineStr">
+        <is>
+          <t>GPO481</t>
+        </is>
+      </c>
+      <c r="C72" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D72" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E72" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F72" s="188" t="n">
+        <v>46152</v>
+      </c>
+      <c r="G72" s="188" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H72" s="134" t="n">
+        <v>500</v>
+      </c>
+      <c r="I72" s="311" t="n">
+        <v>1525.3</v>
+      </c>
+      <c r="J72" s="136" t="n">
+        <v>762650</v>
+      </c>
+      <c r="K72" s="136" t="n">
+        <v>762650</v>
+      </c>
+      <c r="L72" s="136" t="n">
+        <v>52</v>
+      </c>
+      <c r="M72" s="136" t="n">
+        <v>34</v>
+      </c>
+      <c r="N72" s="137" t="n"/>
+      <c r="O72" s="189" t="n"/>
+      <c r="P72" s="137" t="n"/>
+      <c r="Q72" s="134">
+        <f>IF(P72="","",IFERROR(VLOOKUP(O72,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R72" s="134">
+        <f>IF(P72="","",H72)</f>
+        <v/>
+      </c>
+      <c r="S72" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="188" t="n"/>
+      <c r="V72" s="137" t="n"/>
+      <c r="W72" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y72" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="136">
+        <f>S72+W72</f>
+        <v/>
+      </c>
+      <c r="AA72" s="136">
+        <f>K72+L72+M72+IFERROR(VLOOKUP(B72,RemitTable2,9,FALSE),0)+Y72+Z72</f>
+        <v/>
+      </c>
+      <c r="AB72" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC72" s="136">
+        <f>ROUND(AA72/AB72,0)</f>
+        <v/>
+      </c>
+      <c r="AD72" s="132" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AE72" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF72" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="132" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="132" t="inlineStr">
+        <is>
+          <t>GPO475</t>
+        </is>
+      </c>
+      <c r="C73" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D73" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E73" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F73" s="188" t="n">
+        <v>46127</v>
+      </c>
+      <c r="G73" s="188" t="n">
+        <v>46190</v>
+      </c>
+      <c r="H73" s="134" t="n">
+        <v>540</v>
+      </c>
+      <c r="I73" s="311" t="n">
+        <v>1516.8</v>
+      </c>
+      <c r="J73" s="136" t="n">
+        <v>819072</v>
+      </c>
+      <c r="K73" s="136" t="n">
+        <v>819072</v>
+      </c>
+      <c r="L73" s="136" t="n">
+        <v>1985</v>
+      </c>
+      <c r="M73" s="136" t="n">
+        <v>2118</v>
+      </c>
+      <c r="N73" s="132" t="inlineStr">
+        <is>
+          <t>TMS-1000 License 6 screens (CGV 안동)</t>
+        </is>
+      </c>
+      <c r="O73" s="189" t="n"/>
+      <c r="P73" s="137" t="n"/>
+      <c r="Q73" s="134">
+        <f>IF(P73="","",IFERROR(VLOOKUP(O73,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R73" s="134">
+        <f>IF(P73="","",H73)</f>
+        <v/>
+      </c>
+      <c r="S73" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" s="188" t="n"/>
+      <c r="V73" s="137" t="n"/>
+      <c r="W73" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y73" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="136">
+        <f>S73+W73</f>
+        <v/>
+      </c>
+      <c r="AA73" s="136">
+        <f>K73+L73+M73+IFERROR(VLOOKUP(B73,RemitTable2,9,FALSE),0)+Y73+Z73</f>
+        <v/>
+      </c>
+      <c r="AB73" s="168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC73" s="136">
+        <f>ROUND(AA73/AB73,0)</f>
+        <v/>
+      </c>
+      <c r="AD73" s="132" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE73" s="188" t="n">
+        <v>46143</v>
+      </c>
+      <c r="AF73" s="188" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="132" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="132" t="inlineStr">
+        <is>
+          <t>CPO702</t>
+        </is>
+      </c>
+      <c r="C74" s="132" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D74" s="132" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E74" s="132" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F74" s="188" t="n">
+        <v>46181</v>
+      </c>
+      <c r="G74" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="134" t="n">
+        <v>32715</v>
+      </c>
+      <c r="I74" s="311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="132" t="inlineStr">
+        <is>
+          <t>EW CP2215/CP2309-RGB 25대 (롯데 영천/CineQ 청라/CGV 동두천 외)</t>
+        </is>
+      </c>
+      <c r="O74" s="189" t="n"/>
+      <c r="P74" s="137" t="n"/>
+      <c r="Q74" s="134">
+        <f>IF(P74="","",IFERROR(VLOOKUP(O74,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R74" s="134">
+        <f>IF(P74="","",H74)</f>
+        <v/>
+      </c>
+      <c r="S74" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="188" t="n"/>
+      <c r="V74" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W74" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y74" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="136">
+        <f>S74+W74</f>
+        <v/>
+      </c>
+      <c r="AA74" s="136">
+        <f>K74+L74+M74+IFERROR(VLOOKUP(B74,RemitTable2,9,FALSE),0)+Y74+Z74</f>
+        <v/>
+      </c>
+      <c r="AB74" s="168" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC74" s="136">
+        <f>ROUND(AA74/AB74,0)</f>
+        <v/>
+      </c>
+      <c r="AD74" s="132" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="AE74" s="188" t="n">
+        <v>46192</v>
+      </c>
+      <c r="AF74" s="188" t="n">
+        <v>46752</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="132" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="132" t="inlineStr">
+        <is>
+          <t>GPO486</t>
+        </is>
+      </c>
+      <c r="C75" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D75" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E75" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F75" s="188" t="n">
+        <v>46182</v>
+      </c>
+      <c r="G75" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="134" t="n">
+        <v>450</v>
+      </c>
+      <c r="I75" s="311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="132" t="inlineStr">
+        <is>
+          <t>TMS-1000 License Extension 5screens (메가박스 경산 하양)</t>
+        </is>
+      </c>
+      <c r="O75" s="189" t="n"/>
+      <c r="P75" s="137" t="n"/>
+      <c r="Q75" s="134">
+        <f>IF(P75="","",IFERROR(VLOOKUP(O75,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R75" s="134">
+        <f>IF(P75="","",H75)</f>
+        <v/>
+      </c>
+      <c r="S75" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" s="188" t="n"/>
+      <c r="V75" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W75" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y75" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="136">
+        <f>S75+W75</f>
+        <v/>
+      </c>
+      <c r="AA75" s="136">
+        <f>K75+L75+M75+IFERROR(VLOOKUP(B75,RemitTable2,9,FALSE),0)+Y75+Z75</f>
+        <v/>
+      </c>
+      <c r="AB75" s="168" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC75" s="136">
+        <f>ROUND(AA75/AB75,0)</f>
+        <v/>
+      </c>
+      <c r="AD75" s="132" t="inlineStr">
+        <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="AE71" s="188" t="n">
+      <c r="AE75" s="188" t="n">
         <v>46204</v>
       </c>
-      <c r="AF71" s="188" t="n">
+      <c r="AF75" s="188" t="n">
         <v>46568</v>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="284" t="n">
-        <v>48</v>
-      </c>
-      <c r="B72" s="284" t="inlineStr">
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="132" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="132" t="inlineStr">
+        <is>
+          <t>GPO484</t>
+        </is>
+      </c>
+      <c r="C76" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D76" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E76" s="132" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F76" s="188" t="n">
+        <v>46183</v>
+      </c>
+      <c r="G76" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="134" t="n">
+        <v>7407.81</v>
+      </c>
+      <c r="I76" s="311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="132" t="inlineStr">
+        <is>
+          <t>SR-1000/SX-4000 Warranty Ext 11대 (CGV 진주혁신/합천/구례)</t>
+        </is>
+      </c>
+      <c r="O76" s="189" t="n"/>
+      <c r="P76" s="137" t="n"/>
+      <c r="Q76" s="134">
+        <f>IF(P76="","",IFERROR(VLOOKUP(O76,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R76" s="134">
+        <f>IF(P76="","",H76)</f>
+        <v/>
+      </c>
+      <c r="S76" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="188" t="n"/>
+      <c r="V76" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W76" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y76" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="136">
+        <f>S76+W76</f>
+        <v/>
+      </c>
+      <c r="AA76" s="136">
+        <f>K76+L76+M76+IFERROR(VLOOKUP(B76,RemitTable2,9,FALSE),0)+Y76+Z76</f>
+        <v/>
+      </c>
+      <c r="AB76" s="168" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC76" s="136">
+        <f>ROUND(AA76/AB76,0)</f>
+        <v/>
+      </c>
+      <c r="AD76" s="132" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="AE76" s="188" t="n">
+        <v>46156</v>
+      </c>
+      <c r="AF76" s="188" t="n">
+        <v>46752</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="132" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="132" t="inlineStr">
+        <is>
+          <t>GPO489</t>
+        </is>
+      </c>
+      <c r="C77" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D77" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E77" s="132" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+      <c r="F77" s="188" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G77" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="134" t="n">
+        <v>3320</v>
+      </c>
+      <c r="I77" s="311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="132" t="inlineStr">
+        <is>
+          <t>TMS License 7사이트 32screens (메가박스 삼천포/CGV 대구수성 외)</t>
+        </is>
+      </c>
+      <c r="O77" s="189" t="n"/>
+      <c r="P77" s="137" t="n"/>
+      <c r="Q77" s="134">
+        <f>IF(P77="","",IFERROR(VLOOKUP(O77,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R77" s="134">
+        <f>IF(P77="","",H77)</f>
+        <v/>
+      </c>
+      <c r="S77" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="188" t="n"/>
+      <c r="V77" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W77" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y77" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="136">
+        <f>S77+W77</f>
+        <v/>
+      </c>
+      <c r="AA77" s="136">
+        <f>K77+L77+M77+IFERROR(VLOOKUP(B77,RemitTable2,9,FALSE),0)+Y77+Z77</f>
+        <v/>
+      </c>
+      <c r="AB77" s="168" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC77" s="136">
+        <f>ROUND(AA77/AB77,0)</f>
+        <v/>
+      </c>
+      <c r="AD77" s="132" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE77" s="188" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AF77" s="188" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="132" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="132" t="inlineStr">
+        <is>
+          <t>GPO487</t>
+        </is>
+      </c>
+      <c r="C78" s="132" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D78" s="132" t="inlineStr">
+        <is>
+          <t>Net 30 days</t>
+        </is>
+      </c>
+      <c r="E78" s="132" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F78" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="134" t="n">
+        <v>5309</v>
+      </c>
+      <c r="I78" s="311">
+        <f>IFERROR(VLOOKUP(B78,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J78" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="136">
+        <f>IFERROR(ROUND(H78*I78,0),0)</f>
+        <v/>
+      </c>
+      <c r="L78" s="136">
+        <f>IFERROR(VLOOKUP(B78,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M78" s="136">
+        <f>IFERROR(VLOOKUP(B78,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N78" s="132" t="inlineStr">
+        <is>
+          <t>SX-3000 EW 133대 (롯데, gross 33,309 차감 보상판매 Credit 28,000)</t>
+        </is>
+      </c>
+      <c r="O78" s="189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P78" s="137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q78" s="134">
+        <f>IF(P78="","",IFERROR(VLOOKUP(O78,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R78" s="134">
+        <f>IF(P78="","",H78)</f>
+        <v/>
+      </c>
+      <c r="S78" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="188" t="n"/>
+      <c r="V78" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W78" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y78" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="136">
+        <f>S78+W78</f>
+        <v/>
+      </c>
+      <c r="AA78" s="136">
+        <f>K78+L78+M78+IFERROR(VLOOKUP(B78,RemitTable2,9,FALSE),0)+Y78+Z78</f>
+        <v/>
+      </c>
+      <c r="AB78" s="168" t="n">
+        <v>133</v>
+      </c>
+      <c r="AC78" s="136">
+        <f>ROUND(AA78/AB78,0)</f>
+        <v/>
+      </c>
+      <c r="AD78" s="132" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="AE78" s="188" t="n">
+        <v>46204</v>
+      </c>
+      <c r="AF78" s="188" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="284" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="284" t="inlineStr">
         <is>
           <t>CPO688</t>
         </is>
       </c>
-      <c r="C72" s="285" t="inlineStr">
+      <c r="C79" s="285" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D72" s="284" t="inlineStr">
+      <c r="D79" s="284" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E72" s="285" t="inlineStr">
+      <c r="E79" s="285" t="inlineStr">
         <is>
           <t>Inspection</t>
         </is>
       </c>
-      <c r="F72" s="286" t="n">
+      <c r="F79" s="286" t="n">
         <v>46037</v>
       </c>
-      <c r="G72" s="287" t="inlineStr">
+      <c r="G79" s="287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H72" s="288" t="n">
+      <c r="H79" s="288" t="n">
         <v>4180</v>
       </c>
-      <c r="I72" s="289">
-        <f>IFERROR(VLOOKUP(B67,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J72" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="290">
-        <f>IFERROR(ROUND(H67*I67,0),0)</f>
-        <v/>
-      </c>
-      <c r="L72" s="290">
-        <f>IFERROR(VLOOKUP(B67,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M72" s="290">
-        <f>IFERROR(VLOOKUP(B67,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N72" s="284" t="inlineStr">
+      <c r="I79" s="289">
+        <f>IFERROR(VLOOKUP(B79,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J79" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="290">
+        <f>IFERROR(ROUND(H79*I79,0),0)</f>
+        <v/>
+      </c>
+      <c r="L79" s="290">
+        <f>IFERROR(VLOOKUP(B79,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M79" s="290">
+        <f>IFERROR(VLOOKUP(B79,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N79" s="284" t="inlineStr">
         <is>
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O72" s="287" t="inlineStr">
+      <c r="O79" s="287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P72" s="284" t="inlineStr">
+      <c r="P79" s="284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q72" s="288">
-        <f>IF(P72="","",IFERROR(VLOOKUP(O72,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R72" s="290">
-        <f>IF(P72="","",H72)</f>
-        <v/>
-      </c>
-      <c r="S72" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="286" t="n"/>
-      <c r="V72" s="284" t="inlineStr">
+      <c r="Q79" s="288">
+        <f>IF(P79="","",IFERROR(VLOOKUP(O79,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R79" s="290">
+        <f>IF(P79="","",H79)</f>
+        <v/>
+      </c>
+      <c r="S79" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="286" t="n"/>
+      <c r="V79" s="284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W72" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" s="285" t="inlineStr">
+      <c r="W79" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y72" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="290">
-        <f>S72+W72</f>
-        <v/>
-      </c>
-      <c r="AA72" s="290">
-        <f>K72+L72+M72+IFERROR(VLOOKUP(B72,RemitTable2,9,FALSE),0)+Y72+Z72</f>
-        <v/>
-      </c>
-      <c r="AB72" s="291" t="n">
+      <c r="Y79" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="290">
+        <f>S79+W79</f>
+        <v/>
+      </c>
+      <c r="AA79" s="290">
+        <f>K79+L79+M79+IFERROR(VLOOKUP(B79,RemitTable2,9,FALSE),0)+Y79+Z79</f>
+        <v/>
+      </c>
+      <c r="AB79" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="AC72" s="290">
-        <f>ROUND(AA72/AB72,0)</f>
-        <v/>
-      </c>
-      <c r="AD72" s="284" t="inlineStr">
+      <c r="AC79" s="290">
+        <f>ROUND(AA79/AB79,0)</f>
+        <v/>
+      </c>
+      <c r="AD79" s="284" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE72" s="287" t="inlineStr">
+      <c r="AE79" s="287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF72" s="286" t="inlineStr">
+      <c r="AF79" s="286" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="284" t="n">
-        <v>49</v>
-      </c>
-      <c r="B73" s="284" t="inlineStr">
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="284" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="284" t="inlineStr">
         <is>
           <t>SX3000수리</t>
         </is>
       </c>
-      <c r="C73" s="285" t="inlineStr">
+      <c r="C80" s="285" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D73" s="284" t="inlineStr">
+      <c r="D80" s="284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E73" s="285" t="inlineStr">
+      <c r="E80" s="285" t="inlineStr">
         <is>
           <t>수리반환</t>
         </is>
       </c>
-      <c r="F73" s="286" t="n"/>
-      <c r="G73" s="287" t="inlineStr">
+      <c r="F80" s="286" t="n"/>
+      <c r="G80" s="287" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H73" s="288" t="n">
+      <c r="H80" s="288" t="n">
         <v>400</v>
       </c>
-      <c r="I73" s="289">
-        <f>IFERROR(VLOOKUP(B68,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J73" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="290">
-        <f>IFERROR(ROUND(H68*I68,0),0)</f>
-        <v/>
-      </c>
-      <c r="L73" s="290">
-        <f>IFERROR(VLOOKUP(B68,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M73" s="290">
-        <f>IFERROR(VLOOKUP(B68,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N73" s="284" t="inlineStr">
+      <c r="I80" s="289">
+        <f>IFERROR(VLOOKUP(B80,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J80" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="290">
+        <f>IFERROR(ROUND(H80*I80,0),0)</f>
+        <v/>
+      </c>
+      <c r="L80" s="290">
+        <f>IFERROR(VLOOKUP(B80,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M80" s="290">
+        <f>IFERROR(VLOOKUP(B80,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N80" s="284" t="inlineStr">
         <is>
           <t>Display Card (수리반환 5PCS)</t>
         </is>
       </c>
-      <c r="O73" s="287" t="n">
+      <c r="O80" s="287" t="n">
         <v>46125</v>
       </c>
-      <c r="P73" s="284" t="inlineStr">
+      <c r="P80" s="284" t="inlineStr">
         <is>
           <t>22356-26-351613M</t>
         </is>
       </c>
-      <c r="Q73" s="288">
-        <f>IF(P73="","",IFERROR(VLOOKUP(O73,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R73" s="290">
-        <f>IF(P73="","",H73)</f>
-        <v/>
-      </c>
-      <c r="S73" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" s="290" t="n">
+      <c r="Q80" s="288">
+        <f>IF(P80="","",IFERROR(VLOOKUP(O80,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R80" s="290">
+        <f>IF(P80="","",H80)</f>
+        <v/>
+      </c>
+      <c r="S80" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="290" t="n">
         <v>67750</v>
       </c>
-      <c r="U73" s="286" t="n"/>
-      <c r="V73" s="284" t="inlineStr">
+      <c r="U80" s="286" t="n"/>
+      <c r="V80" s="284" t="inlineStr">
         <is>
           <t>운서합동</t>
         </is>
       </c>
-      <c r="W73" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" s="285" t="inlineStr">
+      <c r="W80" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="285" t="inlineStr">
         <is>
           <t>DHL</t>
         </is>
       </c>
-      <c r="Y73" s="290" t="n">
+      <c r="Y80" s="290" t="n">
         <v>216006</v>
       </c>
-      <c r="Z73" s="290">
-        <f>S73+W73</f>
-        <v/>
-      </c>
-      <c r="AA73" s="290">
-        <f>K73+L73+M73+IFERROR(VLOOKUP(B73,RemitTable2,9,FALSE),0)+Y73+Z73</f>
-        <v/>
-      </c>
-      <c r="AB73" s="291" t="n">
+      <c r="Z80" s="290">
+        <f>S80+W80</f>
+        <v/>
+      </c>
+      <c r="AA80" s="290">
+        <f>K80+L80+M80+IFERROR(VLOOKUP(B80,RemitTable2,9,FALSE),0)+Y80+Z80</f>
+        <v/>
+      </c>
+      <c r="AB80" s="291" t="n">
         <v>5</v>
       </c>
-      <c r="AC73" s="290">
-        <f>ROUND(AA73/AB73,0)</f>
-        <v/>
-      </c>
-      <c r="AD73" s="284" t="inlineStr">
+      <c r="AC80" s="290">
+        <f>ROUND(AA80/AB80,0)</f>
+        <v/>
+      </c>
+      <c r="AD80" s="284" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE73" s="287" t="n"/>
-      <c r="AF73" s="286" t="n"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="216" t="n">
-        <v>59</v>
-      </c>
-      <c r="B74" s="216" t="inlineStr">
+      <c r="AE80" s="287" t="n"/>
+      <c r="AF80" s="286" t="n"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="216" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="216" t="inlineStr">
         <is>
           <t>FRC-MONOPLEX26</t>
         </is>
       </c>
-      <c r="C74" s="217" t="inlineStr">
+      <c r="C81" s="217" t="inlineStr">
         <is>
           <t>Ferco</t>
         </is>
       </c>
-      <c r="D74" s="216" t="inlineStr">
+      <c r="D81" s="216" t="inlineStr">
         <is>
           <t>50% TT advance + 50% balance</t>
         </is>
       </c>
-      <c r="E74" s="217" t="inlineStr">
+      <c r="E81" s="217" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="F74" s="218" t="n">
+      <c r="F81" s="218" t="n">
         <v>46048</v>
       </c>
-      <c r="G74" s="219" t="n">
+      <c r="G81" s="219" t="n">
         <v>46133</v>
       </c>
-      <c r="H74" s="220" t="n">
+      <c r="H81" s="220" t="n">
         <v>51952</v>
       </c>
-      <c r="I74" s="221">
-        <f>IFERROR(VLOOKUP(B69,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J74" s="222" t="n">
+      <c r="I81" s="221">
+        <f>IFERROR(VLOOKUP(B81,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J81" s="222" t="n">
         <v>75818749</v>
       </c>
-      <c r="K74" s="222" t="n">
+      <c r="K81" s="222" t="n">
         <v>75818749</v>
       </c>
-      <c r="L74" s="222" t="n">
+      <c r="L81" s="222" t="n">
         <v>25000</v>
       </c>
-      <c r="M74" s="222" t="n">
+      <c r="M81" s="222" t="n">
         <v>16000</v>
       </c>
-      <c r="N74" s="216" t="inlineStr">
+      <c r="N81" s="216" t="inlineStr">
         <is>
           <t>Cinema Seat (Recliner) / 44 EA / Monoplex DH Bangbae</t>
         </is>
       </c>
-      <c r="O74" s="219" t="n">
+      <c r="O81" s="219" t="n">
         <v>46153</v>
       </c>
-      <c r="P74" s="216" t="inlineStr">
+      <c r="P81" s="216" t="inlineStr">
         <is>
           <t>14008-26-101147M</t>
         </is>
       </c>
-      <c r="Q74" s="220">
-        <f>IF(P74="","",IFERROR(VLOOKUP(O74,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R74" s="220">
-        <f>IF(P74="","",H74)</f>
-        <v/>
-      </c>
-      <c r="S74" s="222" t="n">
+      <c r="Q81" s="220">
+        <f>IF(P81="","",IFERROR(VLOOKUP(O81,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R81" s="220">
+        <f>IF(P81="","",H81)</f>
+        <v/>
+      </c>
+      <c r="S81" s="222" t="n">
         <v>31050</v>
       </c>
-      <c r="T74" s="222" t="n">
+      <c r="T81" s="222" t="n">
         <v>7959560</v>
       </c>
-      <c r="U74" s="218" t="n"/>
-      <c r="V74" s="216" t="inlineStr">
+      <c r="U81" s="218" t="n"/>
+      <c r="V81" s="216" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
       </c>
-      <c r="W74" s="222" t="n">
+      <c r="W81" s="222" t="n">
         <v>250000</v>
       </c>
-      <c r="X74" s="217" t="inlineStr">
+      <c r="X81" s="217" t="inlineStr">
         <is>
           <t>진로직스</t>
         </is>
       </c>
-      <c r="Y74" s="222" t="n">
-        <v>5002612</v>
-      </c>
-      <c r="Z74" s="222">
-        <f>S74+W74</f>
-        <v/>
-      </c>
-      <c r="AA74" s="222">
-        <f>K74+L74+M74+IFERROR(VLOOKUP(B74,RemitTable2,9,FALSE),0)+Y74+Z74</f>
-        <v/>
-      </c>
-      <c r="AB74" s="223" t="n">
+      <c r="Y81" s="222" t="n">
+        <v>5233502</v>
+      </c>
+      <c r="Z81" s="222">
+        <f>S81+W81</f>
+        <v/>
+      </c>
+      <c r="AA81" s="222">
+        <f>K81+L81+M81+IFERROR(VLOOKUP(B81,RemitTable2,9,FALSE),0)+Y81+Z81</f>
+        <v/>
+      </c>
+      <c r="AB81" s="223" t="n">
         <v>44</v>
       </c>
-      <c r="AC74" s="222">
-        <f>ROUND(AA74/AB74,0)</f>
-        <v/>
-      </c>
-      <c r="AD74" s="216" t="inlineStr">
+      <c r="AC81" s="222">
+        <f>ROUND(AA81/AB81,0)</f>
+        <v/>
+      </c>
+      <c r="AD81" s="216" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE74" s="219" t="n"/>
-      <c r="AF74" s="218" t="n"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="284" t="n">
-        <v>66</v>
-      </c>
-      <c r="B75" s="284" t="inlineStr">
+      <c r="AE81" s="219" t="n"/>
+      <c r="AF81" s="218" t="n"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="284" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="284" t="inlineStr">
         <is>
           <t>GPO475-수리</t>
         </is>
       </c>
-      <c r="C75" s="285" t="inlineStr">
+      <c r="C82" s="285" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D75" s="284" t="inlineStr">
+      <c r="D82" s="284" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E75" s="285" t="inlineStr">
+      <c r="E82" s="285" t="inlineStr">
         <is>
           <t>수리</t>
         </is>
       </c>
-      <c r="F75" s="286" t="n">
+      <c r="F82" s="286" t="n">
         <v>46126</v>
       </c>
-      <c r="G75" s="287" t="n">
+      <c r="G82" s="287" t="n">
         <v>46190</v>
       </c>
-      <c r="H75" s="288" t="n">
+      <c r="H82" s="288" t="n">
         <v>1500</v>
       </c>
-      <c r="I75" s="289" t="n">
+      <c r="I82" s="289" t="n">
         <v>1516.8</v>
       </c>
-      <c r="J75" s="290" t="n">
+      <c r="J82" s="290" t="n">
         <v>2275200</v>
       </c>
-      <c r="K75" s="290" t="n">
+      <c r="K82" s="290" t="n">
         <v>2275200</v>
       </c>
-      <c r="L75" s="290" t="n">
+      <c r="L82" s="290" t="n">
         <v>5515</v>
       </c>
-      <c r="M75" s="290" t="n">
+      <c r="M82" s="290" t="n">
         <v>5882</v>
       </c>
-      <c r="N75" s="284" t="inlineStr">
+      <c r="N82" s="284" t="inlineStr">
         <is>
           <t>SR-1000 IMB Inspection+Repair (SN A78267)</t>
         </is>
       </c>
-      <c r="O75" s="287" t="n"/>
-      <c r="P75" s="284" t="n"/>
-      <c r="Q75" s="288">
-        <f>IF(P75="","",IFERROR(VLOOKUP(O75,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R75" s="290">
-        <f>IF(P75="","",H75)</f>
-        <v/>
-      </c>
-      <c r="S75" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" s="286" t="n"/>
-      <c r="V75" s="284" t="n"/>
-      <c r="W75" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" s="285" t="inlineStr">
+      <c r="O82" s="287" t="n"/>
+      <c r="P82" s="284" t="n"/>
+      <c r="Q82" s="288">
+        <f>IF(P82="","",IFERROR(VLOOKUP(O82,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R82" s="290">
+        <f>IF(P82="","",H82)</f>
+        <v/>
+      </c>
+      <c r="S82" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="286" t="n"/>
+      <c r="V82" s="284" t="n"/>
+      <c r="W82" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y75" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z75" s="290">
-        <f>S75+W75</f>
-        <v/>
-      </c>
-      <c r="AA75" s="290">
-        <f>K75+L75+M75+IFERROR(VLOOKUP(B75,RemitTable2,9,FALSE),0)+Y75+Z75</f>
-        <v/>
-      </c>
-      <c r="AB75" s="291" t="n">
+      <c r="Y82" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="290">
+        <f>S82+W82</f>
+        <v/>
+      </c>
+      <c r="AA82" s="290">
+        <f>K82+L82+M82+IFERROR(VLOOKUP(B82,RemitTable2,9,FALSE),0)+Y82+Z82</f>
+        <v/>
+      </c>
+      <c r="AB82" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="AC75" s="290">
-        <f>ROUND(AA75/AB75,0)</f>
-        <v/>
-      </c>
-      <c r="AD75" s="284" t="n"/>
-      <c r="AE75" s="287" t="n"/>
-      <c r="AF75" s="286" t="n"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="147" t="inlineStr">
+      <c r="AC82" s="290">
+        <f>ROUND(AA82/AB82,0)</f>
+        <v/>
+      </c>
+      <c r="AD82" s="284" t="n"/>
+      <c r="AE82" s="287" t="n"/>
+      <c r="AF82" s="286" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="147" t="inlineStr">
         <is>
           <t>장비/부품 합계</t>
         </is>
       </c>
-      <c r="B76" s="148" t="n"/>
-      <c r="C76" s="148" t="n"/>
-      <c r="D76" s="148" t="n"/>
-      <c r="E76" s="148" t="n"/>
-      <c r="F76" s="148" t="n"/>
-      <c r="G76" s="149" t="n"/>
-      <c r="H76" s="142">
-        <f>SUBTOTAL(9,H5:H44)</f>
-        <v/>
-      </c>
-      <c r="I76" s="141" t="n"/>
-      <c r="J76" s="142">
-        <f>SUBTOTAL(9,J5:J44)</f>
-        <v/>
-      </c>
-      <c r="K76" s="142">
-        <f>SUBTOTAL(9,K5:K44)</f>
-        <v/>
-      </c>
-      <c r="L76" s="142">
-        <f>SUBTOTAL(9,L5:L44)</f>
-        <v/>
-      </c>
-      <c r="M76" s="142">
-        <f>SUBTOTAL(9,M5:M44)</f>
-        <v/>
-      </c>
-      <c r="N76" s="141" t="n"/>
-      <c r="O76" s="141" t="n"/>
-      <c r="P76" s="141" t="n"/>
-      <c r="Q76" s="142" t="n"/>
-      <c r="R76" s="140" t="n"/>
-      <c r="S76" s="142">
-        <f>SUBTOTAL(9,S5:S44)</f>
-        <v/>
-      </c>
-      <c r="T76" s="142">
-        <f>SUBTOTAL(9,T5:T44)</f>
-        <v/>
-      </c>
-      <c r="U76" s="147" t="n"/>
-      <c r="V76" s="141" t="n"/>
-      <c r="W76" s="142">
-        <f>SUBTOTAL(9,W5:W44)</f>
-        <v/>
-      </c>
-      <c r="X76" s="147" t="n"/>
-      <c r="Y76" s="142">
-        <f>SUBTOTAL(9,Y5:Y44)</f>
-        <v/>
-      </c>
-      <c r="Z76" s="142">
-        <f>SUBTOTAL(9,Z5:Z44)</f>
-        <v/>
-      </c>
-      <c r="AA76" s="142">
-        <f>SUBTOTAL(9,AA5:AA44)</f>
-        <v/>
-      </c>
-      <c r="AB76" s="147" t="n"/>
-      <c r="AC76" s="141" t="n"/>
-      <c r="AD76" s="141" t="n"/>
-      <c r="AE76" s="141" t="n"/>
-      <c r="AF76" s="141" t="n"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="147" t="inlineStr">
+      <c r="B83" s="148" t="n"/>
+      <c r="C83" s="148" t="n"/>
+      <c r="D83" s="148" t="n"/>
+      <c r="E83" s="148" t="n"/>
+      <c r="F83" s="148" t="n"/>
+      <c r="G83" s="149" t="n"/>
+      <c r="H83" s="142">
+        <f>SUBTOTAL(9,H5:H50)</f>
+        <v/>
+      </c>
+      <c r="I83" s="141" t="n"/>
+      <c r="J83" s="142">
+        <f>SUBTOTAL(9,J5:J50)</f>
+        <v/>
+      </c>
+      <c r="K83" s="142">
+        <f>SUBTOTAL(9,K5:K50)</f>
+        <v/>
+      </c>
+      <c r="L83" s="142">
+        <f>SUBTOTAL(9,L5:L50)</f>
+        <v/>
+      </c>
+      <c r="M83" s="142">
+        <f>SUBTOTAL(9,M5:M50)</f>
+        <v/>
+      </c>
+      <c r="N83" s="141" t="n"/>
+      <c r="O83" s="141" t="n"/>
+      <c r="P83" s="141" t="n"/>
+      <c r="Q83" s="142" t="n"/>
+      <c r="R83" s="140" t="n"/>
+      <c r="S83" s="142">
+        <f>SUBTOTAL(9,S5:S50)</f>
+        <v/>
+      </c>
+      <c r="T83" s="142">
+        <f>SUBTOTAL(9,T5:T50)</f>
+        <v/>
+      </c>
+      <c r="U83" s="147" t="n"/>
+      <c r="V83" s="141" t="n"/>
+      <c r="W83" s="142">
+        <f>SUBTOTAL(9,W5:W50)</f>
+        <v/>
+      </c>
+      <c r="X83" s="147" t="n"/>
+      <c r="Y83" s="142">
+        <f>SUBTOTAL(9,Y5:Y50)</f>
+        <v/>
+      </c>
+      <c r="Z83" s="142">
+        <f>SUBTOTAL(9,Z5:Z50)</f>
+        <v/>
+      </c>
+      <c r="AA83" s="142">
+        <f>SUBTOTAL(9,AA5:AA50)</f>
+        <v/>
+      </c>
+      <c r="AB83" s="147" t="n"/>
+      <c r="AC83" s="141" t="n"/>
+      <c r="AD83" s="141" t="n"/>
+      <c r="AE83" s="141" t="n"/>
+      <c r="AF83" s="141" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="147" t="inlineStr">
         <is>
           <t>라이센스/워런티 합계</t>
         </is>
       </c>
-      <c r="B77" s="148" t="n"/>
-      <c r="C77" s="148" t="n"/>
-      <c r="D77" s="148" t="n"/>
-      <c r="E77" s="148" t="n"/>
-      <c r="F77" s="148" t="n"/>
-      <c r="G77" s="149" t="n"/>
-      <c r="H77" s="142">
-        <f>SUBTOTAL(9,H45:H71)</f>
-        <v/>
-      </c>
-      <c r="I77" s="141" t="n"/>
-      <c r="J77" s="142">
-        <f>SUBTOTAL(9,J45:J71)</f>
-        <v/>
-      </c>
-      <c r="K77" s="142">
-        <f>SUBTOTAL(9,K45:K71)</f>
-        <v/>
-      </c>
-      <c r="L77" s="142">
-        <f>SUBTOTAL(9,L45:L71)</f>
-        <v/>
-      </c>
-      <c r="M77" s="142">
-        <f>SUBTOTAL(9,M45:M71)</f>
-        <v/>
-      </c>
-      <c r="N77" s="141" t="n"/>
-      <c r="O77" s="141" t="n"/>
-      <c r="P77" s="141" t="n"/>
-      <c r="Q77" s="142" t="n"/>
-      <c r="R77" s="140" t="n"/>
-      <c r="S77" s="142">
-        <f>SUBTOTAL(9,S45:S71)</f>
-        <v/>
-      </c>
-      <c r="T77" s="142">
-        <f>SUBTOTAL(9,T45:T71)</f>
-        <v/>
-      </c>
-      <c r="U77" s="147" t="n"/>
-      <c r="V77" s="141" t="n"/>
-      <c r="W77" s="142">
-        <f>SUBTOTAL(9,W45:W71)</f>
-        <v/>
-      </c>
-      <c r="X77" s="147" t="n"/>
-      <c r="Y77" s="142">
-        <f>SUBTOTAL(9,Y45:Y71)</f>
-        <v/>
-      </c>
-      <c r="Z77" s="142">
-        <f>SUBTOTAL(9,Z45:Z71)</f>
-        <v/>
-      </c>
-      <c r="AA77" s="142">
-        <f>SUBTOTAL(9,AA45:AA71)</f>
-        <v/>
-      </c>
-      <c r="AB77" s="147" t="n"/>
-      <c r="AC77" s="141" t="n"/>
-      <c r="AD77" s="141" t="n"/>
-      <c r="AE77" s="141" t="n"/>
-      <c r="AF77" s="141" t="n"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="147" t="inlineStr">
+      <c r="B84" s="148" t="n"/>
+      <c r="C84" s="148" t="n"/>
+      <c r="D84" s="148" t="n"/>
+      <c r="E84" s="148" t="n"/>
+      <c r="F84" s="148" t="n"/>
+      <c r="G84" s="149" t="n"/>
+      <c r="H84" s="142">
+        <f>SUBTOTAL(9,H51:H78)</f>
+        <v/>
+      </c>
+      <c r="I84" s="141" t="n"/>
+      <c r="J84" s="142">
+        <f>SUBTOTAL(9,J51:J78)</f>
+        <v/>
+      </c>
+      <c r="K84" s="142">
+        <f>SUBTOTAL(9,K51:K78)</f>
+        <v/>
+      </c>
+      <c r="L84" s="142">
+        <f>SUBTOTAL(9,L51:L78)</f>
+        <v/>
+      </c>
+      <c r="M84" s="142">
+        <f>SUBTOTAL(9,M51:M78)</f>
+        <v/>
+      </c>
+      <c r="N84" s="141" t="n"/>
+      <c r="O84" s="141" t="n"/>
+      <c r="P84" s="141" t="n"/>
+      <c r="Q84" s="142" t="n"/>
+      <c r="R84" s="140" t="n"/>
+      <c r="S84" s="142">
+        <f>SUBTOTAL(9,S51:S78)</f>
+        <v/>
+      </c>
+      <c r="T84" s="142">
+        <f>SUBTOTAL(9,T51:T78)</f>
+        <v/>
+      </c>
+      <c r="U84" s="147" t="n"/>
+      <c r="V84" s="141" t="n"/>
+      <c r="W84" s="142">
+        <f>SUBTOTAL(9,W51:W78)</f>
+        <v/>
+      </c>
+      <c r="X84" s="147" t="n"/>
+      <c r="Y84" s="142">
+        <f>SUBTOTAL(9,Y51:Y78)</f>
+        <v/>
+      </c>
+      <c r="Z84" s="142">
+        <f>SUBTOTAL(9,Z51:Z78)</f>
+        <v/>
+      </c>
+      <c r="AA84" s="142">
+        <f>SUBTOTAL(9,AA51:AA78)</f>
+        <v/>
+      </c>
+      <c r="AB84" s="147" t="n"/>
+      <c r="AC84" s="141" t="n"/>
+      <c r="AD84" s="141" t="n"/>
+      <c r="AE84" s="141" t="n"/>
+      <c r="AF84" s="141" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="147" t="inlineStr">
         <is>
           <t>기타 합계</t>
         </is>
       </c>
-      <c r="B78" s="148" t="n"/>
-      <c r="C78" s="148" t="n"/>
-      <c r="D78" s="148" t="n"/>
-      <c r="E78" s="148" t="n"/>
-      <c r="F78" s="148" t="n"/>
-      <c r="G78" s="149" t="n"/>
-      <c r="H78" s="142">
-        <f>SUBTOTAL(9,H72:H75)</f>
-        <v/>
-      </c>
-      <c r="I78" s="141" t="n"/>
-      <c r="J78" s="142">
-        <f>SUBTOTAL(9,J72:J75)</f>
-        <v/>
-      </c>
-      <c r="K78" s="142">
-        <f>SUBTOTAL(9,K72:K75)</f>
-        <v/>
-      </c>
-      <c r="L78" s="142">
-        <f>SUBTOTAL(9,L72:L75)</f>
-        <v/>
-      </c>
-      <c r="M78" s="142">
-        <f>SUBTOTAL(9,M72:M75)</f>
-        <v/>
-      </c>
-      <c r="N78" s="141" t="n"/>
-      <c r="O78" s="141" t="n"/>
-      <c r="P78" s="141" t="n"/>
-      <c r="Q78" s="142" t="n"/>
-      <c r="R78" s="140" t="n"/>
-      <c r="S78" s="142">
-        <f>SUBTOTAL(9,S72:S75)</f>
-        <v/>
-      </c>
-      <c r="T78" s="142">
-        <f>SUBTOTAL(9,T72:T75)</f>
-        <v/>
-      </c>
-      <c r="U78" s="147" t="n"/>
-      <c r="V78" s="141" t="n"/>
-      <c r="W78" s="142">
-        <f>SUBTOTAL(9,W72:W75)</f>
-        <v/>
-      </c>
-      <c r="X78" s="147" t="n"/>
-      <c r="Y78" s="142">
-        <f>SUBTOTAL(9,Y72:Y75)</f>
-        <v/>
-      </c>
-      <c r="Z78" s="142">
-        <f>SUBTOTAL(9,Z72:Z75)</f>
-        <v/>
-      </c>
-      <c r="AA78" s="142">
-        <f>SUBTOTAL(9,AA72:AA75)</f>
-        <v/>
-      </c>
-      <c r="AB78" s="147" t="n"/>
-      <c r="AC78" s="141" t="n"/>
-      <c r="AD78" s="141" t="n"/>
-      <c r="AE78" s="141" t="n"/>
-      <c r="AF78" s="141" t="n"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="154" t="inlineStr">
+      <c r="B85" s="148" t="n"/>
+      <c r="C85" s="148" t="n"/>
+      <c r="D85" s="148" t="n"/>
+      <c r="E85" s="148" t="n"/>
+      <c r="F85" s="148" t="n"/>
+      <c r="G85" s="149" t="n"/>
+      <c r="H85" s="142">
+        <f>SUBTOTAL(9,H79:H82)</f>
+        <v/>
+      </c>
+      <c r="I85" s="141" t="n"/>
+      <c r="J85" s="142">
+        <f>SUBTOTAL(9,J79:J82)</f>
+        <v/>
+      </c>
+      <c r="K85" s="142">
+        <f>SUBTOTAL(9,K79:K82)</f>
+        <v/>
+      </c>
+      <c r="L85" s="142">
+        <f>SUBTOTAL(9,L79:L82)</f>
+        <v/>
+      </c>
+      <c r="M85" s="142">
+        <f>SUBTOTAL(9,M79:M82)</f>
+        <v/>
+      </c>
+      <c r="N85" s="141" t="n"/>
+      <c r="O85" s="141" t="n"/>
+      <c r="P85" s="141" t="n"/>
+      <c r="Q85" s="142" t="n"/>
+      <c r="R85" s="140" t="n"/>
+      <c r="S85" s="142">
+        <f>SUBTOTAL(9,S79:S82)</f>
+        <v/>
+      </c>
+      <c r="T85" s="142">
+        <f>SUBTOTAL(9,T79:T82)</f>
+        <v/>
+      </c>
+      <c r="U85" s="147" t="n"/>
+      <c r="V85" s="141" t="n"/>
+      <c r="W85" s="142">
+        <f>SUBTOTAL(9,W79:W82)</f>
+        <v/>
+      </c>
+      <c r="X85" s="147" t="n"/>
+      <c r="Y85" s="142">
+        <f>SUBTOTAL(9,Y79:Y82)</f>
+        <v/>
+      </c>
+      <c r="Z85" s="142">
+        <f>SUBTOTAL(9,Z79:Z82)</f>
+        <v/>
+      </c>
+      <c r="AA85" s="142">
+        <f>SUBTOTAL(9,AA79:AA82)</f>
+        <v/>
+      </c>
+      <c r="AB85" s="147" t="n"/>
+      <c r="AC85" s="141" t="n"/>
+      <c r="AD85" s="141" t="n"/>
+      <c r="AE85" s="141" t="n"/>
+      <c r="AF85" s="141" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="154" t="inlineStr">
         <is>
           <t>총 합계</t>
         </is>
       </c>
-      <c r="B79" s="148" t="n"/>
-      <c r="C79" s="148" t="n"/>
-      <c r="D79" s="148" t="n"/>
-      <c r="E79" s="148" t="n"/>
-      <c r="F79" s="148" t="n"/>
-      <c r="G79" s="149" t="n"/>
-      <c r="H79" s="146">
-        <f>SUBTOTAL(9,H5:H75)</f>
-        <v/>
-      </c>
-      <c r="I79" s="145" t="n"/>
-      <c r="J79" s="146">
-        <f>SUBTOTAL(9,J5:J75)</f>
-        <v/>
-      </c>
-      <c r="K79" s="146">
-        <f>SUBTOTAL(9,K5:K75)</f>
-        <v/>
-      </c>
-      <c r="L79" s="146">
-        <f>SUBTOTAL(9,L5:L75)</f>
-        <v/>
-      </c>
-      <c r="M79" s="146">
-        <f>SUBTOTAL(9,M5:M75)</f>
-        <v/>
-      </c>
-      <c r="N79" s="145" t="n"/>
-      <c r="O79" s="145" t="n"/>
-      <c r="P79" s="145" t="n"/>
-      <c r="Q79" s="146" t="n"/>
-      <c r="R79" s="144" t="n"/>
-      <c r="S79" s="146">
-        <f>SUBTOTAL(9,S5:S75)</f>
-        <v/>
-      </c>
-      <c r="T79" s="146">
-        <f>SUBTOTAL(9,T5:T75)</f>
-        <v/>
-      </c>
-      <c r="U79" s="154" t="n"/>
-      <c r="V79" s="145" t="n"/>
-      <c r="W79" s="146">
-        <f>SUBTOTAL(9,W5:W75)</f>
-        <v/>
-      </c>
-      <c r="X79" s="154" t="n"/>
-      <c r="Y79" s="146">
-        <f>SUBTOTAL(9,Y5:Y75)</f>
-        <v/>
-      </c>
-      <c r="Z79" s="146">
-        <f>SUBTOTAL(9,Z5:Z75)</f>
-        <v/>
-      </c>
-      <c r="AA79" s="146">
-        <f>SUBTOTAL(9,AA5:AA75)</f>
-        <v/>
-      </c>
-      <c r="AB79" s="154" t="n"/>
-      <c r="AC79" s="145" t="n"/>
-      <c r="AD79" s="145" t="n"/>
-      <c r="AE79" s="145" t="n"/>
-      <c r="AF79" s="145" t="n"/>
-    </row>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93">
-      <c r="M93" s="40" t="n"/>
+      <c r="B86" s="148" t="n"/>
+      <c r="C86" s="148" t="n"/>
+      <c r="D86" s="148" t="n"/>
+      <c r="E86" s="148" t="n"/>
+      <c r="F86" s="148" t="n"/>
+      <c r="G86" s="149" t="n"/>
+      <c r="H86" s="146">
+        <f>SUBTOTAL(9,H5:H82)</f>
+        <v/>
+      </c>
+      <c r="I86" s="145" t="n"/>
+      <c r="J86" s="146">
+        <f>SUBTOTAL(9,J5:J82)</f>
+        <v/>
+      </c>
+      <c r="K86" s="146">
+        <f>SUBTOTAL(9,K5:K82)</f>
+        <v/>
+      </c>
+      <c r="L86" s="146">
+        <f>SUBTOTAL(9,L5:L82)</f>
+        <v/>
+      </c>
+      <c r="M86" s="146">
+        <f>SUBTOTAL(9,M5:M82)</f>
+        <v/>
+      </c>
+      <c r="N86" s="145" t="n"/>
+      <c r="O86" s="145" t="n"/>
+      <c r="P86" s="145" t="n"/>
+      <c r="Q86" s="146" t="n"/>
+      <c r="R86" s="144" t="n"/>
+      <c r="S86" s="146">
+        <f>SUBTOTAL(9,S5:S82)</f>
+        <v/>
+      </c>
+      <c r="T86" s="146">
+        <f>SUBTOTAL(9,T5:T82)</f>
+        <v/>
+      </c>
+      <c r="U86" s="154" t="n"/>
+      <c r="V86" s="145" t="n"/>
+      <c r="W86" s="146">
+        <f>SUBTOTAL(9,W5:W82)</f>
+        <v/>
+      </c>
+      <c r="X86" s="154" t="n"/>
+      <c r="Y86" s="146">
+        <f>SUBTOTAL(9,Y5:Y82)</f>
+        <v/>
+      </c>
+      <c r="Z86" s="146">
+        <f>SUBTOTAL(9,Z5:Z82)</f>
+        <v/>
+      </c>
+      <c r="AA86" s="146">
+        <f>SUBTOTAL(9,AA5:AA82)</f>
+        <v/>
+      </c>
+      <c r="AB86" s="154" t="n"/>
+      <c r="AC86" s="145" t="n"/>
+      <c r="AD86" s="145" t="n"/>
+      <c r="AE86" s="145" t="n"/>
+      <c r="AF86" s="145" t="n"/>
+    </row>
+    <row r="100">
+      <c r="M100" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A84:G84"/>
+    <mergeCell ref="A85:G85"/>
     <mergeCell ref="G3:N3"/>
-    <mergeCell ref="A79:G79"/>
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A83:G83"/>
     <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="A86:G86"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A76:G76"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="O3:W3"/>
     <mergeCell ref="A2:AF2"/>
@@ -12247,7 +13218,7 @@
       </c>
       <c r="F26" s="224" t="inlineStr">
         <is>
-          <t>EW CP2215/CP2309-RGB 24대 (롯데 영천 외 8개소)</t>
+          <t>EW CP2215/CP2309-RGB 25대 (롯데 영천 외 8개소)</t>
         </is>
       </c>
       <c r="G26" s="227" t="n">
@@ -12419,46 +13390,55 @@
       <c r="L29" s="228" t="n"/>
       <c r="M29" s="160" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
+    <row r="30">
+      <c r="A30" s="224" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="224" t="inlineStr">
+        <is>
+          <t>GPO487</t>
+        </is>
+      </c>
+      <c r="C30" s="225" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D30" s="225" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="E30" s="226" t="n">
+        <v>5309</v>
+      </c>
+      <c r="F30" s="224" t="inlineStr">
+        <is>
+          <t>SX-3000 EW 133대 (롯데, gross 33,309 차감 보상판매 Credit 28,000)</t>
+        </is>
+      </c>
+      <c r="G30" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="227" t="n">
+        <v>46204</v>
+      </c>
+      <c r="J30" s="227" t="n">
+        <v>46387</v>
+      </c>
+      <c r="K30" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+    </row>
     <row r="70">
       <c r="M70" s="40" t="n"/>
     </row>
@@ -13632,7 +14612,7 @@
         </is>
       </c>
       <c r="H27" s="232" t="n">
-        <v>5002612</v>
+        <v>5233502</v>
       </c>
       <c r="I27" s="229" t="inlineStr">
         <is>
@@ -14169,37 +15149,342 @@
       <c r="L39" s="160" t="n"/>
       <c r="M39" s="160" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
+    <row r="40">
+      <c r="A40" s="241" t="inlineStr">
+        <is>
+          <t>23176-26-472403M</t>
+        </is>
+      </c>
+      <c r="B40" s="241" t="inlineStr">
+        <is>
+          <t>GPO483</t>
+        </is>
+      </c>
+      <c r="C40" s="242" t="n">
+        <v>14730</v>
+      </c>
+      <c r="D40" s="243">
+        <f>C40/C40</f>
+        <v/>
+      </c>
+      <c r="E40" s="241" t="inlineStr">
+        <is>
+          <t>스타합동관세사무소</t>
+        </is>
+      </c>
+      <c r="F40" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="241" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="H40" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J40" s="241" t="inlineStr">
+        <is>
+          <t>통관 결제금액 USD 15,870 (HDMI 모듈 3EA USD 1,140 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="241" t="inlineStr">
+        <is>
+          <t>23176-26-606930M</t>
+        </is>
+      </c>
+      <c r="B41" s="241" t="inlineStr">
+        <is>
+          <t>CPO703</t>
+        </is>
+      </c>
+      <c r="C41" s="242" t="n">
+        <v>5445</v>
+      </c>
+      <c r="D41" s="243">
+        <f>C41/(C41+C42)</f>
+        <v/>
+      </c>
+      <c r="E41" s="241" t="inlineStr">
+        <is>
+          <t>스타합동관세사무소</t>
+        </is>
+      </c>
+      <c r="F41" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="241" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="H41" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="241" t="inlineStr">
+        <is>
+          <t>합배송</t>
+        </is>
+      </c>
+      <c r="J41" s="241" t="inlineStr">
+        <is>
+          <t>2건 합산</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="241" t="n"/>
+      <c r="B42" s="241" t="inlineStr">
+        <is>
+          <t>CPO701</t>
+        </is>
+      </c>
+      <c r="C42" s="242" t="n">
+        <v>54</v>
+      </c>
+      <c r="D42" s="243">
+        <f>C42/(C41+C42)</f>
+        <v/>
+      </c>
+      <c r="E42" s="241" t="inlineStr">
+        <is>
+          <t>스타합동관세사무소</t>
+        </is>
+      </c>
+      <c r="F42" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="241" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="H42" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="241" t="inlineStr">
+        <is>
+          <t>합배송</t>
+        </is>
+      </c>
+      <c r="J42" s="241" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="241" t="inlineStr">
+        <is>
+          <t>23176-26-605075M</t>
+        </is>
+      </c>
+      <c r="B43" s="241" t="inlineStr">
+        <is>
+          <t>GPO488</t>
+        </is>
+      </c>
+      <c r="C43" s="242" t="n">
+        <v>180</v>
+      </c>
+      <c r="D43" s="243">
+        <f>C43/C43</f>
+        <v/>
+      </c>
+      <c r="E43" s="241" t="inlineStr">
+        <is>
+          <t>스타합동관세사무소</t>
+        </is>
+      </c>
+      <c r="F43" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="241" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="H43" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J43" s="241" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="241" t="inlineStr">
+        <is>
+          <t>23176-26-618473M</t>
+        </is>
+      </c>
+      <c r="B44" s="241" t="inlineStr">
+        <is>
+          <t>GPO493</t>
+        </is>
+      </c>
+      <c r="C44" s="242" t="n">
+        <v>4470</v>
+      </c>
+      <c r="D44" s="243">
+        <f>C44/C44</f>
+        <v/>
+      </c>
+      <c r="E44" s="241" t="inlineStr">
+        <is>
+          <t>스타합동관세사무소</t>
+        </is>
+      </c>
+      <c r="F44" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="241" t="inlineStr">
+        <is>
+          <t>Fedex</t>
+        </is>
+      </c>
+      <c r="H44" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J44" s="241" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="241" t="inlineStr">
+        <is>
+          <t>14008-26-101364M</t>
+        </is>
+      </c>
+      <c r="B45" s="241" t="inlineStr">
+        <is>
+          <t>GPO482</t>
+        </is>
+      </c>
+      <c r="C45" s="242" t="n">
+        <v>329510</v>
+      </c>
+      <c r="D45" s="243">
+        <f>C45/(C45+C46)</f>
+        <v/>
+      </c>
+      <c r="E45" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F45" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="241" t="inlineStr">
+        <is>
+          <t>훼밀리익스프레스</t>
+        </is>
+      </c>
+      <c r="H45" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="241" t="inlineStr">
+        <is>
+          <t>합배송</t>
+        </is>
+      </c>
+      <c r="J45" s="241" t="inlineStr">
+        <is>
+          <t>2건 합산</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="241" t="n"/>
+      <c r="B46" s="241" t="inlineStr">
+        <is>
+          <t>GPO485</t>
+        </is>
+      </c>
+      <c r="C46" s="242" t="n">
+        <v>5600</v>
+      </c>
+      <c r="D46" s="243">
+        <f>C46/(C45+C46)</f>
+        <v/>
+      </c>
+      <c r="E46" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F46" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="241" t="inlineStr">
+        <is>
+          <t>훼밀리익스프레스</t>
+        </is>
+      </c>
+      <c r="H46" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="241" t="inlineStr">
+        <is>
+          <t>합배송</t>
+        </is>
+      </c>
+      <c r="J46" s="241" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="241" t="inlineStr">
+        <is>
+          <t>14008-26-101205M</t>
+        </is>
+      </c>
+      <c r="B47" s="241" t="inlineStr">
+        <is>
+          <t>EPO18</t>
+        </is>
+      </c>
+      <c r="C47" s="242" t="n">
+        <v>4388.4</v>
+      </c>
+      <c r="D47" s="243">
+        <f>C47/C47</f>
+        <v/>
+      </c>
+      <c r="E47" s="241" t="inlineStr">
+        <is>
+          <t>조운관세사무소</t>
+        </is>
+      </c>
+      <c r="F47" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="241" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="H47" s="244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="241" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="J47" s="241" t="inlineStr">
+        <is>
+          <t>EUR 결제 건</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
       <c r="M71" s="40" t="n"/>
     </row>
@@ -21511,7 +22796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -21554,7 +22839,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="205" t="inlineStr">
         <is>
-          <t>업데이트: 2026-07-02 (관세청 고시환율)</t>
+          <t>업데이트: 2026-08-04 (관세청 고시환율)</t>
         </is>
       </c>
       <c r="B4" s="148" t="n"/>
@@ -22206,6 +23491,86 @@
       </c>
       <c r="D45" s="211" t="n">
         <v>1538.3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="282" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B46" s="282" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C46" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D46" s="211" t="n">
+        <v>1548.52</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="282" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B47" s="282" t="n">
+        <v>46221</v>
+      </c>
+      <c r="C47" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D47" s="211" t="n">
+        <v>1522.44</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="282" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B48" s="282" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C48" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D48" s="211" t="n">
+        <v>1498.25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="282" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B49" s="282" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C49" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D49" s="211" t="n">
+        <v>1478.44</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="282" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B50" s="282" t="n">
+        <v>46242</v>
+      </c>
+      <c r="C50" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D50" s="211" t="n">
+        <v>1457.82</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$40</definedName>
-    <definedName name="RemitTable2">'외화송금내역'!$A$43:$L$97</definedName>
-    <definedName name="FxRateTable">'환율'!$A$7:$D$50</definedName>
+    <definedName name="RemitTable1">'외화송금내역'!$A$3:$L$44</definedName>
+    <definedName name="RemitTable2">'외화송금내역'!$A$47:$L$107</definedName>
+    <definedName name="FxRateTable">'환율'!$A$7:$D$51</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1457,6 +1457,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>RNR 재무팀</author>
+    <author>RNR</author>
   </authors>
   <commentList>
     <comment ref="S5" authorId="0" shapeId="0">
@@ -1660,22 +1661,37 @@
         <t>GDC-INV-2606-025 : gross USD 33,309 차감 구형서버 보상판매 Credit GDC-CN-2604-001 USD 28,000 = 실지급 USD 5,309</t>
       </text>
     </comment>
-    <comment ref="S80" authorId="0" shapeId="0">
+    <comment ref="H79" authorId="1" shapeId="0">
+      <text>
+        <t>CPO700+CPO702 합송금 USD 33,829 (2026-08-07) 중 CPO702 인보이스 32,715 차감 잔여분 = USD 1,114.
+Christie 인보이스 미수취. Christie AR 메일(2026-07-31, Eric Shim): CPO700/CPO702 모두 Extended Warranty 건.
+인보이스 수취 시 품명/계약기간 보완 필요</t>
+      </text>
+    </comment>
+    <comment ref="S82" authorId="0" shapeId="0">
       <text>
         <t>관세율 0.00% - 세율구분 C(가가, WTO/ITA 양허)
 수리반환 재수입 건, 부가세만 과세
 (신고필증 2235626351613M)</t>
       </text>
     </comment>
-    <comment ref="Y80" authorId="0" shapeId="0">
+    <comment ref="Y82" authorId="0" shapeId="0">
       <text>
         <t>DHL 2026-05월 인보이스 (AWB 5094871784 = 수입신고필증 B/L 일치)
 GDC RMA 수리반환 건, 지출결의 2026-1344, 6/9 집행</t>
       </text>
     </comment>
-    <comment ref="Y81" authorId="0" shapeId="0">
+    <comment ref="Y83" authorId="0" shapeId="0">
       <text>
         <t>진로직스 운임 정정 추가정산금 230,890원 반영 (정정 전 4,827,602 → 정정 후 5,058,492, HFIKUO26401C, 입항지 부산 변경분) 지출결의 2026-1536</t>
+      </text>
+    </comment>
+    <comment ref="H84" authorId="1" shapeId="0">
+      <text>
+        <t>Figueras PI 44133 (2026-05-05) 총 EUR 22,080 = RIVA 4031 리클라이너 16EA (Monoplex DH Bangbae).
+지급: 20% EUR 4,416 (2026-05-12) + 60% EUR 13,248 (2026-07-14) = EUR 17,664 기지급.
+잔금 20% EUR 4,416 미지급 (완공 또는 납품 후 30일 조건). J/K열은 기지급분 원화 합계.
+H열은 EUR 금액 (USD 아님)</t>
       </text>
     </comment>
   </commentList>
@@ -1891,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF100"/>
+  <dimension ref="A1:AF102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" style="160" min="1" max="1"/>
@@ -1957,7 +1973,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="170" t="inlineStr">
         <is>
-          <t>회계처리용 통합 데이터  |  기준일: 2026-08-04  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
+          <t>회계처리용 통합 데이터  |  기준일: 2026-08-14  |  노란색=미확인  |  보라색=라이센스/워런티  |  날짜→해당항목 좌측 배치</t>
         </is>
       </c>
       <c r="B2" s="148" t="n"/>
@@ -7322,32 +7338,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G47" s="181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" s="181" t="n">
+        <v>46238</v>
       </c>
       <c r="H47" s="126" t="n">
         <v>180</v>
       </c>
-      <c r="I47" s="310">
-        <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I47" s="310" t="n">
+        <v>1432.9</v>
       </c>
       <c r="J47" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="128">
-        <f>IFERROR(ROUND(H47*I47,0),0)</f>
-        <v/>
-      </c>
-      <c r="L47" s="128">
-        <f>IFERROR(VLOOKUP(B47,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M47" s="128">
-        <f>IFERROR(VLOOKUP(B47,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>257922</v>
+      </c>
+      <c r="K47" s="128" t="n">
+        <v>257922</v>
+      </c>
+      <c r="L47" s="128" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M47" s="128" t="n">
+        <v>8000</v>
       </c>
       <c r="N47" s="124" t="inlineStr">
         <is>
@@ -7453,32 +7463,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G48" s="181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G48" s="181" t="n">
+        <v>46245</v>
       </c>
       <c r="H48" s="126" t="n">
         <v>4470</v>
       </c>
-      <c r="I48" s="310">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE),0)</f>
-        <v/>
+      <c r="I48" s="310" t="n">
+        <v>1419.3</v>
       </c>
       <c r="J48" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="128">
-        <f>IFERROR(ROUND(H48*I48,0),0)</f>
-        <v/>
-      </c>
-      <c r="L48" s="128">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M48" s="128">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE),0)</f>
-        <v/>
+        <v>6344271</v>
+      </c>
+      <c r="K48" s="128" t="n">
+        <v>6344271</v>
+      </c>
+      <c r="L48" s="128" t="n">
+        <v>7500</v>
+      </c>
+      <c r="M48" s="128" t="n">
+        <v>8000</v>
       </c>
       <c r="N48" s="124" t="inlineStr">
         <is>
@@ -10657,28 +10661,26 @@
       <c r="F74" s="188" t="n">
         <v>46181</v>
       </c>
-      <c r="G74" s="188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G74" s="188" t="n">
+        <v>46241</v>
       </c>
       <c r="H74" s="134" t="n">
         <v>32715</v>
       </c>
       <c r="I74" s="311" t="n">
-        <v>0</v>
+        <v>1429.8</v>
       </c>
       <c r="J74" s="136" t="n">
-        <v>0</v>
+        <v>46775907</v>
       </c>
       <c r="K74" s="136" t="n">
-        <v>0</v>
+        <v>46775907</v>
       </c>
       <c r="L74" s="136" t="n">
-        <v>0</v>
+        <v>12088</v>
       </c>
       <c r="M74" s="136" t="n">
-        <v>0</v>
+        <v>7737</v>
       </c>
       <c r="N74" s="132" t="inlineStr">
         <is>
@@ -11220,131 +11222,115 @@
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="284" t="n">
+      <c r="A79" s="132" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="284" t="inlineStr">
-        <is>
-          <t>CPO688</t>
-        </is>
-      </c>
-      <c r="C79" s="285" t="inlineStr">
+      <c r="B79" s="132" t="inlineStr">
+        <is>
+          <t>CPO700</t>
+        </is>
+      </c>
+      <c r="C79" s="132" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D79" s="284" t="inlineStr">
+      <c r="D79" s="132" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E79" s="285" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-      <c r="F79" s="286" t="n">
-        <v>46037</v>
-      </c>
-      <c r="G79" s="287" t="inlineStr">
+      <c r="E79" s="132" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F79" s="188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H79" s="288" t="n">
-        <v>4180</v>
-      </c>
-      <c r="I79" s="289">
-        <f>IFERROR(VLOOKUP(B79,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J79" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="290">
-        <f>IFERROR(ROUND(H79*I79,0),0)</f>
-        <v/>
-      </c>
-      <c r="L79" s="290">
-        <f>IFERROR(VLOOKUP(B79,RemitTable2,10,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="M79" s="290">
-        <f>IFERROR(VLOOKUP(B79,RemitTable2,11,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="N79" s="284" t="inlineStr">
-        <is>
-          <t>Inspection fee</t>
-        </is>
-      </c>
-      <c r="O79" s="287" t="inlineStr">
+      <c r="G79" s="188" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H79" s="134" t="n">
+        <v>1114</v>
+      </c>
+      <c r="I79" s="311" t="n">
+        <v>1429.8</v>
+      </c>
+      <c r="J79" s="136" t="n">
+        <v>1592797</v>
+      </c>
+      <c r="K79" s="136" t="n">
+        <v>1592797</v>
+      </c>
+      <c r="L79" s="136" t="n">
+        <v>412</v>
+      </c>
+      <c r="M79" s="136" t="n">
+        <v>263</v>
+      </c>
+      <c r="N79" s="132" t="inlineStr">
+        <is>
+          <t>EW Extended Warranty (Christie 인보이스 미수취, 대상/기간 미확인)</t>
+        </is>
+      </c>
+      <c r="O79" s="189" t="n"/>
+      <c r="P79" s="137" t="n"/>
+      <c r="Q79" s="134">
+        <f>IF(P79="","",IFERROR(VLOOKUP(O79,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R79" s="134">
+        <f>IF(P79="","",H79)</f>
+        <v/>
+      </c>
+      <c r="S79" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="188" t="n"/>
+      <c r="V79" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P79" s="284" t="inlineStr">
+      <c r="W79" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q79" s="288">
-        <f>IF(P79="","",IFERROR(VLOOKUP(O79,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R79" s="290">
-        <f>IF(P79="","",H79)</f>
-        <v/>
-      </c>
-      <c r="S79" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" s="286" t="n"/>
-      <c r="V79" s="284" t="inlineStr">
+      <c r="Y79" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="136">
+        <f>S79+W79</f>
+        <v/>
+      </c>
+      <c r="AA79" s="136">
+        <f>K79+L79+M79+IFERROR(VLOOKUP(B79,RemitTable2,9,FALSE),0)+Y79+Z79</f>
+        <v/>
+      </c>
+      <c r="AB79" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC79" s="136">
+        <f>ROUND(AA79/AB79,0)</f>
+        <v/>
+      </c>
+      <c r="AD79" s="132" t="n"/>
+      <c r="AE79" s="188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W79" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" s="285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y79" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" s="290">
-        <f>S79+W79</f>
-        <v/>
-      </c>
-      <c r="AA79" s="290">
-        <f>K79+L79+M79+IFERROR(VLOOKUP(B79,RemitTable2,9,FALSE),0)+Y79+Z79</f>
-        <v/>
-      </c>
-      <c r="AB79" s="291" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC79" s="290">
-        <f>ROUND(AA79/AB79,0)</f>
-        <v/>
-      </c>
-      <c r="AD79" s="284" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="AE79" s="287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF79" s="286" t="inlineStr">
+      <c r="AF79" s="188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11356,32 +11342,34 @@
       </c>
       <c r="B80" s="284" t="inlineStr">
         <is>
-          <t>SX3000수리</t>
+          <t>CPO688</t>
         </is>
       </c>
       <c r="C80" s="285" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D80" s="284" t="inlineStr">
         <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E80" s="285" t="inlineStr">
+        <is>
+          <t>Inspection</t>
+        </is>
+      </c>
+      <c r="F80" s="286" t="n">
+        <v>46037</v>
+      </c>
+      <c r="G80" s="287" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E80" s="285" t="inlineStr">
-        <is>
-          <t>수리반환</t>
-        </is>
-      </c>
-      <c r="F80" s="286" t="n"/>
-      <c r="G80" s="287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H80" s="288" t="n">
-        <v>400</v>
+        <v>4180</v>
       </c>
       <c r="I80" s="289">
         <f>IFERROR(VLOOKUP(B80,RemitTable2,7,FALSE),0)</f>
@@ -11404,15 +11392,17 @@
       </c>
       <c r="N80" s="284" t="inlineStr">
         <is>
-          <t>Display Card (수리반환 5PCS)</t>
-        </is>
-      </c>
-      <c r="O80" s="287" t="n">
-        <v>46125</v>
+          <t>Inspection fee</t>
+        </is>
+      </c>
+      <c r="O80" s="287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P80" s="284" t="inlineStr">
         <is>
-          <t>22356-26-351613M</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q80" s="288">
@@ -11427,12 +11417,12 @@
         <v>0</v>
       </c>
       <c r="T80" s="290" t="n">
-        <v>67750</v>
+        <v>0</v>
       </c>
       <c r="U80" s="286" t="n"/>
       <c r="V80" s="284" t="inlineStr">
         <is>
-          <t>운서합동</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W80" s="290" t="n">
@@ -11440,11 +11430,11 @@
       </c>
       <c r="X80" s="285" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y80" s="290" t="n">
-        <v>216006</v>
+        <v>0</v>
       </c>
       <c r="Z80" s="290">
         <f>S80+W80</f>
@@ -11455,7 +11445,7 @@
         <v/>
       </c>
       <c r="AB80" s="291" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC80" s="290">
         <f>ROUND(AA80/AB80,0)</f>
@@ -11463,375 +11453,482 @@
       </c>
       <c r="AD80" s="284" t="inlineStr">
         <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AE80" s="287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF80" s="286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="284" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="284" t="inlineStr">
+        <is>
+          <t>SX3000수리</t>
+        </is>
+      </c>
+      <c r="C81" s="285" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D81" s="284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E81" s="285" t="inlineStr">
+        <is>
+          <t>수리반환</t>
+        </is>
+      </c>
+      <c r="F81" s="286" t="n"/>
+      <c r="G81" s="287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="288" t="n">
+        <v>400</v>
+      </c>
+      <c r="I81" s="289">
+        <f>IFERROR(VLOOKUP(B81,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J81" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="290">
+        <f>IFERROR(ROUND(H81*I81,0),0)</f>
+        <v/>
+      </c>
+      <c r="L81" s="290">
+        <f>IFERROR(VLOOKUP(B81,RemitTable2,10,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="M81" s="290">
+        <f>IFERROR(VLOOKUP(B81,RemitTable2,11,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="N81" s="284" t="inlineStr">
+        <is>
+          <t>Display Card (수리반환 5PCS)</t>
+        </is>
+      </c>
+      <c r="O81" s="287" t="n">
+        <v>46125</v>
+      </c>
+      <c r="P81" s="284" t="inlineStr">
+        <is>
+          <t>22356-26-351613M</t>
+        </is>
+      </c>
+      <c r="Q81" s="288">
+        <f>IF(P81="","",IFERROR(VLOOKUP(O81,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R81" s="290">
+        <f>IF(P81="","",H81)</f>
+        <v/>
+      </c>
+      <c r="S81" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="290" t="n">
+        <v>67750</v>
+      </c>
+      <c r="U81" s="286" t="n"/>
+      <c r="V81" s="284" t="inlineStr">
+        <is>
+          <t>운서합동</t>
+        </is>
+      </c>
+      <c r="W81" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="285" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="Y81" s="290" t="n">
+        <v>216006</v>
+      </c>
+      <c r="Z81" s="290">
+        <f>S81+W81</f>
+        <v/>
+      </c>
+      <c r="AA81" s="290">
+        <f>K81+L81+M81+IFERROR(VLOOKUP(B81,RemitTable2,9,FALSE),0)+Y81+Z81</f>
+        <v/>
+      </c>
+      <c r="AB81" s="291" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="290">
+        <f>ROUND(AA81/AB81,0)</f>
+        <v/>
+      </c>
+      <c r="AD81" s="284" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE80" s="287" t="n"/>
-      <c r="AF80" s="286" t="n"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="216" t="n">
-        <v>77</v>
-      </c>
-      <c r="B81" s="216" t="inlineStr">
+      <c r="AE81" s="287" t="n"/>
+      <c r="AF81" s="286" t="n"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="216" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="216" t="inlineStr">
         <is>
           <t>FRC-MONOPLEX26</t>
         </is>
       </c>
-      <c r="C81" s="217" t="inlineStr">
+      <c r="C82" s="217" t="inlineStr">
         <is>
           <t>Ferco</t>
         </is>
       </c>
-      <c r="D81" s="216" t="inlineStr">
+      <c r="D82" s="216" t="inlineStr">
         <is>
           <t>50% TT advance + 50% balance</t>
         </is>
       </c>
-      <c r="E81" s="217" t="inlineStr">
+      <c r="E82" s="217" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="F81" s="218" t="n">
+      <c r="F82" s="218" t="n">
         <v>46048</v>
       </c>
-      <c r="G81" s="219" t="n">
+      <c r="G82" s="219" t="n">
         <v>46133</v>
       </c>
-      <c r="H81" s="220" t="n">
+      <c r="H82" s="220" t="n">
         <v>51952</v>
       </c>
-      <c r="I81" s="221">
-        <f>IFERROR(VLOOKUP(B81,RemitTable2,7,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="J81" s="222" t="n">
+      <c r="I82" s="221">
+        <f>IFERROR(VLOOKUP(B82,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J82" s="222" t="n">
         <v>75818749</v>
       </c>
-      <c r="K81" s="222" t="n">
+      <c r="K82" s="222" t="n">
         <v>75818749</v>
       </c>
-      <c r="L81" s="222" t="n">
+      <c r="L82" s="222" t="n">
         <v>25000</v>
       </c>
-      <c r="M81" s="222" t="n">
+      <c r="M82" s="222" t="n">
         <v>16000</v>
       </c>
-      <c r="N81" s="216" t="inlineStr">
+      <c r="N82" s="216" t="inlineStr">
         <is>
           <t>Cinema Seat (Recliner) / 44 EA / Monoplex DH Bangbae</t>
         </is>
       </c>
-      <c r="O81" s="219" t="n">
+      <c r="O82" s="219" t="n">
         <v>46153</v>
       </c>
-      <c r="P81" s="216" t="inlineStr">
+      <c r="P82" s="216" t="inlineStr">
         <is>
           <t>14008-26-101147M</t>
         </is>
       </c>
-      <c r="Q81" s="220">
-        <f>IF(P81="","",IFERROR(VLOOKUP(O81,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R81" s="220">
-        <f>IF(P81="","",H81)</f>
-        <v/>
-      </c>
-      <c r="S81" s="222" t="n">
+      <c r="Q82" s="220">
+        <f>IF(P82="","",IFERROR(VLOOKUP(O82,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R82" s="220">
+        <f>IF(P82="","",H82)</f>
+        <v/>
+      </c>
+      <c r="S82" s="222" t="n">
         <v>31050</v>
       </c>
-      <c r="T81" s="222" t="n">
+      <c r="T82" s="222" t="n">
         <v>7959560</v>
       </c>
-      <c r="U81" s="218" t="n"/>
-      <c r="V81" s="216" t="inlineStr">
+      <c r="U82" s="218" t="n"/>
+      <c r="V82" s="216" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
       </c>
-      <c r="W81" s="222" t="n">
+      <c r="W82" s="222" t="n">
         <v>250000</v>
       </c>
-      <c r="X81" s="217" t="inlineStr">
+      <c r="X82" s="217" t="inlineStr">
         <is>
           <t>진로직스</t>
         </is>
       </c>
-      <c r="Y81" s="222" t="n">
+      <c r="Y82" s="222" t="n">
         <v>5233502</v>
       </c>
-      <c r="Z81" s="222">
-        <f>S81+W81</f>
-        <v/>
-      </c>
-      <c r="AA81" s="222">
-        <f>K81+L81+M81+IFERROR(VLOOKUP(B81,RemitTable2,9,FALSE),0)+Y81+Z81</f>
-        <v/>
-      </c>
-      <c r="AB81" s="223" t="n">
+      <c r="Z82" s="222">
+        <f>S82+W82</f>
+        <v/>
+      </c>
+      <c r="AA82" s="222">
+        <f>K82+L82+M82+IFERROR(VLOOKUP(B82,RemitTable2,9,FALSE),0)+Y82+Z82</f>
+        <v/>
+      </c>
+      <c r="AB82" s="223" t="n">
         <v>44</v>
       </c>
-      <c r="AC81" s="222">
-        <f>ROUND(AA81/AB81,0)</f>
-        <v/>
-      </c>
-      <c r="AD81" s="216" t="inlineStr">
+      <c r="AC82" s="222">
+        <f>ROUND(AA82/AB82,0)</f>
+        <v/>
+      </c>
+      <c r="AD82" s="216" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE81" s="219" t="n"/>
-      <c r="AF81" s="218" t="n"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="284" t="n">
-        <v>78</v>
-      </c>
-      <c r="B82" s="284" t="inlineStr">
+      <c r="AE82" s="219" t="n"/>
+      <c r="AF82" s="218" t="n"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="284" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="284" t="inlineStr">
         <is>
           <t>GPO475-수리</t>
         </is>
       </c>
-      <c r="C82" s="285" t="inlineStr">
+      <c r="C83" s="285" t="inlineStr">
         <is>
           <t>GDC</t>
         </is>
       </c>
-      <c r="D82" s="284" t="inlineStr">
+      <c r="D83" s="284" t="inlineStr">
         <is>
           <t>Net 30 days</t>
         </is>
       </c>
-      <c r="E82" s="285" t="inlineStr">
+      <c r="E83" s="285" t="inlineStr">
         <is>
           <t>수리</t>
         </is>
       </c>
-      <c r="F82" s="286" t="n">
+      <c r="F83" s="286" t="n">
         <v>46126</v>
       </c>
-      <c r="G82" s="287" t="n">
+      <c r="G83" s="287" t="n">
         <v>46190</v>
       </c>
-      <c r="H82" s="288" t="n">
+      <c r="H83" s="288" t="n">
         <v>1500</v>
       </c>
-      <c r="I82" s="289" t="n">
+      <c r="I83" s="289" t="n">
         <v>1516.8</v>
       </c>
-      <c r="J82" s="290" t="n">
+      <c r="J83" s="290" t="n">
         <v>2275200</v>
       </c>
-      <c r="K82" s="290" t="n">
+      <c r="K83" s="290" t="n">
         <v>2275200</v>
       </c>
-      <c r="L82" s="290" t="n">
+      <c r="L83" s="290" t="n">
         <v>5515</v>
       </c>
-      <c r="M82" s="290" t="n">
+      <c r="M83" s="290" t="n">
         <v>5882</v>
       </c>
-      <c r="N82" s="284" t="inlineStr">
+      <c r="N83" s="284" t="inlineStr">
         <is>
           <t>SR-1000 IMB Inspection+Repair (SN A78267)</t>
         </is>
       </c>
-      <c r="O82" s="287" t="n"/>
-      <c r="P82" s="284" t="n"/>
-      <c r="Q82" s="288">
-        <f>IF(P82="","",IFERROR(VLOOKUP(O82,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R82" s="290">
-        <f>IF(P82="","",H82)</f>
-        <v/>
-      </c>
-      <c r="S82" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="286" t="n"/>
-      <c r="V82" s="284" t="n"/>
-      <c r="W82" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" s="285" t="inlineStr">
+      <c r="O83" s="287" t="n"/>
+      <c r="P83" s="284" t="n"/>
+      <c r="Q83" s="288">
+        <f>IF(P83="","",IFERROR(VLOOKUP(O83,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R83" s="290">
+        <f>IF(P83="","",H83)</f>
+        <v/>
+      </c>
+      <c r="S83" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="286" t="n"/>
+      <c r="V83" s="284" t="n"/>
+      <c r="W83" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" s="285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y82" s="290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" s="290">
-        <f>S82+W82</f>
-        <v/>
-      </c>
-      <c r="AA82" s="290">
-        <f>K82+L82+M82+IFERROR(VLOOKUP(B82,RemitTable2,9,FALSE),0)+Y82+Z82</f>
-        <v/>
-      </c>
-      <c r="AB82" s="291" t="n">
+      <c r="Y83" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="290">
+        <f>S83+W83</f>
+        <v/>
+      </c>
+      <c r="AA83" s="290">
+        <f>K83+L83+M83+IFERROR(VLOOKUP(B83,RemitTable2,9,FALSE),0)+Y83+Z83</f>
+        <v/>
+      </c>
+      <c r="AB83" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="AC82" s="290">
-        <f>ROUND(AA82/AB82,0)</f>
-        <v/>
-      </c>
-      <c r="AD82" s="284" t="n"/>
-      <c r="AE82" s="287" t="n"/>
-      <c r="AF82" s="286" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="147" t="inlineStr">
-        <is>
-          <t>장비/부품 합계</t>
-        </is>
-      </c>
-      <c r="B83" s="148" t="n"/>
-      <c r="C83" s="148" t="n"/>
-      <c r="D83" s="148" t="n"/>
-      <c r="E83" s="148" t="n"/>
-      <c r="F83" s="148" t="n"/>
-      <c r="G83" s="149" t="n"/>
-      <c r="H83" s="142">
-        <f>SUBTOTAL(9,H5:H50)</f>
-        <v/>
-      </c>
-      <c r="I83" s="141" t="n"/>
-      <c r="J83" s="142">
-        <f>SUBTOTAL(9,J5:J50)</f>
-        <v/>
-      </c>
-      <c r="K83" s="142">
-        <f>SUBTOTAL(9,K5:K50)</f>
-        <v/>
-      </c>
-      <c r="L83" s="142">
-        <f>SUBTOTAL(9,L5:L50)</f>
-        <v/>
-      </c>
-      <c r="M83" s="142">
-        <f>SUBTOTAL(9,M5:M50)</f>
-        <v/>
-      </c>
-      <c r="N83" s="141" t="n"/>
-      <c r="O83" s="141" t="n"/>
-      <c r="P83" s="141" t="n"/>
-      <c r="Q83" s="142" t="n"/>
-      <c r="R83" s="140" t="n"/>
-      <c r="S83" s="142">
-        <f>SUBTOTAL(9,S5:S50)</f>
-        <v/>
-      </c>
-      <c r="T83" s="142">
-        <f>SUBTOTAL(9,T5:T50)</f>
-        <v/>
-      </c>
-      <c r="U83" s="147" t="n"/>
-      <c r="V83" s="141" t="n"/>
-      <c r="W83" s="142">
-        <f>SUBTOTAL(9,W5:W50)</f>
-        <v/>
-      </c>
-      <c r="X83" s="147" t="n"/>
-      <c r="Y83" s="142">
-        <f>SUBTOTAL(9,Y5:Y50)</f>
-        <v/>
-      </c>
-      <c r="Z83" s="142">
-        <f>SUBTOTAL(9,Z5:Z50)</f>
-        <v/>
-      </c>
-      <c r="AA83" s="142">
-        <f>SUBTOTAL(9,AA5:AA50)</f>
-        <v/>
-      </c>
-      <c r="AB83" s="147" t="n"/>
-      <c r="AC83" s="141" t="n"/>
-      <c r="AD83" s="141" t="n"/>
-      <c r="AE83" s="141" t="n"/>
-      <c r="AF83" s="141" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="147" t="inlineStr">
-        <is>
-          <t>라이센스/워런티 합계</t>
-        </is>
-      </c>
-      <c r="B84" s="148" t="n"/>
-      <c r="C84" s="148" t="n"/>
-      <c r="D84" s="148" t="n"/>
-      <c r="E84" s="148" t="n"/>
-      <c r="F84" s="148" t="n"/>
-      <c r="G84" s="149" t="n"/>
-      <c r="H84" s="142">
-        <f>SUBTOTAL(9,H51:H78)</f>
-        <v/>
-      </c>
-      <c r="I84" s="141" t="n"/>
-      <c r="J84" s="142">
-        <f>SUBTOTAL(9,J51:J78)</f>
-        <v/>
-      </c>
-      <c r="K84" s="142">
-        <f>SUBTOTAL(9,K51:K78)</f>
-        <v/>
-      </c>
-      <c r="L84" s="142">
-        <f>SUBTOTAL(9,L51:L78)</f>
-        <v/>
-      </c>
-      <c r="M84" s="142">
-        <f>SUBTOTAL(9,M51:M78)</f>
-        <v/>
-      </c>
-      <c r="N84" s="141" t="n"/>
-      <c r="O84" s="141" t="n"/>
-      <c r="P84" s="141" t="n"/>
-      <c r="Q84" s="142" t="n"/>
-      <c r="R84" s="140" t="n"/>
-      <c r="S84" s="142">
-        <f>SUBTOTAL(9,S51:S78)</f>
-        <v/>
-      </c>
-      <c r="T84" s="142">
-        <f>SUBTOTAL(9,T51:T78)</f>
-        <v/>
-      </c>
-      <c r="U84" s="147" t="n"/>
-      <c r="V84" s="141" t="n"/>
-      <c r="W84" s="142">
-        <f>SUBTOTAL(9,W51:W78)</f>
-        <v/>
-      </c>
-      <c r="X84" s="147" t="n"/>
-      <c r="Y84" s="142">
-        <f>SUBTOTAL(9,Y51:Y78)</f>
-        <v/>
-      </c>
-      <c r="Z84" s="142">
-        <f>SUBTOTAL(9,Z51:Z78)</f>
-        <v/>
-      </c>
-      <c r="AA84" s="142">
-        <f>SUBTOTAL(9,AA51:AA78)</f>
-        <v/>
-      </c>
-      <c r="AB84" s="147" t="n"/>
-      <c r="AC84" s="141" t="n"/>
-      <c r="AD84" s="141" t="n"/>
-      <c r="AE84" s="141" t="n"/>
-      <c r="AF84" s="141" t="n"/>
+      <c r="AC83" s="290">
+        <f>ROUND(AA83/AB83,0)</f>
+        <v/>
+      </c>
+      <c r="AD83" s="284" t="n"/>
+      <c r="AE83" s="287" t="n"/>
+      <c r="AF83" s="286" t="n"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="284" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="284" t="inlineStr">
+        <is>
+          <t>PI44133</t>
+        </is>
+      </c>
+      <c r="C84" s="285" t="inlineStr">
+        <is>
+          <t>Ferco (Figueras)</t>
+        </is>
+      </c>
+      <c r="D84" s="284" t="inlineStr">
+        <is>
+          <t>20/60/20 T/T</t>
+        </is>
+      </c>
+      <c r="E84" s="285" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F84" s="286" t="n">
+        <v>46147</v>
+      </c>
+      <c r="G84" s="287" t="n">
+        <v>46217</v>
+      </c>
+      <c r="H84" s="288" t="n">
+        <v>22080</v>
+      </c>
+      <c r="I84" s="289">
+        <f>IFERROR(VLOOKUP(B84,RemitTable2,7,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="J84" s="290" t="n">
+        <v>30295527</v>
+      </c>
+      <c r="K84" s="290" t="n">
+        <v>30295527</v>
+      </c>
+      <c r="L84" s="290" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M84" s="290" t="n">
+        <v>16000</v>
+      </c>
+      <c r="N84" s="284" t="inlineStr">
+        <is>
+          <t>RIVA 4031 Recliner Seat 16EA (EUR 22,080) / Monoplex DH Bangbae</t>
+        </is>
+      </c>
+      <c r="O84" s="287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P84" s="284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q84" s="288">
+        <f>IF(P84="","",IFERROR(VLOOKUP(O84,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R84" s="290">
+        <f>IF(P84="","",H84)</f>
+        <v/>
+      </c>
+      <c r="S84" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="286" t="n"/>
+      <c r="V84" s="284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W84" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y84" s="290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="290">
+        <f>S84+W84</f>
+        <v/>
+      </c>
+      <c r="AA84" s="290">
+        <f>K84+L84+M84+IFERROR(VLOOKUP(B84,RemitTable2,9,FALSE),0)+Y84+Z84</f>
+        <v/>
+      </c>
+      <c r="AB84" s="291" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC84" s="290">
+        <f>ROUND(AA84/AB84,0)</f>
+        <v/>
+      </c>
+      <c r="AD84" s="284" t="n"/>
+      <c r="AE84" s="287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF84" s="286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="147" t="inlineStr">
         <is>
-          <t>기타 합계</t>
+          <t>장비/부품 합계</t>
         </is>
       </c>
       <c r="B85" s="148" t="n"/>
@@ -11841,24 +11938,24 @@
       <c r="F85" s="148" t="n"/>
       <c r="G85" s="149" t="n"/>
       <c r="H85" s="142">
-        <f>SUBTOTAL(9,H79:H82)</f>
+        <f>SUBTOTAL(9,H5:H50)</f>
         <v/>
       </c>
       <c r="I85" s="141" t="n"/>
       <c r="J85" s="142">
-        <f>SUBTOTAL(9,J79:J82)</f>
+        <f>SUBTOTAL(9,J5:J50)</f>
         <v/>
       </c>
       <c r="K85" s="142">
-        <f>SUBTOTAL(9,K79:K82)</f>
+        <f>SUBTOTAL(9,K5:K50)</f>
         <v/>
       </c>
       <c r="L85" s="142">
-        <f>SUBTOTAL(9,L79:L82)</f>
+        <f>SUBTOTAL(9,L5:L50)</f>
         <v/>
       </c>
       <c r="M85" s="142">
-        <f>SUBTOTAL(9,M79:M82)</f>
+        <f>SUBTOTAL(9,M5:M50)</f>
         <v/>
       </c>
       <c r="N85" s="141" t="n"/>
@@ -11867,30 +11964,30 @@
       <c r="Q85" s="142" t="n"/>
       <c r="R85" s="140" t="n"/>
       <c r="S85" s="142">
-        <f>SUBTOTAL(9,S79:S82)</f>
+        <f>SUBTOTAL(9,S5:S50)</f>
         <v/>
       </c>
       <c r="T85" s="142">
-        <f>SUBTOTAL(9,T79:T82)</f>
+        <f>SUBTOTAL(9,T5:T50)</f>
         <v/>
       </c>
       <c r="U85" s="147" t="n"/>
       <c r="V85" s="141" t="n"/>
       <c r="W85" s="142">
-        <f>SUBTOTAL(9,W79:W82)</f>
+        <f>SUBTOTAL(9,W5:W50)</f>
         <v/>
       </c>
       <c r="X85" s="147" t="n"/>
       <c r="Y85" s="142">
-        <f>SUBTOTAL(9,Y79:Y82)</f>
+        <f>SUBTOTAL(9,Y5:Y50)</f>
         <v/>
       </c>
       <c r="Z85" s="142">
-        <f>SUBTOTAL(9,Z79:Z82)</f>
+        <f>SUBTOTAL(9,Z5:Z50)</f>
         <v/>
       </c>
       <c r="AA85" s="142">
-        <f>SUBTOTAL(9,AA79:AA82)</f>
+        <f>SUBTOTAL(9,AA5:AA50)</f>
         <v/>
       </c>
       <c r="AB85" s="147" t="n"/>
@@ -11900,9 +11997,9 @@
       <c r="AF85" s="141" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="154" t="inlineStr">
-        <is>
-          <t>총 합계</t>
+      <c r="A86" s="147" t="inlineStr">
+        <is>
+          <t>라이센스/워런티 합계</t>
         </is>
       </c>
       <c r="B86" s="148" t="n"/>
@@ -11911,75 +12008,230 @@
       <c r="E86" s="148" t="n"/>
       <c r="F86" s="148" t="n"/>
       <c r="G86" s="149" t="n"/>
-      <c r="H86" s="146">
-        <f>SUBTOTAL(9,H5:H82)</f>
-        <v/>
-      </c>
-      <c r="I86" s="145" t="n"/>
-      <c r="J86" s="146">
-        <f>SUBTOTAL(9,J5:J82)</f>
-        <v/>
-      </c>
-      <c r="K86" s="146">
-        <f>SUBTOTAL(9,K5:K82)</f>
-        <v/>
-      </c>
-      <c r="L86" s="146">
-        <f>SUBTOTAL(9,L5:L82)</f>
-        <v/>
-      </c>
-      <c r="M86" s="146">
-        <f>SUBTOTAL(9,M5:M82)</f>
-        <v/>
-      </c>
-      <c r="N86" s="145" t="n"/>
-      <c r="O86" s="145" t="n"/>
-      <c r="P86" s="145" t="n"/>
-      <c r="Q86" s="146" t="n"/>
-      <c r="R86" s="144" t="n"/>
-      <c r="S86" s="146">
-        <f>SUBTOTAL(9,S5:S82)</f>
-        <v/>
-      </c>
-      <c r="T86" s="146">
-        <f>SUBTOTAL(9,T5:T82)</f>
-        <v/>
-      </c>
-      <c r="U86" s="154" t="n"/>
-      <c r="V86" s="145" t="n"/>
-      <c r="W86" s="146">
-        <f>SUBTOTAL(9,W5:W82)</f>
-        <v/>
-      </c>
-      <c r="X86" s="154" t="n"/>
-      <c r="Y86" s="146">
-        <f>SUBTOTAL(9,Y5:Y82)</f>
-        <v/>
-      </c>
-      <c r="Z86" s="146">
-        <f>SUBTOTAL(9,Z5:Z82)</f>
-        <v/>
-      </c>
-      <c r="AA86" s="146">
-        <f>SUBTOTAL(9,AA5:AA82)</f>
-        <v/>
-      </c>
-      <c r="AB86" s="154" t="n"/>
-      <c r="AC86" s="145" t="n"/>
-      <c r="AD86" s="145" t="n"/>
-      <c r="AE86" s="145" t="n"/>
-      <c r="AF86" s="145" t="n"/>
-    </row>
-    <row r="100">
-      <c r="M100" s="40" t="n"/>
+      <c r="H86" s="142">
+        <f>SUBTOTAL(9,H51:H79)</f>
+        <v/>
+      </c>
+      <c r="I86" s="141" t="n"/>
+      <c r="J86" s="142">
+        <f>SUBTOTAL(9,J51:J79)</f>
+        <v/>
+      </c>
+      <c r="K86" s="142">
+        <f>SUBTOTAL(9,K51:K79)</f>
+        <v/>
+      </c>
+      <c r="L86" s="142">
+        <f>SUBTOTAL(9,L51:L79)</f>
+        <v/>
+      </c>
+      <c r="M86" s="142">
+        <f>SUBTOTAL(9,M51:M79)</f>
+        <v/>
+      </c>
+      <c r="N86" s="141" t="n"/>
+      <c r="O86" s="141" t="n"/>
+      <c r="P86" s="141" t="n"/>
+      <c r="Q86" s="142" t="n"/>
+      <c r="R86" s="140" t="n"/>
+      <c r="S86" s="142">
+        <f>SUBTOTAL(9,S51:S79)</f>
+        <v/>
+      </c>
+      <c r="T86" s="142">
+        <f>SUBTOTAL(9,T51:T79)</f>
+        <v/>
+      </c>
+      <c r="U86" s="147" t="n"/>
+      <c r="V86" s="141" t="n"/>
+      <c r="W86" s="142">
+        <f>SUBTOTAL(9,W51:W79)</f>
+        <v/>
+      </c>
+      <c r="X86" s="147" t="n"/>
+      <c r="Y86" s="142">
+        <f>SUBTOTAL(9,Y51:Y79)</f>
+        <v/>
+      </c>
+      <c r="Z86" s="142">
+        <f>SUBTOTAL(9,Z51:Z79)</f>
+        <v/>
+      </c>
+      <c r="AA86" s="142">
+        <f>SUBTOTAL(9,AA51:AA79)</f>
+        <v/>
+      </c>
+      <c r="AB86" s="147" t="n"/>
+      <c r="AC86" s="141" t="n"/>
+      <c r="AD86" s="141" t="n"/>
+      <c r="AE86" s="141" t="n"/>
+      <c r="AF86" s="141" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="147" t="inlineStr">
+        <is>
+          <t>기타 합계</t>
+        </is>
+      </c>
+      <c r="B87" s="148" t="n"/>
+      <c r="C87" s="148" t="n"/>
+      <c r="D87" s="148" t="n"/>
+      <c r="E87" s="148" t="n"/>
+      <c r="F87" s="148" t="n"/>
+      <c r="G87" s="149" t="n"/>
+      <c r="H87" s="142">
+        <f>SUBTOTAL(9,H80:H84)</f>
+        <v/>
+      </c>
+      <c r="I87" s="141" t="n"/>
+      <c r="J87" s="142">
+        <f>SUBTOTAL(9,J80:J84)</f>
+        <v/>
+      </c>
+      <c r="K87" s="142">
+        <f>SUBTOTAL(9,K80:K84)</f>
+        <v/>
+      </c>
+      <c r="L87" s="142">
+        <f>SUBTOTAL(9,L80:L84)</f>
+        <v/>
+      </c>
+      <c r="M87" s="142">
+        <f>SUBTOTAL(9,M80:M84)</f>
+        <v/>
+      </c>
+      <c r="N87" s="141" t="n"/>
+      <c r="O87" s="141" t="n"/>
+      <c r="P87" s="141" t="n"/>
+      <c r="Q87" s="142" t="n"/>
+      <c r="R87" s="140" t="n"/>
+      <c r="S87" s="142">
+        <f>SUBTOTAL(9,S80:S84)</f>
+        <v/>
+      </c>
+      <c r="T87" s="142">
+        <f>SUBTOTAL(9,T80:T84)</f>
+        <v/>
+      </c>
+      <c r="U87" s="147" t="n"/>
+      <c r="V87" s="141" t="n"/>
+      <c r="W87" s="142">
+        <f>SUBTOTAL(9,W80:W84)</f>
+        <v/>
+      </c>
+      <c r="X87" s="147" t="n"/>
+      <c r="Y87" s="142">
+        <f>SUBTOTAL(9,Y80:Y84)</f>
+        <v/>
+      </c>
+      <c r="Z87" s="142">
+        <f>SUBTOTAL(9,Z80:Z84)</f>
+        <v/>
+      </c>
+      <c r="AA87" s="142">
+        <f>SUBTOTAL(9,AA80:AA84)</f>
+        <v/>
+      </c>
+      <c r="AB87" s="147" t="n"/>
+      <c r="AC87" s="141" t="n"/>
+      <c r="AD87" s="141" t="n"/>
+      <c r="AE87" s="141" t="n"/>
+      <c r="AF87" s="141" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="154" t="inlineStr">
+        <is>
+          <t>총 합계</t>
+        </is>
+      </c>
+      <c r="B88" s="148" t="n"/>
+      <c r="C88" s="148" t="n"/>
+      <c r="D88" s="148" t="n"/>
+      <c r="E88" s="148" t="n"/>
+      <c r="F88" s="148" t="n"/>
+      <c r="G88" s="149" t="n"/>
+      <c r="H88" s="146">
+        <f>SUBTOTAL(9,H5:H84)</f>
+        <v/>
+      </c>
+      <c r="I88" s="145" t="n"/>
+      <c r="J88" s="146">
+        <f>SUBTOTAL(9,J5:J84)</f>
+        <v/>
+      </c>
+      <c r="K88" s="146">
+        <f>SUBTOTAL(9,K5:K84)</f>
+        <v/>
+      </c>
+      <c r="L88" s="146">
+        <f>SUBTOTAL(9,L5:L84)</f>
+        <v/>
+      </c>
+      <c r="M88" s="146">
+        <f>SUBTOTAL(9,M5:M84)</f>
+        <v/>
+      </c>
+      <c r="N88" s="145" t="n"/>
+      <c r="O88" s="145" t="n"/>
+      <c r="P88" s="145" t="n"/>
+      <c r="Q88" s="146" t="n"/>
+      <c r="R88" s="144" t="n"/>
+      <c r="S88" s="146">
+        <f>SUBTOTAL(9,S5:S84)</f>
+        <v/>
+      </c>
+      <c r="T88" s="146">
+        <f>SUBTOTAL(9,T5:T84)</f>
+        <v/>
+      </c>
+      <c r="U88" s="154" t="n"/>
+      <c r="V88" s="145" t="n"/>
+      <c r="W88" s="146">
+        <f>SUBTOTAL(9,W5:W84)</f>
+        <v/>
+      </c>
+      <c r="X88" s="154" t="n"/>
+      <c r="Y88" s="146">
+        <f>SUBTOTAL(9,Y5:Y84)</f>
+        <v/>
+      </c>
+      <c r="Z88" s="146">
+        <f>SUBTOTAL(9,Z5:Z84)</f>
+        <v/>
+      </c>
+      <c r="AA88" s="146">
+        <f>SUBTOTAL(9,AA5:AA84)</f>
+        <v/>
+      </c>
+      <c r="AB88" s="154" t="n"/>
+      <c r="AC88" s="145" t="n"/>
+      <c r="AD88" s="145" t="n"/>
+      <c r="AE88" s="145" t="n"/>
+      <c r="AF88" s="145" t="n"/>
+    </row>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102">
+      <c r="M102" s="40" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A85:G85"/>
     <mergeCell ref="G3:N3"/>
+    <mergeCell ref="A88:G88"/>
     <mergeCell ref="A1:AF1"/>
-    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="A87:G87"/>
     <mergeCell ref="AD3:AF3"/>
     <mergeCell ref="A86:G86"/>
     <mergeCell ref="X3:Z3"/>
@@ -13224,10 +13476,8 @@
       <c r="G26" s="227" t="n">
         <v>46181</v>
       </c>
-      <c r="H26" s="227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H26" s="227" t="n">
+        <v>46241</v>
       </c>
       <c r="I26" s="227" t="n">
         <v>46192</v>
@@ -13434,6 +13684,57 @@
         <v>46387</v>
       </c>
       <c r="K30" s="224" t="inlineStr">
+        <is>
+          <t>라이센스</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="224" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="224" t="inlineStr">
+        <is>
+          <t>CPO700</t>
+        </is>
+      </c>
+      <c r="C31" s="225" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D31" s="225" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="E31" s="226" t="n">
+        <v>1114</v>
+      </c>
+      <c r="F31" s="224" t="inlineStr">
+        <is>
+          <t>EW Extended Warranty (인보이스 미수취, 대상 미확인)</t>
+        </is>
+      </c>
+      <c r="G31" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="227" t="n">
+        <v>46241</v>
+      </c>
+      <c r="I31" s="227" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="J31" s="227" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="K31" s="224" t="inlineStr">
         <is>
           <t>라이센스</t>
         </is>
@@ -15504,7 +15805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="160" min="1" max="1"/>
@@ -17379,321 +17680,325 @@
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="169" t="inlineStr">
+      <c r="A41" s="234" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="234" t="inlineStr">
+        <is>
+          <t>2026.07.14</t>
+        </is>
+      </c>
+      <c r="C41" s="235" t="inlineStr">
+        <is>
+          <t>Ferco (Figueras, EUR)</t>
+        </is>
+      </c>
+      <c r="D41" s="234" t="inlineStr">
+        <is>
+          <t>PI44133-2</t>
+        </is>
+      </c>
+      <c r="E41" s="236" t="n">
+        <v>13248</v>
+      </c>
+      <c r="F41" s="237" t="n">
+        <v>1701.72</v>
+      </c>
+      <c r="G41" s="236" t="n">
+        <v>25</v>
+      </c>
+      <c r="H41" s="238" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I41" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J41" s="238" t="n">
+        <v>22604929</v>
+      </c>
+      <c r="K41" s="238">
+        <f>ROUND((E41+G41)*F41+H41+I41,0)</f>
+        <v/>
+      </c>
+      <c r="L41" s="239">
+        <f>J41-K41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="234" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="234" t="inlineStr">
+        <is>
+          <t>2026.08.04</t>
+        </is>
+      </c>
+      <c r="C42" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D42" s="234" t="inlineStr">
+        <is>
+          <t>GPO488</t>
+        </is>
+      </c>
+      <c r="E42" s="236" t="n">
+        <v>180</v>
+      </c>
+      <c r="F42" s="237" t="n">
+        <v>1432.9</v>
+      </c>
+      <c r="G42" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" s="238" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I42" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J42" s="238" t="n">
+        <v>297080</v>
+      </c>
+      <c r="K42" s="238">
+        <f>ROUND((E42+G42)*F42+H42+I42,0)</f>
+        <v/>
+      </c>
+      <c r="L42" s="239">
+        <f>J42-K42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="234" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="234" t="inlineStr">
+        <is>
+          <t>2026.08.07</t>
+        </is>
+      </c>
+      <c r="C43" s="235" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D43" s="234" t="inlineStr">
+        <is>
+          <t>CPO700, CPO702</t>
+        </is>
+      </c>
+      <c r="E43" s="236" t="n">
+        <v>33829</v>
+      </c>
+      <c r="F43" s="237" t="n">
+        <v>1429.8</v>
+      </c>
+      <c r="G43" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H43" s="238" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I43" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J43" s="238" t="n">
+        <v>48417800</v>
+      </c>
+      <c r="K43" s="238">
+        <f>ROUND((E43+G43)*F43+H43+I43,0)</f>
+        <v/>
+      </c>
+      <c r="L43" s="239">
+        <f>J43-K43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="234" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="234" t="inlineStr">
+        <is>
+          <t>2026.08.11</t>
+        </is>
+      </c>
+      <c r="C44" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D44" s="234" t="inlineStr">
+        <is>
+          <t>GPO493</t>
+        </is>
+      </c>
+      <c r="E44" s="236" t="n">
+        <v>4470</v>
+      </c>
+      <c r="F44" s="237" t="n">
+        <v>1419.3</v>
+      </c>
+      <c r="G44" s="236" t="n">
+        <v>20</v>
+      </c>
+      <c r="H44" s="238" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I44" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J44" s="238" t="n">
+        <v>6388157</v>
+      </c>
+      <c r="K44" s="238">
+        <f>ROUND((E44+G44)*F44+H44+I44,0)</f>
+        <v/>
+      </c>
+      <c r="L44" s="239">
+        <f>J44-K44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="169" t="inlineStr">
         <is>
           <t>② PO별 비용 안분 내역</t>
         </is>
       </c>
-      <c r="B41" s="148" t="n"/>
-      <c r="C41" s="148" t="n"/>
-      <c r="D41" s="148" t="n"/>
-      <c r="E41" s="148" t="n"/>
-      <c r="F41" s="148" t="n"/>
-      <c r="G41" s="148" t="n"/>
-      <c r="H41" s="148" t="n"/>
-      <c r="I41" s="148" t="n"/>
-      <c r="J41" s="148" t="n"/>
-      <c r="K41" s="148" t="n"/>
-      <c r="L41" s="149" t="n"/>
-      <c r="M41" s="115" t="n"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="150" t="inlineStr">
+      <c r="B45" s="148" t="n"/>
+      <c r="C45" s="148" t="n"/>
+      <c r="D45" s="148" t="n"/>
+      <c r="E45" s="148" t="n"/>
+      <c r="F45" s="148" t="n"/>
+      <c r="G45" s="148" t="n"/>
+      <c r="H45" s="148" t="n"/>
+      <c r="I45" s="148" t="n"/>
+      <c r="J45" s="148" t="n"/>
+      <c r="K45" s="148" t="n"/>
+      <c r="L45" s="149" t="n"/>
+      <c r="M45" s="115" t="n"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="150" t="inlineStr">
         <is>
           <t>PO No.</t>
         </is>
       </c>
-      <c r="B42" s="150" t="inlineStr">
+      <c r="B46" s="150" t="inlineStr">
         <is>
           <t>송금일</t>
         </is>
       </c>
-      <c r="C42" s="150" t="inlineStr">
+      <c r="C46" s="150" t="inlineStr">
         <is>
           <t>업체</t>
         </is>
       </c>
-      <c r="D42" s="150" t="inlineStr">
+      <c r="D46" s="150" t="inlineStr">
         <is>
           <t>PO USD</t>
         </is>
       </c>
-      <c r="E42" s="150" t="inlineStr">
+      <c r="E46" s="150" t="inlineStr">
         <is>
           <t>그룹총USD</t>
         </is>
       </c>
-      <c r="F42" s="150" t="inlineStr">
+      <c r="F46" s="150" t="inlineStr">
         <is>
           <t>배부비율</t>
         </is>
       </c>
-      <c r="G42" s="150" t="inlineStr">
+      <c r="G46" s="150" t="inlineStr">
         <is>
           <t>적용환율</t>
         </is>
       </c>
-      <c r="H42" s="150" t="inlineStr">
+      <c r="H46" s="150" t="inlineStr">
         <is>
           <t>원화환산액</t>
         </is>
       </c>
-      <c r="I42" s="150" t="inlineStr">
+      <c r="I46" s="150" t="inlineStr">
         <is>
           <t>중개수수료안분</t>
         </is>
       </c>
-      <c r="J42" s="150" t="inlineStr">
+      <c r="J46" s="150" t="inlineStr">
         <is>
           <t>수수료안분</t>
         </is>
       </c>
-      <c r="K42" s="150" t="inlineStr">
+      <c r="K46" s="150" t="inlineStr">
         <is>
           <t>전신료안분</t>
         </is>
       </c>
-      <c r="L42" s="150" t="inlineStr">
+      <c r="L46" s="150" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
-      </c>
-      <c r="M42" s="115" t="n"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="116" t="inlineStr">
-        <is>
-          <t>CPO678-1</t>
-        </is>
-      </c>
-      <c r="B43" s="116" t="inlineStr">
-        <is>
-          <t>2025.12.16</t>
-        </is>
-      </c>
-      <c r="C43" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D43" s="118" t="n">
-        <v>139083</v>
-      </c>
-      <c r="E43" s="118" t="n">
-        <v>143557</v>
-      </c>
-      <c r="F43" s="122" t="n">
-        <v>0.968835</v>
-      </c>
-      <c r="G43" s="118" t="n">
-        <v>1479.7</v>
-      </c>
-      <c r="H43" s="120" t="n">
-        <v>205801115</v>
-      </c>
-      <c r="I43" s="120" t="n">
-        <v>28672</v>
-      </c>
-      <c r="J43" s="120" t="n">
-        <v>12110</v>
-      </c>
-      <c r="K43" s="120" t="n">
-        <v>7751</v>
-      </c>
-      <c r="L43" s="121" t="n">
-        <v>205849648</v>
-      </c>
-      <c r="M43" s="115" t="n"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="116" t="inlineStr">
-        <is>
-          <t>CPO679</t>
-        </is>
-      </c>
-      <c r="B44" s="116" t="inlineStr">
-        <is>
-          <t>2025.12.16</t>
-        </is>
-      </c>
-      <c r="C44" s="117" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D44" s="118" t="n">
-        <v>4474</v>
-      </c>
-      <c r="E44" s="118" t="n">
-        <v>143557</v>
-      </c>
-      <c r="F44" s="122" t="n">
-        <v>0.031165</v>
-      </c>
-      <c r="G44" s="118" t="n">
-        <v>1479.7</v>
-      </c>
-      <c r="H44" s="120" t="n">
-        <v>6620178</v>
-      </c>
-      <c r="I44" s="120" t="n">
-        <v>922</v>
-      </c>
-      <c r="J44" s="120" t="n">
-        <v>390</v>
-      </c>
-      <c r="K44" s="120" t="n">
-        <v>249</v>
-      </c>
-      <c r="L44" s="121" t="n">
-        <v>6621739</v>
-      </c>
-      <c r="M44" s="115" t="n"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="116" t="inlineStr">
-        <is>
-          <t>MPO65</t>
-        </is>
-      </c>
-      <c r="B45" s="116" t="inlineStr">
-        <is>
-          <t>2025.12.16</t>
-        </is>
-      </c>
-      <c r="C45" s="117" t="inlineStr">
-        <is>
-          <t>MAG</t>
-        </is>
-      </c>
-      <c r="D45" s="118" t="n">
-        <v>4936</v>
-      </c>
-      <c r="E45" s="118" t="n">
-        <v>15040</v>
-      </c>
-      <c r="F45" s="122" t="n">
-        <v>0.328191</v>
-      </c>
-      <c r="G45" s="118" t="n">
-        <v>1480</v>
-      </c>
-      <c r="H45" s="120" t="n">
-        <v>7305280</v>
-      </c>
-      <c r="I45" s="120" t="n">
-        <v>9714</v>
-      </c>
-      <c r="J45" s="120" t="n">
-        <v>3282</v>
-      </c>
-      <c r="K45" s="120" t="n">
-        <v>2626</v>
-      </c>
-      <c r="L45" s="121" t="n">
-        <v>7320902</v>
-      </c>
-      <c r="M45" s="115" t="n"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="116" t="inlineStr">
-        <is>
-          <t>GPO451</t>
-        </is>
-      </c>
-      <c r="B46" s="116" t="inlineStr">
-        <is>
-          <t>2025.12.29</t>
-        </is>
-      </c>
-      <c r="C46" s="117" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D46" s="118" t="n">
-        <v>9060</v>
-      </c>
-      <c r="E46" s="118" t="n">
-        <v>13860</v>
-      </c>
-      <c r="F46" s="122" t="n">
-        <v>0.65368</v>
-      </c>
-      <c r="G46" s="118" t="n">
-        <v>1439.1</v>
-      </c>
-      <c r="H46" s="120" t="n">
-        <v>13038246</v>
-      </c>
-      <c r="I46" s="120" t="n">
-        <v>18814</v>
-      </c>
-      <c r="J46" s="120" t="n">
-        <v>6537</v>
-      </c>
-      <c r="K46" s="120" t="n">
-        <v>5229</v>
-      </c>
-      <c r="L46" s="121" t="n">
-        <v>13068826</v>
       </c>
       <c r="M46" s="115" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="116" t="inlineStr">
         <is>
-          <t>GPO458</t>
+          <t>CPO678-1</t>
         </is>
       </c>
       <c r="B47" s="116" t="inlineStr">
         <is>
-          <t>2025.12.29</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="C47" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D47" s="118" t="n">
-        <v>350</v>
+        <v>139083</v>
       </c>
       <c r="E47" s="118" t="n">
-        <v>13860</v>
+        <v>143557</v>
       </c>
       <c r="F47" s="122" t="n">
-        <v>0.025253</v>
+        <v>0.968835</v>
       </c>
       <c r="G47" s="118" t="n">
-        <v>1439.1</v>
+        <v>1479.7</v>
       </c>
       <c r="H47" s="120" t="n">
-        <v>503685</v>
+        <v>205801115</v>
       </c>
       <c r="I47" s="120" t="n">
-        <v>727</v>
+        <v>28672</v>
       </c>
       <c r="J47" s="120" t="n">
-        <v>253</v>
+        <v>12110</v>
       </c>
       <c r="K47" s="120" t="n">
-        <v>202</v>
+        <v>7751</v>
       </c>
       <c r="L47" s="121" t="n">
-        <v>504867</v>
+        <v>205849648</v>
       </c>
       <c r="M47" s="115" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="116" t="inlineStr">
         <is>
-          <t>CPO680</t>
+          <t>CPO679</t>
         </is>
       </c>
       <c r="B48" s="116" t="inlineStr">
         <is>
-          <t>2026.01.13</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="C48" s="117" t="inlineStr">
@@ -17702,88 +18007,88 @@
         </is>
       </c>
       <c r="D48" s="118" t="n">
-        <v>252</v>
+        <v>4474</v>
       </c>
       <c r="E48" s="118" t="n">
-        <v>252</v>
+        <v>143557</v>
       </c>
       <c r="F48" s="122" t="n">
-        <v>1</v>
+        <v>0.031165</v>
       </c>
       <c r="G48" s="118" t="n">
-        <v>1479</v>
+        <v>1479.7</v>
       </c>
       <c r="H48" s="120" t="n">
-        <v>372708</v>
+        <v>6620178</v>
       </c>
       <c r="I48" s="120" t="n">
-        <v>29580</v>
+        <v>922</v>
       </c>
       <c r="J48" s="120" t="n">
-        <v>2500</v>
+        <v>390</v>
       </c>
       <c r="K48" s="120" t="n">
-        <v>8000</v>
+        <v>249</v>
       </c>
       <c r="L48" s="121" t="n">
-        <v>412788</v>
+        <v>6621739</v>
       </c>
       <c r="M48" s="115" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="116" t="inlineStr">
         <is>
-          <t>GPO459</t>
+          <t>MPO65</t>
         </is>
       </c>
       <c r="B49" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="C49" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D49" s="118" t="n">
-        <v>450</v>
+        <v>4936</v>
       </c>
       <c r="E49" s="118" t="n">
-        <v>3700</v>
+        <v>15040</v>
       </c>
       <c r="F49" s="122" t="n">
-        <v>0.121622</v>
+        <v>0.328191</v>
       </c>
       <c r="G49" s="118" t="n">
-        <v>1475.7</v>
+        <v>1480</v>
       </c>
       <c r="H49" s="120" t="n">
-        <v>664065</v>
+        <v>7305280</v>
       </c>
       <c r="I49" s="120" t="n">
-        <v>3590</v>
+        <v>9714</v>
       </c>
       <c r="J49" s="120" t="n">
-        <v>912</v>
+        <v>3282</v>
       </c>
       <c r="K49" s="120" t="n">
-        <v>973</v>
+        <v>2626</v>
       </c>
       <c r="L49" s="121" t="n">
-        <v>669540</v>
+        <v>7320902</v>
       </c>
       <c r="M49" s="115" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="116" t="inlineStr">
         <is>
-          <t>GPO460</t>
+          <t>GPO451</t>
         </is>
       </c>
       <c r="B50" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2025.12.29</t>
         </is>
       </c>
       <c r="C50" s="117" t="inlineStr">
@@ -17792,43 +18097,43 @@
         </is>
       </c>
       <c r="D50" s="118" t="n">
-        <v>2710</v>
+        <v>9060</v>
       </c>
       <c r="E50" s="118" t="n">
-        <v>3700</v>
+        <v>13860</v>
       </c>
       <c r="F50" s="122" t="n">
-        <v>0.732432</v>
+        <v>0.65368</v>
       </c>
       <c r="G50" s="118" t="n">
-        <v>1475.7</v>
+        <v>1439.1</v>
       </c>
       <c r="H50" s="120" t="n">
-        <v>3999147</v>
+        <v>13038246</v>
       </c>
       <c r="I50" s="120" t="n">
-        <v>21617</v>
+        <v>18814</v>
       </c>
       <c r="J50" s="120" t="n">
-        <v>5493</v>
+        <v>6537</v>
       </c>
       <c r="K50" s="120" t="n">
-        <v>5859</v>
+        <v>5229</v>
       </c>
       <c r="L50" s="121" t="n">
-        <v>4032116</v>
+        <v>13068826</v>
       </c>
       <c r="M50" s="115" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="116" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="B51" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2025.12.29</t>
         </is>
       </c>
       <c r="C51" s="117" t="inlineStr">
@@ -17837,308 +18142,308 @@
         </is>
       </c>
       <c r="D51" s="118" t="n">
-        <v>540</v>
+        <v>350</v>
       </c>
       <c r="E51" s="118" t="n">
-        <v>3700</v>
+        <v>13860</v>
       </c>
       <c r="F51" s="122" t="n">
-        <v>0.145946</v>
+        <v>0.025253</v>
       </c>
       <c r="G51" s="118" t="n">
-        <v>1475.7</v>
+        <v>1439.1</v>
       </c>
       <c r="H51" s="120" t="n">
-        <v>796878</v>
+        <v>503685</v>
       </c>
       <c r="I51" s="120" t="n">
-        <v>4307</v>
+        <v>727</v>
       </c>
       <c r="J51" s="120" t="n">
-        <v>1095</v>
+        <v>253</v>
       </c>
       <c r="K51" s="120" t="n">
-        <v>1168</v>
+        <v>202</v>
       </c>
       <c r="L51" s="121" t="n">
-        <v>803448</v>
+        <v>504867</v>
       </c>
       <c r="M51" s="115" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="116" t="inlineStr">
         <is>
-          <t>MPO66</t>
+          <t>CPO680</t>
         </is>
       </c>
       <c r="B52" s="116" t="inlineStr">
         <is>
-          <t>2026.01.21</t>
+          <t>2026.01.13</t>
         </is>
       </c>
       <c r="C52" s="117" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D52" s="118" t="n">
-        <v>9626.35</v>
+        <v>252</v>
       </c>
       <c r="E52" s="118" t="n">
-        <v>9626.35</v>
+        <v>252</v>
       </c>
       <c r="F52" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="118" t="n">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="H52" s="120" t="n">
-        <v>14208493</v>
+        <v>372708</v>
       </c>
       <c r="I52" s="120" t="n">
-        <v>29520</v>
+        <v>29580</v>
       </c>
       <c r="J52" s="120" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="K52" s="120" t="n">
         <v>8000</v>
       </c>
       <c r="L52" s="121" t="n">
-        <v>14256013</v>
+        <v>412788</v>
       </c>
       <c r="M52" s="115" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="116" t="inlineStr">
         <is>
-          <t>LPO001</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="B53" s="116" t="inlineStr">
         <is>
-          <t>2026.01.30</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C53" s="117" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D53" s="118" t="n">
-        <v>5056.8</v>
+        <v>450</v>
       </c>
       <c r="E53" s="118" t="n">
-        <v>5056.8</v>
+        <v>3700</v>
       </c>
       <c r="F53" s="122" t="n">
-        <v>1</v>
+        <v>0.121622</v>
       </c>
       <c r="G53" s="118" t="n">
-        <v>1445.5</v>
+        <v>1475.7</v>
       </c>
       <c r="H53" s="120" t="n">
-        <v>7309604</v>
+        <v>664065</v>
       </c>
       <c r="I53" s="120" t="n">
-        <v>28910</v>
+        <v>3590</v>
       </c>
       <c r="J53" s="120" t="n">
-        <v>10000</v>
+        <v>912</v>
       </c>
       <c r="K53" s="120" t="n">
-        <v>8000</v>
+        <v>973</v>
       </c>
       <c r="L53" s="121" t="n">
-        <v>7356514</v>
+        <v>669540</v>
       </c>
       <c r="M53" s="115" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="116" t="inlineStr">
         <is>
-          <t>CPO682</t>
+          <t>GPO460</t>
         </is>
       </c>
       <c r="B54" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C54" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D54" s="118" t="n">
-        <v>20174</v>
+        <v>2710</v>
       </c>
       <c r="E54" s="118" t="n">
-        <v>24794</v>
+        <v>3700</v>
       </c>
       <c r="F54" s="122" t="n">
-        <v>0.813665</v>
+        <v>0.732432</v>
       </c>
       <c r="G54" s="118" t="n">
-        <v>1454.7</v>
+        <v>1475.7</v>
       </c>
       <c r="H54" s="120" t="n">
-        <v>29347118</v>
+        <v>3999147</v>
       </c>
       <c r="I54" s="120" t="n">
-        <v>23673</v>
+        <v>21617</v>
       </c>
       <c r="J54" s="120" t="n">
-        <v>10171</v>
+        <v>5493</v>
       </c>
       <c r="K54" s="120" t="n">
-        <v>6509</v>
+        <v>5859</v>
       </c>
       <c r="L54" s="121" t="n">
-        <v>29387471</v>
+        <v>4032116</v>
       </c>
       <c r="M54" s="115" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="116" t="inlineStr">
         <is>
-          <t>CPO683</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="B55" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C55" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D55" s="118" t="n">
-        <v>4620</v>
+        <v>540</v>
       </c>
       <c r="E55" s="118" t="n">
-        <v>24794</v>
+        <v>3700</v>
       </c>
       <c r="F55" s="122" t="n">
-        <v>0.186335</v>
+        <v>0.145946</v>
       </c>
       <c r="G55" s="118" t="n">
-        <v>1454.7</v>
+        <v>1475.7</v>
       </c>
       <c r="H55" s="120" t="n">
-        <v>6720714</v>
+        <v>796878</v>
       </c>
       <c r="I55" s="120" t="n">
-        <v>5421</v>
+        <v>4307</v>
       </c>
       <c r="J55" s="120" t="n">
-        <v>2329</v>
+        <v>1095</v>
       </c>
       <c r="K55" s="120" t="n">
-        <v>1491</v>
+        <v>1168</v>
       </c>
       <c r="L55" s="121" t="n">
-        <v>6729955</v>
+        <v>803448</v>
       </c>
       <c r="M55" s="115" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="116" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>MPO66</t>
         </is>
       </c>
       <c r="B56" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.01.21</t>
         </is>
       </c>
       <c r="C56" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D56" s="118" t="n">
-        <v>1440</v>
+        <v>9626.35</v>
       </c>
       <c r="E56" s="118" t="n">
-        <v>11599.57</v>
+        <v>9626.35</v>
       </c>
       <c r="F56" s="122" t="n">
-        <v>0.124143</v>
+        <v>1</v>
       </c>
       <c r="G56" s="118" t="n">
-        <v>1453.6</v>
+        <v>1476</v>
       </c>
       <c r="H56" s="120" t="n">
-        <v>2093184</v>
+        <v>14208493</v>
       </c>
       <c r="I56" s="120" t="n">
-        <v>3609</v>
+        <v>29520</v>
       </c>
       <c r="J56" s="120" t="n">
-        <v>1241</v>
+        <v>10000</v>
       </c>
       <c r="K56" s="120" t="n">
-        <v>993</v>
+        <v>8000</v>
       </c>
       <c r="L56" s="121" t="n">
-        <v>2099027</v>
+        <v>14256013</v>
       </c>
       <c r="M56" s="115" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="116" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>LPO001</t>
         </is>
       </c>
       <c r="B57" s="116" t="inlineStr">
         <is>
-          <t>2026.02.04</t>
+          <t>2026.01.30</t>
         </is>
       </c>
       <c r="C57" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D57" s="118" t="n">
-        <v>4489</v>
+        <v>5056.8</v>
       </c>
       <c r="E57" s="118" t="n">
-        <v>11599.57</v>
+        <v>5056.8</v>
       </c>
       <c r="F57" s="122" t="n">
-        <v>0.386997</v>
+        <v>1</v>
       </c>
       <c r="G57" s="118" t="n">
-        <v>1453.6</v>
+        <v>1445.5</v>
       </c>
       <c r="H57" s="120" t="n">
-        <v>6525210</v>
+        <v>7309604</v>
       </c>
       <c r="I57" s="120" t="n">
-        <v>11251</v>
+        <v>28910</v>
       </c>
       <c r="J57" s="120" t="n">
-        <v>3870</v>
+        <v>10000</v>
       </c>
       <c r="K57" s="120" t="n">
-        <v>3096</v>
+        <v>8000</v>
       </c>
       <c r="L57" s="121" t="n">
-        <v>6543427</v>
+        <v>7356514</v>
       </c>
       <c r="M57" s="115" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="116" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>CPO682</t>
         </is>
       </c>
       <c r="B58" s="116" t="inlineStr">
@@ -18148,47 +18453,47 @@
       </c>
       <c r="C58" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D58" s="118" t="n">
-        <v>5670.57</v>
+        <v>20174</v>
       </c>
       <c r="E58" s="118" t="n">
-        <v>11599.57</v>
+        <v>24794</v>
       </c>
       <c r="F58" s="122" t="n">
-        <v>0.48886</v>
+        <v>0.813665</v>
       </c>
       <c r="G58" s="118" t="n">
-        <v>1453.6</v>
+        <v>1454.7</v>
       </c>
       <c r="H58" s="120" t="n">
-        <v>8242741</v>
+        <v>29347118</v>
       </c>
       <c r="I58" s="120" t="n">
-        <v>14212</v>
+        <v>23673</v>
       </c>
       <c r="J58" s="120" t="n">
-        <v>4889</v>
+        <v>10171</v>
       </c>
       <c r="K58" s="120" t="n">
-        <v>3911</v>
+        <v>6509</v>
       </c>
       <c r="L58" s="121" t="n">
-        <v>8265753</v>
+        <v>29387471</v>
       </c>
       <c r="M58" s="115" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="116" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>CPO683</t>
         </is>
       </c>
       <c r="B59" s="116" t="inlineStr">
         <is>
-          <t>2026.02.11</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C59" s="117" t="inlineStr">
@@ -18197,178 +18502,178 @@
         </is>
       </c>
       <c r="D59" s="118" t="n">
-        <v>26358</v>
+        <v>4620</v>
       </c>
       <c r="E59" s="118" t="n">
-        <v>26358</v>
+        <v>24794</v>
       </c>
       <c r="F59" s="122" t="n">
-        <v>1</v>
+        <v>0.186335</v>
       </c>
       <c r="G59" s="118" t="n">
-        <v>1460.7</v>
+        <v>1454.7</v>
       </c>
       <c r="H59" s="120" t="n">
-        <v>38501131</v>
+        <v>6720714</v>
       </c>
       <c r="I59" s="120" t="n">
-        <v>29214</v>
+        <v>5421</v>
       </c>
       <c r="J59" s="120" t="n">
-        <v>12500</v>
+        <v>2329</v>
       </c>
       <c r="K59" s="120" t="n">
-        <v>8000</v>
+        <v>1491</v>
       </c>
       <c r="L59" s="121" t="n">
-        <v>38550845</v>
+        <v>6729955</v>
       </c>
       <c r="M59" s="115" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="116" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="B60" s="116" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C60" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D60" s="118" t="n">
-        <v>14793</v>
+        <v>1440</v>
       </c>
       <c r="E60" s="118" t="n">
-        <v>17538</v>
+        <v>11599.57</v>
       </c>
       <c r="F60" s="122" t="n">
-        <v>0.843483</v>
+        <v>0.124143</v>
       </c>
       <c r="G60" s="118" t="n">
-        <v>1451.7</v>
+        <v>1453.6</v>
       </c>
       <c r="H60" s="120" t="n">
-        <v>21474998</v>
+        <v>2093184</v>
       </c>
       <c r="I60" s="120" t="n">
-        <v>24490</v>
+        <v>3609</v>
       </c>
       <c r="J60" s="120" t="n">
-        <v>8435</v>
+        <v>1241</v>
       </c>
       <c r="K60" s="120" t="n">
-        <v>6748</v>
+        <v>993</v>
       </c>
       <c r="L60" s="121" t="n">
-        <v>21514671</v>
+        <v>2099027</v>
       </c>
       <c r="M60" s="115" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="116" t="inlineStr">
         <is>
-          <t>CPO689</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="B61" s="116" t="inlineStr">
         <is>
-          <t>2026.02.19</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C61" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D61" s="118" t="n">
-        <v>2745</v>
+        <v>4489</v>
       </c>
       <c r="E61" s="118" t="n">
-        <v>17538</v>
+        <v>11599.57</v>
       </c>
       <c r="F61" s="122" t="n">
-        <v>0.156517</v>
+        <v>0.386997</v>
       </c>
       <c r="G61" s="118" t="n">
-        <v>1451.7</v>
+        <v>1453.6</v>
       </c>
       <c r="H61" s="120" t="n">
-        <v>3984917</v>
+        <v>6525210</v>
       </c>
       <c r="I61" s="120" t="n">
-        <v>4544</v>
+        <v>11251</v>
       </c>
       <c r="J61" s="120" t="n">
-        <v>1565</v>
+        <v>3870</v>
       </c>
       <c r="K61" s="120" t="n">
-        <v>1252</v>
+        <v>3096</v>
       </c>
       <c r="L61" s="121" t="n">
-        <v>3992278</v>
+        <v>6543427</v>
       </c>
       <c r="M61" s="115" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="116" t="inlineStr">
         <is>
-          <t>CPO667</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="B62" s="116" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.02.04</t>
         </is>
       </c>
       <c r="C62" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D62" s="118" t="n">
-        <v>5673</v>
+        <v>5670.57</v>
       </c>
       <c r="E62" s="118" t="n">
-        <v>142189</v>
+        <v>11599.57</v>
       </c>
       <c r="F62" s="122" t="n">
-        <v>0.039898</v>
+        <v>0.48886</v>
       </c>
       <c r="G62" s="118" t="n">
-        <v>1441.6</v>
+        <v>1453.6</v>
       </c>
       <c r="H62" s="120" t="n">
-        <v>8178197</v>
+        <v>8242741</v>
       </c>
       <c r="I62" s="120" t="n">
-        <v>1150</v>
+        <v>14212</v>
       </c>
       <c r="J62" s="120" t="n">
-        <v>499</v>
+        <v>4889</v>
       </c>
       <c r="K62" s="120" t="n">
-        <v>319</v>
+        <v>3911</v>
       </c>
       <c r="L62" s="121" t="n">
-        <v>8180165</v>
+        <v>8265753</v>
       </c>
       <c r="M62" s="115" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="116" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="B63" s="116" t="inlineStr">
         <is>
-          <t>2026.02.27</t>
+          <t>2026.02.11</t>
         </is>
       </c>
       <c r="C63" s="117" t="inlineStr">
@@ -18377,43 +18682,43 @@
         </is>
       </c>
       <c r="D63" s="118" t="n">
-        <v>136516</v>
+        <v>26358</v>
       </c>
       <c r="E63" s="118" t="n">
-        <v>142189</v>
+        <v>26358</v>
       </c>
       <c r="F63" s="122" t="n">
-        <v>0.960102</v>
+        <v>1</v>
       </c>
       <c r="G63" s="118" t="n">
-        <v>1441.6</v>
+        <v>1460.7</v>
       </c>
       <c r="H63" s="120" t="n">
-        <v>196801466</v>
+        <v>38501131</v>
       </c>
       <c r="I63" s="120" t="n">
-        <v>27682</v>
+        <v>29214</v>
       </c>
       <c r="J63" s="120" t="n">
-        <v>12001</v>
+        <v>12500</v>
       </c>
       <c r="K63" s="120" t="n">
-        <v>7681</v>
+        <v>8000</v>
       </c>
       <c r="L63" s="121" t="n">
-        <v>196848830</v>
+        <v>38550845</v>
       </c>
       <c r="M63" s="115" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="116" t="inlineStr">
         <is>
-          <t>CPO678-2</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="B64" s="116" t="inlineStr">
         <is>
-          <t>2026.03.06</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C64" s="117" t="inlineStr">
@@ -18422,43 +18727,43 @@
         </is>
       </c>
       <c r="D64" s="118" t="n">
-        <v>137850</v>
+        <v>14793</v>
       </c>
       <c r="E64" s="118" t="n">
-        <v>137850</v>
+        <v>17538</v>
       </c>
       <c r="F64" s="122" t="n">
-        <v>1</v>
+        <v>0.843483</v>
       </c>
       <c r="G64" s="118" t="n">
-        <v>1477.6</v>
+        <v>1451.7</v>
       </c>
       <c r="H64" s="120" t="n">
-        <v>203687160</v>
+        <v>21474998</v>
       </c>
       <c r="I64" s="120" t="n">
-        <v>29552</v>
+        <v>24490</v>
       </c>
       <c r="J64" s="120" t="n">
-        <v>12500</v>
+        <v>8435</v>
       </c>
       <c r="K64" s="120" t="n">
-        <v>8000</v>
+        <v>6748</v>
       </c>
       <c r="L64" s="121" t="n">
-        <v>203737212</v>
+        <v>21514671</v>
       </c>
       <c r="M64" s="115" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="116" t="inlineStr">
         <is>
-          <t>CPO690</t>
+          <t>CPO689</t>
         </is>
       </c>
       <c r="B65" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.02.19</t>
         </is>
       </c>
       <c r="C65" s="117" t="inlineStr">
@@ -18467,43 +18772,43 @@
         </is>
       </c>
       <c r="D65" s="118" t="n">
-        <v>9740</v>
+        <v>2745</v>
       </c>
       <c r="E65" s="118" t="n">
-        <v>34354</v>
+        <v>17538</v>
       </c>
       <c r="F65" s="122" t="n">
-        <v>0.283519</v>
+        <v>0.156517</v>
       </c>
       <c r="G65" s="118" t="n">
-        <v>1505.7</v>
+        <v>1451.7</v>
       </c>
       <c r="H65" s="120" t="n">
-        <v>14665518</v>
+        <v>3984917</v>
       </c>
       <c r="I65" s="120" t="n">
-        <v>8538</v>
+        <v>4544</v>
       </c>
       <c r="J65" s="120" t="n">
-        <v>3544</v>
+        <v>1565</v>
       </c>
       <c r="K65" s="120" t="n">
-        <v>2268</v>
+        <v>1252</v>
       </c>
       <c r="L65" s="121" t="n">
-        <v>14679868</v>
+        <v>3992278</v>
       </c>
       <c r="M65" s="115" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="116" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="B66" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C66" s="117" t="inlineStr">
@@ -18512,128 +18817,128 @@
         </is>
       </c>
       <c r="D66" s="118" t="n">
-        <v>24614</v>
+        <v>5673</v>
       </c>
       <c r="E66" s="118" t="n">
-        <v>34354</v>
+        <v>142189</v>
       </c>
       <c r="F66" s="122" t="n">
-        <v>0.716481</v>
+        <v>0.039898</v>
       </c>
       <c r="G66" s="118" t="n">
-        <v>1505.7</v>
+        <v>1441.6</v>
       </c>
       <c r="H66" s="120" t="n">
-        <v>37061300</v>
+        <v>8178197</v>
       </c>
       <c r="I66" s="120" t="n">
-        <v>21576</v>
+        <v>1150</v>
       </c>
       <c r="J66" s="120" t="n">
-        <v>8956</v>
+        <v>499</v>
       </c>
       <c r="K66" s="120" t="n">
-        <v>5732</v>
+        <v>319</v>
       </c>
       <c r="L66" s="121" t="n">
-        <v>37097564</v>
+        <v>8180165</v>
       </c>
       <c r="M66" s="115" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="116" t="inlineStr">
         <is>
-          <t>GPO467</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="B67" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.02.27</t>
         </is>
       </c>
       <c r="C67" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D67" s="118" t="n">
-        <v>1700</v>
+        <v>136516</v>
       </c>
       <c r="E67" s="118" t="n">
-        <v>6553.05</v>
+        <v>142189</v>
       </c>
       <c r="F67" s="122" t="n">
-        <v>0.259421</v>
+        <v>0.960102</v>
       </c>
       <c r="G67" s="118" t="n">
-        <v>1506.4</v>
+        <v>1441.6</v>
       </c>
       <c r="H67" s="120" t="n">
-        <v>2560880</v>
+        <v>196801466</v>
       </c>
       <c r="I67" s="120" t="n">
-        <v>7816</v>
+        <v>27682</v>
       </c>
       <c r="J67" s="120" t="n">
-        <v>2594</v>
+        <v>12001</v>
       </c>
       <c r="K67" s="120" t="n">
-        <v>2075</v>
+        <v>7681</v>
       </c>
       <c r="L67" s="121" t="n">
-        <v>2573365</v>
+        <v>196848830</v>
       </c>
       <c r="M67" s="115" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="116" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>CPO678-2</t>
         </is>
       </c>
       <c r="B68" s="116" t="inlineStr">
         <is>
-          <t>2026.04.01</t>
+          <t>2026.03.06</t>
         </is>
       </c>
       <c r="C68" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D68" s="118" t="n">
-        <v>3993.05</v>
+        <v>137850</v>
       </c>
       <c r="E68" s="118" t="n">
-        <v>6553.05</v>
+        <v>137850</v>
       </c>
       <c r="F68" s="122" t="n">
-        <v>0.6093420000000001</v>
+        <v>1</v>
       </c>
       <c r="G68" s="118" t="n">
-        <v>1506.4</v>
+        <v>1477.6</v>
       </c>
       <c r="H68" s="120" t="n">
-        <v>6015131</v>
+        <v>203687160</v>
       </c>
       <c r="I68" s="120" t="n">
-        <v>18358</v>
+        <v>29552</v>
       </c>
       <c r="J68" s="120" t="n">
-        <v>6093</v>
+        <v>12500</v>
       </c>
       <c r="K68" s="120" t="n">
-        <v>4875</v>
+        <v>8000</v>
       </c>
       <c r="L68" s="121" t="n">
-        <v>6044457</v>
+        <v>203737212</v>
       </c>
       <c r="M68" s="115" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="116" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>CPO690</t>
         </is>
       </c>
       <c r="B69" s="116" t="inlineStr">
@@ -18643,42 +18948,42 @@
       </c>
       <c r="C69" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D69" s="118" t="n">
-        <v>360</v>
+        <v>9740</v>
       </c>
       <c r="E69" s="118" t="n">
-        <v>6553.05</v>
+        <v>34354</v>
       </c>
       <c r="F69" s="122" t="n">
-        <v>0.054936</v>
+        <v>0.283519</v>
       </c>
       <c r="G69" s="118" t="n">
-        <v>1506.4</v>
+        <v>1505.7</v>
       </c>
       <c r="H69" s="120" t="n">
-        <v>542304</v>
+        <v>14665518</v>
       </c>
       <c r="I69" s="120" t="n">
-        <v>1655</v>
+        <v>8538</v>
       </c>
       <c r="J69" s="120" t="n">
-        <v>549</v>
+        <v>3544</v>
       </c>
       <c r="K69" s="120" t="n">
-        <v>439</v>
+        <v>2268</v>
       </c>
       <c r="L69" s="121" t="n">
-        <v>544947</v>
+        <v>14679868</v>
       </c>
       <c r="M69" s="115" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="116" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="B70" s="116" t="inlineStr">
@@ -18688,47 +18993,47 @@
       </c>
       <c r="C70" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D70" s="118" t="n">
-        <v>500</v>
+        <v>24614</v>
       </c>
       <c r="E70" s="118" t="n">
-        <v>6553.05</v>
+        <v>34354</v>
       </c>
       <c r="F70" s="122" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.716481</v>
       </c>
       <c r="G70" s="118" t="n">
-        <v>1506.4</v>
+        <v>1505.7</v>
       </c>
       <c r="H70" s="120" t="n">
-        <v>753200</v>
+        <v>37061300</v>
       </c>
       <c r="I70" s="120" t="n">
-        <v>2299</v>
+        <v>21576</v>
       </c>
       <c r="J70" s="120" t="n">
-        <v>763</v>
+        <v>8956</v>
       </c>
       <c r="K70" s="120" t="n">
-        <v>610</v>
+        <v>5732</v>
       </c>
       <c r="L70" s="121" t="n">
-        <v>756872</v>
+        <v>37097564</v>
       </c>
       <c r="M70" s="115" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="116" t="inlineStr">
         <is>
-          <t>GPO468-1</t>
+          <t>GPO467</t>
         </is>
       </c>
       <c r="B71" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C71" s="117" t="inlineStr">
@@ -18737,43 +19042,43 @@
         </is>
       </c>
       <c r="D71" s="118" t="n">
-        <v>36190</v>
+        <v>1700</v>
       </c>
       <c r="E71" s="118" t="n">
-        <v>57650</v>
+        <v>6553.05</v>
       </c>
       <c r="F71" s="122" t="n">
-        <v>0.627754</v>
+        <v>0.259421</v>
       </c>
       <c r="G71" s="118" t="n">
-        <v>1481.9</v>
+        <v>1506.4</v>
       </c>
       <c r="H71" s="120" t="n">
-        <v>53629961</v>
+        <v>2560880</v>
       </c>
       <c r="I71" s="120" t="n">
-        <v>18605</v>
+        <v>7816</v>
       </c>
       <c r="J71" s="120" t="n">
-        <v>7847</v>
+        <v>2594</v>
       </c>
       <c r="K71" s="120" t="n">
-        <v>5022</v>
+        <v>2075</v>
       </c>
       <c r="L71" s="121" t="n">
-        <v>53661435</v>
+        <v>2573365</v>
       </c>
       <c r="M71" s="115" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="116" t="inlineStr">
         <is>
-          <t>GPO472</t>
+          <t>GPO469</t>
         </is>
       </c>
       <c r="B72" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C72" s="117" t="inlineStr">
@@ -18782,43 +19087,43 @@
         </is>
       </c>
       <c r="D72" s="118" t="n">
-        <v>180</v>
+        <v>3993.05</v>
       </c>
       <c r="E72" s="118" t="n">
-        <v>57650</v>
+        <v>6553.05</v>
       </c>
       <c r="F72" s="122" t="n">
-        <v>0.003122</v>
+        <v>0.6093420000000001</v>
       </c>
       <c r="G72" s="118" t="n">
-        <v>1481.9</v>
+        <v>1506.4</v>
       </c>
       <c r="H72" s="120" t="n">
-        <v>266742</v>
+        <v>6015131</v>
       </c>
       <c r="I72" s="120" t="n">
-        <v>93</v>
+        <v>18358</v>
       </c>
       <c r="J72" s="120" t="n">
-        <v>39</v>
+        <v>6093</v>
       </c>
       <c r="K72" s="120" t="n">
-        <v>25</v>
+        <v>4875</v>
       </c>
       <c r="L72" s="121" t="n">
-        <v>266899</v>
+        <v>6044457</v>
       </c>
       <c r="M72" s="115" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="116" t="inlineStr">
         <is>
-          <t>GPO468-2</t>
+          <t>GPO470</t>
         </is>
       </c>
       <c r="B73" s="116" t="inlineStr">
         <is>
-          <t>2026.04.14</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C73" s="117" t="inlineStr">
@@ -18827,221 +19132,223 @@
         </is>
       </c>
       <c r="D73" s="118" t="n">
-        <v>21280</v>
+        <v>360</v>
       </c>
       <c r="E73" s="118" t="n">
-        <v>57650</v>
+        <v>6553.05</v>
       </c>
       <c r="F73" s="122" t="n">
-        <v>0.369124</v>
+        <v>0.054936</v>
       </c>
       <c r="G73" s="118" t="n">
-        <v>1481.9</v>
+        <v>1506.4</v>
       </c>
       <c r="H73" s="120" t="n">
-        <v>31534832</v>
+        <v>542304</v>
       </c>
       <c r="I73" s="120" t="n">
-        <v>10940</v>
+        <v>1655</v>
       </c>
       <c r="J73" s="120" t="n">
-        <v>4614</v>
+        <v>549</v>
       </c>
       <c r="K73" s="120" t="n">
-        <v>2953</v>
+        <v>439</v>
       </c>
       <c r="L73" s="121" t="n">
-        <v>31553339</v>
+        <v>544947</v>
       </c>
       <c r="M73" s="115" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="116" t="inlineStr">
         <is>
-          <t>CPO692-1</t>
+          <t>GPO471</t>
         </is>
       </c>
       <c r="B74" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.04.01</t>
         </is>
       </c>
       <c r="C74" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D74" s="118" t="n">
-        <v>11000</v>
+        <v>500</v>
       </c>
       <c r="E74" s="118" t="n">
-        <v>297580</v>
+        <v>6553.05</v>
       </c>
       <c r="F74" s="122" t="n">
-        <v>0.036965</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G74" s="118" t="n">
-        <v>1482.8</v>
+        <v>1506.4</v>
       </c>
       <c r="H74" s="120" t="n">
-        <v>16310800</v>
+        <v>753200</v>
       </c>
       <c r="I74" s="120" t="n">
-        <v>1096</v>
+        <v>2299</v>
       </c>
       <c r="J74" s="120" t="n">
-        <v>462</v>
+        <v>763</v>
       </c>
       <c r="K74" s="120" t="n">
-        <v>296</v>
+        <v>610</v>
       </c>
       <c r="L74" s="121" t="n">
-        <v>16312654</v>
+        <v>756872</v>
       </c>
       <c r="M74" s="115" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="116" t="inlineStr">
         <is>
-          <t>CPO692-2</t>
+          <t>GPO468-1</t>
         </is>
       </c>
       <c r="B75" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C75" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D75" s="118" t="n">
-        <v>286580</v>
+        <v>36190</v>
       </c>
       <c r="E75" s="118" t="n">
-        <v>297580</v>
+        <v>57650</v>
       </c>
       <c r="F75" s="122" t="n">
-        <v>0.963035</v>
+        <v>0.627754</v>
       </c>
       <c r="G75" s="118" t="n">
-        <v>1482.8</v>
+        <v>1481.9</v>
       </c>
       <c r="H75" s="120" t="n">
-        <v>424940824</v>
+        <v>53629961</v>
       </c>
       <c r="I75" s="120" t="n">
-        <v>28560</v>
+        <v>18605</v>
       </c>
       <c r="J75" s="120" t="n">
-        <v>12038</v>
+        <v>7847</v>
       </c>
       <c r="K75" s="120" t="n">
-        <v>7704</v>
+        <v>5022</v>
       </c>
       <c r="L75" s="121" t="n">
-        <v>424989126</v>
+        <v>53661435</v>
       </c>
       <c r="M75" s="115" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="116" t="inlineStr">
         <is>
-          <t>EPO18</t>
+          <t>GPO472</t>
         </is>
       </c>
       <c r="B76" s="116" t="inlineStr">
         <is>
-          <t>2026.04.22</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C76" s="117" t="inlineStr">
         <is>
-          <t>MAICO Italia</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D76" s="118" t="n">
-        <v>4388.4</v>
+        <v>180</v>
       </c>
       <c r="E76" s="118" t="n">
-        <v>4388.4</v>
+        <v>57650</v>
       </c>
       <c r="F76" s="122" t="n">
-        <v>1</v>
+        <v>0.003122</v>
       </c>
       <c r="G76" s="118" t="n">
-        <v>1741.08</v>
+        <v>1481.9</v>
       </c>
       <c r="H76" s="120" t="n">
-        <v>7640555</v>
+        <v>266742</v>
       </c>
       <c r="I76" s="120" t="n">
-        <v>43527</v>
+        <v>93</v>
       </c>
       <c r="J76" s="120" t="n">
-        <v>10000</v>
+        <v>39</v>
       </c>
       <c r="K76" s="120" t="n">
-        <v>8000</v>
+        <v>25</v>
       </c>
       <c r="L76" s="121" t="n">
-        <v>7702082</v>
-      </c>
+        <v>266899</v>
+      </c>
+      <c r="M76" s="115" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="116" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>GPO468-2</t>
         </is>
       </c>
       <c r="B77" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.14</t>
         </is>
       </c>
       <c r="C77" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D77" s="118" t="n">
-        <v>17404</v>
+        <v>21280</v>
       </c>
       <c r="E77" s="118" t="n">
-        <v>21439</v>
+        <v>57650</v>
       </c>
       <c r="F77" s="122" t="n">
-        <v>0.811792</v>
+        <v>0.369124</v>
       </c>
       <c r="G77" s="118" t="n">
-        <v>1474.9</v>
+        <v>1481.9</v>
       </c>
       <c r="H77" s="120" t="n">
-        <v>25669160</v>
+        <v>31534832</v>
       </c>
       <c r="I77" s="120" t="n">
-        <v>23946</v>
+        <v>10940</v>
       </c>
       <c r="J77" s="120" t="n">
-        <v>10147</v>
+        <v>4614</v>
       </c>
       <c r="K77" s="120" t="n">
-        <v>6494</v>
+        <v>2953</v>
       </c>
       <c r="L77" s="121" t="n">
-        <v>25709747</v>
-      </c>
+        <v>31553339</v>
+      </c>
+      <c r="M77" s="115" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="116" t="inlineStr">
         <is>
-          <t>CPO695-1</t>
+          <t>CPO692-1</t>
         </is>
       </c>
       <c r="B78" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C78" s="117" t="inlineStr">
@@ -19050,42 +19357,43 @@
         </is>
       </c>
       <c r="D78" s="118" t="n">
-        <v>2058</v>
+        <v>11000</v>
       </c>
       <c r="E78" s="118" t="n">
-        <v>21439</v>
+        <v>297580</v>
       </c>
       <c r="F78" s="122" t="n">
-        <v>0.09599299999999999</v>
+        <v>0.036965</v>
       </c>
       <c r="G78" s="118" t="n">
-        <v>1474.9</v>
+        <v>1482.8</v>
       </c>
       <c r="H78" s="120" t="n">
-        <v>3035344</v>
+        <v>16310800</v>
       </c>
       <c r="I78" s="120" t="n">
-        <v>2832</v>
+        <v>1096</v>
       </c>
       <c r="J78" s="120" t="n">
-        <v>1200</v>
+        <v>462</v>
       </c>
       <c r="K78" s="120" t="n">
-        <v>768</v>
+        <v>296</v>
       </c>
       <c r="L78" s="121" t="n">
-        <v>3040144</v>
-      </c>
+        <v>16312654</v>
+      </c>
+      <c r="M78" s="115" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="116" t="inlineStr">
         <is>
-          <t>CPO695-2</t>
+          <t>CPO692-2</t>
         </is>
       </c>
       <c r="B79" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C79" s="117" t="inlineStr">
@@ -19094,66 +19402,67 @@
         </is>
       </c>
       <c r="D79" s="118" t="n">
-        <v>1977</v>
+        <v>286580</v>
       </c>
       <c r="E79" s="118" t="n">
-        <v>21439</v>
+        <v>297580</v>
       </c>
       <c r="F79" s="122" t="n">
-        <v>0.09221500000000001</v>
+        <v>0.963035</v>
       </c>
       <c r="G79" s="118" t="n">
-        <v>1474.9</v>
+        <v>1482.8</v>
       </c>
       <c r="H79" s="120" t="n">
-        <v>2915877</v>
+        <v>424940824</v>
       </c>
       <c r="I79" s="120" t="n">
-        <v>2720</v>
+        <v>28560</v>
       </c>
       <c r="J79" s="120" t="n">
-        <v>1153</v>
+        <v>12038</v>
       </c>
       <c r="K79" s="120" t="n">
-        <v>738</v>
+        <v>7704</v>
       </c>
       <c r="L79" s="121" t="n">
-        <v>2920488</v>
-      </c>
+        <v>424989126</v>
+      </c>
+      <c r="M79" s="115" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="116" t="inlineStr">
         <is>
-          <t>IPO016</t>
+          <t>EPO18</t>
         </is>
       </c>
       <c r="B80" s="116" t="inlineStr">
         <is>
-          <t>2026.05.04</t>
+          <t>2026.04.22</t>
         </is>
       </c>
       <c r="C80" s="117" t="inlineStr">
         <is>
-          <t>Integ</t>
+          <t>MAICO Italia</t>
         </is>
       </c>
       <c r="D80" s="118" t="n">
-        <v>6800</v>
+        <v>4388.4</v>
       </c>
       <c r="E80" s="118" t="n">
-        <v>6800</v>
+        <v>4388.4</v>
       </c>
       <c r="F80" s="122" t="n">
         <v>1</v>
       </c>
       <c r="G80" s="118" t="n">
-        <v>1475.2</v>
+        <v>1741.08</v>
       </c>
       <c r="H80" s="120" t="n">
-        <v>10031360</v>
+        <v>7640555</v>
       </c>
       <c r="I80" s="120" t="n">
-        <v>29504</v>
+        <v>43527</v>
       </c>
       <c r="J80" s="120" t="n">
         <v>10000</v>
@@ -19162,62 +19471,62 @@
         <v>8000</v>
       </c>
       <c r="L80" s="121" t="n">
-        <v>10078864</v>
+        <v>7702082</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="116" t="inlineStr">
         <is>
-          <t>GPO478</t>
+          <t>CPO694</t>
         </is>
       </c>
       <c r="B81" s="116" t="inlineStr">
         <is>
-          <t>2026.05.19</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C81" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D81" s="118" t="n">
-        <v>180</v>
+        <v>17404</v>
       </c>
       <c r="E81" s="118" t="n">
-        <v>180</v>
+        <v>21439</v>
       </c>
       <c r="F81" s="122" t="n">
-        <v>1</v>
+        <v>0.811792</v>
       </c>
       <c r="G81" s="118" t="n">
-        <v>1518.9</v>
+        <v>1474.9</v>
       </c>
       <c r="H81" s="120" t="n">
-        <v>273402</v>
+        <v>25669160</v>
       </c>
       <c r="I81" s="120" t="n">
-        <v>30378</v>
+        <v>23946</v>
       </c>
       <c r="J81" s="120" t="n">
-        <v>2500</v>
+        <v>10147</v>
       </c>
       <c r="K81" s="120" t="n">
-        <v>8000</v>
+        <v>6494</v>
       </c>
       <c r="L81" s="121" t="n">
-        <v>314280</v>
+        <v>25709747</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="116" t="inlineStr">
         <is>
-          <t>CPO698</t>
+          <t>CPO695-1</t>
         </is>
       </c>
       <c r="B82" s="116" t="inlineStr">
         <is>
-          <t>2026.05.20</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C82" s="117" t="inlineStr">
@@ -19226,623 +19535,617 @@
         </is>
       </c>
       <c r="D82" s="118" t="n">
-        <v>4290</v>
+        <v>2058</v>
       </c>
       <c r="E82" s="118" t="n">
-        <v>4290</v>
+        <v>21439</v>
       </c>
       <c r="F82" s="122" t="n">
-        <v>1</v>
+        <v>0.09599299999999999</v>
       </c>
       <c r="G82" s="118" t="n">
-        <v>1510.6</v>
+        <v>1474.9</v>
       </c>
       <c r="H82" s="120" t="n">
-        <v>6480474</v>
+        <v>3035344</v>
       </c>
       <c r="I82" s="120" t="n">
-        <v>30212</v>
+        <v>2832</v>
       </c>
       <c r="J82" s="120" t="n">
-        <v>7500</v>
+        <v>1200</v>
       </c>
       <c r="K82" s="120" t="n">
-        <v>8000</v>
+        <v>768</v>
       </c>
       <c r="L82" s="121" t="n">
-        <v>6526186</v>
-      </c>
-      <c r="M82" s="40" t="n"/>
+        <v>3040144</v>
+      </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="116" t="inlineStr">
         <is>
-          <t>GPO473-1</t>
+          <t>CPO695-2</t>
         </is>
       </c>
       <c r="B83" s="116" t="inlineStr">
         <is>
-          <t>2026.05.29</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C83" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D83" s="118" t="n">
-        <v>98800</v>
+        <v>1977</v>
       </c>
       <c r="E83" s="118" t="n">
-        <v>99140</v>
+        <v>21439</v>
       </c>
       <c r="F83" s="122" t="n">
-        <v>0.996571</v>
+        <v>0.09221500000000001</v>
       </c>
       <c r="G83" s="118" t="n">
-        <v>1502.8</v>
+        <v>1474.9</v>
       </c>
       <c r="H83" s="120" t="n">
-        <v>148476640</v>
+        <v>2915877</v>
       </c>
       <c r="I83" s="120" t="n">
-        <v>29953</v>
+        <v>2720</v>
       </c>
       <c r="J83" s="120" t="n">
-        <v>12457</v>
+        <v>1153</v>
       </c>
       <c r="K83" s="120" t="n">
-        <v>7973</v>
+        <v>738</v>
       </c>
       <c r="L83" s="121" t="n">
-        <v>148527023</v>
+        <v>2920488</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="116" t="inlineStr">
         <is>
-          <t>GPO480</t>
+          <t>IPO016</t>
         </is>
       </c>
       <c r="B84" s="116" t="inlineStr">
         <is>
-          <t>2026.05.29</t>
+          <t>2026.05.04</t>
         </is>
       </c>
       <c r="C84" s="117" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Integ</t>
         </is>
       </c>
       <c r="D84" s="118" t="n">
-        <v>250</v>
+        <v>6800</v>
       </c>
       <c r="E84" s="118" t="n">
-        <v>99140</v>
+        <v>6800</v>
       </c>
       <c r="F84" s="122" t="n">
-        <v>0.002522</v>
+        <v>1</v>
       </c>
       <c r="G84" s="118" t="n">
-        <v>1502.8</v>
+        <v>1475.2</v>
       </c>
       <c r="H84" s="120" t="n">
-        <v>375700</v>
+        <v>10031360</v>
       </c>
       <c r="I84" s="120" t="n">
-        <v>76</v>
+        <v>29504</v>
       </c>
       <c r="J84" s="120" t="n">
-        <v>32</v>
+        <v>10000</v>
       </c>
       <c r="K84" s="120" t="n">
-        <v>20</v>
+        <v>8000</v>
       </c>
       <c r="L84" s="121" t="n">
-        <v>375828</v>
+        <v>10078864</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="116" t="inlineStr">
-        <is>
-          <t>GPO479</t>
-        </is>
-      </c>
-      <c r="B85" s="116" t="inlineStr">
-        <is>
-          <t>2026.05.29</t>
-        </is>
-      </c>
-      <c r="C85" s="117" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D85" s="118" t="n">
-        <v>90</v>
-      </c>
-      <c r="E85" s="118" t="n">
-        <v>99140</v>
-      </c>
-      <c r="F85" s="122" t="n">
-        <v>0.000908</v>
-      </c>
-      <c r="G85" s="118" t="n">
-        <v>1502.8</v>
-      </c>
-      <c r="H85" s="120" t="n">
-        <v>135252</v>
-      </c>
-      <c r="I85" s="120" t="n">
-        <v>27</v>
-      </c>
-      <c r="J85" s="120" t="n">
-        <v>11</v>
-      </c>
-      <c r="K85" s="120" t="n">
-        <v>7</v>
-      </c>
-      <c r="L85" s="121" t="n">
-        <v>135297</v>
+      <c r="A85" s="234" t="inlineStr">
+        <is>
+          <t>PI44133-1</t>
+        </is>
+      </c>
+      <c r="B85" s="234" t="inlineStr">
+        <is>
+          <t>2026.05.12</t>
+        </is>
+      </c>
+      <c r="C85" s="235" t="inlineStr">
+        <is>
+          <t>Ferco (Figueras)</t>
+        </is>
+      </c>
+      <c r="D85" s="236" t="n">
+        <v>4416</v>
+      </c>
+      <c r="E85" s="236" t="n">
+        <v>4416</v>
+      </c>
+      <c r="F85" s="240">
+        <f>IFERROR(D85/E85,0)</f>
+        <v/>
+      </c>
+      <c r="G85" s="236" t="n">
+        <v>1755.24</v>
+      </c>
+      <c r="H85" s="238" t="n">
+        <v>7751140</v>
+      </c>
+      <c r="I85" s="238" t="n">
+        <v>43881</v>
+      </c>
+      <c r="J85" s="238" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K85" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L85" s="239">
+        <f>H85+I85+J85+K85</f>
+        <v/>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="116" t="inlineStr">
         <is>
-          <t>CPO697</t>
+          <t>GPO478</t>
         </is>
       </c>
       <c r="B86" s="116" t="inlineStr">
         <is>
-          <t>2026.05.29</t>
+          <t>2026.05.19</t>
         </is>
       </c>
       <c r="C86" s="117" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D86" s="118" t="n">
-        <v>15289</v>
+        <v>180</v>
       </c>
       <c r="E86" s="118" t="n">
-        <v>101638</v>
+        <v>180</v>
       </c>
       <c r="F86" s="122" t="n">
-        <v>0.150426</v>
+        <v>1</v>
       </c>
       <c r="G86" s="118" t="n">
-        <v>1502.7</v>
+        <v>1518.9</v>
       </c>
       <c r="H86" s="120" t="n">
-        <v>22974780</v>
+        <v>273402</v>
       </c>
       <c r="I86" s="120" t="n">
-        <v>4521</v>
+        <v>30378</v>
       </c>
       <c r="J86" s="120" t="n">
-        <v>1880</v>
+        <v>2500</v>
       </c>
       <c r="K86" s="120" t="n">
-        <v>1203</v>
+        <v>8000</v>
       </c>
       <c r="L86" s="121" t="n">
-        <v>22982384</v>
+        <v>314280</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="116" t="inlineStr">
         <is>
+          <t>CPO698</t>
+        </is>
+      </c>
+      <c r="B87" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.20</t>
+        </is>
+      </c>
+      <c r="C87" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D87" s="118" t="n">
+        <v>4290</v>
+      </c>
+      <c r="E87" s="118" t="n">
+        <v>4290</v>
+      </c>
+      <c r="F87" s="122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="118" t="n">
+        <v>1510.6</v>
+      </c>
+      <c r="H87" s="120" t="n">
+        <v>6480474</v>
+      </c>
+      <c r="I87" s="120" t="n">
+        <v>30212</v>
+      </c>
+      <c r="J87" s="120" t="n">
+        <v>7500</v>
+      </c>
+      <c r="K87" s="120" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L87" s="121" t="n">
+        <v>6526186</v>
+      </c>
+      <c r="M87" s="40" t="n"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="116" t="inlineStr">
+        <is>
+          <t>GPO473-1</t>
+        </is>
+      </c>
+      <c r="B88" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C88" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D88" s="118" t="n">
+        <v>98800</v>
+      </c>
+      <c r="E88" s="118" t="n">
+        <v>99140</v>
+      </c>
+      <c r="F88" s="122" t="n">
+        <v>0.996571</v>
+      </c>
+      <c r="G88" s="118" t="n">
+        <v>1502.8</v>
+      </c>
+      <c r="H88" s="120" t="n">
+        <v>148476640</v>
+      </c>
+      <c r="I88" s="120" t="n">
+        <v>29953</v>
+      </c>
+      <c r="J88" s="120" t="n">
+        <v>12457</v>
+      </c>
+      <c r="K88" s="120" t="n">
+        <v>7973</v>
+      </c>
+      <c r="L88" s="121" t="n">
+        <v>148527023</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="116" t="inlineStr">
+        <is>
+          <t>GPO480</t>
+        </is>
+      </c>
+      <c r="B89" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C89" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D89" s="118" t="n">
+        <v>250</v>
+      </c>
+      <c r="E89" s="118" t="n">
+        <v>99140</v>
+      </c>
+      <c r="F89" s="122" t="n">
+        <v>0.002522</v>
+      </c>
+      <c r="G89" s="118" t="n">
+        <v>1502.8</v>
+      </c>
+      <c r="H89" s="120" t="n">
+        <v>375700</v>
+      </c>
+      <c r="I89" s="120" t="n">
+        <v>76</v>
+      </c>
+      <c r="J89" s="120" t="n">
+        <v>32</v>
+      </c>
+      <c r="K89" s="120" t="n">
+        <v>20</v>
+      </c>
+      <c r="L89" s="121" t="n">
+        <v>375828</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="116" t="inlineStr">
+        <is>
+          <t>GPO479</t>
+        </is>
+      </c>
+      <c r="B90" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C90" s="117" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D90" s="118" t="n">
+        <v>90</v>
+      </c>
+      <c r="E90" s="118" t="n">
+        <v>99140</v>
+      </c>
+      <c r="F90" s="122" t="n">
+        <v>0.000908</v>
+      </c>
+      <c r="G90" s="118" t="n">
+        <v>1502.8</v>
+      </c>
+      <c r="H90" s="120" t="n">
+        <v>135252</v>
+      </c>
+      <c r="I90" s="120" t="n">
+        <v>27</v>
+      </c>
+      <c r="J90" s="120" t="n">
+        <v>11</v>
+      </c>
+      <c r="K90" s="120" t="n">
+        <v>7</v>
+      </c>
+      <c r="L90" s="121" t="n">
+        <v>135297</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="116" t="inlineStr">
+        <is>
+          <t>CPO697</t>
+        </is>
+      </c>
+      <c r="B91" s="116" t="inlineStr">
+        <is>
+          <t>2026.05.29</t>
+        </is>
+      </c>
+      <c r="C91" s="117" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D91" s="118" t="n">
+        <v>15289</v>
+      </c>
+      <c r="E91" s="118" t="n">
+        <v>101638</v>
+      </c>
+      <c r="F91" s="122" t="n">
+        <v>0.150426</v>
+      </c>
+      <c r="G91" s="118" t="n">
+        <v>1502.7</v>
+      </c>
+      <c r="H91" s="120" t="n">
+        <v>22974780</v>
+      </c>
+      <c r="I91" s="120" t="n">
+        <v>4521</v>
+      </c>
+      <c r="J91" s="120" t="n">
+        <v>1880</v>
+      </c>
+      <c r="K91" s="120" t="n">
+        <v>1203</v>
+      </c>
+      <c r="L91" s="121" t="n">
+        <v>22982384</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="116" t="inlineStr">
+        <is>
           <t>CPO696-1</t>
         </is>
       </c>
-      <c r="B87" s="116" t="inlineStr">
+      <c r="B92" s="116" t="inlineStr">
         <is>
           <t>2026.05.29</t>
         </is>
       </c>
-      <c r="C87" s="117" t="inlineStr">
+      <c r="C92" s="117" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D87" s="118" t="n">
+      <c r="D92" s="118" t="n">
         <v>78209</v>
       </c>
-      <c r="E87" s="118" t="n">
+      <c r="E92" s="118" t="n">
         <v>101638</v>
       </c>
-      <c r="F87" s="122" t="n">
+      <c r="F92" s="122" t="n">
         <v>0.769486</v>
       </c>
-      <c r="G87" s="118" t="n">
+      <c r="G92" s="118" t="n">
         <v>1502.7</v>
       </c>
-      <c r="H87" s="120" t="n">
+      <c r="H92" s="120" t="n">
         <v>117524664</v>
       </c>
-      <c r="I87" s="120" t="n">
+      <c r="I92" s="120" t="n">
         <v>23126</v>
       </c>
-      <c r="J87" s="120" t="n">
+      <c r="J92" s="120" t="n">
         <v>9619</v>
       </c>
-      <c r="K87" s="120" t="n">
+      <c r="K92" s="120" t="n">
         <v>6156</v>
       </c>
-      <c r="L87" s="121" t="n">
+      <c r="L92" s="121" t="n">
         <v>117563565</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="116" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="116" t="inlineStr">
         <is>
           <t>CPO696-2</t>
         </is>
       </c>
-      <c r="B88" s="116" t="inlineStr">
+      <c r="B93" s="116" t="inlineStr">
         <is>
           <t>2026.05.29</t>
         </is>
       </c>
-      <c r="C88" s="117" t="inlineStr">
+      <c r="C93" s="117" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D88" s="118" t="n">
+      <c r="D93" s="118" t="n">
         <v>8140</v>
       </c>
-      <c r="E88" s="118" t="n">
+      <c r="E93" s="118" t="n">
         <v>101638</v>
       </c>
-      <c r="F88" s="122" t="n">
+      <c r="F93" s="122" t="n">
         <v>0.08008800000000001</v>
       </c>
-      <c r="G88" s="118" t="n">
+      <c r="G93" s="118" t="n">
         <v>1502.7</v>
       </c>
-      <c r="H88" s="120" t="n">
+      <c r="H93" s="120" t="n">
         <v>12231978</v>
       </c>
-      <c r="I88" s="120" t="n">
+      <c r="I93" s="120" t="n">
         <v>2407</v>
       </c>
-      <c r="J88" s="120" t="n">
+      <c r="J93" s="120" t="n">
         <v>1001</v>
       </c>
-      <c r="K88" s="120" t="n">
+      <c r="K93" s="120" t="n">
         <v>641</v>
       </c>
-      <c r="L88" s="121" t="n">
+      <c r="L93" s="121" t="n">
         <v>12236027</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="234" t="inlineStr">
-        <is>
-          <t>GPO481</t>
-        </is>
-      </c>
-      <c r="B89" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.10</t>
-        </is>
-      </c>
-      <c r="C89" s="235" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D89" s="236" t="n">
-        <v>500</v>
-      </c>
-      <c r="E89" s="236" t="n">
-        <v>119060</v>
-      </c>
-      <c r="F89" s="240" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="G89" s="236" t="n">
-        <v>1525.3</v>
-      </c>
-      <c r="H89" s="238" t="n">
-        <v>762650</v>
-      </c>
-      <c r="I89" s="238" t="n">
-        <v>128</v>
-      </c>
-      <c r="J89" s="238" t="n">
-        <v>52</v>
-      </c>
-      <c r="K89" s="238" t="n">
-        <v>34</v>
-      </c>
-      <c r="L89" s="239" t="n">
-        <v>762864</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="234" t="inlineStr">
-        <is>
-          <t>GPO473-2</t>
-        </is>
-      </c>
-      <c r="B90" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.10</t>
-        </is>
-      </c>
-      <c r="C90" s="235" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D90" s="236" t="n">
-        <v>69160</v>
-      </c>
-      <c r="E90" s="236" t="n">
-        <v>119060</v>
-      </c>
-      <c r="F90" s="240" t="n">
-        <v>0.580884</v>
-      </c>
-      <c r="G90" s="236" t="n">
-        <v>1525.3</v>
-      </c>
-      <c r="H90" s="238" t="n">
-        <v>105489748</v>
-      </c>
-      <c r="I90" s="238" t="n">
-        <v>17720</v>
-      </c>
-      <c r="J90" s="238" t="n">
-        <v>7261</v>
-      </c>
-      <c r="K90" s="238" t="n">
-        <v>4647</v>
-      </c>
-      <c r="L90" s="239" t="n">
-        <v>105519376</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="234" t="inlineStr">
-        <is>
-          <t>GPO473-3</t>
-        </is>
-      </c>
-      <c r="B91" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.10</t>
-        </is>
-      </c>
-      <c r="C91" s="235" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D91" s="236" t="n">
-        <v>49400</v>
-      </c>
-      <c r="E91" s="236" t="n">
-        <v>119060</v>
-      </c>
-      <c r="F91" s="240" t="n">
-        <v>0.414917</v>
-      </c>
-      <c r="G91" s="236" t="n">
-        <v>1525.3</v>
-      </c>
-      <c r="H91" s="238" t="n">
-        <v>75349820</v>
-      </c>
-      <c r="I91" s="238" t="n">
-        <v>12657</v>
-      </c>
-      <c r="J91" s="238" t="n">
-        <v>5186</v>
-      </c>
-      <c r="K91" s="238" t="n">
-        <v>3319</v>
-      </c>
-      <c r="L91" s="239" t="n">
-        <v>75370982</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="234" t="inlineStr">
-        <is>
-          <t>CPO696-3</t>
-        </is>
-      </c>
-      <c r="B92" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C92" s="235" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D92" s="236" t="n">
-        <v>351274</v>
-      </c>
-      <c r="E92" s="236" t="n">
-        <v>351274</v>
-      </c>
-      <c r="F92" s="240">
-        <f>IFERROR(D92/E92,0)</f>
-        <v/>
-      </c>
-      <c r="G92" s="236" t="n">
-        <v>1518</v>
-      </c>
-      <c r="H92" s="238" t="n">
-        <v>533233932</v>
-      </c>
-      <c r="I92" s="238" t="n">
-        <v>30360</v>
-      </c>
-      <c r="J92" s="238" t="n">
-        <v>12500</v>
-      </c>
-      <c r="K92" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L92" s="239">
-        <f>H92+I92+J92+K92</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="234" t="inlineStr">
-        <is>
-          <t>APO001</t>
-        </is>
-      </c>
-      <c r="B93" s="234" t="inlineStr">
-        <is>
-          <t>2026.06.17</t>
-        </is>
-      </c>
-      <c r="C93" s="235" t="inlineStr">
-        <is>
-          <t>Appotronics</t>
-        </is>
-      </c>
-      <c r="D93" s="236" t="n">
-        <v>12400</v>
-      </c>
-      <c r="E93" s="236" t="n">
-        <v>12400</v>
-      </c>
-      <c r="F93" s="240">
-        <f>IFERROR(D93/E93,0)</f>
-        <v/>
-      </c>
-      <c r="G93" s="236" t="n">
-        <v>1517.1</v>
-      </c>
-      <c r="H93" s="238" t="n">
-        <v>18812040</v>
-      </c>
-      <c r="I93" s="238" t="n">
-        <v>30342</v>
-      </c>
-      <c r="J93" s="238" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K93" s="238" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L93" s="239">
-        <f>H93+I93+J93+K93</f>
-        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="234" t="inlineStr">
         <is>
-          <t>MPO67</t>
+          <t>GPO481</t>
         </is>
       </c>
       <c r="B94" s="234" t="inlineStr">
         <is>
-          <t>2026.06.17</t>
+          <t>2026.06.10</t>
         </is>
       </c>
       <c r="C94" s="235" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D94" s="236" t="n">
-        <v>49138.8</v>
+        <v>500</v>
       </c>
       <c r="E94" s="236" t="n">
-        <v>60726</v>
-      </c>
-      <c r="F94" s="240">
-        <f>IFERROR(D94/E94,0)</f>
-        <v/>
+        <v>119060</v>
+      </c>
+      <c r="F94" s="240" t="n">
+        <v>0.0042</v>
       </c>
       <c r="G94" s="236" t="n">
-        <v>1517.3</v>
+        <v>1525.3</v>
       </c>
       <c r="H94" s="238" t="n">
-        <v>74558330</v>
+        <v>762650</v>
       </c>
       <c r="I94" s="238" t="n">
-        <v>24555</v>
+        <v>128</v>
       </c>
       <c r="J94" s="238" t="n">
-        <v>10115</v>
+        <v>52</v>
       </c>
       <c r="K94" s="238" t="n">
-        <v>6473</v>
-      </c>
-      <c r="L94" s="239">
-        <f>H94+I94+J94+K94</f>
-        <v/>
+        <v>34</v>
+      </c>
+      <c r="L94" s="239" t="n">
+        <v>762864</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="234" t="inlineStr">
         <is>
-          <t>MPO68</t>
+          <t>GPO473-2</t>
         </is>
       </c>
       <c r="B95" s="234" t="inlineStr">
         <is>
-          <t>2026.06.17</t>
+          <t>2026.06.10</t>
         </is>
       </c>
       <c r="C95" s="235" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D95" s="236" t="n">
-        <v>11587.2</v>
+        <v>69160</v>
       </c>
       <c r="E95" s="236" t="n">
-        <v>60726</v>
-      </c>
-      <c r="F95" s="240">
-        <f>IFERROR(D95/E95,0)</f>
-        <v/>
+        <v>119060</v>
+      </c>
+      <c r="F95" s="240" t="n">
+        <v>0.580884</v>
       </c>
       <c r="G95" s="236" t="n">
-        <v>1517.3</v>
+        <v>1525.3</v>
       </c>
       <c r="H95" s="238" t="n">
-        <v>17582284</v>
+        <v>105489748</v>
       </c>
       <c r="I95" s="238" t="n">
-        <v>5791</v>
+        <v>17720</v>
       </c>
       <c r="J95" s="238" t="n">
-        <v>2385</v>
+        <v>7261</v>
       </c>
       <c r="K95" s="238" t="n">
-        <v>1527</v>
-      </c>
-      <c r="L95" s="239">
-        <f>H95+I95+J95+K95</f>
-        <v/>
+        <v>4647</v>
+      </c>
+      <c r="L95" s="239" t="n">
+        <v>105519376</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="234" t="inlineStr">
         <is>
-          <t>GPO475</t>
+          <t>GPO473-3</t>
         </is>
       </c>
       <c r="B96" s="234" t="inlineStr">
         <is>
-          <t>2026.06.17</t>
+          <t>2026.06.10</t>
         </is>
       </c>
       <c r="C96" s="235" t="inlineStr">
@@ -19851,39 +20154,37 @@
         </is>
       </c>
       <c r="D96" s="236" t="n">
-        <v>540</v>
+        <v>49400</v>
       </c>
       <c r="E96" s="236" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F96" s="240">
-        <f>IFERROR(D96/E96,0)</f>
-        <v/>
+        <v>119060</v>
+      </c>
+      <c r="F96" s="240" t="n">
+        <v>0.414917</v>
       </c>
       <c r="G96" s="236" t="n">
-        <v>1516.8</v>
+        <v>1525.3</v>
       </c>
       <c r="H96" s="238" t="n">
-        <v>819072</v>
+        <v>75349820</v>
       </c>
       <c r="I96" s="238" t="n">
-        <v>8030</v>
+        <v>12657</v>
       </c>
       <c r="J96" s="238" t="n">
-        <v>1985</v>
+        <v>5186</v>
       </c>
       <c r="K96" s="238" t="n">
-        <v>2118</v>
-      </c>
-      <c r="L96" s="239">
-        <f>H96+I96+J96+K96</f>
-        <v/>
+        <v>3319</v>
+      </c>
+      <c r="L96" s="239" t="n">
+        <v>75370982</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="234" t="inlineStr">
         <is>
-          <t>GPO475-수리</t>
+          <t>CPO696-3</t>
         </is>
       </c>
       <c r="B97" s="234" t="inlineStr">
@@ -19893,42 +20194,502 @@
       </c>
       <c r="C97" s="235" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D97" s="236" t="n">
-        <v>1500</v>
+        <v>351274</v>
       </c>
       <c r="E97" s="236" t="n">
-        <v>2040</v>
+        <v>351274</v>
       </c>
       <c r="F97" s="240">
         <f>IFERROR(D97/E97,0)</f>
         <v/>
       </c>
       <c r="G97" s="236" t="n">
-        <v>1516.8</v>
+        <v>1518</v>
       </c>
       <c r="H97" s="238" t="n">
-        <v>2275200</v>
+        <v>533233932</v>
       </c>
       <c r="I97" s="238" t="n">
-        <v>22306</v>
+        <v>30360</v>
       </c>
       <c r="J97" s="238" t="n">
-        <v>5515</v>
+        <v>12500</v>
       </c>
       <c r="K97" s="238" t="n">
-        <v>5882</v>
+        <v>8000</v>
       </c>
       <c r="L97" s="239">
         <f>H97+I97+J97+K97</f>
         <v/>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="234" t="inlineStr">
+        <is>
+          <t>APO001</t>
+        </is>
+      </c>
+      <c r="B98" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C98" s="235" t="inlineStr">
+        <is>
+          <t>Appotronics</t>
+        </is>
+      </c>
+      <c r="D98" s="236" t="n">
+        <v>12400</v>
+      </c>
+      <c r="E98" s="236" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F98" s="240">
+        <f>IFERROR(D98/E98,0)</f>
+        <v/>
+      </c>
+      <c r="G98" s="236" t="n">
+        <v>1517.1</v>
+      </c>
+      <c r="H98" s="238" t="n">
+        <v>18812040</v>
+      </c>
+      <c r="I98" s="238" t="n">
+        <v>30342</v>
+      </c>
+      <c r="J98" s="238" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K98" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L98" s="239">
+        <f>H98+I98+J98+K98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="234" t="inlineStr">
+        <is>
+          <t>MPO67</t>
+        </is>
+      </c>
+      <c r="B99" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C99" s="235" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D99" s="236" t="n">
+        <v>49138.8</v>
+      </c>
+      <c r="E99" s="236" t="n">
+        <v>60726</v>
+      </c>
+      <c r="F99" s="240">
+        <f>IFERROR(D99/E99,0)</f>
+        <v/>
+      </c>
+      <c r="G99" s="236" t="n">
+        <v>1517.3</v>
+      </c>
+      <c r="H99" s="238" t="n">
+        <v>74558330</v>
+      </c>
+      <c r="I99" s="238" t="n">
+        <v>24555</v>
+      </c>
+      <c r="J99" s="238" t="n">
+        <v>10115</v>
+      </c>
+      <c r="K99" s="238" t="n">
+        <v>6473</v>
+      </c>
+      <c r="L99" s="239">
+        <f>H99+I99+J99+K99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="234" t="inlineStr">
+        <is>
+          <t>MPO68</t>
+        </is>
+      </c>
+      <c r="B100" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C100" s="235" t="inlineStr">
+        <is>
+          <t>MAG</t>
+        </is>
+      </c>
+      <c r="D100" s="236" t="n">
+        <v>11587.2</v>
+      </c>
+      <c r="E100" s="236" t="n">
+        <v>60726</v>
+      </c>
+      <c r="F100" s="240">
+        <f>IFERROR(D100/E100,0)</f>
+        <v/>
+      </c>
+      <c r="G100" s="236" t="n">
+        <v>1517.3</v>
+      </c>
+      <c r="H100" s="238" t="n">
+        <v>17582284</v>
+      </c>
+      <c r="I100" s="238" t="n">
+        <v>5791</v>
+      </c>
+      <c r="J100" s="238" t="n">
+        <v>2385</v>
+      </c>
+      <c r="K100" s="238" t="n">
+        <v>1527</v>
+      </c>
+      <c r="L100" s="239">
+        <f>H100+I100+J100+K100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="234" t="inlineStr">
+        <is>
+          <t>GPO475</t>
+        </is>
+      </c>
+      <c r="B101" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C101" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D101" s="236" t="n">
+        <v>540</v>
+      </c>
+      <c r="E101" s="236" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F101" s="240">
+        <f>IFERROR(D101/E101,0)</f>
+        <v/>
+      </c>
+      <c r="G101" s="236" t="n">
+        <v>1516.8</v>
+      </c>
+      <c r="H101" s="238" t="n">
+        <v>819072</v>
+      </c>
+      <c r="I101" s="238" t="n">
+        <v>8030</v>
+      </c>
+      <c r="J101" s="238" t="n">
+        <v>1985</v>
+      </c>
+      <c r="K101" s="238" t="n">
+        <v>2118</v>
+      </c>
+      <c r="L101" s="239">
+        <f>H101+I101+J101+K101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="234" t="inlineStr">
+        <is>
+          <t>GPO475-수리</t>
+        </is>
+      </c>
+      <c r="B102" s="234" t="inlineStr">
+        <is>
+          <t>2026.06.17</t>
+        </is>
+      </c>
+      <c r="C102" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D102" s="236" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E102" s="236" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F102" s="240">
+        <f>IFERROR(D102/E102,0)</f>
+        <v/>
+      </c>
+      <c r="G102" s="236" t="n">
+        <v>1516.8</v>
+      </c>
+      <c r="H102" s="238" t="n">
+        <v>2275200</v>
+      </c>
+      <c r="I102" s="238" t="n">
+        <v>22306</v>
+      </c>
+      <c r="J102" s="238" t="n">
+        <v>5515</v>
+      </c>
+      <c r="K102" s="238" t="n">
+        <v>5882</v>
+      </c>
+      <c r="L102" s="239">
+        <f>H102+I102+J102+K102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="234" t="inlineStr">
+        <is>
+          <t>PI44133-2</t>
+        </is>
+      </c>
+      <c r="B103" s="234" t="inlineStr">
+        <is>
+          <t>2026.07.14</t>
+        </is>
+      </c>
+      <c r="C103" s="235" t="inlineStr">
+        <is>
+          <t>Ferco (Figueras)</t>
+        </is>
+      </c>
+      <c r="D103" s="236" t="n">
+        <v>13248</v>
+      </c>
+      <c r="E103" s="236" t="n">
+        <v>13248</v>
+      </c>
+      <c r="F103" s="240">
+        <f>IFERROR(D103/E103,0)</f>
+        <v/>
+      </c>
+      <c r="G103" s="236" t="n">
+        <v>1701.72</v>
+      </c>
+      <c r="H103" s="238" t="n">
+        <v>22544387</v>
+      </c>
+      <c r="I103" s="238" t="n">
+        <v>42543</v>
+      </c>
+      <c r="J103" s="238" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K103" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L103" s="239">
+        <f>H103+I103+J103+K103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="234" t="inlineStr">
+        <is>
+          <t>GPO488</t>
+        </is>
+      </c>
+      <c r="B104" s="234" t="inlineStr">
+        <is>
+          <t>2026.08.04</t>
+        </is>
+      </c>
+      <c r="C104" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D104" s="236" t="n">
+        <v>180</v>
+      </c>
+      <c r="E104" s="236" t="n">
+        <v>180</v>
+      </c>
+      <c r="F104" s="240">
+        <f>IFERROR(D104/E104,0)</f>
+        <v/>
+      </c>
+      <c r="G104" s="236" t="n">
+        <v>1432.9</v>
+      </c>
+      <c r="H104" s="238" t="n">
+        <v>257922</v>
+      </c>
+      <c r="I104" s="238" t="n">
+        <v>28658</v>
+      </c>
+      <c r="J104" s="238" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K104" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L104" s="239">
+        <f>H104+I104+J104+K104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="234" t="inlineStr">
+        <is>
+          <t>CPO700</t>
+        </is>
+      </c>
+      <c r="B105" s="234" t="inlineStr">
+        <is>
+          <t>2026.08.07</t>
+        </is>
+      </c>
+      <c r="C105" s="235" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D105" s="236" t="n">
+        <v>1114</v>
+      </c>
+      <c r="E105" s="236" t="n">
+        <v>33829</v>
+      </c>
+      <c r="F105" s="240">
+        <f>IFERROR(D105/E105,0)</f>
+        <v/>
+      </c>
+      <c r="G105" s="236" t="n">
+        <v>1429.8</v>
+      </c>
+      <c r="H105" s="238" t="n">
+        <v>1592797</v>
+      </c>
+      <c r="I105" s="238" t="n">
+        <v>942</v>
+      </c>
+      <c r="J105" s="238" t="n">
+        <v>412</v>
+      </c>
+      <c r="K105" s="238" t="n">
+        <v>263</v>
+      </c>
+      <c r="L105" s="239">
+        <f>H105+I105+J105+K105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="234" t="inlineStr">
+        <is>
+          <t>CPO702</t>
+        </is>
+      </c>
+      <c r="B106" s="234" t="inlineStr">
+        <is>
+          <t>2026.08.07</t>
+        </is>
+      </c>
+      <c r="C106" s="235" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D106" s="236" t="n">
+        <v>32715</v>
+      </c>
+      <c r="E106" s="236" t="n">
+        <v>33829</v>
+      </c>
+      <c r="F106" s="240">
+        <f>IFERROR(D106/E106,0)</f>
+        <v/>
+      </c>
+      <c r="G106" s="236" t="n">
+        <v>1429.8</v>
+      </c>
+      <c r="H106" s="238" t="n">
+        <v>46775907</v>
+      </c>
+      <c r="I106" s="238" t="n">
+        <v>27654</v>
+      </c>
+      <c r="J106" s="238" t="n">
+        <v>12088</v>
+      </c>
+      <c r="K106" s="238" t="n">
+        <v>7737</v>
+      </c>
+      <c r="L106" s="239">
+        <f>H106+I106+J106+K106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="234" t="inlineStr">
+        <is>
+          <t>GPO493</t>
+        </is>
+      </c>
+      <c r="B107" s="234" t="inlineStr">
+        <is>
+          <t>2026.08.11</t>
+        </is>
+      </c>
+      <c r="C107" s="235" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D107" s="236" t="n">
+        <v>4470</v>
+      </c>
+      <c r="E107" s="236" t="n">
+        <v>4470</v>
+      </c>
+      <c r="F107" s="240">
+        <f>IFERROR(D107/E107,0)</f>
+        <v/>
+      </c>
+      <c r="G107" s="236" t="n">
+        <v>1419.3</v>
+      </c>
+      <c r="H107" s="238" t="n">
+        <v>6344271</v>
+      </c>
+      <c r="I107" s="238" t="n">
+        <v>28386</v>
+      </c>
+      <c r="J107" s="238" t="n">
+        <v>7500</v>
+      </c>
+      <c r="K107" s="238" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L107" s="239">
+        <f>H107+I107+J107+K107</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A45:L45"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -19988,7 +20749,7 @@
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="163" t="inlineStr">
         <is>
-          <t>기준일: 2026-06-16  |  상환 완료 건은 초록색 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
+          <t>기준일: 2026-08-14  |  상환 완료 건은 초록색 표시  |  상환예정일 = 신한은행 PDF 만기일 기준</t>
         </is>
       </c>
     </row>
@@ -22796,7 +23557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -22839,7 +23600,7 @@
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="205" t="inlineStr">
         <is>
-          <t>업데이트: 2026-08-04 (관세청 고시환율)</t>
+          <t>업데이트: 2026-08-14 (관세청 고시환율)</t>
         </is>
       </c>
       <c r="B4" s="148" t="n"/>
@@ -23571,6 +24332,22 @@
       </c>
       <c r="D50" s="211" t="n">
         <v>1457.82</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="282" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B51" s="282" t="n">
+        <v>46249</v>
+      </c>
+      <c r="C51" s="207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D51" s="211" t="n">
+        <v>1427.06</v>
       </c>
     </row>
   </sheetData>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -5914,7 +5914,7 @@
         <v>75349820</v>
       </c>
       <c r="L34" s="213" t="n">
-        <v>5186</v>
+        <v>5187</v>
       </c>
       <c r="M34" s="213" t="n">
         <v>3319</v>
@@ -6591,10 +6591,10 @@
         <v>1517.3</v>
       </c>
       <c r="J40" s="128" t="n">
-        <v>74558330</v>
+        <v>74558301</v>
       </c>
       <c r="K40" s="128" t="n">
-        <v>74558330</v>
+        <v>74558301</v>
       </c>
       <c r="L40" s="128" t="n">
         <v>10115</v>
@@ -6706,10 +6706,10 @@
         <v>1517.3</v>
       </c>
       <c r="J41" s="128" t="n">
-        <v>17582284</v>
+        <v>17581259</v>
       </c>
       <c r="K41" s="128" t="n">
-        <v>17582284</v>
+        <v>17581259</v>
       </c>
       <c r="L41" s="128" t="n">
         <v>2385</v>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y44" s="128" t="n">
-        <v>593662</v>
+        <v>593664</v>
       </c>
       <c r="Z44" s="128">
         <f>S44+W44</f>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="Y55" s="128" t="n">
-        <v>45948</v>
+        <v>45946</v>
       </c>
       <c r="Z55" s="128">
         <f>S55+W55</f>
@@ -8626,15 +8626,11 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="AE56" s="299" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AF56" s="298" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
+      <c r="AE56" s="299" t="n">
+        <v>45913</v>
+      </c>
+      <c r="AF56" s="298" t="n">
+        <v>46262</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
@@ -8751,15 +8747,11 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE57" s="299" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AF57" s="298" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
+      <c r="AE57" s="299" t="n">
+        <v>45992</v>
+      </c>
+      <c r="AF57" s="298" t="n">
+        <v>46356</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
@@ -8876,15 +8868,11 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="AE58" s="299" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AF58" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-21</t>
-        </is>
+      <c r="AE58" s="299" t="n">
+        <v>46013</v>
+      </c>
+      <c r="AF58" s="298" t="n">
+        <v>46377</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
@@ -9001,15 +8989,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE59" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF59" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="AE59" s="299" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AF59" s="298" t="n">
+        <v>46387</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -9126,15 +9110,11 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="AE60" s="299" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AF60" s="298" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
+      <c r="AE60" s="299" t="n">
+        <v>45962</v>
+      </c>
+      <c r="AF60" s="298" t="n">
+        <v>46325</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
@@ -9251,15 +9231,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE61" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF61" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="AE61" s="299" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AF61" s="298" t="n">
+        <v>46387</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
@@ -9382,15 +9358,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE62" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF62" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="AE62" s="299" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AF62" s="298" t="n">
+        <v>46387</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -9507,15 +9479,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE63" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AF63" s="298" t="inlineStr">
-        <is>
-          <t>2027-01-29</t>
-        </is>
+      <c r="AE63" s="299" t="n">
+        <v>46052</v>
+      </c>
+      <c r="AF63" s="298" t="n">
+        <v>46416</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
@@ -9763,15 +9731,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE65" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF65" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="AE65" s="299" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AF65" s="298" t="n">
+        <v>46387</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
@@ -9888,15 +9852,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE66" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF66" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="AE66" s="299" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AF66" s="298" t="n">
+        <v>46387</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
@@ -10013,15 +9973,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE67" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF67" s="298" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
+      <c r="AE67" s="299" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AF67" s="298" t="n">
+        <v>46387</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
@@ -10138,15 +10094,11 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE68" s="299" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AF68" s="298" t="inlineStr">
-        <is>
-          <t>2027-02-28</t>
-        </is>
+      <c r="AE68" s="299" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AF68" s="298" t="n">
+        <v>46446</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
@@ -10263,15 +10215,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE69" s="299" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="AF69" s="298" t="inlineStr">
-        <is>
-          <t>2027-02-22</t>
-        </is>
+      <c r="AE69" s="299" t="n">
+        <v>46023</v>
+      </c>
+      <c r="AF69" s="298" t="n">
+        <v>46440</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -10388,15 +10336,11 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="AE70" s="299" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AF70" s="298" t="inlineStr">
-        <is>
-          <t>2027-02-28</t>
-        </is>
+      <c r="AE70" s="299" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AF70" s="298" t="n">
+        <v>46446</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
@@ -10442,10 +10386,10 @@
         <v>753200</v>
       </c>
       <c r="L71" s="302" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="M71" s="302" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N71" s="296" t="inlineStr">
         <is>
@@ -10638,15 +10582,11 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE72" s="299" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AF72" s="298" t="inlineStr">
-        <is>
-          <t>2027-03-31</t>
-        </is>
+      <c r="AE72" s="299" t="n">
+        <v>46113</v>
+      </c>
+      <c r="AF72" s="298" t="n">
+        <v>46477</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
@@ -11101,7 +11041,7 @@
       </c>
       <c r="AD76" s="304" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="AE76" s="305" t="n">
@@ -13154,14 +13094,6 @@
     <row r="102">
       <c r="M102" s="40" t="n"/>
     </row>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A93:G93"/>
@@ -13363,7 +13295,7 @@
         <v>45982</v>
       </c>
       <c r="H4" s="184" t="n">
-        <v>46014</v>
+        <v>46020</v>
       </c>
       <c r="I4" s="184" t="n">
         <v>45992</v>
@@ -14718,43 +14650,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
     <row r="70">
       <c r="M70" s="40" t="n"/>
     </row>
@@ -17116,22 +17011,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
     <row r="71">
       <c r="M71" s="40" t="n"/>
     </row>
@@ -17151,7 +17030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="12.83203125" customWidth="1" style="160" min="1" max="1"/>
@@ -19450,17 +19329,17 @@
           <t>② PO별 비용 안분 내역</t>
         </is>
       </c>
-      <c r="B50" s="333" t="n"/>
-      <c r="C50" s="333" t="n"/>
-      <c r="D50" s="333" t="n"/>
-      <c r="E50" s="333" t="n"/>
-      <c r="F50" s="333" t="n"/>
-      <c r="G50" s="333" t="n"/>
-      <c r="H50" s="333" t="n"/>
-      <c r="I50" s="333" t="n"/>
-      <c r="J50" s="333" t="n"/>
-      <c r="K50" s="333" t="n"/>
-      <c r="L50" s="333" t="n"/>
+      <c r="B50" s="148" t="n"/>
+      <c r="C50" s="148" t="n"/>
+      <c r="D50" s="148" t="n"/>
+      <c r="E50" s="148" t="n"/>
+      <c r="F50" s="148" t="n"/>
+      <c r="G50" s="148" t="n"/>
+      <c r="H50" s="148" t="n"/>
+      <c r="I50" s="148" t="n"/>
+      <c r="J50" s="148" t="n"/>
+      <c r="K50" s="148" t="n"/>
+      <c r="L50" s="149" t="n"/>
       <c r="M50" s="228" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -20831,10 +20710,10 @@
         <v>2299</v>
       </c>
       <c r="J79" s="238" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="K79" s="238" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L79" s="239">
         <f>H79+I79+J79+K79</f>
@@ -21865,7 +21744,7 @@
         <v>12657</v>
       </c>
       <c r="J101" s="238" t="n">
-        <v>5186</v>
+        <v>5187</v>
       </c>
       <c r="K101" s="238" t="n">
         <v>3319</v>
@@ -22000,7 +21879,7 @@
         <v>1517.3</v>
       </c>
       <c r="H104" s="238" t="n">
-        <v>74558330</v>
+        <v>74558301</v>
       </c>
       <c r="I104" s="238" t="n">
         <v>24555</v>
@@ -22047,7 +21926,7 @@
         <v>1517.3</v>
       </c>
       <c r="H105" s="238" t="n">
-        <v>17582284</v>
+        <v>17581259</v>
       </c>
       <c r="I105" s="238" t="n">
         <v>5791</v>
@@ -22761,17 +22640,6 @@
         <v/>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A50:L50"/>
